--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
@@ -739,10 +739,10 @@
         <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.65579999999</v>
+        <v>74676.65634615401</v>
       </c>
       <c r="O8" t="n">
-        <v>1045473.1812</v>
+        <v>1045473.188846156</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -985,28 +985,28 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.303568532</v>
+        <v>1811.3034121753</v>
       </c>
       <c r="O14" t="n">
-        <v>753502.284509312</v>
+        <v>760747.4331136261</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>1081600</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="15">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.746528748</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.773279546</v>
+        <v>3866374.77541646</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2110,19 +2110,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N41" t="n">
-        <v>15970.739125</v>
+        <v>15970.739135802</v>
       </c>
       <c r="O41" t="n">
-        <v>798536.95625</v>
+        <v>814507.695925902</v>
       </c>
       <c r="P41" t="n">
         <v>26900</v>
       </c>
       <c r="Q41" t="n">
-        <v>1345000</v>
+        <v>1371900</v>
       </c>
     </row>
     <row r="42">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2752,19 +2752,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N57" t="n">
         <v>3585</v>
       </c>
       <c r="O57" t="n">
-        <v>319065</v>
+        <v>329820</v>
       </c>
       <c r="P57" t="n">
         <v>4500</v>
       </c>
       <c r="Q57" t="n">
-        <v>400500</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="58">
@@ -2782,28 +2782,28 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8539724138</v>
+        <v>6272.8539614856</v>
       </c>
       <c r="O58" t="n">
-        <v>771561.0386068973</v>
+        <v>784106.7451857</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>971700</v>
+        <v>987500</v>
       </c>
     </row>
     <row r="59">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2835,19 +2835,19 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>127174.84</v>
+        <v>156522.88</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>239200</v>
+        <v>294400</v>
       </c>
     </row>
     <row r="60">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2955,19 +2955,19 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N62" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371399387</v>
       </c>
       <c r="O62" t="n">
-        <v>129585.6254731467</v>
+        <v>141366.1370377932</v>
       </c>
       <c r="P62" t="n">
         <v>4800</v>
       </c>
       <c r="Q62" t="n">
-        <v>158400</v>
+        <v>172800</v>
       </c>
     </row>
     <row r="63">
@@ -3242,10 +3242,10 @@
         <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>12793.680086207</v>
+        <v>12793.680085837</v>
       </c>
       <c r="O69" t="n">
-        <v>63968.400431035</v>
+        <v>63968.400429185</v>
       </c>
       <c r="P69" t="n">
         <v>24000</v>
@@ -3632,10 +3632,10 @@
         <v>77</v>
       </c>
       <c r="N79" t="n">
-        <v>14857.62306383</v>
+        <v>14857.623050847</v>
       </c>
       <c r="O79" t="n">
-        <v>1144036.97591491</v>
+        <v>1144036.974915219</v>
       </c>
       <c r="P79" t="n">
         <v>34900</v>
@@ -3765,10 +3765,10 @@
         <v>5</v>
       </c>
       <c r="N82" t="n">
-        <v>26465.343333333</v>
+        <v>26465.341428571</v>
       </c>
       <c r="O82" t="n">
-        <v>132326.716666665</v>
+        <v>132326.707142855</v>
       </c>
       <c r="P82" t="n">
         <v>42900</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3925,19 +3925,19 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N86" t="n">
         <v>1800</v>
       </c>
       <c r="O86" t="n">
-        <v>41400</v>
+        <v>43200</v>
       </c>
       <c r="P86" t="n">
         <v>2200</v>
       </c>
       <c r="Q86" t="n">
-        <v>50600</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="87">
@@ -4098,10 +4098,10 @@
         <v>19</v>
       </c>
       <c r="N90" t="n">
-        <v>3910.628317757</v>
+        <v>3910.6283208955</v>
       </c>
       <c r="O90" t="n">
-        <v>74301.93803738299</v>
+        <v>74301.9380970145</v>
       </c>
       <c r="P90" t="n">
         <v>9100</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4919,19 +4919,19 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
-        <v>30708.904814815</v>
+        <v>30708.906428571</v>
       </c>
       <c r="O108" t="n">
-        <v>122835.61925926</v>
+        <v>153544.532142855</v>
       </c>
       <c r="P108" t="n">
         <v>53500</v>
       </c>
       <c r="Q108" t="n">
-        <v>214000</v>
+        <v>267500</v>
       </c>
     </row>
     <row r="109">
@@ -5048,10 +5048,10 @@
         <v>6</v>
       </c>
       <c r="N111" t="n">
-        <v>17085.656666667</v>
+        <v>17085.657567568</v>
       </c>
       <c r="O111" t="n">
-        <v>102513.940000002</v>
+        <v>102513.945405408</v>
       </c>
       <c r="P111" t="n">
         <v>29200</v>
@@ -5137,10 +5137,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>16486.41027027</v>
+        <v>16486.4104</v>
       </c>
       <c r="O113" t="n">
-        <v>16486.41027027</v>
+        <v>16486.4104</v>
       </c>
       <c r="P113" t="n">
         <v>30500</v>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5215,19 +5215,19 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966494465</v>
       </c>
       <c r="O115" t="n">
-        <v>329951.295280908</v>
+        <v>345663.26287823</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
       </c>
       <c r="Q115" t="n">
-        <v>598500</v>
+        <v>627000</v>
       </c>
     </row>
     <row r="116">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5429,19 +5429,19 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N120" t="n">
-        <v>7407.730052356</v>
+        <v>7407.7300522193</v>
       </c>
       <c r="O120" t="n">
-        <v>1096344.047748688</v>
+        <v>1103751.777780676</v>
       </c>
       <c r="P120" t="n">
         <v>10900</v>
       </c>
       <c r="Q120" t="n">
-        <v>1613200</v>
+        <v>1624100</v>
       </c>
     </row>
     <row r="121">
@@ -6200,10 +6200,10 @@
         <v>6</v>
       </c>
       <c r="N139" t="n">
-        <v>36574.852</v>
+        <v>36574.851914894</v>
       </c>
       <c r="O139" t="n">
-        <v>219449.112</v>
+        <v>219449.111489364</v>
       </c>
       <c r="P139" t="n">
         <v>65900</v>
@@ -6416,10 +6416,10 @@
         <v>8</v>
       </c>
       <c r="N144" t="n">
-        <v>36306.262857143</v>
+        <v>36306.261724138</v>
       </c>
       <c r="O144" t="n">
-        <v>290450.102857144</v>
+        <v>290450.093793104</v>
       </c>
       <c r="P144" t="n">
         <v>64900</v>
@@ -6510,10 +6510,10 @@
         <v>11</v>
       </c>
       <c r="N146" t="n">
-        <v>62349.661025641</v>
+        <v>62349.66195122</v>
       </c>
       <c r="O146" t="n">
-        <v>685846.271282051</v>
+        <v>685846.28146342</v>
       </c>
       <c r="P146" t="n">
         <v>109900</v>
@@ -6557,10 +6557,10 @@
         <v>17</v>
       </c>
       <c r="N147" t="n">
-        <v>141416.88438871</v>
+        <v>141416.88436137</v>
       </c>
       <c r="O147" t="n">
-        <v>2404087.03460807</v>
+        <v>2404087.03414329</v>
       </c>
       <c r="P147" t="n">
         <v>251900</v>
@@ -6599,10 +6599,10 @@
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19865772</v>
       </c>
       <c r="O148" t="n">
-        <v>400144.39767124</v>
+        <v>400144.39731544</v>
       </c>
       <c r="P148" t="n">
         <v>312000</v>
@@ -6779,10 +6779,10 @@
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>344599.17885246</v>
+        <v>344599.17888889</v>
       </c>
       <c r="O152" t="n">
-        <v>344599.17885246</v>
+        <v>344599.17888889</v>
       </c>
       <c r="P152" t="n">
         <v>532900</v>
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -7735,19 +7735,19 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N175" t="n">
         <v>8500</v>
       </c>
       <c r="O175" t="n">
-        <v>34000</v>
+        <v>42500</v>
       </c>
       <c r="P175" t="n">
         <v>10200</v>
       </c>
       <c r="Q175" t="n">
-        <v>40800</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="176">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8075,19 +8075,19 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N183" t="n">
         <v>2572.67</v>
       </c>
       <c r="O183" t="n">
-        <v>519679.34</v>
+        <v>522252.01</v>
       </c>
       <c r="P183" t="n">
         <v>4700</v>
       </c>
       <c r="Q183" t="n">
-        <v>949400</v>
+        <v>954100</v>
       </c>
     </row>
     <row r="184">
@@ -8216,10 +8216,10 @@
         <v>74</v>
       </c>
       <c r="N186" t="n">
-        <v>6303.1779439252</v>
+        <v>6303.178</v>
       </c>
       <c r="O186" t="n">
-        <v>466435.1678504648</v>
+        <v>466435.172</v>
       </c>
       <c r="P186" t="n">
         <v>13500</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8305,19 +8305,19 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N188" t="n">
         <v>2570.16</v>
       </c>
       <c r="O188" t="n">
-        <v>447207.84</v>
+        <v>449778</v>
       </c>
       <c r="P188" t="n">
         <v>4700</v>
       </c>
       <c r="Q188" t="n">
-        <v>817800</v>
+        <v>822500</v>
       </c>
     </row>
     <row r="189">
@@ -8393,10 +8393,10 @@
         <v>44</v>
       </c>
       <c r="N190" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2851851852</v>
       </c>
       <c r="O190" t="n">
-        <v>214644.5518279568</v>
+        <v>214644.5481481488</v>
       </c>
       <c r="P190" t="n">
         <v>13500</v>
@@ -8434,10 +8434,10 @@
         <v>115</v>
       </c>
       <c r="N191" t="n">
-        <v>7394.9353846154</v>
+        <v>7394.9353551913</v>
       </c>
       <c r="O191" t="n">
-        <v>850417.569230771</v>
+        <v>850417.5658469995</v>
       </c>
       <c r="P191" t="n">
         <v>17900</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9013,19 +9013,19 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N205" t="n">
-        <v>4333.604375</v>
+        <v>4333.6041176471</v>
       </c>
       <c r="O205" t="n">
-        <v>21668.021875</v>
+        <v>26001.6247058826</v>
       </c>
       <c r="P205" t="n">
         <v>7500</v>
       </c>
       <c r="Q205" t="n">
-        <v>37500</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="206">
@@ -9223,22 +9223,22 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
         <v>27</v>
       </c>
       <c r="N210" t="n">
-        <v>3340.6800775194</v>
+        <v>3340.6800773694</v>
       </c>
       <c r="O210" t="n">
-        <v>90198.36209302381</v>
+        <v>90198.36208897379</v>
       </c>
       <c r="P210" t="n">
         <v>7100</v>
@@ -9662,10 +9662,10 @@
         <v>53</v>
       </c>
       <c r="N220" t="n">
-        <v>732.63410958904</v>
+        <v>732.63409556314</v>
       </c>
       <c r="O220" t="n">
-        <v>38829.60780821912</v>
+        <v>38829.60706484642</v>
       </c>
       <c r="P220" t="n">
         <v>6200</v>
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -9971,19 +9971,19 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="N227" t="n">
         <v>2833</v>
       </c>
       <c r="O227" t="n">
-        <v>1830118</v>
+        <v>1841450</v>
       </c>
       <c r="P227" t="n">
         <v>3500</v>
       </c>
       <c r="Q227" t="n">
-        <v>2261000</v>
+        <v>2275000</v>
       </c>
     </row>
     <row r="228">
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>9532</v>
+        <v>9610</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10053,19 +10053,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>9532</v>
+        <v>9610</v>
       </c>
       <c r="N229" t="n">
         <v>1726.32</v>
       </c>
       <c r="O229" t="n">
-        <v>16455282.24</v>
+        <v>16589935.2</v>
       </c>
       <c r="P229" t="n">
         <v>1500</v>
       </c>
       <c r="Q229" t="n">
-        <v>14298000</v>
+        <v>14415000</v>
       </c>
     </row>
     <row r="230">
@@ -10131,7 +10131,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10140,19 +10140,19 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="N231" t="n">
-        <v>4937.3101589595</v>
+        <v>4937.3101582734</v>
       </c>
       <c r="O231" t="n">
-        <v>1140518.646719645</v>
+        <v>1170142.507510796</v>
       </c>
       <c r="P231" t="n">
         <v>7500</v>
       </c>
       <c r="Q231" t="n">
-        <v>1732500</v>
+        <v>1777500</v>
       </c>
     </row>
     <row r="232">
@@ -10595,28 +10595,28 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1425</v>
+        <v>1590</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M242" t="n">
-        <v>1425</v>
+        <v>1574</v>
       </c>
       <c r="N242" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0510925004</v>
       </c>
       <c r="O242" t="n">
-        <v>1564723.706818132</v>
+        <v>1728332.41959563</v>
       </c>
       <c r="P242" t="n">
         <v>1500</v>
       </c>
       <c r="Q242" t="n">
-        <v>2137500</v>
+        <v>2361000</v>
       </c>
     </row>
     <row r="243">
@@ -10928,13 +10928,13 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M250" t="n">
         <v>21</v>
@@ -11051,28 +11051,28 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M253" t="n">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N253" t="n">
         <v>1789</v>
       </c>
       <c r="O253" t="n">
-        <v>1028675</v>
+        <v>1034042</v>
       </c>
       <c r="P253" t="n">
         <v>2700</v>
       </c>
       <c r="Q253" t="n">
-        <v>1552500</v>
+        <v>1560600</v>
       </c>
     </row>
     <row r="254">
@@ -11218,28 +11218,28 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M257" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N257" t="n">
         <v>1789</v>
       </c>
       <c r="O257" t="n">
-        <v>867665</v>
+        <v>871243</v>
       </c>
       <c r="P257" t="n">
         <v>2700</v>
       </c>
       <c r="Q257" t="n">
-        <v>1309500</v>
+        <v>1314900</v>
       </c>
     </row>
     <row r="258">
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11309,19 +11309,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N259" t="n">
         <v>1789</v>
       </c>
       <c r="O259" t="n">
-        <v>783582</v>
+        <v>796105</v>
       </c>
       <c r="P259" t="n">
         <v>2700</v>
       </c>
       <c r="Q259" t="n">
-        <v>1182600</v>
+        <v>1201500</v>
       </c>
     </row>
     <row r="260">
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11483,19 +11483,19 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N263" t="n">
         <v>2189</v>
       </c>
       <c r="O263" t="n">
-        <v>606353</v>
+        <v>608542</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
       </c>
       <c r="Q263" t="n">
-        <v>1246500</v>
+        <v>1251000</v>
       </c>
     </row>
     <row r="264">
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11785,19 +11785,19 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N270" t="n">
         <v>13593.35</v>
       </c>
       <c r="O270" t="n">
-        <v>4213938.5</v>
+        <v>4254718.55</v>
       </c>
       <c r="P270" t="n">
         <v>25500</v>
       </c>
       <c r="Q270" t="n">
-        <v>7905000</v>
+        <v>7981500</v>
       </c>
     </row>
     <row r="271">
@@ -12109,13 +12109,13 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M278" t="n">
         <v>59</v>
@@ -12475,28 +12475,28 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M286" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N286" t="n">
-        <v>2033.5815122873</v>
+        <v>2033.5818888889</v>
       </c>
       <c r="O286" t="n">
-        <v>368078.2537240013</v>
+        <v>374179.0675555576</v>
       </c>
       <c r="P286" t="n">
         <v>4100</v>
       </c>
       <c r="Q286" t="n">
-        <v>742100</v>
+        <v>754400</v>
       </c>
     </row>
     <row r="287">
@@ -12779,10 +12779,10 @@
         <v>2839</v>
       </c>
       <c r="N293" t="n">
-        <v>3158.8608104732</v>
+        <v>3158.8608103175</v>
       </c>
       <c r="O293" t="n">
-        <v>8968005.840933416</v>
+        <v>8968005.840491382</v>
       </c>
       <c r="P293" t="n">
         <v>5600</v>
@@ -12871,10 +12871,10 @@
         <v>235</v>
       </c>
       <c r="N295" t="n">
-        <v>3841.6246596357</v>
+        <v>3841.6246462715</v>
       </c>
       <c r="O295" t="n">
-        <v>902781.7950143896</v>
+        <v>902781.7918738024</v>
       </c>
       <c r="P295" t="n">
         <v>6900</v>
@@ -13041,22 +13041,22 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" t="n">
         <v>94</v>
       </c>
       <c r="N299" t="n">
-        <v>3230.0679765396</v>
+        <v>3230.0679854015</v>
       </c>
       <c r="O299" t="n">
-        <v>303626.3897947224</v>
+        <v>303626.390627741</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13178,19 +13178,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N302" t="n">
         <v>1480</v>
       </c>
       <c r="O302" t="n">
-        <v>446960</v>
+        <v>455840</v>
       </c>
       <c r="P302" t="n">
         <v>2600</v>
       </c>
       <c r="Q302" t="n">
-        <v>785200</v>
+        <v>800800</v>
       </c>
     </row>
     <row r="303">
@@ -13302,7 +13302,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -13311,19 +13311,19 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="N305" t="n">
         <v>2742</v>
       </c>
       <c r="O305" t="n">
-        <v>208392</v>
+        <v>230328</v>
       </c>
       <c r="P305" t="n">
         <v>3500</v>
       </c>
       <c r="Q305" t="n">
-        <v>266000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="306">
@@ -13394,7 +13394,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13403,19 +13403,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N307" t="n">
         <v>7507.39</v>
       </c>
       <c r="O307" t="n">
-        <v>2192157.88</v>
+        <v>2199665.27</v>
       </c>
       <c r="P307" t="n">
         <v>13500</v>
       </c>
       <c r="Q307" t="n">
-        <v>3942000</v>
+        <v>3955500</v>
       </c>
     </row>
     <row r="308">
@@ -13724,10 +13724,10 @@
         <v>475</v>
       </c>
       <c r="N314" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070249</v>
       </c>
       <c r="O314" t="n">
-        <v>1802962.253338585</v>
+        <v>1802962.253336828</v>
       </c>
       <c r="P314" t="n">
         <v>6200</v>
@@ -13881,28 +13881,28 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M318" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N318" t="n">
         <v>2612.77</v>
       </c>
       <c r="O318" t="n">
-        <v>1450087.35</v>
+        <v>1452700.12</v>
       </c>
       <c r="P318" t="n">
         <v>4900</v>
       </c>
       <c r="Q318" t="n">
-        <v>2719500</v>
+        <v>2724400</v>
       </c>
     </row>
     <row r="319">
@@ -14159,10 +14159,10 @@
         <v>21</v>
       </c>
       <c r="N324" t="n">
-        <v>4967.81144</v>
+        <v>4967.810952381</v>
       </c>
       <c r="O324" t="n">
-        <v>104324.04024</v>
+        <v>104324.030000001</v>
       </c>
       <c r="P324" t="n">
         <v>7500</v>
@@ -14196,28 +14196,28 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>985</v>
+        <v>1048</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M325" t="n">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="N325" t="n">
         <v>1203.38</v>
       </c>
       <c r="O325" t="n">
-        <v>1185329.3</v>
+        <v>1211803.66</v>
       </c>
       <c r="P325" t="n">
         <v>1900</v>
       </c>
       <c r="Q325" t="n">
-        <v>1871500</v>
+        <v>1913300</v>
       </c>
     </row>
     <row r="326">
@@ -14242,28 +14242,28 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M326" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N326" t="n">
         <v>3472</v>
       </c>
       <c r="O326" t="n">
-        <v>562464</v>
+        <v>565936</v>
       </c>
       <c r="P326" t="n">
         <v>4800</v>
       </c>
       <c r="Q326" t="n">
-        <v>777600</v>
+        <v>782400</v>
       </c>
     </row>
     <row r="327">
@@ -14421,28 +14421,28 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M330" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="N330" t="n">
         <v>2331</v>
       </c>
       <c r="O330" t="n">
-        <v>974358</v>
+        <v>979020</v>
       </c>
       <c r="P330" t="n">
         <v>3500</v>
       </c>
       <c r="Q330" t="n">
-        <v>1463000</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="331">
@@ -14462,13 +14462,13 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M331" t="n">
         <v>530</v>
@@ -14687,13 +14687,13 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M336" t="n">
         <v>29</v>
@@ -14728,13 +14728,13 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M337" t="n">
         <v>12</v>
@@ -14810,28 +14810,28 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M339" t="n">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="N339" t="n">
         <v>1789</v>
       </c>
       <c r="O339" t="n">
-        <v>1413310</v>
+        <v>1425833</v>
       </c>
       <c r="P339" t="n">
         <v>2700</v>
       </c>
       <c r="Q339" t="n">
-        <v>2133000</v>
+        <v>2151900</v>
       </c>
     </row>
     <row r="340">
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -14909,19 +14909,19 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N341" t="n">
-        <v>3594.2542925089</v>
+        <v>3594.2543127962</v>
       </c>
       <c r="O341" t="n">
-        <v>1322685.579643275</v>
+        <v>1326279.841421798</v>
       </c>
       <c r="P341" t="n">
         <v>6500</v>
       </c>
       <c r="Q341" t="n">
-        <v>2392000</v>
+        <v>2398500</v>
       </c>
     </row>
     <row r="342">
@@ -14949,28 +14949,28 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>1746</v>
+        <v>1836</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M342" t="n">
-        <v>1746</v>
+        <v>1762</v>
       </c>
       <c r="N342" t="n">
         <v>489.88</v>
       </c>
       <c r="O342" t="n">
-        <v>855330.48</v>
+        <v>863168.5599999999</v>
       </c>
       <c r="P342" t="n">
         <v>700</v>
       </c>
       <c r="Q342" t="n">
-        <v>1222200</v>
+        <v>1233400</v>
       </c>
     </row>
     <row r="343">
@@ -15842,7 +15842,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>2751</v>
+        <v>2765</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15851,19 +15851,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>2751</v>
+        <v>2765</v>
       </c>
       <c r="N363" t="n">
         <v>1441.01</v>
       </c>
       <c r="O363" t="n">
-        <v>3964218.51</v>
+        <v>3984392.65</v>
       </c>
       <c r="P363" t="n">
         <v>2100</v>
       </c>
       <c r="Q363" t="n">
-        <v>5777100</v>
+        <v>5806500</v>
       </c>
     </row>
     <row r="364">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16031,19 +16031,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N367" t="n">
-        <v>4242.5421445221</v>
+        <v>4242.5421395349</v>
       </c>
       <c r="O367" t="n">
-        <v>1713987.026386928</v>
+        <v>1718229.566511635</v>
       </c>
       <c r="P367" t="n">
         <v>5900</v>
       </c>
       <c r="Q367" t="n">
-        <v>2383600</v>
+        <v>2389500</v>
       </c>
     </row>
     <row r="368">
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16121,19 +16121,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="N369" t="n">
-        <v>3041.6600119048</v>
+        <v>3041.6600117855</v>
       </c>
       <c r="O369" t="n">
-        <v>590082.0423095311</v>
+        <v>641790.2624867405</v>
       </c>
       <c r="P369" t="n">
         <v>5500</v>
       </c>
       <c r="Q369" t="n">
-        <v>1067000</v>
+        <v>1160500</v>
       </c>
     </row>
     <row r="370">
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K371" t="n">
         <v>0</v>
@@ -16208,19 +16208,19 @@
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N371" t="n">
         <v>4086.2</v>
       </c>
       <c r="O371" t="n">
-        <v>1920514</v>
+        <v>1924600.2</v>
       </c>
       <c r="P371" t="n">
         <v>6900</v>
       </c>
       <c r="Q371" t="n">
-        <v>3243000</v>
+        <v>3249900</v>
       </c>
     </row>
     <row r="372">
@@ -16371,22 +16371,22 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M375" t="n">
         <v>660</v>
       </c>
       <c r="N375" t="n">
-        <v>1592.5679711276</v>
+        <v>1592.5680015373</v>
       </c>
       <c r="O375" t="n">
-        <v>1051094.860944216</v>
+        <v>1051094.881014618</v>
       </c>
       <c r="P375" t="n">
         <v>3900</v>
@@ -16540,13 +16540,13 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M379" t="n">
         <v>129</v>
@@ -16881,7 +16881,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
@@ -16890,19 +16890,19 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N387" t="n">
         <v>5633.97</v>
       </c>
       <c r="O387" t="n">
-        <v>371842.02</v>
+        <v>383109.96</v>
       </c>
       <c r="P387" t="n">
         <v>9600</v>
       </c>
       <c r="Q387" t="n">
-        <v>633600</v>
+        <v>652800</v>
       </c>
     </row>
     <row r="388">
@@ -16976,28 +16976,28 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N389" t="n">
         <v>4648.6</v>
       </c>
       <c r="O389" t="n">
-        <v>1250473.4</v>
+        <v>1264419.2</v>
       </c>
       <c r="P389" t="n">
         <v>8900</v>
       </c>
       <c r="Q389" t="n">
-        <v>2394100</v>
+        <v>2420800</v>
       </c>
     </row>
     <row r="390">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -17114,19 +17114,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="N392" t="n">
         <v>1312.43</v>
       </c>
       <c r="O392" t="n">
-        <v>1376739.07</v>
+        <v>1379363.93</v>
       </c>
       <c r="P392" t="n">
         <v>2300</v>
       </c>
       <c r="Q392" t="n">
-        <v>2412700</v>
+        <v>2417300</v>
       </c>
     </row>
     <row r="393">
@@ -17231,7 +17231,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -17240,19 +17240,19 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N395" t="n">
         <v>1343.77</v>
       </c>
       <c r="O395" t="n">
-        <v>326536.11</v>
+        <v>327879.88</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
       </c>
       <c r="Q395" t="n">
-        <v>607500</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="396">
@@ -17363,28 +17363,28 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>3124</v>
+        <v>3196</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>3124</v>
+        <v>3195</v>
       </c>
       <c r="N398" t="n">
         <v>1387.55</v>
       </c>
       <c r="O398" t="n">
-        <v>4334706.2</v>
+        <v>4433222.25</v>
       </c>
       <c r="P398" t="n">
         <v>2300</v>
       </c>
       <c r="Q398" t="n">
-        <v>7185200</v>
+        <v>7348500</v>
       </c>
     </row>
     <row r="399">
@@ -17539,13 +17539,13 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M402" t="n">
         <v>144</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
@@ -17597,19 +17597,19 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N403" t="n">
         <v>16897</v>
       </c>
       <c r="O403" t="n">
-        <v>980026</v>
+        <v>1013820</v>
       </c>
       <c r="P403" t="n">
         <v>27900</v>
       </c>
       <c r="Q403" t="n">
-        <v>1618200</v>
+        <v>1674000</v>
       </c>
     </row>
     <row r="404">
@@ -18507,28 +18507,28 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N424" t="n">
         <v>3751</v>
       </c>
       <c r="O424" t="n">
-        <v>273823</v>
+        <v>277574</v>
       </c>
       <c r="P424" t="n">
         <v>6400</v>
       </c>
       <c r="Q424" t="n">
-        <v>467200</v>
+        <v>473600</v>
       </c>
     </row>
     <row r="425">
@@ -18597,13 +18597,13 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M426" t="n">
         <v>66</v>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -18742,19 +18742,19 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>614</v>
+        <v>646</v>
       </c>
       <c r="N429" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9227791832</v>
       </c>
       <c r="O429" t="n">
-        <v>1001386.612719236</v>
+        <v>1053576.115352347</v>
       </c>
       <c r="P429" t="n">
         <v>2500</v>
       </c>
       <c r="Q429" t="n">
-        <v>1535000</v>
+        <v>1615000</v>
       </c>
     </row>
     <row r="430">
@@ -18791,10 +18791,10 @@
         <v>14</v>
       </c>
       <c r="N430" t="n">
-        <v>1467.3289090909</v>
+        <v>1467.3293594306</v>
       </c>
       <c r="O430" t="n">
-        <v>20542.6047272726</v>
+        <v>20542.6110320284</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -18825,28 +18825,28 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M431" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N431" t="n">
-        <v>1690.6051240876</v>
+        <v>1690.6056882022</v>
       </c>
       <c r="O431" t="n">
-        <v>38883.9178540148</v>
+        <v>106508.1583567386</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
       </c>
       <c r="Q431" t="n">
-        <v>66700</v>
+        <v>182700</v>
       </c>
     </row>
     <row r="432">
@@ -18871,28 +18871,28 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>1289</v>
+        <v>1396</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M432" t="n">
-        <v>1289</v>
+        <v>1366</v>
       </c>
       <c r="N432" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927149023</v>
       </c>
       <c r="O432" t="n">
-        <v>1998198.460945708</v>
+        <v>2117563.248556542</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3222500</v>
+        <v>3415000</v>
       </c>
     </row>
     <row r="433">
@@ -18963,28 +18963,28 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>959</v>
+        <v>987</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M434" t="n">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="N434" t="n">
-        <v>2403.5095333845</v>
+        <v>2403.5094737645</v>
       </c>
       <c r="O434" t="n">
-        <v>2304965.642515736</v>
+        <v>2319386.642182742</v>
       </c>
       <c r="P434" t="n">
         <v>3500</v>
       </c>
       <c r="Q434" t="n">
-        <v>3356500</v>
+        <v>3377500</v>
       </c>
     </row>
     <row r="435">
@@ -19053,28 +19053,28 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M436" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N436" t="n">
-        <v>2521.5499887387</v>
+        <v>2521.550368364</v>
       </c>
       <c r="O436" t="n">
-        <v>799331.3464301679</v>
+        <v>809417.668244844</v>
       </c>
       <c r="P436" t="n">
         <v>3900</v>
       </c>
       <c r="Q436" t="n">
-        <v>1236300</v>
+        <v>1251900</v>
       </c>
     </row>
     <row r="437">
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -19103,19 +19103,19 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N437" t="n">
-        <v>1232.8083690987</v>
+        <v>1232.8086134454</v>
       </c>
       <c r="O437" t="n">
-        <v>77666.92725321811</v>
+        <v>80132.559873951</v>
       </c>
       <c r="P437" t="n">
         <v>2400</v>
       </c>
       <c r="Q437" t="n">
-        <v>151200</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="438">
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -19401,19 +19401,19 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="N444" t="n">
-        <v>893.67886945501</v>
+        <v>893.6788774226</v>
       </c>
       <c r="O444" t="n">
-        <v>252911.1200557679</v>
+        <v>277934.1308784286</v>
       </c>
       <c r="P444" t="n">
         <v>1200</v>
       </c>
       <c r="Q444" t="n">
-        <v>339600</v>
+        <v>373200</v>
       </c>
     </row>
     <row r="445">
@@ -21106,7 +21106,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -21115,19 +21115,19 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N483" t="n">
         <v>6280.31</v>
       </c>
       <c r="O483" t="n">
-        <v>69083.41</v>
+        <v>81644.03</v>
       </c>
       <c r="P483" t="n">
         <v>10500</v>
       </c>
       <c r="Q483" t="n">
-        <v>115500</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="484">
@@ -23134,7 +23134,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -23143,19 +23143,19 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N531" t="n">
         <v>8794.48</v>
       </c>
       <c r="O531" t="n">
-        <v>2216208.96</v>
+        <v>2233797.92</v>
       </c>
       <c r="P531" t="n">
         <v>14500</v>
       </c>
       <c r="Q531" t="n">
-        <v>3654000</v>
+        <v>3683000</v>
       </c>
     </row>
     <row r="532">
@@ -23221,13 +23221,13 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M533" t="n">
         <v>387</v>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -23394,19 +23394,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N537" t="n">
         <v>13152</v>
       </c>
       <c r="O537" t="n">
-        <v>1446720</v>
+        <v>1459872</v>
       </c>
       <c r="P537" t="n">
         <v>16900</v>
       </c>
       <c r="Q537" t="n">
-        <v>1859000</v>
+        <v>1875900</v>
       </c>
     </row>
     <row r="538">
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -23435,19 +23435,19 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N538" t="n">
         <v>6652</v>
       </c>
       <c r="O538" t="n">
-        <v>4443536</v>
+        <v>4450188</v>
       </c>
       <c r="P538" t="n">
         <v>5900</v>
       </c>
       <c r="Q538" t="n">
-        <v>3941200</v>
+        <v>3947100</v>
       </c>
     </row>
     <row r="539">
@@ -23552,13 +23552,13 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M541" t="n">
         <v>86</v>
@@ -23593,13 +23593,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M542" t="n">
         <v>29</v>
@@ -23646,10 +23646,10 @@
         <v>248</v>
       </c>
       <c r="N543" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8734867503</v>
       </c>
       <c r="O543" t="n">
-        <v>503408.6251162808</v>
+        <v>503408.6247140744</v>
       </c>
       <c r="P543" t="n">
         <v>3600</v>
@@ -24167,13 +24167,13 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M556" t="n">
         <v>138</v>
@@ -24392,10 +24392,10 @@
         <v>185</v>
       </c>
       <c r="N561" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.7397015834</v>
       </c>
       <c r="O561" t="n">
-        <v>495936.8447256075</v>
+        <v>495936.844792929</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
@@ -25727,28 +25727,28 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M593" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="N593" t="n">
         <v>3877.89</v>
       </c>
       <c r="O593" t="n">
-        <v>539026.71</v>
+        <v>608828.73</v>
       </c>
       <c r="P593" t="n">
         <v>6500</v>
       </c>
       <c r="Q593" t="n">
-        <v>903500</v>
+        <v>1020500</v>
       </c>
     </row>
     <row r="594">
@@ -25829,10 +25829,10 @@
         <v>5</v>
       </c>
       <c r="N595" t="n">
-        <v>4285.1951158107</v>
+        <v>4285.1951004016</v>
       </c>
       <c r="O595" t="n">
-        <v>21425.9755790535</v>
+        <v>21425.975502008</v>
       </c>
       <c r="P595" t="n">
         <v>6900</v>
@@ -26559,10 +26559,10 @@
         <v>89</v>
       </c>
       <c r="N612" t="n">
-        <v>11562.038549223</v>
+        <v>11562.038560411</v>
       </c>
       <c r="O612" t="n">
-        <v>1029021.430880847</v>
+        <v>1029021.431876579</v>
       </c>
       <c r="P612" t="n">
         <v>18500</v>
@@ -26605,10 +26605,10 @@
         <v>2</v>
       </c>
       <c r="N613" t="n">
-        <v>13513.642887324</v>
+        <v>13513.642867133</v>
       </c>
       <c r="O613" t="n">
-        <v>27027.285774648</v>
+        <v>27027.285734266</v>
       </c>
       <c r="P613" t="n">
         <v>21900</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
@@ -26776,19 +26776,19 @@
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N617" t="n">
         <v>1650</v>
       </c>
       <c r="O617" t="n">
-        <v>660000</v>
+        <v>661650</v>
       </c>
       <c r="P617" t="n">
         <v>2900</v>
       </c>
       <c r="Q617" t="n">
-        <v>1160000</v>
+        <v>1162900</v>
       </c>
     </row>
     <row r="618">
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -26817,19 +26817,19 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N618" t="n">
         <v>2856</v>
       </c>
       <c r="O618" t="n">
-        <v>354144</v>
+        <v>368424</v>
       </c>
       <c r="P618" t="n">
         <v>2400</v>
       </c>
       <c r="Q618" t="n">
-        <v>297600</v>
+        <v>309600</v>
       </c>
     </row>
     <row r="619">
@@ -26849,28 +26849,28 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M619" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N619" t="n">
         <v>926</v>
       </c>
       <c r="O619" t="n">
-        <v>15742</v>
+        <v>22224</v>
       </c>
       <c r="P619" t="n">
         <v>1600</v>
       </c>
       <c r="Q619" t="n">
-        <v>27200</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="620">
@@ -26890,28 +26890,28 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
       </c>
       <c r="L620" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M620" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N620" t="n">
         <v>1679</v>
       </c>
       <c r="O620" t="n">
-        <v>708538</v>
+        <v>711896</v>
       </c>
       <c r="P620" t="n">
         <v>2900</v>
       </c>
       <c r="Q620" t="n">
-        <v>1223800</v>
+        <v>1229600</v>
       </c>
     </row>
     <row r="621">
@@ -26972,28 +26972,28 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M622" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N622" t="n">
         <v>889</v>
       </c>
       <c r="O622" t="n">
-        <v>39116</v>
+        <v>42672</v>
       </c>
       <c r="P622" t="n">
         <v>1500</v>
       </c>
       <c r="Q622" t="n">
-        <v>66000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="623">
@@ -27013,28 +27013,28 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
       </c>
       <c r="L623" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M623" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N623" t="n">
         <v>1664</v>
       </c>
       <c r="O623" t="n">
-        <v>758784</v>
+        <v>765440</v>
       </c>
       <c r="P623" t="n">
         <v>2900</v>
       </c>
       <c r="Q623" t="n">
-        <v>1322400</v>
+        <v>1334000</v>
       </c>
     </row>
     <row r="624">
@@ -27054,28 +27054,28 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M624" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N624" t="n">
         <v>1358</v>
       </c>
       <c r="O624" t="n">
-        <v>351722</v>
+        <v>354438</v>
       </c>
       <c r="P624" t="n">
         <v>2400</v>
       </c>
       <c r="Q624" t="n">
-        <v>621600</v>
+        <v>626400</v>
       </c>
     </row>
     <row r="625">
@@ -27136,28 +27136,28 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M626" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N626" t="n">
         <v>3451</v>
       </c>
       <c r="O626" t="n">
-        <v>1566754</v>
+        <v>1577107</v>
       </c>
       <c r="P626" t="n">
         <v>2900</v>
       </c>
       <c r="Q626" t="n">
-        <v>1316600</v>
+        <v>1325300</v>
       </c>
     </row>
     <row r="627">
@@ -27177,13 +27177,13 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M627" t="n">
         <v>201</v>
@@ -27259,7 +27259,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -27268,19 +27268,19 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N629" t="n">
         <v>1627</v>
       </c>
       <c r="O629" t="n">
-        <v>650800</v>
+        <v>652427</v>
       </c>
       <c r="P629" t="n">
         <v>2900</v>
       </c>
       <c r="Q629" t="n">
-        <v>1160000</v>
+        <v>1162900</v>
       </c>
     </row>
     <row r="630">
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -27309,19 +27309,19 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="N630" t="n">
         <v>2737</v>
       </c>
       <c r="O630" t="n">
-        <v>1228913</v>
+        <v>1253546</v>
       </c>
       <c r="P630" t="n">
         <v>2300</v>
       </c>
       <c r="Q630" t="n">
-        <v>1032700</v>
+        <v>1053400</v>
       </c>
     </row>
     <row r="631">
@@ -27382,13 +27382,13 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
       </c>
       <c r="L632" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M632" t="n">
         <v>336</v>
@@ -28061,7 +28061,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -28070,19 +28070,19 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="N648" t="n">
         <v>4793.53</v>
       </c>
       <c r="O648" t="n">
-        <v>1744844.92</v>
+        <v>1773606.1</v>
       </c>
       <c r="P648" t="n">
         <v>7900</v>
       </c>
       <c r="Q648" t="n">
-        <v>2875600</v>
+        <v>2923000</v>
       </c>
     </row>
     <row r="649">
@@ -28189,13 +28189,13 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M651" t="n">
         <v>245</v>
@@ -28230,7 +28230,7 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -28239,19 +28239,19 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N652" t="n">
         <v>8300</v>
       </c>
       <c r="O652" t="n">
-        <v>888100</v>
+        <v>913000</v>
       </c>
       <c r="P652" t="n">
         <v>14900</v>
       </c>
       <c r="Q652" t="n">
-        <v>1594300</v>
+        <v>1639000</v>
       </c>
     </row>
     <row r="653">
@@ -28276,13 +28276,13 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M653" t="n">
         <v>58</v>
@@ -28450,13 +28450,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M657" t="n">
         <v>52</v>
@@ -28829,7 +28829,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -28838,19 +28838,19 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N666" t="n">
         <v>16974.69</v>
       </c>
       <c r="O666" t="n">
-        <v>1595620.86</v>
+        <v>1612595.55</v>
       </c>
       <c r="P666" t="n">
         <v>26900</v>
       </c>
       <c r="Q666" t="n">
-        <v>2528600</v>
+        <v>2555500</v>
       </c>
     </row>
     <row r="667">
@@ -29085,13 +29085,13 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M672" t="n">
         <v>33</v>
@@ -29259,28 +29259,28 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M676" t="n">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="N676" t="n">
-        <v>1560.9979018405</v>
+        <v>1560.9978377282</v>
       </c>
       <c r="O676" t="n">
-        <v>902256.787263809</v>
+        <v>920988.724259638</v>
       </c>
       <c r="P676" t="n">
         <v>2900</v>
       </c>
       <c r="Q676" t="n">
-        <v>1676200</v>
+        <v>1711000</v>
       </c>
     </row>
     <row r="677">
@@ -29305,28 +29305,28 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M677" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N677" t="n">
         <v>3487.53</v>
       </c>
       <c r="O677" t="n">
-        <v>104625.9</v>
+        <v>108113.43</v>
       </c>
       <c r="P677" t="n">
         <v>6500</v>
       </c>
       <c r="Q677" t="n">
-        <v>195000</v>
+        <v>201500</v>
       </c>
     </row>
     <row r="678">
@@ -30198,10 +30198,10 @@
         <v>21</v>
       </c>
       <c r="N698" t="n">
-        <v>9994.7101428571</v>
+        <v>9994.7101388889</v>
       </c>
       <c r="O698" t="n">
-        <v>209888.9129999991</v>
+        <v>209888.9129166669</v>
       </c>
       <c r="P698" t="n">
         <v>20800</v>
@@ -31328,7 +31328,7 @@
         </is>
       </c>
       <c r="J725" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K725" t="n">
         <v>0</v>
@@ -31337,19 +31337,19 @@
         <v>0</v>
       </c>
       <c r="M725" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N725" t="n">
         <v>4534.2</v>
       </c>
       <c r="O725" t="n">
-        <v>90684</v>
+        <v>95218.2</v>
       </c>
       <c r="P725" t="n">
         <v>7900</v>
       </c>
       <c r="Q725" t="n">
-        <v>158000</v>
+        <v>165900</v>
       </c>
     </row>
     <row r="726">
@@ -31461,13 +31461,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M728" t="n">
         <v>101</v>
@@ -31507,28 +31507,28 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M729" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="N729" t="n">
-        <v>3113.8900218818</v>
+        <v>3113.8900216685</v>
       </c>
       <c r="O729" t="n">
-        <v>239769.5316848986</v>
+        <v>267794.541863491</v>
       </c>
       <c r="P729" t="n">
         <v>5000</v>
       </c>
       <c r="Q729" t="n">
-        <v>385000</v>
+        <v>430000</v>
       </c>
     </row>
     <row r="730">
@@ -31553,13 +31553,13 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M730" t="n">
         <v>34</v>
@@ -31645,13 +31645,13 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M732" t="n">
         <v>96</v>
@@ -31691,13 +31691,13 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M733" t="n">
         <v>52</v>
@@ -31783,13 +31783,13 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M735" t="n">
         <v>19</v>
@@ -31829,28 +31829,28 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M736" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N736" t="n">
         <v>2495.98</v>
       </c>
       <c r="O736" t="n">
-        <v>289533.68</v>
+        <v>297021.62</v>
       </c>
       <c r="P736" t="n">
         <v>4100</v>
       </c>
       <c r="Q736" t="n">
-        <v>475600</v>
+        <v>487900</v>
       </c>
     </row>
     <row r="737">
@@ -31921,13 +31921,13 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M738" t="n">
         <v>28</v>
@@ -31967,28 +31967,28 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M739" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N739" t="n">
-        <v>1595.0095763657</v>
+        <v>1595.0095814978</v>
       </c>
       <c r="O739" t="n">
-        <v>33495.2011036797</v>
+        <v>43065.25870044059</v>
       </c>
       <c r="P739" t="n">
         <v>2600</v>
       </c>
       <c r="Q739" t="n">
-        <v>54600</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="740">
@@ -32108,28 +32108,28 @@
         </is>
       </c>
       <c r="J742" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K742" t="n">
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M742" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N742" t="n">
         <v>4227.77</v>
       </c>
       <c r="O742" t="n">
-        <v>101466.48</v>
+        <v>126833.1</v>
       </c>
       <c r="P742" t="n">
         <v>6900</v>
       </c>
       <c r="Q742" t="n">
-        <v>165600</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="743">
@@ -32200,13 +32200,13 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M744" t="n">
         <v>40</v>
@@ -32246,13 +32246,13 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M745" t="n">
         <v>82</v>
@@ -32338,28 +32338,28 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M747" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="N747" t="n">
-        <v>1664.3622356902</v>
+        <v>1664.3625947335</v>
       </c>
       <c r="O747" t="n">
-        <v>269626.6821818124</v>
+        <v>309571.442620431</v>
       </c>
       <c r="P747" t="n">
         <v>2900</v>
       </c>
       <c r="Q747" t="n">
-        <v>469800</v>
+        <v>539400</v>
       </c>
     </row>
     <row r="748">
@@ -32384,28 +32384,28 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M748" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N748" t="n">
         <v>15502</v>
       </c>
       <c r="O748" t="n">
-        <v>201526</v>
+        <v>217028</v>
       </c>
       <c r="P748" t="n">
         <v>25900</v>
       </c>
       <c r="Q748" t="n">
-        <v>336700</v>
+        <v>362600</v>
       </c>
     </row>
     <row r="749">
@@ -33026,13 +33026,13 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M762" t="n">
         <v>12</v>
@@ -33302,7 +33302,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -33311,19 +33311,19 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="N768" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724843483</v>
       </c>
       <c r="O768" t="n">
-        <v>2228426.034001152</v>
+        <v>2242653.802763206</v>
       </c>
       <c r="P768" t="n">
         <v>4900</v>
       </c>
       <c r="Q768" t="n">
-        <v>6139700</v>
+        <v>6178900</v>
       </c>
     </row>
     <row r="769">
@@ -33348,7 +33348,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -33357,19 +33357,19 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="N769" t="n">
         <v>2325</v>
       </c>
       <c r="O769" t="n">
-        <v>771900</v>
+        <v>785850</v>
       </c>
       <c r="P769" t="n">
         <v>4900</v>
       </c>
       <c r="Q769" t="n">
-        <v>1626800</v>
+        <v>1656200</v>
       </c>
     </row>
     <row r="770">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="J811" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K811" t="n">
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M811" t="n">
         <v>196</v>
@@ -35840,22 +35840,22 @@
         </is>
       </c>
       <c r="J823" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K823" t="n">
         <v>0</v>
       </c>
       <c r="L823" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M823" t="n">
         <v>152</v>
       </c>
       <c r="N823" t="n">
-        <v>2252.2960775371</v>
+        <v>2252.2960568182</v>
       </c>
       <c r="O823" t="n">
-        <v>342349.0037856392</v>
+        <v>342349.0006363664</v>
       </c>
       <c r="P823" t="n">
         <v>3900</v>
@@ -36073,7 +36073,7 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
@@ -36082,19 +36082,19 @@
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N828" t="n">
-        <v>2328.1187653599</v>
+        <v>2328.1187675234</v>
       </c>
       <c r="O828" t="n">
-        <v>1082575.225892354</v>
+        <v>1091887.701968475</v>
       </c>
       <c r="P828" t="n">
         <v>4500</v>
       </c>
       <c r="Q828" t="n">
-        <v>2092500</v>
+        <v>2110500</v>
       </c>
     </row>
     <row r="829">
@@ -36303,7 +36303,7 @@
         </is>
       </c>
       <c r="J833" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K833" t="n">
         <v>0</v>
@@ -36312,19 +36312,19 @@
         <v>0</v>
       </c>
       <c r="M833" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N833" t="n">
         <v>3519</v>
       </c>
       <c r="O833" t="n">
-        <v>270963</v>
+        <v>285039</v>
       </c>
       <c r="P833" t="n">
         <v>5900</v>
       </c>
       <c r="Q833" t="n">
-        <v>454300</v>
+        <v>477900</v>
       </c>
     </row>
     <row r="834">
@@ -36717,13 +36717,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M842" t="n">
         <v>24</v>
@@ -36809,22 +36809,22 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K844" t="n">
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M844" t="n">
         <v>15</v>
       </c>
       <c r="N844" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.8218486172</v>
       </c>
       <c r="O844" t="n">
-        <v>73617.32809734451</v>
+        <v>73617.327729258</v>
       </c>
       <c r="P844" t="n">
         <v>8200</v>
@@ -38276,13 +38276,13 @@
         </is>
       </c>
       <c r="J876" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K876" t="n">
         <v>0</v>
       </c>
       <c r="L876" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M876" t="n">
         <v>98</v>
@@ -39470,28 +39470,28 @@
         </is>
       </c>
       <c r="J902" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K902" t="n">
         <v>0</v>
       </c>
       <c r="L902" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M902" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N902" t="n">
         <v>3639.35</v>
       </c>
       <c r="O902" t="n">
-        <v>65508.3</v>
+        <v>76426.34999999999</v>
       </c>
       <c r="P902" t="n">
         <v>7500</v>
       </c>
       <c r="Q902" t="n">
-        <v>135000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="903">
@@ -39516,13 +39516,13 @@
         </is>
       </c>
       <c r="J903" t="n">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="K903" t="n">
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M903" t="n">
         <v>1760</v>
@@ -39562,7 +39562,7 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
@@ -39571,19 +39571,19 @@
         <v>0</v>
       </c>
       <c r="M904" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N904" t="n">
         <v>10713.21</v>
       </c>
       <c r="O904" t="n">
-        <v>224977.41</v>
+        <v>246403.83</v>
       </c>
       <c r="P904" t="n">
         <v>20900</v>
       </c>
       <c r="Q904" t="n">
-        <v>438900</v>
+        <v>480700</v>
       </c>
     </row>
     <row r="905">
@@ -39608,13 +39608,13 @@
         </is>
       </c>
       <c r="J905" t="n">
+        <v>2</v>
+      </c>
+      <c r="K905" t="n">
+        <v>0</v>
+      </c>
+      <c r="L905" t="n">
         <v>1</v>
-      </c>
-      <c r="K905" t="n">
-        <v>0</v>
-      </c>
-      <c r="L905" t="n">
-        <v>0</v>
       </c>
       <c r="M905" t="n">
         <v>1</v>
@@ -40071,7 +40071,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40080,19 +40080,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="N915" t="n">
         <v>1337.29</v>
       </c>
       <c r="O915" t="n">
-        <v>112332.36</v>
+        <v>127042.55</v>
       </c>
       <c r="P915" t="n">
         <v>2600</v>
       </c>
       <c r="Q915" t="n">
-        <v>218400</v>
+        <v>247000</v>
       </c>
     </row>
     <row r="916">
@@ -40175,10 +40175,10 @@
         <v>1327</v>
       </c>
       <c r="N917" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388215585</v>
       </c>
       <c r="O917" t="n">
-        <v>2011783.515009583</v>
+        <v>2011783.51620813</v>
       </c>
       <c r="P917" t="n">
         <v>2300</v>
@@ -40209,28 +40209,28 @@
         </is>
       </c>
       <c r="J918" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="K918" t="n">
         <v>0</v>
       </c>
       <c r="L918" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M918" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="N918" t="n">
-        <v>4248.6103213611</v>
+        <v>4248.60975</v>
       </c>
       <c r="O918" t="n">
-        <v>497087.4075992487</v>
+        <v>556567.8772499999</v>
       </c>
       <c r="P918" t="n">
         <v>5900</v>
       </c>
       <c r="Q918" t="n">
-        <v>690300</v>
+        <v>772900</v>
       </c>
     </row>
     <row r="919">
@@ -40299,7 +40299,7 @@
         </is>
       </c>
       <c r="J920" t="n">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="K920" t="n">
         <v>0</v>
@@ -40308,19 +40308,19 @@
         <v>0</v>
       </c>
       <c r="M920" t="n">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="N920" t="n">
-        <v>2458.5136716147</v>
+        <v>2458.513771616</v>
       </c>
       <c r="O920" t="n">
-        <v>759680.7245289423</v>
+        <v>882606.4440101441</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
       </c>
       <c r="Q920" t="n">
-        <v>1081500</v>
+        <v>1256500</v>
       </c>
     </row>
     <row r="921">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40354,19 +40354,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="N921" t="n">
-        <v>1907.3946829268</v>
+        <v>1907.3948946136</v>
       </c>
       <c r="O921" t="n">
-        <v>114443.680975608</v>
+        <v>162128.566042156</v>
       </c>
       <c r="P921" t="n">
         <v>2500</v>
       </c>
       <c r="Q921" t="n">
-        <v>150000</v>
+        <v>212500</v>
       </c>
     </row>
     <row r="922">
@@ -40391,7 +40391,7 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
@@ -40400,19 +40400,19 @@
         <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="N922" t="n">
-        <v>1771.0915140845</v>
+        <v>1771.0916367843</v>
       </c>
       <c r="O922" t="n">
-        <v>322338.655563379</v>
+        <v>366615.9688143501</v>
       </c>
       <c r="P922" t="n">
         <v>2500</v>
       </c>
       <c r="Q922" t="n">
-        <v>455000</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="923">
@@ -40437,28 +40437,28 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M923" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N923" t="n">
-        <v>2079.3843686869</v>
+        <v>2079.3844162754</v>
       </c>
       <c r="O923" t="n">
-        <v>804721.7506818303</v>
+        <v>806801.1535148552</v>
       </c>
       <c r="P923" t="n">
         <v>2900</v>
       </c>
       <c r="Q923" t="n">
-        <v>1122300</v>
+        <v>1125200</v>
       </c>
     </row>
     <row r="924">
@@ -40483,28 +40483,28 @@
         </is>
       </c>
       <c r="J924" t="n">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K924" t="n">
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M924" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N924" t="n">
-        <v>1803.0147280335</v>
+        <v>1803.0147201337</v>
       </c>
       <c r="O924" t="n">
-        <v>759069.2005021035</v>
+        <v>760872.2118964214</v>
       </c>
       <c r="P924" t="n">
         <v>2500</v>
       </c>
       <c r="Q924" t="n">
-        <v>1052500</v>
+        <v>1055000</v>
       </c>
     </row>
     <row r="925">
@@ -40575,22 +40575,22 @@
         </is>
       </c>
       <c r="J926" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K926" t="n">
         <v>0</v>
       </c>
       <c r="L926" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M926" t="n">
         <v>51</v>
       </c>
       <c r="N926" t="n">
-        <v>2122.1642044444</v>
+        <v>2122.1642147294</v>
       </c>
       <c r="O926" t="n">
-        <v>108230.3744266644</v>
+        <v>108230.3749511994</v>
       </c>
       <c r="P926" t="n">
         <v>2900</v>
@@ -40621,28 +40621,28 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M927" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N927" t="n">
-        <v>2108.7892625995</v>
+        <v>2108.7892332099</v>
       </c>
       <c r="O927" t="n">
-        <v>347950.2283289175</v>
+        <v>350059.0127128434</v>
       </c>
       <c r="P927" t="n">
         <v>2900</v>
       </c>
       <c r="Q927" t="n">
-        <v>478500</v>
+        <v>481400</v>
       </c>
     </row>
     <row r="928">
@@ -40667,22 +40667,22 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M928" t="n">
         <v>413</v>
       </c>
       <c r="N928" t="n">
-        <v>2056.0840859599</v>
+        <v>2056.0840977981</v>
       </c>
       <c r="O928" t="n">
-        <v>849162.7275014388</v>
+        <v>849162.7323906154</v>
       </c>
       <c r="P928" t="n">
         <v>2900</v>
@@ -40713,13 +40713,13 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M929" t="n">
         <v>244</v>
@@ -40759,7 +40759,7 @@
         </is>
       </c>
       <c r="J930" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K930" t="n">
         <v>0</v>
@@ -40768,19 +40768,19 @@
         <v>0</v>
       </c>
       <c r="M930" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N930" t="n">
-        <v>1655.9315593531</v>
+        <v>1655.9315670732</v>
       </c>
       <c r="O930" t="n">
-        <v>556393.0039426417</v>
+        <v>559704.8696707416</v>
       </c>
       <c r="P930" t="n">
         <v>2500</v>
       </c>
       <c r="Q930" t="n">
-        <v>840000</v>
+        <v>845000</v>
       </c>
     </row>
     <row r="931">
@@ -40946,7 +40946,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -40955,19 +40955,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="N934" t="n">
         <v>2454</v>
       </c>
       <c r="O934" t="n">
-        <v>1384056</v>
+        <v>1403688</v>
       </c>
       <c r="P934" t="n">
         <v>4200</v>
       </c>
       <c r="Q934" t="n">
-        <v>2368800</v>
+        <v>2402400</v>
       </c>
     </row>
     <row r="935">
@@ -40992,22 +40992,22 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M935" t="n">
         <v>636</v>
       </c>
       <c r="N935" t="n">
-        <v>1592.2740100137</v>
+        <v>1592.2739613309</v>
       </c>
       <c r="O935" t="n">
-        <v>1012686.270368713</v>
+        <v>1012686.239406452</v>
       </c>
       <c r="P935" t="n">
         <v>2500</v>
@@ -41135,10 +41135,10 @@
         <v>237</v>
       </c>
       <c r="N938" t="n">
-        <v>2311.9281444759</v>
+        <v>2311.9289139073</v>
       </c>
       <c r="O938" t="n">
-        <v>547926.9702407883</v>
+        <v>547927.15259603</v>
       </c>
       <c r="P938" t="n">
         <v>3500</v>
@@ -41181,10 +41181,10 @@
         <v>209</v>
       </c>
       <c r="N939" t="n">
-        <v>1906.1878571429</v>
+        <v>1906.1879253112</v>
       </c>
       <c r="O939" t="n">
-        <v>398393.2621428661</v>
+        <v>398393.2763900408</v>
       </c>
       <c r="P939" t="n">
         <v>2900</v>
@@ -41215,28 +41215,28 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M940" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N940" t="n">
-        <v>3033.7328518519</v>
+        <v>3033.732946593</v>
       </c>
       <c r="O940" t="n">
-        <v>803939.2057407534</v>
+        <v>813040.4296869241</v>
       </c>
       <c r="P940" t="n">
         <v>4500</v>
       </c>
       <c r="Q940" t="n">
-        <v>1192500</v>
+        <v>1206000</v>
       </c>
     </row>
     <row r="941">
@@ -41261,7 +41261,7 @@
         </is>
       </c>
       <c r="J941" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="K941" t="n">
         <v>0</v>
@@ -41270,19 +41270,19 @@
         <v>0</v>
       </c>
       <c r="M941" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="N941" t="n">
-        <v>1668.6124489796</v>
+        <v>1668.6118590522</v>
       </c>
       <c r="O941" t="n">
-        <v>420490.3371428592</v>
+        <v>440513.5307897808</v>
       </c>
       <c r="P941" t="n">
         <v>2500</v>
       </c>
       <c r="Q941" t="n">
-        <v>630000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="942">
@@ -41319,10 +41319,10 @@
         <v>195</v>
       </c>
       <c r="N942" t="n">
-        <v>2546.9861569689</v>
+        <v>2546.9862532982</v>
       </c>
       <c r="O942" t="n">
-        <v>496662.3006089355</v>
+        <v>496662.3193931491</v>
       </c>
       <c r="P942" t="n">
         <v>3900</v>
@@ -41353,7 +41353,7 @@
         </is>
       </c>
       <c r="J943" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="K943" t="n">
         <v>0</v>
@@ -41362,19 +41362,19 @@
         <v>0</v>
       </c>
       <c r="M943" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="N943" t="n">
-        <v>1259.2741948888</v>
+        <v>1259.274157743</v>
       </c>
       <c r="O943" t="n">
-        <v>1419202.017639678</v>
+        <v>1421720.524091847</v>
       </c>
       <c r="P943" t="n">
         <v>1900</v>
       </c>
       <c r="Q943" t="n">
-        <v>2141300</v>
+        <v>2145100</v>
       </c>
     </row>
     <row r="944">
@@ -41532,28 +41532,28 @@
         </is>
       </c>
       <c r="J947" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K947" t="n">
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M947" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N947" t="n">
-        <v>2556.7442028986</v>
+        <v>2556.7441826923</v>
       </c>
       <c r="O947" t="n">
-        <v>411635.8166666746</v>
+        <v>416749.3017788449</v>
       </c>
       <c r="P947" t="n">
         <v>3900</v>
       </c>
       <c r="Q947" t="n">
-        <v>627900</v>
+        <v>635700</v>
       </c>
     </row>
     <row r="948">
@@ -41576,7 +41576,7 @@
         </is>
       </c>
       <c r="J948" t="n">
-        <v>2782</v>
+        <v>2806</v>
       </c>
       <c r="K948" t="n">
         <v>0</v>
@@ -41585,19 +41585,19 @@
         <v>0</v>
       </c>
       <c r="M948" t="n">
-        <v>2782</v>
+        <v>2806</v>
       </c>
       <c r="N948" t="n">
-        <v>692.1519887834301</v>
+        <v>692.15197854077</v>
       </c>
       <c r="O948" t="n">
-        <v>1925566.832795502</v>
+        <v>1942178.451785401</v>
       </c>
       <c r="P948" t="n">
         <v>1200</v>
       </c>
       <c r="Q948" t="n">
-        <v>3338400</v>
+        <v>3367200</v>
       </c>
     </row>
     <row r="949">
@@ -41903,7 +41903,7 @@
         </is>
       </c>
       <c r="J955" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K955" t="n">
         <v>0</v>
@@ -41912,19 +41912,19 @@
         <v>0</v>
       </c>
       <c r="M955" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N955" t="n">
         <v>5510.92</v>
       </c>
       <c r="O955" t="n">
-        <v>38576.44</v>
+        <v>44087.36</v>
       </c>
       <c r="P955" t="n">
         <v>4900</v>
       </c>
       <c r="Q955" t="n">
-        <v>34300</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="956">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="J962" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="K962" t="n">
         <v>0</v>
@@ -42241,19 +42241,19 @@
         <v>0</v>
       </c>
       <c r="M962" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="N962" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O962" t="n">
-        <v>3721278.08</v>
+        <v>3774950.36</v>
       </c>
       <c r="P962" t="n">
         <v>14900</v>
       </c>
       <c r="Q962" t="n">
-        <v>6198400</v>
+        <v>6287800</v>
       </c>
     </row>
     <row r="963">
@@ -42967,7 +42967,7 @@
         </is>
       </c>
       <c r="J978" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K978" t="n">
         <v>0</v>
@@ -42976,19 +42976,19 @@
         <v>0</v>
       </c>
       <c r="M978" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N978" t="n">
-        <v>872.15418521463</v>
+        <v>872.15418355185</v>
       </c>
       <c r="O978" t="n">
-        <v>459625.25560811</v>
+        <v>460497.4089153768</v>
       </c>
       <c r="P978" t="n">
         <v>1200</v>
       </c>
       <c r="Q978" t="n">
-        <v>632400</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="979">
@@ -43104,7 +43104,7 @@
         </is>
       </c>
       <c r="J981" t="n">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="K981" t="n">
         <v>0</v>
@@ -43113,19 +43113,19 @@
         <v>0</v>
       </c>
       <c r="M981" t="n">
-        <v>1561</v>
+        <v>1595</v>
       </c>
       <c r="N981" t="n">
-        <v>711.33665018328</v>
+        <v>711.33665411716</v>
       </c>
       <c r="O981" t="n">
-        <v>1110396.5109361</v>
+        <v>1134581.96331687</v>
       </c>
       <c r="P981" t="n">
         <v>900</v>
       </c>
       <c r="Q981" t="n">
-        <v>1404900</v>
+        <v>1435500</v>
       </c>
     </row>
     <row r="982">
@@ -43160,10 +43160,10 @@
         <v>351</v>
       </c>
       <c r="N982" t="n">
-        <v>2286.1662851537</v>
+        <v>2286.1662924282</v>
       </c>
       <c r="O982" t="n">
-        <v>802444.3660889487</v>
+        <v>802444.3686422982</v>
       </c>
       <c r="P982" t="n">
         <v>3000</v>
@@ -43546,10 +43546,10 @@
         <v>34</v>
       </c>
       <c r="N991" t="n">
-        <v>1415.1363934426</v>
+        <v>1415.1367741935</v>
       </c>
       <c r="O991" t="n">
-        <v>48114.6373770484</v>
+        <v>48114.650322579</v>
       </c>
       <c r="P991" t="n">
         <v>2500</v>
@@ -43712,28 +43712,28 @@
         </is>
       </c>
       <c r="J995" t="n">
-        <v>2353</v>
+        <v>2477</v>
       </c>
       <c r="K995" t="n">
         <v>0</v>
       </c>
       <c r="L995" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M995" t="n">
-        <v>2353</v>
+        <v>2421</v>
       </c>
       <c r="N995" t="n">
-        <v>517.28707627294</v>
+        <v>517.28700890476</v>
       </c>
       <c r="O995" t="n">
-        <v>1217176.490470228</v>
+        <v>1252351.848558424</v>
       </c>
       <c r="P995" t="n">
         <v>900</v>
       </c>
       <c r="Q995" t="n">
-        <v>2117700</v>
+        <v>2178900</v>
       </c>
     </row>
     <row r="996">
@@ -43897,28 +43897,28 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
       </c>
       <c r="L999" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M999" t="n">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="N999" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8439531303</v>
       </c>
       <c r="O999" t="n">
-        <v>5344429.78921776</v>
+        <v>5350651.599384116</v>
       </c>
       <c r="P999" t="n">
         <v>4500</v>
       </c>
       <c r="Q999" t="n">
-        <v>7731000</v>
+        <v>7740000</v>
       </c>
     </row>
     <row r="1000">
@@ -44029,28 +44029,28 @@
         </is>
       </c>
       <c r="J1002" t="n">
-        <v>15478</v>
+        <v>15650</v>
       </c>
       <c r="K1002" t="n">
         <v>0</v>
       </c>
       <c r="L1002" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1002" t="n">
-        <v>15478</v>
+        <v>15638</v>
       </c>
       <c r="N1002" t="n">
-        <v>703.79553851454</v>
+        <v>703.79555062954</v>
       </c>
       <c r="O1002" t="n">
-        <v>10893347.34512805</v>
+        <v>11005954.82074475</v>
       </c>
       <c r="P1002" t="n">
         <v>900</v>
       </c>
       <c r="Q1002" t="n">
-        <v>13930200</v>
+        <v>14074200</v>
       </c>
     </row>
     <row r="1003">
@@ -44131,10 +44131,10 @@
         <v>45</v>
       </c>
       <c r="N1004" t="n">
-        <v>3006.0208333333</v>
+        <v>3006.0208256881</v>
       </c>
       <c r="O1004" t="n">
-        <v>135270.9374999985</v>
+        <v>135270.9371559645</v>
       </c>
       <c r="P1004" t="n">
         <v>3900</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="J1010" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K1010" t="n">
         <v>0</v>
@@ -44398,19 +44398,19 @@
         <v>0</v>
       </c>
       <c r="M1010" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N1010" t="n">
         <v>1937</v>
       </c>
       <c r="O1010" t="n">
-        <v>832910</v>
+        <v>834847</v>
       </c>
       <c r="P1010" t="n">
         <v>3300</v>
       </c>
       <c r="Q1010" t="n">
-        <v>1419000</v>
+        <v>1422300</v>
       </c>
     </row>
     <row r="1011">
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="J1012" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1012" t="n">
         <v>0</v>
@@ -44483,19 +44483,19 @@
         <v>0</v>
       </c>
       <c r="M1012" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N1012" t="n">
         <v>2525.02</v>
       </c>
       <c r="O1012" t="n">
-        <v>70700.56</v>
+        <v>73225.58</v>
       </c>
       <c r="P1012" t="n">
         <v>3000</v>
       </c>
       <c r="Q1012" t="n">
-        <v>84000</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="1013">
@@ -44527,10 +44527,10 @@
         <v>430</v>
       </c>
       <c r="N1013" t="n">
-        <v>2077.4944179523</v>
+        <v>2077.494338843</v>
       </c>
       <c r="O1013" t="n">
-        <v>893322.599719489</v>
+        <v>893322.56570249</v>
       </c>
       <c r="P1013" t="n">
         <v>2900</v>
@@ -44784,10 +44784,10 @@
         <v>81</v>
       </c>
       <c r="N1019" t="n">
-        <v>1595.5196456996</v>
+        <v>1595.5196827833</v>
       </c>
       <c r="O1019" t="n">
-        <v>129237.0913016676</v>
+        <v>129237.0943054473</v>
       </c>
       <c r="P1019" t="n">
         <v>2500</v>
@@ -44818,13 +44818,13 @@
         </is>
       </c>
       <c r="J1020" t="n">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="K1020" t="n">
         <v>0</v>
       </c>
       <c r="L1020" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1020" t="n">
         <v>433</v>
@@ -45953,7 +45953,7 @@
         </is>
       </c>
       <c r="J1044" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K1044" t="n">
         <v>0</v>
@@ -45962,19 +45962,19 @@
         <v>0</v>
       </c>
       <c r="M1044" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N1044" t="n">
-        <v>1322.925</v>
+        <v>1322.9251724138</v>
       </c>
       <c r="O1044" t="n">
-        <v>6614.625</v>
+        <v>9260.476206896601</v>
       </c>
       <c r="P1044" t="n">
         <v>7900</v>
       </c>
       <c r="Q1044" t="n">
-        <v>39500</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="1045">
@@ -46695,7 +46695,7 @@
         </is>
       </c>
       <c r="J1060" t="n">
-        <v>1075</v>
+        <v>1101</v>
       </c>
       <c r="K1060" t="n">
         <v>0</v>
@@ -46704,19 +46704,19 @@
         <v>0</v>
       </c>
       <c r="M1060" t="n">
-        <v>1075</v>
+        <v>1101</v>
       </c>
       <c r="N1060" t="n">
-        <v>1783.7988883868</v>
+        <v>1783.7989012952</v>
       </c>
       <c r="O1060" t="n">
-        <v>1917583.80501581</v>
+        <v>1963962.590326015</v>
       </c>
       <c r="P1060" t="n">
         <v>1500</v>
       </c>
       <c r="Q1060" t="n">
-        <v>1612500</v>
+        <v>1651500</v>
       </c>
     </row>
     <row r="1061">
@@ -48366,10 +48366,10 @@
         <v>43</v>
       </c>
       <c r="N1095" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398312236</v>
       </c>
       <c r="O1095" t="n">
-        <v>303018.4127334171</v>
+        <v>303018.4127426148</v>
       </c>
       <c r="P1095" t="n">
         <v>9900</v>
@@ -48493,13 +48493,13 @@
         </is>
       </c>
       <c r="J1098" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1098" t="n">
         <v>29</v>
@@ -48597,10 +48597,10 @@
         <v>24</v>
       </c>
       <c r="N1100" t="n">
-        <v>44113.603675676</v>
+        <v>44113.603597884</v>
       </c>
       <c r="O1100" t="n">
-        <v>1058726.488216224</v>
+        <v>1058726.486349216</v>
       </c>
       <c r="P1100" t="n">
         <v>71900</v>
@@ -48727,7 +48727,7 @@
         </is>
       </c>
       <c r="J1103" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K1103" t="n">
         <v>0</v>
@@ -48736,19 +48736,19 @@
         <v>0</v>
       </c>
       <c r="M1103" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="N1103" t="n">
-        <v>2397.6836666667</v>
+        <v>2397.6389361702</v>
       </c>
       <c r="O1103" t="n">
-        <v>40760.6223333339</v>
+        <v>81519.7238297868</v>
       </c>
       <c r="P1103" t="n">
         <v>2000</v>
       </c>
       <c r="Q1103" t="n">
-        <v>34000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="1104">
@@ -48920,7 +48920,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -48929,19 +48929,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1107" t="n">
         <v>3155</v>
       </c>
       <c r="O1107" t="n">
-        <v>9465</v>
+        <v>12620</v>
       </c>
       <c r="P1107" t="n">
         <v>5900</v>
       </c>
       <c r="Q1107" t="n">
-        <v>17700</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="1108">
@@ -49231,13 +49231,13 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1114" t="n">
         <v>762</v>
@@ -49272,7 +49272,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49281,19 +49281,19 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N1115" t="n">
         <v>1267</v>
       </c>
       <c r="O1115" t="n">
-        <v>573951</v>
+        <v>584087</v>
       </c>
       <c r="P1115" t="n">
         <v>1900</v>
       </c>
       <c r="Q1115" t="n">
-        <v>860700</v>
+        <v>875900</v>
       </c>
     </row>
     <row r="1116">
@@ -49489,7 +49489,7 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
@@ -49498,19 +49498,19 @@
         <v>0</v>
       </c>
       <c r="M1120" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="N1120" t="n">
         <v>1297.52</v>
       </c>
       <c r="O1120" t="n">
-        <v>144024.72</v>
+        <v>149214.8</v>
       </c>
       <c r="P1120" t="n">
         <v>1800</v>
       </c>
       <c r="Q1120" t="n">
-        <v>199800</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="1121">
@@ -49615,13 +49615,13 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1123" t="n">
         <v>1460</v>
@@ -50257,7 +50257,7 @@
         </is>
       </c>
       <c r="J1138" t="n">
-        <v>1861</v>
+        <v>1873</v>
       </c>
       <c r="K1138" t="n">
         <v>0</v>
@@ -50266,19 +50266,19 @@
         <v>0</v>
       </c>
       <c r="M1138" t="n">
-        <v>1861</v>
+        <v>1873</v>
       </c>
       <c r="N1138" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1138" t="n">
-        <v>2189596.77</v>
+        <v>2203715.61</v>
       </c>
       <c r="P1138" t="n">
         <v>1900</v>
       </c>
       <c r="Q1138" t="n">
-        <v>3535900</v>
+        <v>3558700</v>
       </c>
     </row>
     <row r="1139">
@@ -50345,28 +50345,28 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1140" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="N1140" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1140" t="n">
-        <v>601379.1</v>
+        <v>680926.6</v>
       </c>
       <c r="P1140" t="n">
         <v>5100</v>
       </c>
       <c r="Q1140" t="n">
-        <v>963900</v>
+        <v>1091400</v>
       </c>
     </row>
     <row r="1141">
@@ -50993,13 +50993,13 @@
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
       </c>
       <c r="L1155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1155" t="n">
         <v>74</v>
@@ -51312,10 +51312,10 @@
         <v>386</v>
       </c>
       <c r="N1162" t="n">
-        <v>22951.705024752</v>
+        <v>22951.705030902</v>
       </c>
       <c r="O1162" t="n">
-        <v>8859358.139554271</v>
+        <v>8859358.141928172</v>
       </c>
       <c r="P1162" t="n">
         <v>37900</v>
@@ -51489,10 +51489,10 @@
         <v>4</v>
       </c>
       <c r="N1166" t="n">
-        <v>705.52801652893</v>
+        <v>705.52802098951</v>
       </c>
       <c r="O1166" t="n">
-        <v>2822.11206611572</v>
+        <v>2822.11208395804</v>
       </c>
       <c r="P1166" t="n">
         <v>1500</v>
@@ -52112,13 +52112,13 @@
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1180" t="n">
         <v>17</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="J1211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1211" t="n">
         <v>0</v>
@@ -53547,19 +53547,19 @@
         <v>0</v>
       </c>
       <c r="M1211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1211" t="n">
         <v>2400</v>
       </c>
       <c r="O1211" t="n">
-        <v>4800</v>
+        <v>7200</v>
       </c>
       <c r="P1211" t="n">
         <v>2900</v>
       </c>
       <c r="Q1211" t="n">
-        <v>5800</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="1212">
@@ -54233,7 +54233,7 @@
         </is>
       </c>
       <c r="J1226" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="K1226" t="n">
         <v>0</v>
@@ -54242,19 +54242,19 @@
         <v>0</v>
       </c>
       <c r="M1226" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="N1226" t="n">
         <v>2058.92</v>
       </c>
       <c r="O1226" t="n">
-        <v>609440.3200000001</v>
+        <v>644441.9600000001</v>
       </c>
       <c r="P1226" t="n">
         <v>2500</v>
       </c>
       <c r="Q1226" t="n">
-        <v>740000</v>
+        <v>782500</v>
       </c>
     </row>
     <row r="1227">
@@ -61643,7 +61643,7 @@
         </is>
       </c>
       <c r="J1406" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K1406" t="n">
         <v>0</v>
@@ -61652,19 +61652,19 @@
         <v>0</v>
       </c>
       <c r="M1406" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1406" t="n">
         <v>2200</v>
       </c>
       <c r="O1406" t="n">
-        <v>114400</v>
+        <v>116600</v>
       </c>
       <c r="P1406" t="n">
         <v>2700</v>
       </c>
       <c r="Q1406" t="n">
-        <v>140400</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="1407">
@@ -61919,28 +61919,28 @@
         </is>
       </c>
       <c r="J1412" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="K1412" t="n">
         <v>0</v>
       </c>
       <c r="L1412" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1412" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="N1412" t="n">
         <v>4550</v>
       </c>
       <c r="O1412" t="n">
-        <v>737100</v>
+        <v>800800</v>
       </c>
       <c r="P1412" t="n">
         <v>6500</v>
       </c>
       <c r="Q1412" t="n">
-        <v>1053000</v>
+        <v>1144000</v>
       </c>
     </row>
     <row r="1413">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
@@ -739,10 +739,10 @@
         <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.65634615401</v>
+        <v>74676.65579999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1045473.188846156</v>
+        <v>1045473.1812</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -985,28 +985,28 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3034121753</v>
+        <v>1811.303568532</v>
       </c>
       <c r="O14" t="n">
-        <v>760747.4331136261</v>
+        <v>753502.284509312</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>1092000</v>
+        <v>1081600</v>
       </c>
     </row>
     <row r="15">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.746528748</v>
+        <v>3376.7465268817</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.77541646</v>
+        <v>3866374.773279546</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2110,19 +2110,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N41" t="n">
-        <v>15970.739135802</v>
+        <v>15970.739125</v>
       </c>
       <c r="O41" t="n">
-        <v>814507.695925902</v>
+        <v>798536.95625</v>
       </c>
       <c r="P41" t="n">
         <v>26900</v>
       </c>
       <c r="Q41" t="n">
-        <v>1371900</v>
+        <v>1345000</v>
       </c>
     </row>
     <row r="42">
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2752,19 +2752,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N57" t="n">
         <v>3585</v>
       </c>
       <c r="O57" t="n">
-        <v>329820</v>
+        <v>319065</v>
       </c>
       <c r="P57" t="n">
         <v>4500</v>
       </c>
       <c r="Q57" t="n">
-        <v>414000</v>
+        <v>400500</v>
       </c>
     </row>
     <row r="58">
@@ -2782,28 +2782,28 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8539614856</v>
+        <v>6272.8539724138</v>
       </c>
       <c r="O58" t="n">
-        <v>784106.7451857</v>
+        <v>771561.0386068973</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>987500</v>
+        <v>971700</v>
       </c>
     </row>
     <row r="59">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2835,19 +2835,19 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>156522.88</v>
+        <v>127174.84</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>294400</v>
+        <v>239200</v>
       </c>
     </row>
     <row r="60">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2955,19 +2955,19 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N62" t="n">
-        <v>3926.8371399387</v>
+        <v>3926.8371355499</v>
       </c>
       <c r="O62" t="n">
-        <v>141366.1370377932</v>
+        <v>129585.6254731467</v>
       </c>
       <c r="P62" t="n">
         <v>4800</v>
       </c>
       <c r="Q62" t="n">
-        <v>172800</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="63">
@@ -3242,10 +3242,10 @@
         <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>12793.680085837</v>
+        <v>12793.680086207</v>
       </c>
       <c r="O69" t="n">
-        <v>63968.400429185</v>
+        <v>63968.400431035</v>
       </c>
       <c r="P69" t="n">
         <v>24000</v>
@@ -3632,10 +3632,10 @@
         <v>77</v>
       </c>
       <c r="N79" t="n">
-        <v>14857.623050847</v>
+        <v>14857.62306383</v>
       </c>
       <c r="O79" t="n">
-        <v>1144036.974915219</v>
+        <v>1144036.97591491</v>
       </c>
       <c r="P79" t="n">
         <v>34900</v>
@@ -3765,10 +3765,10 @@
         <v>5</v>
       </c>
       <c r="N82" t="n">
-        <v>26465.341428571</v>
+        <v>26465.343333333</v>
       </c>
       <c r="O82" t="n">
-        <v>132326.707142855</v>
+        <v>132326.716666665</v>
       </c>
       <c r="P82" t="n">
         <v>42900</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3925,19 +3925,19 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N86" t="n">
         <v>1800</v>
       </c>
       <c r="O86" t="n">
-        <v>43200</v>
+        <v>41400</v>
       </c>
       <c r="P86" t="n">
         <v>2200</v>
       </c>
       <c r="Q86" t="n">
-        <v>52800</v>
+        <v>50600</v>
       </c>
     </row>
     <row r="87">
@@ -4098,10 +4098,10 @@
         <v>19</v>
       </c>
       <c r="N90" t="n">
-        <v>3910.6283208955</v>
+        <v>3910.628317757</v>
       </c>
       <c r="O90" t="n">
-        <v>74301.9380970145</v>
+        <v>74301.93803738299</v>
       </c>
       <c r="P90" t="n">
         <v>9100</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4919,19 +4919,19 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>30708.906428571</v>
+        <v>30708.904814815</v>
       </c>
       <c r="O108" t="n">
-        <v>153544.532142855</v>
+        <v>122835.61925926</v>
       </c>
       <c r="P108" t="n">
         <v>53500</v>
       </c>
       <c r="Q108" t="n">
-        <v>267500</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="109">
@@ -5048,10 +5048,10 @@
         <v>6</v>
       </c>
       <c r="N111" t="n">
-        <v>17085.657567568</v>
+        <v>17085.656666667</v>
       </c>
       <c r="O111" t="n">
-        <v>102513.945405408</v>
+        <v>102513.940000002</v>
       </c>
       <c r="P111" t="n">
         <v>29200</v>
@@ -5137,10 +5137,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>16486.4104</v>
+        <v>16486.41027027</v>
       </c>
       <c r="O113" t="n">
-        <v>16486.4104</v>
+        <v>16486.41027027</v>
       </c>
       <c r="P113" t="n">
         <v>30500</v>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5215,19 +5215,19 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966494465</v>
+        <v>15711.966441948</v>
       </c>
       <c r="O115" t="n">
-        <v>345663.26287823</v>
+        <v>329951.295280908</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
       </c>
       <c r="Q115" t="n">
-        <v>627000</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="116">
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5429,19 +5429,19 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N120" t="n">
-        <v>7407.7300522193</v>
+        <v>7407.730052356</v>
       </c>
       <c r="O120" t="n">
-        <v>1103751.777780676</v>
+        <v>1096344.047748688</v>
       </c>
       <c r="P120" t="n">
         <v>10900</v>
       </c>
       <c r="Q120" t="n">
-        <v>1624100</v>
+        <v>1613200</v>
       </c>
     </row>
     <row r="121">
@@ -6200,10 +6200,10 @@
         <v>6</v>
       </c>
       <c r="N139" t="n">
-        <v>36574.851914894</v>
+        <v>36574.852</v>
       </c>
       <c r="O139" t="n">
-        <v>219449.111489364</v>
+        <v>219449.112</v>
       </c>
       <c r="P139" t="n">
         <v>65900</v>
@@ -6416,10 +6416,10 @@
         <v>8</v>
       </c>
       <c r="N144" t="n">
-        <v>36306.261724138</v>
+        <v>36306.262857143</v>
       </c>
       <c r="O144" t="n">
-        <v>290450.093793104</v>
+        <v>290450.102857144</v>
       </c>
       <c r="P144" t="n">
         <v>64900</v>
@@ -6510,10 +6510,10 @@
         <v>11</v>
       </c>
       <c r="N146" t="n">
-        <v>62349.66195122</v>
+        <v>62349.661025641</v>
       </c>
       <c r="O146" t="n">
-        <v>685846.28146342</v>
+        <v>685846.271282051</v>
       </c>
       <c r="P146" t="n">
         <v>109900</v>
@@ -6557,10 +6557,10 @@
         <v>17</v>
       </c>
       <c r="N147" t="n">
-        <v>141416.88436137</v>
+        <v>141416.88438871</v>
       </c>
       <c r="O147" t="n">
-        <v>2404087.03414329</v>
+        <v>2404087.03460807</v>
       </c>
       <c r="P147" t="n">
         <v>251900</v>
@@ -6599,10 +6599,10 @@
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>200072.19865772</v>
+        <v>200072.19883562</v>
       </c>
       <c r="O148" t="n">
-        <v>400144.39731544</v>
+        <v>400144.39767124</v>
       </c>
       <c r="P148" t="n">
         <v>312000</v>
@@ -6779,10 +6779,10 @@
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>344599.17888889</v>
+        <v>344599.17885246</v>
       </c>
       <c r="O152" t="n">
-        <v>344599.17888889</v>
+        <v>344599.17885246</v>
       </c>
       <c r="P152" t="n">
         <v>532900</v>
@@ -7212,13 +7212,13 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -7735,19 +7735,19 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N175" t="n">
         <v>8500</v>
       </c>
       <c r="O175" t="n">
-        <v>42500</v>
+        <v>34000</v>
       </c>
       <c r="P175" t="n">
         <v>10200</v>
       </c>
       <c r="Q175" t="n">
-        <v>51000</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="176">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -8075,19 +8075,19 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N183" t="n">
         <v>2572.67</v>
       </c>
       <c r="O183" t="n">
-        <v>522252.01</v>
+        <v>519679.34</v>
       </c>
       <c r="P183" t="n">
         <v>4700</v>
       </c>
       <c r="Q183" t="n">
-        <v>954100</v>
+        <v>949400</v>
       </c>
     </row>
     <row r="184">
@@ -8216,10 +8216,10 @@
         <v>74</v>
       </c>
       <c r="N186" t="n">
-        <v>6303.178</v>
+        <v>6303.1779439252</v>
       </c>
       <c r="O186" t="n">
-        <v>466435.172</v>
+        <v>466435.1678504648</v>
       </c>
       <c r="P186" t="n">
         <v>13500</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8305,19 +8305,19 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N188" t="n">
         <v>2570.16</v>
       </c>
       <c r="O188" t="n">
-        <v>449778</v>
+        <v>447207.84</v>
       </c>
       <c r="P188" t="n">
         <v>4700</v>
       </c>
       <c r="Q188" t="n">
-        <v>822500</v>
+        <v>817800</v>
       </c>
     </row>
     <row r="189">
@@ -8393,10 +8393,10 @@
         <v>44</v>
       </c>
       <c r="N190" t="n">
-        <v>4878.2851851852</v>
+        <v>4878.2852688172</v>
       </c>
       <c r="O190" t="n">
-        <v>214644.5481481488</v>
+        <v>214644.5518279568</v>
       </c>
       <c r="P190" t="n">
         <v>13500</v>
@@ -8434,10 +8434,10 @@
         <v>115</v>
       </c>
       <c r="N191" t="n">
-        <v>7394.9353551913</v>
+        <v>7394.9353846154</v>
       </c>
       <c r="O191" t="n">
-        <v>850417.5658469995</v>
+        <v>850417.569230771</v>
       </c>
       <c r="P191" t="n">
         <v>17900</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9013,19 +9013,19 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N205" t="n">
-        <v>4333.6041176471</v>
+        <v>4333.604375</v>
       </c>
       <c r="O205" t="n">
-        <v>26001.6247058826</v>
+        <v>21668.021875</v>
       </c>
       <c r="P205" t="n">
         <v>7500</v>
       </c>
       <c r="Q205" t="n">
-        <v>45000</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="206">
@@ -9223,22 +9223,22 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
         <v>27</v>
       </c>
       <c r="N210" t="n">
-        <v>3340.6800773694</v>
+        <v>3340.6800775194</v>
       </c>
       <c r="O210" t="n">
-        <v>90198.36208897379</v>
+        <v>90198.36209302381</v>
       </c>
       <c r="P210" t="n">
         <v>7100</v>
@@ -9662,10 +9662,10 @@
         <v>53</v>
       </c>
       <c r="N220" t="n">
-        <v>732.63409556314</v>
+        <v>732.63410958904</v>
       </c>
       <c r="O220" t="n">
-        <v>38829.60706484642</v>
+        <v>38829.60780821912</v>
       </c>
       <c r="P220" t="n">
         <v>6200</v>
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -9971,19 +9971,19 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="N227" t="n">
         <v>2833</v>
       </c>
       <c r="O227" t="n">
-        <v>1841450</v>
+        <v>1830118</v>
       </c>
       <c r="P227" t="n">
         <v>3500</v>
       </c>
       <c r="Q227" t="n">
-        <v>2275000</v>
+        <v>2261000</v>
       </c>
     </row>
     <row r="228">
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>9610</v>
+        <v>9532</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10053,19 +10053,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>9610</v>
+        <v>9532</v>
       </c>
       <c r="N229" t="n">
         <v>1726.32</v>
       </c>
       <c r="O229" t="n">
-        <v>16589935.2</v>
+        <v>16455282.24</v>
       </c>
       <c r="P229" t="n">
         <v>1500</v>
       </c>
       <c r="Q229" t="n">
-        <v>14415000</v>
+        <v>14298000</v>
       </c>
     </row>
     <row r="230">
@@ -10131,7 +10131,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10140,19 +10140,19 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="N231" t="n">
-        <v>4937.3101582734</v>
+        <v>4937.3101589595</v>
       </c>
       <c r="O231" t="n">
-        <v>1170142.507510796</v>
+        <v>1140518.646719645</v>
       </c>
       <c r="P231" t="n">
         <v>7500</v>
       </c>
       <c r="Q231" t="n">
-        <v>1777500</v>
+        <v>1732500</v>
       </c>
     </row>
     <row r="232">
@@ -10595,28 +10595,28 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1590</v>
+        <v>1425</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>1574</v>
+        <v>1425</v>
       </c>
       <c r="N242" t="n">
-        <v>1098.0510925004</v>
+        <v>1098.0517240829</v>
       </c>
       <c r="O242" t="n">
-        <v>1728332.41959563</v>
+        <v>1564723.706818132</v>
       </c>
       <c r="P242" t="n">
         <v>1500</v>
       </c>
       <c r="Q242" t="n">
-        <v>2361000</v>
+        <v>2137500</v>
       </c>
     </row>
     <row r="243">
@@ -10928,13 +10928,13 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
         <v>21</v>
@@ -11051,28 +11051,28 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="N253" t="n">
         <v>1789</v>
       </c>
       <c r="O253" t="n">
-        <v>1034042</v>
+        <v>1028675</v>
       </c>
       <c r="P253" t="n">
         <v>2700</v>
       </c>
       <c r="Q253" t="n">
-        <v>1560600</v>
+        <v>1552500</v>
       </c>
     </row>
     <row r="254">
@@ -11218,28 +11218,28 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N257" t="n">
         <v>1789</v>
       </c>
       <c r="O257" t="n">
-        <v>871243</v>
+        <v>867665</v>
       </c>
       <c r="P257" t="n">
         <v>2700</v>
       </c>
       <c r="Q257" t="n">
-        <v>1314900</v>
+        <v>1309500</v>
       </c>
     </row>
     <row r="258">
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11309,19 +11309,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="N259" t="n">
         <v>1789</v>
       </c>
       <c r="O259" t="n">
-        <v>796105</v>
+        <v>783582</v>
       </c>
       <c r="P259" t="n">
         <v>2700</v>
       </c>
       <c r="Q259" t="n">
-        <v>1201500</v>
+        <v>1182600</v>
       </c>
     </row>
     <row r="260">
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11483,19 +11483,19 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N263" t="n">
         <v>2189</v>
       </c>
       <c r="O263" t="n">
-        <v>608542</v>
+        <v>606353</v>
       </c>
       <c r="P263" t="n">
         <v>4500</v>
       </c>
       <c r="Q263" t="n">
-        <v>1251000</v>
+        <v>1246500</v>
       </c>
     </row>
     <row r="264">
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11785,19 +11785,19 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N270" t="n">
         <v>13593.35</v>
       </c>
       <c r="O270" t="n">
-        <v>4254718.55</v>
+        <v>4213938.5</v>
       </c>
       <c r="P270" t="n">
         <v>25500</v>
       </c>
       <c r="Q270" t="n">
-        <v>7981500</v>
+        <v>7905000</v>
       </c>
     </row>
     <row r="271">
@@ -12109,13 +12109,13 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>59</v>
@@ -12475,28 +12475,28 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="N286" t="n">
-        <v>2033.5818888889</v>
+        <v>2033.5815122873</v>
       </c>
       <c r="O286" t="n">
-        <v>374179.0675555576</v>
+        <v>368078.2537240013</v>
       </c>
       <c r="P286" t="n">
         <v>4100</v>
       </c>
       <c r="Q286" t="n">
-        <v>754400</v>
+        <v>742100</v>
       </c>
     </row>
     <row r="287">
@@ -12779,10 +12779,10 @@
         <v>2839</v>
       </c>
       <c r="N293" t="n">
-        <v>3158.8608103175</v>
+        <v>3158.8608104732</v>
       </c>
       <c r="O293" t="n">
-        <v>8968005.840491382</v>
+        <v>8968005.840933416</v>
       </c>
       <c r="P293" t="n">
         <v>5600</v>
@@ -12871,10 +12871,10 @@
         <v>235</v>
       </c>
       <c r="N295" t="n">
-        <v>3841.6246462715</v>
+        <v>3841.6246596357</v>
       </c>
       <c r="O295" t="n">
-        <v>902781.7918738024</v>
+        <v>902781.7950143896</v>
       </c>
       <c r="P295" t="n">
         <v>6900</v>
@@ -13041,22 +13041,22 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
         <v>94</v>
       </c>
       <c r="N299" t="n">
-        <v>3230.0679854015</v>
+        <v>3230.0679765396</v>
       </c>
       <c r="O299" t="n">
-        <v>303626.390627741</v>
+        <v>303626.3897947224</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13178,19 +13178,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="N302" t="n">
         <v>1480</v>
       </c>
       <c r="O302" t="n">
-        <v>455840</v>
+        <v>446960</v>
       </c>
       <c r="P302" t="n">
         <v>2600</v>
       </c>
       <c r="Q302" t="n">
-        <v>800800</v>
+        <v>785200</v>
       </c>
     </row>
     <row r="303">
@@ -13302,7 +13302,7 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
@@ -13311,19 +13311,19 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N305" t="n">
         <v>2742</v>
       </c>
       <c r="O305" t="n">
-        <v>230328</v>
+        <v>208392</v>
       </c>
       <c r="P305" t="n">
         <v>3500</v>
       </c>
       <c r="Q305" t="n">
-        <v>294000</v>
+        <v>266000</v>
       </c>
     </row>
     <row r="306">
@@ -13394,7 +13394,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13403,19 +13403,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N307" t="n">
         <v>7507.39</v>
       </c>
       <c r="O307" t="n">
-        <v>2199665.27</v>
+        <v>2192157.88</v>
       </c>
       <c r="P307" t="n">
         <v>13500</v>
       </c>
       <c r="Q307" t="n">
-        <v>3955500</v>
+        <v>3942000</v>
       </c>
     </row>
     <row r="308">
@@ -13724,10 +13724,10 @@
         <v>475</v>
       </c>
       <c r="N314" t="n">
-        <v>3795.7100070249</v>
+        <v>3795.7100070286</v>
       </c>
       <c r="O314" t="n">
-        <v>1802962.253336828</v>
+        <v>1802962.253338585</v>
       </c>
       <c r="P314" t="n">
         <v>6200</v>
@@ -13881,28 +13881,28 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N318" t="n">
         <v>2612.77</v>
       </c>
       <c r="O318" t="n">
-        <v>1452700.12</v>
+        <v>1450087.35</v>
       </c>
       <c r="P318" t="n">
         <v>4900</v>
       </c>
       <c r="Q318" t="n">
-        <v>2724400</v>
+        <v>2719500</v>
       </c>
     </row>
     <row r="319">
@@ -14159,10 +14159,10 @@
         <v>21</v>
       </c>
       <c r="N324" t="n">
-        <v>4967.810952381</v>
+        <v>4967.81144</v>
       </c>
       <c r="O324" t="n">
-        <v>104324.030000001</v>
+        <v>104324.04024</v>
       </c>
       <c r="P324" t="n">
         <v>7500</v>
@@ -14196,28 +14196,28 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>1048</v>
+        <v>985</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>1007</v>
+        <v>985</v>
       </c>
       <c r="N325" t="n">
         <v>1203.38</v>
       </c>
       <c r="O325" t="n">
-        <v>1211803.66</v>
+        <v>1185329.3</v>
       </c>
       <c r="P325" t="n">
         <v>1900</v>
       </c>
       <c r="Q325" t="n">
-        <v>1913300</v>
+        <v>1871500</v>
       </c>
     </row>
     <row r="326">
@@ -14242,28 +14242,28 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N326" t="n">
         <v>3472</v>
       </c>
       <c r="O326" t="n">
-        <v>565936</v>
+        <v>562464</v>
       </c>
       <c r="P326" t="n">
         <v>4800</v>
       </c>
       <c r="Q326" t="n">
-        <v>782400</v>
+        <v>777600</v>
       </c>
     </row>
     <row r="327">
@@ -14421,28 +14421,28 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N330" t="n">
         <v>2331</v>
       </c>
       <c r="O330" t="n">
-        <v>979020</v>
+        <v>974358</v>
       </c>
       <c r="P330" t="n">
         <v>3500</v>
       </c>
       <c r="Q330" t="n">
-        <v>1470000</v>
+        <v>1463000</v>
       </c>
     </row>
     <row r="331">
@@ -14462,13 +14462,13 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M331" t="n">
         <v>530</v>
@@ -14687,13 +14687,13 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M336" t="n">
         <v>29</v>
@@ -14728,13 +14728,13 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
         <v>12</v>
@@ -14810,28 +14810,28 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>799</v>
+        <v>790</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="N339" t="n">
         <v>1789</v>
       </c>
       <c r="O339" t="n">
-        <v>1425833</v>
+        <v>1413310</v>
       </c>
       <c r="P339" t="n">
         <v>2700</v>
       </c>
       <c r="Q339" t="n">
-        <v>2151900</v>
+        <v>2133000</v>
       </c>
     </row>
     <row r="340">
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -14909,19 +14909,19 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N341" t="n">
-        <v>3594.2543127962</v>
+        <v>3594.2542925089</v>
       </c>
       <c r="O341" t="n">
-        <v>1326279.841421798</v>
+        <v>1322685.579643275</v>
       </c>
       <c r="P341" t="n">
         <v>6500</v>
       </c>
       <c r="Q341" t="n">
-        <v>2398500</v>
+        <v>2392000</v>
       </c>
     </row>
     <row r="342">
@@ -14949,28 +14949,28 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>1836</v>
+        <v>1746</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>1762</v>
+        <v>1746</v>
       </c>
       <c r="N342" t="n">
         <v>489.88</v>
       </c>
       <c r="O342" t="n">
-        <v>863168.5599999999</v>
+        <v>855330.48</v>
       </c>
       <c r="P342" t="n">
         <v>700</v>
       </c>
       <c r="Q342" t="n">
-        <v>1233400</v>
+        <v>1222200</v>
       </c>
     </row>
     <row r="343">
@@ -15842,7 +15842,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>2765</v>
+        <v>2751</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15851,19 +15851,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>2765</v>
+        <v>2751</v>
       </c>
       <c r="N363" t="n">
         <v>1441.01</v>
       </c>
       <c r="O363" t="n">
-        <v>3984392.65</v>
+        <v>3964218.51</v>
       </c>
       <c r="P363" t="n">
         <v>2100</v>
       </c>
       <c r="Q363" t="n">
-        <v>5806500</v>
+        <v>5777100</v>
       </c>
     </row>
     <row r="364">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16031,19 +16031,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N367" t="n">
-        <v>4242.5421395349</v>
+        <v>4242.5421445221</v>
       </c>
       <c r="O367" t="n">
-        <v>1718229.566511635</v>
+        <v>1713987.026386928</v>
       </c>
       <c r="P367" t="n">
         <v>5900</v>
       </c>
       <c r="Q367" t="n">
-        <v>2389500</v>
+        <v>2383600</v>
       </c>
     </row>
     <row r="368">
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16121,19 +16121,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="N369" t="n">
-        <v>3041.6600117855</v>
+        <v>3041.6600119048</v>
       </c>
       <c r="O369" t="n">
-        <v>641790.2624867405</v>
+        <v>590082.0423095311</v>
       </c>
       <c r="P369" t="n">
         <v>5500</v>
       </c>
       <c r="Q369" t="n">
-        <v>1160500</v>
+        <v>1067000</v>
       </c>
     </row>
     <row r="370">
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K371" t="n">
         <v>0</v>
@@ -16208,19 +16208,19 @@
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N371" t="n">
         <v>4086.2</v>
       </c>
       <c r="O371" t="n">
-        <v>1924600.2</v>
+        <v>1920514</v>
       </c>
       <c r="P371" t="n">
         <v>6900</v>
       </c>
       <c r="Q371" t="n">
-        <v>3249900</v>
+        <v>3243000</v>
       </c>
     </row>
     <row r="372">
@@ -16371,22 +16371,22 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>660</v>
       </c>
       <c r="N375" t="n">
-        <v>1592.5680015373</v>
+        <v>1592.5679711276</v>
       </c>
       <c r="O375" t="n">
-        <v>1051094.881014618</v>
+        <v>1051094.860944216</v>
       </c>
       <c r="P375" t="n">
         <v>3900</v>
@@ -16540,13 +16540,13 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M379" t="n">
         <v>129</v>
@@ -16881,7 +16881,7 @@
         </is>
       </c>
       <c r="J387" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K387" t="n">
         <v>0</v>
@@ -16890,19 +16890,19 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N387" t="n">
         <v>5633.97</v>
       </c>
       <c r="O387" t="n">
-        <v>383109.96</v>
+        <v>371842.02</v>
       </c>
       <c r="P387" t="n">
         <v>9600</v>
       </c>
       <c r="Q387" t="n">
-        <v>652800</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="388">
@@ -16976,28 +16976,28 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N389" t="n">
         <v>4648.6</v>
       </c>
       <c r="O389" t="n">
-        <v>1264419.2</v>
+        <v>1250473.4</v>
       </c>
       <c r="P389" t="n">
         <v>8900</v>
       </c>
       <c r="Q389" t="n">
-        <v>2420800</v>
+        <v>2394100</v>
       </c>
     </row>
     <row r="390">
@@ -17105,7 +17105,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -17114,19 +17114,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="N392" t="n">
         <v>1312.43</v>
       </c>
       <c r="O392" t="n">
-        <v>1379363.93</v>
+        <v>1376739.07</v>
       </c>
       <c r="P392" t="n">
         <v>2300</v>
       </c>
       <c r="Q392" t="n">
-        <v>2417300</v>
+        <v>2412700</v>
       </c>
     </row>
     <row r="393">
@@ -17231,7 +17231,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -17240,19 +17240,19 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N395" t="n">
         <v>1343.77</v>
       </c>
       <c r="O395" t="n">
-        <v>327879.88</v>
+        <v>326536.11</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
       </c>
       <c r="Q395" t="n">
-        <v>610000</v>
+        <v>607500</v>
       </c>
     </row>
     <row r="396">
@@ -17363,28 +17363,28 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>3196</v>
+        <v>3124</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>3195</v>
+        <v>3124</v>
       </c>
       <c r="N398" t="n">
         <v>1387.55</v>
       </c>
       <c r="O398" t="n">
-        <v>4433222.25</v>
+        <v>4334706.2</v>
       </c>
       <c r="P398" t="n">
         <v>2300</v>
       </c>
       <c r="Q398" t="n">
-        <v>7348500</v>
+        <v>7185200</v>
       </c>
     </row>
     <row r="399">
@@ -17539,13 +17539,13 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
       </c>
       <c r="L402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M402" t="n">
         <v>144</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
@@ -17597,19 +17597,19 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N403" t="n">
         <v>16897</v>
       </c>
       <c r="O403" t="n">
-        <v>1013820</v>
+        <v>980026</v>
       </c>
       <c r="P403" t="n">
         <v>27900</v>
       </c>
       <c r="Q403" t="n">
-        <v>1674000</v>
+        <v>1618200</v>
       </c>
     </row>
     <row r="404">
@@ -18507,28 +18507,28 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N424" t="n">
         <v>3751</v>
       </c>
       <c r="O424" t="n">
-        <v>277574</v>
+        <v>273823</v>
       </c>
       <c r="P424" t="n">
         <v>6400</v>
       </c>
       <c r="Q424" t="n">
-        <v>473600</v>
+        <v>467200</v>
       </c>
     </row>
     <row r="425">
@@ -18597,13 +18597,13 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M426" t="n">
         <v>66</v>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>646</v>
+        <v>614</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -18742,19 +18742,19 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>646</v>
+        <v>614</v>
       </c>
       <c r="N429" t="n">
-        <v>1630.9227791832</v>
+        <v>1630.9228220183</v>
       </c>
       <c r="O429" t="n">
-        <v>1053576.115352347</v>
+        <v>1001386.612719236</v>
       </c>
       <c r="P429" t="n">
         <v>2500</v>
       </c>
       <c r="Q429" t="n">
-        <v>1615000</v>
+        <v>1535000</v>
       </c>
     </row>
     <row r="430">
@@ -18791,10 +18791,10 @@
         <v>14</v>
       </c>
       <c r="N430" t="n">
-        <v>1467.3293594306</v>
+        <v>1467.3289090909</v>
       </c>
       <c r="O430" t="n">
-        <v>20542.6110320284</v>
+        <v>20542.6047272726</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -18825,28 +18825,28 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N431" t="n">
-        <v>1690.6056882022</v>
+        <v>1690.6051240876</v>
       </c>
       <c r="O431" t="n">
-        <v>106508.1583567386</v>
+        <v>38883.9178540148</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
       </c>
       <c r="Q431" t="n">
-        <v>182700</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="432">
@@ -18871,28 +18871,28 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>1396</v>
+        <v>1289</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>1366</v>
+        <v>1289</v>
       </c>
       <c r="N432" t="n">
-        <v>1550.1927149023</v>
+        <v>1550.1927548066</v>
       </c>
       <c r="O432" t="n">
-        <v>2117563.248556542</v>
+        <v>1998198.460945708</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3415000</v>
+        <v>3222500</v>
       </c>
     </row>
     <row r="433">
@@ -18963,28 +18963,28 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>987</v>
+        <v>959</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="N434" t="n">
-        <v>2403.5094737645</v>
+        <v>2403.5095333845</v>
       </c>
       <c r="O434" t="n">
-        <v>2319386.642182742</v>
+        <v>2304965.642515736</v>
       </c>
       <c r="P434" t="n">
         <v>3500</v>
       </c>
       <c r="Q434" t="n">
-        <v>3377500</v>
+        <v>3356500</v>
       </c>
     </row>
     <row r="435">
@@ -19053,28 +19053,28 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N436" t="n">
-        <v>2521.550368364</v>
+        <v>2521.5499887387</v>
       </c>
       <c r="O436" t="n">
-        <v>809417.668244844</v>
+        <v>799331.3464301679</v>
       </c>
       <c r="P436" t="n">
         <v>3900</v>
       </c>
       <c r="Q436" t="n">
-        <v>1251900</v>
+        <v>1236300</v>
       </c>
     </row>
     <row r="437">
@@ -19094,7 +19094,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -19103,19 +19103,19 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N437" t="n">
-        <v>1232.8086134454</v>
+        <v>1232.8083690987</v>
       </c>
       <c r="O437" t="n">
-        <v>80132.559873951</v>
+        <v>77666.92725321811</v>
       </c>
       <c r="P437" t="n">
         <v>2400</v>
       </c>
       <c r="Q437" t="n">
-        <v>156000</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="438">
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -19401,19 +19401,19 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="N444" t="n">
-        <v>893.6788774226</v>
+        <v>893.67886945501</v>
       </c>
       <c r="O444" t="n">
-        <v>277934.1308784286</v>
+        <v>252911.1200557679</v>
       </c>
       <c r="P444" t="n">
         <v>1200</v>
       </c>
       <c r="Q444" t="n">
-        <v>373200</v>
+        <v>339600</v>
       </c>
     </row>
     <row r="445">
@@ -21106,7 +21106,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -21115,19 +21115,19 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N483" t="n">
         <v>6280.31</v>
       </c>
       <c r="O483" t="n">
-        <v>81644.03</v>
+        <v>69083.41</v>
       </c>
       <c r="P483" t="n">
         <v>10500</v>
       </c>
       <c r="Q483" t="n">
-        <v>136500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="484">
@@ -23134,7 +23134,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -23143,19 +23143,19 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N531" t="n">
         <v>8794.48</v>
       </c>
       <c r="O531" t="n">
-        <v>2233797.92</v>
+        <v>2216208.96</v>
       </c>
       <c r="P531" t="n">
         <v>14500</v>
       </c>
       <c r="Q531" t="n">
-        <v>3683000</v>
+        <v>3654000</v>
       </c>
     </row>
     <row r="532">
@@ -23221,13 +23221,13 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M533" t="n">
         <v>387</v>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -23394,19 +23394,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N537" t="n">
         <v>13152</v>
       </c>
       <c r="O537" t="n">
-        <v>1459872</v>
+        <v>1446720</v>
       </c>
       <c r="P537" t="n">
         <v>16900</v>
       </c>
       <c r="Q537" t="n">
-        <v>1875900</v>
+        <v>1859000</v>
       </c>
     </row>
     <row r="538">
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -23435,19 +23435,19 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N538" t="n">
         <v>6652</v>
       </c>
       <c r="O538" t="n">
-        <v>4450188</v>
+        <v>4443536</v>
       </c>
       <c r="P538" t="n">
         <v>5900</v>
       </c>
       <c r="Q538" t="n">
-        <v>3947100</v>
+        <v>3941200</v>
       </c>
     </row>
     <row r="539">
@@ -23552,13 +23552,13 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M541" t="n">
         <v>86</v>
@@ -23593,13 +23593,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>29</v>
@@ -23646,10 +23646,10 @@
         <v>248</v>
       </c>
       <c r="N543" t="n">
-        <v>2029.8734867503</v>
+        <v>2029.8734883721</v>
       </c>
       <c r="O543" t="n">
-        <v>503408.6247140744</v>
+        <v>503408.6251162808</v>
       </c>
       <c r="P543" t="n">
         <v>3600</v>
@@ -24167,13 +24167,13 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M556" t="n">
         <v>138</v>
@@ -24392,10 +24392,10 @@
         <v>185</v>
       </c>
       <c r="N561" t="n">
-        <v>2680.7397015834</v>
+        <v>2680.7397012195</v>
       </c>
       <c r="O561" t="n">
-        <v>495936.844792929</v>
+        <v>495936.8447256075</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
@@ -25727,28 +25727,28 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="N593" t="n">
         <v>3877.89</v>
       </c>
       <c r="O593" t="n">
-        <v>608828.73</v>
+        <v>539026.71</v>
       </c>
       <c r="P593" t="n">
         <v>6500</v>
       </c>
       <c r="Q593" t="n">
-        <v>1020500</v>
+        <v>903500</v>
       </c>
     </row>
     <row r="594">
@@ -25829,10 +25829,10 @@
         <v>5</v>
       </c>
       <c r="N595" t="n">
-        <v>4285.1951004016</v>
+        <v>4285.1951158107</v>
       </c>
       <c r="O595" t="n">
-        <v>21425.975502008</v>
+        <v>21425.9755790535</v>
       </c>
       <c r="P595" t="n">
         <v>6900</v>
@@ -26559,10 +26559,10 @@
         <v>89</v>
       </c>
       <c r="N612" t="n">
-        <v>11562.038560411</v>
+        <v>11562.038549223</v>
       </c>
       <c r="O612" t="n">
-        <v>1029021.431876579</v>
+        <v>1029021.430880847</v>
       </c>
       <c r="P612" t="n">
         <v>18500</v>
@@ -26605,10 +26605,10 @@
         <v>2</v>
       </c>
       <c r="N613" t="n">
-        <v>13513.642867133</v>
+        <v>13513.642887324</v>
       </c>
       <c r="O613" t="n">
-        <v>27027.285734266</v>
+        <v>27027.285774648</v>
       </c>
       <c r="P613" t="n">
         <v>21900</v>
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
@@ -26776,19 +26776,19 @@
         <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N617" t="n">
         <v>1650</v>
       </c>
       <c r="O617" t="n">
-        <v>661650</v>
+        <v>660000</v>
       </c>
       <c r="P617" t="n">
         <v>2900</v>
       </c>
       <c r="Q617" t="n">
-        <v>1162900</v>
+        <v>1160000</v>
       </c>
     </row>
     <row r="618">
@@ -26808,7 +26808,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -26817,19 +26817,19 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="N618" t="n">
         <v>2856</v>
       </c>
       <c r="O618" t="n">
-        <v>368424</v>
+        <v>354144</v>
       </c>
       <c r="P618" t="n">
         <v>2400</v>
       </c>
       <c r="Q618" t="n">
-        <v>309600</v>
+        <v>297600</v>
       </c>
     </row>
     <row r="619">
@@ -26849,28 +26849,28 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N619" t="n">
         <v>926</v>
       </c>
       <c r="O619" t="n">
-        <v>22224</v>
+        <v>15742</v>
       </c>
       <c r="P619" t="n">
         <v>1600</v>
       </c>
       <c r="Q619" t="n">
-        <v>38400</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="620">
@@ -26890,28 +26890,28 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
       </c>
       <c r="L620" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N620" t="n">
         <v>1679</v>
       </c>
       <c r="O620" t="n">
-        <v>711896</v>
+        <v>708538</v>
       </c>
       <c r="P620" t="n">
         <v>2900</v>
       </c>
       <c r="Q620" t="n">
-        <v>1229600</v>
+        <v>1223800</v>
       </c>
     </row>
     <row r="621">
@@ -26972,28 +26972,28 @@
         </is>
       </c>
       <c r="J622" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="K622" t="n">
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M622" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N622" t="n">
         <v>889</v>
       </c>
       <c r="O622" t="n">
-        <v>42672</v>
+        <v>39116</v>
       </c>
       <c r="P622" t="n">
         <v>1500</v>
       </c>
       <c r="Q622" t="n">
-        <v>72000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="623">
@@ -27013,28 +27013,28 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
       </c>
       <c r="L623" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="N623" t="n">
         <v>1664</v>
       </c>
       <c r="O623" t="n">
-        <v>765440</v>
+        <v>758784</v>
       </c>
       <c r="P623" t="n">
         <v>2900</v>
       </c>
       <c r="Q623" t="n">
-        <v>1334000</v>
+        <v>1322400</v>
       </c>
     </row>
     <row r="624">
@@ -27054,28 +27054,28 @@
         </is>
       </c>
       <c r="J624" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="K624" t="n">
         <v>0</v>
       </c>
       <c r="L624" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N624" t="n">
         <v>1358</v>
       </c>
       <c r="O624" t="n">
-        <v>354438</v>
+        <v>351722</v>
       </c>
       <c r="P624" t="n">
         <v>2400</v>
       </c>
       <c r="Q624" t="n">
-        <v>626400</v>
+        <v>621600</v>
       </c>
     </row>
     <row r="625">
@@ -27136,28 +27136,28 @@
         </is>
       </c>
       <c r="J626" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="K626" t="n">
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M626" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N626" t="n">
         <v>3451</v>
       </c>
       <c r="O626" t="n">
-        <v>1577107</v>
+        <v>1566754</v>
       </c>
       <c r="P626" t="n">
         <v>2900</v>
       </c>
       <c r="Q626" t="n">
-        <v>1325300</v>
+        <v>1316600</v>
       </c>
     </row>
     <row r="627">
@@ -27177,13 +27177,13 @@
         </is>
       </c>
       <c r="J627" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
       <c r="L627" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M627" t="n">
         <v>201</v>
@@ -27259,7 +27259,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -27268,19 +27268,19 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N629" t="n">
         <v>1627</v>
       </c>
       <c r="O629" t="n">
-        <v>652427</v>
+        <v>650800</v>
       </c>
       <c r="P629" t="n">
         <v>2900</v>
       </c>
       <c r="Q629" t="n">
-        <v>1162900</v>
+        <v>1160000</v>
       </c>
     </row>
     <row r="630">
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -27309,19 +27309,19 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="N630" t="n">
         <v>2737</v>
       </c>
       <c r="O630" t="n">
-        <v>1253546</v>
+        <v>1228913</v>
       </c>
       <c r="P630" t="n">
         <v>2300</v>
       </c>
       <c r="Q630" t="n">
-        <v>1053400</v>
+        <v>1032700</v>
       </c>
     </row>
     <row r="631">
@@ -27382,13 +27382,13 @@
         </is>
       </c>
       <c r="J632" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
       </c>
       <c r="L632" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M632" t="n">
         <v>336</v>
@@ -28061,7 +28061,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -28070,19 +28070,19 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="N648" t="n">
         <v>4793.53</v>
       </c>
       <c r="O648" t="n">
-        <v>1773606.1</v>
+        <v>1744844.92</v>
       </c>
       <c r="P648" t="n">
         <v>7900</v>
       </c>
       <c r="Q648" t="n">
-        <v>2923000</v>
+        <v>2875600</v>
       </c>
     </row>
     <row r="649">
@@ -28189,13 +28189,13 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M651" t="n">
         <v>245</v>
@@ -28230,7 +28230,7 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -28239,19 +28239,19 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N652" t="n">
         <v>8300</v>
       </c>
       <c r="O652" t="n">
-        <v>913000</v>
+        <v>888100</v>
       </c>
       <c r="P652" t="n">
         <v>14900</v>
       </c>
       <c r="Q652" t="n">
-        <v>1639000</v>
+        <v>1594300</v>
       </c>
     </row>
     <row r="653">
@@ -28276,13 +28276,13 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
       </c>
       <c r="L653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M653" t="n">
         <v>58</v>
@@ -28450,13 +28450,13 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M657" t="n">
         <v>52</v>
@@ -28829,7 +28829,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -28838,19 +28838,19 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N666" t="n">
         <v>16974.69</v>
       </c>
       <c r="O666" t="n">
-        <v>1612595.55</v>
+        <v>1595620.86</v>
       </c>
       <c r="P666" t="n">
         <v>26900</v>
       </c>
       <c r="Q666" t="n">
-        <v>2555500</v>
+        <v>2528600</v>
       </c>
     </row>
     <row r="667">
@@ -29085,13 +29085,13 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
       </c>
       <c r="L672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M672" t="n">
         <v>33</v>
@@ -29259,28 +29259,28 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="N676" t="n">
-        <v>1560.9978377282</v>
+        <v>1560.9979018405</v>
       </c>
       <c r="O676" t="n">
-        <v>920988.724259638</v>
+        <v>902256.787263809</v>
       </c>
       <c r="P676" t="n">
         <v>2900</v>
       </c>
       <c r="Q676" t="n">
-        <v>1711000</v>
+        <v>1676200</v>
       </c>
     </row>
     <row r="677">
@@ -29305,28 +29305,28 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N677" t="n">
         <v>3487.53</v>
       </c>
       <c r="O677" t="n">
-        <v>108113.43</v>
+        <v>104625.9</v>
       </c>
       <c r="P677" t="n">
         <v>6500</v>
       </c>
       <c r="Q677" t="n">
-        <v>201500</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="678">
@@ -30198,10 +30198,10 @@
         <v>21</v>
       </c>
       <c r="N698" t="n">
-        <v>9994.7101388889</v>
+        <v>9994.7101428571</v>
       </c>
       <c r="O698" t="n">
-        <v>209888.9129166669</v>
+        <v>209888.9129999991</v>
       </c>
       <c r="P698" t="n">
         <v>20800</v>
@@ -31328,7 +31328,7 @@
         </is>
       </c>
       <c r="J725" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K725" t="n">
         <v>0</v>
@@ -31337,19 +31337,19 @@
         <v>0</v>
       </c>
       <c r="M725" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N725" t="n">
         <v>4534.2</v>
       </c>
       <c r="O725" t="n">
-        <v>95218.2</v>
+        <v>90684</v>
       </c>
       <c r="P725" t="n">
         <v>7900</v>
       </c>
       <c r="Q725" t="n">
-        <v>165900</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="726">
@@ -31461,13 +31461,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M728" t="n">
         <v>101</v>
@@ -31507,28 +31507,28 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M729" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N729" t="n">
-        <v>3113.8900216685</v>
+        <v>3113.8900218818</v>
       </c>
       <c r="O729" t="n">
-        <v>267794.541863491</v>
+        <v>239769.5316848986</v>
       </c>
       <c r="P729" t="n">
         <v>5000</v>
       </c>
       <c r="Q729" t="n">
-        <v>430000</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="730">
@@ -31553,13 +31553,13 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M730" t="n">
         <v>34</v>
@@ -31645,13 +31645,13 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M732" t="n">
         <v>96</v>
@@ -31691,13 +31691,13 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M733" t="n">
         <v>52</v>
@@ -31783,13 +31783,13 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M735" t="n">
         <v>19</v>
@@ -31829,28 +31829,28 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N736" t="n">
         <v>2495.98</v>
       </c>
       <c r="O736" t="n">
-        <v>297021.62</v>
+        <v>289533.68</v>
       </c>
       <c r="P736" t="n">
         <v>4100</v>
       </c>
       <c r="Q736" t="n">
-        <v>487900</v>
+        <v>475600</v>
       </c>
     </row>
     <row r="737">
@@ -31921,13 +31921,13 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M738" t="n">
         <v>28</v>
@@ -31967,28 +31967,28 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M739" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N739" t="n">
-        <v>1595.0095814978</v>
+        <v>1595.0095763657</v>
       </c>
       <c r="O739" t="n">
-        <v>43065.25870044059</v>
+        <v>33495.2011036797</v>
       </c>
       <c r="P739" t="n">
         <v>2600</v>
       </c>
       <c r="Q739" t="n">
-        <v>70200</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="740">
@@ -32108,28 +32108,28 @@
         </is>
       </c>
       <c r="J742" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K742" t="n">
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M742" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N742" t="n">
         <v>4227.77</v>
       </c>
       <c r="O742" t="n">
-        <v>126833.1</v>
+        <v>101466.48</v>
       </c>
       <c r="P742" t="n">
         <v>6900</v>
       </c>
       <c r="Q742" t="n">
-        <v>207000</v>
+        <v>165600</v>
       </c>
     </row>
     <row r="743">
@@ -32200,13 +32200,13 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M744" t="n">
         <v>40</v>
@@ -32246,13 +32246,13 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M745" t="n">
         <v>82</v>
@@ -32338,28 +32338,28 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M747" t="n">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="N747" t="n">
-        <v>1664.3625947335</v>
+        <v>1664.3622356902</v>
       </c>
       <c r="O747" t="n">
-        <v>309571.442620431</v>
+        <v>269626.6821818124</v>
       </c>
       <c r="P747" t="n">
         <v>2900</v>
       </c>
       <c r="Q747" t="n">
-        <v>539400</v>
+        <v>469800</v>
       </c>
     </row>
     <row r="748">
@@ -32384,28 +32384,28 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N748" t="n">
         <v>15502</v>
       </c>
       <c r="O748" t="n">
-        <v>217028</v>
+        <v>201526</v>
       </c>
       <c r="P748" t="n">
         <v>25900</v>
       </c>
       <c r="Q748" t="n">
-        <v>362600</v>
+        <v>336700</v>
       </c>
     </row>
     <row r="749">
@@ -33026,13 +33026,13 @@
         </is>
       </c>
       <c r="J762" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K762" t="n">
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M762" t="n">
         <v>12</v>
@@ -33302,7 +33302,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -33311,19 +33311,19 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="N768" t="n">
-        <v>1778.4724843483</v>
+        <v>1778.4724932172</v>
       </c>
       <c r="O768" t="n">
-        <v>2242653.802763206</v>
+        <v>2228426.034001152</v>
       </c>
       <c r="P768" t="n">
         <v>4900</v>
       </c>
       <c r="Q768" t="n">
-        <v>6178900</v>
+        <v>6139700</v>
       </c>
     </row>
     <row r="769">
@@ -33348,7 +33348,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -33357,19 +33357,19 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N769" t="n">
         <v>2325</v>
       </c>
       <c r="O769" t="n">
-        <v>785850</v>
+        <v>771900</v>
       </c>
       <c r="P769" t="n">
         <v>4900</v>
       </c>
       <c r="Q769" t="n">
-        <v>1656200</v>
+        <v>1626800</v>
       </c>
     </row>
     <row r="770">
@@ -35288,13 +35288,13 @@
         </is>
       </c>
       <c r="J811" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K811" t="n">
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M811" t="n">
         <v>196</v>
@@ -35840,22 +35840,22 @@
         </is>
       </c>
       <c r="J823" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="K823" t="n">
         <v>0</v>
       </c>
       <c r="L823" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M823" t="n">
         <v>152</v>
       </c>
       <c r="N823" t="n">
-        <v>2252.2960568182</v>
+        <v>2252.2960775371</v>
       </c>
       <c r="O823" t="n">
-        <v>342349.0006363664</v>
+        <v>342349.0037856392</v>
       </c>
       <c r="P823" t="n">
         <v>3900</v>
@@ -36073,7 +36073,7 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
@@ -36082,19 +36082,19 @@
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N828" t="n">
-        <v>2328.1187675234</v>
+        <v>2328.1187653599</v>
       </c>
       <c r="O828" t="n">
-        <v>1091887.701968475</v>
+        <v>1082575.225892354</v>
       </c>
       <c r="P828" t="n">
         <v>4500</v>
       </c>
       <c r="Q828" t="n">
-        <v>2110500</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="829">
@@ -36303,7 +36303,7 @@
         </is>
       </c>
       <c r="J833" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K833" t="n">
         <v>0</v>
@@ -36312,19 +36312,19 @@
         <v>0</v>
       </c>
       <c r="M833" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N833" t="n">
         <v>3519</v>
       </c>
       <c r="O833" t="n">
-        <v>285039</v>
+        <v>270963</v>
       </c>
       <c r="P833" t="n">
         <v>5900</v>
       </c>
       <c r="Q833" t="n">
-        <v>477900</v>
+        <v>454300</v>
       </c>
     </row>
     <row r="834">
@@ -36717,13 +36717,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>24</v>
@@ -36809,22 +36809,22 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K844" t="n">
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M844" t="n">
         <v>15</v>
       </c>
       <c r="N844" t="n">
-        <v>4907.8218486172</v>
+        <v>4907.8218731563</v>
       </c>
       <c r="O844" t="n">
-        <v>73617.327729258</v>
+        <v>73617.32809734451</v>
       </c>
       <c r="P844" t="n">
         <v>8200</v>
@@ -38276,13 +38276,13 @@
         </is>
       </c>
       <c r="J876" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K876" t="n">
         <v>0</v>
       </c>
       <c r="L876" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M876" t="n">
         <v>98</v>
@@ -39470,28 +39470,28 @@
         </is>
       </c>
       <c r="J902" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K902" t="n">
         <v>0</v>
       </c>
       <c r="L902" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M902" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N902" t="n">
         <v>3639.35</v>
       </c>
       <c r="O902" t="n">
-        <v>76426.34999999999</v>
+        <v>65508.3</v>
       </c>
       <c r="P902" t="n">
         <v>7500</v>
       </c>
       <c r="Q902" t="n">
-        <v>157500</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="903">
@@ -39516,13 +39516,13 @@
         </is>
       </c>
       <c r="J903" t="n">
-        <v>1763</v>
+        <v>1760</v>
       </c>
       <c r="K903" t="n">
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M903" t="n">
         <v>1760</v>
@@ -39562,7 +39562,7 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
@@ -39571,19 +39571,19 @@
         <v>0</v>
       </c>
       <c r="M904" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N904" t="n">
         <v>10713.21</v>
       </c>
       <c r="O904" t="n">
-        <v>246403.83</v>
+        <v>224977.41</v>
       </c>
       <c r="P904" t="n">
         <v>20900</v>
       </c>
       <c r="Q904" t="n">
-        <v>480700</v>
+        <v>438900</v>
       </c>
     </row>
     <row r="905">
@@ -39608,13 +39608,13 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
       </c>
       <c r="L905" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M905" t="n">
         <v>1</v>
@@ -40071,7 +40071,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40080,19 +40080,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="N915" t="n">
         <v>1337.29</v>
       </c>
       <c r="O915" t="n">
-        <v>127042.55</v>
+        <v>112332.36</v>
       </c>
       <c r="P915" t="n">
         <v>2600</v>
       </c>
       <c r="Q915" t="n">
-        <v>247000</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="916">
@@ -40175,10 +40175,10 @@
         <v>1327</v>
       </c>
       <c r="N917" t="n">
-        <v>1516.0388215585</v>
+        <v>1516.0388206553</v>
       </c>
       <c r="O917" t="n">
-        <v>2011783.51620813</v>
+        <v>2011783.515009583</v>
       </c>
       <c r="P917" t="n">
         <v>2300</v>
@@ -40209,28 +40209,28 @@
         </is>
       </c>
       <c r="J918" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="K918" t="n">
         <v>0</v>
       </c>
       <c r="L918" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M918" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="N918" t="n">
-        <v>4248.60975</v>
+        <v>4248.6103213611</v>
       </c>
       <c r="O918" t="n">
-        <v>556567.8772499999</v>
+        <v>497087.4075992487</v>
       </c>
       <c r="P918" t="n">
         <v>5900</v>
       </c>
       <c r="Q918" t="n">
-        <v>772900</v>
+        <v>690300</v>
       </c>
     </row>
     <row r="919">
@@ -40299,7 +40299,7 @@
         </is>
       </c>
       <c r="J920" t="n">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="K920" t="n">
         <v>0</v>
@@ -40308,19 +40308,19 @@
         <v>0</v>
       </c>
       <c r="M920" t="n">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="N920" t="n">
-        <v>2458.513771616</v>
+        <v>2458.5136716147</v>
       </c>
       <c r="O920" t="n">
-        <v>882606.4440101441</v>
+        <v>759680.7245289423</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
       </c>
       <c r="Q920" t="n">
-        <v>1256500</v>
+        <v>1081500</v>
       </c>
     </row>
     <row r="921">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40354,19 +40354,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="N921" t="n">
-        <v>1907.3948946136</v>
+        <v>1907.3946829268</v>
       </c>
       <c r="O921" t="n">
-        <v>162128.566042156</v>
+        <v>114443.680975608</v>
       </c>
       <c r="P921" t="n">
         <v>2500</v>
       </c>
       <c r="Q921" t="n">
-        <v>212500</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="922">
@@ -40391,7 +40391,7 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
@@ -40400,19 +40400,19 @@
         <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="N922" t="n">
-        <v>1771.0916367843</v>
+        <v>1771.0915140845</v>
       </c>
       <c r="O922" t="n">
-        <v>366615.9688143501</v>
+        <v>322338.655563379</v>
       </c>
       <c r="P922" t="n">
         <v>2500</v>
       </c>
       <c r="Q922" t="n">
-        <v>517500</v>
+        <v>455000</v>
       </c>
     </row>
     <row r="923">
@@ -40437,28 +40437,28 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N923" t="n">
-        <v>2079.3844162754</v>
+        <v>2079.3843686869</v>
       </c>
       <c r="O923" t="n">
-        <v>806801.1535148552</v>
+        <v>804721.7506818303</v>
       </c>
       <c r="P923" t="n">
         <v>2900</v>
       </c>
       <c r="Q923" t="n">
-        <v>1125200</v>
+        <v>1122300</v>
       </c>
     </row>
     <row r="924">
@@ -40483,28 +40483,28 @@
         </is>
       </c>
       <c r="J924" t="n">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="K924" t="n">
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M924" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N924" t="n">
-        <v>1803.0147201337</v>
+        <v>1803.0147280335</v>
       </c>
       <c r="O924" t="n">
-        <v>760872.2118964214</v>
+        <v>759069.2005021035</v>
       </c>
       <c r="P924" t="n">
         <v>2500</v>
       </c>
       <c r="Q924" t="n">
-        <v>1055000</v>
+        <v>1052500</v>
       </c>
     </row>
     <row r="925">
@@ -40575,22 +40575,22 @@
         </is>
       </c>
       <c r="J926" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K926" t="n">
         <v>0</v>
       </c>
       <c r="L926" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M926" t="n">
         <v>51</v>
       </c>
       <c r="N926" t="n">
-        <v>2122.1642147294</v>
+        <v>2122.1642044444</v>
       </c>
       <c r="O926" t="n">
-        <v>108230.3749511994</v>
+        <v>108230.3744266644</v>
       </c>
       <c r="P926" t="n">
         <v>2900</v>
@@ -40621,28 +40621,28 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M927" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N927" t="n">
-        <v>2108.7892332099</v>
+        <v>2108.7892625995</v>
       </c>
       <c r="O927" t="n">
-        <v>350059.0127128434</v>
+        <v>347950.2283289175</v>
       </c>
       <c r="P927" t="n">
         <v>2900</v>
       </c>
       <c r="Q927" t="n">
-        <v>481400</v>
+        <v>478500</v>
       </c>
     </row>
     <row r="928">
@@ -40667,22 +40667,22 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M928" t="n">
         <v>413</v>
       </c>
       <c r="N928" t="n">
-        <v>2056.0840977981</v>
+        <v>2056.0840859599</v>
       </c>
       <c r="O928" t="n">
-        <v>849162.7323906154</v>
+        <v>849162.7275014388</v>
       </c>
       <c r="P928" t="n">
         <v>2900</v>
@@ -40713,13 +40713,13 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M929" t="n">
         <v>244</v>
@@ -40759,7 +40759,7 @@
         </is>
       </c>
       <c r="J930" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K930" t="n">
         <v>0</v>
@@ -40768,19 +40768,19 @@
         <v>0</v>
       </c>
       <c r="M930" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N930" t="n">
-        <v>1655.9315670732</v>
+        <v>1655.9315593531</v>
       </c>
       <c r="O930" t="n">
-        <v>559704.8696707416</v>
+        <v>556393.0039426417</v>
       </c>
       <c r="P930" t="n">
         <v>2500</v>
       </c>
       <c r="Q930" t="n">
-        <v>845000</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="931">
@@ -40946,7 +40946,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -40955,19 +40955,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="N934" t="n">
         <v>2454</v>
       </c>
       <c r="O934" t="n">
-        <v>1403688</v>
+        <v>1384056</v>
       </c>
       <c r="P934" t="n">
         <v>4200</v>
       </c>
       <c r="Q934" t="n">
-        <v>2402400</v>
+        <v>2368800</v>
       </c>
     </row>
     <row r="935">
@@ -40992,22 +40992,22 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M935" t="n">
         <v>636</v>
       </c>
       <c r="N935" t="n">
-        <v>1592.2739613309</v>
+        <v>1592.2740100137</v>
       </c>
       <c r="O935" t="n">
-        <v>1012686.239406452</v>
+        <v>1012686.270368713</v>
       </c>
       <c r="P935" t="n">
         <v>2500</v>
@@ -41135,10 +41135,10 @@
         <v>237</v>
       </c>
       <c r="N938" t="n">
-        <v>2311.9289139073</v>
+        <v>2311.9281444759</v>
       </c>
       <c r="O938" t="n">
-        <v>547927.15259603</v>
+        <v>547926.9702407883</v>
       </c>
       <c r="P938" t="n">
         <v>3500</v>
@@ -41181,10 +41181,10 @@
         <v>209</v>
       </c>
       <c r="N939" t="n">
-        <v>1906.1879253112</v>
+        <v>1906.1878571429</v>
       </c>
       <c r="O939" t="n">
-        <v>398393.2763900408</v>
+        <v>398393.2621428661</v>
       </c>
       <c r="P939" t="n">
         <v>2900</v>
@@ -41215,28 +41215,28 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M940" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N940" t="n">
-        <v>3033.732946593</v>
+        <v>3033.7328518519</v>
       </c>
       <c r="O940" t="n">
-        <v>813040.4296869241</v>
+        <v>803939.2057407534</v>
       </c>
       <c r="P940" t="n">
         <v>4500</v>
       </c>
       <c r="Q940" t="n">
-        <v>1206000</v>
+        <v>1192500</v>
       </c>
     </row>
     <row r="941">
@@ -41261,7 +41261,7 @@
         </is>
       </c>
       <c r="J941" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="K941" t="n">
         <v>0</v>
@@ -41270,19 +41270,19 @@
         <v>0</v>
       </c>
       <c r="M941" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="N941" t="n">
-        <v>1668.6118590522</v>
+        <v>1668.6124489796</v>
       </c>
       <c r="O941" t="n">
-        <v>440513.5307897808</v>
+        <v>420490.3371428592</v>
       </c>
       <c r="P941" t="n">
         <v>2500</v>
       </c>
       <c r="Q941" t="n">
-        <v>660000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="942">
@@ -41319,10 +41319,10 @@
         <v>195</v>
       </c>
       <c r="N942" t="n">
-        <v>2546.9862532982</v>
+        <v>2546.9861569689</v>
       </c>
       <c r="O942" t="n">
-        <v>496662.3193931491</v>
+        <v>496662.3006089355</v>
       </c>
       <c r="P942" t="n">
         <v>3900</v>
@@ -41353,7 +41353,7 @@
         </is>
       </c>
       <c r="J943" t="n">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="K943" t="n">
         <v>0</v>
@@ -41362,19 +41362,19 @@
         <v>0</v>
       </c>
       <c r="M943" t="n">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="N943" t="n">
-        <v>1259.274157743</v>
+        <v>1259.2741948888</v>
       </c>
       <c r="O943" t="n">
-        <v>1421720.524091847</v>
+        <v>1419202.017639678</v>
       </c>
       <c r="P943" t="n">
         <v>1900</v>
       </c>
       <c r="Q943" t="n">
-        <v>2145100</v>
+        <v>2141300</v>
       </c>
     </row>
     <row r="944">
@@ -41532,28 +41532,28 @@
         </is>
       </c>
       <c r="J947" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K947" t="n">
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M947" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N947" t="n">
-        <v>2556.7441826923</v>
+        <v>2556.7442028986</v>
       </c>
       <c r="O947" t="n">
-        <v>416749.3017788449</v>
+        <v>411635.8166666746</v>
       </c>
       <c r="P947" t="n">
         <v>3900</v>
       </c>
       <c r="Q947" t="n">
-        <v>635700</v>
+        <v>627900</v>
       </c>
     </row>
     <row r="948">
@@ -41576,7 +41576,7 @@
         </is>
       </c>
       <c r="J948" t="n">
-        <v>2806</v>
+        <v>2782</v>
       </c>
       <c r="K948" t="n">
         <v>0</v>
@@ -41585,19 +41585,19 @@
         <v>0</v>
       </c>
       <c r="M948" t="n">
-        <v>2806</v>
+        <v>2782</v>
       </c>
       <c r="N948" t="n">
-        <v>692.15197854077</v>
+        <v>692.1519887834301</v>
       </c>
       <c r="O948" t="n">
-        <v>1942178.451785401</v>
+        <v>1925566.832795502</v>
       </c>
       <c r="P948" t="n">
         <v>1200</v>
       </c>
       <c r="Q948" t="n">
-        <v>3367200</v>
+        <v>3338400</v>
       </c>
     </row>
     <row r="949">
@@ -41903,7 +41903,7 @@
         </is>
       </c>
       <c r="J955" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K955" t="n">
         <v>0</v>
@@ -41912,19 +41912,19 @@
         <v>0</v>
       </c>
       <c r="M955" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N955" t="n">
         <v>5510.92</v>
       </c>
       <c r="O955" t="n">
-        <v>44087.36</v>
+        <v>38576.44</v>
       </c>
       <c r="P955" t="n">
         <v>4900</v>
       </c>
       <c r="Q955" t="n">
-        <v>39200</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="956">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="J962" t="n">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K962" t="n">
         <v>0</v>
@@ -42241,19 +42241,19 @@
         <v>0</v>
       </c>
       <c r="M962" t="n">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N962" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O962" t="n">
-        <v>3774950.36</v>
+        <v>3721278.08</v>
       </c>
       <c r="P962" t="n">
         <v>14900</v>
       </c>
       <c r="Q962" t="n">
-        <v>6287800</v>
+        <v>6198400</v>
       </c>
     </row>
     <row r="963">
@@ -42967,7 +42967,7 @@
         </is>
       </c>
       <c r="J978" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K978" t="n">
         <v>0</v>
@@ -42976,19 +42976,19 @@
         <v>0</v>
       </c>
       <c r="M978" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="N978" t="n">
-        <v>872.15418355185</v>
+        <v>872.15418521463</v>
       </c>
       <c r="O978" t="n">
-        <v>460497.4089153768</v>
+        <v>459625.25560811</v>
       </c>
       <c r="P978" t="n">
         <v>1200</v>
       </c>
       <c r="Q978" t="n">
-        <v>633600</v>
+        <v>632400</v>
       </c>
     </row>
     <row r="979">
@@ -43104,7 +43104,7 @@
         </is>
       </c>
       <c r="J981" t="n">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="K981" t="n">
         <v>0</v>
@@ -43113,19 +43113,19 @@
         <v>0</v>
       </c>
       <c r="M981" t="n">
-        <v>1595</v>
+        <v>1561</v>
       </c>
       <c r="N981" t="n">
-        <v>711.33665411716</v>
+        <v>711.33665018328</v>
       </c>
       <c r="O981" t="n">
-        <v>1134581.96331687</v>
+        <v>1110396.5109361</v>
       </c>
       <c r="P981" t="n">
         <v>900</v>
       </c>
       <c r="Q981" t="n">
-        <v>1435500</v>
+        <v>1404900</v>
       </c>
     </row>
     <row r="982">
@@ -43160,10 +43160,10 @@
         <v>351</v>
       </c>
       <c r="N982" t="n">
-        <v>2286.1662924282</v>
+        <v>2286.1662851537</v>
       </c>
       <c r="O982" t="n">
-        <v>802444.3686422982</v>
+        <v>802444.3660889487</v>
       </c>
       <c r="P982" t="n">
         <v>3000</v>
@@ -43546,10 +43546,10 @@
         <v>34</v>
       </c>
       <c r="N991" t="n">
-        <v>1415.1367741935</v>
+        <v>1415.1363934426</v>
       </c>
       <c r="O991" t="n">
-        <v>48114.650322579</v>
+        <v>48114.6373770484</v>
       </c>
       <c r="P991" t="n">
         <v>2500</v>
@@ -43712,28 +43712,28 @@
         </is>
       </c>
       <c r="J995" t="n">
-        <v>2477</v>
+        <v>2353</v>
       </c>
       <c r="K995" t="n">
         <v>0</v>
       </c>
       <c r="L995" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M995" t="n">
-        <v>2421</v>
+        <v>2353</v>
       </c>
       <c r="N995" t="n">
-        <v>517.28700890476</v>
+        <v>517.28707627294</v>
       </c>
       <c r="O995" t="n">
-        <v>1252351.848558424</v>
+        <v>1217176.490470228</v>
       </c>
       <c r="P995" t="n">
         <v>900</v>
       </c>
       <c r="Q995" t="n">
-        <v>2178900</v>
+        <v>2117700</v>
       </c>
     </row>
     <row r="996">
@@ -43897,28 +43897,28 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
       </c>
       <c r="L999" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M999" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="N999" t="n">
-        <v>3110.8439531303</v>
+        <v>3110.8438819661</v>
       </c>
       <c r="O999" t="n">
-        <v>5350651.599384116</v>
+        <v>5344429.78921776</v>
       </c>
       <c r="P999" t="n">
         <v>4500</v>
       </c>
       <c r="Q999" t="n">
-        <v>7740000</v>
+        <v>7731000</v>
       </c>
     </row>
     <row r="1000">
@@ -44029,28 +44029,28 @@
         </is>
       </c>
       <c r="J1002" t="n">
-        <v>15650</v>
+        <v>15478</v>
       </c>
       <c r="K1002" t="n">
         <v>0</v>
       </c>
       <c r="L1002" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1002" t="n">
-        <v>15638</v>
+        <v>15478</v>
       </c>
       <c r="N1002" t="n">
-        <v>703.79555062954</v>
+        <v>703.79553851454</v>
       </c>
       <c r="O1002" t="n">
-        <v>11005954.82074475</v>
+        <v>10893347.34512805</v>
       </c>
       <c r="P1002" t="n">
         <v>900</v>
       </c>
       <c r="Q1002" t="n">
-        <v>14074200</v>
+        <v>13930200</v>
       </c>
     </row>
     <row r="1003">
@@ -44131,10 +44131,10 @@
         <v>45</v>
       </c>
       <c r="N1004" t="n">
-        <v>3006.0208256881</v>
+        <v>3006.0208333333</v>
       </c>
       <c r="O1004" t="n">
-        <v>135270.9371559645</v>
+        <v>135270.9374999985</v>
       </c>
       <c r="P1004" t="n">
         <v>3900</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="J1010" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K1010" t="n">
         <v>0</v>
@@ -44398,19 +44398,19 @@
         <v>0</v>
       </c>
       <c r="M1010" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N1010" t="n">
         <v>1937</v>
       </c>
       <c r="O1010" t="n">
-        <v>834847</v>
+        <v>832910</v>
       </c>
       <c r="P1010" t="n">
         <v>3300</v>
       </c>
       <c r="Q1010" t="n">
-        <v>1422300</v>
+        <v>1419000</v>
       </c>
     </row>
     <row r="1011">
@@ -44474,7 +44474,7 @@
         </is>
       </c>
       <c r="J1012" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1012" t="n">
         <v>0</v>
@@ -44483,19 +44483,19 @@
         <v>0</v>
       </c>
       <c r="M1012" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N1012" t="n">
         <v>2525.02</v>
       </c>
       <c r="O1012" t="n">
-        <v>73225.58</v>
+        <v>70700.56</v>
       </c>
       <c r="P1012" t="n">
         <v>3000</v>
       </c>
       <c r="Q1012" t="n">
-        <v>87000</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="1013">
@@ -44527,10 +44527,10 @@
         <v>430</v>
       </c>
       <c r="N1013" t="n">
-        <v>2077.494338843</v>
+        <v>2077.4944179523</v>
       </c>
       <c r="O1013" t="n">
-        <v>893322.56570249</v>
+        <v>893322.599719489</v>
       </c>
       <c r="P1013" t="n">
         <v>2900</v>
@@ -44784,10 +44784,10 @@
         <v>81</v>
       </c>
       <c r="N1019" t="n">
-        <v>1595.5196827833</v>
+        <v>1595.5196456996</v>
       </c>
       <c r="O1019" t="n">
-        <v>129237.0943054473</v>
+        <v>129237.0913016676</v>
       </c>
       <c r="P1019" t="n">
         <v>2500</v>
@@ -44818,13 +44818,13 @@
         </is>
       </c>
       <c r="J1020" t="n">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="K1020" t="n">
         <v>0</v>
       </c>
       <c r="L1020" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M1020" t="n">
         <v>433</v>
@@ -45953,7 +45953,7 @@
         </is>
       </c>
       <c r="J1044" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K1044" t="n">
         <v>0</v>
@@ -45962,19 +45962,19 @@
         <v>0</v>
       </c>
       <c r="M1044" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N1044" t="n">
-        <v>1322.9251724138</v>
+        <v>1322.925</v>
       </c>
       <c r="O1044" t="n">
-        <v>9260.476206896601</v>
+        <v>6614.625</v>
       </c>
       <c r="P1044" t="n">
         <v>7900</v>
       </c>
       <c r="Q1044" t="n">
-        <v>55300</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="1045">
@@ -46695,7 +46695,7 @@
         </is>
       </c>
       <c r="J1060" t="n">
-        <v>1101</v>
+        <v>1075</v>
       </c>
       <c r="K1060" t="n">
         <v>0</v>
@@ -46704,19 +46704,19 @@
         <v>0</v>
       </c>
       <c r="M1060" t="n">
-        <v>1101</v>
+        <v>1075</v>
       </c>
       <c r="N1060" t="n">
-        <v>1783.7989012952</v>
+        <v>1783.7988883868</v>
       </c>
       <c r="O1060" t="n">
-        <v>1963962.590326015</v>
+        <v>1917583.80501581</v>
       </c>
       <c r="P1060" t="n">
         <v>1500</v>
       </c>
       <c r="Q1060" t="n">
-        <v>1651500</v>
+        <v>1612500</v>
       </c>
     </row>
     <row r="1061">
@@ -48366,10 +48366,10 @@
         <v>43</v>
       </c>
       <c r="N1095" t="n">
-        <v>7046.9398312236</v>
+        <v>7046.9398310097</v>
       </c>
       <c r="O1095" t="n">
-        <v>303018.4127426148</v>
+        <v>303018.4127334171</v>
       </c>
       <c r="P1095" t="n">
         <v>9900</v>
@@ -48493,13 +48493,13 @@
         </is>
       </c>
       <c r="J1098" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1098" t="n">
         <v>29</v>
@@ -48597,10 +48597,10 @@
         <v>24</v>
       </c>
       <c r="N1100" t="n">
-        <v>44113.603597884</v>
+        <v>44113.603675676</v>
       </c>
       <c r="O1100" t="n">
-        <v>1058726.486349216</v>
+        <v>1058726.488216224</v>
       </c>
       <c r="P1100" t="n">
         <v>71900</v>
@@ -48727,7 +48727,7 @@
         </is>
       </c>
       <c r="J1103" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K1103" t="n">
         <v>0</v>
@@ -48736,19 +48736,19 @@
         <v>0</v>
       </c>
       <c r="M1103" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="N1103" t="n">
-        <v>2397.6389361702</v>
+        <v>2397.6836666667</v>
       </c>
       <c r="O1103" t="n">
-        <v>81519.7238297868</v>
+        <v>40760.6223333339</v>
       </c>
       <c r="P1103" t="n">
         <v>2000</v>
       </c>
       <c r="Q1103" t="n">
-        <v>68000</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="1104">
@@ -48920,7 +48920,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -48929,19 +48929,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1107" t="n">
         <v>3155</v>
       </c>
       <c r="O1107" t="n">
-        <v>12620</v>
+        <v>9465</v>
       </c>
       <c r="P1107" t="n">
         <v>5900</v>
       </c>
       <c r="Q1107" t="n">
-        <v>23600</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="1108">
@@ -49231,13 +49231,13 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1114" t="n">
         <v>762</v>
@@ -49272,7 +49272,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49281,19 +49281,19 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="N1115" t="n">
         <v>1267</v>
       </c>
       <c r="O1115" t="n">
-        <v>584087</v>
+        <v>573951</v>
       </c>
       <c r="P1115" t="n">
         <v>1900</v>
       </c>
       <c r="Q1115" t="n">
-        <v>875900</v>
+        <v>860700</v>
       </c>
     </row>
     <row r="1116">
@@ -49489,7 +49489,7 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
@@ -49498,19 +49498,19 @@
         <v>0</v>
       </c>
       <c r="M1120" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N1120" t="n">
         <v>1297.52</v>
       </c>
       <c r="O1120" t="n">
-        <v>149214.8</v>
+        <v>144024.72</v>
       </c>
       <c r="P1120" t="n">
         <v>1800</v>
       </c>
       <c r="Q1120" t="n">
-        <v>207000</v>
+        <v>199800</v>
       </c>
     </row>
     <row r="1121">
@@ -49615,13 +49615,13 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1123" t="n">
         <v>1460</v>
@@ -50257,7 +50257,7 @@
         </is>
       </c>
       <c r="J1138" t="n">
-        <v>1873</v>
+        <v>1861</v>
       </c>
       <c r="K1138" t="n">
         <v>0</v>
@@ -50266,19 +50266,19 @@
         <v>0</v>
       </c>
       <c r="M1138" t="n">
-        <v>1873</v>
+        <v>1861</v>
       </c>
       <c r="N1138" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1138" t="n">
-        <v>2203715.61</v>
+        <v>2189596.77</v>
       </c>
       <c r="P1138" t="n">
         <v>1900</v>
       </c>
       <c r="Q1138" t="n">
-        <v>3558700</v>
+        <v>3535900</v>
       </c>
     </row>
     <row r="1139">
@@ -50345,28 +50345,28 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1140" t="n">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="N1140" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1140" t="n">
-        <v>680926.6</v>
+        <v>601379.1</v>
       </c>
       <c r="P1140" t="n">
         <v>5100</v>
       </c>
       <c r="Q1140" t="n">
-        <v>1091400</v>
+        <v>963900</v>
       </c>
     </row>
     <row r="1141">
@@ -50993,13 +50993,13 @@
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
       </c>
       <c r="L1155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1155" t="n">
         <v>74</v>
@@ -51312,10 +51312,10 @@
         <v>386</v>
       </c>
       <c r="N1162" t="n">
-        <v>22951.705030902</v>
+        <v>22951.705024752</v>
       </c>
       <c r="O1162" t="n">
-        <v>8859358.141928172</v>
+        <v>8859358.139554271</v>
       </c>
       <c r="P1162" t="n">
         <v>37900</v>
@@ -51489,10 +51489,10 @@
         <v>4</v>
       </c>
       <c r="N1166" t="n">
-        <v>705.52802098951</v>
+        <v>705.52801652893</v>
       </c>
       <c r="O1166" t="n">
-        <v>2822.11208395804</v>
+        <v>2822.11206611572</v>
       </c>
       <c r="P1166" t="n">
         <v>1500</v>
@@ -52112,13 +52112,13 @@
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1180" t="n">
         <v>17</v>
@@ -53538,7 +53538,7 @@
         </is>
       </c>
       <c r="J1211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1211" t="n">
         <v>0</v>
@@ -53547,19 +53547,19 @@
         <v>0</v>
       </c>
       <c r="M1211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1211" t="n">
         <v>2400</v>
       </c>
       <c r="O1211" t="n">
-        <v>7200</v>
+        <v>4800</v>
       </c>
       <c r="P1211" t="n">
         <v>2900</v>
       </c>
       <c r="Q1211" t="n">
-        <v>8700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="1212">
@@ -54233,7 +54233,7 @@
         </is>
       </c>
       <c r="J1226" t="n">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="K1226" t="n">
         <v>0</v>
@@ -54242,19 +54242,19 @@
         <v>0</v>
       </c>
       <c r="M1226" t="n">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="N1226" t="n">
         <v>2058.92</v>
       </c>
       <c r="O1226" t="n">
-        <v>644441.9600000001</v>
+        <v>609440.3200000001</v>
       </c>
       <c r="P1226" t="n">
         <v>2500</v>
       </c>
       <c r="Q1226" t="n">
-        <v>782500</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="1227">
@@ -61643,7 +61643,7 @@
         </is>
       </c>
       <c r="J1406" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1406" t="n">
         <v>0</v>
@@ -61652,19 +61652,19 @@
         <v>0</v>
       </c>
       <c r="M1406" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N1406" t="n">
         <v>2200</v>
       </c>
       <c r="O1406" t="n">
-        <v>116600</v>
+        <v>114400</v>
       </c>
       <c r="P1406" t="n">
         <v>2700</v>
       </c>
       <c r="Q1406" t="n">
-        <v>143100</v>
+        <v>140400</v>
       </c>
     </row>
     <row r="1407">
@@ -61919,28 +61919,28 @@
         </is>
       </c>
       <c r="J1412" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="K1412" t="n">
         <v>0</v>
       </c>
       <c r="L1412" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1412" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="N1412" t="n">
         <v>4550</v>
       </c>
       <c r="O1412" t="n">
-        <v>800800</v>
+        <v>737100</v>
       </c>
       <c r="P1412" t="n">
         <v>6500</v>
       </c>
       <c r="Q1412" t="n">
-        <v>1144000</v>
+        <v>1053000</v>
       </c>
     </row>
     <row r="1413">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -739,10 +739,10 @@
         <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.65579999999</v>
+        <v>74676.655510204</v>
       </c>
       <c r="O8" t="n">
-        <v>1045473.1812</v>
+        <v>1045473.177142856</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -994,19 +994,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.303568532</v>
+        <v>1811.3036050799</v>
       </c>
       <c r="O14" t="n">
-        <v>753502.284509312</v>
+        <v>742634.4780827591</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>1081600</v>
+        <v>1066000</v>
       </c>
     </row>
     <row r="15">
@@ -1077,10 +1077,10 @@
         <v>155</v>
       </c>
       <c r="N16" t="n">
-        <v>1990.0437084871</v>
+        <v>1990.0436380597</v>
       </c>
       <c r="O16" t="n">
-        <v>308456.7748155005</v>
+        <v>308456.7638992535</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.7465222073</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.773279546</v>
+        <v>3866374.767927359</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2752,19 +2752,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N57" t="n">
         <v>3585</v>
       </c>
       <c r="O57" t="n">
-        <v>319065</v>
+        <v>315480</v>
       </c>
       <c r="P57" t="n">
         <v>4500</v>
       </c>
       <c r="Q57" t="n">
-        <v>400500</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="58">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2955,19 +2955,19 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N62" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O62" t="n">
-        <v>129585.6254731467</v>
+        <v>125658.7882906848</v>
       </c>
       <c r="P62" t="n">
         <v>4800</v>
       </c>
       <c r="Q62" t="n">
-        <v>158400</v>
+        <v>153600</v>
       </c>
     </row>
     <row r="63">
@@ -3593,10 +3593,10 @@
         <v>41</v>
       </c>
       <c r="N78" t="n">
-        <v>15403.520437158</v>
+        <v>15403.520494505</v>
       </c>
       <c r="O78" t="n">
-        <v>631544.337923478</v>
+        <v>631544.3402747051</v>
       </c>
       <c r="P78" t="n">
         <v>33500</v>
@@ -4964,10 +4964,10 @@
         <v>13</v>
       </c>
       <c r="N109" t="n">
-        <v>12837.964266667</v>
+        <v>12837.964861111</v>
       </c>
       <c r="O109" t="n">
-        <v>166893.535466671</v>
+        <v>166893.543194443</v>
       </c>
       <c r="P109" t="n">
         <v>22900</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -5173,19 +5173,19 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N114" t="n">
         <v>36762.36</v>
       </c>
       <c r="O114" t="n">
-        <v>4779106.8</v>
+        <v>4742344.44</v>
       </c>
       <c r="P114" t="n">
         <v>57100</v>
       </c>
       <c r="Q114" t="n">
-        <v>7423000</v>
+        <v>7365900</v>
       </c>
     </row>
     <row r="115">
@@ -5218,10 +5218,10 @@
         <v>21</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966415094</v>
       </c>
       <c r="O115" t="n">
-        <v>329951.295280908</v>
+        <v>329951.294716974</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
@@ -5312,10 +5312,10 @@
         <v>7</v>
       </c>
       <c r="N117" t="n">
-        <v>30238.812195122</v>
+        <v>30238.812222222</v>
       </c>
       <c r="O117" t="n">
-        <v>211671.685365854</v>
+        <v>211671.685555554</v>
       </c>
       <c r="P117" t="n">
         <v>51100</v>
@@ -6510,10 +6510,10 @@
         <v>11</v>
       </c>
       <c r="N146" t="n">
-        <v>62349.661025641</v>
+        <v>62349.660526316</v>
       </c>
       <c r="O146" t="n">
-        <v>685846.271282051</v>
+        <v>685846.265789476</v>
       </c>
       <c r="P146" t="n">
         <v>109900</v>
@@ -6557,10 +6557,10 @@
         <v>17</v>
       </c>
       <c r="N147" t="n">
-        <v>141416.88438871</v>
+        <v>141416.8844164</v>
       </c>
       <c r="O147" t="n">
-        <v>2404087.03460807</v>
+        <v>2404087.0350788</v>
       </c>
       <c r="P147" t="n">
         <v>251900</v>
@@ -6599,10 +6599,10 @@
         <v>2</v>
       </c>
       <c r="N148" t="n">
-        <v>200072.19883562</v>
+        <v>200072.19889655</v>
       </c>
       <c r="O148" t="n">
-        <v>400144.39767124</v>
+        <v>400144.3977931</v>
       </c>
       <c r="P148" t="n">
         <v>312000</v>
@@ -6826,10 +6826,10 @@
         <v>1</v>
       </c>
       <c r="N153" t="n">
-        <v>263530.18090909</v>
+        <v>263530.18</v>
       </c>
       <c r="O153" t="n">
-        <v>263530.18090909</v>
+        <v>263530.18</v>
       </c>
       <c r="P153" t="n">
         <v>402900</v>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7182,19 +7182,19 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N162" t="n">
         <v>20961.76</v>
       </c>
       <c r="O162" t="n">
-        <v>1404437.92</v>
+        <v>1383476.16</v>
       </c>
       <c r="P162" t="n">
         <v>38300</v>
       </c>
       <c r="Q162" t="n">
-        <v>2566100</v>
+        <v>2527800</v>
       </c>
     </row>
     <row r="163">
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8509,19 +8509,19 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N193" t="n">
         <v>3667.11</v>
       </c>
       <c r="O193" t="n">
-        <v>77009.31</v>
+        <v>73342.2</v>
       </c>
       <c r="P193" t="n">
         <v>7300</v>
       </c>
       <c r="Q193" t="n">
-        <v>153300</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="194">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8587,19 +8587,19 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N195" t="n">
         <v>3564.14</v>
       </c>
       <c r="O195" t="n">
-        <v>231669.1</v>
+        <v>228104.96</v>
       </c>
       <c r="P195" t="n">
         <v>5500</v>
       </c>
       <c r="Q195" t="n">
-        <v>357500</v>
+        <v>352000</v>
       </c>
     </row>
     <row r="196">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9271,19 +9271,19 @@
         <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N211" t="n">
         <v>2903.52</v>
       </c>
       <c r="O211" t="n">
-        <v>232281.6</v>
+        <v>229378.08</v>
       </c>
       <c r="P211" t="n">
         <v>7100</v>
       </c>
       <c r="Q211" t="n">
-        <v>568000</v>
+        <v>560900</v>
       </c>
     </row>
     <row r="212">
@@ -10481,10 +10481,10 @@
         <v>107</v>
       </c>
       <c r="N239" t="n">
-        <v>1946.3308465608</v>
+        <v>1946.3308510638</v>
       </c>
       <c r="O239" t="n">
-        <v>208257.4005820056</v>
+        <v>208257.4010638266</v>
       </c>
       <c r="P239" t="n">
         <v>3500</v>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -10604,19 +10604,19 @@
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="N242" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0519160318</v>
       </c>
       <c r="O242" t="n">
-        <v>1564723.706818132</v>
+        <v>1560331.772681188</v>
       </c>
       <c r="P242" t="n">
         <v>1500</v>
       </c>
       <c r="Q242" t="n">
-        <v>2137500</v>
+        <v>2131500</v>
       </c>
     </row>
     <row r="243">
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="J264" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -11529,19 +11529,19 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N264" t="n">
         <v>7569</v>
       </c>
       <c r="O264" t="n">
-        <v>439002</v>
+        <v>416295</v>
       </c>
       <c r="P264" t="n">
         <v>12900</v>
       </c>
       <c r="Q264" t="n">
-        <v>748200</v>
+        <v>709500</v>
       </c>
     </row>
     <row r="265">
@@ -12487,10 +12487,10 @@
         <v>181</v>
       </c>
       <c r="N286" t="n">
-        <v>2033.5815122873</v>
+        <v>2033.5814772727</v>
       </c>
       <c r="O286" t="n">
-        <v>368078.2537240013</v>
+        <v>368078.2473863587</v>
       </c>
       <c r="P286" t="n">
         <v>4100</v>
@@ -12779,10 +12779,10 @@
         <v>2839</v>
       </c>
       <c r="N293" t="n">
-        <v>3158.8608104732</v>
+        <v>3158.8608123465</v>
       </c>
       <c r="O293" t="n">
-        <v>8968005.840933416</v>
+        <v>8968005.846251713</v>
       </c>
       <c r="P293" t="n">
         <v>5600</v>
@@ -13053,10 +13053,10 @@
         <v>94</v>
       </c>
       <c r="N299" t="n">
-        <v>3230.0679765396</v>
+        <v>3230.0679433681</v>
       </c>
       <c r="O299" t="n">
-        <v>303626.3897947224</v>
+        <v>303626.3866766014</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13538,7 +13538,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13547,19 +13547,19 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N310" t="n">
         <v>5002</v>
       </c>
       <c r="O310" t="n">
-        <v>1205482</v>
+        <v>1200480</v>
       </c>
       <c r="P310" t="n">
         <v>8400</v>
       </c>
       <c r="Q310" t="n">
-        <v>2024400</v>
+        <v>2016000</v>
       </c>
     </row>
     <row r="311">
@@ -14113,10 +14113,10 @@
         <v>331</v>
       </c>
       <c r="N323" t="n">
-        <v>4890.9300453258</v>
+        <v>4890.9300453515</v>
       </c>
       <c r="O323" t="n">
-        <v>1618897.84500284</v>
+        <v>1618897.845011347</v>
       </c>
       <c r="P323" t="n">
         <v>8200</v>
@@ -14912,10 +14912,10 @@
         <v>368</v>
       </c>
       <c r="N341" t="n">
-        <v>3594.2542925089</v>
+        <v>3594.2542686567</v>
       </c>
       <c r="O341" t="n">
-        <v>1322685.579643275</v>
+        <v>1322685.570865666</v>
       </c>
       <c r="P341" t="n">
         <v>6500</v>
@@ -14949,7 +14949,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>1746</v>
+        <v>1739</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -14958,19 +14958,19 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>1746</v>
+        <v>1739</v>
       </c>
       <c r="N342" t="n">
         <v>489.88</v>
       </c>
       <c r="O342" t="n">
-        <v>855330.48</v>
+        <v>851901.3199999999</v>
       </c>
       <c r="P342" t="n">
         <v>700</v>
       </c>
       <c r="Q342" t="n">
-        <v>1222200</v>
+        <v>1217300</v>
       </c>
     </row>
     <row r="343">
@@ -15084,10 +15084,10 @@
         <v>1</v>
       </c>
       <c r="N345" t="n">
-        <v>3240.850028169</v>
+        <v>3240.85002886</v>
       </c>
       <c r="O345" t="n">
-        <v>3240.850028169</v>
+        <v>3240.85002886</v>
       </c>
       <c r="P345" t="n">
         <v>5200</v>
@@ -15431,10 +15431,10 @@
         <v>199</v>
       </c>
       <c r="N353" t="n">
-        <v>5191.4800264901</v>
+        <v>5191.4800265252</v>
       </c>
       <c r="O353" t="n">
-        <v>1033104.52527153</v>
+        <v>1033104.525278515</v>
       </c>
       <c r="P353" t="n">
         <v>9100</v>
@@ -16075,10 +16075,10 @@
         <v>6</v>
       </c>
       <c r="N368" t="n">
-        <v>4193.85</v>
+        <v>4242.3899305556</v>
       </c>
       <c r="O368" t="n">
-        <v>25163.1</v>
+        <v>25454.3395833336</v>
       </c>
       <c r="P368" t="n">
         <v>7500</v>
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16121,19 +16121,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N369" t="n">
-        <v>3041.6600119048</v>
+        <v>3041.6600119617</v>
       </c>
       <c r="O369" t="n">
-        <v>590082.0423095311</v>
+        <v>568790.4222368379</v>
       </c>
       <c r="P369" t="n">
         <v>5500</v>
       </c>
       <c r="Q369" t="n">
-        <v>1067000</v>
+        <v>1028500</v>
       </c>
     </row>
     <row r="370">
@@ -16255,10 +16255,10 @@
         <v>59</v>
       </c>
       <c r="N372" t="n">
-        <v>6441.03</v>
+        <v>6470.8036363636</v>
       </c>
       <c r="O372" t="n">
-        <v>380020.77</v>
+        <v>381777.4145454524</v>
       </c>
       <c r="P372" t="n">
         <v>10500</v>
@@ -16383,10 +16383,10 @@
         <v>660</v>
       </c>
       <c r="N375" t="n">
-        <v>1592.5679711276</v>
+        <v>1592.5679397781</v>
       </c>
       <c r="O375" t="n">
-        <v>1051094.860944216</v>
+        <v>1051094.840253546</v>
       </c>
       <c r="P375" t="n">
         <v>3900</v>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -16985,19 +16985,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N389" t="n">
         <v>4648.6</v>
       </c>
       <c r="O389" t="n">
-        <v>1250473.4</v>
+        <v>1245824.8</v>
       </c>
       <c r="P389" t="n">
         <v>8900</v>
       </c>
       <c r="Q389" t="n">
-        <v>2394100</v>
+        <v>2385200</v>
       </c>
     </row>
     <row r="390">
@@ -18745,10 +18745,10 @@
         <v>614</v>
       </c>
       <c r="N429" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9228476208</v>
       </c>
       <c r="O429" t="n">
-        <v>1001386.612719236</v>
+        <v>1001386.628439171</v>
       </c>
       <c r="P429" t="n">
         <v>2500</v>
@@ -18791,10 +18791,10 @@
         <v>14</v>
       </c>
       <c r="N430" t="n">
-        <v>1467.3289090909</v>
+        <v>1467.328030303</v>
       </c>
       <c r="O430" t="n">
-        <v>20542.6047272726</v>
+        <v>20542.592424242</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -18837,10 +18837,10 @@
         <v>23</v>
       </c>
       <c r="N431" t="n">
-        <v>1690.6051240876</v>
+        <v>1690.604715</v>
       </c>
       <c r="O431" t="n">
-        <v>38883.9178540148</v>
+        <v>38883.908445</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
@@ -18871,7 +18871,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -18880,19 +18880,19 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="N432" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927793589</v>
       </c>
       <c r="O432" t="n">
-        <v>1998198.460945708</v>
+        <v>1996648.299814263</v>
       </c>
       <c r="P432" t="n">
         <v>2500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3222500</v>
+        <v>3220000</v>
       </c>
     </row>
     <row r="433">
@@ -18917,7 +18917,7 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
@@ -18926,19 +18926,19 @@
         <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N433" t="n">
-        <v>1579.391452381</v>
+        <v>1579.3914319809</v>
       </c>
       <c r="O433" t="n">
-        <v>183209.408476196</v>
+        <v>181630.0146778035</v>
       </c>
       <c r="P433" t="n">
         <v>2900</v>
       </c>
       <c r="Q433" t="n">
-        <v>336400</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="434">
@@ -18975,10 +18975,10 @@
         <v>959</v>
       </c>
       <c r="N434" t="n">
-        <v>2403.5095333845</v>
+        <v>2403.5096714419</v>
       </c>
       <c r="O434" t="n">
-        <v>2304965.642515736</v>
+        <v>2304965.774912782</v>
       </c>
       <c r="P434" t="n">
         <v>3500</v>
@@ -19065,10 +19065,10 @@
         <v>317</v>
       </c>
       <c r="N436" t="n">
-        <v>2521.5499887387</v>
+        <v>2521.5498862344</v>
       </c>
       <c r="O436" t="n">
-        <v>799331.3464301679</v>
+        <v>799331.3139363049</v>
       </c>
       <c r="P436" t="n">
         <v>3900</v>
@@ -19433,7 +19433,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -19442,19 +19442,19 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N445" t="n">
         <v>2423.42</v>
       </c>
       <c r="O445" t="n">
-        <v>746413.36</v>
+        <v>743989.9400000001</v>
       </c>
       <c r="P445" t="n">
         <v>3150</v>
       </c>
       <c r="Q445" t="n">
-        <v>970200</v>
+        <v>967050</v>
       </c>
     </row>
     <row r="446">
@@ -23552,7 +23552,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -23561,19 +23561,19 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="N541" t="n">
         <v>2517.22</v>
       </c>
       <c r="O541" t="n">
-        <v>216480.92</v>
+        <v>211446.48</v>
       </c>
       <c r="P541" t="n">
         <v>4200</v>
       </c>
       <c r="Q541" t="n">
-        <v>361200</v>
+        <v>352800</v>
       </c>
     </row>
     <row r="542">
@@ -23646,10 +23646,10 @@
         <v>248</v>
       </c>
       <c r="N543" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8735277516</v>
       </c>
       <c r="O543" t="n">
-        <v>503408.6251162808</v>
+        <v>503408.6348823968</v>
       </c>
       <c r="P543" t="n">
         <v>3600</v>
@@ -24003,7 +24003,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -24012,19 +24012,19 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N552" t="n">
         <v>1866.74</v>
       </c>
       <c r="O552" t="n">
-        <v>881101.28</v>
+        <v>877367.8</v>
       </c>
       <c r="P552" t="n">
         <v>2900</v>
       </c>
       <c r="Q552" t="n">
-        <v>1368800</v>
+        <v>1363000</v>
       </c>
     </row>
     <row r="553">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -24176,19 +24176,19 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N556" t="n">
         <v>7103</v>
       </c>
       <c r="O556" t="n">
-        <v>980214</v>
+        <v>973111</v>
       </c>
       <c r="P556" t="n">
         <v>10700</v>
       </c>
       <c r="Q556" t="n">
-        <v>1476600</v>
+        <v>1465900</v>
       </c>
     </row>
     <row r="557">
@@ -24392,10 +24392,10 @@
         <v>185</v>
       </c>
       <c r="N561" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.739700672</v>
       </c>
       <c r="O561" t="n">
-        <v>495936.8447256075</v>
+        <v>495936.84462432</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
@@ -24800,7 +24800,7 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
@@ -24809,19 +24809,19 @@
         <v>0</v>
       </c>
       <c r="M571" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N571" t="n">
         <v>14060.64</v>
       </c>
       <c r="O571" t="n">
-        <v>56242.56</v>
+        <v>28121.28</v>
       </c>
       <c r="P571" t="n">
         <v>22900</v>
       </c>
       <c r="Q571" t="n">
-        <v>91600</v>
+        <v>45800</v>
       </c>
     </row>
     <row r="572">
@@ -25488,10 +25488,10 @@
         <v>435</v>
       </c>
       <c r="N587" t="n">
-        <v>998.76124730022</v>
+        <v>998.76125748503</v>
       </c>
       <c r="O587" t="n">
-        <v>434461.1425755957</v>
+        <v>434461.1470059881</v>
       </c>
       <c r="P587" t="n">
         <v>1600</v>
@@ -25693,10 +25693,10 @@
         <v>1</v>
       </c>
       <c r="N592" t="n">
-        <v>1359.89</v>
+        <v>1406.381965812</v>
       </c>
       <c r="O592" t="n">
-        <v>1359.89</v>
+        <v>1406.381965812</v>
       </c>
       <c r="P592" t="n">
         <v>2600</v>
@@ -25727,7 +25727,7 @@
         </is>
       </c>
       <c r="J593" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="K593" t="n">
         <v>0</v>
@@ -25736,19 +25736,19 @@
         <v>0</v>
       </c>
       <c r="M593" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="N593" t="n">
         <v>3877.89</v>
       </c>
       <c r="O593" t="n">
-        <v>539026.71</v>
+        <v>492492.03</v>
       </c>
       <c r="P593" t="n">
         <v>6500</v>
       </c>
       <c r="Q593" t="n">
-        <v>903500</v>
+        <v>825500</v>
       </c>
     </row>
     <row r="594">
@@ -25829,10 +25829,10 @@
         <v>5</v>
       </c>
       <c r="N595" t="n">
-        <v>4285.1951158107</v>
+        <v>4285.1951469098</v>
       </c>
       <c r="O595" t="n">
-        <v>21425.9755790535</v>
+        <v>21425.975734549</v>
       </c>
       <c r="P595" t="n">
         <v>6900</v>
@@ -26559,10 +26559,10 @@
         <v>89</v>
       </c>
       <c r="N612" t="n">
-        <v>11562.038549223</v>
+        <v>11562.038545455</v>
       </c>
       <c r="O612" t="n">
-        <v>1029021.430880847</v>
+        <v>1029021.430545495</v>
       </c>
       <c r="P612" t="n">
         <v>18500</v>
@@ -28795,10 +28795,10 @@
         <v>2</v>
       </c>
       <c r="N665" t="n">
-        <v>1466.8806936416</v>
+        <v>1466.8807100592</v>
       </c>
       <c r="O665" t="n">
-        <v>2933.7613872832</v>
+        <v>2933.7614201184</v>
       </c>
       <c r="P665" t="n">
         <v>3400</v>
@@ -28829,7 +28829,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -28838,19 +28838,19 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N666" t="n">
         <v>16974.69</v>
       </c>
       <c r="O666" t="n">
-        <v>1595620.86</v>
+        <v>1578646.17</v>
       </c>
       <c r="P666" t="n">
         <v>26900</v>
       </c>
       <c r="Q666" t="n">
-        <v>2528600</v>
+        <v>2501700</v>
       </c>
     </row>
     <row r="667">
@@ -29259,7 +29259,7 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
@@ -29268,19 +29268,19 @@
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N676" t="n">
-        <v>1560.9979018405</v>
+        <v>1560.9980701754</v>
       </c>
       <c r="O676" t="n">
-        <v>902256.787263809</v>
+        <v>899134.8884210304</v>
       </c>
       <c r="P676" t="n">
         <v>2900</v>
       </c>
       <c r="Q676" t="n">
-        <v>1676200</v>
+        <v>1670400</v>
       </c>
     </row>
     <row r="677">
@@ -29305,7 +29305,7 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
@@ -29314,19 +29314,19 @@
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N677" t="n">
         <v>3487.53</v>
       </c>
       <c r="O677" t="n">
-        <v>104625.9</v>
+        <v>101138.37</v>
       </c>
       <c r="P677" t="n">
         <v>6500</v>
       </c>
       <c r="Q677" t="n">
-        <v>195000</v>
+        <v>188500</v>
       </c>
     </row>
     <row r="678">
@@ -29725,7 +29725,7 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
@@ -29734,19 +29734,19 @@
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N687" t="n">
-        <v>2568.835631068</v>
+        <v>2568.8356026059</v>
       </c>
       <c r="O687" t="n">
-        <v>434133.221650492</v>
+        <v>428995.5456351853</v>
       </c>
       <c r="P687" t="n">
         <v>4500</v>
       </c>
       <c r="Q687" t="n">
-        <v>760500</v>
+        <v>751500</v>
       </c>
     </row>
     <row r="688">
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="J692" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K692" t="n">
         <v>0</v>
@@ -29944,19 +29944,19 @@
         <v>0</v>
       </c>
       <c r="M692" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N692" t="n">
-        <v>7969.9501638124</v>
+        <v>7969.9501643017</v>
       </c>
       <c r="O692" t="n">
-        <v>1354891.527848108</v>
+        <v>1346921.577766987</v>
       </c>
       <c r="P692" t="n">
         <v>12900</v>
       </c>
       <c r="Q692" t="n">
-        <v>2193000</v>
+        <v>2180100</v>
       </c>
     </row>
     <row r="693">
@@ -31519,10 +31519,10 @@
         <v>77</v>
       </c>
       <c r="N729" t="n">
-        <v>3113.8900218818</v>
+        <v>3113.890023175</v>
       </c>
       <c r="O729" t="n">
-        <v>239769.5316848986</v>
+        <v>239769.531784475</v>
       </c>
       <c r="P729" t="n">
         <v>5000</v>
@@ -31933,10 +31933,10 @@
         <v>28</v>
       </c>
       <c r="N738" t="n">
-        <v>5218.1704503582</v>
+        <v>5234.4433367983</v>
       </c>
       <c r="O738" t="n">
-        <v>146108.7726100296</v>
+        <v>146564.4134303524</v>
       </c>
       <c r="P738" t="n">
         <v>8500</v>
@@ -31979,10 +31979,10 @@
         <v>21</v>
       </c>
       <c r="N739" t="n">
-        <v>1595.0095763657</v>
+        <v>1595.0095696489</v>
       </c>
       <c r="O739" t="n">
-        <v>33495.2011036797</v>
+        <v>33495.2009626269</v>
       </c>
       <c r="P739" t="n">
         <v>2600</v>
@@ -32025,10 +32025,10 @@
         <v>31</v>
       </c>
       <c r="N740" t="n">
-        <v>3610.6500218579</v>
+        <v>3610.6500224972</v>
       </c>
       <c r="O740" t="n">
-        <v>111930.1506775949</v>
+        <v>111930.1506974132</v>
       </c>
       <c r="P740" t="n">
         <v>5800</v>
@@ -32350,10 +32350,10 @@
         <v>162</v>
       </c>
       <c r="N747" t="n">
-        <v>1664.3622356902</v>
+        <v>1664.362204192</v>
       </c>
       <c r="O747" t="n">
-        <v>269626.6821818124</v>
+        <v>269626.677079104</v>
       </c>
       <c r="P747" t="n">
         <v>2900</v>
@@ -32396,10 +32396,10 @@
         <v>13</v>
       </c>
       <c r="N748" t="n">
-        <v>15502</v>
+        <v>15692.208588957</v>
       </c>
       <c r="O748" t="n">
-        <v>201526</v>
+        <v>203998.711656441</v>
       </c>
       <c r="P748" t="n">
         <v>25900</v>
@@ -33256,7 +33256,7 @@
         </is>
       </c>
       <c r="J767" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K767" t="n">
         <v>0</v>
@@ -33265,19 +33265,19 @@
         <v>0</v>
       </c>
       <c r="M767" t="n">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="N767" t="n">
         <v>3486</v>
       </c>
       <c r="O767" t="n">
-        <v>2314704</v>
+        <v>2300760</v>
       </c>
       <c r="P767" t="n">
         <v>6900</v>
       </c>
       <c r="Q767" t="n">
-        <v>4581600</v>
+        <v>4554000</v>
       </c>
     </row>
     <row r="768">
@@ -33314,10 +33314,10 @@
         <v>1253</v>
       </c>
       <c r="N768" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724989266</v>
       </c>
       <c r="O768" t="n">
-        <v>2228426.034001152</v>
+        <v>2228426.04115503</v>
       </c>
       <c r="P768" t="n">
         <v>4900</v>
@@ -35070,10 +35070,10 @@
         <v>1</v>
       </c>
       <c r="N806" t="n">
-        <v>26445.443529412</v>
+        <v>26445.44375</v>
       </c>
       <c r="O806" t="n">
-        <v>26445.443529412</v>
+        <v>26445.44375</v>
       </c>
       <c r="P806" t="n">
         <v>44900</v>
@@ -35852,10 +35852,10 @@
         <v>152</v>
       </c>
       <c r="N823" t="n">
-        <v>2252.2960775371</v>
+        <v>2252.2960914286</v>
       </c>
       <c r="O823" t="n">
-        <v>342349.0037856392</v>
+        <v>342349.0058971472</v>
       </c>
       <c r="P823" t="n">
         <v>3900</v>
@@ -36085,10 +36085,10 @@
         <v>465</v>
       </c>
       <c r="N828" t="n">
-        <v>2328.1187653599</v>
+        <v>2328.11876101</v>
       </c>
       <c r="O828" t="n">
-        <v>1082575.225892354</v>
+        <v>1082575.22386965</v>
       </c>
       <c r="P828" t="n">
         <v>4500</v>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K837" t="n">
         <v>0</v>
@@ -36496,19 +36496,19 @@
         <v>0</v>
       </c>
       <c r="M837" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N837" t="n">
         <v>4544</v>
       </c>
       <c r="O837" t="n">
-        <v>1335936</v>
+        <v>1331392</v>
       </c>
       <c r="P837" t="n">
         <v>7900</v>
       </c>
       <c r="Q837" t="n">
-        <v>2322600</v>
+        <v>2314700</v>
       </c>
     </row>
     <row r="838">
@@ -36821,10 +36821,10 @@
         <v>15</v>
       </c>
       <c r="N844" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.821884273</v>
       </c>
       <c r="O844" t="n">
-        <v>73617.32809734451</v>
+        <v>73617.32826409501</v>
       </c>
       <c r="P844" t="n">
         <v>8200</v>
@@ -37039,7 +37039,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -37048,19 +37048,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N849" t="n">
         <v>52443</v>
       </c>
       <c r="O849" t="n">
-        <v>3671010</v>
+        <v>3618567</v>
       </c>
       <c r="P849" t="n">
         <v>83900</v>
       </c>
       <c r="Q849" t="n">
-        <v>5873000</v>
+        <v>5789100</v>
       </c>
     </row>
     <row r="850">
@@ -37097,10 +37097,10 @@
         <v>24</v>
       </c>
       <c r="N850" t="n">
-        <v>3903.7357803468</v>
+        <v>3903.7358031838</v>
       </c>
       <c r="O850" t="n">
-        <v>93689.65872832319</v>
+        <v>93689.6592764112</v>
       </c>
       <c r="P850" t="n">
         <v>7500</v>
@@ -37552,10 +37552,10 @@
         <v>15</v>
       </c>
       <c r="N860" t="n">
-        <v>5869.1728472222</v>
+        <v>5869.1728258706</v>
       </c>
       <c r="O860" t="n">
-        <v>88037.592708333</v>
+        <v>88037.592388059</v>
       </c>
       <c r="P860" t="n">
         <v>9500</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="J887" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K887" t="n">
         <v>0</v>
@@ -38786,19 +38786,19 @@
         <v>0</v>
       </c>
       <c r="M887" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N887" t="n">
         <v>59834</v>
       </c>
       <c r="O887" t="n">
-        <v>4008878</v>
+        <v>3949044</v>
       </c>
       <c r="P887" t="n">
         <v>7900</v>
       </c>
       <c r="Q887" t="n">
-        <v>529300</v>
+        <v>521400</v>
       </c>
     </row>
     <row r="888">
@@ -38823,7 +38823,7 @@
         </is>
       </c>
       <c r="J888" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K888" t="n">
         <v>0</v>
@@ -38832,19 +38832,19 @@
         <v>0</v>
       </c>
       <c r="M888" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N888" t="n">
         <v>21346</v>
       </c>
       <c r="O888" t="n">
-        <v>917878</v>
+        <v>896532</v>
       </c>
       <c r="P888" t="n">
         <v>34900</v>
       </c>
       <c r="Q888" t="n">
-        <v>1500700</v>
+        <v>1465800</v>
       </c>
     </row>
     <row r="889">
@@ -39148,7 +39148,7 @@
         </is>
       </c>
       <c r="J895" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K895" t="n">
         <v>0</v>
@@ -39157,19 +39157,19 @@
         <v>0</v>
       </c>
       <c r="M895" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N895" t="n">
         <v>5215</v>
       </c>
       <c r="O895" t="n">
-        <v>140805</v>
+        <v>130375</v>
       </c>
       <c r="P895" t="n">
         <v>8900</v>
       </c>
       <c r="Q895" t="n">
-        <v>240300</v>
+        <v>222500</v>
       </c>
     </row>
     <row r="896">
@@ -39516,7 +39516,7 @@
         </is>
       </c>
       <c r="J903" t="n">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="K903" t="n">
         <v>0</v>
@@ -39525,19 +39525,19 @@
         <v>0</v>
       </c>
       <c r="M903" t="n">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="N903" t="n">
         <v>1326</v>
       </c>
       <c r="O903" t="n">
-        <v>2333760</v>
+        <v>2332434</v>
       </c>
       <c r="P903" t="n">
         <v>2500</v>
       </c>
       <c r="Q903" t="n">
-        <v>4400000</v>
+        <v>4397500</v>
       </c>
     </row>
     <row r="904">
@@ -40175,10 +40175,10 @@
         <v>1327</v>
       </c>
       <c r="N917" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388192979</v>
       </c>
       <c r="O917" t="n">
-        <v>2011783.515009583</v>
+        <v>2011783.513208313</v>
       </c>
       <c r="P917" t="n">
         <v>2300</v>
@@ -40209,7 +40209,7 @@
         </is>
       </c>
       <c r="J918" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K918" t="n">
         <v>0</v>
@@ -40218,19 +40218,19 @@
         <v>0</v>
       </c>
       <c r="M918" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N918" t="n">
-        <v>4248.6103213611</v>
+        <v>4248.611257732</v>
       </c>
       <c r="O918" t="n">
-        <v>497087.4075992487</v>
+        <v>492838.905896912</v>
       </c>
       <c r="P918" t="n">
         <v>5900</v>
       </c>
       <c r="Q918" t="n">
-        <v>690300</v>
+        <v>684400</v>
       </c>
     </row>
     <row r="919">
@@ -40311,10 +40311,10 @@
         <v>309</v>
       </c>
       <c r="N920" t="n">
-        <v>2458.5136716147</v>
+        <v>2458.5136620146</v>
       </c>
       <c r="O920" t="n">
-        <v>759680.7245289423</v>
+        <v>759680.7215625114</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
@@ -40357,10 +40357,10 @@
         <v>60</v>
       </c>
       <c r="N921" t="n">
-        <v>1907.3946829268</v>
+        <v>1907.3946349467</v>
       </c>
       <c r="O921" t="n">
-        <v>114443.680975608</v>
+        <v>114443.678096802</v>
       </c>
       <c r="P921" t="n">
         <v>2500</v>
@@ -40437,7 +40437,7 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
@@ -40446,19 +40446,19 @@
         <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="N923" t="n">
-        <v>2079.3843686869</v>
+        <v>2079.3843256997</v>
       </c>
       <c r="O923" t="n">
-        <v>804721.7506818303</v>
+        <v>779769.1221373875</v>
       </c>
       <c r="P923" t="n">
         <v>2900</v>
       </c>
       <c r="Q923" t="n">
-        <v>1122300</v>
+        <v>1087500</v>
       </c>
     </row>
     <row r="924">
@@ -40495,10 +40495,10 @@
         <v>421</v>
       </c>
       <c r="N924" t="n">
-        <v>1803.0147280335</v>
+        <v>1803.0147949081</v>
       </c>
       <c r="O924" t="n">
-        <v>759069.2005021035</v>
+        <v>759069.2286563101</v>
       </c>
       <c r="P924" t="n">
         <v>2500</v>
@@ -40541,10 +40541,10 @@
         <v>101</v>
       </c>
       <c r="N925" t="n">
-        <v>3306.595599022</v>
+        <v>3306.5955223881</v>
       </c>
       <c r="O925" t="n">
-        <v>333966.155501222</v>
+        <v>333966.1477611981</v>
       </c>
       <c r="P925" t="n">
         <v>4900</v>
@@ -40587,10 +40587,10 @@
         <v>51</v>
       </c>
       <c r="N926" t="n">
-        <v>2122.1642044444</v>
+        <v>2122.1641906742</v>
       </c>
       <c r="O926" t="n">
-        <v>108230.3744266644</v>
+        <v>108230.3737243842</v>
       </c>
       <c r="P926" t="n">
         <v>2900</v>
@@ -40633,10 +40633,10 @@
         <v>165</v>
       </c>
       <c r="N927" t="n">
-        <v>2108.7892625995</v>
+        <v>2108.7893319081</v>
       </c>
       <c r="O927" t="n">
-        <v>347950.2283289175</v>
+        <v>347950.2397648365</v>
       </c>
       <c r="P927" t="n">
         <v>2900</v>
@@ -40667,7 +40667,7 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
@@ -40676,19 +40676,19 @@
         <v>0</v>
       </c>
       <c r="M928" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="N928" t="n">
-        <v>2056.0840859599</v>
+        <v>2056.0840312319</v>
       </c>
       <c r="O928" t="n">
-        <v>849162.7275014388</v>
+        <v>840938.3687738471</v>
       </c>
       <c r="P928" t="n">
         <v>2900</v>
       </c>
       <c r="Q928" t="n">
-        <v>1197700</v>
+        <v>1186100</v>
       </c>
     </row>
     <row r="929">
@@ -40713,7 +40713,7 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
@@ -40722,19 +40722,19 @@
         <v>0</v>
       </c>
       <c r="M929" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N929" t="n">
-        <v>3224.5675687104</v>
+        <v>3224.5675847458</v>
       </c>
       <c r="O929" t="n">
-        <v>786794.4867653375</v>
+        <v>780345.3555084836</v>
       </c>
       <c r="P929" t="n">
         <v>4500</v>
       </c>
       <c r="Q929" t="n">
-        <v>1098000</v>
+        <v>1089000</v>
       </c>
     </row>
     <row r="930">
@@ -40771,10 +40771,10 @@
         <v>336</v>
       </c>
       <c r="N930" t="n">
-        <v>1655.9315593531</v>
+        <v>1655.9315412844</v>
       </c>
       <c r="O930" t="n">
-        <v>556393.0039426417</v>
+        <v>556392.9978715584</v>
       </c>
       <c r="P930" t="n">
         <v>2500</v>
@@ -40946,7 +40946,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -40955,19 +40955,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="N934" t="n">
         <v>2454</v>
       </c>
       <c r="O934" t="n">
-        <v>1384056</v>
+        <v>1376694</v>
       </c>
       <c r="P934" t="n">
         <v>4200</v>
       </c>
       <c r="Q934" t="n">
-        <v>2368800</v>
+        <v>2356200</v>
       </c>
     </row>
     <row r="935">
@@ -41004,10 +41004,10 @@
         <v>636</v>
       </c>
       <c r="N935" t="n">
-        <v>1592.2740100137</v>
+        <v>1592.274090065</v>
       </c>
       <c r="O935" t="n">
-        <v>1012686.270368713</v>
+        <v>1012686.32128134</v>
       </c>
       <c r="P935" t="n">
         <v>2500</v>
@@ -41135,10 +41135,10 @@
         <v>237</v>
       </c>
       <c r="N938" t="n">
-        <v>2311.9281444759</v>
+        <v>2311.9280428571</v>
       </c>
       <c r="O938" t="n">
-        <v>547926.9702407883</v>
+        <v>547926.9461571327</v>
       </c>
       <c r="P938" t="n">
         <v>3500</v>
@@ -41181,10 +41181,10 @@
         <v>209</v>
       </c>
       <c r="N939" t="n">
-        <v>1906.1878571429</v>
+        <v>1906.1877678571</v>
       </c>
       <c r="O939" t="n">
-        <v>398393.2621428661</v>
+        <v>398393.2434821339</v>
       </c>
       <c r="P939" t="n">
         <v>2900</v>
@@ -41227,10 +41227,10 @@
         <v>265</v>
       </c>
       <c r="N940" t="n">
-        <v>3033.7328518519</v>
+        <v>3033.7328200371</v>
       </c>
       <c r="O940" t="n">
-        <v>803939.2057407534</v>
+        <v>803939.1973098315</v>
       </c>
       <c r="P940" t="n">
         <v>4500</v>
@@ -41261,7 +41261,7 @@
         </is>
       </c>
       <c r="J941" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K941" t="n">
         <v>0</v>
@@ -41270,19 +41270,19 @@
         <v>0</v>
       </c>
       <c r="M941" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N941" t="n">
-        <v>1668.6124489796</v>
+        <v>1668.6125935484</v>
       </c>
       <c r="O941" t="n">
-        <v>420490.3371428592</v>
+        <v>415484.5357935516</v>
       </c>
       <c r="P941" t="n">
         <v>2500</v>
       </c>
       <c r="Q941" t="n">
-        <v>630000</v>
+        <v>622500</v>
       </c>
     </row>
     <row r="942">
@@ -41319,10 +41319,10 @@
         <v>195</v>
       </c>
       <c r="N942" t="n">
-        <v>2546.9861569689</v>
+        <v>2546.986027972</v>
       </c>
       <c r="O942" t="n">
-        <v>496662.3006089355</v>
+        <v>496662.27545454</v>
       </c>
       <c r="P942" t="n">
         <v>3900</v>
@@ -41365,10 +41365,10 @@
         <v>1127</v>
       </c>
       <c r="N943" t="n">
-        <v>1259.2741948888</v>
+        <v>1259.2742318172</v>
       </c>
       <c r="O943" t="n">
-        <v>1419202.017639678</v>
+        <v>1419202.059257984</v>
       </c>
       <c r="P943" t="n">
         <v>1900</v>
@@ -41544,10 +41544,10 @@
         <v>161</v>
       </c>
       <c r="N947" t="n">
-        <v>2556.7442028986</v>
+        <v>2556.7442542787</v>
       </c>
       <c r="O947" t="n">
-        <v>411635.8166666746</v>
+        <v>411635.8249388707</v>
       </c>
       <c r="P947" t="n">
         <v>3900</v>
@@ -41588,10 +41588,10 @@
         <v>2782</v>
       </c>
       <c r="N948" t="n">
-        <v>692.1519887834301</v>
+        <v>692.151995671</v>
       </c>
       <c r="O948" t="n">
-        <v>1925566.832795502</v>
+        <v>1925566.851956722</v>
       </c>
       <c r="P948" t="n">
         <v>1200</v>
@@ -42149,10 +42149,10 @@
         <v>539</v>
       </c>
       <c r="N960" t="n">
-        <v>2857.22</v>
+        <v>2861.1357880311</v>
       </c>
       <c r="O960" t="n">
-        <v>1540041.58</v>
+        <v>1542152.189748763</v>
       </c>
       <c r="P960" t="n">
         <v>4900</v>
@@ -42373,7 +42373,7 @@
         </is>
       </c>
       <c r="J965" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K965" t="n">
         <v>0</v>
@@ -42382,19 +42382,19 @@
         <v>0</v>
       </c>
       <c r="M965" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N965" t="n">
-        <v>1530.4499206664</v>
+        <v>1530.4499206349</v>
       </c>
       <c r="O965" t="n">
-        <v>492804.8744545808</v>
+        <v>491274.4245238029</v>
       </c>
       <c r="P965" t="n">
         <v>2600</v>
       </c>
       <c r="Q965" t="n">
-        <v>837200</v>
+        <v>834600</v>
       </c>
     </row>
     <row r="966">
@@ -43072,10 +43072,10 @@
         <v>4300</v>
       </c>
       <c r="N980" t="n">
-        <v>345.55838654429</v>
+        <v>345.55838640256</v>
       </c>
       <c r="O980" t="n">
-        <v>1485901.062140447</v>
+        <v>1485901.061531008</v>
       </c>
       <c r="P980" t="n">
         <v>600</v>
@@ -43712,7 +43712,7 @@
         </is>
       </c>
       <c r="J995" t="n">
-        <v>2353</v>
+        <v>2311</v>
       </c>
       <c r="K995" t="n">
         <v>0</v>
@@ -43721,19 +43721,19 @@
         <v>0</v>
       </c>
       <c r="M995" t="n">
-        <v>2353</v>
+        <v>2311</v>
       </c>
       <c r="N995" t="n">
-        <v>517.28707627294</v>
+        <v>517.28716412902</v>
       </c>
       <c r="O995" t="n">
-        <v>1217176.490470228</v>
+        <v>1195450.636302165</v>
       </c>
       <c r="P995" t="n">
         <v>900</v>
       </c>
       <c r="Q995" t="n">
-        <v>2117700</v>
+        <v>2079900</v>
       </c>
     </row>
     <row r="996">
@@ -43897,7 +43897,7 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
@@ -43906,19 +43906,19 @@
         <v>0</v>
       </c>
       <c r="M999" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="N999" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8436976288</v>
       </c>
       <c r="O999" t="n">
-        <v>5344429.78921776</v>
+        <v>5341318.628828649</v>
       </c>
       <c r="P999" t="n">
         <v>4500</v>
       </c>
       <c r="Q999" t="n">
-        <v>7731000</v>
+        <v>7726500</v>
       </c>
     </row>
     <row r="1000">
@@ -44029,7 +44029,7 @@
         </is>
       </c>
       <c r="J1002" t="n">
-        <v>15478</v>
+        <v>15426</v>
       </c>
       <c r="K1002" t="n">
         <v>0</v>
@@ -44038,19 +44038,19 @@
         <v>0</v>
       </c>
       <c r="M1002" t="n">
-        <v>15478</v>
+        <v>15426</v>
       </c>
       <c r="N1002" t="n">
-        <v>703.79553851454</v>
+        <v>703.79553051727</v>
       </c>
       <c r="O1002" t="n">
-        <v>10893347.34512805</v>
+        <v>10856749.85375941</v>
       </c>
       <c r="P1002" t="n">
         <v>900</v>
       </c>
       <c r="Q1002" t="n">
-        <v>13930200</v>
+        <v>13883400</v>
       </c>
     </row>
     <row r="1003">
@@ -44527,10 +44527,10 @@
         <v>430</v>
       </c>
       <c r="N1013" t="n">
-        <v>2077.4944179523</v>
+        <v>2077.4944303797</v>
       </c>
       <c r="O1013" t="n">
-        <v>893322.599719489</v>
+        <v>893322.605063271</v>
       </c>
       <c r="P1013" t="n">
         <v>2900</v>
@@ -44784,10 +44784,10 @@
         <v>81</v>
       </c>
       <c r="N1019" t="n">
-        <v>1595.5196456996</v>
+        <v>1595.5195815035</v>
       </c>
       <c r="O1019" t="n">
-        <v>129237.0913016676</v>
+        <v>129237.0861017835</v>
       </c>
       <c r="P1019" t="n">
         <v>2500</v>
@@ -45538,10 +45538,10 @@
         <v>7</v>
       </c>
       <c r="N1035" t="n">
-        <v>11866.99440678</v>
+        <v>11866.994561404</v>
       </c>
       <c r="O1035" t="n">
-        <v>83068.96084746001</v>
+        <v>83068.961929828</v>
       </c>
       <c r="P1035" t="n">
         <v>55000</v>
@@ -45631,10 +45631,10 @@
         <v>700</v>
       </c>
       <c r="N1037" t="n">
-        <v>3063.6218721917</v>
+        <v>3063.6218731269</v>
       </c>
       <c r="O1037" t="n">
-        <v>2144535.31053419</v>
+        <v>2144535.31118883</v>
       </c>
       <c r="P1037" t="n">
         <v>3500</v>
@@ -45726,10 +45726,10 @@
         <v>2</v>
       </c>
       <c r="N1039" t="n">
-        <v>3879.9738095238</v>
+        <v>3879.9757142857</v>
       </c>
       <c r="O1039" t="n">
-        <v>7759.9476190476</v>
+        <v>7759.9514285714</v>
       </c>
       <c r="P1039" t="n">
         <v>12500</v>
@@ -48366,10 +48366,10 @@
         <v>43</v>
       </c>
       <c r="N1095" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398308668</v>
       </c>
       <c r="O1095" t="n">
-        <v>303018.4127334171</v>
+        <v>303018.4127272724</v>
       </c>
       <c r="P1095" t="n">
         <v>9900</v>
@@ -48981,10 +48981,10 @@
         <v>104</v>
       </c>
       <c r="N1108" t="n">
-        <v>430.6099770247</v>
+        <v>430.60997670355</v>
       </c>
       <c r="O1108" t="n">
-        <v>44783.4376105688</v>
+        <v>44783.4375771692</v>
       </c>
       <c r="P1108" t="n">
         <v>2200</v>
@@ -50345,7 +50345,7 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
@@ -50354,19 +50354,19 @@
         <v>0</v>
       </c>
       <c r="M1140" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N1140" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1140" t="n">
-        <v>601379.1</v>
+        <v>595015.3</v>
       </c>
       <c r="P1140" t="n">
         <v>5100</v>
       </c>
       <c r="Q1140" t="n">
-        <v>963900</v>
+        <v>953700</v>
       </c>
     </row>
     <row r="1141">
@@ -50864,7 +50864,7 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -50873,19 +50873,19 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="N1152" t="n">
-        <v>2523.3377672076</v>
+        <v>2523.3377665827</v>
       </c>
       <c r="O1152" t="n">
-        <v>4991162.103536633</v>
+        <v>4988638.764533998</v>
       </c>
       <c r="P1152" t="n">
         <v>2800</v>
       </c>
       <c r="Q1152" t="n">
-        <v>5538400</v>
+        <v>5535600</v>
       </c>
     </row>
     <row r="1153">
@@ -51540,10 +51540,10 @@
         <v>1</v>
       </c>
       <c r="N1167" t="n">
-        <v>1757.3204971319</v>
+        <v>1757.320503876</v>
       </c>
       <c r="O1167" t="n">
-        <v>1757.3204971319</v>
+        <v>1757.320503876</v>
       </c>
       <c r="P1167" t="n">
         <v>2000</v>
@@ -54233,7 +54233,7 @@
         </is>
       </c>
       <c r="J1226" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K1226" t="n">
         <v>0</v>
@@ -54242,19 +54242,19 @@
         <v>0</v>
       </c>
       <c r="M1226" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="N1226" t="n">
         <v>2058.92</v>
       </c>
       <c r="O1226" t="n">
-        <v>609440.3200000001</v>
+        <v>599145.72</v>
       </c>
       <c r="P1226" t="n">
         <v>2500</v>
       </c>
       <c r="Q1226" t="n">
-        <v>740000</v>
+        <v>727500</v>
       </c>
     </row>
     <row r="1227">
@@ -61919,7 +61919,7 @@
         </is>
       </c>
       <c r="J1412" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K1412" t="n">
         <v>0</v>
@@ -61928,19 +61928,19 @@
         <v>0</v>
       </c>
       <c r="M1412" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N1412" t="n">
         <v>4550</v>
       </c>
       <c r="O1412" t="n">
-        <v>737100</v>
+        <v>723450</v>
       </c>
       <c r="P1412" t="n">
         <v>6500</v>
       </c>
       <c r="Q1412" t="n">
-        <v>1053000</v>
+        <v>1033500</v>
       </c>
     </row>
     <row r="1413">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -16075,10 +16075,10 @@
         <v>6</v>
       </c>
       <c r="N368" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O368" t="n">
-        <v>25454.3395833336</v>
+        <v>25163.1</v>
       </c>
       <c r="P368" t="n">
         <v>7500</v>
@@ -16255,10 +16255,10 @@
         <v>59</v>
       </c>
       <c r="N372" t="n">
-        <v>6470.8036363636</v>
+        <v>6441.03</v>
       </c>
       <c r="O372" t="n">
-        <v>381777.4145454524</v>
+        <v>380020.77</v>
       </c>
       <c r="P372" t="n">
         <v>10500</v>
@@ -25693,10 +25693,10 @@
         <v>1</v>
       </c>
       <c r="N592" t="n">
-        <v>1406.381965812</v>
+        <v>1359.89</v>
       </c>
       <c r="O592" t="n">
-        <v>1406.381965812</v>
+        <v>1359.89</v>
       </c>
       <c r="P592" t="n">
         <v>2600</v>
@@ -31933,10 +31933,10 @@
         <v>28</v>
       </c>
       <c r="N738" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O738" t="n">
-        <v>146564.4134303524</v>
+        <v>146108.772806654</v>
       </c>
       <c r="P738" t="n">
         <v>8500</v>
@@ -32396,10 +32396,10 @@
         <v>13</v>
       </c>
       <c r="N748" t="n">
-        <v>15692.208588957</v>
+        <v>15502</v>
       </c>
       <c r="O748" t="n">
-        <v>203998.711656441</v>
+        <v>201526</v>
       </c>
       <c r="P748" t="n">
         <v>25900</v>
@@ -42149,10 +42149,10 @@
         <v>539</v>
       </c>
       <c r="N960" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O960" t="n">
-        <v>1542152.189748763</v>
+        <v>1540041.58</v>
       </c>
       <c r="P960" t="n">
         <v>4900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -689,19 +689,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>66707.977073171</v>
+        <v>66707.97725</v>
       </c>
       <c r="O7" t="n">
-        <v>600371.793658539</v>
+        <v>533663.818</v>
       </c>
       <c r="P7" t="n">
         <v>125900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1133100</v>
+        <v>1007200</v>
       </c>
     </row>
     <row r="8">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -994,19 +994,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3037351443</v>
+        <v>1811.3037703513</v>
       </c>
       <c r="O14" t="n">
-        <v>742634.531409163</v>
+        <v>720898.9005998174</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>1066000</v>
+        <v>1034800</v>
       </c>
     </row>
     <row r="15">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.746520334</v>
+        <v>3376.7465175202</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.76578243</v>
+        <v>3866374.762560629</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -1325,10 +1325,10 @@
         <v>34</v>
       </c>
       <c r="N22" t="n">
-        <v>5758.9597797357</v>
+        <v>5784.4419026549</v>
       </c>
       <c r="O22" t="n">
-        <v>195804.6325110138</v>
+        <v>196671.0246902666</v>
       </c>
       <c r="P22" t="n">
         <v>16900</v>
@@ -2559,10 +2559,10 @@
         <v>294</v>
       </c>
       <c r="N52" t="n">
-        <v>4604.2</v>
+        <v>4644.5877192982</v>
       </c>
       <c r="O52" t="n">
-        <v>1353634.8</v>
+        <v>1365508.789473671</v>
       </c>
       <c r="P52" t="n">
         <v>7500</v>
@@ -2596,10 +2596,10 @@
         <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>1854.2367246377</v>
+        <v>1854.2372274143</v>
       </c>
       <c r="O53" t="n">
-        <v>12979.6570724639</v>
+        <v>12979.6605919001</v>
       </c>
       <c r="P53" t="n">
         <v>3200</v>
@@ -2638,10 +2638,10 @@
         <v>51</v>
       </c>
       <c r="N54" t="n">
-        <v>1933.3875757576</v>
+        <v>1933.3879908676</v>
       </c>
       <c r="O54" t="n">
-        <v>98602.76636363759</v>
+        <v>98602.78753424759</v>
       </c>
       <c r="P54" t="n">
         <v>4500</v>
@@ -2794,10 +2794,10 @@
         <v>123</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8539724138</v>
+        <v>6272.8541142857</v>
       </c>
       <c r="O58" t="n">
-        <v>771561.0386068973</v>
+        <v>771561.0560571412</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2835,19 +2835,19 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>127174.84</v>
+        <v>117392.16</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>239200</v>
+        <v>220800</v>
       </c>
     </row>
     <row r="60">
@@ -3000,10 +3000,10 @@
         <v>19</v>
       </c>
       <c r="N63" t="n">
-        <v>11324.694893617</v>
+        <v>11324.694146341</v>
       </c>
       <c r="O63" t="n">
-        <v>215169.202978723</v>
+        <v>215169.188780479</v>
       </c>
       <c r="P63" t="n">
         <v>19900</v>
@@ -3203,10 +3203,10 @@
         <v>296</v>
       </c>
       <c r="N68" t="n">
-        <v>2474.7042715232</v>
+        <v>2487.0572046589</v>
       </c>
       <c r="O68" t="n">
-        <v>732512.4643708672</v>
+        <v>736168.9325790344</v>
       </c>
       <c r="P68" t="n">
         <v>4500</v>
@@ -3320,10 +3320,10 @@
         <v>56</v>
       </c>
       <c r="N71" t="n">
-        <v>3716.3301863354</v>
+        <v>3716.330188383</v>
       </c>
       <c r="O71" t="n">
-        <v>208114.4904347824</v>
+        <v>208114.490549448</v>
       </c>
       <c r="P71" t="n">
         <v>9500</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3395,19 +3395,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N73" t="n">
         <v>32298.94</v>
       </c>
       <c r="O73" t="n">
-        <v>2325523.68</v>
+        <v>2293224.74</v>
       </c>
       <c r="P73" t="n">
         <v>45900</v>
       </c>
       <c r="Q73" t="n">
-        <v>3304800</v>
+        <v>3258900</v>
       </c>
     </row>
     <row r="74">
@@ -3593,10 +3593,10 @@
         <v>41</v>
       </c>
       <c r="N78" t="n">
-        <v>15403.520494505</v>
+        <v>15403.520852273</v>
       </c>
       <c r="O78" t="n">
-        <v>631544.3402747051</v>
+        <v>631544.354943193</v>
       </c>
       <c r="P78" t="n">
         <v>33500</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3629,19 +3629,19 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N79" t="n">
-        <v>14857.62306383</v>
+        <v>14857.623171806</v>
       </c>
       <c r="O79" t="n">
-        <v>1144036.97591491</v>
+        <v>1129179.361057256</v>
       </c>
       <c r="P79" t="n">
         <v>34900</v>
       </c>
       <c r="Q79" t="n">
-        <v>2687300</v>
+        <v>2652400</v>
       </c>
     </row>
     <row r="80">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4095,19 +4095,19 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N90" t="n">
-        <v>3910.628317757</v>
+        <v>3910.628245614</v>
       </c>
       <c r="O90" t="n">
-        <v>74301.93803738299</v>
+        <v>66480.680175438</v>
       </c>
       <c r="P90" t="n">
         <v>9100</v>
       </c>
       <c r="Q90" t="n">
-        <v>172900</v>
+        <v>154700</v>
       </c>
     </row>
     <row r="91">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -5003,19 +5003,19 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N110" t="n">
-        <v>10994.352121212</v>
+        <v>10994.352244898</v>
       </c>
       <c r="O110" t="n">
-        <v>142926.577575756</v>
+        <v>131932.226938776</v>
       </c>
       <c r="P110" t="n">
         <v>16900</v>
       </c>
       <c r="Q110" t="n">
-        <v>219700</v>
+        <v>202800</v>
       </c>
     </row>
     <row r="111">
@@ -5053,10 +5053,10 @@
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>18835.015416667</v>
+        <v>20547.289545455</v>
       </c>
       <c r="O111" t="n">
-        <v>18835.015416667</v>
+        <v>20547.289545455</v>
       </c>
       <c r="P111" t="n">
         <v>40500</v>
@@ -5176,10 +5176,10 @@
         <v>20</v>
       </c>
       <c r="N114" t="n">
-        <v>15711.966317829</v>
+        <v>15834.716054688</v>
       </c>
       <c r="O114" t="n">
-        <v>314239.32635658</v>
+        <v>316694.32109376</v>
       </c>
       <c r="P114" t="n">
         <v>28500</v>
@@ -5223,10 +5223,10 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>9392.0744155844</v>
+        <v>9642.5297333333</v>
       </c>
       <c r="O115" t="n">
-        <v>9392.0744155844</v>
+        <v>9642.5297333333</v>
       </c>
       <c r="P115" t="n">
         <v>18500</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6512,19 +6512,19 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>200072.19902098</v>
+        <v>200072.19914894</v>
       </c>
       <c r="O146" t="n">
-        <v>400144.39804196</v>
+        <v>200072.19914894</v>
       </c>
       <c r="P146" t="n">
         <v>312000</v>
       </c>
       <c r="Q146" t="n">
-        <v>624000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="147">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6554,19 +6554,19 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N147" t="n">
-        <v>174389.78625</v>
+        <v>174389.78666667</v>
       </c>
       <c r="O147" t="n">
-        <v>1220728.50375</v>
+        <v>1046338.72000002</v>
       </c>
       <c r="P147" t="n">
         <v>368200</v>
       </c>
       <c r="Q147" t="n">
-        <v>2577400</v>
+        <v>2209200</v>
       </c>
     </row>
     <row r="148">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6601,19 +6601,19 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N148" t="n">
-        <v>251809.29411765</v>
+        <v>251809.29393939</v>
       </c>
       <c r="O148" t="n">
-        <v>1510855.7647059</v>
+        <v>1259046.46969695</v>
       </c>
       <c r="P148" t="n">
         <v>584000</v>
       </c>
       <c r="Q148" t="n">
-        <v>3504000</v>
+        <v>2920000</v>
       </c>
     </row>
     <row r="149">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6895,19 +6895,19 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N155" t="n">
         <v>1977.88</v>
       </c>
       <c r="O155" t="n">
-        <v>193832.24</v>
+        <v>191854.36</v>
       </c>
       <c r="P155" t="n">
         <v>2900</v>
       </c>
       <c r="Q155" t="n">
-        <v>284200</v>
+        <v>281300</v>
       </c>
     </row>
     <row r="156">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -7898,19 +7898,19 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N179" t="n">
         <v>5686.27</v>
       </c>
       <c r="O179" t="n">
-        <v>22745.08</v>
+        <v>17058.81</v>
       </c>
       <c r="P179" t="n">
         <v>11500</v>
       </c>
       <c r="Q179" t="n">
-        <v>46000</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="180">
@@ -8262,10 +8262,10 @@
         <v>44</v>
       </c>
       <c r="N187" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2859036145</v>
       </c>
       <c r="O187" t="n">
-        <v>214644.5518279568</v>
+        <v>214644.579759038</v>
       </c>
       <c r="P187" t="n">
         <v>13500</v>
@@ -8303,10 +8303,10 @@
         <v>115</v>
       </c>
       <c r="N188" t="n">
-        <v>7394.9353846154</v>
+        <v>7477.1013333333</v>
       </c>
       <c r="O188" t="n">
-        <v>850417.569230771</v>
+        <v>859866.6533333295</v>
       </c>
       <c r="P188" t="n">
         <v>17900</v>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8339,19 +8339,19 @@
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N189" t="n">
         <v>3114.49</v>
       </c>
       <c r="O189" t="n">
-        <v>230472.26</v>
+        <v>224243.28</v>
       </c>
       <c r="P189" t="n">
         <v>5500</v>
       </c>
       <c r="Q189" t="n">
-        <v>407000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="190">
@@ -9104,10 +9104,10 @@
         <v>27</v>
       </c>
       <c r="N207" t="n">
-        <v>3340.6800784314</v>
+        <v>3340.6800808081</v>
       </c>
       <c r="O207" t="n">
-        <v>90198.3621176478</v>
+        <v>90198.36218181869</v>
       </c>
       <c r="P207" t="n">
         <v>7100</v>
@@ -9187,10 +9187,10 @@
         <v>101</v>
       </c>
       <c r="N209" t="n">
-        <v>2563.34</v>
+        <v>2576.9026455026</v>
       </c>
       <c r="O209" t="n">
-        <v>258897.34</v>
+        <v>260267.1671957626</v>
       </c>
       <c r="P209" t="n">
         <v>4700</v>
@@ -9275,10 +9275,10 @@
         <v>62</v>
       </c>
       <c r="N211" t="n">
-        <v>11513.19</v>
+        <v>11705.0765</v>
       </c>
       <c r="O211" t="n">
-        <v>713817.78</v>
+        <v>725714.7429999999</v>
       </c>
       <c r="P211" t="n">
         <v>17900</v>
@@ -9400,10 +9400,10 @@
         <v>4</v>
       </c>
       <c r="N214" t="n">
-        <v>39146.275</v>
+        <v>39146.2755</v>
       </c>
       <c r="O214" t="n">
-        <v>156585.1</v>
+        <v>156585.102</v>
       </c>
       <c r="P214" t="n">
         <v>70900</v>
@@ -9831,7 +9831,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -9840,19 +9840,19 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="N224" t="n">
         <v>2833</v>
       </c>
       <c r="O224" t="n">
-        <v>1830118</v>
+        <v>1804621</v>
       </c>
       <c r="P224" t="n">
         <v>3500</v>
       </c>
       <c r="Q224" t="n">
-        <v>2261000</v>
+        <v>2229500</v>
       </c>
     </row>
     <row r="225">
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>9504</v>
+        <v>9464</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -9922,19 +9922,19 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>9504</v>
+        <v>9464</v>
       </c>
       <c r="N226" t="n">
         <v>1726.32</v>
       </c>
       <c r="O226" t="n">
-        <v>16406945.28</v>
+        <v>16337892.48</v>
       </c>
       <c r="P226" t="n">
         <v>1500</v>
       </c>
       <c r="Q226" t="n">
-        <v>14256000</v>
+        <v>14196000</v>
       </c>
     </row>
     <row r="227">
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -10178,19 +10178,19 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N232" t="n">
         <v>6513</v>
       </c>
       <c r="O232" t="n">
-        <v>905307</v>
+        <v>898794</v>
       </c>
       <c r="P232" t="n">
         <v>11500</v>
       </c>
       <c r="Q232" t="n">
-        <v>1598500</v>
+        <v>1587000</v>
       </c>
     </row>
     <row r="233">
@@ -10464,7 +10464,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10473,19 +10473,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0523152957</v>
+        <v>1098.0525080824</v>
       </c>
       <c r="O239" t="n">
-        <v>1550449.869197529</v>
+        <v>1541665.72134769</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
       </c>
       <c r="Q239" t="n">
-        <v>2118000</v>
+        <v>2106000</v>
       </c>
     </row>
     <row r="240">
@@ -11657,10 +11657,10 @@
         <v>310</v>
       </c>
       <c r="N267" t="n">
-        <v>13593.35</v>
+        <v>13624.59908046</v>
       </c>
       <c r="O267" t="n">
-        <v>4213938.5</v>
+        <v>4223625.714942601</v>
       </c>
       <c r="P267" t="n">
         <v>25500</v>
@@ -12356,10 +12356,10 @@
         <v>181</v>
       </c>
       <c r="N283" t="n">
-        <v>2033.5796673597</v>
+        <v>2033.5778733032</v>
       </c>
       <c r="O283" t="n">
-        <v>368077.9197921057</v>
+        <v>368077.5950678792</v>
       </c>
       <c r="P283" t="n">
         <v>4100</v>
@@ -12648,10 +12648,10 @@
         <v>2839</v>
       </c>
       <c r="N290" t="n">
-        <v>3158.860813208</v>
+        <v>3158.8608137572</v>
       </c>
       <c r="O290" t="n">
-        <v>8968005.848697511</v>
+        <v>8968005.850256691</v>
       </c>
       <c r="P290" t="n">
         <v>5600</v>
@@ -12740,10 +12740,10 @@
         <v>234</v>
       </c>
       <c r="N292" t="n">
-        <v>3841.6246641075</v>
+        <v>3841.6246911197</v>
       </c>
       <c r="O292" t="n">
-        <v>898940.1714011549</v>
+        <v>898940.1777220098</v>
       </c>
       <c r="P292" t="n">
         <v>6900</v>
@@ -12922,10 +12922,10 @@
         <v>94</v>
       </c>
       <c r="N296" t="n">
-        <v>3230.0678931298</v>
+        <v>3230.067792</v>
       </c>
       <c r="O296" t="n">
-        <v>303626.3819542012</v>
+        <v>303626.372448</v>
       </c>
       <c r="P296" t="n">
         <v>6200</v>
@@ -13142,10 +13142,10 @@
         <v>44</v>
       </c>
       <c r="N301" t="n">
-        <v>2694.8235409253</v>
+        <v>2694.8235120643</v>
       </c>
       <c r="O301" t="n">
-        <v>118572.2358007132</v>
+        <v>118572.2345308292</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13636,19 +13636,19 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N312" t="n">
         <v>3684</v>
       </c>
       <c r="O312" t="n">
-        <v>1212036</v>
+        <v>1200984</v>
       </c>
       <c r="P312" t="n">
         <v>6200</v>
       </c>
       <c r="Q312" t="n">
-        <v>2039800</v>
+        <v>2021200</v>
       </c>
     </row>
     <row r="313">
@@ -13982,10 +13982,10 @@
         <v>331</v>
       </c>
       <c r="N320" t="n">
-        <v>4890.9300453515</v>
+        <v>4890.9300454545</v>
       </c>
       <c r="O320" t="n">
-        <v>1618897.845011347</v>
+        <v>1618897.845045439</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14028,10 +14028,10 @@
         <v>21</v>
       </c>
       <c r="N321" t="n">
-        <v>4967.8119354839</v>
+        <v>4967.814</v>
       </c>
       <c r="O321" t="n">
-        <v>104324.0506451619</v>
+        <v>104324.094</v>
       </c>
       <c r="P321" t="n">
         <v>7500</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>1695</v>
+        <v>1623</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -14827,19 +14827,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>1695</v>
+        <v>1623</v>
       </c>
       <c r="N339" t="n">
         <v>489.88</v>
       </c>
       <c r="O339" t="n">
-        <v>830346.6</v>
+        <v>795075.24</v>
       </c>
       <c r="P339" t="n">
         <v>700</v>
       </c>
       <c r="Q339" t="n">
-        <v>1186500</v>
+        <v>1136100</v>
       </c>
     </row>
     <row r="340">
@@ -14953,10 +14953,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3240.8500289017</v>
+        <v>3240.8500291121</v>
       </c>
       <c r="O342" t="n">
-        <v>3240.8500289017</v>
+        <v>3240.8500291121</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -14999,10 +14999,10 @@
         <v>6</v>
       </c>
       <c r="N343" t="n">
-        <v>4891</v>
+        <v>4898.3218562874</v>
       </c>
       <c r="O343" t="n">
-        <v>29346</v>
+        <v>29389.9311377244</v>
       </c>
       <c r="P343" t="n">
         <v>8200</v>
@@ -15711,7 +15711,7 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
@@ -15720,19 +15720,19 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="N360" t="n">
         <v>1441.01</v>
       </c>
       <c r="O360" t="n">
-        <v>3964218.51</v>
+        <v>3961336.49</v>
       </c>
       <c r="P360" t="n">
         <v>2100</v>
       </c>
       <c r="Q360" t="n">
-        <v>5777100</v>
+        <v>5772900</v>
       </c>
     </row>
     <row r="361">
@@ -15981,7 +15981,7 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
@@ -15990,19 +15990,19 @@
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N366" t="n">
-        <v>3041.6600120048</v>
+        <v>3041.6600123153</v>
       </c>
       <c r="O366" t="n">
-        <v>568790.4222448976</v>
+        <v>565748.7622906457</v>
       </c>
       <c r="P366" t="n">
         <v>5500</v>
       </c>
       <c r="Q366" t="n">
-        <v>1028500</v>
+        <v>1023000</v>
       </c>
     </row>
     <row r="367">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16077,19 +16077,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N368" t="n">
         <v>4086.2</v>
       </c>
       <c r="O368" t="n">
-        <v>1920514</v>
+        <v>1908255.4</v>
       </c>
       <c r="P368" t="n">
         <v>6900</v>
       </c>
       <c r="Q368" t="n">
-        <v>3243000</v>
+        <v>3222300</v>
       </c>
     </row>
     <row r="369">
@@ -16252,10 +16252,10 @@
         <v>650</v>
       </c>
       <c r="N372" t="n">
-        <v>1592.567877551</v>
+        <v>1592.567808681</v>
       </c>
       <c r="O372" t="n">
-        <v>1035169.12040815</v>
+        <v>1035169.07564265</v>
       </c>
       <c r="P372" t="n">
         <v>3900</v>
@@ -16845,7 +16845,7 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
@@ -16854,19 +16854,19 @@
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N386" t="n">
         <v>4648.6</v>
       </c>
       <c r="O386" t="n">
-        <v>1245824.8</v>
+        <v>1231879</v>
       </c>
       <c r="P386" t="n">
         <v>8900</v>
       </c>
       <c r="Q386" t="n">
-        <v>2385200</v>
+        <v>2358500</v>
       </c>
     </row>
     <row r="387">
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -16983,19 +16983,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="N389" t="n">
         <v>1312.43</v>
       </c>
       <c r="O389" t="n">
-        <v>1376739.07</v>
+        <v>1374114.21</v>
       </c>
       <c r="P389" t="n">
         <v>2300</v>
       </c>
       <c r="Q389" t="n">
-        <v>2412700</v>
+        <v>2408100</v>
       </c>
     </row>
     <row r="390">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -17109,19 +17109,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N392" t="n">
         <v>1343.77</v>
       </c>
       <c r="O392" t="n">
-        <v>318473.49</v>
+        <v>313098.41</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
       </c>
       <c r="Q392" t="n">
-        <v>592500</v>
+        <v>582500</v>
       </c>
     </row>
     <row r="393">
@@ -17232,7 +17232,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>3122</v>
+        <v>3100</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -17241,19 +17241,19 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>3122</v>
+        <v>3100</v>
       </c>
       <c r="N395" t="n">
         <v>1387.55</v>
       </c>
       <c r="O395" t="n">
-        <v>4331931.1</v>
+        <v>4301405</v>
       </c>
       <c r="P395" t="n">
         <v>2300</v>
       </c>
       <c r="Q395" t="n">
-        <v>7180600</v>
+        <v>7130000</v>
       </c>
     </row>
     <row r="396">
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -18385,19 +18385,19 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N421" t="n">
         <v>3751</v>
       </c>
       <c r="O421" t="n">
-        <v>270072</v>
+        <v>258819</v>
       </c>
       <c r="P421" t="n">
         <v>6400</v>
       </c>
       <c r="Q421" t="n">
-        <v>460800</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="422">
@@ -18602,7 +18602,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -18611,19 +18611,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="N426" t="n">
-        <v>1630.9229073724</v>
+        <v>1630.9229356747</v>
       </c>
       <c r="O426" t="n">
-        <v>965506.3611644608</v>
+        <v>962244.532048073</v>
       </c>
       <c r="P426" t="n">
         <v>2500</v>
       </c>
       <c r="Q426" t="n">
-        <v>1480000</v>
+        <v>1475000</v>
       </c>
     </row>
     <row r="427">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
@@ -18703,19 +18703,19 @@
         <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="N428" t="n">
-        <v>1550.1928456407</v>
+        <v>1550.192872291</v>
       </c>
       <c r="O428" t="n">
-        <v>1942391.635587797</v>
+        <v>1937741.09036375</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
       </c>
       <c r="Q428" t="n">
-        <v>3132500</v>
+        <v>3125000</v>
       </c>
     </row>
     <row r="429">
@@ -18798,10 +18798,10 @@
         <v>951</v>
       </c>
       <c r="N430" t="n">
-        <v>2403.5097473321</v>
+        <v>2403.5098964308</v>
       </c>
       <c r="O430" t="n">
-        <v>2285737.769712827</v>
+        <v>2285737.911505691</v>
       </c>
       <c r="P430" t="n">
         <v>3500</v>
@@ -18876,7 +18876,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -18885,19 +18885,19 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N432" t="n">
-        <v>2521.5490111248</v>
+        <v>2521.5486317136</v>
       </c>
       <c r="O432" t="n">
-        <v>799331.0365265616</v>
+        <v>789244.7217263569</v>
       </c>
       <c r="P432" t="n">
         <v>3900</v>
       </c>
       <c r="Q432" t="n">
-        <v>1236300</v>
+        <v>1220700</v>
       </c>
     </row>
     <row r="433">
@@ -19057,10 +19057,10 @@
         <v>17</v>
       </c>
       <c r="N436" t="n">
-        <v>11507.72</v>
+        <v>11658.147712418</v>
       </c>
       <c r="O436" t="n">
-        <v>195631.24</v>
+        <v>198188.511111106</v>
       </c>
       <c r="P436" t="n">
         <v>25800</v>
@@ -20929,7 +20929,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -20938,19 +20938,19 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N479" t="n">
         <v>6280.31</v>
       </c>
       <c r="O479" t="n">
-        <v>69083.41</v>
+        <v>50242.48</v>
       </c>
       <c r="P479" t="n">
         <v>10500</v>
       </c>
       <c r="Q479" t="n">
-        <v>115500</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="480">
@@ -22205,7 +22205,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -22214,19 +22214,19 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N509" t="n">
         <v>9338</v>
       </c>
       <c r="O509" t="n">
-        <v>392196</v>
+        <v>382858</v>
       </c>
       <c r="P509" t="n">
         <v>15500</v>
       </c>
       <c r="Q509" t="n">
-        <v>651000</v>
+        <v>635500</v>
       </c>
     </row>
     <row r="510">
@@ -22679,10 +22679,10 @@
         <v>11</v>
       </c>
       <c r="N520" t="n">
-        <v>2661.82</v>
+        <v>2667.5690712743</v>
       </c>
       <c r="O520" t="n">
-        <v>29280.02</v>
+        <v>29343.2597840173</v>
       </c>
       <c r="P520" t="n">
         <v>3200</v>
@@ -22761,10 +22761,10 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>4488</v>
+        <v>4508.1255605381</v>
       </c>
       <c r="O522" t="n">
-        <v>4488</v>
+        <v>4508.1255605381</v>
       </c>
       <c r="P522" t="n">
         <v>6200</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -22881,19 +22881,19 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="N525" t="n">
         <v>1969</v>
       </c>
       <c r="O525" t="n">
-        <v>439087</v>
+        <v>433180</v>
       </c>
       <c r="P525" t="n">
         <v>1500</v>
       </c>
       <c r="Q525" t="n">
-        <v>334500</v>
+        <v>330000</v>
       </c>
     </row>
     <row r="526">
@@ -23469,10 +23469,10 @@
         <v>248</v>
       </c>
       <c r="N539" t="n">
-        <v>2029.8735277516</v>
+        <v>2029.8735344015</v>
       </c>
       <c r="O539" t="n">
-        <v>503408.6348823968</v>
+        <v>503408.636531572</v>
       </c>
       <c r="P539" t="n">
         <v>3600</v>
@@ -23551,10 +23551,10 @@
         <v>1</v>
       </c>
       <c r="N541" t="n">
-        <v>22485.695955056</v>
+        <v>22485.695945946</v>
       </c>
       <c r="O541" t="n">
-        <v>22485.695955056</v>
+        <v>22485.695945946</v>
       </c>
       <c r="P541" t="n">
         <v>36500</v>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -23712,19 +23712,19 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="N545" t="n">
         <v>2673</v>
       </c>
       <c r="O545" t="n">
-        <v>799227</v>
+        <v>785862</v>
       </c>
       <c r="P545" t="n">
         <v>2500</v>
       </c>
       <c r="Q545" t="n">
-        <v>747500</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="546">
@@ -24297,10 +24297,10 @@
         <v>622</v>
       </c>
       <c r="N559" t="n">
-        <v>880.32918386061</v>
+        <v>880.32919651056</v>
       </c>
       <c r="O559" t="n">
-        <v>547564.7523612995</v>
+        <v>547564.7602295683</v>
       </c>
       <c r="P559" t="n">
         <v>1200</v>
@@ -25550,7 +25550,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>127</v>
+        <v>358</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -25559,19 +25559,19 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>127</v>
+        <v>358</v>
       </c>
       <c r="N589" t="n">
         <v>3877.89</v>
       </c>
       <c r="O589" t="n">
-        <v>492492.03</v>
+        <v>1388284.62</v>
       </c>
       <c r="P589" t="n">
         <v>6500</v>
       </c>
       <c r="Q589" t="n">
-        <v>825500</v>
+        <v>2327000</v>
       </c>
     </row>
     <row r="590">
@@ -25652,10 +25652,10 @@
         <v>5</v>
       </c>
       <c r="N591" t="n">
-        <v>4285.1951678535</v>
+        <v>4285.1952156057</v>
       </c>
       <c r="O591" t="n">
-        <v>21425.9758392675</v>
+        <v>21425.9760780285</v>
       </c>
       <c r="P591" t="n">
         <v>6900</v>
@@ -26428,10 +26428,10 @@
         <v>2</v>
       </c>
       <c r="N609" t="n">
-        <v>13513.642887324</v>
+        <v>13805.304244604</v>
       </c>
       <c r="O609" t="n">
-        <v>27027.285774648</v>
+        <v>27610.608489208</v>
       </c>
       <c r="P609" t="n">
         <v>21900</v>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
@@ -26599,19 +26599,19 @@
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="N613" t="n">
         <v>1650</v>
       </c>
       <c r="O613" t="n">
-        <v>660000</v>
+        <v>656700</v>
       </c>
       <c r="P613" t="n">
         <v>2900</v>
       </c>
       <c r="Q613" t="n">
-        <v>1160000</v>
+        <v>1154200</v>
       </c>
     </row>
     <row r="614">
@@ -26836,7 +26836,7 @@
         </is>
       </c>
       <c r="J619" t="n">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
@@ -26845,19 +26845,19 @@
         <v>0</v>
       </c>
       <c r="M619" t="n">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="N619" t="n">
         <v>1664</v>
       </c>
       <c r="O619" t="n">
-        <v>758784</v>
+        <v>745472</v>
       </c>
       <c r="P619" t="n">
         <v>2900</v>
       </c>
       <c r="Q619" t="n">
-        <v>1322400</v>
+        <v>1299200</v>
       </c>
     </row>
     <row r="620">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
@@ -26886,19 +26886,19 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N620" t="n">
         <v>1358</v>
       </c>
       <c r="O620" t="n">
-        <v>343574</v>
+        <v>335426</v>
       </c>
       <c r="P620" t="n">
         <v>2400</v>
       </c>
       <c r="Q620" t="n">
-        <v>607200</v>
+        <v>592800</v>
       </c>
     </row>
     <row r="621">
@@ -26918,7 +26918,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -26927,19 +26927,19 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="N621" t="n">
         <v>881</v>
       </c>
       <c r="O621" t="n">
-        <v>402617</v>
+        <v>397331</v>
       </c>
       <c r="P621" t="n">
         <v>1500</v>
       </c>
       <c r="Q621" t="n">
-        <v>685500</v>
+        <v>676500</v>
       </c>
     </row>
     <row r="622">
@@ -27000,7 +27000,7 @@
         </is>
       </c>
       <c r="J623" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K623" t="n">
         <v>0</v>
@@ -27009,19 +27009,19 @@
         <v>0</v>
       </c>
       <c r="M623" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N623" t="n">
         <v>1352</v>
       </c>
       <c r="O623" t="n">
-        <v>271752</v>
+        <v>269048</v>
       </c>
       <c r="P623" t="n">
         <v>2400</v>
       </c>
       <c r="Q623" t="n">
-        <v>482400</v>
+        <v>477600</v>
       </c>
     </row>
     <row r="624">
@@ -27884,7 +27884,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -27893,19 +27893,19 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N644" t="n">
         <v>4793.53</v>
       </c>
       <c r="O644" t="n">
-        <v>1725670.8</v>
+        <v>1720877.27</v>
       </c>
       <c r="P644" t="n">
         <v>7900</v>
       </c>
       <c r="Q644" t="n">
-        <v>2844000</v>
+        <v>2836100</v>
       </c>
     </row>
     <row r="645">
@@ -28099,7 +28099,7 @@
         </is>
       </c>
       <c r="J649" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K649" t="n">
         <v>0</v>
@@ -28108,19 +28108,19 @@
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N649" t="n">
         <v>22730.48</v>
       </c>
       <c r="O649" t="n">
-        <v>1318367.84</v>
+        <v>1295637.36</v>
       </c>
       <c r="P649" t="n">
         <v>36900</v>
       </c>
       <c r="Q649" t="n">
-        <v>2140200</v>
+        <v>2103300</v>
       </c>
     </row>
     <row r="650">
@@ -28372,10 +28372,10 @@
         <v>143</v>
       </c>
       <c r="N655" t="n">
-        <v>27123.765268022</v>
+        <v>27123.765259259</v>
       </c>
       <c r="O655" t="n">
-        <v>3878698.433327146</v>
+        <v>3878698.432074037</v>
       </c>
       <c r="P655" t="n">
         <v>44500</v>
@@ -29048,10 +29048,10 @@
         <v>47</v>
       </c>
       <c r="N671" t="n">
-        <v>5431.12</v>
+        <v>5453.6557676349</v>
       </c>
       <c r="O671" t="n">
-        <v>255262.64</v>
+        <v>256321.8210788403</v>
       </c>
       <c r="P671" t="n">
         <v>8900</v>
@@ -29082,7 +29082,7 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -29091,19 +29091,19 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N672" t="n">
-        <v>1560.9982458387</v>
+        <v>1560.9983239983</v>
       </c>
       <c r="O672" t="n">
-        <v>885086.0053905429</v>
+        <v>880403.0547350412</v>
       </c>
       <c r="P672" t="n">
         <v>2900</v>
       </c>
       <c r="Q672" t="n">
-        <v>1644300</v>
+        <v>1635600</v>
       </c>
     </row>
     <row r="673">
@@ -29309,10 +29309,10 @@
         <v>22</v>
       </c>
       <c r="N677" t="n">
-        <v>26854</v>
+        <v>27226.972222222</v>
       </c>
       <c r="O677" t="n">
-        <v>590788</v>
+        <v>598993.388888884</v>
       </c>
       <c r="P677" t="n">
         <v>43900</v>
@@ -29968,7 +29968,7 @@
         </is>
       </c>
       <c r="J693" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K693" t="n">
         <v>0</v>
@@ -29977,19 +29977,19 @@
         <v>0</v>
       </c>
       <c r="M693" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N693" t="n">
         <v>9627.34</v>
       </c>
       <c r="O693" t="n">
-        <v>442857.64</v>
+        <v>413975.62</v>
       </c>
       <c r="P693" t="n">
         <v>15900</v>
       </c>
       <c r="Q693" t="n">
-        <v>731400</v>
+        <v>683700</v>
       </c>
     </row>
     <row r="694">
@@ -30646,10 +30646,10 @@
         <v>25</v>
       </c>
       <c r="N709" t="n">
-        <v>13878.97</v>
+        <v>13971.496466667</v>
       </c>
       <c r="O709" t="n">
-        <v>346974.25</v>
+        <v>349287.411666675</v>
       </c>
       <c r="P709" t="n">
         <v>21900</v>
@@ -31342,10 +31342,10 @@
         <v>69</v>
       </c>
       <c r="N725" t="n">
-        <v>3113.8900237812</v>
+        <v>3117.5970357143</v>
       </c>
       <c r="O725" t="n">
-        <v>214858.4116409028</v>
+        <v>215114.1954642867</v>
       </c>
       <c r="P725" t="n">
         <v>5000</v>
@@ -31618,10 +31618,10 @@
         <v>19</v>
       </c>
       <c r="N731" t="n">
-        <v>8878.450000000001</v>
+        <v>9099.032608695699</v>
       </c>
       <c r="O731" t="n">
-        <v>168690.55</v>
+        <v>172881.6195652183</v>
       </c>
       <c r="P731" t="n">
         <v>14100</v>
@@ -31664,10 +31664,10 @@
         <v>113</v>
       </c>
       <c r="N732" t="n">
-        <v>2495.98</v>
+        <v>2498.7228351648</v>
       </c>
       <c r="O732" t="n">
-        <v>282045.74</v>
+        <v>282355.6803736224</v>
       </c>
       <c r="P732" t="n">
         <v>4100</v>
@@ -31756,10 +31756,10 @@
         <v>24</v>
       </c>
       <c r="N734" t="n">
-        <v>5218.1704631579</v>
+        <v>5218.1704646251</v>
       </c>
       <c r="O734" t="n">
-        <v>125236.0911157896</v>
+        <v>125236.0911510024</v>
       </c>
       <c r="P734" t="n">
         <v>8500</v>
@@ -31802,10 +31802,10 @@
         <v>21</v>
       </c>
       <c r="N735" t="n">
-        <v>1595.009520202</v>
+        <v>1595.0095153061</v>
       </c>
       <c r="O735" t="n">
-        <v>33495.199924242</v>
+        <v>33495.1998214281</v>
       </c>
       <c r="P735" t="n">
         <v>2600</v>
@@ -31848,10 +31848,10 @@
         <v>28</v>
       </c>
       <c r="N736" t="n">
-        <v>3610.6500229095</v>
+        <v>3610.650023015</v>
       </c>
       <c r="O736" t="n">
-        <v>101098.200641466</v>
+        <v>101098.20064442</v>
       </c>
       <c r="P736" t="n">
         <v>5800</v>
@@ -31989,10 +31989,10 @@
         <v>43</v>
       </c>
       <c r="N739" t="n">
-        <v>3965.02</v>
+        <v>3969.9272029703</v>
       </c>
       <c r="O739" t="n">
-        <v>170495.86</v>
+        <v>170706.8697277229</v>
       </c>
       <c r="P739" t="n">
         <v>6500</v>
@@ -32035,10 +32035,10 @@
         <v>40</v>
       </c>
       <c r="N740" t="n">
-        <v>5791.05</v>
+        <v>5844.4237327189</v>
       </c>
       <c r="O740" t="n">
-        <v>231642</v>
+        <v>233776.949308756</v>
       </c>
       <c r="P740" t="n">
         <v>9300</v>
@@ -32173,10 +32173,10 @@
         <v>162</v>
       </c>
       <c r="N743" t="n">
-        <v>1664.3618458274</v>
+        <v>1664.3615095729</v>
       </c>
       <c r="O743" t="n">
-        <v>269626.6190240388</v>
+        <v>269626.5645508098</v>
       </c>
       <c r="P743" t="n">
         <v>2900</v>
@@ -32757,7 +32757,7 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
@@ -32766,19 +32766,19 @@
         <v>0</v>
       </c>
       <c r="M756" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N756" t="n">
         <v>63521</v>
       </c>
       <c r="O756" t="n">
-        <v>444647</v>
+        <v>317605</v>
       </c>
       <c r="P756" t="n">
         <v>105900</v>
       </c>
       <c r="Q756" t="n">
-        <v>741300</v>
+        <v>529500</v>
       </c>
     </row>
     <row r="757">
@@ -32861,10 +32861,10 @@
         <v>12</v>
       </c>
       <c r="N758" t="n">
-        <v>42899</v>
+        <v>44124.685714286</v>
       </c>
       <c r="O758" t="n">
-        <v>514788</v>
+        <v>529496.2285714321</v>
       </c>
       <c r="P758" t="n">
         <v>70900</v>
@@ -32895,7 +32895,7 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
@@ -32904,19 +32904,19 @@
         <v>0</v>
       </c>
       <c r="M759" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N759" t="n">
         <v>34546</v>
       </c>
       <c r="O759" t="n">
-        <v>1692754</v>
+        <v>1623662</v>
       </c>
       <c r="P759" t="n">
         <v>57900</v>
       </c>
       <c r="Q759" t="n">
-        <v>2837100</v>
+        <v>2721300</v>
       </c>
     </row>
     <row r="760">
@@ -33137,10 +33137,10 @@
         <v>1253</v>
       </c>
       <c r="N764" t="n">
-        <v>1778.4725014327</v>
+        <v>1778.4725043029</v>
       </c>
       <c r="O764" t="n">
-        <v>2228426.044295173</v>
+        <v>2228426.047891534</v>
       </c>
       <c r="P764" t="n">
         <v>4900</v>
@@ -33321,10 +33321,10 @@
         <v>43</v>
       </c>
       <c r="N768" t="n">
-        <v>22739</v>
+        <v>22795.894912427</v>
       </c>
       <c r="O768" t="n">
-        <v>977777</v>
+        <v>980223.481234361</v>
       </c>
       <c r="P768" t="n">
         <v>36900</v>
@@ -33413,10 +33413,10 @@
         <v>177</v>
       </c>
       <c r="N770" t="n">
-        <v>16058</v>
+        <v>16092.045229682</v>
       </c>
       <c r="O770" t="n">
-        <v>2842266</v>
+        <v>2848292.005653714</v>
       </c>
       <c r="P770" t="n">
         <v>25900</v>
@@ -34939,10 +34939,10 @@
         <v>12</v>
       </c>
       <c r="N803" t="n">
-        <v>2853.4366666667</v>
+        <v>2853.4352</v>
       </c>
       <c r="O803" t="n">
-        <v>34241.2400000004</v>
+        <v>34241.2224</v>
       </c>
       <c r="P803" t="n">
         <v>4500</v>
@@ -35353,10 +35353,10 @@
         <v>1</v>
       </c>
       <c r="N812" t="n">
-        <v>8508</v>
+        <v>9704.4375</v>
       </c>
       <c r="O812" t="n">
-        <v>8508</v>
+        <v>9704.4375</v>
       </c>
       <c r="P812" t="n">
         <v>14500</v>
@@ -35617,7 +35617,7 @@
         </is>
       </c>
       <c r="J818" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K818" t="n">
         <v>0</v>
@@ -35626,19 +35626,19 @@
         <v>0</v>
       </c>
       <c r="M818" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N818" t="n">
-        <v>2252.2960914286</v>
+        <v>2252.2962193699</v>
       </c>
       <c r="O818" t="n">
-        <v>342349.0058971472</v>
+        <v>340096.7291248549</v>
       </c>
       <c r="P818" t="n">
         <v>3900</v>
       </c>
       <c r="Q818" t="n">
-        <v>592800</v>
+        <v>588900</v>
       </c>
     </row>
     <row r="819">
@@ -35862,10 +35862,10 @@
         <v>465</v>
       </c>
       <c r="N823" t="n">
-        <v>2328.11876101</v>
+        <v>2328.1187566293</v>
       </c>
       <c r="O823" t="n">
-        <v>1082575.22386965</v>
+        <v>1082575.221832625</v>
       </c>
       <c r="P823" t="n">
         <v>4500</v>
@@ -35908,10 +35908,10 @@
         <v>87</v>
       </c>
       <c r="N824" t="n">
-        <v>21676</v>
+        <v>21748.414253898</v>
       </c>
       <c r="O824" t="n">
-        <v>1885812</v>
+        <v>1892112.040089126</v>
       </c>
       <c r="P824" t="n">
         <v>34900</v>
@@ -36264,7 +36264,7 @@
         </is>
       </c>
       <c r="J832" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K832" t="n">
         <v>0</v>
@@ -36273,19 +36273,19 @@
         <v>0</v>
       </c>
       <c r="M832" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N832" t="n">
         <v>4544</v>
       </c>
       <c r="O832" t="n">
-        <v>1331392</v>
+        <v>1326848</v>
       </c>
       <c r="P832" t="n">
         <v>7900</v>
       </c>
       <c r="Q832" t="n">
-        <v>2314700</v>
+        <v>2306800</v>
       </c>
     </row>
     <row r="833">
@@ -36460,10 +36460,10 @@
         <v>42</v>
       </c>
       <c r="N836" t="n">
-        <v>17981</v>
+        <v>18473.630136986</v>
       </c>
       <c r="O836" t="n">
-        <v>755202</v>
+        <v>775892.4657534121</v>
       </c>
       <c r="P836" t="n">
         <v>29900</v>
@@ -36598,10 +36598,10 @@
         <v>15</v>
       </c>
       <c r="N839" t="n">
-        <v>4907.8218926975</v>
+        <v>4907.821904048</v>
       </c>
       <c r="O839" t="n">
-        <v>73617.3283904625</v>
+        <v>73617.32856071999</v>
       </c>
       <c r="P839" t="n">
         <v>8200</v>
@@ -36874,10 +36874,10 @@
         <v>24</v>
       </c>
       <c r="N845" t="n">
-        <v>3903.7358031838</v>
+        <v>3903.7358605664</v>
       </c>
       <c r="O845" t="n">
-        <v>93689.6592764112</v>
+        <v>93689.6606535936</v>
       </c>
       <c r="P845" t="n">
         <v>7500</v>
@@ -37329,10 +37329,10 @@
         <v>15</v>
       </c>
       <c r="N855" t="n">
-        <v>5869.1727972028</v>
+        <v>5869.1727755511</v>
       </c>
       <c r="O855" t="n">
-        <v>88037.591958042</v>
+        <v>88037.59163326651</v>
       </c>
       <c r="P855" t="n">
         <v>9500</v>
@@ -37593,7 +37593,7 @@
         </is>
       </c>
       <c r="J861" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K861" t="n">
         <v>0</v>
@@ -37602,19 +37602,19 @@
         <v>0</v>
       </c>
       <c r="M861" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N861" t="n">
         <v>6645</v>
       </c>
       <c r="O861" t="n">
-        <v>53160</v>
+        <v>33225</v>
       </c>
       <c r="P861" t="n">
         <v>10900</v>
       </c>
       <c r="Q861" t="n">
-        <v>87200</v>
+        <v>54500</v>
       </c>
     </row>
     <row r="862">
@@ -37697,10 +37697,10 @@
         <v>20</v>
       </c>
       <c r="N863" t="n">
-        <v>27186</v>
+        <v>27422.4</v>
       </c>
       <c r="O863" t="n">
-        <v>543720</v>
+        <v>548448</v>
       </c>
       <c r="P863" t="n">
         <v>43900</v>
@@ -37835,10 +37835,10 @@
         <v>1</v>
       </c>
       <c r="N866" t="n">
-        <v>3898</v>
+        <v>3903.9739463602</v>
       </c>
       <c r="O866" t="n">
-        <v>3898</v>
+        <v>3903.9739463602</v>
       </c>
       <c r="P866" t="n">
         <v>6900</v>
@@ -37881,10 +37881,10 @@
         <v>190</v>
       </c>
       <c r="N867" t="n">
-        <v>13565</v>
+        <v>13585.460030166</v>
       </c>
       <c r="O867" t="n">
-        <v>2577350</v>
+        <v>2581237.40573154</v>
       </c>
       <c r="P867" t="n">
         <v>22500</v>
@@ -37915,7 +37915,7 @@
         </is>
       </c>
       <c r="J868" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K868" t="n">
         <v>0</v>
@@ -37924,19 +37924,19 @@
         <v>0</v>
       </c>
       <c r="M868" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N868" t="n">
         <v>7635</v>
       </c>
       <c r="O868" t="n">
-        <v>3489195</v>
+        <v>3466290</v>
       </c>
       <c r="P868" t="n">
         <v>13900</v>
       </c>
       <c r="Q868" t="n">
-        <v>6352300</v>
+        <v>6310600</v>
       </c>
     </row>
     <row r="869">
@@ -38065,10 +38065,10 @@
         <v>98</v>
       </c>
       <c r="N871" t="n">
-        <v>8806</v>
+        <v>8836.1575342466</v>
       </c>
       <c r="O871" t="n">
-        <v>862988</v>
+        <v>865943.4383561668</v>
       </c>
       <c r="P871" t="n">
         <v>14900</v>
@@ -38741,7 +38741,7 @@
         </is>
       </c>
       <c r="J886" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K886" t="n">
         <v>0</v>
@@ -38750,19 +38750,19 @@
         <v>0</v>
       </c>
       <c r="M886" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N886" t="n">
         <v>10755</v>
       </c>
       <c r="O886" t="n">
-        <v>2925360</v>
+        <v>2914605</v>
       </c>
       <c r="P886" t="n">
         <v>17900</v>
       </c>
       <c r="Q886" t="n">
-        <v>4868800</v>
+        <v>4850900</v>
       </c>
     </row>
     <row r="887">
@@ -39259,10 +39259,10 @@
         <v>18</v>
       </c>
       <c r="N897" t="n">
-        <v>3639.35</v>
+        <v>3647.235915493</v>
       </c>
       <c r="O897" t="n">
-        <v>65508.3</v>
+        <v>65650.246478874</v>
       </c>
       <c r="P897" t="n">
         <v>7500</v>
@@ -39351,10 +39351,10 @@
         <v>21</v>
       </c>
       <c r="N899" t="n">
-        <v>10713.21</v>
+        <v>10816.221634615</v>
       </c>
       <c r="O899" t="n">
-        <v>224977.41</v>
+        <v>227140.654326915</v>
       </c>
       <c r="P899" t="n">
         <v>20900</v>
@@ -39443,10 +39443,10 @@
         <v>48</v>
       </c>
       <c r="N901" t="n">
-        <v>12489</v>
+        <v>12664.079439252</v>
       </c>
       <c r="O901" t="n">
-        <v>599472</v>
+        <v>607875.8130840959</v>
       </c>
       <c r="P901" t="n">
         <v>20900</v>
@@ -39535,10 +39535,10 @@
         <v>29</v>
       </c>
       <c r="N903" t="n">
-        <v>21762</v>
+        <v>21937.5</v>
       </c>
       <c r="O903" t="n">
-        <v>631098</v>
+        <v>636187.5</v>
       </c>
       <c r="P903" t="n">
         <v>35900</v>
@@ -39569,7 +39569,7 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
@@ -39578,19 +39578,19 @@
         <v>0</v>
       </c>
       <c r="M904" t="n">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="N904" t="n">
         <v>3821</v>
       </c>
       <c r="O904" t="n">
-        <v>5956939</v>
+        <v>5945476</v>
       </c>
       <c r="P904" t="n">
         <v>5900</v>
       </c>
       <c r="Q904" t="n">
-        <v>9198100</v>
+        <v>9180400</v>
       </c>
     </row>
     <row r="905">
@@ -39952,10 +39952,10 @@
         <v>1326</v>
       </c>
       <c r="N912" t="n">
-        <v>1516.038818618</v>
+        <v>1516.0388180509</v>
       </c>
       <c r="O912" t="n">
-        <v>2010267.473487468</v>
+        <v>2010267.472735493</v>
       </c>
       <c r="P912" t="n">
         <v>2300</v>
@@ -39986,7 +39986,7 @@
         </is>
       </c>
       <c r="J913" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K913" t="n">
         <v>0</v>
@@ -39995,19 +39995,19 @@
         <v>0</v>
       </c>
       <c r="M913" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N913" t="n">
-        <v>4248.6119474836</v>
+        <v>4248.6122696629</v>
       </c>
       <c r="O913" t="n">
-        <v>412115.3589059092</v>
+        <v>407866.7778876384</v>
       </c>
       <c r="P913" t="n">
         <v>5900</v>
       </c>
       <c r="Q913" t="n">
-        <v>572300</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="914">
@@ -40088,10 +40088,10 @@
         <v>305</v>
       </c>
       <c r="N915" t="n">
-        <v>2458.5136155257</v>
+        <v>2458.5135821813</v>
       </c>
       <c r="O915" t="n">
-        <v>749846.6527353385</v>
+        <v>749846.6425652965</v>
       </c>
       <c r="P915" t="n">
         <v>3500</v>
@@ -40134,10 +40134,10 @@
         <v>60</v>
       </c>
       <c r="N916" t="n">
-        <v>1907.3946039604</v>
+        <v>1907.3945816073</v>
       </c>
       <c r="O916" t="n">
-        <v>114443.676237624</v>
+        <v>114443.674896438</v>
       </c>
       <c r="P916" t="n">
         <v>2500</v>
@@ -40180,10 +40180,10 @@
         <v>182</v>
       </c>
       <c r="N917" t="n">
-        <v>1771.0914991182</v>
+        <v>1771.0914183976</v>
       </c>
       <c r="O917" t="n">
-        <v>322338.6528395124</v>
+        <v>322338.6381483632</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
@@ -40214,7 +40214,7 @@
         </is>
       </c>
       <c r="J918" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K918" t="n">
         <v>0</v>
@@ -40223,19 +40223,19 @@
         <v>0</v>
       </c>
       <c r="M918" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N918" t="n">
-        <v>2079.3842820513</v>
+        <v>2079.384280218</v>
       </c>
       <c r="O918" t="n">
-        <v>779769.1057692375</v>
+        <v>777689.720801532</v>
       </c>
       <c r="P918" t="n">
         <v>2900</v>
       </c>
       <c r="Q918" t="n">
-        <v>1087500</v>
+        <v>1084600</v>
       </c>
     </row>
     <row r="919">
@@ -40272,10 +40272,10 @@
         <v>421</v>
       </c>
       <c r="N919" t="n">
-        <v>1803.0148044218</v>
+        <v>1803.0149016773</v>
       </c>
       <c r="O919" t="n">
-        <v>759069.2326615778</v>
+        <v>759069.2736061433</v>
       </c>
       <c r="P919" t="n">
         <v>2500</v>
@@ -40318,10 +40318,10 @@
         <v>101</v>
       </c>
       <c r="N920" t="n">
-        <v>3306.595494368</v>
+        <v>3306.5954716981</v>
       </c>
       <c r="O920" t="n">
-        <v>333966.144931168</v>
+        <v>333966.1426415081</v>
       </c>
       <c r="P920" t="n">
         <v>4900</v>
@@ -40364,10 +40364,10 @@
         <v>51</v>
       </c>
       <c r="N921" t="n">
-        <v>2122.1641906742</v>
+        <v>2122.1641716329</v>
       </c>
       <c r="O921" t="n">
-        <v>108230.3737243842</v>
+        <v>108230.3727532779</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
@@ -40398,7 +40398,7 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
@@ -40407,19 +40407,19 @@
         <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N922" t="n">
-        <v>2108.7893820527</v>
+        <v>2108.7895881384</v>
       </c>
       <c r="O922" t="n">
-        <v>345841.4586566428</v>
+        <v>339515.1236902824</v>
       </c>
       <c r="P922" t="n">
         <v>2900</v>
       </c>
       <c r="Q922" t="n">
-        <v>475600</v>
+        <v>466900</v>
       </c>
     </row>
     <row r="923">
@@ -40444,7 +40444,7 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
@@ -40453,19 +40453,19 @@
         <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N923" t="n">
-        <v>2056.0840312319</v>
+        <v>2056.0839842611</v>
       </c>
       <c r="O923" t="n">
-        <v>840938.3687738471</v>
+        <v>824489.6776887011</v>
       </c>
       <c r="P923" t="n">
         <v>2900</v>
       </c>
       <c r="Q923" t="n">
-        <v>1186100</v>
+        <v>1162900</v>
       </c>
     </row>
     <row r="924">
@@ -40502,10 +40502,10 @@
         <v>242</v>
       </c>
       <c r="N924" t="n">
-        <v>3224.5676430401</v>
+        <v>3224.5678063672</v>
       </c>
       <c r="O924" t="n">
-        <v>780345.3696157042</v>
+        <v>780345.4091408624</v>
       </c>
       <c r="P924" t="n">
         <v>4500</v>
@@ -40548,10 +40548,10 @@
         <v>336</v>
       </c>
       <c r="N925" t="n">
-        <v>1655.9314708603</v>
+        <v>1655.9314682295</v>
       </c>
       <c r="O925" t="n">
-        <v>556392.9742090608</v>
+        <v>556392.973325112</v>
       </c>
       <c r="P925" t="n">
         <v>2500</v>
@@ -40677,7 +40677,7 @@
         </is>
       </c>
       <c r="J928" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="K928" t="n">
         <v>0</v>
@@ -40686,19 +40686,19 @@
         <v>0</v>
       </c>
       <c r="M928" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="N928" t="n">
         <v>1662</v>
       </c>
       <c r="O928" t="n">
-        <v>417162</v>
+        <v>383922</v>
       </c>
       <c r="P928" t="n">
         <v>2900</v>
       </c>
       <c r="Q928" t="n">
-        <v>727900</v>
+        <v>669900</v>
       </c>
     </row>
     <row r="929">
@@ -40723,7 +40723,7 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>561</v>
+        <v>915</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
@@ -40732,19 +40732,19 @@
         <v>0</v>
       </c>
       <c r="M929" t="n">
-        <v>561</v>
+        <v>915</v>
       </c>
       <c r="N929" t="n">
         <v>2454</v>
       </c>
       <c r="O929" t="n">
-        <v>1376694</v>
+        <v>2245410</v>
       </c>
       <c r="P929" t="n">
         <v>4200</v>
       </c>
       <c r="Q929" t="n">
-        <v>2356200</v>
+        <v>3843000</v>
       </c>
     </row>
     <row r="930">
@@ -40769,7 +40769,7 @@
         </is>
       </c>
       <c r="J930" t="n">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="K930" t="n">
         <v>0</v>
@@ -40778,19 +40778,19 @@
         <v>0</v>
       </c>
       <c r="M930" t="n">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="N930" t="n">
-        <v>1592.2743101761</v>
+        <v>1592.2744517433</v>
       </c>
       <c r="O930" t="n">
-        <v>1001540.541100767</v>
+        <v>993579.2578878192</v>
       </c>
       <c r="P930" t="n">
         <v>2500</v>
       </c>
       <c r="Q930" t="n">
-        <v>1572500</v>
+        <v>1560000</v>
       </c>
     </row>
     <row r="931">
@@ -40912,10 +40912,10 @@
         <v>237</v>
       </c>
       <c r="N933" t="n">
-        <v>2311.9274887892</v>
+        <v>2311.9273755656</v>
       </c>
       <c r="O933" t="n">
-        <v>547926.8148430404</v>
+        <v>547926.7880090472</v>
       </c>
       <c r="P933" t="n">
         <v>3500</v>
@@ -40946,7 +40946,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -40955,19 +40955,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="N934" t="n">
-        <v>1906.1875409836</v>
+        <v>1906.1874003466</v>
       </c>
       <c r="O934" t="n">
-        <v>394580.8209836052</v>
+        <v>371706.543067587</v>
       </c>
       <c r="P934" t="n">
         <v>2900</v>
       </c>
       <c r="Q934" t="n">
-        <v>600300</v>
+        <v>565500</v>
       </c>
     </row>
     <row r="935">
@@ -40992,7 +40992,7 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
@@ -41001,19 +41001,19 @@
         <v>0</v>
       </c>
       <c r="M935" t="n">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N935" t="n">
-        <v>3033.7325612053</v>
+        <v>3033.7324288425</v>
       </c>
       <c r="O935" t="n">
-        <v>803939.1287194045</v>
+        <v>791804.1639278926</v>
       </c>
       <c r="P935" t="n">
         <v>4500</v>
       </c>
       <c r="Q935" t="n">
-        <v>1192500</v>
+        <v>1174500</v>
       </c>
     </row>
     <row r="936">
@@ -41050,10 +41050,10 @@
         <v>241</v>
       </c>
       <c r="N936" t="n">
-        <v>1668.6130481283</v>
+        <v>1668.6136503497</v>
       </c>
       <c r="O936" t="n">
-        <v>402135.7445989203</v>
+        <v>402135.8897342777</v>
       </c>
       <c r="P936" t="n">
         <v>2500</v>
@@ -41096,10 +41096,10 @@
         <v>195</v>
       </c>
       <c r="N937" t="n">
-        <v>2546.985477707</v>
+        <v>2546.9854340836</v>
       </c>
       <c r="O937" t="n">
-        <v>496662.168152865</v>
+        <v>496662.159646302</v>
       </c>
       <c r="P937" t="n">
         <v>3900</v>
@@ -41142,10 +41142,10 @@
         <v>1110</v>
       </c>
       <c r="N938" t="n">
-        <v>1259.2742532126</v>
+        <v>1259.2742585952</v>
       </c>
       <c r="O938" t="n">
-        <v>1397794.421065986</v>
+        <v>1397794.427040672</v>
       </c>
       <c r="P938" t="n">
         <v>1900</v>
@@ -41229,10 +41229,10 @@
         <v>20</v>
       </c>
       <c r="N940" t="n">
-        <v>2842.2738983051</v>
+        <v>2842.2738509317</v>
       </c>
       <c r="O940" t="n">
-        <v>56845.477966102</v>
+        <v>56845.477018634</v>
       </c>
       <c r="P940" t="n">
         <v>4900</v>
@@ -41321,10 +41321,10 @@
         <v>161</v>
       </c>
       <c r="N942" t="n">
-        <v>2556.7442751843</v>
+        <v>2556.7443391521</v>
       </c>
       <c r="O942" t="n">
-        <v>411635.8283046723</v>
+        <v>411635.8386034881</v>
       </c>
       <c r="P942" t="n">
         <v>3900</v>
@@ -41365,10 +41365,10 @@
         <v>2770</v>
       </c>
       <c r="N943" t="n">
-        <v>692.15200959024</v>
+        <v>692.15203442189</v>
       </c>
       <c r="O943" t="n">
-        <v>1917261.066564965</v>
+        <v>1917261.135348635</v>
       </c>
       <c r="P943" t="n">
         <v>1200</v>
@@ -41504,10 +41504,10 @@
         <v>75</v>
       </c>
       <c r="N946" t="n">
-        <v>1955.2371191444</v>
+        <v>1955.2371159315</v>
       </c>
       <c r="O946" t="n">
-        <v>146642.78393583</v>
+        <v>146642.7836948625</v>
       </c>
       <c r="P946" t="n">
         <v>3000</v>
@@ -42009,7 +42009,7 @@
         </is>
       </c>
       <c r="J957" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="K957" t="n">
         <v>0</v>
@@ -42018,19 +42018,19 @@
         <v>0</v>
       </c>
       <c r="M957" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N957" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O957" t="n">
-        <v>3721278.08</v>
+        <v>3685496.56</v>
       </c>
       <c r="P957" t="n">
         <v>14900</v>
       </c>
       <c r="Q957" t="n">
-        <v>6198400</v>
+        <v>6138800</v>
       </c>
     </row>
     <row r="958">
@@ -42067,10 +42067,10 @@
         <v>45</v>
       </c>
       <c r="N958" t="n">
-        <v>3026.5145673077</v>
+        <v>3026.5146116505</v>
       </c>
       <c r="O958" t="n">
-        <v>136193.1555288465</v>
+        <v>136193.1575242725</v>
       </c>
       <c r="P958" t="n">
         <v>7000</v>
@@ -42162,10 +42162,10 @@
         <v>321</v>
       </c>
       <c r="N960" t="n">
-        <v>1530.4499206349</v>
+        <v>1530.4499204455</v>
       </c>
       <c r="O960" t="n">
-        <v>491274.4245238029</v>
+        <v>491274.4244630055</v>
       </c>
       <c r="P960" t="n">
         <v>2600</v>
@@ -42700,7 +42700,7 @@
         </is>
       </c>
       <c r="J972" t="n">
-        <v>3574</v>
+        <v>3572</v>
       </c>
       <c r="K972" t="n">
         <v>0</v>
@@ -42709,19 +42709,19 @@
         <v>0</v>
       </c>
       <c r="M972" t="n">
-        <v>3574</v>
+        <v>3572</v>
       </c>
       <c r="N972" t="n">
-        <v>481.48791530945</v>
+        <v>481.48791484103</v>
       </c>
       <c r="O972" t="n">
-        <v>1720837.809315974</v>
+        <v>1719874.831812159</v>
       </c>
       <c r="P972" t="n">
         <v>650</v>
       </c>
       <c r="Q972" t="n">
-        <v>2323100</v>
+        <v>2321800</v>
       </c>
     </row>
     <row r="973">
@@ -42881,7 +42881,7 @@
         </is>
       </c>
       <c r="J976" t="n">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="K976" t="n">
         <v>0</v>
@@ -42890,19 +42890,19 @@
         <v>0</v>
       </c>
       <c r="M976" t="n">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="N976" t="n">
-        <v>711.33665006743</v>
+        <v>711.3366499515799</v>
       </c>
       <c r="O976" t="n">
-        <v>1110396.510755258</v>
+        <v>1109685.173924465</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>1404900</v>
+        <v>1404000</v>
       </c>
     </row>
     <row r="977">
@@ -43489,7 +43489,7 @@
         </is>
       </c>
       <c r="J990" t="n">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="K990" t="n">
         <v>0</v>
@@ -43498,19 +43498,19 @@
         <v>0</v>
       </c>
       <c r="M990" t="n">
-        <v>2285</v>
+        <v>2277</v>
       </c>
       <c r="N990" t="n">
-        <v>517.28728171896</v>
+        <v>517.28742027978</v>
       </c>
       <c r="O990" t="n">
-        <v>1182001.438727824</v>
+        <v>1177863.455977059</v>
       </c>
       <c r="P990" t="n">
         <v>900</v>
       </c>
       <c r="Q990" t="n">
-        <v>2056500</v>
+        <v>2049300</v>
       </c>
     </row>
     <row r="991">
@@ -43686,10 +43686,10 @@
         <v>1717</v>
       </c>
       <c r="N994" t="n">
-        <v>3110.8435374771</v>
+        <v>3110.8434146796</v>
       </c>
       <c r="O994" t="n">
-        <v>5341318.353848181</v>
+        <v>5341318.143004873</v>
       </c>
       <c r="P994" t="n">
         <v>4500</v>
@@ -43806,7 +43806,7 @@
         </is>
       </c>
       <c r="J997" t="n">
-        <v>15426</v>
+        <v>15402</v>
       </c>
       <c r="K997" t="n">
         <v>0</v>
@@ -43815,19 +43815,19 @@
         <v>0</v>
       </c>
       <c r="M997" t="n">
-        <v>15426</v>
+        <v>15402</v>
       </c>
       <c r="N997" t="n">
-        <v>703.79547499887</v>
+        <v>703.79546441605</v>
       </c>
       <c r="O997" t="n">
-        <v>10856748.99733257</v>
+        <v>10839857.742936</v>
       </c>
       <c r="P997" t="n">
         <v>900</v>
       </c>
       <c r="Q997" t="n">
-        <v>13883400</v>
+        <v>13861800</v>
       </c>
     </row>
     <row r="998">
@@ -43908,10 +43908,10 @@
         <v>45</v>
       </c>
       <c r="N999" t="n">
-        <v>3006.0208333333</v>
+        <v>3006.0208571429</v>
       </c>
       <c r="O999" t="n">
-        <v>135270.9374999985</v>
+        <v>135270.9385714305</v>
       </c>
       <c r="P999" t="n">
         <v>3900</v>
@@ -44166,7 +44166,7 @@
         </is>
       </c>
       <c r="J1005" t="n">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="K1005" t="n">
         <v>0</v>
@@ -44175,19 +44175,19 @@
         <v>0</v>
       </c>
       <c r="M1005" t="n">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N1005" t="n">
         <v>1937</v>
       </c>
       <c r="O1005" t="n">
-        <v>832910</v>
+        <v>825162</v>
       </c>
       <c r="P1005" t="n">
         <v>3300</v>
       </c>
       <c r="Q1005" t="n">
-        <v>1419000</v>
+        <v>1405800</v>
       </c>
     </row>
     <row r="1006">
@@ -44251,7 +44251,7 @@
         </is>
       </c>
       <c r="J1007" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K1007" t="n">
         <v>0</v>
@@ -44260,19 +44260,19 @@
         <v>0</v>
       </c>
       <c r="M1007" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N1007" t="n">
         <v>2525.02</v>
       </c>
       <c r="O1007" t="n">
-        <v>70700.56</v>
+        <v>65650.52</v>
       </c>
       <c r="P1007" t="n">
         <v>3000</v>
       </c>
       <c r="Q1007" t="n">
-        <v>84000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="1008">
@@ -44292,7 +44292,7 @@
         </is>
       </c>
       <c r="J1008" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K1008" t="n">
         <v>0</v>
@@ -44301,19 +44301,19 @@
         <v>0</v>
       </c>
       <c r="M1008" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N1008" t="n">
-        <v>2077.4944303797</v>
+        <v>2077.4944744318</v>
       </c>
       <c r="O1008" t="n">
-        <v>893322.605063271</v>
+        <v>891245.1295312422</v>
       </c>
       <c r="P1008" t="n">
         <v>2900</v>
       </c>
       <c r="Q1008" t="n">
-        <v>1247000</v>
+        <v>1244100</v>
       </c>
     </row>
     <row r="1009">
@@ -44561,10 +44561,10 @@
         <v>81</v>
       </c>
       <c r="N1014" t="n">
-        <v>1595.5194396439</v>
+        <v>1595.5193419662</v>
       </c>
       <c r="O1014" t="n">
-        <v>129237.0746111559</v>
+        <v>129237.0666992622</v>
       </c>
       <c r="P1014" t="n">
         <v>2500</v>
@@ -45113,7 +45113,7 @@
         </is>
       </c>
       <c r="J1026" t="n">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="K1026" t="n">
         <v>0</v>
@@ -45122,19 +45122,19 @@
         <v>0</v>
       </c>
       <c r="M1026" t="n">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="N1026" t="n">
         <v>1669.6</v>
       </c>
       <c r="O1026" t="n">
-        <v>1744732</v>
+        <v>1734714.4</v>
       </c>
       <c r="P1026" t="n">
         <v>2900</v>
       </c>
       <c r="Q1026" t="n">
-        <v>3030500</v>
+        <v>3013100</v>
       </c>
     </row>
     <row r="1027">
@@ -45598,10 +45598,10 @@
         <v>12</v>
       </c>
       <c r="N1036" t="n">
-        <v>875.69014545455</v>
+        <v>875.6901492537301</v>
       </c>
       <c r="O1036" t="n">
-        <v>10508.2817454546</v>
+        <v>10508.28179104476</v>
       </c>
       <c r="P1036" t="n">
         <v>4500</v>
@@ -45984,10 +45984,10 @@
         <v>20</v>
       </c>
       <c r="N1044" t="n">
-        <v>4337.31</v>
+        <v>4388.3371764706</v>
       </c>
       <c r="O1044" t="n">
-        <v>86746.20000000001</v>
+        <v>87766.74352941199</v>
       </c>
       <c r="P1044" t="n">
         <v>12900</v>
@@ -48143,10 +48143,10 @@
         <v>43</v>
       </c>
       <c r="N1090" t="n">
-        <v>7046.939830831</v>
+        <v>7046.9398307595</v>
       </c>
       <c r="O1090" t="n">
-        <v>303018.412725733</v>
+        <v>303018.4127226585</v>
       </c>
       <c r="P1090" t="n">
         <v>9900</v>
@@ -48795,7 +48795,7 @@
         </is>
       </c>
       <c r="J1104" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="K1104" t="n">
         <v>0</v>
@@ -48804,19 +48804,19 @@
         <v>0</v>
       </c>
       <c r="M1104" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="N1104" t="n">
-        <v>465.8709058296</v>
+        <v>465.87091402715</v>
       </c>
       <c r="O1104" t="n">
-        <v>103889.2120000008</v>
+        <v>99230.50468778294</v>
       </c>
       <c r="P1104" t="n">
         <v>2500</v>
       </c>
       <c r="Q1104" t="n">
-        <v>557500</v>
+        <v>532500</v>
       </c>
     </row>
     <row r="1105">
@@ -49562,7 +49562,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49571,19 +49571,19 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N1122" t="n">
         <v>5816</v>
       </c>
       <c r="O1122" t="n">
-        <v>476912</v>
+        <v>471096</v>
       </c>
       <c r="P1122" t="n">
         <v>5900</v>
       </c>
       <c r="Q1122" t="n">
-        <v>483800</v>
+        <v>477900</v>
       </c>
     </row>
     <row r="1123">
@@ -50034,7 +50034,7 @@
         </is>
       </c>
       <c r="J1133" t="n">
-        <v>1831</v>
+        <v>1813</v>
       </c>
       <c r="K1133" t="n">
         <v>0</v>
@@ -50043,19 +50043,19 @@
         <v>0</v>
       </c>
       <c r="M1133" t="n">
-        <v>1831</v>
+        <v>1813</v>
       </c>
       <c r="N1133" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1133" t="n">
-        <v>2154299.67</v>
+        <v>2133121.41</v>
       </c>
       <c r="P1133" t="n">
         <v>1900</v>
       </c>
       <c r="Q1133" t="n">
-        <v>3478900</v>
+        <v>3444700</v>
       </c>
     </row>
     <row r="1134">
@@ -50122,7 +50122,7 @@
         </is>
       </c>
       <c r="J1135" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K1135" t="n">
         <v>0</v>
@@ -50131,19 +50131,19 @@
         <v>0</v>
       </c>
       <c r="M1135" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N1135" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1135" t="n">
-        <v>553650.6</v>
+        <v>537741.1</v>
       </c>
       <c r="P1135" t="n">
         <v>5100</v>
       </c>
       <c r="Q1135" t="n">
-        <v>887400</v>
+        <v>861900</v>
       </c>
     </row>
     <row r="1136">
@@ -50175,10 +50175,10 @@
         <v>125</v>
       </c>
       <c r="N1136" t="n">
-        <v>1213.6820912548</v>
+        <v>1213.6821153846</v>
       </c>
       <c r="O1136" t="n">
-        <v>151710.26140685</v>
+        <v>151710.264423075</v>
       </c>
       <c r="P1136" t="n">
         <v>1500</v>
@@ -50424,7 +50424,7 @@
         </is>
       </c>
       <c r="J1142" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K1142" t="n">
         <v>0</v>
@@ -50433,19 +50433,19 @@
         <v>0</v>
       </c>
       <c r="M1142" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N1142" t="n">
-        <v>2830.2246883469</v>
+        <v>2830.224701087</v>
       </c>
       <c r="O1142" t="n">
-        <v>370759.4341734439</v>
+        <v>367929.21114131</v>
       </c>
       <c r="P1142" t="n">
         <v>2400</v>
       </c>
       <c r="Q1142" t="n">
-        <v>314400</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="1143">
@@ -50858,7 +50858,7 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -50867,19 +50867,19 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N1152" t="n">
         <v>12251</v>
       </c>
       <c r="O1152" t="n">
-        <v>539044</v>
+        <v>526793</v>
       </c>
       <c r="P1152" t="n">
         <v>13000</v>
       </c>
       <c r="Q1152" t="n">
-        <v>572000</v>
+        <v>559000</v>
       </c>
     </row>
     <row r="1153">
@@ -51089,10 +51089,10 @@
         <v>386</v>
       </c>
       <c r="N1157" t="n">
-        <v>22951.705024752</v>
+        <v>23008.657146402</v>
       </c>
       <c r="O1157" t="n">
-        <v>8859358.139554271</v>
+        <v>8881341.658511173</v>
       </c>
       <c r="P1157" t="n">
         <v>37900</v>
@@ -51317,10 +51317,10 @@
         <v>1</v>
       </c>
       <c r="N1162" t="n">
-        <v>1757.3205078125</v>
+        <v>1757.320513834</v>
       </c>
       <c r="O1162" t="n">
-        <v>1757.3205078125</v>
+        <v>1757.320513834</v>
       </c>
       <c r="P1162" t="n">
         <v>2000</v>
@@ -53598,10 +53598,10 @@
         <v>1</v>
       </c>
       <c r="N1212" t="n">
-        <v>970.63133333333</v>
+        <v>1039.9621428571</v>
       </c>
       <c r="O1212" t="n">
-        <v>970.63133333333</v>
+        <v>1039.9621428571</v>
       </c>
       <c r="P1212" t="n">
         <v>7200</v>
@@ -54068,10 +54068,10 @@
         <v>56</v>
       </c>
       <c r="N1222" t="n">
-        <v>3306.0098320158</v>
+        <v>3306.0098310139</v>
       </c>
       <c r="O1222" t="n">
-        <v>185136.5505928848</v>
+        <v>185136.5505367784</v>
       </c>
       <c r="P1222" t="n">
         <v>4200</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1325,10 +1325,10 @@
         <v>34</v>
       </c>
       <c r="N22" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O22" t="n">
-        <v>196671.0246902666</v>
+        <v>195804.6324778774</v>
       </c>
       <c r="P22" t="n">
         <v>16900</v>
@@ -2559,10 +2559,10 @@
         <v>294</v>
       </c>
       <c r="N52" t="n">
-        <v>4644.5877192982</v>
+        <v>4604.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1365508.789473671</v>
+        <v>1353634.8</v>
       </c>
       <c r="P52" t="n">
         <v>7500</v>
@@ -3203,10 +3203,10 @@
         <v>296</v>
       </c>
       <c r="N68" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O68" t="n">
-        <v>736168.9325790344</v>
+        <v>732512.4559068361</v>
       </c>
       <c r="P68" t="n">
         <v>4500</v>
@@ -5053,10 +5053,10 @@
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>20547.289545455</v>
+        <v>18835.016818182</v>
       </c>
       <c r="O111" t="n">
-        <v>20547.289545455</v>
+        <v>18835.016818182</v>
       </c>
       <c r="P111" t="n">
         <v>40500</v>
@@ -5176,10 +5176,10 @@
         <v>20</v>
       </c>
       <c r="N114" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O114" t="n">
-        <v>316694.32109376</v>
+        <v>314239.32578126</v>
       </c>
       <c r="P114" t="n">
         <v>28500</v>
@@ -5223,10 +5223,10 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="O115" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="P115" t="n">
         <v>18500</v>
@@ -8303,10 +8303,10 @@
         <v>115</v>
       </c>
       <c r="N188" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O188" t="n">
-        <v>859866.6533333295</v>
+        <v>850417.576111106</v>
       </c>
       <c r="P188" t="n">
         <v>17900</v>
@@ -9187,10 +9187,10 @@
         <v>101</v>
       </c>
       <c r="N209" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O209" t="n">
-        <v>260267.1671957626</v>
+        <v>258897.34</v>
       </c>
       <c r="P209" t="n">
         <v>4700</v>
@@ -9275,10 +9275,10 @@
         <v>62</v>
       </c>
       <c r="N211" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O211" t="n">
-        <v>725714.7429999999</v>
+        <v>713817.78</v>
       </c>
       <c r="P211" t="n">
         <v>17900</v>
@@ -11657,10 +11657,10 @@
         <v>310</v>
       </c>
       <c r="N267" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O267" t="n">
-        <v>4223625.714942601</v>
+        <v>4213938.5</v>
       </c>
       <c r="P267" t="n">
         <v>25500</v>
@@ -14999,10 +14999,10 @@
         <v>6</v>
       </c>
       <c r="N343" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O343" t="n">
-        <v>29389.9311377244</v>
+        <v>29346</v>
       </c>
       <c r="P343" t="n">
         <v>8200</v>
@@ -19057,10 +19057,10 @@
         <v>17</v>
       </c>
       <c r="N436" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O436" t="n">
-        <v>198188.511111106</v>
+        <v>195631.24</v>
       </c>
       <c r="P436" t="n">
         <v>25800</v>
@@ -22679,10 +22679,10 @@
         <v>11</v>
       </c>
       <c r="N520" t="n">
-        <v>2667.5690712743</v>
+        <v>2661.82</v>
       </c>
       <c r="O520" t="n">
-        <v>29343.2597840173</v>
+        <v>29280.02</v>
       </c>
       <c r="P520" t="n">
         <v>3200</v>
@@ -22761,10 +22761,10 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O522" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="P522" t="n">
         <v>6200</v>
@@ -26428,10 +26428,10 @@
         <v>2</v>
       </c>
       <c r="N609" t="n">
-        <v>13805.304244604</v>
+        <v>13513.64294964</v>
       </c>
       <c r="O609" t="n">
-        <v>27610.608489208</v>
+        <v>27027.28589928</v>
       </c>
       <c r="P609" t="n">
         <v>21900</v>
@@ -29048,10 +29048,10 @@
         <v>47</v>
       </c>
       <c r="N671" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O671" t="n">
-        <v>256321.8210788403</v>
+        <v>255262.64</v>
       </c>
       <c r="P671" t="n">
         <v>8900</v>
@@ -29309,10 +29309,10 @@
         <v>22</v>
       </c>
       <c r="N677" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O677" t="n">
-        <v>598993.388888884</v>
+        <v>590788</v>
       </c>
       <c r="P677" t="n">
         <v>43900</v>
@@ -30646,10 +30646,10 @@
         <v>25</v>
       </c>
       <c r="N709" t="n">
-        <v>13971.496466667</v>
+        <v>13878.97</v>
       </c>
       <c r="O709" t="n">
-        <v>349287.411666675</v>
+        <v>346974.25</v>
       </c>
       <c r="P709" t="n">
         <v>21900</v>
@@ -31342,10 +31342,10 @@
         <v>69</v>
       </c>
       <c r="N725" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O725" t="n">
-        <v>215114.1954642867</v>
+        <v>214858.4116428555</v>
       </c>
       <c r="P725" t="n">
         <v>5000</v>
@@ -31618,10 +31618,10 @@
         <v>19</v>
       </c>
       <c r="N731" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O731" t="n">
-        <v>172881.6195652183</v>
+        <v>168690.55</v>
       </c>
       <c r="P731" t="n">
         <v>14100</v>
@@ -31664,10 +31664,10 @@
         <v>113</v>
       </c>
       <c r="N732" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O732" t="n">
-        <v>282355.6803736224</v>
+        <v>282045.74</v>
       </c>
       <c r="P732" t="n">
         <v>4100</v>
@@ -31989,10 +31989,10 @@
         <v>43</v>
       </c>
       <c r="N739" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O739" t="n">
-        <v>170706.8697277229</v>
+        <v>170495.86</v>
       </c>
       <c r="P739" t="n">
         <v>6500</v>
@@ -32035,10 +32035,10 @@
         <v>40</v>
       </c>
       <c r="N740" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O740" t="n">
-        <v>233776.949308756</v>
+        <v>231642</v>
       </c>
       <c r="P740" t="n">
         <v>9300</v>
@@ -32861,10 +32861,10 @@
         <v>12</v>
       </c>
       <c r="N758" t="n">
-        <v>44124.685714286</v>
+        <v>42899</v>
       </c>
       <c r="O758" t="n">
-        <v>529496.2285714321</v>
+        <v>514788</v>
       </c>
       <c r="P758" t="n">
         <v>70900</v>
@@ -33321,10 +33321,10 @@
         <v>43</v>
       </c>
       <c r="N768" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O768" t="n">
-        <v>980223.481234361</v>
+        <v>977777</v>
       </c>
       <c r="P768" t="n">
         <v>36900</v>
@@ -33413,10 +33413,10 @@
         <v>177</v>
       </c>
       <c r="N770" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O770" t="n">
-        <v>2848292.005653714</v>
+        <v>2842266</v>
       </c>
       <c r="P770" t="n">
         <v>25900</v>
@@ -35353,10 +35353,10 @@
         <v>1</v>
       </c>
       <c r="N812" t="n">
-        <v>9704.4375</v>
+        <v>8508</v>
       </c>
       <c r="O812" t="n">
-        <v>9704.4375</v>
+        <v>8508</v>
       </c>
       <c r="P812" t="n">
         <v>14500</v>
@@ -35908,10 +35908,10 @@
         <v>87</v>
       </c>
       <c r="N824" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O824" t="n">
-        <v>1892112.040089126</v>
+        <v>1885812</v>
       </c>
       <c r="P824" t="n">
         <v>34900</v>
@@ -36460,10 +36460,10 @@
         <v>42</v>
       </c>
       <c r="N836" t="n">
-        <v>18473.630136986</v>
+        <v>17981</v>
       </c>
       <c r="O836" t="n">
-        <v>775892.4657534121</v>
+        <v>755202</v>
       </c>
       <c r="P836" t="n">
         <v>29900</v>
@@ -37697,10 +37697,10 @@
         <v>20</v>
       </c>
       <c r="N863" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O863" t="n">
-        <v>548448</v>
+        <v>543720</v>
       </c>
       <c r="P863" t="n">
         <v>43900</v>
@@ -37835,10 +37835,10 @@
         <v>1</v>
       </c>
       <c r="N866" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O866" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="P866" t="n">
         <v>6900</v>
@@ -37881,10 +37881,10 @@
         <v>190</v>
       </c>
       <c r="N867" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O867" t="n">
-        <v>2581237.40573154</v>
+        <v>2577350</v>
       </c>
       <c r="P867" t="n">
         <v>22500</v>
@@ -38065,10 +38065,10 @@
         <v>98</v>
       </c>
       <c r="N871" t="n">
-        <v>8836.1575342466</v>
+        <v>8806</v>
       </c>
       <c r="O871" t="n">
-        <v>865943.4383561668</v>
+        <v>862988</v>
       </c>
       <c r="P871" t="n">
         <v>14900</v>
@@ -39259,10 +39259,10 @@
         <v>18</v>
       </c>
       <c r="N897" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O897" t="n">
-        <v>65650.246478874</v>
+        <v>65508.3</v>
       </c>
       <c r="P897" t="n">
         <v>7500</v>
@@ -39351,10 +39351,10 @@
         <v>21</v>
       </c>
       <c r="N899" t="n">
-        <v>10816.221634615</v>
+        <v>10713.21</v>
       </c>
       <c r="O899" t="n">
-        <v>227140.654326915</v>
+        <v>224977.41</v>
       </c>
       <c r="P899" t="n">
         <v>20900</v>
@@ -39443,10 +39443,10 @@
         <v>48</v>
       </c>
       <c r="N901" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O901" t="n">
-        <v>607875.8130840959</v>
+        <v>599472</v>
       </c>
       <c r="P901" t="n">
         <v>20900</v>
@@ -39535,10 +39535,10 @@
         <v>29</v>
       </c>
       <c r="N903" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O903" t="n">
-        <v>636187.5</v>
+        <v>631098</v>
       </c>
       <c r="P903" t="n">
         <v>35900</v>
@@ -45984,10 +45984,10 @@
         <v>20</v>
       </c>
       <c r="N1044" t="n">
-        <v>4388.3371764706</v>
+        <v>4337.31</v>
       </c>
       <c r="O1044" t="n">
-        <v>87766.74352941199</v>
+        <v>86746.20000000001</v>
       </c>
       <c r="P1044" t="n">
         <v>12900</v>
@@ -51089,10 +51089,10 @@
         <v>386</v>
       </c>
       <c r="N1157" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O1157" t="n">
-        <v>8881341.658511173</v>
+        <v>8859358.134789102</v>
       </c>
       <c r="P1157" t="n">
         <v>37900</v>
@@ -53598,10 +53598,10 @@
         <v>1</v>
       </c>
       <c r="N1212" t="n">
-        <v>1039.9621428571</v>
+        <v>970.63142857143</v>
       </c>
       <c r="O1212" t="n">
-        <v>1039.9621428571</v>
+        <v>970.63142857143</v>
       </c>
       <c r="P1212" t="n">
         <v>7200</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -997,10 +997,10 @@
         <v>398</v>
       </c>
       <c r="N14" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O14" t="n">
-        <v>722766.5221070776</v>
+        <v>720898.9122625308</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1077,10 +1077,10 @@
         <v>155</v>
       </c>
       <c r="N16" t="n">
-        <v>2001.2446341463</v>
+        <v>1990.0436022514</v>
       </c>
       <c r="O16" t="n">
-        <v>310192.9182926765</v>
+        <v>308456.758348967</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
@@ -2794,10 +2794,10 @@
         <v>114</v>
       </c>
       <c r="N58" t="n">
-        <v>6300.2067296512</v>
+        <v>6272.8541860465</v>
       </c>
       <c r="O58" t="n">
-        <v>718223.5671802368</v>
+        <v>715105.377209301</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
@@ -7643,10 +7643,10 @@
         <v>312</v>
       </c>
       <c r="N173" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O173" t="n">
-        <v>1208164.924750431</v>
+        <v>1206089.04</v>
       </c>
       <c r="P173" t="n">
         <v>5500</v>
@@ -7866,10 +7866,10 @@
         <v>202</v>
       </c>
       <c r="N178" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O178" t="n">
-        <v>523171.8086827894</v>
+        <v>519679.34</v>
       </c>
       <c r="P178" t="n">
         <v>4700</v>
@@ -8096,10 +8096,10 @@
         <v>174</v>
       </c>
       <c r="N183" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O183" t="n">
-        <v>451955.2692993594</v>
+        <v>447207.84</v>
       </c>
       <c r="P183" t="n">
         <v>4700</v>
@@ -8261,10 +8261,10 @@
         <v>72</v>
       </c>
       <c r="N187" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O187" t="n">
-        <v>225078.9692422392</v>
+        <v>224243.28</v>
       </c>
       <c r="P187" t="n">
         <v>5500</v>
@@ -8573,10 +8573,10 @@
         <v>30</v>
       </c>
       <c r="N195" t="n">
-        <v>4411.4198473282</v>
+        <v>4378</v>
       </c>
       <c r="O195" t="n">
-        <v>132342.595419846</v>
+        <v>131340</v>
       </c>
       <c r="P195" t="n">
         <v>3900</v>
@@ -9106,10 +9106,10 @@
         <v>101</v>
       </c>
       <c r="N207" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O207" t="n">
-        <v>262367.8137265454</v>
+        <v>258897.34</v>
       </c>
       <c r="P207" t="n">
         <v>4700</v>
@@ -9762,10 +9762,10 @@
         <v>637</v>
       </c>
       <c r="N222" t="n">
-        <v>2837.5718128026</v>
+        <v>2833</v>
       </c>
       <c r="O222" t="n">
-        <v>1807533.244755256</v>
+        <v>1804621</v>
       </c>
       <c r="P222" t="n">
         <v>3500</v>
@@ -10013,10 +10013,10 @@
         <v>3</v>
       </c>
       <c r="N228" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O228" t="n">
-        <v>10468.8588953487</v>
+        <v>10368.39</v>
       </c>
       <c r="P228" t="n">
         <v>5700</v>
@@ -12142,10 +12142,10 @@
         <v>12</v>
       </c>
       <c r="N278" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O278" t="n">
-        <v>31060.2708661416</v>
+        <v>30987.0729448824</v>
       </c>
       <c r="P278" t="n">
         <v>4500</v>
@@ -12521,10 +12521,10 @@
         <v>51</v>
       </c>
       <c r="N287" t="n">
-        <v>6816.3581538462</v>
+        <v>6713.08</v>
       </c>
       <c r="O287" t="n">
-        <v>347634.2658461562</v>
+        <v>342367.08</v>
       </c>
       <c r="P287" t="n">
         <v>9900</v>
@@ -13194,10 +13194,10 @@
         <v>291</v>
       </c>
       <c r="N302" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O302" t="n">
-        <v>2193740.57525658</v>
+        <v>2184650.49</v>
       </c>
       <c r="P302" t="n">
         <v>13500</v>
@@ -13292,10 +13292,10 @@
         <v>329</v>
       </c>
       <c r="N304" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O304" t="n">
-        <v>2930701.862595431</v>
+        <v>2893884</v>
       </c>
       <c r="P304" t="n">
         <v>14900</v>
@@ -13512,10 +13512,10 @@
         <v>468</v>
       </c>
       <c r="N309" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O309" t="n">
-        <v>1779210.462485477</v>
+        <v>1776392.283299821</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13558,10 +13558,10 @@
         <v>326</v>
       </c>
       <c r="N310" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O310" t="n">
-        <v>1204666.74480408</v>
+        <v>1200984</v>
       </c>
       <c r="P310" t="n">
         <v>6200</v>
@@ -13996,10 +13996,10 @@
         <v>967</v>
       </c>
       <c r="N320" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O320" t="n">
-        <v>1173116.377131265</v>
+        <v>1163668.46</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
@@ -14487,10 +14487,10 @@
         <v>29</v>
       </c>
       <c r="N331" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O331" t="n">
-        <v>251950.84115884</v>
+        <v>251198</v>
       </c>
       <c r="P331" t="n">
         <v>14200</v>
@@ -14964,10 +14964,10 @@
         <v>30</v>
       </c>
       <c r="N342" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O342" t="n">
-        <v>246295.479452055</v>
+        <v>244620</v>
       </c>
       <c r="P342" t="n">
         <v>13500</v>
@@ -15008,10 +15008,10 @@
         <v>394</v>
       </c>
       <c r="N343" t="n">
-        <v>616.28176305926</v>
+        <v>616.01871898278</v>
       </c>
       <c r="O343" t="n">
-        <v>242815.0146453484</v>
+        <v>242711.3752792153</v>
       </c>
       <c r="P343" t="n">
         <v>800</v>
@@ -16043,10 +16043,10 @@
         <v>59</v>
       </c>
       <c r="N367" t="n">
-        <v>6493.1840890688</v>
+        <v>6441.03</v>
       </c>
       <c r="O367" t="n">
-        <v>383097.8612550592</v>
+        <v>380020.77</v>
       </c>
       <c r="P367" t="n">
         <v>10500</v>
@@ -16299,10 +16299,10 @@
         <v>91</v>
       </c>
       <c r="N373" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O373" t="n">
-        <v>333124.428</v>
+        <v>332692.36</v>
       </c>
       <c r="P373" t="n">
         <v>5500</v>
@@ -16946,10 +16946,10 @@
         <v>2571</v>
       </c>
       <c r="N388" t="n">
-        <v>1535.9702761427</v>
+        <v>1532.6290291403</v>
       </c>
       <c r="O388" t="n">
-        <v>3948979.579962882</v>
+        <v>3940389.233919711</v>
       </c>
       <c r="P388" t="n">
         <v>1200</v>
@@ -18090,10 +18090,10 @@
         <v>107</v>
       </c>
       <c r="N414" t="n">
-        <v>9795.0468</v>
+        <v>9678.9</v>
       </c>
       <c r="O414" t="n">
-        <v>1048070.0076</v>
+        <v>1035642.3</v>
       </c>
       <c r="P414" t="n">
         <v>15500</v>
@@ -19946,10 +19946,10 @@
         <v>50</v>
       </c>
       <c r="N456" t="n">
-        <v>2678.0253782895</v>
+        <v>2651.8557072368</v>
       </c>
       <c r="O456" t="n">
-        <v>133901.268914475</v>
+        <v>132592.78536184</v>
       </c>
       <c r="P456" t="n">
         <v>3800</v>
@@ -20309,10 +20309,10 @@
         <v>40</v>
       </c>
       <c r="N464" t="n">
-        <v>3319.8424657534</v>
+        <v>3253</v>
       </c>
       <c r="O464" t="n">
-        <v>132793.698630136</v>
+        <v>130120</v>
       </c>
       <c r="P464" t="n">
         <v>3900</v>
@@ -22644,10 +22644,10 @@
         <v>11</v>
       </c>
       <c r="N519" t="n">
-        <v>2696.7673085339</v>
+        <v>2661.82</v>
       </c>
       <c r="O519" t="n">
-        <v>29664.4403938729</v>
+        <v>29280.02</v>
       </c>
       <c r="P519" t="n">
         <v>3200</v>
@@ -22726,10 +22726,10 @@
         <v>1</v>
       </c>
       <c r="N521" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O521" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="P521" t="n">
         <v>6200</v>
@@ -22849,10 +22849,10 @@
         <v>220</v>
       </c>
       <c r="N524" t="n">
-        <v>1979.2819843342</v>
+        <v>1969</v>
       </c>
       <c r="O524" t="n">
-        <v>435442.036553524</v>
+        <v>433180</v>
       </c>
       <c r="P524" t="n">
         <v>1500</v>
@@ -22934,10 +22934,10 @@
         <v>252</v>
       </c>
       <c r="N526" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O526" t="n">
-        <v>2222375.373355587</v>
+        <v>2216208.96</v>
       </c>
       <c r="P526" t="n">
         <v>14500</v>
@@ -23267,10 +23267,10 @@
         <v>1</v>
       </c>
       <c r="N534" t="n">
-        <v>15626.086956522</v>
+        <v>14975</v>
       </c>
       <c r="O534" t="n">
-        <v>15626.086956522</v>
+        <v>14975</v>
       </c>
       <c r="P534" t="n">
         <v>19900</v>
@@ -23352,10 +23352,10 @@
         <v>54</v>
       </c>
       <c r="N536" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O536" t="n">
-        <v>138168.9445984902</v>
+        <v>135929.88</v>
       </c>
       <c r="P536" t="n">
         <v>4200</v>
@@ -23434,10 +23434,10 @@
         <v>248</v>
       </c>
       <c r="N538" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O538" t="n">
-        <v>504873.4760814704</v>
+        <v>503408.6620368592</v>
       </c>
       <c r="P538" t="n">
         <v>3600</v>
@@ -23516,10 +23516,10 @@
         <v>1</v>
       </c>
       <c r="N540" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O540" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="P540" t="n">
         <v>36500</v>
@@ -23967,10 +23967,10 @@
         <v>136</v>
       </c>
       <c r="N551" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O551" t="n">
-        <v>970600.7480190191</v>
+        <v>966008</v>
       </c>
       <c r="P551" t="n">
         <v>10700</v>
@@ -25097,10 +25097,10 @@
         <v>1</v>
       </c>
       <c r="N578" t="n">
-        <v>15639.519117647</v>
+        <v>14371.45</v>
       </c>
       <c r="O578" t="n">
-        <v>15639.519117647</v>
+        <v>14371.45</v>
       </c>
       <c r="P578" t="n">
         <v>23300</v>
@@ -26347,10 +26347,10 @@
         <v>89</v>
       </c>
       <c r="N607" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O607" t="n">
-        <v>1037102.750680632</v>
+        <v>1029021.429528759</v>
       </c>
       <c r="P607" t="n">
         <v>18500</v>
@@ -26439,10 +26439,10 @@
         <v>75</v>
       </c>
       <c r="N609" t="n">
-        <v>12155.852217573</v>
+        <v>12005.159832636</v>
       </c>
       <c r="O609" t="n">
-        <v>911688.9163179749</v>
+        <v>900386.9874477</v>
       </c>
       <c r="P609" t="n">
         <v>19500</v>
@@ -28076,10 +28076,10 @@
         <v>57</v>
       </c>
       <c r="N648" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O648" t="n">
-        <v>1300607.835805611</v>
+        <v>1295637.36</v>
       </c>
       <c r="P648" t="n">
         <v>36900</v>
@@ -33657,10 +33657,10 @@
         <v>24</v>
       </c>
       <c r="N775" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O775" t="n">
-        <v>280370.27027028</v>
+        <v>274800</v>
       </c>
       <c r="P775" t="n">
         <v>18300</v>
@@ -33749,10 +33749,10 @@
         <v>79</v>
       </c>
       <c r="N777" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O777" t="n">
-        <v>502884.375</v>
+        <v>497700</v>
       </c>
       <c r="P777" t="n">
         <v>10200</v>
@@ -33933,10 +33933,10 @@
         <v>47</v>
       </c>
       <c r="N781" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O781" t="n">
-        <v>346451.2377850167</v>
+        <v>339810</v>
       </c>
       <c r="P781" t="n">
         <v>11600</v>
@@ -33979,10 +33979,10 @@
         <v>61</v>
       </c>
       <c r="N782" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O782" t="n">
-        <v>322804.2402826834</v>
+        <v>317200</v>
       </c>
       <c r="P782" t="n">
         <v>8500</v>
@@ -34025,10 +34025,10 @@
         <v>66</v>
       </c>
       <c r="N783" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O783" t="n">
-        <v>93742.3728813528</v>
+        <v>92400</v>
       </c>
       <c r="P783" t="n">
         <v>2300</v>
@@ -34071,10 +34071,10 @@
         <v>72</v>
       </c>
       <c r="N784" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O784" t="n">
-        <v>438127.6595744664</v>
+        <v>432000</v>
       </c>
       <c r="P784" t="n">
         <v>10000</v>
@@ -34163,10 +34163,10 @@
         <v>107</v>
       </c>
       <c r="N786" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O786" t="n">
-        <v>133030.251798565</v>
+        <v>131610</v>
       </c>
       <c r="P786" t="n">
         <v>2000</v>
@@ -34306,10 +34306,10 @@
         <v>92</v>
       </c>
       <c r="N789" t="n">
-        <v>1441.9626168224</v>
+        <v>1390</v>
       </c>
       <c r="O789" t="n">
-        <v>132660.5607476608</v>
+        <v>127880</v>
       </c>
       <c r="P789" t="n">
         <v>2300</v>
@@ -34352,10 +34352,10 @@
         <v>30</v>
       </c>
       <c r="N790" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O790" t="n">
-        <v>58329.139072848</v>
+        <v>56100</v>
       </c>
       <c r="P790" t="n">
         <v>3000</v>
@@ -34398,10 +34398,10 @@
         <v>94</v>
       </c>
       <c r="N791" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O791" t="n">
-        <v>198432.2613533836</v>
+        <v>189866.84</v>
       </c>
       <c r="P791" t="n">
         <v>3300</v>
@@ -34444,10 +34444,10 @@
         <v>73</v>
       </c>
       <c r="N792" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O792" t="n">
-        <v>39368.09891808376</v>
+        <v>37960</v>
       </c>
       <c r="P792" t="n">
         <v>850</v>
@@ -34490,10 +34490,10 @@
         <v>56</v>
       </c>
       <c r="N793" t="n">
-        <v>2318.1974248927</v>
+        <v>2260</v>
       </c>
       <c r="O793" t="n">
-        <v>129819.0557939912</v>
+        <v>126560</v>
       </c>
       <c r="P793" t="n">
         <v>3800</v>
@@ -34582,10 +34582,10 @@
         <v>55</v>
       </c>
       <c r="N795" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O795" t="n">
-        <v>102985.8823529415</v>
+        <v>101200</v>
       </c>
       <c r="P795" t="n">
         <v>3000</v>
@@ -34674,10 +34674,10 @@
         <v>74</v>
       </c>
       <c r="N797" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O797" t="n">
-        <v>213006.4108352158</v>
+        <v>210160</v>
       </c>
       <c r="P797" t="n">
         <v>4600</v>
@@ -34950,10 +34950,10 @@
         <v>69</v>
       </c>
       <c r="N803" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O803" t="n">
-        <v>956615.107758654</v>
+        <v>944403</v>
       </c>
       <c r="P803" t="n">
         <v>21900</v>
@@ -36149,10 +36149,10 @@
         <v>83</v>
       </c>
       <c r="N829" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O829" t="n">
-        <v>750773.7594339643</v>
+        <v>747249</v>
       </c>
       <c r="P829" t="n">
         <v>14900</v>
@@ -37064,10 +37064,10 @@
         <v>12</v>
       </c>
       <c r="N849" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O849" t="n">
-        <v>50683.91752577279</v>
+        <v>50424</v>
       </c>
       <c r="P849" t="n">
         <v>7900</v>
@@ -37202,10 +37202,10 @@
         <v>1</v>
       </c>
       <c r="N852" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="O852" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="P852" t="n">
         <v>16900</v>
@@ -40099,10 +40099,10 @@
         <v>60</v>
       </c>
       <c r="N915" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O915" t="n">
-        <v>116765.440067622</v>
+        <v>114443.668300932</v>
       </c>
       <c r="P915" t="n">
         <v>2500</v>
@@ -40145,10 +40145,10 @@
         <v>182</v>
       </c>
       <c r="N916" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O916" t="n">
-        <v>327001.7630379682</v>
+        <v>322338.613670892</v>
       </c>
       <c r="P916" t="n">
         <v>2500</v>
@@ -40191,10 +40191,10 @@
         <v>374</v>
       </c>
       <c r="N917" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O917" t="n">
-        <v>783733.9365803134</v>
+        <v>777689.6993264145</v>
       </c>
       <c r="P917" t="n">
         <v>2900</v>
@@ -40237,10 +40237,10 @@
         <v>413</v>
       </c>
       <c r="N918" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O918" t="n">
-        <v>755157.7978205688</v>
+        <v>744645.1889264632</v>
       </c>
       <c r="P918" t="n">
         <v>2500</v>
@@ -40329,10 +40329,10 @@
         <v>50</v>
       </c>
       <c r="N920" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O920" t="n">
-        <v>106874.10180451</v>
+        <v>106108.20586466</v>
       </c>
       <c r="P920" t="n">
         <v>2900</v>
@@ -40467,10 +40467,10 @@
         <v>242</v>
       </c>
       <c r="N923" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O923" t="n">
-        <v>792792.2122995094</v>
+        <v>780345.4392733714</v>
       </c>
       <c r="P923" t="n">
         <v>4500</v>
@@ -40831,10 +40831,10 @@
         <v>6</v>
       </c>
       <c r="N931" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O931" t="n">
-        <v>32487.45975</v>
+        <v>32086.38</v>
       </c>
       <c r="P931" t="n">
         <v>9500</v>
@@ -41153,10 +41153,10 @@
         <v>31</v>
       </c>
       <c r="N938" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O938" t="n">
-        <v>94597.12</v>
+        <v>92380</v>
       </c>
       <c r="P938" t="n">
         <v>4800</v>
@@ -42404,10 +42404,10 @@
         <v>1150</v>
       </c>
       <c r="N965" t="n">
-        <v>577.72789151821</v>
+        <v>574.67194894975</v>
       </c>
       <c r="O965" t="n">
-        <v>664387.0752459414</v>
+        <v>660872.7412922125</v>
       </c>
       <c r="P965" t="n">
         <v>800</v>
@@ -42943,10 +42943,10 @@
         <v>84</v>
       </c>
       <c r="N977" t="n">
-        <v>2733.0090825688</v>
+        <v>2590.4171559633</v>
       </c>
       <c r="O977" t="n">
-        <v>229572.7629357792</v>
+        <v>217595.0411009172</v>
       </c>
       <c r="P977" t="n">
         <v>2800</v>
@@ -43739,10 +43739,10 @@
         <v>15396</v>
       </c>
       <c r="N995" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O995" t="n">
-        <v>10841523.79071732</v>
+        <v>10835634.82071747</v>
       </c>
       <c r="P995" t="n">
         <v>900</v>
@@ -43968,10 +43968,10 @@
         <v>34</v>
       </c>
       <c r="N1000" t="n">
-        <v>3442.356096181</v>
+        <v>3384.9037623762</v>
       </c>
       <c r="O1000" t="n">
-        <v>117040.107270154</v>
+        <v>115086.7279207908</v>
       </c>
       <c r="P1000" t="n">
         <v>4500</v>
@@ -44269,10 +44269,10 @@
         <v>28</v>
       </c>
       <c r="N1007" t="n">
-        <v>3674.9932848233</v>
+        <v>3629.7161122661</v>
       </c>
       <c r="O1007" t="n">
-        <v>102899.8119750524</v>
+        <v>101632.0511434508</v>
       </c>
       <c r="P1007" t="n">
         <v>4900</v>
@@ -46227,10 +46227,10 @@
         <v>25</v>
       </c>
       <c r="N1049" t="n">
-        <v>2602.7576774194</v>
+        <v>2505.760516129</v>
       </c>
       <c r="O1049" t="n">
-        <v>65068.941935485</v>
+        <v>62644.012903225</v>
       </c>
       <c r="P1049" t="n">
         <v>3000</v>
@@ -48859,10 +48859,10 @@
         <v>82</v>
       </c>
       <c r="N1105" t="n">
-        <v>2851.4129341317</v>
+        <v>2752.52</v>
       </c>
       <c r="O1105" t="n">
-        <v>233815.8605987994</v>
+        <v>225706.64</v>
       </c>
       <c r="P1105" t="n">
         <v>4500</v>
@@ -49539,10 +49539,10 @@
         <v>575</v>
       </c>
       <c r="N1121" t="n">
-        <v>827.85503734979</v>
+        <v>824.64111075024</v>
       </c>
       <c r="O1121" t="n">
-        <v>476016.6464761292</v>
+        <v>474168.6386813881</v>
       </c>
       <c r="P1121" t="n">
         <v>1000</v>
@@ -49668,10 +49668,10 @@
         <v>332</v>
       </c>
       <c r="N1124" t="n">
-        <v>2496.9418200728</v>
+        <v>2489.1752678107</v>
       </c>
       <c r="O1124" t="n">
-        <v>828984.6842641697</v>
+        <v>826406.1889131524</v>
       </c>
       <c r="P1124" t="n">
         <v>3000</v>
@@ -49712,10 +49712,10 @@
         <v>20</v>
       </c>
       <c r="N1125" t="n">
-        <v>2967.9876840215</v>
+        <v>2952.0877378815</v>
       </c>
       <c r="O1125" t="n">
-        <v>59359.75368043</v>
+        <v>59041.75475763</v>
       </c>
       <c r="P1125" t="n">
         <v>3800</v>
@@ -49756,10 +49756,10 @@
         <v>76</v>
       </c>
       <c r="N1126" t="n">
-        <v>3178.8430970149</v>
+        <v>3167.0258208955</v>
       </c>
       <c r="O1126" t="n">
-        <v>241592.0753731324</v>
+        <v>240693.962388058</v>
       </c>
       <c r="P1126" t="n">
         <v>4000</v>
@@ -49885,10 +49885,10 @@
         <v>70</v>
       </c>
       <c r="N1129" t="n">
-        <v>2998.8631649832</v>
+        <v>2988.7998653199</v>
       </c>
       <c r="O1129" t="n">
-        <v>209920.421548824</v>
+        <v>209215.990572393</v>
       </c>
       <c r="P1129" t="n">
         <v>3800</v>
@@ -50055,10 +50055,10 @@
         <v>169</v>
       </c>
       <c r="N1133" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O1133" t="n">
-        <v>539562.0993227166</v>
+        <v>537741.1</v>
       </c>
       <c r="P1133" t="n">
         <v>5100</v>
@@ -50181,10 +50181,10 @@
         <v>1231</v>
       </c>
       <c r="N1136" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O1136" t="n">
-        <v>2220158.81035807</v>
+        <v>2208768.5001389</v>
       </c>
       <c r="P1136" t="n">
         <v>1600</v>
@@ -50357,10 +50357,10 @@
         <v>130</v>
       </c>
       <c r="N1140" t="n">
-        <v>3081.4280769231</v>
+        <v>2830.2251183432</v>
       </c>
       <c r="O1140" t="n">
-        <v>400585.650000003</v>
+        <v>367929.265384616</v>
       </c>
       <c r="P1140" t="n">
         <v>2400</v>
@@ -50574,10 +50574,10 @@
         <v>1977</v>
       </c>
       <c r="N1145" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O1145" t="n">
-        <v>5022374.276044039</v>
+        <v>4988638.734674577</v>
       </c>
       <c r="P1145" t="n">
         <v>2800</v>
@@ -51187,10 +51187,10 @@
         <v>4</v>
       </c>
       <c r="N1159" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O1159" t="n">
-        <v>2828.48731927712</v>
+        <v>2822.11204819276</v>
       </c>
       <c r="P1159" t="n">
         <v>1500</v>
@@ -52236,10 +52236,10 @@
         <v>1</v>
       </c>
       <c r="N1182" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O1182" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="P1182" t="n">
         <v>1600</v>
@@ -53662,10 +53662,10 @@
         <v>29</v>
       </c>
       <c r="N1213" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O1213" t="n">
-        <v>6667.3226369614</v>
+        <v>6595.06306793275</v>
       </c>
       <c r="P1213" t="n">
         <v>1200</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -645,10 +645,10 @@
         <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>96741.407125</v>
+        <v>96741.407307692</v>
       </c>
       <c r="O6" t="n">
-        <v>1257638.292625</v>
+        <v>1257638.294999996</v>
       </c>
       <c r="P6" t="n">
         <v>188900</v>
@@ -739,10 +739,10 @@
         <v>13</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.65386363601</v>
+        <v>74676.651315789</v>
       </c>
       <c r="O8" t="n">
-        <v>970796.5002272681</v>
+        <v>970796.467105257</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -991,22 +991,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M14" t="n">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3039621792</v>
+        <v>1811.3040256176</v>
       </c>
       <c r="O14" t="n">
-        <v>720898.9769473216</v>
+        <v>686484.2257090705</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>1034800</v>
+        <v>985400</v>
       </c>
     </row>
     <row r="15">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.762560629</v>
+        <v>3866374.756101455</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -1601,10 +1601,10 @@
         <v>11</v>
       </c>
       <c r="N29" t="n">
-        <v>27815.961111111</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O29" t="n">
-        <v>305975.572222221</v>
+        <v>305975.572394371</v>
       </c>
       <c r="P29" t="n">
         <v>58600</v>
@@ -1681,22 +1681,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>13386</v>
       </c>
       <c r="O31" t="n">
-        <v>80316</v>
+        <v>66930</v>
       </c>
       <c r="P31" t="n">
         <v>23900</v>
       </c>
       <c r="Q31" t="n">
-        <v>143400</v>
+        <v>119500</v>
       </c>
     </row>
     <row r="32">
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8542228739</v>
+        <v>6272.8542666667</v>
       </c>
       <c r="O58" t="n">
-        <v>677468.2560703811</v>
+        <v>671195.4065333368</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>853200</v>
+        <v>845300</v>
       </c>
     </row>
     <row r="59">
@@ -3203,10 +3203,10 @@
         <v>296</v>
       </c>
       <c r="N68" t="n">
-        <v>2474.7042429285</v>
+        <v>2474.7042140468</v>
       </c>
       <c r="O68" t="n">
-        <v>732512.4559068361</v>
+        <v>732512.4473578528</v>
       </c>
       <c r="P68" t="n">
         <v>4500</v>
@@ -5053,10 +5053,10 @@
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>18835.017619048</v>
+        <v>18835.019473684</v>
       </c>
       <c r="O111" t="n">
-        <v>18835.017619048</v>
+        <v>18835.019473684</v>
       </c>
       <c r="P111" t="n">
         <v>40500</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N112" t="n">
-        <v>16486.410204082</v>
+        <v>16486.41</v>
       </c>
       <c r="O112" t="n">
-        <v>98918.461224492</v>
+        <v>82432.05</v>
       </c>
       <c r="P112" t="n">
         <v>30500</v>
       </c>
       <c r="Q112" t="n">
-        <v>183000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="113">
@@ -5176,10 +5176,10 @@
         <v>15</v>
       </c>
       <c r="N114" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O114" t="n">
-        <v>235679.493</v>
+        <v>235679.492771085</v>
       </c>
       <c r="P114" t="n">
         <v>28500</v>
@@ -5223,10 +5223,10 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>9392.0745333333</v>
+        <v>9392.0745945946</v>
       </c>
       <c r="O115" t="n">
-        <v>9392.0745333333</v>
+        <v>9392.0745945946</v>
       </c>
       <c r="P115" t="n">
         <v>18500</v>
@@ -5270,10 +5270,10 @@
         <v>6</v>
       </c>
       <c r="N116" t="n">
-        <v>30238.812307692</v>
+        <v>30238.812337662</v>
       </c>
       <c r="O116" t="n">
-        <v>181432.873846152</v>
+        <v>181432.874025972</v>
       </c>
       <c r="P116" t="n">
         <v>51100</v>
@@ -5813,22 +5813,22 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N130" t="n">
-        <v>8171.5889473684</v>
+        <v>8171.5888888889</v>
       </c>
       <c r="O130" t="n">
-        <v>73544.30052631561</v>
+        <v>65372.7111111112</v>
       </c>
       <c r="P130" t="n">
         <v>17200</v>
       </c>
       <c r="Q130" t="n">
-        <v>154800</v>
+        <v>137600</v>
       </c>
     </row>
     <row r="131">
@@ -6288,10 +6288,10 @@
         <v>4</v>
       </c>
       <c r="N141" t="n">
-        <v>80027.73</v>
+        <v>80027.72500000001</v>
       </c>
       <c r="O141" t="n">
-        <v>320110.92</v>
+        <v>320110.9</v>
       </c>
       <c r="P141" t="n">
         <v>129900</v>
@@ -6368,22 +6368,22 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>22147.31</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>22147.31</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
         <v>32900</v>
       </c>
       <c r="Q143" t="n">
-        <v>32900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -6557,10 +6557,10 @@
         <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="O147" t="n">
-        <v>200072.19914894</v>
+        <v>200072.19977273</v>
       </c>
       <c r="P147" t="n">
         <v>312000</v>
@@ -6599,10 +6599,10 @@
         <v>6</v>
       </c>
       <c r="N148" t="n">
-        <v>174389.78756757</v>
+        <v>174389.79096774</v>
       </c>
       <c r="O148" t="n">
-        <v>1046338.72540542</v>
+        <v>1046338.74580644</v>
       </c>
       <c r="P148" t="n">
         <v>368200</v>
@@ -7852,22 +7852,22 @@
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M178" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N178" t="n">
         <v>6187.41</v>
       </c>
       <c r="O178" t="n">
-        <v>222746.76</v>
+        <v>216559.35</v>
       </c>
       <c r="P178" t="n">
         <v>11500</v>
       </c>
       <c r="Q178" t="n">
-        <v>414000</v>
+        <v>402500</v>
       </c>
     </row>
     <row r="179">
@@ -8174,22 +8174,22 @@
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N185" t="n">
         <v>2570.16</v>
       </c>
       <c r="O185" t="n">
-        <v>447207.84</v>
+        <v>444637.68</v>
       </c>
       <c r="P185" t="n">
         <v>4700</v>
       </c>
       <c r="Q185" t="n">
-        <v>817800</v>
+        <v>813100</v>
       </c>
     </row>
     <row r="186">
@@ -9482,22 +9482,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N216" t="n">
-        <v>27450.51804878</v>
+        <v>27450.518024691</v>
       </c>
       <c r="O216" t="n">
-        <v>1152921.75804876</v>
+        <v>1125471.239012331</v>
       </c>
       <c r="P216" t="n">
         <v>40900</v>
       </c>
       <c r="Q216" t="n">
-        <v>1717800</v>
+        <v>1676900</v>
       </c>
     </row>
     <row r="217">
@@ -10479,10 +10479,10 @@
         <v>1387</v>
       </c>
       <c r="N239" t="n">
-        <v>1098.0529624405</v>
+        <v>1098.053336357</v>
       </c>
       <c r="O239" t="n">
-        <v>1522999.458904974</v>
+        <v>1522999.977527159</v>
       </c>
       <c r="P239" t="n">
         <v>1500</v>
@@ -11987,22 +11987,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N275" t="n">
         <v>1194.83</v>
       </c>
       <c r="O275" t="n">
-        <v>47793.2</v>
+        <v>46598.37</v>
       </c>
       <c r="P275" t="n">
         <v>2500</v>
       </c>
       <c r="Q275" t="n">
-        <v>100000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="276">
@@ -12226,10 +12226,10 @@
         <v>12</v>
       </c>
       <c r="N280" t="n">
-        <v>2582.2560663507</v>
+        <v>2582.256064019</v>
       </c>
       <c r="O280" t="n">
-        <v>30987.0727962084</v>
+        <v>30987.072768228</v>
       </c>
       <c r="P280" t="n">
         <v>4500</v>
@@ -12353,22 +12353,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M283" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N283" t="n">
-        <v>2033.5756109726</v>
+        <v>2033.574464752</v>
       </c>
       <c r="O283" t="n">
-        <v>357909.3075311776</v>
+        <v>353841.956866848</v>
       </c>
       <c r="P283" t="n">
         <v>4100</v>
       </c>
       <c r="Q283" t="n">
-        <v>721600</v>
+        <v>713400</v>
       </c>
     </row>
     <row r="284">
@@ -13145,10 +13145,10 @@
         <v>44</v>
       </c>
       <c r="N301" t="n">
-        <v>2694.8235120643</v>
+        <v>2694.8234975369</v>
       </c>
       <c r="O301" t="n">
-        <v>118572.2345308292</v>
+        <v>118572.2338916236</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -13180,22 +13180,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M302" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N302" t="n">
         <v>2742</v>
       </c>
       <c r="O302" t="n">
-        <v>208392</v>
+        <v>200166</v>
       </c>
       <c r="P302" t="n">
         <v>3500</v>
       </c>
       <c r="Q302" t="n">
-        <v>266000</v>
+        <v>255500</v>
       </c>
     </row>
     <row r="303">
@@ -14074,22 +14074,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M322" t="n">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="N322" t="n">
         <v>1203.38</v>
       </c>
       <c r="O322" t="n">
-        <v>1162465.08</v>
+        <v>1154041.42</v>
       </c>
       <c r="P322" t="n">
         <v>1900</v>
       </c>
       <c r="Q322" t="n">
-        <v>1835400</v>
+        <v>1822100</v>
       </c>
     </row>
     <row r="323">
@@ -14956,10 +14956,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3240.8500293255</v>
+        <v>3240.8500293686</v>
       </c>
       <c r="O342" t="n">
-        <v>3240.8500293255</v>
+        <v>3240.8500293686</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -15990,22 +15990,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N366" t="n">
-        <v>3041.6600124378</v>
+        <v>3041.6600124456</v>
       </c>
       <c r="O366" t="n">
-        <v>541415.4822139284</v>
+        <v>538373.8222028712</v>
       </c>
       <c r="P366" t="n">
         <v>5500</v>
       </c>
       <c r="Q366" t="n">
-        <v>979000</v>
+        <v>973500</v>
       </c>
     </row>
     <row r="367">
@@ -16249,22 +16249,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M372" t="n">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="N372" t="n">
-        <v>1592.5677332171</v>
+        <v>1592.567707231</v>
       </c>
       <c r="O372" t="n">
-        <v>1000132.536460339</v>
+        <v>985799.4107759889</v>
       </c>
       <c r="P372" t="n">
         <v>3900</v>
       </c>
       <c r="Q372" t="n">
-        <v>2449200</v>
+        <v>2414100</v>
       </c>
     </row>
     <row r="373">
@@ -16854,22 +16854,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M386" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="N386" t="n">
         <v>4648.6</v>
       </c>
       <c r="O386" t="n">
-        <v>1208636</v>
+        <v>1180744.4</v>
       </c>
       <c r="P386" t="n">
         <v>8900</v>
       </c>
       <c r="Q386" t="n">
-        <v>2314000</v>
+        <v>2260600</v>
       </c>
     </row>
     <row r="387">
@@ -17241,22 +17241,22 @@
         <v>0</v>
       </c>
       <c r="L395" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M395" t="n">
-        <v>3052</v>
+        <v>3002</v>
       </c>
       <c r="N395" t="n">
         <v>1387.55</v>
       </c>
       <c r="O395" t="n">
-        <v>4234802.6</v>
+        <v>4165425.1</v>
       </c>
       <c r="P395" t="n">
         <v>2300</v>
       </c>
       <c r="Q395" t="n">
-        <v>7019600</v>
+        <v>6904600</v>
       </c>
     </row>
     <row r="396">
@@ -18611,22 +18611,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M426" t="n">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="N426" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O426" t="n">
-        <v>882329.3534079202</v>
+        <v>872543.826789266</v>
       </c>
       <c r="P426" t="n">
         <v>2500</v>
       </c>
       <c r="Q426" t="n">
-        <v>1352500</v>
+        <v>1337500</v>
       </c>
     </row>
     <row r="427">
@@ -18709,10 +18709,10 @@
         <v>68</v>
       </c>
       <c r="N428" t="n">
-        <v>1690.603799682</v>
+        <v>1690.6035821697</v>
       </c>
       <c r="O428" t="n">
-        <v>114961.058378376</v>
+        <v>114961.0435875396</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
@@ -18749,22 +18749,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M429" t="n">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="N429" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O429" t="n">
-        <v>1844729.5940185</v>
+        <v>1832328.076255412</v>
       </c>
       <c r="P429" t="n">
         <v>2500</v>
       </c>
       <c r="Q429" t="n">
-        <v>2975000</v>
+        <v>2955000</v>
       </c>
     </row>
     <row r="430">
@@ -18847,10 +18847,10 @@
         <v>935</v>
       </c>
       <c r="N431" t="n">
-        <v>2403.5100306848</v>
+        <v>2403.5100778841</v>
       </c>
       <c r="O431" t="n">
-        <v>2247281.878690288</v>
+        <v>2247281.922821634</v>
       </c>
       <c r="P431" t="n">
         <v>3500</v>
@@ -18931,22 +18931,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M433" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N433" t="n">
-        <v>2521.5479047619</v>
+        <v>2521.5475490196</v>
       </c>
       <c r="O433" t="n">
-        <v>769072.1109523795</v>
+        <v>761507.3598039192</v>
       </c>
       <c r="P433" t="n">
         <v>3900</v>
       </c>
       <c r="Q433" t="n">
-        <v>1189500</v>
+        <v>1177800</v>
       </c>
     </row>
     <row r="434">
@@ -18978,10 +18978,10 @@
         <v>63</v>
       </c>
       <c r="N434" t="n">
-        <v>1232.8083690987</v>
+        <v>1232.8081659389</v>
       </c>
       <c r="O434" t="n">
-        <v>77666.92725321811</v>
+        <v>77666.9144541507</v>
       </c>
       <c r="P434" t="n">
         <v>2400</v>
@@ -20254,22 +20254,22 @@
         <v>0</v>
       </c>
       <c r="L463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N463" t="n">
         <v>36029</v>
       </c>
       <c r="O463" t="n">
-        <v>72058</v>
+        <v>36029</v>
       </c>
       <c r="P463" t="n">
         <v>10900</v>
       </c>
       <c r="Q463" t="n">
-        <v>21800</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="464">
@@ -22927,22 +22927,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M526" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N526" t="n">
         <v>1969</v>
       </c>
       <c r="O526" t="n">
-        <v>427273</v>
+        <v>419397</v>
       </c>
       <c r="P526" t="n">
         <v>1500</v>
       </c>
       <c r="Q526" t="n">
-        <v>325500</v>
+        <v>319500</v>
       </c>
     </row>
     <row r="527">
@@ -23263,22 +23263,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M534" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N534" t="n">
         <v>13152</v>
       </c>
       <c r="O534" t="n">
-        <v>1446720</v>
+        <v>1433568</v>
       </c>
       <c r="P534" t="n">
         <v>16900</v>
       </c>
       <c r="Q534" t="n">
-        <v>1859000</v>
+        <v>1842100</v>
       </c>
     </row>
     <row r="535">
@@ -23304,22 +23304,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M535" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N535" t="n">
         <v>6652</v>
       </c>
       <c r="O535" t="n">
-        <v>4443536</v>
+        <v>4436884</v>
       </c>
       <c r="P535" t="n">
         <v>5900</v>
       </c>
       <c r="Q535" t="n">
-        <v>3941200</v>
+        <v>3935300</v>
       </c>
     </row>
     <row r="536">
@@ -23430,22 +23430,22 @@
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M538" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N538" t="n">
         <v>2517.22</v>
       </c>
       <c r="O538" t="n">
-        <v>130895.44</v>
+        <v>115792.12</v>
       </c>
       <c r="P538" t="n">
         <v>4200</v>
       </c>
       <c r="Q538" t="n">
-        <v>218400</v>
+        <v>193200</v>
       </c>
     </row>
     <row r="539">
@@ -23512,22 +23512,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M540" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N540" t="n">
-        <v>2029.8736372454</v>
+        <v>2029.8736443149</v>
       </c>
       <c r="O540" t="n">
-        <v>503408.6620368592</v>
+        <v>501378.7901457803</v>
       </c>
       <c r="P540" t="n">
         <v>3600</v>
       </c>
       <c r="Q540" t="n">
-        <v>892800</v>
+        <v>889200</v>
       </c>
     </row>
     <row r="541">
@@ -24346,10 +24346,10 @@
         <v>617</v>
       </c>
       <c r="N560" t="n">
-        <v>880.32929682061</v>
+        <v>880.32931844615</v>
       </c>
       <c r="O560" t="n">
-        <v>543163.1761383164</v>
+        <v>543163.1894812746</v>
       </c>
       <c r="P560" t="n">
         <v>1200</v>
@@ -26159,22 +26159,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M603" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N603" t="n">
-        <v>4605.2146231618</v>
+        <v>4605.2146487985</v>
       </c>
       <c r="O603" t="n">
-        <v>967095.070863978</v>
+        <v>939463.788354894</v>
       </c>
       <c r="P603" t="n">
         <v>7600</v>
       </c>
       <c r="Q603" t="n">
-        <v>1596000</v>
+        <v>1550400</v>
       </c>
     </row>
     <row r="604">
@@ -29004,22 +29004,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M670" t="n">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="N670" t="n">
-        <v>1560.9988178914</v>
+        <v>1560.9988868445</v>
       </c>
       <c r="O670" t="n">
-        <v>772694.4148562429</v>
+        <v>753962.4623458935</v>
       </c>
       <c r="P670" t="n">
         <v>2900</v>
       </c>
       <c r="Q670" t="n">
-        <v>1435500</v>
+        <v>1400700</v>
       </c>
     </row>
     <row r="671">
@@ -31206,22 +31206,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M722" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="N722" t="n">
         <v>2634.61</v>
       </c>
       <c r="O722" t="n">
-        <v>237114.9</v>
+        <v>205499.58</v>
       </c>
       <c r="P722" t="n">
         <v>4200</v>
       </c>
       <c r="Q722" t="n">
-        <v>378000</v>
+        <v>327600</v>
       </c>
     </row>
     <row r="723">
@@ -31252,22 +31252,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M723" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="N723" t="n">
-        <v>3113.8900249066</v>
+        <v>3113.8900261438</v>
       </c>
       <c r="O723" t="n">
-        <v>174377.8413947696</v>
+        <v>56050.0204705884</v>
       </c>
       <c r="P723" t="n">
         <v>5000</v>
       </c>
       <c r="Q723" t="n">
-        <v>280000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="724">
@@ -31298,22 +31298,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M724" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N724" t="n">
         <v>5569.98</v>
       </c>
       <c r="O724" t="n">
-        <v>77979.72</v>
+        <v>0</v>
       </c>
       <c r="P724" t="n">
         <v>8900</v>
       </c>
       <c r="Q724" t="n">
-        <v>124600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
@@ -31344,22 +31344,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M725" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="N725" t="n">
         <v>4690.64</v>
       </c>
       <c r="O725" t="n">
-        <v>262675.84</v>
+        <v>46906.4</v>
       </c>
       <c r="P725" t="n">
         <v>7500</v>
       </c>
       <c r="Q725" t="n">
-        <v>420000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="726">
@@ -31390,22 +31390,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M726" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="N726" t="n">
         <v>5410.72</v>
       </c>
       <c r="O726" t="n">
-        <v>465321.92</v>
+        <v>189375.2</v>
       </c>
       <c r="P726" t="n">
         <v>8700</v>
       </c>
       <c r="Q726" t="n">
-        <v>748200</v>
+        <v>304500</v>
       </c>
     </row>
     <row r="727">
@@ -31436,22 +31436,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M727" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N727" t="n">
         <v>10911.29</v>
       </c>
       <c r="O727" t="n">
-        <v>403717.73</v>
+        <v>294604.83</v>
       </c>
       <c r="P727" t="n">
         <v>17400</v>
       </c>
       <c r="Q727" t="n">
-        <v>643800</v>
+        <v>469800</v>
       </c>
     </row>
     <row r="728">
@@ -31528,22 +31528,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M729" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N729" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O729" t="n">
-        <v>44392.25</v>
+        <v>35513.8</v>
       </c>
       <c r="P729" t="n">
         <v>14100</v>
       </c>
       <c r="Q729" t="n">
-        <v>70500</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="730">
@@ -31620,22 +31620,22 @@
         <v>0</v>
       </c>
       <c r="L731" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M731" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N731" t="n">
         <v>3254.49</v>
       </c>
       <c r="O731" t="n">
-        <v>302667.57</v>
+        <v>283140.63</v>
       </c>
       <c r="P731" t="n">
         <v>5200</v>
       </c>
       <c r="Q731" t="n">
-        <v>483600</v>
+        <v>452400</v>
       </c>
     </row>
     <row r="732">
@@ -31672,10 +31672,10 @@
         <v>7</v>
       </c>
       <c r="N732" t="n">
-        <v>5218.1704867257</v>
+        <v>5218.170490524</v>
       </c>
       <c r="O732" t="n">
-        <v>36527.1934070799</v>
+        <v>36527.193433668</v>
       </c>
       <c r="P732" t="n">
         <v>8500</v>
@@ -31712,22 +31712,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M733" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N733" t="n">
-        <v>1595.0094973545</v>
+        <v>1595.0094864865</v>
       </c>
       <c r="O733" t="n">
-        <v>33495.1994444445</v>
+        <v>7975.0474324325</v>
       </c>
       <c r="P733" t="n">
         <v>2600</v>
       </c>
       <c r="Q733" t="n">
-        <v>54600</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="734">
@@ -31758,22 +31758,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M734" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N734" t="n">
-        <v>3610.6500236967</v>
+        <v>3610.6500238379</v>
       </c>
       <c r="O734" t="n">
-        <v>101098.2006635076</v>
+        <v>90266.25059594749</v>
       </c>
       <c r="P734" t="n">
         <v>5800</v>
       </c>
       <c r="Q734" t="n">
-        <v>162400</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="735">
@@ -31853,22 +31853,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M736" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N736" t="n">
         <v>4227.77</v>
       </c>
       <c r="O736" t="n">
-        <v>12683.31</v>
+        <v>8455.540000000001</v>
       </c>
       <c r="P736" t="n">
         <v>6900</v>
       </c>
       <c r="Q736" t="n">
-        <v>20700</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="737">
@@ -31899,22 +31899,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M737" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N737" t="n">
         <v>3965.02</v>
       </c>
       <c r="O737" t="n">
-        <v>126880.64</v>
+        <v>95160.48</v>
       </c>
       <c r="P737" t="n">
         <v>6500</v>
       </c>
       <c r="Q737" t="n">
-        <v>208000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="738">
@@ -31945,22 +31945,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M738" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N738" t="n">
         <v>5791.05</v>
       </c>
       <c r="O738" t="n">
-        <v>208477.8</v>
+        <v>173731.5</v>
       </c>
       <c r="P738" t="n">
         <v>9300</v>
       </c>
       <c r="Q738" t="n">
-        <v>334800</v>
+        <v>279000</v>
       </c>
     </row>
     <row r="739">
@@ -31991,22 +31991,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M739" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="N739" t="n">
         <v>10977.27</v>
       </c>
       <c r="O739" t="n">
-        <v>801340.7100000001</v>
+        <v>691568.01</v>
       </c>
       <c r="P739" t="n">
         <v>17900</v>
       </c>
       <c r="Q739" t="n">
-        <v>1306700</v>
+        <v>1127700</v>
       </c>
     </row>
     <row r="740">
@@ -32083,22 +32083,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M741" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N741" t="n">
-        <v>1664.3609992194</v>
+        <v>1664.360841938</v>
       </c>
       <c r="O741" t="n">
-        <v>256311.5938797876</v>
+        <v>252982.847974576</v>
       </c>
       <c r="P741" t="n">
         <v>2900</v>
       </c>
       <c r="Q741" t="n">
-        <v>446600</v>
+        <v>440800</v>
       </c>
     </row>
     <row r="742">
@@ -32129,22 +32129,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M742" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N742" t="n">
         <v>15502</v>
       </c>
       <c r="O742" t="n">
-        <v>201526</v>
+        <v>186024</v>
       </c>
       <c r="P742" t="n">
         <v>25900</v>
       </c>
       <c r="Q742" t="n">
-        <v>336700</v>
+        <v>310800</v>
       </c>
     </row>
     <row r="743">
@@ -32915,10 +32915,10 @@
         <v>19</v>
       </c>
       <c r="N759" t="n">
-        <v>23521.624852941</v>
+        <v>23521.624776119</v>
       </c>
       <c r="O759" t="n">
-        <v>446910.872205879</v>
+        <v>446910.870746261</v>
       </c>
       <c r="P759" t="n">
         <v>39000</v>
@@ -33053,10 +33053,10 @@
         <v>1241</v>
       </c>
       <c r="N762" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O762" t="n">
-        <v>2207084.397126528</v>
+        <v>2207084.401193657</v>
       </c>
       <c r="P762" t="n">
         <v>4900</v>
@@ -35539,22 +35539,22 @@
         <v>0</v>
       </c>
       <c r="L816" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M816" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N816" t="n">
-        <v>2252.2963076923</v>
+        <v>2252.2963603819</v>
       </c>
       <c r="O816" t="n">
-        <v>340096.7424615373</v>
+        <v>337844.454057285</v>
       </c>
       <c r="P816" t="n">
         <v>3900</v>
       </c>
       <c r="Q816" t="n">
-        <v>588900</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="817">
@@ -36002,22 +36002,22 @@
         <v>0</v>
       </c>
       <c r="L826" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M826" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N826" t="n">
         <v>3519</v>
       </c>
       <c r="O826" t="n">
-        <v>267444</v>
+        <v>256887</v>
       </c>
       <c r="P826" t="n">
         <v>5900</v>
       </c>
       <c r="Q826" t="n">
-        <v>448400</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="827">
@@ -36186,22 +36186,22 @@
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M830" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N830" t="n">
         <v>4544</v>
       </c>
       <c r="O830" t="n">
-        <v>1304128</v>
+        <v>1299584</v>
       </c>
       <c r="P830" t="n">
         <v>7900</v>
       </c>
       <c r="Q830" t="n">
-        <v>2267300</v>
+        <v>2259400</v>
       </c>
     </row>
     <row r="831">
@@ -36330,10 +36330,10 @@
         <v>43</v>
       </c>
       <c r="N833" t="n">
-        <v>16285.911097561</v>
+        <v>16285.911111111</v>
       </c>
       <c r="O833" t="n">
-        <v>700294.177195123</v>
+        <v>700294.177777773</v>
       </c>
       <c r="P833" t="n">
         <v>29900</v>
@@ -36514,10 +36514,10 @@
         <v>15</v>
       </c>
       <c r="N837" t="n">
-        <v>4907.8219155354</v>
+        <v>4907.8219300912</v>
       </c>
       <c r="O837" t="n">
-        <v>73617.328733031</v>
+        <v>73617.32895136799</v>
       </c>
       <c r="P837" t="n">
         <v>8200</v>
@@ -36790,10 +36790,10 @@
         <v>23</v>
       </c>
       <c r="N843" t="n">
-        <v>3903.7358951965</v>
+        <v>3903.7359183673</v>
       </c>
       <c r="O843" t="n">
-        <v>89785.92558951951</v>
+        <v>89785.9261224479</v>
       </c>
       <c r="P843" t="n">
         <v>7500</v>
@@ -37193,22 +37193,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M852" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N852" t="n">
         <v>2629</v>
       </c>
       <c r="O852" t="n">
-        <v>675653</v>
+        <v>673024</v>
       </c>
       <c r="P852" t="n">
         <v>4500</v>
       </c>
       <c r="Q852" t="n">
-        <v>1156500</v>
+        <v>1152000</v>
       </c>
     </row>
     <row r="853">
@@ -38476,22 +38476,22 @@
         <v>0</v>
       </c>
       <c r="L880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M880" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N880" t="n">
         <v>59834</v>
       </c>
       <c r="O880" t="n">
-        <v>3949044</v>
+        <v>3889210</v>
       </c>
       <c r="P880" t="n">
         <v>7900</v>
       </c>
       <c r="Q880" t="n">
-        <v>521400</v>
+        <v>513500</v>
       </c>
     </row>
     <row r="881">
@@ -39215,22 +39215,22 @@
         <v>0</v>
       </c>
       <c r="L896" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M896" t="n">
-        <v>1739</v>
+        <v>1731</v>
       </c>
       <c r="N896" t="n">
         <v>1326</v>
       </c>
       <c r="O896" t="n">
-        <v>2305914</v>
+        <v>2295306</v>
       </c>
       <c r="P896" t="n">
         <v>2500</v>
       </c>
       <c r="Q896" t="n">
-        <v>4347500</v>
+        <v>4327500</v>
       </c>
     </row>
     <row r="897">
@@ -39537,22 +39537,22 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M903" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N903" t="n">
         <v>15472</v>
       </c>
       <c r="O903" t="n">
-        <v>263024</v>
+        <v>247552</v>
       </c>
       <c r="P903" t="n">
         <v>25900</v>
       </c>
       <c r="Q903" t="n">
-        <v>440300</v>
+        <v>414400</v>
       </c>
     </row>
     <row r="904">
@@ -39868,10 +39868,10 @@
         <v>1326</v>
       </c>
       <c r="N910" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O910" t="n">
-        <v>2010267.4669963</v>
+        <v>2010267.466237961</v>
       </c>
       <c r="P910" t="n">
         <v>2300</v>
@@ -39908,22 +39908,22 @@
         <v>0</v>
       </c>
       <c r="L911" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M911" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N911" t="n">
-        <v>4248.6172239748</v>
+        <v>4248.6195698925</v>
       </c>
       <c r="O911" t="n">
-        <v>152950.2200630928</v>
+        <v>0</v>
       </c>
       <c r="P911" t="n">
         <v>5900</v>
       </c>
       <c r="Q911" t="n">
-        <v>212400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="912">
@@ -40096,10 +40096,10 @@
         <v>182</v>
       </c>
       <c r="N915" t="n">
-        <v>1771.091283906</v>
+        <v>1771.0912628399</v>
       </c>
       <c r="O915" t="n">
-        <v>322338.613670892</v>
+        <v>322338.6098368618</v>
       </c>
       <c r="P915" t="n">
         <v>2500</v>
@@ -40142,10 +40142,10 @@
         <v>374</v>
       </c>
       <c r="N916" t="n">
-        <v>2079.3842227979</v>
+        <v>2079.3842209265</v>
       </c>
       <c r="O916" t="n">
-        <v>777689.6993264145</v>
+        <v>777689.6986265109</v>
       </c>
       <c r="P916" t="n">
         <v>2900</v>
@@ -40188,10 +40188,10 @@
         <v>413</v>
       </c>
       <c r="N917" t="n">
-        <v>1803.0149867608</v>
+        <v>1803.0149882284</v>
       </c>
       <c r="O917" t="n">
-        <v>744645.1895322104</v>
+        <v>744645.1901383292</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
@@ -40234,10 +40234,10 @@
         <v>99</v>
       </c>
       <c r="N918" t="n">
-        <v>3306.5954602774</v>
+        <v>3306.5954545455</v>
       </c>
       <c r="O918" t="n">
-        <v>327352.9505674626</v>
+        <v>327352.9500000045</v>
       </c>
       <c r="P918" t="n">
         <v>4900</v>
@@ -40280,10 +40280,10 @@
         <v>50</v>
       </c>
       <c r="N919" t="n">
-        <v>2122.1641172932</v>
+        <v>2122.1641155235</v>
       </c>
       <c r="O919" t="n">
-        <v>106108.20586466</v>
+        <v>106108.205776175</v>
       </c>
       <c r="P919" t="n">
         <v>2900</v>
@@ -40326,10 +40326,10 @@
         <v>133</v>
       </c>
       <c r="N920" t="n">
-        <v>2108.7897651007</v>
+        <v>2108.7897869955</v>
       </c>
       <c r="O920" t="n">
-        <v>280469.0387583931</v>
+        <v>280469.0416704015</v>
       </c>
       <c r="P920" t="n">
         <v>2900</v>
@@ -40372,10 +40372,10 @@
         <v>393</v>
       </c>
       <c r="N921" t="n">
-        <v>2056.0838952972</v>
+        <v>2056.0838880663</v>
       </c>
       <c r="O921" t="n">
-        <v>808040.9708517996</v>
+        <v>808040.9680100559</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
@@ -40464,10 +40464,10 @@
         <v>311</v>
       </c>
       <c r="N923" t="n">
-        <v>1655.93135625</v>
+        <v>1655.931342723</v>
       </c>
       <c r="O923" t="n">
-        <v>514994.6517937499</v>
+        <v>514994.647586853</v>
       </c>
       <c r="P923" t="n">
         <v>2500</v>
@@ -40691,22 +40691,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M928" t="n">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="N928" t="n">
-        <v>1592.2746762208</v>
+        <v>1592.2747647377</v>
       </c>
       <c r="O928" t="n">
-        <v>964918.4537898048</v>
+        <v>955364.85884262</v>
       </c>
       <c r="P928" t="n">
         <v>2500</v>
       </c>
       <c r="Q928" t="n">
-        <v>1515000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="929">
@@ -40828,10 +40828,10 @@
         <v>233</v>
       </c>
       <c r="N931" t="n">
-        <v>2311.9269828927</v>
+        <v>2311.9267563291</v>
       </c>
       <c r="O931" t="n">
-        <v>538678.9870139991</v>
+        <v>538678.9342246803</v>
       </c>
       <c r="P931" t="n">
         <v>3500</v>
@@ -40874,10 +40874,10 @@
         <v>179</v>
       </c>
       <c r="N932" t="n">
-        <v>1906.1869325153</v>
+        <v>1906.1867602592</v>
       </c>
       <c r="O932" t="n">
-        <v>341207.4609202387</v>
+        <v>341207.4300863968</v>
       </c>
       <c r="P932" t="n">
         <v>2900</v>
@@ -40920,10 +40920,10 @@
         <v>258</v>
       </c>
       <c r="N933" t="n">
-        <v>3033.7319844358</v>
+        <v>3033.7318786693</v>
       </c>
       <c r="O933" t="n">
-        <v>782702.8519844364</v>
+        <v>782702.8246966794</v>
       </c>
       <c r="P933" t="n">
         <v>4500</v>
@@ -40966,10 +40966,10 @@
         <v>241</v>
       </c>
       <c r="N934" t="n">
-        <v>1668.6155910543</v>
+        <v>1668.6157419355</v>
       </c>
       <c r="O934" t="n">
-        <v>402136.3574440863</v>
+        <v>402136.3938064555</v>
       </c>
       <c r="P934" t="n">
         <v>2500</v>
@@ -41006,22 +41006,22 @@
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M935" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N935" t="n">
-        <v>2546.9852428811</v>
+        <v>2546.9851864407</v>
       </c>
       <c r="O935" t="n">
-        <v>466098.2994472413</v>
+        <v>463551.3039322074</v>
       </c>
       <c r="P935" t="n">
         <v>3900</v>
       </c>
       <c r="Q935" t="n">
-        <v>713700</v>
+        <v>709800</v>
       </c>
     </row>
     <row r="936">
@@ -41058,10 +41058,10 @@
         <v>1110</v>
       </c>
       <c r="N936" t="n">
-        <v>1259.2744102228</v>
+        <v>1259.2744140796</v>
       </c>
       <c r="O936" t="n">
-        <v>1397794.595347308</v>
+        <v>1397794.599628356</v>
       </c>
       <c r="P936" t="n">
         <v>1900</v>
@@ -41237,10 +41237,10 @@
         <v>158</v>
       </c>
       <c r="N940" t="n">
-        <v>2556.7444501279</v>
+        <v>2556.7446648794</v>
       </c>
       <c r="O940" t="n">
-        <v>403965.6231202082</v>
+        <v>403965.6570509452</v>
       </c>
       <c r="P940" t="n">
         <v>3900</v>
@@ -41281,10 +41281,10 @@
         <v>2746</v>
       </c>
       <c r="N941" t="n">
-        <v>692.15204525288</v>
+        <v>692.15205253785</v>
       </c>
       <c r="O941" t="n">
-        <v>1900649.516264409</v>
+        <v>1900649.536268936</v>
       </c>
       <c r="P941" t="n">
         <v>1200</v>
@@ -41466,10 +41466,10 @@
         <v>570</v>
       </c>
       <c r="N945" t="n">
-        <v>1185.3195720165</v>
+        <v>1185.3195716639</v>
       </c>
       <c r="O945" t="n">
-        <v>675632.156049405</v>
+        <v>675632.155848423</v>
       </c>
       <c r="P945" t="n">
         <v>1900</v>
@@ -41648,22 +41648,22 @@
         <v>0</v>
       </c>
       <c r="L949" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M949" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N949" t="n">
         <v>2392.8</v>
       </c>
       <c r="O949" t="n">
-        <v>287136</v>
+        <v>284743.2</v>
       </c>
       <c r="P949" t="n">
         <v>7900</v>
       </c>
       <c r="Q949" t="n">
-        <v>948000</v>
+        <v>940100</v>
       </c>
     </row>
     <row r="950">
@@ -41931,22 +41931,22 @@
         <v>0</v>
       </c>
       <c r="L955" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M955" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N955" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O955" t="n">
-        <v>3569206.62</v>
+        <v>3551315.86</v>
       </c>
       <c r="P955" t="n">
         <v>14900</v>
       </c>
       <c r="Q955" t="n">
-        <v>5945100</v>
+        <v>5915300</v>
       </c>
     </row>
     <row r="956">
@@ -41983,10 +41983,10 @@
         <v>45</v>
       </c>
       <c r="N956" t="n">
-        <v>3026.514679803</v>
+        <v>3026.5146568627</v>
       </c>
       <c r="O956" t="n">
-        <v>136193.160591135</v>
+        <v>136193.1595588215</v>
       </c>
       <c r="P956" t="n">
         <v>7000</v>
@@ -42853,10 +42853,10 @@
         <v>351</v>
       </c>
       <c r="N975" t="n">
-        <v>2286.1661647535</v>
+        <v>2286.1649330955</v>
       </c>
       <c r="O975" t="n">
-        <v>802444.3238284786</v>
+        <v>802443.8915165205</v>
       </c>
       <c r="P975" t="n">
         <v>3000</v>
@@ -43104,22 +43104,22 @@
         <v>0</v>
       </c>
       <c r="L981" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M981" t="n">
-        <v>3029</v>
+        <v>3009</v>
       </c>
       <c r="N981" t="n">
         <v>177.65</v>
       </c>
       <c r="O981" t="n">
-        <v>538101.85</v>
+        <v>534548.85</v>
       </c>
       <c r="P981" t="n">
         <v>300</v>
       </c>
       <c r="Q981" t="n">
-        <v>908700</v>
+        <v>902700</v>
       </c>
     </row>
     <row r="982">
@@ -43373,10 +43373,10 @@
         <v>2218</v>
       </c>
       <c r="N987" t="n">
-        <v>517.28760395334</v>
+        <v>517.28764753291</v>
       </c>
       <c r="O987" t="n">
-        <v>1147343.905568508</v>
+        <v>1147344.002227994</v>
       </c>
       <c r="P987" t="n">
         <v>900</v>
@@ -43558,10 +43558,10 @@
         <v>1708</v>
       </c>
       <c r="N991" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O991" t="n">
-        <v>5313320.325693576</v>
+        <v>5313320.130537326</v>
       </c>
       <c r="P991" t="n">
         <v>4500</v>
@@ -43684,22 +43684,22 @@
         <v>0</v>
       </c>
       <c r="L994" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M994" t="n">
-        <v>15348</v>
+        <v>15324</v>
       </c>
       <c r="N994" t="n">
-        <v>703.79543678174</v>
+        <v>703.79542528945</v>
       </c>
       <c r="O994" t="n">
-        <v>10801852.36372615</v>
+        <v>10784961.09713553</v>
       </c>
       <c r="P994" t="n">
         <v>900</v>
       </c>
       <c r="Q994" t="n">
-        <v>13813200</v>
+        <v>13791600</v>
       </c>
     </row>
     <row r="995">
@@ -44044,22 +44044,22 @@
         <v>0</v>
       </c>
       <c r="L1002" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1002" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N1002" t="n">
         <v>1937</v>
       </c>
       <c r="O1002" t="n">
-        <v>825162</v>
+        <v>821288</v>
       </c>
       <c r="P1002" t="n">
         <v>3300</v>
       </c>
       <c r="Q1002" t="n">
-        <v>1405800</v>
+        <v>1399200</v>
       </c>
     </row>
     <row r="1003">
@@ -44129,22 +44129,22 @@
         <v>0</v>
       </c>
       <c r="L1004" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1004" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N1004" t="n">
         <v>2525.02</v>
       </c>
       <c r="O1004" t="n">
-        <v>35350.28</v>
+        <v>30300.24</v>
       </c>
       <c r="P1004" t="n">
         <v>3000</v>
       </c>
       <c r="Q1004" t="n">
-        <v>42000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="1005">
@@ -44176,10 +44176,10 @@
         <v>429</v>
       </c>
       <c r="N1005" t="n">
-        <v>2077.4944871795</v>
+        <v>2077.4945</v>
       </c>
       <c r="O1005" t="n">
-        <v>891245.1350000055</v>
+        <v>891245.1404999999</v>
       </c>
       <c r="P1005" t="n">
         <v>2900</v>
@@ -44433,10 +44433,10 @@
         <v>81</v>
       </c>
       <c r="N1011" t="n">
-        <v>1595.5191410878</v>
+        <v>1595.5191323094</v>
       </c>
       <c r="O1011" t="n">
-        <v>129237.0504281118</v>
+        <v>129237.0497170614</v>
       </c>
       <c r="P1011" t="n">
         <v>2500</v>
@@ -44868,10 +44868,10 @@
         <v>21</v>
       </c>
       <c r="N1020" t="n">
-        <v>2098.4047922438</v>
+        <v>2098.4048459384</v>
       </c>
       <c r="O1020" t="n">
-        <v>44066.5006371198</v>
+        <v>44066.50176470639</v>
       </c>
       <c r="P1020" t="n">
         <v>9500</v>
@@ -45236,10 +45236,10 @@
         <v>3</v>
       </c>
       <c r="N1028" t="n">
-        <v>5796.3337037037</v>
+        <v>5796.334</v>
       </c>
       <c r="O1028" t="n">
-        <v>17389.0011111111</v>
+        <v>17389.002</v>
       </c>
       <c r="P1028" t="n">
         <v>15900</v>
@@ -45415,22 +45415,22 @@
         <v>0</v>
       </c>
       <c r="L1032" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1032" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N1032" t="n">
-        <v>875.69015037594</v>
+        <v>875.69015686275</v>
       </c>
       <c r="O1032" t="n">
-        <v>8756.9015037594</v>
+        <v>3502.760627451</v>
       </c>
       <c r="P1032" t="n">
         <v>4500</v>
       </c>
       <c r="Q1032" t="n">
-        <v>45000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1033">
@@ -48197,10 +48197,10 @@
         <v>16</v>
       </c>
       <c r="N1091" t="n">
-        <v>665.32330236486</v>
+        <v>665.3233262441501</v>
       </c>
       <c r="O1091" t="n">
-        <v>10645.17283783776</v>
+        <v>10645.1732199064</v>
       </c>
       <c r="P1091" t="n">
         <v>2900</v>
@@ -50863,10 +50863,10 @@
         <v>385</v>
       </c>
       <c r="N1152" t="n">
-        <v>22951.704981273</v>
+        <v>22951.704968711</v>
       </c>
       <c r="O1152" t="n">
-        <v>8836406.417790106</v>
+        <v>8836406.412953736</v>
       </c>
       <c r="P1152" t="n">
         <v>37900</v>
@@ -51991,22 +51991,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1177" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N1177" t="n">
         <v>13900</v>
       </c>
       <c r="O1177" t="n">
-        <v>291900</v>
+        <v>278000</v>
       </c>
       <c r="P1177" t="n">
         <v>16700</v>
       </c>
       <c r="Q1177" t="n">
-        <v>350700</v>
+        <v>334000</v>
       </c>
     </row>
     <row r="1178">
@@ -53790,22 +53790,22 @@
         <v>0</v>
       </c>
       <c r="L1216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1216" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N1216" t="n">
         <v>2058.92</v>
       </c>
       <c r="O1216" t="n">
-        <v>512671.08</v>
+        <v>508553.24</v>
       </c>
       <c r="P1216" t="n">
         <v>2500</v>
       </c>
       <c r="Q1216" t="n">
-        <v>622500</v>
+        <v>617500</v>
       </c>
     </row>
     <row r="1217">
@@ -61476,22 +61476,22 @@
         <v>0</v>
       </c>
       <c r="L1402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1402" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N1402" t="n">
         <v>4550</v>
       </c>
       <c r="O1402" t="n">
-        <v>718900</v>
+        <v>714350</v>
       </c>
       <c r="P1402" t="n">
         <v>6500</v>
       </c>
       <c r="Q1402" t="n">
-        <v>1027000</v>
+        <v>1020500</v>
       </c>
     </row>
     <row r="1403">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>330</v>
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>26</v>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>346</v>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>35</v>
@@ -2907,13 +2907,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>3</v>
@@ -5651,13 +5651,13 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
         <v>30</v>
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>311</v>
@@ -8883,13 +8883,13 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
         <v>7</v>
@@ -9139,13 +9139,13 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
         <v>100</v>
@@ -9877,13 +9877,13 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>9377</v>
+        <v>9317</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
         <v>9317</v>
@@ -10428,13 +10428,13 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>1387</v>
+        <v>1359</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
         <v>1359</v>
@@ -11662,10 +11662,10 @@
         <v>283</v>
       </c>
       <c r="N267" t="n">
-        <v>17261.351724138</v>
+        <v>17207.41</v>
       </c>
       <c r="O267" t="n">
-        <v>4884962.537931054</v>
+        <v>4869697.03</v>
       </c>
       <c r="P267" t="n">
         <v>20000</v>
@@ -11744,10 +11744,10 @@
         <v>190</v>
       </c>
       <c r="N269" t="n">
-        <v>5050.3355704698</v>
+        <v>5000</v>
       </c>
       <c r="O269" t="n">
-        <v>959563.7583892619</v>
+        <v>950000</v>
       </c>
       <c r="P269" t="n">
         <v>4900</v>
@@ -11872,10 +11872,10 @@
         <v>107</v>
       </c>
       <c r="N272" t="n">
-        <v>2808.0329005282</v>
+        <v>2804.33</v>
       </c>
       <c r="O272" t="n">
-        <v>300459.5203565174</v>
+        <v>300063.31</v>
       </c>
       <c r="P272" t="n">
         <v>4900</v>
@@ -12175,10 +12175,10 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>12</v>
+        <v>1092</v>
       </c>
       <c r="K279" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="K280" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -12354,13 +12354,13 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
         <v>173</v>
@@ -12646,13 +12646,13 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
         <v>2836</v>
@@ -12738,13 +12738,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>228</v>
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>92</v>
@@ -13140,13 +13140,13 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>34</v>
@@ -13475,10 +13475,10 @@
         <v>654</v>
       </c>
       <c r="N308" t="n">
-        <v>6511.2612966601</v>
+        <v>6507</v>
       </c>
       <c r="O308" t="n">
-        <v>4258364.888015705</v>
+        <v>4255578</v>
       </c>
       <c r="P308" t="n">
         <v>9900</v>
@@ -13545,13 +13545,13 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M310" t="n">
         <v>119</v>
@@ -13847,13 +13847,13 @@
         </is>
       </c>
       <c r="J317" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>383</v>
@@ -14075,13 +14075,13 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
         <v>955</v>
@@ -14486,10 +14486,10 @@
         <v>758</v>
       </c>
       <c r="N331" t="n">
-        <v>5672.995244381</v>
+        <v>5667.94</v>
       </c>
       <c r="O331" t="n">
-        <v>4300130.395240798</v>
+        <v>4296298.52</v>
       </c>
       <c r="P331" t="n">
         <v>9500</v>
@@ -14578,10 +14578,10 @@
         <v>29</v>
       </c>
       <c r="N333" t="n">
-        <v>8688.0641925777</v>
+        <v>8662</v>
       </c>
       <c r="O333" t="n">
-        <v>251953.8615847533</v>
+        <v>251198</v>
       </c>
       <c r="P333" t="n">
         <v>14200</v>
@@ -14779,13 +14779,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>366</v>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>1487</v>
+        <v>1474</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>1474</v>
@@ -14963,10 +14963,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3259.9983308715</v>
+        <v>3240.8500295421</v>
       </c>
       <c r="O342" t="n">
-        <v>3259.9983308715</v>
+        <v>3240.8500295421</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -15089,10 +15089,10 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K345" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -15218,13 +15218,13 @@
         </is>
       </c>
       <c r="J348" t="n">
-        <v>6382</v>
+        <v>6376</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>6376</v>
@@ -15529,10 +15529,10 @@
         <v>1</v>
       </c>
       <c r="N355" t="n">
-        <v>2670.3450834879</v>
+        <v>2665.4</v>
       </c>
       <c r="O355" t="n">
-        <v>2670.3450834879</v>
+        <v>2665.4</v>
       </c>
       <c r="P355" t="n">
         <v>20900</v>
@@ -15767,13 +15767,13 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>2737</v>
+        <v>2727</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M361" t="n">
         <v>2727</v>
@@ -16037,13 +16037,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>165</v>
@@ -16124,10 +16124,10 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>467</v>
+        <v>8147</v>
       </c>
       <c r="K369" t="n">
-        <v>7680</v>
+        <v>0</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -16296,13 +16296,13 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>607</v>
@@ -16806,13 +16806,13 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
       </c>
       <c r="L385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
         <v>65</v>
@@ -17030,13 +17030,13 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M390" t="n">
         <v>1039</v>
@@ -17288,13 +17288,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>3002</v>
+        <v>2981</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>2981</v>
@@ -18432,13 +18432,13 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M422" t="n">
         <v>62</v>
@@ -18658,13 +18658,13 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M427" t="n">
         <v>532</v>
@@ -19273,13 +19273,13 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M441" t="n">
         <v>170</v>
@@ -21031,13 +21031,13 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
       </c>
       <c r="L481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M481" t="n">
         <v>7</v>
@@ -22004,10 +22004,10 @@
         <v>1</v>
       </c>
       <c r="N504" t="n">
-        <v>21575.611111111</v>
+        <v>19418.05</v>
       </c>
       <c r="O504" t="n">
-        <v>21575.611111111</v>
+        <v>19418.05</v>
       </c>
       <c r="P504" t="n">
         <v>25300</v>
@@ -22781,10 +22781,10 @@
         <v>11</v>
       </c>
       <c r="N522" t="n">
-        <v>2673.5203076923</v>
+        <v>2661.82</v>
       </c>
       <c r="O522" t="n">
-        <v>29408.7233846153</v>
+        <v>29280.02</v>
       </c>
       <c r="P522" t="n">
         <v>3200</v>
@@ -22863,10 +22863,10 @@
         <v>1</v>
       </c>
       <c r="N524" t="n">
-        <v>4530.3396226415</v>
+        <v>4488</v>
       </c>
       <c r="O524" t="n">
-        <v>4530.3396226415</v>
+        <v>4488</v>
       </c>
       <c r="P524" t="n">
         <v>6200</v>
@@ -24092,13 +24092,13 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M554" t="n">
         <v>135</v>
@@ -25652,13 +25652,13 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M591" t="n">
         <v>307</v>
@@ -26259,10 +26259,10 @@
         <v>4</v>
       </c>
       <c r="N605" t="n">
-        <v>3592.9712903777</v>
+        <v>3591.13</v>
       </c>
       <c r="O605" t="n">
-        <v>14371.8851615108</v>
+        <v>14364.52</v>
       </c>
       <c r="P605" t="n">
         <v>6300</v>
@@ -28621,13 +28621,13 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M661" t="n">
         <v>88</v>
@@ -30569,10 +30569,10 @@
         <v>15</v>
       </c>
       <c r="N707" t="n">
-        <v>13028.454945848</v>
+        <v>12981.59</v>
       </c>
       <c r="O707" t="n">
-        <v>195426.82418772</v>
+        <v>194723.85</v>
       </c>
       <c r="P707" t="n">
         <v>21900</v>
@@ -30615,10 +30615,10 @@
         <v>25</v>
       </c>
       <c r="N708" t="n">
-        <v>13925.387959866</v>
+        <v>13878.97</v>
       </c>
       <c r="O708" t="n">
-        <v>348134.69899665</v>
+        <v>346974.25</v>
       </c>
       <c r="P708" t="n">
         <v>21900</v>
@@ -31391,13 +31391,13 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K726" t="n">
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M726" t="n">
         <v>27</v>
@@ -31854,13 +31854,13 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
         <v>1</v>
@@ -31992,13 +31992,13 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M739" t="n">
         <v>62</v>
@@ -33336,10 +33336,10 @@
         <v>177</v>
       </c>
       <c r="N768" t="n">
-        <v>16069.364472753</v>
+        <v>16058</v>
       </c>
       <c r="O768" t="n">
-        <v>2844277.511677281</v>
+        <v>2842266</v>
       </c>
       <c r="P768" t="n">
         <v>25900</v>
@@ -34896,13 +34896,13 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
       </c>
       <c r="L802" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M802" t="n">
         <v>66</v>
@@ -36153,10 +36153,10 @@
         <v>207</v>
       </c>
       <c r="N829" t="n">
-        <v>9197.9305103149</v>
+        <v>9178</v>
       </c>
       <c r="O829" t="n">
-        <v>1903971.615635184</v>
+        <v>1899846</v>
       </c>
       <c r="P829" t="n">
         <v>14900</v>
@@ -36187,13 +36187,13 @@
         </is>
       </c>
       <c r="J830" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="K830" t="n">
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M830" t="n">
         <v>274</v>
@@ -36291,10 +36291,10 @@
         <v>165</v>
       </c>
       <c r="N832" t="n">
-        <v>13973.183823529</v>
+        <v>13922</v>
       </c>
       <c r="O832" t="n">
-        <v>2305575.330882285</v>
+        <v>2297130</v>
       </c>
       <c r="P832" t="n">
         <v>22900</v>
@@ -36337,10 +36337,10 @@
         <v>43</v>
       </c>
       <c r="N833" t="n">
-        <v>16489.485</v>
+        <v>16285.911125</v>
       </c>
       <c r="O833" t="n">
-        <v>709047.855</v>
+        <v>700294.178375</v>
       </c>
       <c r="P833" t="n">
         <v>29900</v>
@@ -36785,13 +36785,13 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M843" t="n">
         <v>20</v>
@@ -37516,13 +37516,13 @@
         </is>
       </c>
       <c r="J859" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K859" t="n">
         <v>0</v>
       </c>
       <c r="L859" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M859" t="n">
         <v>4</v>
@@ -37712,10 +37712,10 @@
         <v>1</v>
       </c>
       <c r="N863" t="n">
-        <v>7649.2538461538</v>
+        <v>7562</v>
       </c>
       <c r="O863" t="n">
-        <v>7649.2538461538</v>
+        <v>7562</v>
       </c>
       <c r="P863" t="n">
         <v>12900</v>
@@ -37884,13 +37884,13 @@
         </is>
       </c>
       <c r="J867" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K867" t="n">
         <v>0</v>
       </c>
       <c r="L867" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M867" t="n">
         <v>73</v>
@@ -38172,10 +38172,10 @@
         <v>111</v>
       </c>
       <c r="N873" t="n">
-        <v>18015.037131882</v>
+        <v>17992</v>
       </c>
       <c r="O873" t="n">
-        <v>1999669.121638902</v>
+        <v>1997112</v>
       </c>
       <c r="P873" t="n">
         <v>28900</v>
@@ -38664,13 +38664,13 @@
         </is>
       </c>
       <c r="J884" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K884" t="n">
         <v>0</v>
       </c>
       <c r="L884" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M884" t="n">
         <v>269</v>
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="J896" t="n">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="K896" t="n">
         <v>0</v>
       </c>
       <c r="L896" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M896" t="n">
         <v>1726</v>
@@ -39817,13 +39817,13 @@
         </is>
       </c>
       <c r="J909" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
       </c>
       <c r="L909" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M909" t="n">
         <v>26</v>
@@ -40011,10 +40011,10 @@
         <v>60</v>
       </c>
       <c r="N913" t="n">
-        <v>1909.016377551</v>
+        <v>1907.3944387755</v>
       </c>
       <c r="O913" t="n">
-        <v>114540.98265306</v>
+        <v>114443.66632653</v>
       </c>
       <c r="P913" t="n">
         <v>2500</v>
@@ -40091,13 +40091,13 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M915" t="n">
         <v>370</v>
@@ -40333,10 +40333,10 @@
         <v>393</v>
       </c>
       <c r="N920" t="n">
-        <v>2056.692917654</v>
+        <v>2056.0838862559</v>
       </c>
       <c r="O920" t="n">
-        <v>808280.3166380221</v>
+        <v>808040.9672985687</v>
       </c>
       <c r="P920" t="n">
         <v>2900</v>
@@ -40367,13 +40367,13 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
       </c>
       <c r="L921" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M921" t="n">
         <v>238</v>
@@ -40413,13 +40413,13 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
         <v>309</v>
@@ -40600,13 +40600,13 @@
         </is>
       </c>
       <c r="J926" t="n">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="K926" t="n">
         <v>0</v>
       </c>
       <c r="L926" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M926" t="n">
         <v>887</v>
@@ -40777,13 +40777,13 @@
         </is>
       </c>
       <c r="J930" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K930" t="n">
         <v>0</v>
       </c>
       <c r="L930" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M930" t="n">
         <v>232</v>
@@ -41791,13 +41791,13 @@
         </is>
       </c>
       <c r="J952" t="n">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K952" t="n">
         <v>0</v>
       </c>
       <c r="L952" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M952" t="n">
         <v>534</v>
@@ -41886,13 +41886,13 @@
         </is>
       </c>
       <c r="J954" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K954" t="n">
         <v>0</v>
       </c>
       <c r="L954" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M954" t="n">
         <v>395</v>
@@ -43059,13 +43059,13 @@
         </is>
       </c>
       <c r="J980" t="n">
-        <v>3009</v>
+        <v>2979</v>
       </c>
       <c r="K980" t="n">
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M980" t="n">
         <v>2979</v>
@@ -43322,13 +43322,13 @@
         </is>
       </c>
       <c r="J986" t="n">
-        <v>2218</v>
+        <v>2194</v>
       </c>
       <c r="K986" t="n">
         <v>0</v>
       </c>
       <c r="L986" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M986" t="n">
         <v>2194</v>
@@ -43639,13 +43639,13 @@
         </is>
       </c>
       <c r="J993" t="n">
-        <v>15324</v>
+        <v>15276</v>
       </c>
       <c r="K993" t="n">
         <v>0</v>
       </c>
       <c r="L993" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M993" t="n">
         <v>15276</v>
@@ -43999,13 +43999,13 @@
         </is>
       </c>
       <c r="J1001" t="n">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="K1001" t="n">
         <v>0</v>
       </c>
       <c r="L1001" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M1001" t="n">
         <v>411</v>
@@ -44946,13 +44946,13 @@
         </is>
       </c>
       <c r="J1022" t="n">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="K1022" t="n">
         <v>0</v>
       </c>
       <c r="L1022" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1022" t="n">
         <v>1023</v>
@@ -45229,13 +45229,13 @@
         </is>
       </c>
       <c r="J1028" t="n">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="K1028" t="n">
         <v>0</v>
       </c>
       <c r="L1028" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1028" t="n">
         <v>691</v>
@@ -46686,13 +46686,13 @@
         </is>
       </c>
       <c r="J1059" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1059" t="n">
         <v>0</v>
       </c>
       <c r="L1059" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1059" t="n">
         <v>2</v>
@@ -48005,13 +48005,13 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
       </c>
       <c r="L1087" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1087" t="n">
         <v>25</v>
@@ -48239,13 +48239,13 @@
         </is>
       </c>
       <c r="J1092" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K1092" t="n">
         <v>0</v>
       </c>
       <c r="L1092" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1092" t="n">
         <v>4</v>
@@ -49382,13 +49382,13 @@
         </is>
       </c>
       <c r="J1118" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K1118" t="n">
         <v>0</v>
       </c>
       <c r="L1118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1118" t="n">
         <v>320</v>
@@ -49769,13 +49769,13 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>1803</v>
+        <v>1782</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M1127" t="n">
         <v>1782</v>
@@ -49857,13 +49857,13 @@
         </is>
       </c>
       <c r="J1129" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="K1129" t="n">
         <v>0</v>
       </c>
       <c r="L1129" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1129" t="n">
         <v>152</v>
@@ -50027,13 +50027,13 @@
         </is>
       </c>
       <c r="J1133" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K1133" t="n">
         <v>0</v>
       </c>
       <c r="L1133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1133" t="n">
         <v>120</v>
@@ -53837,13 +53837,13 @@
         </is>
       </c>
       <c r="J1217" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K1217" t="n">
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1217" t="n">
         <v>96</v>
@@ -61431,13 +61431,13 @@
         </is>
       </c>
       <c r="J1401" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K1401" t="n">
         <v>0</v>
       </c>
       <c r="L1401" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1401" t="n">
         <v>154</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -692,10 +692,10 @@
         <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>66707.97725</v>
+        <v>66707.977837838</v>
       </c>
       <c r="O7" t="n">
-        <v>533663.818</v>
+        <v>533663.822702704</v>
       </c>
       <c r="P7" t="n">
         <v>125900</v>
@@ -997,10 +997,10 @@
         <v>310</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3044243338</v>
+        <v>1811.3044829343</v>
       </c>
       <c r="O14" t="n">
-        <v>561504.371543478</v>
+        <v>561504.389709633</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
@@ -1071,22 +1071,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="N16" t="n">
-        <v>1990.0435660377</v>
+        <v>1990.0435416667</v>
       </c>
       <c r="O16" t="n">
-        <v>308456.7527358435</v>
+        <v>304476.6618750051</v>
       </c>
       <c r="P16" t="n">
         <v>4400</v>
       </c>
       <c r="Q16" t="n">
-        <v>682000</v>
+        <v>673200</v>
       </c>
     </row>
     <row r="17">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.7465014893</v>
+        <v>3376.746498645</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.744205249</v>
+        <v>3866374.740948525</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -1634,22 +1634,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>20826.676585366</v>
+        <v>20826.676923077</v>
       </c>
       <c r="O30" t="n">
-        <v>83306.706341464</v>
+        <v>41653.353846154</v>
       </c>
       <c r="P30" t="n">
         <v>39100</v>
       </c>
       <c r="Q30" t="n">
-        <v>156400</v>
+        <v>78200</v>
       </c>
     </row>
     <row r="31">
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8545</v>
+        <v>6272.8545786963</v>
       </c>
       <c r="O58" t="n">
-        <v>483009.7965000001</v>
+        <v>445372.6750874373</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>608300</v>
+        <v>560900</v>
       </c>
     </row>
     <row r="59">
@@ -2832,22 +2832,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>85598.45</v>
+        <v>83152.78</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>161000</v>
+        <v>156400</v>
       </c>
     </row>
     <row r="60">
@@ -3203,10 +3203,10 @@
         <v>94</v>
       </c>
       <c r="N68" t="n">
-        <v>2413.001059322</v>
+        <v>2413.0010615711</v>
       </c>
       <c r="O68" t="n">
-        <v>226822.099576268</v>
+        <v>226822.0997876834</v>
       </c>
       <c r="P68" t="n">
         <v>4700</v>
@@ -3242,10 +3242,10 @@
         <v>296</v>
       </c>
       <c r="N69" t="n">
-        <v>2474.7042140468</v>
+        <v>2474.7042043551</v>
       </c>
       <c r="O69" t="n">
-        <v>732512.4473578528</v>
+        <v>732512.4444891096</v>
       </c>
       <c r="P69" t="n">
         <v>4500</v>
@@ -4137,10 +4137,10 @@
         <v>17</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6282248521</v>
+        <v>3910.6281963928</v>
       </c>
       <c r="O91" t="n">
-        <v>66480.6798224857</v>
+        <v>66480.6793386776</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
@@ -5092,10 +5092,10 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>18835.023125</v>
+        <v>18835.024666667</v>
       </c>
       <c r="O112" t="n">
-        <v>18835.023125</v>
+        <v>18835.024666667</v>
       </c>
       <c r="P112" t="n">
         <v>40500</v>
@@ -6557,10 +6557,10 @@
         <v>2</v>
       </c>
       <c r="N147" t="n">
-        <v>200072.19992308</v>
+        <v>200072.2</v>
       </c>
       <c r="O147" t="n">
-        <v>400144.39984616</v>
+        <v>400144.4</v>
       </c>
       <c r="P147" t="n">
         <v>312000</v>
@@ -7677,22 +7677,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N174" t="n">
         <v>3865.67</v>
       </c>
       <c r="O174" t="n">
-        <v>1155835.33</v>
+        <v>1151969.66</v>
       </c>
       <c r="P174" t="n">
         <v>5500</v>
       </c>
       <c r="Q174" t="n">
-        <v>1644500</v>
+        <v>1639000</v>
       </c>
     </row>
     <row r="175">
@@ -8295,22 +8295,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N188" t="n">
         <v>3114.49</v>
       </c>
       <c r="O188" t="n">
-        <v>186869.4</v>
+        <v>183754.91</v>
       </c>
       <c r="P188" t="n">
         <v>5500</v>
       </c>
       <c r="Q188" t="n">
-        <v>330000</v>
+        <v>324500</v>
       </c>
     </row>
     <row r="189">
@@ -8334,22 +8334,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M189" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N189" t="n">
         <v>3667.11</v>
       </c>
       <c r="O189" t="n">
-        <v>58673.76</v>
+        <v>47672.43</v>
       </c>
       <c r="P189" t="n">
         <v>7300</v>
       </c>
       <c r="Q189" t="n">
-        <v>116800</v>
+        <v>94900</v>
       </c>
     </row>
     <row r="190">
@@ -8373,22 +8373,22 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M190" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N190" t="n">
         <v>2791.02</v>
       </c>
       <c r="O190" t="n">
-        <v>83730.60000000001</v>
+        <v>75357.53999999999</v>
       </c>
       <c r="P190" t="n">
         <v>3900</v>
       </c>
       <c r="Q190" t="n">
-        <v>117000</v>
+        <v>105300</v>
       </c>
     </row>
     <row r="191">
@@ -8412,22 +8412,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M191" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N191" t="n">
         <v>3564.14</v>
       </c>
       <c r="O191" t="n">
-        <v>228104.96</v>
+        <v>220976.68</v>
       </c>
       <c r="P191" t="n">
         <v>5500</v>
       </c>
       <c r="Q191" t="n">
-        <v>352000</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="192">
@@ -8844,10 +8844,10 @@
         <v>5</v>
       </c>
       <c r="N201" t="n">
-        <v>4333.604375</v>
+        <v>4333.6046666667</v>
       </c>
       <c r="O201" t="n">
-        <v>21668.021875</v>
+        <v>21668.0233333335</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9018,22 +9018,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M205" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N205" t="n">
-        <v>4276.1766336634</v>
+        <v>4276.1769072165</v>
       </c>
       <c r="O205" t="n">
-        <v>124009.1223762386</v>
+        <v>106904.4226804125</v>
       </c>
       <c r="P205" t="n">
         <v>7800</v>
       </c>
       <c r="Q205" t="n">
-        <v>226200</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="206">
@@ -9057,22 +9057,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M206" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N206" t="n">
-        <v>3340.6800808081</v>
+        <v>3340.6800817996</v>
       </c>
       <c r="O206" t="n">
-        <v>90198.36218181869</v>
+        <v>70154.2817177916</v>
       </c>
       <c r="P206" t="n">
         <v>7100</v>
       </c>
       <c r="Q206" t="n">
-        <v>191700</v>
+        <v>149100</v>
       </c>
     </row>
     <row r="207">
@@ -9140,22 +9140,22 @@
         <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N208" t="n">
         <v>2563.34</v>
       </c>
       <c r="O208" t="n">
-        <v>256334</v>
+        <v>253770.66</v>
       </c>
       <c r="P208" t="n">
         <v>4700</v>
       </c>
       <c r="Q208" t="n">
-        <v>470000</v>
+        <v>465300</v>
       </c>
     </row>
     <row r="209">
@@ -9878,22 +9878,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M225" t="n">
-        <v>9298</v>
+        <v>9292</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>16051323.36</v>
+        <v>16040965.44</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>13947000</v>
+        <v>13938000</v>
       </c>
     </row>
     <row r="226">
@@ -9965,22 +9965,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M227" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N227" t="n">
-        <v>4937.3101608187</v>
+        <v>4937.3101611722</v>
       </c>
       <c r="O227" t="n">
-        <v>1091145.545540933</v>
+        <v>1076333.61513554</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
       </c>
       <c r="Q227" t="n">
-        <v>1657500</v>
+        <v>1635000</v>
       </c>
     </row>
     <row r="228">
@@ -10134,22 +10134,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M231" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N231" t="n">
         <v>6513</v>
       </c>
       <c r="O231" t="n">
-        <v>898794</v>
+        <v>879255</v>
       </c>
       <c r="P231" t="n">
         <v>11500</v>
       </c>
       <c r="Q231" t="n">
-        <v>1587000</v>
+        <v>1552500</v>
       </c>
     </row>
     <row r="232">
@@ -10429,22 +10429,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M238" t="n">
-        <v>1239</v>
+        <v>1167</v>
       </c>
       <c r="N238" t="n">
-        <v>1098.0548595108</v>
+        <v>1098.0555939754</v>
       </c>
       <c r="O238" t="n">
-        <v>1360489.970933881</v>
+        <v>1281430.878169292</v>
       </c>
       <c r="P238" t="n">
         <v>1500</v>
       </c>
       <c r="Q238" t="n">
-        <v>1858500</v>
+        <v>1750500</v>
       </c>
     </row>
     <row r="239">
@@ -11262,22 +11262,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M258" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N258" t="n">
         <v>3395</v>
       </c>
       <c r="O258" t="n">
-        <v>475300</v>
+        <v>468510</v>
       </c>
       <c r="P258" t="n">
         <v>5500</v>
       </c>
       <c r="Q258" t="n">
-        <v>770000</v>
+        <v>759000</v>
       </c>
     </row>
     <row r="259">
@@ -11354,22 +11354,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M260" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N260" t="n">
         <v>7569</v>
       </c>
       <c r="O260" t="n">
-        <v>416295</v>
+        <v>370881</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>
       </c>
       <c r="Q260" t="n">
-        <v>709500</v>
+        <v>632100</v>
       </c>
     </row>
     <row r="261">
@@ -12176,22 +12176,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M279" t="n">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="N279" t="n">
-        <v>2582.2560231583</v>
+        <v>2582.2560112135</v>
       </c>
       <c r="O279" t="n">
-        <v>2819823.577288864</v>
+        <v>2799165.516155434</v>
       </c>
       <c r="P279" t="n">
         <v>4500</v>
       </c>
       <c r="Q279" t="n">
-        <v>4914000</v>
+        <v>4878000</v>
       </c>
     </row>
     <row r="280">
@@ -12228,10 +12228,10 @@
         <v>1434</v>
       </c>
       <c r="N280" t="n">
-        <v>5216.8959678619</v>
+        <v>5216.8959654608</v>
       </c>
       <c r="O280" t="n">
-        <v>7481028.817913965</v>
+        <v>7481028.814470787</v>
       </c>
       <c r="P280" t="n">
         <v>8500</v>
@@ -12361,10 +12361,10 @@
         <v>140</v>
       </c>
       <c r="N283" t="n">
-        <v>2033.5682467532</v>
+        <v>2033.5670707071</v>
       </c>
       <c r="O283" t="n">
-        <v>284699.554545448</v>
+        <v>284699.389898994</v>
       </c>
       <c r="P283" t="n">
         <v>4100</v>
@@ -12653,10 +12653,10 @@
         <v>2836</v>
       </c>
       <c r="N290" t="n">
-        <v>3158.8608147003</v>
+        <v>3158.860814779</v>
       </c>
       <c r="O290" t="n">
-        <v>8958529.27049005</v>
+        <v>8958529.270713244</v>
       </c>
       <c r="P290" t="n">
         <v>5600</v>
@@ -12745,10 +12745,10 @@
         <v>228</v>
       </c>
       <c r="N292" t="n">
-        <v>3841.6247184466</v>
+        <v>3841.6247414634</v>
       </c>
       <c r="O292" t="n">
-        <v>875890.4358058248</v>
+        <v>875890.4410536552</v>
       </c>
       <c r="P292" t="n">
         <v>6900</v>
@@ -12927,10 +12927,10 @@
         <v>92</v>
       </c>
       <c r="N296" t="n">
-        <v>3230.067752443</v>
+        <v>3230.0677414075</v>
       </c>
       <c r="O296" t="n">
-        <v>297166.233224756</v>
+        <v>297166.23220949</v>
       </c>
       <c r="P296" t="n">
         <v>6200</v>
@@ -13720,22 +13720,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M314" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N314" t="n">
         <v>7939.23</v>
       </c>
       <c r="O314" t="n">
-        <v>1286155.26</v>
+        <v>1262337.57</v>
       </c>
       <c r="P314" t="n">
         <v>14900</v>
       </c>
       <c r="Q314" t="n">
-        <v>2413800</v>
+        <v>2369100</v>
       </c>
     </row>
     <row r="315">
@@ -13761,22 +13761,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N315" t="n">
         <v>2612.77</v>
       </c>
       <c r="O315" t="n">
-        <v>1450087.35</v>
+        <v>1447474.58</v>
       </c>
       <c r="P315" t="n">
         <v>4900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2719500</v>
+        <v>2714600</v>
       </c>
     </row>
     <row r="316">
@@ -13987,10 +13987,10 @@
         <v>331</v>
       </c>
       <c r="N320" t="n">
-        <v>4890.9300463499</v>
+        <v>4890.9300464306</v>
       </c>
       <c r="O320" t="n">
-        <v>1618897.845341817</v>
+        <v>1618897.845368529</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14076,22 +14076,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M322" t="n">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="N322" t="n">
         <v>1203.38</v>
       </c>
       <c r="O322" t="n">
-        <v>1089058.9</v>
+        <v>1074618.34</v>
       </c>
       <c r="P322" t="n">
         <v>1900</v>
       </c>
       <c r="Q322" t="n">
-        <v>1719500</v>
+        <v>1696700</v>
       </c>
     </row>
     <row r="323">
@@ -14122,22 +14122,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M323" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="N323" t="n">
         <v>3472</v>
       </c>
       <c r="O323" t="n">
-        <v>558992</v>
+        <v>534688</v>
       </c>
       <c r="P323" t="n">
         <v>4800</v>
       </c>
       <c r="Q323" t="n">
-        <v>772800</v>
+        <v>739200</v>
       </c>
     </row>
     <row r="324">
@@ -14786,10 +14786,10 @@
         <v>366</v>
       </c>
       <c r="N338" t="n">
-        <v>3594.25414277</v>
+        <v>3594.2541391941</v>
       </c>
       <c r="O338" t="n">
-        <v>1315497.01625382</v>
+        <v>1315497.014945041</v>
       </c>
       <c r="P338" t="n">
         <v>6500</v>
@@ -14829,22 +14829,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M339" t="n">
-        <v>1010</v>
+        <v>974</v>
       </c>
       <c r="N339" t="n">
         <v>489.88</v>
       </c>
       <c r="O339" t="n">
-        <v>494778.8</v>
+        <v>477143.12</v>
       </c>
       <c r="P339" t="n">
         <v>700</v>
       </c>
       <c r="Q339" t="n">
-        <v>707000</v>
+        <v>681800</v>
       </c>
     </row>
     <row r="340">
@@ -14958,10 +14958,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3240.850029985</v>
+        <v>3240.8500301659</v>
       </c>
       <c r="O342" t="n">
-        <v>3240.850029985</v>
+        <v>3240.8500301659</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -15096,10 +15096,10 @@
         <v>288</v>
       </c>
       <c r="N345" t="n">
-        <v>14822.378863905</v>
+        <v>14822.378862559</v>
       </c>
       <c r="O345" t="n">
-        <v>4268845.11280464</v>
+        <v>4268845.112416992</v>
       </c>
       <c r="P345" t="n">
         <v>24900</v>
@@ -15219,22 +15219,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M348" t="n">
-        <v>6376</v>
+        <v>6373</v>
       </c>
       <c r="N348" t="n">
         <v>2090.85</v>
       </c>
       <c r="O348" t="n">
-        <v>13331259.6</v>
+        <v>13324987.05</v>
       </c>
       <c r="P348" t="n">
         <v>2900</v>
       </c>
       <c r="Q348" t="n">
-        <v>18490400</v>
+        <v>18481700</v>
       </c>
     </row>
     <row r="349">
@@ -15724,22 +15724,22 @@
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N360" t="n">
         <v>15851.61</v>
       </c>
       <c r="O360" t="n">
-        <v>269477.37</v>
+        <v>253625.76</v>
       </c>
       <c r="P360" t="n">
         <v>23900</v>
       </c>
       <c r="Q360" t="n">
-        <v>406300</v>
+        <v>382400</v>
       </c>
     </row>
     <row r="361">
@@ -16038,22 +16038,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M367" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N367" t="n">
-        <v>3041.6600125945</v>
+        <v>3041.6600126502</v>
       </c>
       <c r="O367" t="n">
-        <v>498832.242065498</v>
+        <v>477540.6219860814</v>
       </c>
       <c r="P367" t="n">
         <v>5500</v>
       </c>
       <c r="Q367" t="n">
-        <v>902000</v>
+        <v>863500</v>
       </c>
     </row>
     <row r="368">
@@ -16131,10 +16131,10 @@
         <v>8137</v>
       </c>
       <c r="N369" t="n">
-        <v>4372.2107876031</v>
+        <v>4372.2107877711</v>
       </c>
       <c r="O369" t="n">
-        <v>35576679.17872642</v>
+        <v>35576679.18009344</v>
       </c>
       <c r="P369" t="n">
         <v>7500</v>
@@ -16166,25 +16166,25 @@
         <v>59</v>
       </c>
       <c r="K370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N370" t="n">
         <v>6441.03</v>
       </c>
       <c r="O370" t="n">
-        <v>380020.77</v>
+        <v>386461.8</v>
       </c>
       <c r="P370" t="n">
         <v>10500</v>
       </c>
       <c r="Q370" t="n">
-        <v>619500</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="371">
@@ -16297,22 +16297,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M373" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="N373" t="n">
-        <v>1592.567520267</v>
+        <v>1592.5674522293</v>
       </c>
       <c r="O373" t="n">
-        <v>821764.840457772</v>
+        <v>812209.4006369429</v>
       </c>
       <c r="P373" t="n">
         <v>3900</v>
       </c>
       <c r="Q373" t="n">
-        <v>2012400</v>
+        <v>1989000</v>
       </c>
     </row>
     <row r="374">
@@ -16422,25 +16422,25 @@
         <v>91</v>
       </c>
       <c r="K376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N376" t="n">
         <v>3655.96</v>
       </c>
       <c r="O376" t="n">
-        <v>332692.36</v>
+        <v>340004.28</v>
       </c>
       <c r="P376" t="n">
         <v>5500</v>
       </c>
       <c r="Q376" t="n">
-        <v>500500</v>
+        <v>511500</v>
       </c>
     </row>
     <row r="377">
@@ -16466,22 +16466,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M377" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N377" t="n">
         <v>5331.69</v>
       </c>
       <c r="O377" t="n">
-        <v>687788.0099999999</v>
+        <v>671792.9399999999</v>
       </c>
       <c r="P377" t="n">
         <v>7900</v>
       </c>
       <c r="Q377" t="n">
-        <v>1019100</v>
+        <v>995400</v>
       </c>
     </row>
     <row r="378">
@@ -16509,25 +16509,25 @@
         <v>16</v>
       </c>
       <c r="K378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N378" t="n">
         <v>4717</v>
       </c>
       <c r="O378" t="n">
-        <v>75472</v>
+        <v>80189</v>
       </c>
       <c r="P378" t="n">
         <v>7900</v>
       </c>
       <c r="Q378" t="n">
-        <v>126400</v>
+        <v>134300</v>
       </c>
     </row>
     <row r="379">
@@ -16853,22 +16853,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M386" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="N386" t="n">
         <v>6242.93</v>
       </c>
       <c r="O386" t="n">
-        <v>2272426.52</v>
+        <v>2253697.73</v>
       </c>
       <c r="P386" t="n">
         <v>10400</v>
       </c>
       <c r="Q386" t="n">
-        <v>3785600</v>
+        <v>3754400</v>
       </c>
     </row>
     <row r="387">
@@ -16902,22 +16902,22 @@
         <v>0</v>
       </c>
       <c r="L387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M387" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N387" t="n">
         <v>4648.6</v>
       </c>
       <c r="O387" t="n">
-        <v>1157501.4</v>
+        <v>1148204.2</v>
       </c>
       <c r="P387" t="n">
         <v>8900</v>
       </c>
       <c r="Q387" t="n">
-        <v>2216100</v>
+        <v>2198300</v>
       </c>
     </row>
     <row r="388">
@@ -17289,22 +17289,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M396" t="n">
-        <v>2935</v>
+        <v>2869</v>
       </c>
       <c r="N396" t="n">
         <v>1387.55</v>
       </c>
       <c r="O396" t="n">
-        <v>4072459.25</v>
+        <v>3980880.95</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
       </c>
       <c r="Q396" t="n">
-        <v>6750500</v>
+        <v>6598700</v>
       </c>
     </row>
     <row r="397">
@@ -17421,22 +17421,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="N399" t="n">
-        <v>2021.7211218335</v>
+        <v>2021.7211225106</v>
       </c>
       <c r="O399" t="n">
-        <v>2130894.062412509</v>
+        <v>2128872.342003662</v>
       </c>
       <c r="P399" t="n">
         <v>2400</v>
       </c>
       <c r="Q399" t="n">
-        <v>2529600</v>
+        <v>2527200</v>
       </c>
     </row>
     <row r="400">
@@ -18433,22 +18433,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N422" t="n">
         <v>3751</v>
       </c>
       <c r="O422" t="n">
-        <v>210056</v>
+        <v>206305</v>
       </c>
       <c r="P422" t="n">
         <v>6400</v>
       </c>
       <c r="Q422" t="n">
-        <v>358400</v>
+        <v>352000</v>
       </c>
     </row>
     <row r="423">
@@ -18523,22 +18523,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M424" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N424" t="n">
         <v>6557.57</v>
       </c>
       <c r="O424" t="n">
-        <v>426242.05</v>
+        <v>406569.34</v>
       </c>
       <c r="P424" t="n">
         <v>9900</v>
       </c>
       <c r="Q424" t="n">
-        <v>643500</v>
+        <v>613800</v>
       </c>
     </row>
     <row r="425">
@@ -18659,22 +18659,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M427" t="n">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N427" t="n">
-        <v>1630.923147125</v>
+        <v>1630.9231587595</v>
       </c>
       <c r="O427" t="n">
-        <v>807306.957826875</v>
+        <v>802414.194109674</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1237500</v>
+        <v>1230000</v>
       </c>
     </row>
     <row r="428">
@@ -18757,10 +18757,10 @@
         <v>52</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.6028354857</v>
+        <v>1690.6026503973</v>
       </c>
       <c r="O429" t="n">
-        <v>87911.34744525641</v>
+        <v>87911.33782065961</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
@@ -18797,22 +18797,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M430" t="n">
-        <v>1017</v>
+        <v>988</v>
       </c>
       <c r="N430" t="n">
-        <v>1550.1931350849</v>
+        <v>1550.1931558806</v>
       </c>
       <c r="O430" t="n">
-        <v>1576546.418381343</v>
+        <v>1531590.838010033</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
       </c>
       <c r="Q430" t="n">
-        <v>2542500</v>
+        <v>2470000</v>
       </c>
     </row>
     <row r="431">
@@ -18849,10 +18849,10 @@
         <v>112</v>
       </c>
       <c r="N431" t="n">
-        <v>1579.3910473815</v>
+        <v>1579.391025</v>
       </c>
       <c r="O431" t="n">
-        <v>176891.797306728</v>
+        <v>176891.7948</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
@@ -18889,22 +18889,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M432" t="n">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="N432" t="n">
-        <v>2403.5103430475</v>
+        <v>2403.5103724115</v>
       </c>
       <c r="O432" t="n">
-        <v>2172773.35011494</v>
+        <v>2163159.33517035</v>
       </c>
       <c r="P432" t="n">
         <v>3500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3164000</v>
+        <v>3150000</v>
       </c>
     </row>
     <row r="433">
@@ -18979,22 +18979,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M434" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="N434" t="n">
-        <v>2521.5446987952</v>
+        <v>2521.5439240506</v>
       </c>
       <c r="O434" t="n">
-        <v>738812.5967469936</v>
+        <v>731247.737974674</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
       </c>
       <c r="Q434" t="n">
-        <v>1142700</v>
+        <v>1131000</v>
       </c>
     </row>
     <row r="435">
@@ -22689,10 +22689,10 @@
         <v>6</v>
       </c>
       <c r="N520" t="n">
-        <v>7537.4721641791</v>
+        <v>7537.4721804511</v>
       </c>
       <c r="O520" t="n">
-        <v>45224.8329850746</v>
+        <v>45224.8330827066</v>
       </c>
       <c r="P520" t="n">
         <v>8900</v>
@@ -22973,22 +22973,22 @@
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M527" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N527" t="n">
         <v>17232</v>
       </c>
       <c r="O527" t="n">
-        <v>1206240</v>
+        <v>1189008</v>
       </c>
       <c r="P527" t="n">
         <v>22500</v>
       </c>
       <c r="Q527" t="n">
-        <v>1575000</v>
+        <v>1552500</v>
       </c>
     </row>
     <row r="528">
@@ -23520,10 +23520,10 @@
         <v>246</v>
       </c>
       <c r="N540" t="n">
-        <v>2029.8736782737</v>
+        <v>2029.8737073653</v>
       </c>
       <c r="O540" t="n">
-        <v>499348.9248553302</v>
+        <v>499348.9320118638</v>
       </c>
       <c r="P540" t="n">
         <v>3600</v>
@@ -24348,10 +24348,10 @@
         <v>617</v>
       </c>
       <c r="N560" t="n">
-        <v>880.32935107376</v>
+        <v>880.3293685687599</v>
       </c>
       <c r="O560" t="n">
-        <v>543163.2096125099</v>
+        <v>543163.2204069248</v>
       </c>
       <c r="P560" t="n">
         <v>1200</v>
@@ -24721,22 +24721,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M569" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N569" t="n">
         <v>5894.64</v>
       </c>
       <c r="O569" t="n">
-        <v>742724.64</v>
+        <v>730935.36</v>
       </c>
       <c r="P569" t="n">
         <v>11000</v>
       </c>
       <c r="Q569" t="n">
-        <v>1386000</v>
+        <v>1364000</v>
       </c>
     </row>
     <row r="570">
@@ -27936,22 +27936,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M645" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N645" t="n">
         <v>8300</v>
       </c>
       <c r="O645" t="n">
-        <v>888100</v>
+        <v>879800</v>
       </c>
       <c r="P645" t="n">
         <v>14900</v>
       </c>
       <c r="Q645" t="n">
-        <v>1594300</v>
+        <v>1579400</v>
       </c>
     </row>
     <row r="646">
@@ -28965,22 +28965,22 @@
         <v>0</v>
       </c>
       <c r="L669" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M669" t="n">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="N669" t="n">
-        <v>1560.999261745</v>
+        <v>1560.9993877551</v>
       </c>
       <c r="O669" t="n">
-        <v>732108.653758405</v>
+        <v>694644.7275510195</v>
       </c>
       <c r="P669" t="n">
         <v>2900</v>
       </c>
       <c r="Q669" t="n">
-        <v>1360100</v>
+        <v>1290500</v>
       </c>
     </row>
     <row r="670">
@@ -29267,22 +29267,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M676" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N676" t="n">
         <v>10307</v>
       </c>
       <c r="O676" t="n">
-        <v>453508</v>
+        <v>443201</v>
       </c>
       <c r="P676" t="n">
         <v>13500</v>
       </c>
       <c r="Q676" t="n">
-        <v>594000</v>
+        <v>580500</v>
       </c>
     </row>
     <row r="677">
@@ -29682,22 +29682,22 @@
         <v>0</v>
       </c>
       <c r="L686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M686" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N686" t="n">
         <v>8968.24</v>
       </c>
       <c r="O686" t="n">
-        <v>475316.72</v>
+        <v>466348.48</v>
       </c>
       <c r="P686" t="n">
         <v>18600</v>
       </c>
       <c r="Q686" t="n">
-        <v>985800</v>
+        <v>967200</v>
       </c>
     </row>
     <row r="687">
@@ -29933,22 +29933,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M692" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N692" t="n">
         <v>31416</v>
       </c>
       <c r="O692" t="n">
-        <v>1288056</v>
+        <v>1256640</v>
       </c>
       <c r="P692" t="n">
         <v>26400</v>
       </c>
       <c r="Q692" t="n">
-        <v>1082400</v>
+        <v>1056000</v>
       </c>
     </row>
     <row r="693">
@@ -31351,22 +31351,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M725" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N725" t="n">
         <v>10911.29</v>
       </c>
       <c r="O725" t="n">
-        <v>294604.83</v>
+        <v>250959.67</v>
       </c>
       <c r="P725" t="n">
         <v>17400</v>
       </c>
       <c r="Q725" t="n">
-        <v>469800</v>
+        <v>400200</v>
       </c>
     </row>
     <row r="726">
@@ -31535,22 +31535,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M729" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N729" t="n">
         <v>3254.49</v>
       </c>
       <c r="O729" t="n">
-        <v>263613.69</v>
+        <v>257104.71</v>
       </c>
       <c r="P729" t="n">
         <v>5200</v>
       </c>
       <c r="Q729" t="n">
-        <v>421200</v>
+        <v>410800</v>
       </c>
     </row>
     <row r="730">
@@ -31581,22 +31581,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M730" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N730" t="n">
-        <v>5218.1705134189</v>
+        <v>5218.1705164319</v>
       </c>
       <c r="O730" t="n">
-        <v>5218.1705134189</v>
+        <v>0</v>
       </c>
       <c r="P730" t="n">
         <v>8500</v>
       </c>
       <c r="Q730" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="731">
@@ -31768,22 +31768,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M734" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N734" t="n">
         <v>3965.02</v>
       </c>
       <c r="O734" t="n">
-        <v>83265.42</v>
+        <v>75335.38</v>
       </c>
       <c r="P734" t="n">
         <v>6500</v>
       </c>
       <c r="Q734" t="n">
-        <v>136500</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="735">
@@ -31814,22 +31814,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M735" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N735" t="n">
         <v>5791.05</v>
       </c>
       <c r="O735" t="n">
-        <v>150567.3</v>
+        <v>138985.2</v>
       </c>
       <c r="P735" t="n">
         <v>9300</v>
       </c>
       <c r="Q735" t="n">
-        <v>241800</v>
+        <v>223200</v>
       </c>
     </row>
     <row r="736">
@@ -31958,10 +31958,10 @@
         <v>77</v>
       </c>
       <c r="N738" t="n">
-        <v>1664.359264432</v>
+        <v>1664.3592041199</v>
       </c>
       <c r="O738" t="n">
-        <v>128155.663361264</v>
+        <v>128155.6587172323</v>
       </c>
       <c r="P738" t="n">
         <v>2900</v>
@@ -32732,22 +32732,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M755" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N755" t="n">
         <v>3646</v>
       </c>
       <c r="O755" t="n">
-        <v>933376</v>
+        <v>918792</v>
       </c>
       <c r="P755" t="n">
         <v>6900</v>
       </c>
       <c r="Q755" t="n">
-        <v>1766400</v>
+        <v>1738800</v>
       </c>
     </row>
     <row r="756">
@@ -32784,10 +32784,10 @@
         <v>19</v>
       </c>
       <c r="N756" t="n">
-        <v>23521.62469697</v>
+        <v>23521.62453125</v>
       </c>
       <c r="O756" t="n">
-        <v>446910.86924243</v>
+        <v>446910.86609375</v>
       </c>
       <c r="P756" t="n">
         <v>39000</v>
@@ -32913,25 +32913,25 @@
         <v>1241</v>
       </c>
       <c r="K759" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L759" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M759" t="n">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="N759" t="n">
-        <v>1778.4725650066</v>
+        <v>1778.4725680247</v>
       </c>
       <c r="O759" t="n">
-        <v>2207084.453173191</v>
+        <v>2192856.676374455</v>
       </c>
       <c r="P759" t="n">
         <v>4900</v>
       </c>
       <c r="Q759" t="n">
-        <v>6080900</v>
+        <v>6041700</v>
       </c>
     </row>
     <row r="760">
@@ -32962,22 +32962,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M760" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N760" t="n">
         <v>2325</v>
       </c>
       <c r="O760" t="n">
-        <v>771900</v>
+        <v>757950</v>
       </c>
       <c r="P760" t="n">
         <v>4900</v>
       </c>
       <c r="Q760" t="n">
-        <v>1626800</v>
+        <v>1597400</v>
       </c>
     </row>
     <row r="761">
@@ -35316,22 +35316,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M811" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N811" t="n">
         <v>13019</v>
       </c>
       <c r="O811" t="n">
-        <v>898311</v>
+        <v>872273</v>
       </c>
       <c r="P811" t="n">
         <v>20900</v>
       </c>
       <c r="Q811" t="n">
-        <v>1442100</v>
+        <v>1400300</v>
       </c>
     </row>
     <row r="812">
@@ -35414,10 +35414,10 @@
         <v>138</v>
       </c>
       <c r="N813" t="n">
-        <v>2252.2964527845</v>
+        <v>2252.2965479115</v>
       </c>
       <c r="O813" t="n">
-        <v>310816.910484261</v>
+        <v>310816.923611787</v>
       </c>
       <c r="P813" t="n">
         <v>3900</v>
@@ -35825,22 +35825,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M822" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N822" t="n">
         <v>50153.86</v>
       </c>
       <c r="O822" t="n">
-        <v>2959077.74</v>
+        <v>2808616.16</v>
       </c>
       <c r="P822" t="n">
         <v>11500</v>
       </c>
       <c r="Q822" t="n">
-        <v>678500</v>
+        <v>644000</v>
       </c>
     </row>
     <row r="823">
@@ -36055,22 +36055,22 @@
         <v>0</v>
       </c>
       <c r="L827" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M827" t="n">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N827" t="n">
         <v>4544</v>
       </c>
       <c r="O827" t="n">
-        <v>1222336</v>
+        <v>1204160</v>
       </c>
       <c r="P827" t="n">
         <v>7900</v>
       </c>
       <c r="Q827" t="n">
-        <v>2125100</v>
+        <v>2093500</v>
       </c>
     </row>
     <row r="828">
@@ -36383,10 +36383,10 @@
         <v>15</v>
       </c>
       <c r="N834" t="n">
-        <v>4907.821941896</v>
+        <v>4907.8219448698</v>
       </c>
       <c r="O834" t="n">
-        <v>73617.32912844</v>
+        <v>73617.32917304701</v>
       </c>
       <c r="P834" t="n">
         <v>8200</v>
@@ -36659,10 +36659,10 @@
         <v>20</v>
       </c>
       <c r="N840" t="n">
-        <v>3903.7361658031</v>
+        <v>3903.7362017804</v>
       </c>
       <c r="O840" t="n">
-        <v>78074.72331606199</v>
+        <v>78074.724035608</v>
       </c>
       <c r="P840" t="n">
         <v>7500</v>
@@ -38483,22 +38483,22 @@
         <v>0</v>
       </c>
       <c r="L880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M880" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N880" t="n">
         <v>10219</v>
       </c>
       <c r="O880" t="n">
-        <v>909491</v>
+        <v>899272</v>
       </c>
       <c r="P880" t="n">
         <v>16900</v>
       </c>
       <c r="Q880" t="n">
-        <v>1504100</v>
+        <v>1487200</v>
       </c>
     </row>
     <row r="881">
@@ -38716,22 +38716,22 @@
         <v>0</v>
       </c>
       <c r="L885" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M885" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N885" t="n">
         <v>5215</v>
       </c>
       <c r="O885" t="n">
-        <v>114730</v>
+        <v>99085</v>
       </c>
       <c r="P885" t="n">
         <v>8900</v>
       </c>
       <c r="Q885" t="n">
-        <v>195800</v>
+        <v>169100</v>
       </c>
     </row>
     <row r="886">
@@ -39498,22 +39498,22 @@
         <v>0</v>
       </c>
       <c r="L902" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M902" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N902" t="n">
         <v>7253</v>
       </c>
       <c r="O902" t="n">
-        <v>841348</v>
+        <v>819589</v>
       </c>
       <c r="P902" t="n">
         <v>11900</v>
       </c>
       <c r="Q902" t="n">
-        <v>1380400</v>
+        <v>1344700</v>
       </c>
     </row>
     <row r="903">
@@ -39737,10 +39737,10 @@
         <v>1326</v>
       </c>
       <c r="N907" t="n">
-        <v>1516.0388115466</v>
+        <v>1516.0388110875</v>
       </c>
       <c r="O907" t="n">
-        <v>2010267.464110792</v>
+        <v>2010267.463502025</v>
       </c>
       <c r="P907" t="n">
         <v>2300</v>
@@ -39821,22 +39821,22 @@
         <v>0</v>
       </c>
       <c r="L909" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M909" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="N909" t="n">
-        <v>2458.5134059343</v>
+        <v>2458.5133829585</v>
       </c>
       <c r="O909" t="n">
-        <v>747388.0754040272</v>
+        <v>740012.5282705085</v>
       </c>
       <c r="P909" t="n">
         <v>3500</v>
       </c>
       <c r="Q909" t="n">
-        <v>1064000</v>
+        <v>1053500</v>
       </c>
     </row>
     <row r="910">
@@ -39867,22 +39867,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M910" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N910" t="n">
-        <v>1907.3942832168</v>
+        <v>1907.3941918295</v>
       </c>
       <c r="O910" t="n">
-        <v>68666.1941958048</v>
+        <v>59129.2199467145</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
       </c>
       <c r="Q910" t="n">
-        <v>90000</v>
+        <v>77500</v>
       </c>
     </row>
     <row r="911">
@@ -39965,10 +39965,10 @@
         <v>370</v>
       </c>
       <c r="N912" t="n">
-        <v>2079.3842021449</v>
+        <v>2079.3841889251</v>
       </c>
       <c r="O912" t="n">
-        <v>769372.154793613</v>
+        <v>769372.1499022869</v>
       </c>
       <c r="P912" t="n">
         <v>2900</v>
@@ -40011,10 +40011,10 @@
         <v>317</v>
       </c>
       <c r="N913" t="n">
-        <v>1803.0151441578</v>
+        <v>1803.0151566778</v>
       </c>
       <c r="O913" t="n">
-        <v>571555.8006980226</v>
+        <v>571555.8046668626</v>
       </c>
       <c r="P913" t="n">
         <v>2500</v>
@@ -40057,10 +40057,10 @@
         <v>99</v>
       </c>
       <c r="N914" t="n">
-        <v>3306.5953548387</v>
+        <v>3306.5953488372</v>
       </c>
       <c r="O914" t="n">
-        <v>327352.9401290313</v>
+        <v>327352.9395348828</v>
       </c>
       <c r="P914" t="n">
         <v>4900</v>
@@ -40103,10 +40103,10 @@
         <v>2</v>
       </c>
       <c r="N915" t="n">
-        <v>2122.1640091884</v>
+        <v>2122.1640073529</v>
       </c>
       <c r="O915" t="n">
-        <v>4244.3280183768</v>
+        <v>4244.3280147058</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
@@ -40149,10 +40149,10 @@
         <v>133</v>
       </c>
       <c r="N916" t="n">
-        <v>2108.7899828473</v>
+        <v>2108.7899885584</v>
       </c>
       <c r="O916" t="n">
-        <v>280469.0677186909</v>
+        <v>280469.0684782672</v>
       </c>
       <c r="P916" t="n">
         <v>2900</v>
@@ -40195,10 +40195,10 @@
         <v>393</v>
       </c>
       <c r="N917" t="n">
-        <v>2056.0838571429</v>
+        <v>2056.0838222089</v>
       </c>
       <c r="O917" t="n">
-        <v>808040.9558571597</v>
+        <v>808040.9421280978</v>
       </c>
       <c r="P917" t="n">
         <v>2900</v>
@@ -40241,10 +40241,10 @@
         <v>178</v>
       </c>
       <c r="N918" t="n">
-        <v>3224.5682755432</v>
+        <v>3224.568287037</v>
       </c>
       <c r="O918" t="n">
-        <v>573973.1530466896</v>
+        <v>573973.1550925861</v>
       </c>
       <c r="P918" t="n">
         <v>4500</v>
@@ -40287,10 +40287,10 @@
         <v>237</v>
       </c>
       <c r="N919" t="n">
-        <v>1655.9310860458</v>
+        <v>1655.931057226</v>
       </c>
       <c r="O919" t="n">
-        <v>392455.6673928546</v>
+        <v>392455.660562562</v>
       </c>
       <c r="P919" t="n">
         <v>2500</v>
@@ -40514,22 +40514,22 @@
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M924" t="n">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="N924" t="n">
-        <v>1592.2754925187</v>
+        <v>1592.2755269762</v>
       </c>
       <c r="O924" t="n">
-        <v>890082.0003179533</v>
+        <v>886897.4685257433</v>
       </c>
       <c r="P924" t="n">
         <v>2500</v>
       </c>
       <c r="Q924" t="n">
-        <v>1397500</v>
+        <v>1392500</v>
       </c>
     </row>
     <row r="925">
@@ -40645,22 +40645,22 @@
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M927" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N927" t="n">
-        <v>2311.9248916968</v>
+        <v>2311.9247818182</v>
       </c>
       <c r="O927" t="n">
-        <v>508623.476173296</v>
+        <v>503999.6024363675</v>
       </c>
       <c r="P927" t="n">
         <v>3500</v>
       </c>
       <c r="Q927" t="n">
-        <v>770000</v>
+        <v>763000</v>
       </c>
     </row>
     <row r="928">
@@ -40697,10 +40697,10 @@
         <v>167</v>
       </c>
       <c r="N928" t="n">
-        <v>1906.1862686567</v>
+        <v>1906.18625</v>
       </c>
       <c r="O928" t="n">
-        <v>318333.1068656689</v>
+        <v>318333.10375</v>
       </c>
       <c r="P928" t="n">
         <v>2900</v>
@@ -40743,10 +40743,10 @@
         <v>257</v>
       </c>
       <c r="N929" t="n">
-        <v>3033.7296483516</v>
+        <v>3033.7290022676</v>
       </c>
       <c r="O929" t="n">
-        <v>779668.5196263612</v>
+        <v>779668.3535827732</v>
       </c>
       <c r="P929" t="n">
         <v>4500</v>
@@ -40789,10 +40789,10 @@
         <v>233</v>
       </c>
       <c r="N930" t="n">
-        <v>1668.6186615679</v>
+        <v>1668.6190998043</v>
       </c>
       <c r="O930" t="n">
-        <v>388788.1481453207</v>
+        <v>388788.2502544019</v>
       </c>
       <c r="P930" t="n">
         <v>2500</v>
@@ -40835,10 +40835,10 @@
         <v>182</v>
       </c>
       <c r="N931" t="n">
-        <v>2546.9851286449</v>
+        <v>2546.9850949914</v>
       </c>
       <c r="O931" t="n">
-        <v>463551.2934133718</v>
+        <v>463551.2872884347</v>
       </c>
       <c r="P931" t="n">
         <v>3900</v>
@@ -40881,10 +40881,10 @@
         <v>1110</v>
       </c>
       <c r="N932" t="n">
-        <v>1259.2744276316</v>
+        <v>1259.2744422442</v>
       </c>
       <c r="O932" t="n">
-        <v>1397794.614671076</v>
+        <v>1397794.630891062</v>
       </c>
       <c r="P932" t="n">
         <v>1900</v>
@@ -41754,22 +41754,22 @@
         <v>0</v>
       </c>
       <c r="L951" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M951" t="n">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="N951" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O951" t="n">
-        <v>3506588.959999999</v>
+        <v>3435025.92</v>
       </c>
       <c r="P951" t="n">
         <v>14900</v>
       </c>
       <c r="Q951" t="n">
-        <v>5840800</v>
+        <v>5721600</v>
       </c>
     </row>
     <row r="952">
@@ -42582,22 +42582,22 @@
         <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M969" t="n">
-        <v>4300</v>
+        <v>4299</v>
       </c>
       <c r="N969" t="n">
-        <v>345.55838640256</v>
+        <v>345.55838633169</v>
       </c>
       <c r="O969" t="n">
-        <v>1485901.061531008</v>
+        <v>1485555.502839935</v>
       </c>
       <c r="P969" t="n">
         <v>600</v>
       </c>
       <c r="Q969" t="n">
-        <v>2580000</v>
+        <v>2579400</v>
       </c>
     </row>
     <row r="970">
@@ -42676,10 +42676,10 @@
         <v>351</v>
       </c>
       <c r="N971" t="n">
-        <v>2286.1648643761</v>
+        <v>2286.164845735</v>
       </c>
       <c r="O971" t="n">
-        <v>802443.8673960111</v>
+        <v>802443.8608529851</v>
       </c>
       <c r="P971" t="n">
         <v>3000</v>
@@ -42883,22 +42883,22 @@
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M976" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N976" t="n">
         <v>1326</v>
       </c>
       <c r="O976" t="n">
-        <v>25194</v>
+        <v>13260</v>
       </c>
       <c r="P976" t="n">
         <v>2900</v>
       </c>
       <c r="Q976" t="n">
-        <v>55100</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="977">
@@ -42927,22 +42927,22 @@
         <v>0</v>
       </c>
       <c r="L977" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M977" t="n">
-        <v>2669</v>
+        <v>2629</v>
       </c>
       <c r="N977" t="n">
         <v>177.65</v>
       </c>
       <c r="O977" t="n">
-        <v>474147.85</v>
+        <v>467041.85</v>
       </c>
       <c r="P977" t="n">
         <v>300</v>
       </c>
       <c r="Q977" t="n">
-        <v>800700</v>
+        <v>788700</v>
       </c>
     </row>
     <row r="978">
@@ -43196,10 +43196,10 @@
         <v>2026</v>
       </c>
       <c r="N983" t="n">
-        <v>517.28807221513</v>
+        <v>517.28815469086</v>
       </c>
       <c r="O983" t="n">
-        <v>1048025.634307853</v>
+        <v>1048025.801403682</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
@@ -43375,22 +43375,22 @@
         <v>0</v>
       </c>
       <c r="L987" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M987" t="n">
-        <v>1708</v>
+        <v>1670</v>
       </c>
       <c r="N987" t="n">
-        <v>3110.8429525518</v>
+        <v>3110.8427709611</v>
       </c>
       <c r="O987" t="n">
-        <v>5313319.762958474</v>
+        <v>5195107.427505037</v>
       </c>
       <c r="P987" t="n">
         <v>4500</v>
       </c>
       <c r="Q987" t="n">
-        <v>7686000</v>
+        <v>7515000</v>
       </c>
     </row>
     <row r="988">
@@ -43507,22 +43507,22 @@
         <v>0</v>
       </c>
       <c r="L990" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M990" t="n">
-        <v>14846</v>
+        <v>14774</v>
       </c>
       <c r="N990" t="n">
-        <v>703.79534416571</v>
+        <v>703.79533220158</v>
       </c>
       <c r="O990" t="n">
-        <v>10448545.67948413</v>
+        <v>10397872.23794614</v>
       </c>
       <c r="P990" t="n">
         <v>900</v>
       </c>
       <c r="Q990" t="n">
-        <v>13361400</v>
+        <v>13296600</v>
       </c>
     </row>
     <row r="991">
@@ -43952,22 +43952,22 @@
         <v>0</v>
       </c>
       <c r="L1000" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1000" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N1000" t="n">
         <v>2525.02</v>
       </c>
       <c r="O1000" t="n">
-        <v>30300.24</v>
+        <v>27775.22</v>
       </c>
       <c r="P1000" t="n">
         <v>3000</v>
       </c>
       <c r="Q1000" t="n">
-        <v>36000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="1001">
@@ -43999,10 +43999,10 @@
         <v>429</v>
       </c>
       <c r="N1001" t="n">
-        <v>2077.4945520231</v>
+        <v>2077.4945652174</v>
       </c>
       <c r="O1001" t="n">
-        <v>891245.1628179098</v>
+        <v>891245.1684782647</v>
       </c>
       <c r="P1001" t="n">
         <v>2900</v>
@@ -44256,10 +44256,10 @@
         <v>81</v>
       </c>
       <c r="N1007" t="n">
-        <v>1595.5190882035</v>
+        <v>1595.5155551576</v>
       </c>
       <c r="O1007" t="n">
-        <v>129237.0461444835</v>
+        <v>129236.7599677656</v>
       </c>
       <c r="P1007" t="n">
         <v>2500</v>
@@ -44685,22 +44685,22 @@
         <v>0</v>
       </c>
       <c r="L1016" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1016" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N1016" t="n">
-        <v>2098.4049008499</v>
+        <v>2098.4049147727</v>
       </c>
       <c r="O1016" t="n">
-        <v>44066.5029178479</v>
+        <v>41968.098295454</v>
       </c>
       <c r="P1016" t="n">
         <v>9500</v>
       </c>
       <c r="Q1016" t="n">
-        <v>199500</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="1017">
@@ -45010,10 +45010,10 @@
         <v>7</v>
       </c>
       <c r="N1023" t="n">
-        <v>11866.994561404</v>
+        <v>11866.994642857</v>
       </c>
       <c r="O1023" t="n">
-        <v>83068.961929828</v>
+        <v>83068.962499999</v>
       </c>
       <c r="P1023" t="n">
         <v>55000</v>
@@ -45758,22 +45758,22 @@
         <v>0</v>
       </c>
       <c r="L1039" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1039" t="n">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N1039" t="n">
-        <v>3414.5660805577</v>
+        <v>3414.5660775194</v>
       </c>
       <c r="O1039" t="n">
-        <v>2830675.280782333</v>
+        <v>2827260.712186063</v>
       </c>
       <c r="P1039" t="n">
         <v>3500</v>
       </c>
       <c r="Q1039" t="n">
-        <v>2901500</v>
+        <v>2898000</v>
       </c>
     </row>
     <row r="1040">
@@ -47740,10 +47740,10 @@
         <v>41</v>
       </c>
       <c r="N1081" t="n">
-        <v>7046.9398299681</v>
+        <v>7046.939829932</v>
       </c>
       <c r="O1081" t="n">
-        <v>288924.5330286921</v>
+        <v>288924.533027212</v>
       </c>
       <c r="P1081" t="n">
         <v>9900</v>
@@ -47835,10 +47835,10 @@
         <v>6</v>
       </c>
       <c r="N1083" t="n">
-        <v>8931.440833333299</v>
+        <v>8931.4408695652</v>
       </c>
       <c r="O1083" t="n">
-        <v>53588.6449999998</v>
+        <v>53588.6452173912</v>
       </c>
       <c r="P1083" t="n">
         <v>19900</v>
@@ -48020,10 +48020,10 @@
         <v>16</v>
       </c>
       <c r="N1087" t="n">
-        <v>665.32342381786</v>
+        <v>665.32343283582</v>
       </c>
       <c r="O1087" t="n">
-        <v>10645.17478108576</v>
+        <v>10645.17492537312</v>
       </c>
       <c r="P1087" t="n">
         <v>2900</v>
@@ -48781,22 +48781,22 @@
         <v>0</v>
       </c>
       <c r="L1104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1104" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N1104" t="n">
         <v>2459</v>
       </c>
       <c r="O1104" t="n">
-        <v>213933</v>
+        <v>211474</v>
       </c>
       <c r="P1104" t="n">
         <v>3900</v>
       </c>
       <c r="Q1104" t="n">
-        <v>339300</v>
+        <v>335400</v>
       </c>
     </row>
     <row r="1105">
@@ -49077,22 +49077,22 @@
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1111" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N1111" t="n">
-        <v>5577.2680778032</v>
+        <v>5577.2680733945</v>
       </c>
       <c r="O1111" t="n">
-        <v>741776.6543478256</v>
+        <v>736199.3856880739</v>
       </c>
       <c r="P1111" t="n">
         <v>6500</v>
       </c>
       <c r="Q1111" t="n">
-        <v>864500</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="1112">
@@ -49637,22 +49637,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1124" t="n">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="N1124" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1124" t="n">
-        <v>2040172.38</v>
+        <v>2036642.67</v>
       </c>
       <c r="P1124" t="n">
         <v>1900</v>
       </c>
       <c r="Q1124" t="n">
-        <v>3294600</v>
+        <v>3288900</v>
       </c>
     </row>
     <row r="1125">
@@ -49725,22 +49725,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1126" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="N1126" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1126" t="n">
-        <v>474103.1</v>
+        <v>445466</v>
       </c>
       <c r="P1126" t="n">
         <v>5100</v>
       </c>
       <c r="Q1126" t="n">
-        <v>759900</v>
+        <v>714000</v>
       </c>
     </row>
     <row r="1127">
@@ -50250,10 +50250,10 @@
         <v>1971</v>
       </c>
       <c r="N1138" t="n">
-        <v>2523.3377476715</v>
+        <v>2523.3377470356</v>
       </c>
       <c r="O1138" t="n">
-        <v>4973498.700660527</v>
+        <v>4973498.699407168</v>
       </c>
       <c r="P1138" t="n">
         <v>2800</v>
@@ -53235,22 +53235,22 @@
         <v>0</v>
       </c>
       <c r="L1204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1204" t="n">
         <v>9973.190000000001</v>
       </c>
       <c r="O1204" t="n">
-        <v>29919.57</v>
+        <v>19946.38</v>
       </c>
       <c r="P1204" t="n">
         <v>21500</v>
       </c>
       <c r="Q1204" t="n">
-        <v>64500</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="1205">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -991,22 +991,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M14" t="n">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O14" t="n">
-        <v>561504.389709633</v>
+        <v>398487.051602398</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>806000</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="15">
@@ -1158,10 +1158,10 @@
         <v>1145</v>
       </c>
       <c r="N18" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O18" t="n">
-        <v>3866374.740948525</v>
+        <v>3866374.739861805</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -1681,22 +1681,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
         <v>13386</v>
       </c>
       <c r="O31" t="n">
-        <v>66930</v>
+        <v>53544</v>
       </c>
       <c r="P31" t="n">
         <v>23900</v>
       </c>
       <c r="Q31" t="n">
-        <v>119500</v>
+        <v>95600</v>
       </c>
     </row>
     <row r="32">
@@ -3203,10 +3203,10 @@
         <v>94</v>
       </c>
       <c r="N68" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O68" t="n">
-        <v>226822.0997876834</v>
+        <v>226822.0998937342</v>
       </c>
       <c r="P68" t="n">
         <v>4700</v>
@@ -3236,22 +3236,22 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N69" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O69" t="n">
-        <v>732512.4444891096</v>
+        <v>725088.3204215901</v>
       </c>
       <c r="P69" t="n">
         <v>4500</v>
       </c>
       <c r="Q69" t="n">
-        <v>1332000</v>
+        <v>1318500</v>
       </c>
     </row>
     <row r="70">
@@ -3671,10 +3671,10 @@
         <v>76</v>
       </c>
       <c r="N80" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O80" t="n">
-        <v>1129179.362123916</v>
+        <v>1129179.3632</v>
       </c>
       <c r="P80" t="n">
         <v>34900</v>
@@ -4131,22 +4131,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O91" t="n">
-        <v>66480.6793386776</v>
+        <v>62570.0510843376</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
       </c>
       <c r="Q91" t="n">
-        <v>154700</v>
+        <v>145600</v>
       </c>
     </row>
     <row r="92">
@@ -4597,10 +4597,10 @@
         <v>6</v>
       </c>
       <c r="N101" t="n">
-        <v>28751.742258065</v>
+        <v>28751.742333333</v>
       </c>
       <c r="O101" t="n">
-        <v>172510.45354839</v>
+        <v>172510.453999998</v>
       </c>
       <c r="P101" t="n">
         <v>34800</v>
@@ -5092,10 +5092,10 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>18835.024666667</v>
+        <v>18835.026428571</v>
       </c>
       <c r="O112" t="n">
-        <v>18835.024666667</v>
+        <v>18835.026428571</v>
       </c>
       <c r="P112" t="n">
         <v>40500</v>
@@ -5423,22 +5423,22 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N120" t="n">
-        <v>7407.7300524934</v>
+        <v>7407.7300526316</v>
       </c>
       <c r="O120" t="n">
-        <v>1096344.047769023</v>
+        <v>1088936.317736845</v>
       </c>
       <c r="P120" t="n">
         <v>10900</v>
       </c>
       <c r="Q120" t="n">
-        <v>1613200</v>
+        <v>1602300</v>
       </c>
     </row>
     <row r="121">
@@ -5702,10 +5702,10 @@
         <v>30</v>
       </c>
       <c r="N127" t="n">
-        <v>14708.815744681</v>
+        <v>14708.815698925</v>
       </c>
       <c r="O127" t="n">
-        <v>441264.47234043</v>
+        <v>441264.47096775</v>
       </c>
       <c r="P127" t="n">
         <v>16900</v>
@@ -6557,10 +6557,10 @@
         <v>2</v>
       </c>
       <c r="N147" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O147" t="n">
-        <v>400144.4</v>
+        <v>400144.40015624</v>
       </c>
       <c r="P147" t="n">
         <v>312000</v>
@@ -7090,22 +7090,22 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N160" t="n">
         <v>20961.76</v>
       </c>
       <c r="O160" t="n">
-        <v>1299629.12</v>
+        <v>1278667.36</v>
       </c>
       <c r="P160" t="n">
         <v>38300</v>
       </c>
       <c r="Q160" t="n">
-        <v>2374600</v>
+        <v>2336300</v>
       </c>
     </row>
     <row r="161">
@@ -7207,22 +7207,22 @@
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N163" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O163" t="n">
-        <v>5180017.415555556</v>
+        <v>5118350.542440315</v>
       </c>
       <c r="P163" t="n">
         <v>98900</v>
       </c>
       <c r="Q163" t="n">
-        <v>8307600</v>
+        <v>8208700</v>
       </c>
     </row>
     <row r="164">
@@ -8295,22 +8295,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N188" t="n">
         <v>3114.49</v>
       </c>
       <c r="O188" t="n">
-        <v>183754.91</v>
+        <v>180640.42</v>
       </c>
       <c r="P188" t="n">
         <v>5500</v>
       </c>
       <c r="Q188" t="n">
-        <v>324500</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="189">
@@ -9484,22 +9484,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N216" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O216" t="n">
-        <v>37364.34103448252</v>
+        <v>36631.7076124565</v>
       </c>
       <c r="P216" t="n">
         <v>6200</v>
       </c>
       <c r="Q216" t="n">
-        <v>316200</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="217">
@@ -9878,22 +9878,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M225" t="n">
-        <v>9292</v>
+        <v>9267</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>16040965.44</v>
+        <v>15997807.44</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>13938000</v>
+        <v>13900500</v>
       </c>
     </row>
     <row r="226">
@@ -9919,22 +9919,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M226" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N226" t="n">
         <v>2088.01</v>
       </c>
       <c r="O226" t="n">
-        <v>338257.6200000001</v>
+        <v>329905.58</v>
       </c>
       <c r="P226" t="n">
         <v>3500</v>
       </c>
       <c r="Q226" t="n">
-        <v>567000</v>
+        <v>553000</v>
       </c>
     </row>
     <row r="227">
@@ -9971,10 +9971,10 @@
         <v>218</v>
       </c>
       <c r="N227" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O227" t="n">
-        <v>1076333.61513554</v>
+        <v>1076333.615161286</v>
       </c>
       <c r="P227" t="n">
         <v>7500</v>
@@ -10429,22 +10429,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M238" t="n">
-        <v>1167</v>
+        <v>1117</v>
       </c>
       <c r="N238" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O238" t="n">
-        <v>1281430.878169292</v>
+        <v>1226528.499155847</v>
       </c>
       <c r="P238" t="n">
         <v>1500</v>
       </c>
       <c r="Q238" t="n">
-        <v>1750500</v>
+        <v>1675500</v>
       </c>
     </row>
     <row r="239">
@@ -11011,22 +11011,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N252" t="n">
         <v>2331</v>
       </c>
       <c r="O252" t="n">
-        <v>832167</v>
+        <v>829836</v>
       </c>
       <c r="P252" t="n">
         <v>3500</v>
       </c>
       <c r="Q252" t="n">
-        <v>1249500</v>
+        <v>1246000</v>
       </c>
     </row>
     <row r="253">
@@ -11262,22 +11262,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M258" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N258" t="n">
         <v>3395</v>
       </c>
       <c r="O258" t="n">
-        <v>468510</v>
+        <v>454930</v>
       </c>
       <c r="P258" t="n">
         <v>5500</v>
       </c>
       <c r="Q258" t="n">
-        <v>759000</v>
+        <v>737000</v>
       </c>
     </row>
     <row r="259">
@@ -12176,22 +12176,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M279" t="n">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="N279" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O279" t="n">
-        <v>2799165.516155434</v>
+        <v>2757849.396819001</v>
       </c>
       <c r="P279" t="n">
         <v>4500</v>
       </c>
       <c r="Q279" t="n">
-        <v>4878000</v>
+        <v>4806000</v>
       </c>
     </row>
     <row r="280">
@@ -12228,10 +12228,10 @@
         <v>1434</v>
       </c>
       <c r="N280" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O280" t="n">
-        <v>7481028.814470787</v>
+        <v>7481028.809298206</v>
       </c>
       <c r="P280" t="n">
         <v>8500</v>
@@ -12355,22 +12355,22 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M283" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N283" t="n">
-        <v>2033.5670707071</v>
+        <v>2033.5662758621</v>
       </c>
       <c r="O283" t="n">
-        <v>284699.389898994</v>
+        <v>278598.5797931077</v>
       </c>
       <c r="P283" t="n">
         <v>4100</v>
       </c>
       <c r="Q283" t="n">
-        <v>574000</v>
+        <v>561700</v>
       </c>
     </row>
     <row r="284">
@@ -12653,10 +12653,10 @@
         <v>2836</v>
       </c>
       <c r="N290" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O290" t="n">
-        <v>8958529.270713244</v>
+        <v>8958529.272612229</v>
       </c>
       <c r="P290" t="n">
         <v>5600</v>
@@ -12693,22 +12693,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N291" t="n">
         <v>1903</v>
       </c>
       <c r="O291" t="n">
-        <v>19030</v>
+        <v>17127</v>
       </c>
       <c r="P291" t="n">
         <v>3200</v>
       </c>
       <c r="Q291" t="n">
-        <v>32000</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="292">
@@ -12921,22 +12921,22 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N296" t="n">
-        <v>3230.0677414075</v>
+        <v>3230.0677302632</v>
       </c>
       <c r="O296" t="n">
-        <v>297166.23220949</v>
+        <v>293936.1634539512</v>
       </c>
       <c r="P296" t="n">
         <v>6200</v>
       </c>
       <c r="Q296" t="n">
-        <v>570400</v>
+        <v>564200</v>
       </c>
     </row>
     <row r="297">
@@ -13147,10 +13147,10 @@
         <v>34</v>
       </c>
       <c r="N301" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O301" t="n">
-        <v>91623.9975214046</v>
+        <v>91623.99580381639</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -13274,22 +13274,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N304" t="n">
         <v>7507.39</v>
       </c>
       <c r="O304" t="n">
-        <v>2184650.49</v>
+        <v>2177143.1</v>
       </c>
       <c r="P304" t="n">
         <v>13500</v>
       </c>
       <c r="Q304" t="n">
-        <v>3928500</v>
+        <v>3915000</v>
       </c>
     </row>
     <row r="305">
@@ -13502,10 +13502,10 @@
         <v>196</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M309" t="n">
         <v>196</v>
@@ -13598,10 +13598,10 @@
         <v>468</v>
       </c>
       <c r="N311" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O311" t="n">
-        <v>1776392.283305063</v>
+        <v>1776392.283307403</v>
       </c>
       <c r="P311" t="n">
         <v>6200</v>
@@ -13761,22 +13761,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M315" t="n">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N315" t="n">
         <v>2612.77</v>
       </c>
       <c r="O315" t="n">
-        <v>1447474.58</v>
+        <v>1434410.73</v>
       </c>
       <c r="P315" t="n">
         <v>4900</v>
       </c>
       <c r="Q315" t="n">
-        <v>2714600</v>
+        <v>2690100</v>
       </c>
     </row>
     <row r="316">
@@ -13848,22 +13848,22 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M317" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N317" t="n">
         <v>4357.55</v>
       </c>
       <c r="O317" t="n">
-        <v>1668941.65</v>
+        <v>1660226.55</v>
       </c>
       <c r="P317" t="n">
         <v>7500</v>
       </c>
       <c r="Q317" t="n">
-        <v>2872500</v>
+        <v>2857500</v>
       </c>
     </row>
     <row r="318">
@@ -13987,10 +13987,10 @@
         <v>331</v>
       </c>
       <c r="N320" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O320" t="n">
-        <v>1618897.845368529</v>
+        <v>1618897.84542225</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14076,22 +14076,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M322" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="N322" t="n">
         <v>1203.38</v>
       </c>
       <c r="O322" t="n">
-        <v>1074618.34</v>
+        <v>1072211.58</v>
       </c>
       <c r="P322" t="n">
         <v>1900</v>
       </c>
       <c r="Q322" t="n">
-        <v>1696700</v>
+        <v>1692900</v>
       </c>
     </row>
     <row r="323">
@@ -14122,22 +14122,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N323" t="n">
         <v>3472</v>
       </c>
       <c r="O323" t="n">
-        <v>534688</v>
+        <v>531216</v>
       </c>
       <c r="P323" t="n">
         <v>4800</v>
       </c>
       <c r="Q323" t="n">
-        <v>739200</v>
+        <v>734400</v>
       </c>
     </row>
     <row r="324">
@@ -14786,10 +14786,10 @@
         <v>366</v>
       </c>
       <c r="N338" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O338" t="n">
-        <v>1315497.014945041</v>
+        <v>1315497.009694002</v>
       </c>
       <c r="P338" t="n">
         <v>6500</v>
@@ -14958,10 +14958,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="O342" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -15096,10 +15096,10 @@
         <v>288</v>
       </c>
       <c r="N345" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O345" t="n">
-        <v>4268845.112416992</v>
+        <v>4268845.11222288</v>
       </c>
       <c r="P345" t="n">
         <v>24900</v>
@@ -15768,22 +15768,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M361" t="n">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="N361" t="n">
         <v>1441.01</v>
       </c>
       <c r="O361" t="n">
-        <v>3923870.23</v>
+        <v>3920988.21</v>
       </c>
       <c r="P361" t="n">
         <v>2100</v>
       </c>
       <c r="Q361" t="n">
-        <v>5718300</v>
+        <v>5714100</v>
       </c>
     </row>
     <row r="362">
@@ -16038,22 +16038,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M367" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="N367" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O367" t="n">
-        <v>477540.6219860814</v>
+        <v>444082.3618622446</v>
       </c>
       <c r="P367" t="n">
         <v>5500</v>
       </c>
       <c r="Q367" t="n">
-        <v>863500</v>
+        <v>803000</v>
       </c>
     </row>
     <row r="368">
@@ -16251,22 +16251,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M372" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N372" t="n">
         <v>4443</v>
       </c>
       <c r="O372" t="n">
-        <v>488730</v>
+        <v>470958</v>
       </c>
       <c r="P372" t="n">
         <v>6300</v>
       </c>
       <c r="Q372" t="n">
-        <v>693000</v>
+        <v>667800</v>
       </c>
     </row>
     <row r="373">
@@ -16297,22 +16297,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M373" t="n">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="N373" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O373" t="n">
-        <v>812209.4006369429</v>
+        <v>789913.4304</v>
       </c>
       <c r="P373" t="n">
         <v>3900</v>
       </c>
       <c r="Q373" t="n">
-        <v>1989000</v>
+        <v>1934400</v>
       </c>
     </row>
     <row r="374">
@@ -17031,22 +17031,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M390" t="n">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="N390" t="n">
         <v>1312.43</v>
       </c>
       <c r="O390" t="n">
-        <v>1363614.77</v>
+        <v>1359677.48</v>
       </c>
       <c r="P390" t="n">
         <v>2300</v>
       </c>
       <c r="Q390" t="n">
-        <v>2389700</v>
+        <v>2382800</v>
       </c>
     </row>
     <row r="391">
@@ -17157,22 +17157,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M393" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N393" t="n">
         <v>1343.77</v>
       </c>
       <c r="O393" t="n">
-        <v>302348.25</v>
+        <v>296973.17</v>
       </c>
       <c r="P393" t="n">
         <v>2500</v>
       </c>
       <c r="Q393" t="n">
-        <v>562500</v>
+        <v>552500</v>
       </c>
     </row>
     <row r="394">
@@ -17289,22 +17289,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M396" t="n">
-        <v>2869</v>
+        <v>2749</v>
       </c>
       <c r="N396" t="n">
         <v>1387.55</v>
       </c>
       <c r="O396" t="n">
-        <v>3980880.95</v>
+        <v>3814374.95</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
       </c>
       <c r="Q396" t="n">
-        <v>6598700</v>
+        <v>6322700</v>
       </c>
     </row>
     <row r="397">
@@ -17465,22 +17465,22 @@
         <v>0</v>
       </c>
       <c r="L400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N400" t="n">
         <v>13304.13</v>
       </c>
       <c r="O400" t="n">
-        <v>1915794.72</v>
+        <v>1902490.59</v>
       </c>
       <c r="P400" t="n">
         <v>20900</v>
       </c>
       <c r="Q400" t="n">
-        <v>3009600</v>
+        <v>2988700</v>
       </c>
     </row>
     <row r="401">
@@ -17514,22 +17514,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N401" t="n">
         <v>16897</v>
       </c>
       <c r="O401" t="n">
-        <v>929335</v>
+        <v>912438</v>
       </c>
       <c r="P401" t="n">
         <v>27900</v>
       </c>
       <c r="Q401" t="n">
-        <v>1534500</v>
+        <v>1506600</v>
       </c>
     </row>
     <row r="402">
@@ -18659,22 +18659,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M427" t="n">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="N427" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O427" t="n">
-        <v>802414.194109674</v>
+        <v>795890.5084712383</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1230000</v>
+        <v>1220000</v>
       </c>
     </row>
     <row r="428">
@@ -18711,10 +18711,10 @@
         <v>14</v>
       </c>
       <c r="N428" t="n">
-        <v>1467.327254902</v>
+        <v>1467.3264227642</v>
       </c>
       <c r="O428" t="n">
-        <v>20542.581568628</v>
+        <v>20542.5699186988</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
@@ -18757,10 +18757,10 @@
         <v>52</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.6026503973</v>
+        <v>1690.6023498845</v>
       </c>
       <c r="O429" t="n">
-        <v>87911.33782065961</v>
+        <v>87911.322193994</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
@@ -18797,22 +18797,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M430" t="n">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="N430" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O430" t="n">
-        <v>1531590.838010033</v>
+        <v>1502137.195071192</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
       </c>
       <c r="Q430" t="n">
-        <v>2470000</v>
+        <v>2422500</v>
       </c>
     </row>
     <row r="431">
@@ -18849,10 +18849,10 @@
         <v>112</v>
       </c>
       <c r="N431" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O431" t="n">
-        <v>176891.7948</v>
+        <v>176891.7846464608</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
@@ -18889,22 +18889,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M432" t="n">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="N432" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O432" t="n">
-        <v>2163159.33517035</v>
+        <v>2139124.309178212</v>
       </c>
       <c r="P432" t="n">
         <v>3500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3150000</v>
+        <v>3115000</v>
       </c>
     </row>
     <row r="433">
@@ -18979,22 +18979,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M434" t="n">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="N434" t="n">
-        <v>2521.5439240506</v>
+        <v>2521.5426705653</v>
       </c>
       <c r="O434" t="n">
-        <v>731247.737974674</v>
+        <v>703510.4050877186</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
       </c>
       <c r="Q434" t="n">
-        <v>1131000</v>
+        <v>1088100</v>
       </c>
     </row>
     <row r="435">
@@ -20256,22 +20256,22 @@
         <v>0</v>
       </c>
       <c r="L463" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M463" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N463" t="n">
-        <v>36029</v>
+        <v>0</v>
       </c>
       <c r="O463" t="n">
-        <v>36029</v>
+        <v>0</v>
       </c>
       <c r="P463" t="n">
         <v>10900</v>
       </c>
       <c r="Q463" t="n">
-        <v>10900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -21821,22 +21821,22 @@
         <v>0</v>
       </c>
       <c r="L500" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M500" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N500" t="n">
         <v>8600</v>
       </c>
       <c r="O500" t="n">
-        <v>154800</v>
+        <v>129000</v>
       </c>
       <c r="P500" t="n">
         <v>14900</v>
       </c>
       <c r="Q500" t="n">
-        <v>268200</v>
+        <v>223500</v>
       </c>
     </row>
     <row r="501">
@@ -22929,22 +22929,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M526" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="N526" t="n">
         <v>1969</v>
       </c>
       <c r="O526" t="n">
-        <v>399707</v>
+        <v>385924</v>
       </c>
       <c r="P526" t="n">
         <v>1500</v>
       </c>
       <c r="Q526" t="n">
-        <v>304500</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="527">
@@ -23514,22 +23514,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M540" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N540" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O540" t="n">
-        <v>499348.9320118638</v>
+        <v>497319.058753706</v>
       </c>
       <c r="P540" t="n">
         <v>3600</v>
       </c>
       <c r="Q540" t="n">
-        <v>885600</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="541">
@@ -24348,10 +24348,10 @@
         <v>617</v>
       </c>
       <c r="N560" t="n">
-        <v>880.3293685687599</v>
+        <v>880.32937295274</v>
       </c>
       <c r="O560" t="n">
-        <v>543163.2204069248</v>
+        <v>543163.2231118405</v>
       </c>
       <c r="P560" t="n">
         <v>1200</v>
@@ -24721,22 +24721,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M569" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N569" t="n">
         <v>5894.64</v>
       </c>
       <c r="O569" t="n">
-        <v>730935.36</v>
+        <v>725040.7200000001</v>
       </c>
       <c r="P569" t="n">
         <v>11000</v>
       </c>
       <c r="Q569" t="n">
-        <v>1364000</v>
+        <v>1353000</v>
       </c>
     </row>
     <row r="570">
@@ -25362,10 +25362,10 @@
         <v>435</v>
       </c>
       <c r="N584" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O584" t="n">
-        <v>434461.1480501751</v>
+        <v>434461.148498908</v>
       </c>
       <c r="P584" t="n">
         <v>1600</v>
@@ -25607,22 +25607,22 @@
         <v>0</v>
       </c>
       <c r="L590" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M590" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="N590" t="n">
         <v>3877.89</v>
       </c>
       <c r="O590" t="n">
-        <v>1163367</v>
+        <v>1050908.19</v>
       </c>
       <c r="P590" t="n">
         <v>6500</v>
       </c>
       <c r="Q590" t="n">
-        <v>1950000</v>
+        <v>1761500</v>
       </c>
     </row>
     <row r="591">
@@ -25703,10 +25703,10 @@
         <v>5</v>
       </c>
       <c r="N592" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O592" t="n">
-        <v>21425.9763759085</v>
+        <v>21425.9764033265</v>
       </c>
       <c r="P592" t="n">
         <v>6900</v>
@@ -25992,22 +25992,22 @@
         <v>0</v>
       </c>
       <c r="L599" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M599" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N599" t="n">
         <v>1106</v>
       </c>
       <c r="O599" t="n">
-        <v>360556</v>
+        <v>353920</v>
       </c>
       <c r="P599" t="n">
         <v>2100</v>
       </c>
       <c r="Q599" t="n">
-        <v>684600</v>
+        <v>672000</v>
       </c>
     </row>
     <row r="600">
@@ -26433,10 +26433,10 @@
         <v>75</v>
       </c>
       <c r="N609" t="n">
-        <v>12005.159831933</v>
+        <v>12005.159831224</v>
       </c>
       <c r="O609" t="n">
-        <v>900386.987394975</v>
+        <v>900386.9873418</v>
       </c>
       <c r="P609" t="n">
         <v>19500</v>
@@ -26842,22 +26842,22 @@
         <v>0</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M619" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N619" t="n">
         <v>1358</v>
       </c>
       <c r="O619" t="n">
-        <v>335426</v>
+        <v>334068</v>
       </c>
       <c r="P619" t="n">
         <v>2400</v>
       </c>
       <c r="Q619" t="n">
-        <v>592800</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="620">
@@ -28965,22 +28965,22 @@
         <v>0</v>
       </c>
       <c r="L669" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M669" t="n">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="N669" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O669" t="n">
-        <v>694644.7275510195</v>
+        <v>675912.7587389816</v>
       </c>
       <c r="P669" t="n">
         <v>2900</v>
       </c>
       <c r="Q669" t="n">
-        <v>1290500</v>
+        <v>1255700</v>
       </c>
     </row>
     <row r="670">
@@ -29396,10 +29396,10 @@
         <v>1</v>
       </c>
       <c r="N679" t="n">
-        <v>1508.5872340426</v>
+        <v>1508.5871111111</v>
       </c>
       <c r="O679" t="n">
-        <v>1508.5872340426</v>
+        <v>1508.5871111111</v>
       </c>
       <c r="P679" t="n">
         <v>3600</v>
@@ -29437,10 +29437,10 @@
         <v>160</v>
       </c>
       <c r="N680" t="n">
-        <v>2568.8355</v>
+        <v>2568.8354697987</v>
       </c>
       <c r="O680" t="n">
-        <v>411013.6800000001</v>
+        <v>411013.675167792</v>
       </c>
       <c r="P680" t="n">
         <v>4500</v>
@@ -31034,22 +31034,22 @@
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M718" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N718" t="n">
         <v>4534.2</v>
       </c>
       <c r="O718" t="n">
-        <v>45342</v>
+        <v>13602.6</v>
       </c>
       <c r="P718" t="n">
         <v>7900</v>
       </c>
       <c r="Q718" t="n">
-        <v>79000</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="719">
@@ -31259,22 +31259,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M723" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N723" t="n">
         <v>4690.64</v>
       </c>
       <c r="O723" t="n">
-        <v>46906.4</v>
+        <v>42215.76</v>
       </c>
       <c r="P723" t="n">
         <v>7500</v>
       </c>
       <c r="Q723" t="n">
-        <v>75000</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="724">
@@ -31305,22 +31305,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M724" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N724" t="n">
         <v>5410.72</v>
       </c>
       <c r="O724" t="n">
-        <v>54107.2</v>
+        <v>16232.16</v>
       </c>
       <c r="P724" t="n">
         <v>8700</v>
       </c>
       <c r="Q724" t="n">
-        <v>87000</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="725">
@@ -31587,10 +31587,10 @@
         <v>25</v>
       </c>
       <c r="N730" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O730" t="n">
-        <v>90266.25062189001</v>
+        <v>90266.25062422</v>
       </c>
       <c r="P730" t="n">
         <v>5800</v>
@@ -31722,22 +31722,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M733" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N733" t="n">
         <v>3965.02</v>
       </c>
       <c r="O733" t="n">
-        <v>75335.38</v>
+        <v>71370.36</v>
       </c>
       <c r="P733" t="n">
         <v>6500</v>
       </c>
       <c r="Q733" t="n">
-        <v>123500</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="734">
@@ -31906,22 +31906,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M737" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N737" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O737" t="n">
-        <v>128155.6587172323</v>
+        <v>124826.9272121775</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
       </c>
       <c r="Q737" t="n">
-        <v>223300</v>
+        <v>217500</v>
       </c>
     </row>
     <row r="738">
@@ -31952,22 +31952,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M738" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N738" t="n">
         <v>15502</v>
       </c>
       <c r="O738" t="n">
-        <v>170522</v>
+        <v>155020</v>
       </c>
       <c r="P738" t="n">
         <v>25900</v>
       </c>
       <c r="Q738" t="n">
-        <v>284900</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="739">
@@ -34764,22 +34764,22 @@
         <v>0</v>
       </c>
       <c r="L799" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M799" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N799" t="n">
         <v>11857</v>
       </c>
       <c r="O799" t="n">
-        <v>59285</v>
+        <v>47428</v>
       </c>
       <c r="P799" t="n">
         <v>19900</v>
       </c>
       <c r="Q799" t="n">
-        <v>99500</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="800">
@@ -35224,22 +35224,22 @@
         <v>0</v>
       </c>
       <c r="L809" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M809" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N809" t="n">
         <v>3764</v>
       </c>
       <c r="O809" t="n">
-        <v>432860</v>
+        <v>429096</v>
       </c>
       <c r="P809" t="n">
         <v>6200</v>
       </c>
       <c r="Q809" t="n">
-        <v>713000</v>
+        <v>706800</v>
       </c>
     </row>
     <row r="810">
@@ -35362,22 +35362,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M812" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N812" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O812" t="n">
-        <v>310816.923611787</v>
+        <v>308564.6281672872</v>
       </c>
       <c r="P812" t="n">
         <v>3900</v>
       </c>
       <c r="Q812" t="n">
-        <v>538200</v>
+        <v>534300</v>
       </c>
     </row>
     <row r="813">
@@ -36337,10 +36337,10 @@
         <v>15</v>
       </c>
       <c r="N833" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O833" t="n">
-        <v>73617.32917304701</v>
+        <v>73617.32962674899</v>
       </c>
       <c r="P833" t="n">
         <v>8200</v>
@@ -36469,22 +36469,22 @@
         <v>0</v>
       </c>
       <c r="L836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M836" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N836" t="n">
         <v>13210</v>
       </c>
       <c r="O836" t="n">
-        <v>1585200</v>
+        <v>1571990</v>
       </c>
       <c r="P836" t="n">
         <v>23900</v>
       </c>
       <c r="Q836" t="n">
-        <v>2868000</v>
+        <v>2844100</v>
       </c>
     </row>
     <row r="837">
@@ -38486,22 +38486,22 @@
         <v>0</v>
       </c>
       <c r="L880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M880" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N880" t="n">
         <v>10755</v>
       </c>
       <c r="O880" t="n">
-        <v>2893095</v>
+        <v>2882340</v>
       </c>
       <c r="P880" t="n">
         <v>17900</v>
       </c>
       <c r="Q880" t="n">
-        <v>4815100</v>
+        <v>4797200</v>
       </c>
     </row>
     <row r="881">
@@ -39685,22 +39685,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M906" t="n">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="N906" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O906" t="n">
-        <v>2010267.463502025</v>
+        <v>2008751.42362524</v>
       </c>
       <c r="P906" t="n">
         <v>2300</v>
       </c>
       <c r="Q906" t="n">
-        <v>3049800</v>
+        <v>3047500</v>
       </c>
     </row>
     <row r="907">
@@ -39781,10 +39781,10 @@
         <v>301</v>
       </c>
       <c r="N908" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O908" t="n">
-        <v>740012.5282705085</v>
+        <v>740012.5251110318</v>
       </c>
       <c r="P908" t="n">
         <v>3500</v>
@@ -39821,22 +39821,22 @@
         <v>0</v>
       </c>
       <c r="L909" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M909" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="N909" t="n">
-        <v>1907.3941918295</v>
+        <v>1907.3940437158</v>
       </c>
       <c r="O909" t="n">
-        <v>59129.2199467145</v>
+        <v>13351.7583060106</v>
       </c>
       <c r="P909" t="n">
         <v>2500</v>
       </c>
       <c r="Q909" t="n">
-        <v>77500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="910">
@@ -39867,22 +39867,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M910" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N910" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O910" t="n">
-        <v>279832.399215213</v>
+        <v>278061.3055159677</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
       </c>
       <c r="Q910" t="n">
-        <v>395000</v>
+        <v>392500</v>
       </c>
     </row>
     <row r="911">
@@ -39919,10 +39919,10 @@
         <v>370</v>
       </c>
       <c r="N911" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O911" t="n">
-        <v>769372.1499022869</v>
+        <v>769372.147097206</v>
       </c>
       <c r="P911" t="n">
         <v>2900</v>
@@ -39965,10 +39965,10 @@
         <v>317</v>
       </c>
       <c r="N912" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O912" t="n">
-        <v>571555.8046668626</v>
+        <v>571555.8096551746</v>
       </c>
       <c r="P912" t="n">
         <v>2500</v>
@@ -40057,10 +40057,10 @@
         <v>2</v>
       </c>
       <c r="N914" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O914" t="n">
-        <v>4244.3280147058</v>
+        <v>4244.3280073574</v>
       </c>
       <c r="P914" t="n">
         <v>2900</v>
@@ -40103,10 +40103,10 @@
         <v>133</v>
       </c>
       <c r="N915" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O915" t="n">
-        <v>280469.0684782672</v>
+        <v>280469.0768911956</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
@@ -40149,10 +40149,10 @@
         <v>393</v>
       </c>
       <c r="N916" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O916" t="n">
-        <v>808040.9421280978</v>
+        <v>808040.9014911903</v>
       </c>
       <c r="P916" t="n">
         <v>2900</v>
@@ -40195,10 +40195,10 @@
         <v>178</v>
       </c>
       <c r="N917" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O917" t="n">
-        <v>573973.1550925861</v>
+        <v>573973.1578293182</v>
       </c>
       <c r="P917" t="n">
         <v>4500</v>
@@ -40241,10 +40241,10 @@
         <v>237</v>
       </c>
       <c r="N918" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O918" t="n">
-        <v>392455.660562562</v>
+        <v>392455.6523076861</v>
       </c>
       <c r="P918" t="n">
         <v>2500</v>
@@ -40422,22 +40422,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M922" t="n">
-        <v>881</v>
+        <v>860</v>
       </c>
       <c r="N922" t="n">
         <v>2454</v>
       </c>
       <c r="O922" t="n">
-        <v>2161974</v>
+        <v>2110440</v>
       </c>
       <c r="P922" t="n">
         <v>4200</v>
       </c>
       <c r="Q922" t="n">
-        <v>3700200</v>
+        <v>3612000</v>
       </c>
     </row>
     <row r="923">
@@ -40468,22 +40468,22 @@
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M923" t="n">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="N923" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O923" t="n">
-        <v>886897.4685257433</v>
+        <v>861421.1509372753</v>
       </c>
       <c r="P923" t="n">
         <v>2500</v>
       </c>
       <c r="Q923" t="n">
-        <v>1392500</v>
+        <v>1352500</v>
       </c>
     </row>
     <row r="924">
@@ -40605,10 +40605,10 @@
         <v>218</v>
       </c>
       <c r="N926" t="n">
-        <v>2311.9247818182</v>
+        <v>2311.9246983547</v>
       </c>
       <c r="O926" t="n">
-        <v>503999.6024363675</v>
+        <v>503999.5842413246</v>
       </c>
       <c r="P926" t="n">
         <v>3500</v>
@@ -40691,22 +40691,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M928" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N928" t="n">
-        <v>3033.7290022676</v>
+        <v>3033.7273039216</v>
       </c>
       <c r="O928" t="n">
-        <v>779668.3535827732</v>
+        <v>770566.7351960865</v>
       </c>
       <c r="P928" t="n">
         <v>4500</v>
       </c>
       <c r="Q928" t="n">
-        <v>1156500</v>
+        <v>1143000</v>
       </c>
     </row>
     <row r="929">
@@ -40737,22 +40737,22 @@
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M929" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N929" t="n">
-        <v>1668.6190998043</v>
+        <v>1668.6199591002</v>
       </c>
       <c r="O929" t="n">
-        <v>388788.2502544019</v>
+        <v>387119.8305112464</v>
       </c>
       <c r="P929" t="n">
         <v>2500</v>
       </c>
       <c r="Q929" t="n">
-        <v>582500</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="930">
@@ -40783,22 +40783,22 @@
         <v>0</v>
       </c>
       <c r="L930" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M930" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="N930" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O930" t="n">
-        <v>463551.2872884347</v>
+        <v>443175.39</v>
       </c>
       <c r="P930" t="n">
         <v>3900</v>
       </c>
       <c r="Q930" t="n">
-        <v>709800</v>
+        <v>678600</v>
       </c>
     </row>
     <row r="931">
@@ -40835,10 +40835,10 @@
         <v>1110</v>
       </c>
       <c r="N931" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O931" t="n">
-        <v>1397794.630891062</v>
+        <v>1397794.654875054</v>
       </c>
       <c r="P931" t="n">
         <v>1900</v>
@@ -41008,22 +41008,22 @@
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M935" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N935" t="n">
-        <v>2556.7452252252</v>
+        <v>2556.7453211009</v>
       </c>
       <c r="O935" t="n">
-        <v>396295.509909906</v>
+        <v>393738.7794495386</v>
       </c>
       <c r="P935" t="n">
         <v>3900</v>
       </c>
       <c r="Q935" t="n">
-        <v>604500</v>
+        <v>600600</v>
       </c>
     </row>
     <row r="936">
@@ -41058,10 +41058,10 @@
         <v>2722</v>
       </c>
       <c r="N936" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O936" t="n">
-        <v>1884037.988313682</v>
+        <v>1884038.009017295</v>
       </c>
       <c r="P936" t="n">
         <v>1200</v>
@@ -41379,22 +41379,22 @@
         <v>0</v>
       </c>
       <c r="L943" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M943" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N943" t="n">
         <v>5510.92</v>
       </c>
       <c r="O943" t="n">
-        <v>33065.52</v>
+        <v>27554.6</v>
       </c>
       <c r="P943" t="n">
         <v>4900</v>
       </c>
       <c r="Q943" t="n">
-        <v>29400</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="944">
@@ -41613,22 +41613,22 @@
         <v>0</v>
       </c>
       <c r="L948" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M948" t="n">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N948" t="n">
         <v>2857.22</v>
       </c>
       <c r="O948" t="n">
-        <v>1457182.2</v>
+        <v>1451467.76</v>
       </c>
       <c r="P948" t="n">
         <v>4900</v>
       </c>
       <c r="Q948" t="n">
-        <v>2499000</v>
+        <v>2489200</v>
       </c>
     </row>
     <row r="949">
@@ -41708,22 +41708,22 @@
         <v>0</v>
       </c>
       <c r="L950" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M950" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N950" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O950" t="n">
-        <v>3435025.92</v>
+        <v>3417135.16</v>
       </c>
       <c r="P950" t="n">
         <v>14900</v>
       </c>
       <c r="Q950" t="n">
-        <v>5721600</v>
+        <v>5691800</v>
       </c>
     </row>
     <row r="951">
@@ -43010,22 +43010,22 @@
         <v>0</v>
       </c>
       <c r="L979" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M979" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N979" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O979" t="n">
-        <v>129036.6993350368</v>
+        <v>125004.3022307678</v>
       </c>
       <c r="P979" t="n">
         <v>4200</v>
       </c>
       <c r="Q979" t="n">
-        <v>134400</v>
+        <v>130200</v>
       </c>
     </row>
     <row r="980">
@@ -43144,22 +43144,22 @@
         <v>0</v>
       </c>
       <c r="L982" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M982" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="N982" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O982" t="n">
-        <v>1048025.801403682</v>
+        <v>1041301.242462703</v>
       </c>
       <c r="P982" t="n">
         <v>900</v>
       </c>
       <c r="Q982" t="n">
-        <v>1823400</v>
+        <v>1811700</v>
       </c>
     </row>
     <row r="983">
@@ -43286,10 +43286,10 @@
         <v>1</v>
       </c>
       <c r="N985" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="O985" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="P985" t="n">
         <v>3600</v>
@@ -43335,10 +43335,10 @@
         <v>1670</v>
       </c>
       <c r="N986" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O986" t="n">
-        <v>5195107.427505037</v>
+        <v>5195107.297747039</v>
       </c>
       <c r="P986" t="n">
         <v>4500</v>
@@ -43461,22 +43461,22 @@
         <v>0</v>
       </c>
       <c r="L989" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M989" t="n">
-        <v>14774</v>
+        <v>14755</v>
       </c>
       <c r="N989" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O989" t="n">
-        <v>10397872.23794614</v>
+        <v>10384499.94919393</v>
       </c>
       <c r="P989" t="n">
         <v>900</v>
       </c>
       <c r="Q989" t="n">
-        <v>13296600</v>
+        <v>13279500</v>
       </c>
     </row>
     <row r="990">
@@ -43557,10 +43557,10 @@
         <v>45</v>
       </c>
       <c r="N991" t="n">
-        <v>3006.0208530806</v>
+        <v>3006.0208653846</v>
       </c>
       <c r="O991" t="n">
-        <v>135270.938388627</v>
+        <v>135270.938942307</v>
       </c>
       <c r="P991" t="n">
         <v>3900</v>
@@ -43821,22 +43821,22 @@
         <v>0</v>
       </c>
       <c r="L997" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M997" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N997" t="n">
         <v>1937</v>
       </c>
       <c r="O997" t="n">
-        <v>796107</v>
+        <v>792233</v>
       </c>
       <c r="P997" t="n">
         <v>3300</v>
       </c>
       <c r="Q997" t="n">
-        <v>1356300</v>
+        <v>1349700</v>
       </c>
     </row>
     <row r="998">
@@ -43947,22 +43947,22 @@
         <v>0</v>
       </c>
       <c r="L1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1000" t="n">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N1000" t="n">
-        <v>2077.4945652174</v>
+        <v>2077.4945784884</v>
       </c>
       <c r="O1000" t="n">
-        <v>891245.1684782647</v>
+        <v>887090.1850145467</v>
       </c>
       <c r="P1000" t="n">
         <v>2900</v>
       </c>
       <c r="Q1000" t="n">
-        <v>1244100</v>
+        <v>1238300</v>
       </c>
     </row>
     <row r="1001">
@@ -44210,10 +44210,10 @@
         <v>81</v>
       </c>
       <c r="N1006" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O1006" t="n">
-        <v>129236.7599677656</v>
+        <v>129236.7578686749</v>
       </c>
       <c r="P1006" t="n">
         <v>2500</v>
@@ -44768,22 +44768,22 @@
         <v>0</v>
       </c>
       <c r="L1018" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1018" t="n">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="N1018" t="n">
         <v>1669.6</v>
       </c>
       <c r="O1018" t="n">
-        <v>1701322.4</v>
+        <v>1694644</v>
       </c>
       <c r="P1018" t="n">
         <v>2900</v>
       </c>
       <c r="Q1018" t="n">
-        <v>2955100</v>
+        <v>2943500</v>
       </c>
     </row>
     <row r="1019">
@@ -45051,22 +45051,22 @@
         <v>0</v>
       </c>
       <c r="L1024" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1024" t="n">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="N1024" t="n">
-        <v>3063.6218891688</v>
+        <v>3063.6218939394</v>
       </c>
       <c r="O1024" t="n">
-        <v>2116962.725415641</v>
+        <v>2110835.484924247</v>
       </c>
       <c r="P1024" t="n">
         <v>3500</v>
       </c>
       <c r="Q1024" t="n">
-        <v>2418500</v>
+        <v>2411500</v>
       </c>
     </row>
     <row r="1025">
@@ -45103,10 +45103,10 @@
         <v>2</v>
       </c>
       <c r="N1025" t="n">
-        <v>3879.9761538462</v>
+        <v>3879.9772727273</v>
       </c>
       <c r="O1025" t="n">
-        <v>7759.9523076924</v>
+        <v>7759.9545454546</v>
       </c>
       <c r="P1025" t="n">
         <v>12500</v>
@@ -47123,22 +47123,22 @@
         <v>0</v>
       </c>
       <c r="L1068" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1068" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1068" t="n">
         <v>10541.34</v>
       </c>
       <c r="O1068" t="n">
-        <v>21082.68</v>
+        <v>10541.34</v>
       </c>
       <c r="P1068" t="n">
         <v>49000</v>
       </c>
       <c r="Q1068" t="n">
-        <v>98000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="1069">
@@ -47694,10 +47694,10 @@
         <v>41</v>
       </c>
       <c r="N1080" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O1080" t="n">
-        <v>288924.533027212</v>
+        <v>288924.5330257278</v>
       </c>
       <c r="P1080" t="n">
         <v>9900</v>
@@ -47974,10 +47974,10 @@
         <v>16</v>
       </c>
       <c r="N1086" t="n">
-        <v>665.32343283582</v>
+        <v>665.3234571176</v>
       </c>
       <c r="O1086" t="n">
-        <v>10645.17492537312</v>
+        <v>10645.1753138816</v>
       </c>
       <c r="P1086" t="n">
         <v>2900</v>
@@ -48205,22 +48205,22 @@
         <v>0</v>
       </c>
       <c r="L1091" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1091" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N1091" t="n">
         <v>7811.9</v>
       </c>
       <c r="O1091" t="n">
-        <v>2015470.2</v>
+        <v>1999846.4</v>
       </c>
       <c r="P1091" t="n">
         <v>13900</v>
       </c>
       <c r="Q1091" t="n">
-        <v>3586200</v>
+        <v>3558400</v>
       </c>
     </row>
     <row r="1092">
@@ -48303,22 +48303,22 @@
         <v>0</v>
       </c>
       <c r="L1093" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1093" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N1093" t="n">
-        <v>430.60997670355</v>
+        <v>430.60997668998</v>
       </c>
       <c r="O1093" t="n">
-        <v>44783.4375771692</v>
+        <v>44352.82759906794</v>
       </c>
       <c r="P1093" t="n">
         <v>2200</v>
       </c>
       <c r="Q1093" t="n">
-        <v>228800</v>
+        <v>226600</v>
       </c>
     </row>
     <row r="1094">
@@ -48352,22 +48352,22 @@
         <v>0</v>
       </c>
       <c r="L1094" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1094" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N1094" t="n">
-        <v>465.8709360519</v>
+        <v>465.87093953488</v>
       </c>
       <c r="O1094" t="n">
-        <v>87117.8650417053</v>
+        <v>85254.38193488304</v>
       </c>
       <c r="P1094" t="n">
         <v>2500</v>
       </c>
       <c r="Q1094" t="n">
-        <v>467500</v>
+        <v>457500</v>
       </c>
     </row>
     <row r="1095">
@@ -49679,22 +49679,22 @@
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1125" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="N1125" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1125" t="n">
-        <v>445466</v>
+        <v>416828.9</v>
       </c>
       <c r="P1125" t="n">
         <v>5100</v>
       </c>
       <c r="Q1125" t="n">
-        <v>714000</v>
+        <v>668100</v>
       </c>
     </row>
     <row r="1126">
@@ -49981,22 +49981,22 @@
         <v>0</v>
       </c>
       <c r="L1132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1132" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1132" t="n">
-        <v>2830.2251183432</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O1132" t="n">
-        <v>367929.265384616</v>
+        <v>362268.819047616</v>
       </c>
       <c r="P1132" t="n">
         <v>2400</v>
       </c>
       <c r="Q1132" t="n">
-        <v>312000</v>
+        <v>307200</v>
       </c>
     </row>
     <row r="1133">
@@ -50069,22 +50069,22 @@
         <v>0</v>
       </c>
       <c r="L1134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1134" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N1134" t="n">
-        <v>15219.155340909</v>
+        <v>15219.155287356</v>
       </c>
       <c r="O1134" t="n">
-        <v>593547.058295451</v>
+        <v>578327.900919528</v>
       </c>
       <c r="P1134" t="n">
         <v>16000</v>
       </c>
       <c r="Q1134" t="n">
-        <v>624000</v>
+        <v>608000</v>
       </c>
     </row>
     <row r="1135">
@@ -50248,10 +50248,10 @@
         <v>5</v>
       </c>
       <c r="N1138" t="n">
-        <v>8922.214777777799</v>
+        <v>8922.214942528701</v>
       </c>
       <c r="O1138" t="n">
-        <v>44611.073888889</v>
+        <v>44611.0747126435</v>
       </c>
       <c r="P1138" t="n">
         <v>8200</v>
@@ -50371,22 +50371,22 @@
         <v>0</v>
       </c>
       <c r="L1141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1141" t="n">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="N1141" t="n">
-        <v>3153.2320501475</v>
+        <v>3153.2320511559</v>
       </c>
       <c r="O1141" t="n">
-        <v>4859130.589277297</v>
+        <v>4855977.358780086</v>
       </c>
       <c r="P1141" t="n">
         <v>3300</v>
       </c>
       <c r="Q1141" t="n">
-        <v>5085300</v>
+        <v>5082000</v>
       </c>
     </row>
     <row r="1142">
@@ -50868,10 +50868,10 @@
         <v>1</v>
       </c>
       <c r="N1152" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="O1152" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="P1152" t="n">
         <v>2000</v>
@@ -52734,22 +52734,22 @@
         <v>0</v>
       </c>
       <c r="L1193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1193" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N1193" t="n">
         <v>1900</v>
       </c>
       <c r="O1193" t="n">
-        <v>136800</v>
+        <v>134900</v>
       </c>
       <c r="P1193" t="n">
         <v>2300</v>
       </c>
       <c r="Q1193" t="n">
-        <v>165600</v>
+        <v>163300</v>
       </c>
     </row>
     <row r="1194">
@@ -53149,10 +53149,10 @@
         <v>1</v>
       </c>
       <c r="N1202" t="n">
-        <v>970.63153846154</v>
+        <v>970.63162162162</v>
       </c>
       <c r="O1202" t="n">
-        <v>970.63153846154</v>
+        <v>970.63162162162</v>
       </c>
       <c r="P1202" t="n">
         <v>7200</v>
@@ -53567,22 +53567,22 @@
         <v>0</v>
       </c>
       <c r="L1211" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M1211" t="n">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="N1211" t="n">
         <v>2058.92</v>
       </c>
       <c r="O1211" t="n">
-        <v>483846.2</v>
+        <v>364428.84</v>
       </c>
       <c r="P1211" t="n">
         <v>2500</v>
       </c>
       <c r="Q1211" t="n">
-        <v>587500</v>
+        <v>442500</v>
       </c>
     </row>
     <row r="1212">
@@ -61253,22 +61253,22 @@
         <v>0</v>
       </c>
       <c r="L1397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1397" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N1397" t="n">
         <v>4550</v>
       </c>
       <c r="O1397" t="n">
-        <v>555100</v>
+        <v>550550</v>
       </c>
       <c r="P1397" t="n">
         <v>5500</v>
       </c>
       <c r="Q1397" t="n">
-        <v>671000</v>
+        <v>665500</v>
       </c>
     </row>
     <row r="1398">
@@ -61662,22 +61662,22 @@
         <v>0</v>
       </c>
       <c r="L1406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1406" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N1406" t="n">
-        <v>2402.6744966443</v>
+        <v>2402.6744594595</v>
       </c>
       <c r="O1406" t="n">
-        <v>86496.28187919479</v>
+        <v>84093.60608108251</v>
       </c>
       <c r="P1406" t="n">
         <v>3000</v>
       </c>
       <c r="Q1406" t="n">
-        <v>108000</v>
+        <v>105000</v>
       </c>
     </row>
   </sheetData>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>209</v>
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>69</v>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>89</v>
@@ -7848,13 +7848,13 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
         <v>2</v>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
         <v>24</v>
@@ -12170,13 +12170,13 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
         <v>1056</v>
@@ -13366,13 +13366,13 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
       </c>
       <c r="L306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M306" t="n">
         <v>327</v>
@@ -13755,13 +13755,13 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>548</v>
@@ -14070,13 +14070,13 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>891</v>
+        <v>821</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
         <v>821</v>
@@ -14561,13 +14561,13 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M333" t="n">
         <v>28</v>
@@ -14774,13 +14774,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>365</v>
@@ -14823,13 +14823,13 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>973</v>
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M361" t="n">
         <v>2719</v>
@@ -16032,13 +16032,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>143</v>
@@ -16291,13 +16291,13 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>488</v>
@@ -17283,13 +17283,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>2749</v>
+        <v>2739</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>2739</v>
@@ -18653,13 +18653,13 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M427" t="n">
         <v>482</v>
@@ -18791,13 +18791,13 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>969</v>
+        <v>947</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M430" t="n">
         <v>947</v>
@@ -18883,13 +18883,13 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M432" t="n">
         <v>864</v>
@@ -18973,13 +18973,13 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M434" t="n">
         <v>276</v>
@@ -25555,13 +25555,13 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M589" t="n">
         <v>259</v>
@@ -25940,13 +25940,13 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M598" t="n">
         <v>308</v>
@@ -28821,13 +28821,13 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
       </c>
       <c r="L666" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M666" t="n">
         <v>39</v>
@@ -31115,13 +31115,13 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K720" t="n">
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M720" t="n">
         <v>62</v>
@@ -31161,13 +31161,13 @@
         </is>
       </c>
       <c r="J721" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M721" t="n">
         <v>9</v>
@@ -31483,13 +31483,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M728" t="n">
         <v>74</v>
@@ -31854,13 +31854,13 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M736" t="n">
         <v>69</v>
@@ -36642,13 +36642,13 @@
         </is>
       </c>
       <c r="J840" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K840" t="n">
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M840" t="n">
         <v>26</v>
@@ -36964,13 +36964,13 @@
         </is>
       </c>
       <c r="J847" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K847" t="n">
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M847" t="n">
         <v>255</v>
@@ -38434,10 +38434,10 @@
         </is>
       </c>
       <c r="J879" t="n">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K879" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L879" t="n">
         <v>0</v>
@@ -39815,13 +39815,13 @@
         </is>
       </c>
       <c r="J909" t="n">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
       </c>
       <c r="L909" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M909" t="n">
         <v>109</v>
@@ -39861,13 +39861,13 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M910" t="n">
         <v>346</v>
@@ -39953,13 +39953,13 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K912" t="n">
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M912" t="n">
         <v>98</v>
@@ -40091,13 +40091,13 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M915" t="n">
         <v>392</v>
@@ -40183,13 +40183,13 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M917" t="n">
         <v>236</v>
@@ -40416,13 +40416,13 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
         <v>540</v>
@@ -40547,13 +40547,13 @@
         </is>
       </c>
       <c r="J925" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K925" t="n">
         <v>0</v>
       </c>
       <c r="L925" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M925" t="n">
         <v>217</v>
@@ -40639,13 +40639,13 @@
         </is>
       </c>
       <c r="J927" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K927" t="n">
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M927" t="n">
         <v>253</v>
@@ -40731,13 +40731,13 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M929" t="n">
         <v>163</v>
@@ -40956,13 +40956,13 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M934" t="n">
         <v>142</v>
@@ -41000,13 +41000,13 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>2722</v>
+        <v>2698</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M935" t="n">
         <v>2698</v>
@@ -42829,13 +42829,13 @@
         </is>
       </c>
       <c r="J975" t="n">
-        <v>2629</v>
+        <v>2609</v>
       </c>
       <c r="K975" t="n">
         <v>0</v>
       </c>
       <c r="L975" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M975" t="n">
         <v>2609</v>
@@ -43409,13 +43409,13 @@
         </is>
       </c>
       <c r="J988" t="n">
-        <v>14755</v>
+        <v>14749</v>
       </c>
       <c r="K988" t="n">
         <v>0</v>
       </c>
       <c r="L988" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M988" t="n">
         <v>14749</v>
@@ -43725,13 +43725,13 @@
         </is>
       </c>
       <c r="J995" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K995" t="n">
         <v>0</v>
       </c>
       <c r="L995" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M995" t="n">
         <v>195</v>
@@ -43769,13 +43769,13 @@
         </is>
       </c>
       <c r="J996" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K996" t="n">
         <v>0</v>
       </c>
       <c r="L996" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M996" t="n">
         <v>407</v>
@@ -43854,13 +43854,13 @@
         </is>
       </c>
       <c r="J998" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K998" t="n">
         <v>0</v>
       </c>
       <c r="L998" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M998" t="n">
         <v>9</v>
@@ -43895,13 +43895,13 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
       </c>
       <c r="L999" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M999" t="n">
         <v>426</v>
@@ -44198,13 +44198,13 @@
         </is>
       </c>
       <c r="J1006" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K1006" t="n">
         <v>0</v>
       </c>
       <c r="L1006" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1006" t="n">
         <v>432</v>
@@ -44685,10 +44685,10 @@
         </is>
       </c>
       <c r="J1016" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1016" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1016" t="n">
         <v>0</v>
@@ -45048,13 +45048,13 @@
         </is>
       </c>
       <c r="J1024" t="n">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="K1024" t="n">
         <v>0</v>
       </c>
       <c r="L1024" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1024" t="n">
         <v>687</v>
@@ -45238,13 +45238,13 @@
         </is>
       </c>
       <c r="J1028" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K1028" t="n">
         <v>0</v>
       </c>
       <c r="L1028" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1028" t="n">
         <v>46</v>
@@ -48014,13 +48014,13 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
       </c>
       <c r="L1087" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1087" t="n">
         <v>78</v>
@@ -48480,13 +48480,13 @@
         </is>
       </c>
       <c r="J1097" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K1097" t="n">
         <v>0</v>
       </c>
       <c r="L1097" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1097" t="n">
         <v>74</v>
@@ -49072,13 +49072,13 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1111" t="n">
         <v>119</v>
@@ -49116,13 +49116,13 @@
         </is>
       </c>
       <c r="J1112" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K1112" t="n">
         <v>0</v>
       </c>
       <c r="L1112" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1112" t="n">
         <v>75</v>
@@ -49588,13 +49588,13 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>1731</v>
+        <v>1610</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M1123" t="n">
         <v>1610</v>
@@ -49676,13 +49676,13 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="K1125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M1125" t="n">
         <v>115</v>
@@ -51903,10 +51903,10 @@
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="K1175" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="L1175" t="n">
         <v>0</v>
@@ -51995,10 +51995,10 @@
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="K1177" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="L1177" t="n">
         <v>0</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -991,22 +991,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O14" t="n">
-        <v>378562.8079518032</v>
+        <v>360449.7613333267</v>
       </c>
       <c r="P14" t="n">
         <v>2600</v>
       </c>
       <c r="Q14" t="n">
-        <v>543400</v>
+        <v>517400</v>
       </c>
     </row>
     <row r="15">
@@ -3359,10 +3359,10 @@
         <v>54</v>
       </c>
       <c r="N72" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O72" t="n">
-        <v>200681.8303846158</v>
+        <v>200681.8304516136</v>
       </c>
       <c r="P72" t="n">
         <v>9500</v>
@@ -4955,22 +4955,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
-        <v>30708.862857143</v>
+        <v>30708.856153846</v>
       </c>
       <c r="O109" t="n">
-        <v>61417.725714286</v>
+        <v>30708.856153846</v>
       </c>
       <c r="P109" t="n">
         <v>53500</v>
       </c>
       <c r="Q109" t="n">
-        <v>107000</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="110">
@@ -5167,22 +5167,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N114" t="n">
         <v>36762.36</v>
       </c>
       <c r="O114" t="n">
-        <v>3161562.96</v>
+        <v>3124800.6</v>
       </c>
       <c r="P114" t="n">
         <v>57100</v>
       </c>
       <c r="Q114" t="n">
-        <v>4910600</v>
+        <v>4853500</v>
       </c>
     </row>
     <row r="115">
@@ -5303,22 +5303,22 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N117" t="n">
-        <v>30238.812535211</v>
+        <v>30238.812571429</v>
       </c>
       <c r="O117" t="n">
-        <v>181432.875211266</v>
+        <v>151194.062857145</v>
       </c>
       <c r="P117" t="n">
         <v>51100</v>
       </c>
       <c r="Q117" t="n">
-        <v>306600</v>
+        <v>255500</v>
       </c>
     </row>
     <row r="118">
@@ -5429,10 +5429,10 @@
         <v>147</v>
       </c>
       <c r="N120" t="n">
-        <v>7407.7300526316</v>
+        <v>7407.7300533333</v>
       </c>
       <c r="O120" t="n">
-        <v>1088936.317736845</v>
+        <v>1088936.317839995</v>
       </c>
       <c r="P120" t="n">
         <v>10900</v>
@@ -6197,10 +6197,10 @@
         <v>6</v>
       </c>
       <c r="N139" t="n">
-        <v>36574.852142857</v>
+        <v>36574.852195122</v>
       </c>
       <c r="O139" t="n">
-        <v>219449.112857142</v>
+        <v>219449.113170732</v>
       </c>
       <c r="P139" t="n">
         <v>65900</v>
@@ -6515,10 +6515,10 @@
         <v>15</v>
       </c>
       <c r="N146" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O146" t="n">
-        <v>2121253.26818175</v>
+        <v>2121253.2684039</v>
       </c>
       <c r="P146" t="n">
         <v>251900</v>
@@ -8792,22 +8792,22 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M200" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N200" t="n">
         <v>8500</v>
       </c>
       <c r="O200" t="n">
-        <v>144500</v>
+        <v>136000</v>
       </c>
       <c r="P200" t="n">
         <v>10200</v>
       </c>
       <c r="Q200" t="n">
-        <v>173400</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="201">
@@ -8844,10 +8844,10 @@
         <v>5</v>
       </c>
       <c r="N201" t="n">
-        <v>4333.6046666667</v>
+        <v>4333.6116666667</v>
       </c>
       <c r="O201" t="n">
-        <v>21668.0233333335</v>
+        <v>21668.0583333335</v>
       </c>
       <c r="P201" t="n">
         <v>7500</v>
@@ -9878,22 +9878,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M225" t="n">
-        <v>9267</v>
+        <v>9262</v>
       </c>
       <c r="N225" t="n">
         <v>1726.32</v>
       </c>
       <c r="O225" t="n">
-        <v>15997807.44</v>
+        <v>15989175.84</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
       </c>
       <c r="Q225" t="n">
-        <v>13900500</v>
+        <v>13893000</v>
       </c>
     </row>
     <row r="226">
@@ -10429,22 +10429,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="N238" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O238" t="n">
-        <v>1226528.67488709</v>
+        <v>1225431.17947121</v>
       </c>
       <c r="P238" t="n">
         <v>1500</v>
       </c>
       <c r="Q238" t="n">
-        <v>1675500</v>
+        <v>1674000</v>
       </c>
     </row>
     <row r="239">
@@ -10470,22 +10470,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N239" t="n">
-        <v>21084.771458886</v>
+        <v>21084.771462766</v>
       </c>
       <c r="O239" t="n">
-        <v>2488003.032148548</v>
+        <v>2466918.261143622</v>
       </c>
       <c r="P239" t="n">
         <v>30000</v>
       </c>
       <c r="Q239" t="n">
-        <v>3540000</v>
+        <v>3510000</v>
       </c>
     </row>
     <row r="240">
@@ -10552,22 +10552,22 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N241" t="n">
-        <v>31233.611793893</v>
+        <v>31233.611800766</v>
       </c>
       <c r="O241" t="n">
-        <v>1936483.931221366</v>
+        <v>1905250.319846726</v>
       </c>
       <c r="P241" t="n">
         <v>45500</v>
       </c>
       <c r="Q241" t="n">
-        <v>2821000</v>
+        <v>2775500</v>
       </c>
     </row>
     <row r="242">
@@ -11175,22 +11175,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M256" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N256" t="n">
         <v>1267</v>
       </c>
       <c r="O256" t="n">
-        <v>244531</v>
+        <v>241997</v>
       </c>
       <c r="P256" t="n">
         <v>1900</v>
       </c>
       <c r="Q256" t="n">
-        <v>366700</v>
+        <v>362900</v>
       </c>
     </row>
     <row r="257">
@@ -11733,22 +11733,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N269" t="n">
         <v>5000</v>
       </c>
       <c r="O269" t="n">
-        <v>950000</v>
+        <v>945000</v>
       </c>
       <c r="P269" t="n">
         <v>4900</v>
       </c>
       <c r="Q269" t="n">
-        <v>931000</v>
+        <v>926100</v>
       </c>
     </row>
     <row r="270">
@@ -12176,22 +12176,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M279" t="n">
-        <v>1056</v>
+        <v>1044</v>
       </c>
       <c r="N279" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O279" t="n">
-        <v>2726862.309541286</v>
+        <v>2695875.227628084</v>
       </c>
       <c r="P279" t="n">
         <v>4500</v>
       </c>
       <c r="Q279" t="n">
-        <v>4752000</v>
+        <v>4698000</v>
       </c>
     </row>
     <row r="280">
@@ -12361,10 +12361,10 @@
         <v>137</v>
       </c>
       <c r="N283" t="n">
-        <v>2033.5658041958</v>
+        <v>2033.56088</v>
       </c>
       <c r="O283" t="n">
-        <v>278598.5151748246</v>
+        <v>278597.84056</v>
       </c>
       <c r="P283" t="n">
         <v>4100</v>
@@ -12653,10 +12653,10 @@
         <v>2836</v>
       </c>
       <c r="N290" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O290" t="n">
-        <v>8958529.294275867</v>
+        <v>8958529.295871399</v>
       </c>
       <c r="P290" t="n">
         <v>5600</v>
@@ -12745,10 +12745,10 @@
         <v>228</v>
       </c>
       <c r="N292" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O292" t="n">
-        <v>875890.4410536552</v>
+        <v>875890.4474190276</v>
       </c>
       <c r="P292" t="n">
         <v>6900</v>
@@ -12927,10 +12927,10 @@
         <v>91</v>
       </c>
       <c r="N296" t="n">
-        <v>3230.0675874126</v>
+        <v>3230.0675313059</v>
       </c>
       <c r="O296" t="n">
-        <v>293936.1504545466</v>
+        <v>293936.1453488369</v>
       </c>
       <c r="P296" t="n">
         <v>6200</v>
@@ -13147,10 +13147,10 @@
         <v>34</v>
       </c>
       <c r="N301" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O301" t="n">
-        <v>91623.9933333322</v>
+        <v>91623.9916558742</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -13598,10 +13598,10 @@
         <v>468</v>
       </c>
       <c r="N311" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O311" t="n">
-        <v>1776392.28331447</v>
+        <v>1776392.28331681</v>
       </c>
       <c r="P311" t="n">
         <v>6200</v>
@@ -13987,10 +13987,10 @@
         <v>331</v>
       </c>
       <c r="N320" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O320" t="n">
-        <v>1618897.845476335</v>
+        <v>1618897.84550351</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14076,22 +14076,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M322" t="n">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="N322" t="n">
         <v>1203.38</v>
       </c>
       <c r="O322" t="n">
-        <v>987974.9800000001</v>
+        <v>980754.7000000001</v>
       </c>
       <c r="P322" t="n">
         <v>1900</v>
       </c>
       <c r="Q322" t="n">
-        <v>1559900</v>
+        <v>1548500</v>
       </c>
     </row>
     <row r="323">
@@ -14122,22 +14122,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M323" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N323" t="n">
         <v>3472</v>
       </c>
       <c r="O323" t="n">
-        <v>531216</v>
+        <v>524272</v>
       </c>
       <c r="P323" t="n">
         <v>4800</v>
       </c>
       <c r="Q323" t="n">
-        <v>734400</v>
+        <v>724800</v>
       </c>
     </row>
     <row r="324">
@@ -14429,22 +14429,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N330" t="n">
         <v>7041</v>
       </c>
       <c r="O330" t="n">
-        <v>323886</v>
+        <v>316845</v>
       </c>
       <c r="P330" t="n">
         <v>11500</v>
       </c>
       <c r="Q330" t="n">
-        <v>529000</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="331">
@@ -14829,22 +14829,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M339" t="n">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="N339" t="n">
         <v>489.88</v>
       </c>
       <c r="O339" t="n">
-        <v>476653.24</v>
+        <v>467345.52</v>
       </c>
       <c r="P339" t="n">
         <v>700</v>
       </c>
       <c r="Q339" t="n">
-        <v>681100</v>
+        <v>667800</v>
       </c>
     </row>
     <row r="340">
@@ -14958,10 +14958,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="O342" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="P342" t="n">
         <v>5200</v>
@@ -15096,10 +15096,10 @@
         <v>288</v>
       </c>
       <c r="N345" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O345" t="n">
-        <v>4268845.11222288</v>
+        <v>4268845.111248576</v>
       </c>
       <c r="P345" t="n">
         <v>24900</v>
@@ -15219,22 +15219,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M348" t="n">
-        <v>6373</v>
+        <v>6357</v>
       </c>
       <c r="N348" t="n">
         <v>2090.85</v>
       </c>
       <c r="O348" t="n">
-        <v>13324987.05</v>
+        <v>13291533.45</v>
       </c>
       <c r="P348" t="n">
         <v>2900</v>
       </c>
       <c r="Q348" t="n">
-        <v>18481700</v>
+        <v>18435300</v>
       </c>
     </row>
     <row r="349">
@@ -16044,10 +16044,10 @@
         <v>143</v>
       </c>
       <c r="N367" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O367" t="n">
-        <v>434957.3818392231</v>
+        <v>434957.381851135</v>
       </c>
       <c r="P367" t="n">
         <v>5500</v>
@@ -16297,22 +16297,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M373" t="n">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="N373" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O373" t="n">
-        <v>777172.8646452359</v>
+        <v>751691.7488900671</v>
       </c>
       <c r="P373" t="n">
         <v>3900</v>
       </c>
       <c r="Q373" t="n">
-        <v>1903200</v>
+        <v>1840800</v>
       </c>
     </row>
     <row r="374">
@@ -16553,22 +16553,22 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M379" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N379" t="n">
         <v>2695.04</v>
       </c>
       <c r="O379" t="n">
-        <v>161702.4</v>
+        <v>159007.36</v>
       </c>
       <c r="P379" t="n">
         <v>7300</v>
       </c>
       <c r="Q379" t="n">
-        <v>438000</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="380">
@@ -16638,22 +16638,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N381" t="n">
         <v>7507</v>
       </c>
       <c r="O381" t="n">
-        <v>1418823</v>
+        <v>1411316</v>
       </c>
       <c r="P381" t="n">
         <v>13400</v>
       </c>
       <c r="Q381" t="n">
-        <v>2532600</v>
+        <v>2519200</v>
       </c>
     </row>
     <row r="382">
@@ -17201,22 +17201,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M394" t="n">
-        <v>1787</v>
+        <v>1780</v>
       </c>
       <c r="N394" t="n">
         <v>1530.63</v>
       </c>
       <c r="O394" t="n">
-        <v>2735235.81</v>
+        <v>2724521.4</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
       </c>
       <c r="Q394" t="n">
-        <v>5182300</v>
+        <v>5162000</v>
       </c>
     </row>
     <row r="395">
@@ -17289,22 +17289,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M396" t="n">
-        <v>2739</v>
+        <v>2722</v>
       </c>
       <c r="N396" t="n">
         <v>1387.55</v>
       </c>
       <c r="O396" t="n">
-        <v>3800499.45</v>
+        <v>3776911.1</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
       </c>
       <c r="Q396" t="n">
-        <v>6299700</v>
+        <v>6260600</v>
       </c>
     </row>
     <row r="397">
@@ -17421,22 +17421,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="N399" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O399" t="n">
-        <v>2128872.342003662</v>
+        <v>2126850.621594197</v>
       </c>
       <c r="P399" t="n">
         <v>2400</v>
       </c>
       <c r="Q399" t="n">
-        <v>2527200</v>
+        <v>2524800</v>
       </c>
     </row>
     <row r="400">
@@ -18433,22 +18433,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M422" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N422" t="n">
         <v>3751</v>
       </c>
       <c r="O422" t="n">
-        <v>206305</v>
+        <v>198803</v>
       </c>
       <c r="P422" t="n">
         <v>6400</v>
       </c>
       <c r="Q422" t="n">
-        <v>352000</v>
+        <v>339200</v>
       </c>
     </row>
     <row r="423">
@@ -18523,22 +18523,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M424" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N424" t="n">
         <v>6557.57</v>
       </c>
       <c r="O424" t="n">
-        <v>406569.34</v>
+        <v>393454.2</v>
       </c>
       <c r="P424" t="n">
         <v>9900</v>
       </c>
       <c r="Q424" t="n">
-        <v>613800</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="425">
@@ -18659,22 +18659,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M427" t="n">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="N427" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O427" t="n">
-        <v>786105.0362876965</v>
+        <v>771426.7387196127</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1205000</v>
+        <v>1182500</v>
       </c>
     </row>
     <row r="428">
@@ -18711,10 +18711,10 @@
         <v>14</v>
       </c>
       <c r="N428" t="n">
-        <v>1467.3264227642</v>
+        <v>1467.3258333333</v>
       </c>
       <c r="O428" t="n">
-        <v>20542.5699186988</v>
+        <v>20542.5616666662</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
@@ -18751,22 +18751,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M429" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.6006518987</v>
+        <v>1690.6000587084</v>
       </c>
       <c r="O429" t="n">
-        <v>87911.2338987324</v>
+        <v>84530.00293541999</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
       </c>
       <c r="Q429" t="n">
-        <v>150800</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="430">
@@ -18797,22 +18797,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M430" t="n">
-        <v>947</v>
+        <v>911</v>
       </c>
       <c r="N430" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O430" t="n">
-        <v>1468033.075928791</v>
+        <v>1412226.146157117</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
       </c>
       <c r="Q430" t="n">
-        <v>2367500</v>
+        <v>2277500</v>
       </c>
     </row>
     <row r="431">
@@ -18843,22 +18843,22 @@
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M431" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N431" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O431" t="n">
-        <v>176891.7794923888</v>
+        <v>173732.992602037</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
       </c>
       <c r="Q431" t="n">
-        <v>324800</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="432">
@@ -18889,22 +18889,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M432" t="n">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="N432" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O432" t="n">
-        <v>2076633.32783593</v>
+        <v>2023756.22501675</v>
       </c>
       <c r="P432" t="n">
         <v>3500</v>
       </c>
       <c r="Q432" t="n">
-        <v>3024000</v>
+        <v>2947000</v>
       </c>
     </row>
     <row r="433">
@@ -18979,22 +18979,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M434" t="n">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="N434" t="n">
-        <v>2521.5415942029</v>
+        <v>2521.5405895197</v>
       </c>
       <c r="O434" t="n">
-        <v>695945.4800000003</v>
+        <v>673251.3374017599</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
       </c>
       <c r="Q434" t="n">
-        <v>1076400</v>
+        <v>1041300</v>
       </c>
     </row>
     <row r="435">
@@ -19026,10 +19026,10 @@
         <v>63</v>
       </c>
       <c r="N435" t="n">
-        <v>1232.8080088496</v>
+        <v>1232.8076255708</v>
       </c>
       <c r="O435" t="n">
-        <v>77666.90455752479</v>
+        <v>77666.8804109604</v>
       </c>
       <c r="P435" t="n">
         <v>2400</v>
@@ -23468,22 +23468,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M539" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N539" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O539" t="n">
-        <v>497319.058753706</v>
+        <v>495289.1854923205</v>
       </c>
       <c r="P539" t="n">
         <v>3600</v>
       </c>
       <c r="Q539" t="n">
-        <v>882000</v>
+        <v>878400</v>
       </c>
     </row>
     <row r="540">
@@ -24675,22 +24675,22 @@
         <v>0</v>
       </c>
       <c r="L568" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M568" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N568" t="n">
         <v>5894.64</v>
       </c>
       <c r="O568" t="n">
-        <v>725040.7200000001</v>
+        <v>719146.0800000001</v>
       </c>
       <c r="P568" t="n">
         <v>11000</v>
       </c>
       <c r="Q568" t="n">
-        <v>1353000</v>
+        <v>1342000</v>
       </c>
     </row>
     <row r="569">
@@ -26069,22 +26069,22 @@
         <v>0</v>
       </c>
       <c r="L601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N601" t="n">
         <v>29957</v>
       </c>
       <c r="O601" t="n">
-        <v>89871</v>
+        <v>59914</v>
       </c>
       <c r="P601" t="n">
         <v>50900</v>
       </c>
       <c r="Q601" t="n">
-        <v>152700</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="602">
@@ -26295,10 +26295,10 @@
         <v>89</v>
       </c>
       <c r="N606" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O606" t="n">
-        <v>1029021.428842124</v>
+        <v>1029021.428496003</v>
       </c>
       <c r="P606" t="n">
         <v>18500</v>
@@ -27042,22 +27042,22 @@
         <v>0</v>
       </c>
       <c r="L624" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M624" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N624" t="n">
         <v>853</v>
       </c>
       <c r="O624" t="n">
-        <v>66534</v>
+        <v>63122</v>
       </c>
       <c r="P624" t="n">
         <v>1500</v>
       </c>
       <c r="Q624" t="n">
-        <v>117000</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="625">
@@ -27083,22 +27083,22 @@
         <v>0</v>
       </c>
       <c r="L625" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M625" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="N625" t="n">
         <v>1647</v>
       </c>
       <c r="O625" t="n">
-        <v>533628</v>
+        <v>525393</v>
       </c>
       <c r="P625" t="n">
         <v>2900</v>
       </c>
       <c r="Q625" t="n">
-        <v>939600</v>
+        <v>925100</v>
       </c>
     </row>
     <row r="626">
@@ -28449,10 +28449,10 @@
         <v>2</v>
       </c>
       <c r="N657" t="n">
-        <v>1466.8807100592</v>
+        <v>1466.8807185629</v>
       </c>
       <c r="O657" t="n">
-        <v>2933.7614201184</v>
+        <v>2933.7614371258</v>
       </c>
       <c r="P657" t="n">
         <v>3400</v>
@@ -28919,22 +28919,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M668" t="n">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="N668" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O668" t="n">
-        <v>675912.8072700114</v>
+        <v>649375.8726743808</v>
       </c>
       <c r="P668" t="n">
         <v>2900</v>
       </c>
       <c r="Q668" t="n">
-        <v>1255700</v>
+        <v>1206400</v>
       </c>
     </row>
     <row r="669">
@@ -29636,22 +29636,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M685" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N685" t="n">
         <v>8968.24</v>
       </c>
       <c r="O685" t="n">
-        <v>466348.48</v>
+        <v>457380.24</v>
       </c>
       <c r="P685" t="n">
         <v>18600</v>
       </c>
       <c r="Q685" t="n">
-        <v>967200</v>
+        <v>948600</v>
       </c>
     </row>
     <row r="686">
@@ -31173,10 +31173,10 @@
         <v>9</v>
       </c>
       <c r="N721" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O721" t="n">
-        <v>28025.0102393613</v>
+        <v>28025.010244233</v>
       </c>
       <c r="P721" t="n">
         <v>5000</v>
@@ -31259,22 +31259,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M723" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N723" t="n">
         <v>5410.72</v>
       </c>
       <c r="O723" t="n">
-        <v>16232.16</v>
+        <v>0</v>
       </c>
       <c r="P723" t="n">
         <v>8700</v>
       </c>
       <c r="Q723" t="n">
-        <v>26100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
@@ -31443,22 +31443,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M727" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N727" t="n">
         <v>2495.98</v>
       </c>
       <c r="O727" t="n">
-        <v>249598</v>
+        <v>247102.02</v>
       </c>
       <c r="P727" t="n">
         <v>4100</v>
       </c>
       <c r="Q727" t="n">
-        <v>410000</v>
+        <v>405900</v>
       </c>
     </row>
     <row r="728">
@@ -31489,22 +31489,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M728" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N728" t="n">
         <v>3254.49</v>
       </c>
       <c r="O728" t="n">
-        <v>240832.26</v>
+        <v>227814.3</v>
       </c>
       <c r="P728" t="n">
         <v>5200</v>
       </c>
       <c r="Q728" t="n">
-        <v>384800</v>
+        <v>364000</v>
       </c>
     </row>
     <row r="729">
@@ -31541,10 +31541,10 @@
         <v>25</v>
       </c>
       <c r="N729" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O729" t="n">
-        <v>90266.2506305175</v>
+        <v>90266.25063451749</v>
       </c>
       <c r="P729" t="n">
         <v>5800</v>
@@ -31676,22 +31676,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M732" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N732" t="n">
         <v>3965.02</v>
       </c>
       <c r="O732" t="n">
-        <v>71370.36</v>
+        <v>63440.32</v>
       </c>
       <c r="P732" t="n">
         <v>6500</v>
       </c>
       <c r="Q732" t="n">
-        <v>117000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="733">
@@ -31860,22 +31860,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M736" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="N736" t="n">
-        <v>1664.3585273632</v>
+        <v>1664.3584236948</v>
       </c>
       <c r="O736" t="n">
-        <v>114840.7383880608</v>
+        <v>99861.50542168799</v>
       </c>
       <c r="P736" t="n">
         <v>2900</v>
       </c>
       <c r="Q736" t="n">
-        <v>200100</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="737">
@@ -32088,22 +32088,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M741" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N741" t="n">
         <v>10451.48</v>
       </c>
       <c r="O741" t="n">
-        <v>355350.32</v>
+        <v>313544.4</v>
       </c>
       <c r="P741" t="n">
         <v>16900</v>
       </c>
       <c r="Q741" t="n">
-        <v>574600</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="742">
@@ -32692,10 +32692,10 @@
         <v>19</v>
       </c>
       <c r="N754" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O754" t="n">
-        <v>446910.86609375</v>
+        <v>446910.862741941</v>
       </c>
       <c r="P754" t="n">
         <v>39000</v>
@@ -32830,10 +32830,10 @@
         <v>1233</v>
       </c>
       <c r="N757" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O757" t="n">
-        <v>2192856.683843476</v>
+        <v>2192856.692288293</v>
       </c>
       <c r="P757" t="n">
         <v>4900</v>
@@ -32870,22 +32870,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M758" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="N758" t="n">
         <v>2325</v>
       </c>
       <c r="O758" t="n">
-        <v>757950</v>
+        <v>744000</v>
       </c>
       <c r="P758" t="n">
         <v>4900</v>
       </c>
       <c r="Q758" t="n">
-        <v>1597400</v>
+        <v>1568000</v>
       </c>
     </row>
     <row r="759">
@@ -35549,22 +35549,22 @@
         <v>0</v>
       </c>
       <c r="L816" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M816" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N816" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O816" t="n">
-        <v>1066278.386990796</v>
+        <v>1063950.263972522</v>
       </c>
       <c r="P816" t="n">
         <v>4500</v>
       </c>
       <c r="Q816" t="n">
-        <v>2061000</v>
+        <v>2056500</v>
       </c>
     </row>
     <row r="817">
@@ -36193,22 +36193,22 @@
         <v>0</v>
       </c>
       <c r="L830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M830" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N830" t="n">
         <v>3396.38</v>
       </c>
       <c r="O830" t="n">
-        <v>71323.98</v>
+        <v>67927.60000000001</v>
       </c>
       <c r="P830" t="n">
         <v>6500</v>
       </c>
       <c r="Q830" t="n">
-        <v>136500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="831">
@@ -36567,10 +36567,10 @@
         <v>20</v>
       </c>
       <c r="N838" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O838" t="n">
-        <v>78074.724035608</v>
+        <v>78074.73625865999</v>
       </c>
       <c r="P838" t="n">
         <v>7500</v>
@@ -37022,10 +37022,10 @@
         <v>15</v>
       </c>
       <c r="N848" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O848" t="n">
-        <v>88037.5911971835</v>
+        <v>88037.59108761299</v>
       </c>
       <c r="P848" t="n">
         <v>9500</v>
@@ -37660,22 +37660,22 @@
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M862" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N862" t="n">
         <v>5682</v>
       </c>
       <c r="O862" t="n">
-        <v>414786</v>
+        <v>403422</v>
       </c>
       <c r="P862" t="n">
         <v>9900</v>
       </c>
       <c r="Q862" t="n">
-        <v>722700</v>
+        <v>702900</v>
       </c>
     </row>
     <row r="863">
@@ -37752,22 +37752,22 @@
         <v>0</v>
       </c>
       <c r="L864" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M864" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N864" t="n">
         <v>8806</v>
       </c>
       <c r="O864" t="n">
-        <v>792540</v>
+        <v>783734</v>
       </c>
       <c r="P864" t="n">
         <v>14900</v>
       </c>
       <c r="Q864" t="n">
-        <v>1341000</v>
+        <v>1326100</v>
       </c>
     </row>
     <row r="865">
@@ -38207,22 +38207,22 @@
         <v>0</v>
       </c>
       <c r="L874" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M874" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N874" t="n">
         <v>11015</v>
       </c>
       <c r="O874" t="n">
-        <v>330450</v>
+        <v>319435</v>
       </c>
       <c r="P874" t="n">
         <v>17900</v>
       </c>
       <c r="Q874" t="n">
-        <v>537000</v>
+        <v>519100</v>
       </c>
     </row>
     <row r="875">
@@ -39222,22 +39222,22 @@
         <v>0</v>
       </c>
       <c r="L896" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M896" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N896" t="n">
         <v>21762</v>
       </c>
       <c r="O896" t="n">
-        <v>631098</v>
+        <v>609336</v>
       </c>
       <c r="P896" t="n">
         <v>35900</v>
       </c>
       <c r="Q896" t="n">
-        <v>1041100</v>
+        <v>1005200</v>
       </c>
     </row>
     <row r="897">
@@ -39406,22 +39406,22 @@
         <v>0</v>
       </c>
       <c r="L900" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M900" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N900" t="n">
         <v>7253</v>
       </c>
       <c r="O900" t="n">
-        <v>819589</v>
+        <v>812336</v>
       </c>
       <c r="P900" t="n">
         <v>11900</v>
       </c>
       <c r="Q900" t="n">
-        <v>1344700</v>
+        <v>1332800</v>
       </c>
     </row>
     <row r="901">
@@ -39867,22 +39867,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M910" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="N910" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O910" t="n">
-        <v>719466.9108612711</v>
+        <v>711149.369693562</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
       </c>
       <c r="Q910" t="n">
-        <v>1003400</v>
+        <v>991800</v>
       </c>
     </row>
     <row r="911">
@@ -39919,10 +39919,10 @@
         <v>317</v>
       </c>
       <c r="N911" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O911" t="n">
-        <v>571555.8258243302</v>
+        <v>571555.8273565815</v>
       </c>
       <c r="P911" t="n">
         <v>2500</v>
@@ -39965,10 +39965,10 @@
         <v>98</v>
       </c>
       <c r="N912" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O912" t="n">
-        <v>324046.3418181794</v>
+        <v>324046.3333333296</v>
       </c>
       <c r="P912" t="n">
         <v>4900</v>
@@ -40011,10 +40011,10 @@
         <v>2</v>
       </c>
       <c r="N913" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O913" t="n">
-        <v>4244.328</v>
+        <v>4244.3279667794</v>
       </c>
       <c r="P913" t="n">
         <v>2900</v>
@@ -40057,10 +40057,10 @@
         <v>133</v>
       </c>
       <c r="N914" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O914" t="n">
-        <v>280469.0792041586</v>
+        <v>280469.1051851899</v>
       </c>
       <c r="P914" t="n">
         <v>2900</v>
@@ -40097,22 +40097,22 @@
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M915" t="n">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="N915" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O915" t="n">
-        <v>805984.8147714663</v>
+        <v>795704.3812936845</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
       </c>
       <c r="Q915" t="n">
-        <v>1136800</v>
+        <v>1122300</v>
       </c>
     </row>
     <row r="916">
@@ -40422,22 +40422,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M922" t="n">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="N922" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O922" t="n">
-        <v>859829.0991678</v>
+        <v>848683.273703464</v>
       </c>
       <c r="P922" t="n">
         <v>2500</v>
       </c>
       <c r="Q922" t="n">
-        <v>1350000</v>
+        <v>1332500</v>
       </c>
     </row>
     <row r="923">
@@ -40559,10 +40559,10 @@
         <v>217</v>
       </c>
       <c r="N925" t="n">
-        <v>2311.9221535181</v>
+        <v>2311.9216849015</v>
       </c>
       <c r="O925" t="n">
-        <v>501687.1073134277</v>
+        <v>501687.0056236255</v>
       </c>
       <c r="P925" t="n">
         <v>3500</v>
@@ -40599,22 +40599,22 @@
         <v>0</v>
       </c>
       <c r="L926" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M926" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N926" t="n">
-        <v>1906.1853846154</v>
+        <v>1906.1853271028</v>
       </c>
       <c r="O926" t="n">
-        <v>318332.9592307718</v>
+        <v>314520.578971962</v>
       </c>
       <c r="P926" t="n">
         <v>2900</v>
       </c>
       <c r="Q926" t="n">
-        <v>484300</v>
+        <v>478500</v>
       </c>
     </row>
     <row r="927">
@@ -40651,10 +40651,10 @@
         <v>253</v>
       </c>
       <c r="N927" t="n">
-        <v>3033.7269651741</v>
+        <v>3033.724972973</v>
       </c>
       <c r="O927" t="n">
-        <v>767532.9221890472</v>
+        <v>767532.4181621691</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
@@ -40691,22 +40691,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M928" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N928" t="n">
-        <v>1668.6236893204</v>
+        <v>1668.6240987654</v>
       </c>
       <c r="O928" t="n">
-        <v>387120.6959223328</v>
+        <v>375440.422222215</v>
       </c>
       <c r="P928" t="n">
         <v>2500</v>
       </c>
       <c r="Q928" t="n">
-        <v>580000</v>
+        <v>562500</v>
       </c>
     </row>
     <row r="929">
@@ -40743,10 +40743,10 @@
         <v>163</v>
       </c>
       <c r="N929" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O929" t="n">
-        <v>415158.5047289744</v>
+        <v>415158.5031086077</v>
       </c>
       <c r="P929" t="n">
         <v>3900</v>
@@ -40783,22 +40783,22 @@
         <v>0</v>
       </c>
       <c r="L930" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M930" t="n">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="N930" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O930" t="n">
-        <v>1397794.654875054</v>
+        <v>1387720.500842764</v>
       </c>
       <c r="P930" t="n">
         <v>1900</v>
       </c>
       <c r="Q930" t="n">
-        <v>2109000</v>
+        <v>2093800</v>
       </c>
     </row>
     <row r="931">
@@ -41006,22 +41006,22 @@
         <v>0</v>
       </c>
       <c r="L935" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M935" t="n">
-        <v>2698</v>
+        <v>2686</v>
       </c>
       <c r="N935" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O935" t="n">
-        <v>1867426.410642784</v>
+        <v>1859120.595703773</v>
       </c>
       <c r="P935" t="n">
         <v>1200</v>
       </c>
       <c r="Q935" t="n">
-        <v>3237600</v>
+        <v>3223200</v>
       </c>
     </row>
     <row r="936">
@@ -42835,22 +42835,22 @@
         <v>0</v>
       </c>
       <c r="L975" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M975" t="n">
-        <v>2609</v>
+        <v>2589</v>
       </c>
       <c r="N975" t="n">
         <v>177.65</v>
       </c>
       <c r="O975" t="n">
-        <v>463488.85</v>
+        <v>459935.85</v>
       </c>
       <c r="P975" t="n">
         <v>300</v>
       </c>
       <c r="Q975" t="n">
-        <v>782700</v>
+        <v>776700</v>
       </c>
     </row>
     <row r="976">
@@ -43098,22 +43098,22 @@
         <v>0</v>
       </c>
       <c r="L981" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M981" t="n">
-        <v>2013</v>
+        <v>1961</v>
       </c>
       <c r="N981" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O981" t="n">
-        <v>1041301.47496058</v>
+        <v>1014402.632448726</v>
       </c>
       <c r="P981" t="n">
         <v>900</v>
       </c>
       <c r="Q981" t="n">
-        <v>1811700</v>
+        <v>1764900</v>
       </c>
     </row>
     <row r="982">
@@ -43283,22 +43283,22 @@
         <v>0</v>
       </c>
       <c r="L985" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M985" t="n">
-        <v>1670</v>
+        <v>1650</v>
       </c>
       <c r="N985" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O985" t="n">
-        <v>5195107.172896169</v>
+        <v>5132890.230858225</v>
       </c>
       <c r="P985" t="n">
         <v>4500</v>
       </c>
       <c r="Q985" t="n">
-        <v>7515000</v>
+        <v>7425000</v>
       </c>
     </row>
     <row r="986">
@@ -43415,22 +43415,22 @@
         <v>0</v>
       </c>
       <c r="L988" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M988" t="n">
-        <v>14749</v>
+        <v>14694</v>
       </c>
       <c r="N988" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O988" t="n">
-        <v>10380276.83197312</v>
+        <v>10341567.67195468</v>
       </c>
       <c r="P988" t="n">
         <v>900</v>
       </c>
       <c r="Q988" t="n">
-        <v>13274100</v>
+        <v>13224600</v>
       </c>
     </row>
     <row r="989">
@@ -44164,10 +44164,10 @@
         <v>81</v>
       </c>
       <c r="N1005" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O1005" t="n">
-        <v>129236.7403678068</v>
+        <v>129236.7263411907</v>
       </c>
       <c r="P1005" t="n">
         <v>2500</v>
@@ -44204,22 +44204,22 @@
         <v>0</v>
       </c>
       <c r="L1006" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1006" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="N1006" t="n">
         <v>1567.02</v>
       </c>
       <c r="O1006" t="n">
-        <v>676952.64</v>
+        <v>670684.5599999999</v>
       </c>
       <c r="P1006" t="n">
         <v>2900</v>
       </c>
       <c r="Q1006" t="n">
-        <v>1252800</v>
+        <v>1241200</v>
       </c>
     </row>
     <row r="1007">
@@ -45581,22 +45581,22 @@
         <v>0</v>
       </c>
       <c r="L1035" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1035" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N1035" t="n">
         <v>4337.31</v>
       </c>
       <c r="O1035" t="n">
-        <v>86746.20000000001</v>
+        <v>82408.89000000001</v>
       </c>
       <c r="P1035" t="n">
         <v>12900</v>
       </c>
       <c r="Q1035" t="n">
-        <v>258000</v>
+        <v>245100</v>
       </c>
     </row>
     <row r="1036">
@@ -47977,10 +47977,10 @@
         <v>16</v>
       </c>
       <c r="N1086" t="n">
-        <v>665.32347555556</v>
+        <v>665.32351302785</v>
       </c>
       <c r="O1086" t="n">
-        <v>10645.17560888896</v>
+        <v>10645.1762084456</v>
       </c>
       <c r="P1086" t="n">
         <v>2900</v>
@@ -48312,10 +48312,10 @@
         <v>103</v>
       </c>
       <c r="N1093" t="n">
-        <v>430.60997668998</v>
+        <v>430.6099765808</v>
       </c>
       <c r="O1093" t="n">
-        <v>44352.82759906794</v>
+        <v>44352.8275878224</v>
       </c>
       <c r="P1093" t="n">
         <v>2200</v>
@@ -48410,10 +48410,10 @@
         <v>13</v>
       </c>
       <c r="N1095" t="n">
-        <v>315.02679218968</v>
+        <v>315.02685915493</v>
       </c>
       <c r="O1095" t="n">
-        <v>4095.34829846584</v>
+        <v>4095.34916901409</v>
       </c>
       <c r="P1095" t="n">
         <v>2200</v>
@@ -49594,22 +49594,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1123" t="n">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="N1123" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1123" t="n">
-        <v>1894277.7</v>
+        <v>1884865.14</v>
       </c>
       <c r="P1123" t="n">
         <v>1900</v>
       </c>
       <c r="Q1123" t="n">
-        <v>3059000</v>
+        <v>3043800</v>
       </c>
     </row>
     <row r="1124">
@@ -49682,22 +49682,22 @@
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1125" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N1125" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1125" t="n">
-        <v>365918.5</v>
+        <v>362736.6</v>
       </c>
       <c r="P1125" t="n">
         <v>5100</v>
       </c>
       <c r="Q1125" t="n">
-        <v>586500</v>
+        <v>581400</v>
       </c>
     </row>
     <row r="1126">
@@ -50251,10 +50251,10 @@
         <v>5</v>
       </c>
       <c r="N1138" t="n">
-        <v>8922.214942528701</v>
+        <v>8922.215</v>
       </c>
       <c r="O1138" t="n">
-        <v>44611.0747126435</v>
+        <v>44611.075</v>
       </c>
       <c r="P1138" t="n">
         <v>8200</v>
@@ -50637,22 +50637,22 @@
         <v>0</v>
       </c>
       <c r="L1147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1147" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N1147" t="n">
-        <v>22951.704962406</v>
+        <v>22951.704956085</v>
       </c>
       <c r="O1147" t="n">
-        <v>8836406.410526309</v>
+        <v>8813454.70313664</v>
       </c>
       <c r="P1147" t="n">
         <v>37900</v>
       </c>
       <c r="Q1147" t="n">
-        <v>14591500</v>
+        <v>14553600</v>
       </c>
     </row>
     <row r="1148">
@@ -50871,10 +50871,10 @@
         <v>1</v>
       </c>
       <c r="N1152" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="O1152" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="P1152" t="n">
         <v>2000</v>
@@ -51909,22 +51909,22 @@
         <v>0</v>
       </c>
       <c r="L1175" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M1175" t="n">
-        <v>288</v>
+        <v>202</v>
       </c>
       <c r="N1175" t="n">
         <v>7480</v>
       </c>
       <c r="O1175" t="n">
-        <v>2154240</v>
+        <v>1510960</v>
       </c>
       <c r="P1175" t="n">
         <v>9500</v>
       </c>
       <c r="Q1175" t="n">
-        <v>2736000</v>
+        <v>1919000</v>
       </c>
     </row>
     <row r="1176">
@@ -52001,22 +52001,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="M1177" t="n">
-        <v>720</v>
+        <v>581</v>
       </c>
       <c r="N1177" t="n">
         <v>9240</v>
       </c>
       <c r="O1177" t="n">
-        <v>6652800</v>
+        <v>5368440</v>
       </c>
       <c r="P1177" t="n">
         <v>11500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>8280000</v>
+        <v>6681500</v>
       </c>
     </row>
     <row r="1178">
@@ -53146,22 +53146,22 @@
         <v>0</v>
       </c>
       <c r="L1202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1202" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N1202" t="n">
         <v>6500</v>
       </c>
       <c r="O1202" t="n">
-        <v>45500</v>
+        <v>39000</v>
       </c>
       <c r="P1202" t="n">
         <v>7800</v>
       </c>
       <c r="Q1202" t="n">
-        <v>54600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="1203">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1030,22 +1030,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3059701493</v>
+        <v>1811.3062015504</v>
       </c>
       <c r="O15" t="n">
-        <v>163017.537313437</v>
+        <v>112300.9844961248</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
       </c>
       <c r="Q15" t="n">
-        <v>234000</v>
+        <v>161200</v>
       </c>
     </row>
     <row r="16">
@@ -1152,22 +1152,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N18" t="n">
-        <v>3133.3923529412</v>
+        <v>3133.3971428571</v>
       </c>
       <c r="O18" t="n">
-        <v>53267.6700000004</v>
+        <v>43867.5599999994</v>
       </c>
       <c r="P18" t="n">
         <v>6500</v>
       </c>
       <c r="Q18" t="n">
-        <v>110500</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="19">
@@ -1197,10 +1197,10 @@
         <v>1145</v>
       </c>
       <c r="N19" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O19" t="n">
-        <v>3866374.724584986</v>
+        <v>3866374.711397792</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -1358,22 +1358,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N23" t="n">
-        <v>5758.9597782705</v>
+        <v>5758.9597777778</v>
       </c>
       <c r="O23" t="n">
-        <v>195804.632461197</v>
+        <v>190045.6726666674</v>
       </c>
       <c r="P23" t="n">
         <v>16900</v>
       </c>
       <c r="Q23" t="n">
-        <v>574600</v>
+        <v>557700</v>
       </c>
     </row>
     <row r="24">
@@ -1673,22 +1673,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>20826.677105263</v>
+        <v>20826.677297297</v>
       </c>
       <c r="O31" t="n">
-        <v>20826.677105263</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>39100</v>
       </c>
       <c r="Q31" t="n">
-        <v>39100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2506,22 +2506,22 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N51" t="n">
         <v>35831.14</v>
       </c>
       <c r="O51" t="n">
-        <v>358311.4</v>
+        <v>322480.26</v>
       </c>
       <c r="P51" t="n">
         <v>62900</v>
       </c>
       <c r="Q51" t="n">
-        <v>629000</v>
+        <v>566100</v>
       </c>
     </row>
     <row r="52">
@@ -2780,22 +2780,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8546302251</v>
+        <v>6272.8546451613</v>
       </c>
       <c r="O58" t="n">
-        <v>401462.6963344064</v>
+        <v>388916.9880000006</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>505600</v>
+        <v>489800</v>
       </c>
     </row>
     <row r="59">
@@ -2824,22 +2824,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>78261.44</v>
+        <v>75815.77</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>147200</v>
+        <v>142600</v>
       </c>
     </row>
     <row r="60">
@@ -2863,22 +2863,22 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N60" t="n">
-        <v>12357.960416667</v>
+        <v>12357.96041958</v>
       </c>
       <c r="O60" t="n">
-        <v>284233.089583341</v>
+        <v>271875.12923076</v>
       </c>
       <c r="P60" t="n">
         <v>15900</v>
       </c>
       <c r="Q60" t="n">
-        <v>365700</v>
+        <v>349800</v>
       </c>
     </row>
     <row r="61">
@@ -2905,22 +2905,22 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>2717.93</v>
+        <v>2717.85</v>
       </c>
       <c r="O61" t="n">
-        <v>8153.789999999999</v>
+        <v>5435.7</v>
       </c>
       <c r="P61" t="n">
         <v>5100</v>
       </c>
       <c r="Q61" t="n">
-        <v>15300</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="62">
@@ -3267,22 +3267,22 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N70" t="n">
         <v>3526.1</v>
       </c>
       <c r="O70" t="n">
-        <v>246827</v>
+        <v>243300.9</v>
       </c>
       <c r="P70" t="n">
         <v>6300</v>
       </c>
       <c r="Q70" t="n">
-        <v>441000</v>
+        <v>434700</v>
       </c>
     </row>
     <row r="71">
@@ -3702,10 +3702,10 @@
         <v>76</v>
       </c>
       <c r="N81" t="n">
-        <v>14857.623214286</v>
+        <v>14857.623243243</v>
       </c>
       <c r="O81" t="n">
-        <v>1129179.364285736</v>
+        <v>1129179.366486468</v>
       </c>
       <c r="P81" t="n">
         <v>34900</v>
@@ -3782,22 +3782,22 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>11882.07</v>
       </c>
       <c r="O83" t="n">
-        <v>11882.07</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
         <v>21200</v>
       </c>
       <c r="Q83" t="n">
-        <v>21200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5123,10 +5123,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="O113" t="n">
-        <v>16486.408923077</v>
+        <v>16614.210542636</v>
       </c>
       <c r="P113" t="n">
         <v>30500</v>
@@ -5204,10 +5204,10 @@
         <v>15</v>
       </c>
       <c r="N115" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O115" t="n">
-        <v>235679.490126045</v>
+        <v>235679.489361705</v>
       </c>
       <c r="P115" t="n">
         <v>28500</v>
@@ -5251,10 +5251,10 @@
         <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>9392.0747222222</v>
+        <v>9392.075000000001</v>
       </c>
       <c r="O116" t="n">
-        <v>9392.0747222222</v>
+        <v>9392.075000000001</v>
       </c>
       <c r="P116" t="n">
         <v>18500</v>
@@ -5847,10 +5847,10 @@
         <v>6</v>
       </c>
       <c r="N131" t="n">
-        <v>8171.5886666667</v>
+        <v>8171.5885714286</v>
       </c>
       <c r="O131" t="n">
-        <v>49029.5320000002</v>
+        <v>49029.5314285716</v>
       </c>
       <c r="P131" t="n">
         <v>17200</v>
@@ -5941,10 +5941,10 @@
         <v>7</v>
       </c>
       <c r="N133" t="n">
-        <v>34563.464615385</v>
+        <v>34563.466</v>
       </c>
       <c r="O133" t="n">
-        <v>241944.252307695</v>
+        <v>241944.262</v>
       </c>
       <c r="P133" t="n">
         <v>55900</v>
@@ -6186,10 +6186,10 @@
         <v>6</v>
       </c>
       <c r="N139" t="n">
-        <v>36574.852195122</v>
+        <v>36574.852307692</v>
       </c>
       <c r="O139" t="n">
-        <v>219449.113170732</v>
+        <v>219449.113846152</v>
       </c>
       <c r="P139" t="n">
         <v>65900</v>
@@ -6404,22 +6404,22 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N144" t="n">
-        <v>56906.802982456</v>
+        <v>56906.803962264</v>
       </c>
       <c r="O144" t="n">
-        <v>455254.423859648</v>
+        <v>398347.627735848</v>
       </c>
       <c r="P144" t="n">
         <v>95900</v>
       </c>
       <c r="Q144" t="n">
-        <v>767200</v>
+        <v>671300</v>
       </c>
     </row>
     <row r="145">
@@ -7666,22 +7666,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M174" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N174" t="n">
         <v>3865.67</v>
       </c>
       <c r="O174" t="n">
-        <v>1151969.66</v>
+        <v>1144238.32</v>
       </c>
       <c r="P174" t="n">
         <v>5500</v>
       </c>
       <c r="Q174" t="n">
-        <v>1639000</v>
+        <v>1628000</v>
       </c>
     </row>
     <row r="175">
@@ -7711,10 +7711,10 @@
         <v>22</v>
       </c>
       <c r="N175" t="n">
-        <v>16010.3</v>
+        <v>16128.022794118</v>
       </c>
       <c r="O175" t="n">
-        <v>352226.6</v>
+        <v>354816.501470596</v>
       </c>
       <c r="P175" t="n">
         <v>30500</v>
@@ -8238,22 +8238,22 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M187" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N187" t="n">
         <v>3114.49</v>
       </c>
       <c r="O187" t="n">
-        <v>180640.42</v>
+        <v>174411.44</v>
       </c>
       <c r="P187" t="n">
         <v>5500</v>
       </c>
       <c r="Q187" t="n">
-        <v>319000</v>
+        <v>308000</v>
       </c>
     </row>
     <row r="188">
@@ -9821,22 +9821,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M224" t="n">
-        <v>9259</v>
+        <v>9256</v>
       </c>
       <c r="N224" t="n">
         <v>1726.32</v>
       </c>
       <c r="O224" t="n">
-        <v>15983996.88</v>
+        <v>15978817.92</v>
       </c>
       <c r="P224" t="n">
         <v>1500</v>
       </c>
       <c r="Q224" t="n">
-        <v>13888500</v>
+        <v>13884000</v>
       </c>
     </row>
     <row r="225">
@@ -10372,22 +10372,22 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M237" t="n">
-        <v>1102</v>
+        <v>1054</v>
       </c>
       <c r="N237" t="n">
-        <v>1098.0580436917</v>
+        <v>1098.0583408184</v>
       </c>
       <c r="O237" t="n">
-        <v>1210059.964148253</v>
+        <v>1157353.491222593</v>
       </c>
       <c r="P237" t="n">
         <v>1500</v>
       </c>
       <c r="Q237" t="n">
-        <v>1653000</v>
+        <v>1581000</v>
       </c>
     </row>
     <row r="238">
@@ -11344,10 +11344,10 @@
         <v>49</v>
       </c>
       <c r="N260" t="n">
-        <v>7569</v>
+        <v>7769.0616740088</v>
       </c>
       <c r="O260" t="n">
-        <v>370881</v>
+        <v>380684.0220264312</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>
@@ -12166,10 +12166,10 @@
         <v>999</v>
       </c>
       <c r="N279" t="n">
-        <v>2582.2558569052</v>
+        <v>2582.2558256496</v>
       </c>
       <c r="O279" t="n">
-        <v>2579673.601048294</v>
+        <v>2579673.569823951</v>
       </c>
       <c r="P279" t="n">
         <v>4500</v>
@@ -12212,10 +12212,10 @@
         <v>1417</v>
       </c>
       <c r="N280" t="n">
-        <v>5216.8961652752</v>
+        <v>5216.8961603854</v>
       </c>
       <c r="O280" t="n">
-        <v>7392341.866194958</v>
+        <v>7392341.859266113</v>
       </c>
       <c r="P280" t="n">
         <v>8500</v>
@@ -12637,10 +12637,10 @@
         <v>2830</v>
       </c>
       <c r="N290" t="n">
-        <v>3158.8608249792</v>
+        <v>3158.860825504</v>
       </c>
       <c r="O290" t="n">
-        <v>8939576.134691136</v>
+        <v>8939576.13617632</v>
       </c>
       <c r="P290" t="n">
         <v>5600</v>
@@ -12729,10 +12729,10 @@
         <v>228</v>
       </c>
       <c r="N292" t="n">
-        <v>3841.6247787611</v>
+        <v>3841.6247928994</v>
       </c>
       <c r="O292" t="n">
-        <v>875890.4495575308</v>
+        <v>875890.4527810632</v>
       </c>
       <c r="P292" t="n">
         <v>6900</v>
@@ -12911,10 +12911,10 @@
         <v>85</v>
       </c>
       <c r="N296" t="n">
-        <v>3230.0674157303</v>
+        <v>3230.0673863636</v>
       </c>
       <c r="O296" t="n">
-        <v>274555.7303370755</v>
+        <v>274555.727840906</v>
       </c>
       <c r="P296" t="n">
         <v>6200</v>
@@ -13131,10 +13131,10 @@
         <v>33</v>
       </c>
       <c r="N301" t="n">
-        <v>2694.823243369</v>
+        <v>2694.8232244517</v>
       </c>
       <c r="O301" t="n">
-        <v>88929.167031177</v>
+        <v>88929.16640690609</v>
       </c>
       <c r="P301" t="n">
         <v>4900</v>
@@ -13582,10 +13582,10 @@
         <v>468</v>
       </c>
       <c r="N311" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O311" t="n">
-        <v>1776392.283326217</v>
+        <v>1776392.283529422</v>
       </c>
       <c r="P311" t="n">
         <v>6200</v>
@@ -13971,10 +13971,10 @@
         <v>325</v>
       </c>
       <c r="N320" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O320" t="n">
-        <v>1589552.26564381</v>
+        <v>1597240.547460707</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14419,10 +14419,10 @@
         <v>45</v>
       </c>
       <c r="N330" t="n">
-        <v>7041</v>
+        <v>7095.9541463415</v>
       </c>
       <c r="O330" t="n">
-        <v>316845</v>
+        <v>319317.9365853675</v>
       </c>
       <c r="P330" t="n">
         <v>11500</v>
@@ -14511,10 +14511,10 @@
         <v>1</v>
       </c>
       <c r="N332" t="n">
-        <v>8012</v>
+        <v>8088.1838351823</v>
       </c>
       <c r="O332" t="n">
-        <v>8012</v>
+        <v>8088.1838351823</v>
       </c>
       <c r="P332" t="n">
         <v>13200</v>
@@ -14764,22 +14764,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N338" t="n">
-        <v>3594.2540740741</v>
+        <v>3594.2540520446</v>
       </c>
       <c r="O338" t="n">
-        <v>1304714.228888898</v>
+        <v>1301119.966840145</v>
       </c>
       <c r="P338" t="n">
         <v>6500</v>
       </c>
       <c r="Q338" t="n">
-        <v>2359500</v>
+        <v>2353000</v>
       </c>
     </row>
     <row r="339">
@@ -14813,22 +14813,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M339" t="n">
-        <v>853</v>
+        <v>829</v>
       </c>
       <c r="N339" t="n">
         <v>489.88</v>
       </c>
       <c r="O339" t="n">
-        <v>417867.64</v>
+        <v>406110.52</v>
       </c>
       <c r="P339" t="n">
         <v>700</v>
       </c>
       <c r="Q339" t="n">
-        <v>597100</v>
+        <v>580300</v>
       </c>
     </row>
     <row r="340">
@@ -14988,10 +14988,10 @@
         <v>5</v>
       </c>
       <c r="N343" t="n">
-        <v>4891</v>
+        <v>4913.5912240185</v>
       </c>
       <c r="O343" t="n">
-        <v>24455</v>
+        <v>24567.9561200925</v>
       </c>
       <c r="P343" t="n">
         <v>8200</v>
@@ -16063,22 +16063,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M368" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N368" t="n">
         <v>3981.47</v>
       </c>
       <c r="O368" t="n">
-        <v>613146.38</v>
+        <v>605183.4399999999</v>
       </c>
       <c r="P368" t="n">
         <v>7000</v>
       </c>
       <c r="Q368" t="n">
-        <v>1078000</v>
+        <v>1064000</v>
       </c>
     </row>
     <row r="369">
@@ -16115,10 +16115,10 @@
         <v>8137</v>
       </c>
       <c r="N369" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O369" t="n">
-        <v>35576679.18739314</v>
+        <v>35596953.68894314</v>
       </c>
       <c r="P369" t="n">
         <v>7500</v>
@@ -16235,22 +16235,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N372" t="n">
         <v>4443</v>
       </c>
       <c r="O372" t="n">
-        <v>470958</v>
+        <v>466515</v>
       </c>
       <c r="P372" t="n">
         <v>6300</v>
       </c>
       <c r="Q372" t="n">
-        <v>667800</v>
+        <v>661500</v>
       </c>
     </row>
     <row r="373">
@@ -16281,22 +16281,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N373" t="n">
-        <v>1592.5669608416</v>
+        <v>1592.5669555035</v>
       </c>
       <c r="O373" t="n">
-        <v>715062.5654178783</v>
+        <v>713469.9960655679</v>
       </c>
       <c r="P373" t="n">
         <v>3900</v>
       </c>
       <c r="Q373" t="n">
-        <v>1751100</v>
+        <v>1747200</v>
       </c>
     </row>
     <row r="374">
@@ -16971,22 +16971,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N389" t="n">
-        <v>32440</v>
+        <v>0</v>
       </c>
       <c r="O389" t="n">
-        <v>32440</v>
+        <v>0</v>
       </c>
       <c r="P389" t="n">
         <v>43900</v>
       </c>
       <c r="Q389" t="n">
-        <v>43900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -17273,22 +17273,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M396" t="n">
-        <v>2618</v>
+        <v>2576</v>
       </c>
       <c r="N396" t="n">
         <v>1387.55</v>
       </c>
       <c r="O396" t="n">
-        <v>3632605.9</v>
+        <v>3574328.8</v>
       </c>
       <c r="P396" t="n">
         <v>2300</v>
       </c>
       <c r="Q396" t="n">
-        <v>6021400</v>
+        <v>5924800</v>
       </c>
     </row>
     <row r="397">
@@ -17814,10 +17814,10 @@
         <v>1</v>
       </c>
       <c r="N408" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="O408" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="P408" t="n">
         <v>6900</v>
@@ -18417,22 +18417,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N422" t="n">
         <v>3751</v>
       </c>
       <c r="O422" t="n">
-        <v>187550</v>
+        <v>183799</v>
       </c>
       <c r="P422" t="n">
         <v>6400</v>
       </c>
       <c r="Q422" t="n">
-        <v>320000</v>
+        <v>313600</v>
       </c>
     </row>
     <row r="423">
@@ -18643,22 +18643,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M427" t="n">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="N427" t="n">
-        <v>1630.9234624043</v>
+        <v>1630.9234875283</v>
       </c>
       <c r="O427" t="n">
-        <v>740439.2519315522</v>
+        <v>727391.8754376218</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1135000</v>
+        <v>1115000</v>
       </c>
     </row>
     <row r="428">
@@ -18735,22 +18735,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M429" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="N429" t="n">
-        <v>1690.5992886179</v>
+        <v>1690.5983498584</v>
       </c>
       <c r="O429" t="n">
-        <v>82839.36514227709</v>
+        <v>23668.3768980176</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
       </c>
       <c r="Q429" t="n">
-        <v>142100</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="430">
@@ -18781,22 +18781,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M430" t="n">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="N430" t="n">
-        <v>1550.1935205388</v>
+        <v>1550.1935332762</v>
       </c>
       <c r="O430" t="n">
-        <v>1068083.335651233</v>
+        <v>1057231.989694368</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
       </c>
       <c r="Q430" t="n">
-        <v>1722500</v>
+        <v>1705000</v>
       </c>
     </row>
     <row r="431">
@@ -18827,22 +18827,22 @@
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M431" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N431" t="n">
-        <v>1579.3907948718</v>
+        <v>1579.3907235142</v>
       </c>
       <c r="O431" t="n">
-        <v>173732.987435898</v>
+        <v>168994.8074160194</v>
       </c>
       <c r="P431" t="n">
         <v>2900</v>
       </c>
       <c r="Q431" t="n">
-        <v>319000</v>
+        <v>310300</v>
       </c>
     </row>
     <row r="432">
@@ -18873,22 +18873,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M432" t="n">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="N432" t="n">
-        <v>2403.5114869613</v>
+        <v>2403.5115510508</v>
       </c>
       <c r="O432" t="n">
-        <v>1949247.815925614</v>
+        <v>1918002.217738538</v>
       </c>
       <c r="P432" t="n">
         <v>3500</v>
       </c>
       <c r="Q432" t="n">
-        <v>2838500</v>
+        <v>2793000</v>
       </c>
     </row>
     <row r="433">
@@ -18963,22 +18963,22 @@
         <v>0</v>
       </c>
       <c r="L434" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M434" t="n">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="N434" t="n">
-        <v>2521.5362299465</v>
+        <v>2521.5346723647</v>
       </c>
       <c r="O434" t="n">
-        <v>630384.057486625</v>
+        <v>610211.3907122574</v>
       </c>
       <c r="P434" t="n">
         <v>3900</v>
       </c>
       <c r="Q434" t="n">
-        <v>975000</v>
+        <v>943800</v>
       </c>
     </row>
     <row r="435">
@@ -19218,10 +19218,10 @@
         <v>169</v>
       </c>
       <c r="N440" t="n">
-        <v>1830.7563519313</v>
+        <v>1830.7553551913</v>
       </c>
       <c r="O440" t="n">
-        <v>309397.8234763897</v>
+        <v>309397.6550273297</v>
       </c>
       <c r="P440" t="n">
         <v>3150</v>
@@ -20327,22 +20327,22 @@
         <v>0</v>
       </c>
       <c r="L465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N465" t="n">
         <v>3253</v>
       </c>
       <c r="O465" t="n">
-        <v>126867</v>
+        <v>123614</v>
       </c>
       <c r="P465" t="n">
         <v>3900</v>
       </c>
       <c r="Q465" t="n">
-        <v>152100</v>
+        <v>148200</v>
       </c>
     </row>
     <row r="466">
@@ -22632,10 +22632,10 @@
         <v>1</v>
       </c>
       <c r="N519" t="n">
-        <v>5162.2539766082</v>
+        <v>5162.2539411765</v>
       </c>
       <c r="O519" t="n">
-        <v>5162.2539766082</v>
+        <v>5162.2539411765</v>
       </c>
       <c r="P519" t="n">
         <v>8200</v>
@@ -23249,22 +23249,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M534" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N534" t="n">
         <v>13152</v>
       </c>
       <c r="O534" t="n">
-        <v>1433568</v>
+        <v>1420416</v>
       </c>
       <c r="P534" t="n">
         <v>16900</v>
       </c>
       <c r="Q534" t="n">
-        <v>1842100</v>
+        <v>1825200</v>
       </c>
     </row>
     <row r="535">
@@ -23422,10 +23422,10 @@
         <v>40</v>
       </c>
       <c r="N538" t="n">
-        <v>2517.22</v>
+        <v>2528.6359637188</v>
       </c>
       <c r="O538" t="n">
-        <v>100688.8</v>
+        <v>101145.438548752</v>
       </c>
       <c r="P538" t="n">
         <v>4200</v>
@@ -23498,22 +23498,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M540" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N540" t="n">
-        <v>2029.8737350598</v>
+        <v>2029.8737443834</v>
       </c>
       <c r="O540" t="n">
-        <v>468900.8327988138</v>
+        <v>466870.961208182</v>
       </c>
       <c r="P540" t="n">
         <v>3600</v>
       </c>
       <c r="Q540" t="n">
-        <v>831600</v>
+        <v>828000</v>
       </c>
     </row>
     <row r="541">
@@ -23586,10 +23586,10 @@
         <v>1</v>
       </c>
       <c r="N542" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="O542" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="P542" t="n">
         <v>36500</v>
@@ -24705,22 +24705,22 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M569" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N569" t="n">
         <v>5894.64</v>
       </c>
       <c r="O569" t="n">
-        <v>713251.4400000001</v>
+        <v>695567.52</v>
       </c>
       <c r="P569" t="n">
         <v>11000</v>
       </c>
       <c r="Q569" t="n">
-        <v>1331000</v>
+        <v>1298000</v>
       </c>
     </row>
     <row r="570">
@@ -25681,22 +25681,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M592" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N592" t="n">
-        <v>4285.1954215582</v>
+        <v>4285.1954682454</v>
       </c>
       <c r="O592" t="n">
-        <v>1032732.096595526</v>
+        <v>1007020.935037669</v>
       </c>
       <c r="P592" t="n">
         <v>6900</v>
       </c>
       <c r="Q592" t="n">
-        <v>1662900</v>
+        <v>1621500</v>
       </c>
     </row>
     <row r="593">
@@ -25730,22 +25730,22 @@
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M593" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N593" t="n">
         <v>9776.99</v>
       </c>
       <c r="O593" t="n">
-        <v>2444247.5</v>
+        <v>2424693.52</v>
       </c>
       <c r="P593" t="n">
         <v>15900</v>
       </c>
       <c r="Q593" t="n">
-        <v>3975000</v>
+        <v>3943200</v>
       </c>
     </row>
     <row r="594">
@@ -26192,10 +26192,10 @@
         <v>201</v>
       </c>
       <c r="N604" t="n">
-        <v>4605.2146660482</v>
+        <v>4657.0557317073</v>
       </c>
       <c r="O604" t="n">
-        <v>925648.1478756883</v>
+        <v>936068.2020731673</v>
       </c>
       <c r="P604" t="n">
         <v>7600</v>
@@ -26233,10 +26233,10 @@
         <v>4</v>
       </c>
       <c r="N605" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O605" t="n">
-        <v>14364.52</v>
+        <v>14394.451279736</v>
       </c>
       <c r="P605" t="n">
         <v>6300</v>
@@ -28996,10 +28996,10 @@
         <v>377</v>
       </c>
       <c r="N670" t="n">
-        <v>1561.0000887728</v>
+        <v>1561.000152391</v>
       </c>
       <c r="O670" t="n">
-        <v>588497.0334673455</v>
+        <v>588497.057451407</v>
       </c>
       <c r="P670" t="n">
         <v>2900</v>
@@ -29292,22 +29292,22 @@
         <v>0</v>
       </c>
       <c r="L677" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M677" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N677" t="n">
         <v>10307</v>
       </c>
       <c r="O677" t="n">
-        <v>443201</v>
+        <v>432894</v>
       </c>
       <c r="P677" t="n">
         <v>13500</v>
       </c>
       <c r="Q677" t="n">
-        <v>580500</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="678">
@@ -31192,22 +31192,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N722" t="n">
         <v>2634.61</v>
       </c>
       <c r="O722" t="n">
-        <v>160711.21</v>
+        <v>158076.6</v>
       </c>
       <c r="P722" t="n">
         <v>4200</v>
       </c>
       <c r="Q722" t="n">
-        <v>256200</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="723">
@@ -31983,10 +31983,10 @@
         <v>49</v>
       </c>
       <c r="N739" t="n">
-        <v>1664.3571460424</v>
+        <v>1664.3569717514</v>
       </c>
       <c r="O739" t="n">
-        <v>81553.5001560776</v>
+        <v>81553.4916158186</v>
       </c>
       <c r="P739" t="n">
         <v>2900</v>
@@ -32947,10 +32947,10 @@
         <v>1233</v>
       </c>
       <c r="N760" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O760" t="n">
-        <v>2192856.713121554</v>
+        <v>2192856.737129421</v>
       </c>
       <c r="P760" t="n">
         <v>4900</v>
@@ -34927,22 +34927,22 @@
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M803" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N803" t="n">
         <v>7713</v>
       </c>
       <c r="O803" t="n">
-        <v>1442331</v>
+        <v>1434618</v>
       </c>
       <c r="P803" t="n">
         <v>12500</v>
       </c>
       <c r="Q803" t="n">
-        <v>2337500</v>
+        <v>2325000</v>
       </c>
     </row>
     <row r="804">
@@ -35433,22 +35433,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M814" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N814" t="n">
-        <v>2252.2966541823</v>
+        <v>2252.2966708385</v>
       </c>
       <c r="O814" t="n">
-        <v>308564.6416229751</v>
+        <v>304060.0505631975</v>
       </c>
       <c r="P814" t="n">
         <v>3900</v>
       </c>
       <c r="Q814" t="n">
-        <v>534300</v>
+        <v>526500</v>
       </c>
     </row>
     <row r="815">
@@ -35666,22 +35666,22 @@
         <v>0</v>
       </c>
       <c r="L819" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M819" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N819" t="n">
-        <v>2328.1187258454</v>
+        <v>2328.1187254606</v>
       </c>
       <c r="O819" t="n">
-        <v>1063950.257711348</v>
+        <v>1061622.138810034</v>
       </c>
       <c r="P819" t="n">
         <v>4500</v>
       </c>
       <c r="Q819" t="n">
-        <v>2056500</v>
+        <v>2052000</v>
       </c>
     </row>
     <row r="820">
@@ -36684,10 +36684,10 @@
         <v>18</v>
       </c>
       <c r="N841" t="n">
-        <v>3903.7364457831</v>
+        <v>3903.7364581763</v>
       </c>
       <c r="O841" t="n">
-        <v>70267.2560240958</v>
+        <v>70267.2562471734</v>
       </c>
       <c r="P841" t="n">
         <v>7500</v>
@@ -37139,10 +37139,10 @@
         <v>15</v>
       </c>
       <c r="N851" t="n">
-        <v>5869.1726950355</v>
+        <v>5869.172680203</v>
       </c>
       <c r="O851" t="n">
-        <v>88037.5904255325</v>
+        <v>88037.59020304499</v>
       </c>
       <c r="P851" t="n">
         <v>9500</v>
@@ -37369,10 +37369,10 @@
         <v>2</v>
       </c>
       <c r="N856" t="n">
-        <v>8637</v>
+        <v>9422.1818181818</v>
       </c>
       <c r="O856" t="n">
-        <v>17274</v>
+        <v>18844.3636363636</v>
       </c>
       <c r="P856" t="n">
         <v>14500</v>
@@ -37415,10 +37415,10 @@
         <v>4</v>
       </c>
       <c r="N857" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O857" t="n">
-        <v>26580</v>
+        <v>26667.1951886276</v>
       </c>
       <c r="P857" t="n">
         <v>10900</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L865" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M865" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N865" t="n">
         <v>8806</v>
       </c>
       <c r="O865" t="n">
-        <v>766122</v>
+        <v>757316</v>
       </c>
       <c r="P865" t="n">
         <v>14900</v>
       </c>
       <c r="Q865" t="n">
-        <v>1296300</v>
+        <v>1281400</v>
       </c>
     </row>
     <row r="866">
@@ -38465,22 +38465,22 @@
         <v>0</v>
       </c>
       <c r="L880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M880" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N880" t="n">
         <v>10755</v>
       </c>
       <c r="O880" t="n">
-        <v>2957625</v>
+        <v>2946870</v>
       </c>
       <c r="P880" t="n">
         <v>17900</v>
       </c>
       <c r="Q880" t="n">
-        <v>4922500</v>
+        <v>4904600</v>
       </c>
     </row>
     <row r="881">
@@ -39339,22 +39339,22 @@
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M899" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N899" t="n">
         <v>15472</v>
       </c>
       <c r="O899" t="n">
-        <v>247552</v>
+        <v>232080</v>
       </c>
       <c r="P899" t="n">
         <v>25900</v>
       </c>
       <c r="Q899" t="n">
-        <v>414400</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="900">
@@ -39760,10 +39760,10 @@
         <v>301</v>
       </c>
       <c r="N908" t="n">
-        <v>2458.5132504039</v>
+        <v>2477.7391560769</v>
       </c>
       <c r="O908" t="n">
-        <v>740012.488371574</v>
+        <v>745799.4859791469</v>
       </c>
       <c r="P908" t="n">
         <v>3500</v>
@@ -39806,10 +39806,10 @@
         <v>5</v>
       </c>
       <c r="N909" t="n">
-        <v>1907.3938009479</v>
+        <v>1951.7948205626</v>
       </c>
       <c r="O909" t="n">
-        <v>9536.9690047395</v>
+        <v>9758.974102813001</v>
       </c>
       <c r="P909" t="n">
         <v>2500</v>
@@ -39852,10 +39852,10 @@
         <v>109</v>
       </c>
       <c r="N910" t="n">
-        <v>1771.0905981795</v>
+        <v>1799.166010568</v>
       </c>
       <c r="O910" t="n">
-        <v>193048.8752015655</v>
+        <v>196109.095151912</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
@@ -39892,22 +39892,22 @@
         <v>0</v>
       </c>
       <c r="L911" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M911" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="N911" t="n">
-        <v>2079.3840473807</v>
+        <v>2079.3840374332</v>
       </c>
       <c r="O911" t="n">
-        <v>694514.2718251537</v>
+        <v>684117.3483155228</v>
       </c>
       <c r="P911" t="n">
         <v>2900</v>
       </c>
       <c r="Q911" t="n">
-        <v>968600</v>
+        <v>954100</v>
       </c>
     </row>
     <row r="912">
@@ -39944,10 +39944,10 @@
         <v>317</v>
       </c>
       <c r="N912" t="n">
-        <v>1803.0155591997</v>
+        <v>1817.3204760331</v>
       </c>
       <c r="O912" t="n">
-        <v>571555.9322663049</v>
+        <v>576090.5909024928</v>
       </c>
       <c r="P912" t="n">
         <v>2500</v>
@@ -39990,10 +39990,10 @@
         <v>98</v>
       </c>
       <c r="N913" t="n">
-        <v>3306.5951935915</v>
+        <v>3306.5951807229</v>
       </c>
       <c r="O913" t="n">
-        <v>324046.328971967</v>
+        <v>324046.3277108442</v>
       </c>
       <c r="P913" t="n">
         <v>4900</v>
@@ -40036,10 +40036,10 @@
         <v>108</v>
       </c>
       <c r="N914" t="n">
-        <v>2108.7914267016</v>
+        <v>2142.8043145161</v>
       </c>
       <c r="O914" t="n">
-        <v>227749.4740837728</v>
+        <v>231422.8659677388</v>
       </c>
       <c r="P914" t="n">
         <v>2900</v>
@@ -40082,10 +40082,10 @@
         <v>373</v>
       </c>
       <c r="N915" t="n">
-        <v>2056.0834183673</v>
+        <v>2056.0833654773</v>
       </c>
       <c r="O915" t="n">
-        <v>766919.1150510029</v>
+        <v>766919.0953230329</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
@@ -40128,10 +40128,10 @@
         <v>177</v>
       </c>
       <c r="N916" t="n">
-        <v>3224.5685238095</v>
+        <v>3224.5685400763</v>
       </c>
       <c r="O916" t="n">
-        <v>570748.6287142815</v>
+        <v>570748.6315935052</v>
       </c>
       <c r="P916" t="n">
         <v>4500</v>
@@ -40174,10 +40174,10 @@
         <v>235</v>
       </c>
       <c r="N917" t="n">
-        <v>1655.9309666884</v>
+        <v>1669.0127123107</v>
       </c>
       <c r="O917" t="n">
-        <v>389143.777171774</v>
+        <v>392217.9873930145</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
@@ -40355,22 +40355,22 @@
         <v>0</v>
       </c>
       <c r="L921" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M921" t="n">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="N921" t="n">
         <v>2454</v>
       </c>
       <c r="O921" t="n">
-        <v>2088354</v>
+        <v>2071176</v>
       </c>
       <c r="P921" t="n">
         <v>4200</v>
       </c>
       <c r="Q921" t="n">
-        <v>3574200</v>
+        <v>3544800</v>
       </c>
     </row>
     <row r="922">
@@ -40401,22 +40401,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M922" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="N922" t="n">
-        <v>1592.2773416667</v>
+        <v>1592.2776475694</v>
       </c>
       <c r="O922" t="n">
-        <v>773846.7880500163</v>
+        <v>767477.8261284508</v>
       </c>
       <c r="P922" t="n">
         <v>2500</v>
       </c>
       <c r="Q922" t="n">
-        <v>1215000</v>
+        <v>1205000</v>
       </c>
     </row>
     <row r="923">
@@ -40538,10 +40538,10 @@
         <v>216</v>
       </c>
       <c r="N925" t="n">
-        <v>2311.9204895105</v>
+        <v>2311.9203981265</v>
       </c>
       <c r="O925" t="n">
-        <v>499374.825734268</v>
+        <v>499374.805995324</v>
       </c>
       <c r="P925" t="n">
         <v>3500</v>
@@ -40584,10 +40584,10 @@
         <v>160</v>
       </c>
       <c r="N926" t="n">
-        <v>1906.1849324324</v>
+        <v>1906.1837238494</v>
       </c>
       <c r="O926" t="n">
-        <v>304989.589189184</v>
+        <v>304989.395815904</v>
       </c>
       <c r="P926" t="n">
         <v>2900</v>
@@ -40624,22 +40624,22 @@
         <v>0</v>
       </c>
       <c r="L927" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M927" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N927" t="n">
-        <v>3033.7213312693</v>
+        <v>3033.7208805031</v>
       </c>
       <c r="O927" t="n">
-        <v>746295.4474922478</v>
+        <v>731126.7322012471</v>
       </c>
       <c r="P927" t="n">
         <v>4500</v>
       </c>
       <c r="Q927" t="n">
-        <v>1107000</v>
+        <v>1084500</v>
       </c>
     </row>
     <row r="928">
@@ -40670,22 +40670,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M928" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N928" t="n">
-        <v>1668.628045977</v>
+        <v>1668.6281268012</v>
       </c>
       <c r="O928" t="n">
-        <v>358755.029885055</v>
+        <v>357086.4191354568</v>
       </c>
       <c r="P928" t="n">
         <v>2500</v>
       </c>
       <c r="Q928" t="n">
-        <v>537500</v>
+        <v>535000</v>
       </c>
     </row>
     <row r="929">
@@ -40722,10 +40722,10 @@
         <v>163</v>
       </c>
       <c r="N929" t="n">
-        <v>2546.9843873518</v>
+        <v>2609.1059349593</v>
       </c>
       <c r="O929" t="n">
-        <v>415158.4551383434</v>
+        <v>425284.2673983659</v>
       </c>
       <c r="P929" t="n">
         <v>3900</v>
@@ -40768,10 +40768,10 @@
         <v>1090</v>
       </c>
       <c r="N930" t="n">
-        <v>1259.2745258911</v>
+        <v>1264.6608869878</v>
       </c>
       <c r="O930" t="n">
-        <v>1372609.233221299</v>
+        <v>1378480.366816702</v>
       </c>
       <c r="P930" t="n">
         <v>1900</v>
@@ -42563,10 +42563,10 @@
         <v>351</v>
       </c>
       <c r="N969" t="n">
-        <v>2286.1647937672</v>
+        <v>2286.1647358665</v>
       </c>
       <c r="O969" t="n">
-        <v>802443.8426122873</v>
+        <v>802443.8222891415</v>
       </c>
       <c r="P969" t="n">
         <v>3000</v>
@@ -42814,22 +42814,22 @@
         <v>0</v>
       </c>
       <c r="L975" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M975" t="n">
-        <v>2179</v>
+        <v>2159</v>
       </c>
       <c r="N975" t="n">
         <v>177.65</v>
       </c>
       <c r="O975" t="n">
-        <v>387099.35</v>
+        <v>383546.35</v>
       </c>
       <c r="P975" t="n">
         <v>300</v>
       </c>
       <c r="Q975" t="n">
-        <v>653700</v>
+        <v>647700</v>
       </c>
     </row>
     <row r="976">
@@ -43077,22 +43077,22 @@
         <v>0</v>
       </c>
       <c r="L981" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M981" t="n">
-        <v>1670</v>
+        <v>1622</v>
       </c>
       <c r="N981" t="n">
-        <v>517.28908220781</v>
+        <v>517.28922545101</v>
       </c>
       <c r="O981" t="n">
-        <v>863872.7672870427</v>
+        <v>839043.1236815383</v>
       </c>
       <c r="P981" t="n">
         <v>900</v>
       </c>
       <c r="Q981" t="n">
-        <v>1503000</v>
+        <v>1459800</v>
       </c>
     </row>
     <row r="982">
@@ -43268,10 +43268,10 @@
         <v>1622</v>
       </c>
       <c r="N985" t="n">
-        <v>3110.842321894</v>
+        <v>3110.8421999117</v>
       </c>
       <c r="O985" t="n">
-        <v>5045786.246112068</v>
+        <v>5045786.048256777</v>
       </c>
       <c r="P985" t="n">
         <v>4500</v>
@@ -43394,22 +43394,22 @@
         <v>0</v>
       </c>
       <c r="L988" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M988" t="n">
-        <v>14546</v>
+        <v>14530</v>
       </c>
       <c r="N988" t="n">
-        <v>703.79521051815</v>
+        <v>703.79520622865</v>
       </c>
       <c r="O988" t="n">
-        <v>10237405.13219701</v>
+        <v>10226144.34650229</v>
       </c>
       <c r="P988" t="n">
         <v>900</v>
       </c>
       <c r="Q988" t="n">
-        <v>13091400</v>
+        <v>13077000</v>
       </c>
     </row>
     <row r="989">
@@ -44143,10 +44143,10 @@
         <v>81</v>
       </c>
       <c r="N1005" t="n">
-        <v>1595.513125523</v>
+        <v>1595.5130117944</v>
       </c>
       <c r="O1005" t="n">
-        <v>129236.563167363</v>
+        <v>129236.5539553464</v>
       </c>
       <c r="P1005" t="n">
         <v>2500</v>
@@ -44578,10 +44578,10 @@
         <v>20</v>
       </c>
       <c r="N1014" t="n">
-        <v>2098.4049570201</v>
+        <v>2098.4049712644</v>
       </c>
       <c r="O1014" t="n">
-        <v>41968.099140402</v>
+        <v>41968.099425288</v>
       </c>
       <c r="P1014" t="n">
         <v>9500</v>
@@ -45180,10 +45180,10 @@
         <v>2</v>
       </c>
       <c r="N1027" t="n">
-        <v>875.69016</v>
+        <v>875.69016806723</v>
       </c>
       <c r="O1027" t="n">
-        <v>1751.38032</v>
+        <v>1751.38033613446</v>
       </c>
       <c r="P1027" t="n">
         <v>4500</v>
@@ -45694,22 +45694,22 @@
         <v>0</v>
       </c>
       <c r="L1038" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1038" t="n">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N1038" t="n">
-        <v>3414.5660775194</v>
+        <v>3414.5660744763</v>
       </c>
       <c r="O1038" t="n">
-        <v>2827260.712186063</v>
+        <v>2823846.1435919</v>
       </c>
       <c r="P1038" t="n">
         <v>3500</v>
       </c>
       <c r="Q1038" t="n">
-        <v>2898000</v>
+        <v>2894500</v>
       </c>
     </row>
     <row r="1039">
@@ -46060,22 +46060,22 @@
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1046" t="n">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="N1046" t="n">
-        <v>1783.798877225</v>
+        <v>1783.7988767123</v>
       </c>
       <c r="O1046" t="n">
-        <v>1906880.999753525</v>
+        <v>1905097.200328736</v>
       </c>
       <c r="P1046" t="n">
         <v>1500</v>
       </c>
       <c r="Q1046" t="n">
-        <v>1603500</v>
+        <v>1602000</v>
       </c>
     </row>
     <row r="1047">
@@ -47771,10 +47771,10 @@
         <v>6</v>
       </c>
       <c r="N1082" t="n">
-        <v>8931.441000000001</v>
+        <v>8931.441052631601</v>
       </c>
       <c r="O1082" t="n">
-        <v>53588.64600000001</v>
+        <v>53588.64631578961</v>
       </c>
       <c r="P1082" t="n">
         <v>19900</v>
@@ -47907,10 +47907,10 @@
         <v>24</v>
       </c>
       <c r="N1085" t="n">
-        <v>44113.603820225</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O1085" t="n">
-        <v>1058726.4916854</v>
+        <v>1058726.492203392</v>
       </c>
       <c r="P1085" t="n">
         <v>71900</v>
@@ -48236,22 +48236,22 @@
         <v>0</v>
       </c>
       <c r="L1092" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1092" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="N1092" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1092" t="n">
-        <v>1351642.8</v>
+        <v>1333315.44</v>
       </c>
       <c r="P1092" t="n">
         <v>7900</v>
       </c>
       <c r="Q1092" t="n">
-        <v>2330500</v>
+        <v>2298900</v>
       </c>
     </row>
     <row r="1093">
@@ -49672,10 +49672,10 @@
         <v>1562</v>
       </c>
       <c r="N1125" t="n">
-        <v>1176.57</v>
+        <v>1179.3131202642</v>
       </c>
       <c r="O1125" t="n">
-        <v>1837802.34</v>
+        <v>1842087.09385268</v>
       </c>
       <c r="P1125" t="n">
         <v>1900</v>
@@ -50715,10 +50715,10 @@
         <v>382</v>
       </c>
       <c r="N1149" t="n">
-        <v>22951.704904943</v>
+        <v>22951.7048659</v>
       </c>
       <c r="O1149" t="n">
-        <v>8767551.273688225</v>
+        <v>8767551.2587738</v>
       </c>
       <c r="P1149" t="n">
         <v>37900</v>
@@ -50892,10 +50892,10 @@
         <v>4</v>
       </c>
       <c r="N1153" t="n">
-        <v>705.52800453515</v>
+        <v>705.5279984837</v>
       </c>
       <c r="O1153" t="n">
-        <v>2822.1120181406</v>
+        <v>2822.1119939348</v>
       </c>
       <c r="P1153" t="n">
         <v>1500</v>
@@ -51613,22 +51613,22 @@
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1169" t="n">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="O1169" t="n">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="P1169" t="n">
         <v>36000</v>
       </c>
       <c r="Q1169" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1170">
@@ -51981,22 +51981,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1177" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N1177" t="n">
         <v>7480</v>
       </c>
       <c r="O1177" t="n">
-        <v>920040</v>
+        <v>912560</v>
       </c>
       <c r="P1177" t="n">
         <v>9500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>1168500</v>
+        <v>1159000</v>
       </c>
     </row>
     <row r="1178">
@@ -52073,22 +52073,22 @@
         <v>0</v>
       </c>
       <c r="L1179" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1179" t="n">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="N1179" t="n">
         <v>9240</v>
       </c>
       <c r="O1179" t="n">
-        <v>3797640</v>
+        <v>3575880</v>
       </c>
       <c r="P1179" t="n">
         <v>11500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>4726500</v>
+        <v>4450500</v>
       </c>
     </row>
     <row r="1180">
@@ -53786,10 +53786,10 @@
         <v>56</v>
       </c>
       <c r="N1216" t="n">
-        <v>3306.00983</v>
+        <v>3306.00915</v>
       </c>
       <c r="O1216" t="n">
-        <v>185136.55048</v>
+        <v>185136.5124</v>
       </c>
       <c r="P1216" t="n">
         <v>4200</v>
@@ -61420,22 +61420,22 @@
         <v>0</v>
       </c>
       <c r="L1401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1401" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N1401" t="n">
         <v>4550</v>
       </c>
       <c r="O1401" t="n">
-        <v>532350</v>
+        <v>527800</v>
       </c>
       <c r="P1401" t="n">
         <v>5500</v>
       </c>
       <c r="Q1401" t="n">
-        <v>643500</v>
+        <v>638000</v>
       </c>
     </row>
     <row r="1402">
@@ -61789,10 +61789,10 @@
         <v>27</v>
       </c>
       <c r="N1409" t="n">
-        <v>2403.9772661871</v>
+        <v>2403.9772463768</v>
       </c>
       <c r="O1409" t="n">
-        <v>64907.38618705171</v>
+        <v>64907.3856521736</v>
       </c>
       <c r="P1409" t="n">
         <v>3000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -692,10 +692,10 @@
         <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>66707.99230769199</v>
+        <v>108400.4875</v>
       </c>
       <c r="O7" t="n">
-        <v>466955.946153844</v>
+        <v>758803.4125</v>
       </c>
       <c r="P7" t="n">
         <v>125900</v>
@@ -739,10 +739,10 @@
         <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>74676.64464285701</v>
+        <v>87122.75208333301</v>
       </c>
       <c r="O8" t="n">
-        <v>672089.8017857131</v>
+        <v>784104.768749997</v>
       </c>
       <c r="P8" t="n">
         <v>144900</v>
@@ -1036,10 +1036,10 @@
         <v>55</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O15" t="n">
-        <v>99621.883822362</v>
+        <v>99621.89704676</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
@@ -1191,22 +1191,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="N19" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O19" t="n">
-        <v>3866374.708087483</v>
+        <v>3852867.717800932</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
       </c>
       <c r="Q19" t="n">
-        <v>5152500</v>
+        <v>5134500</v>
       </c>
     </row>
     <row r="20">
@@ -1673,22 +1673,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N31" t="n">
-        <v>20826.677297297</v>
+        <v>20826.6775</v>
       </c>
       <c r="O31" t="n">
-        <v>249920.127567564</v>
+        <v>229093.4525</v>
       </c>
       <c r="P31" t="n">
         <v>39100</v>
       </c>
       <c r="Q31" t="n">
-        <v>469200</v>
+        <v>430100</v>
       </c>
     </row>
     <row r="32">
@@ -1720,22 +1720,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>13386</v>
       </c>
       <c r="O32" t="n">
-        <v>53544</v>
+        <v>26772</v>
       </c>
       <c r="P32" t="n">
         <v>23900</v>
       </c>
       <c r="Q32" t="n">
-        <v>95600</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="33">
@@ -2738,25 +2738,25 @@
         <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="N57" t="n">
         <v>3585</v>
       </c>
       <c r="O57" t="n">
-        <v>129060</v>
+        <v>387180</v>
       </c>
       <c r="P57" t="n">
         <v>4500</v>
       </c>
       <c r="Q57" t="n">
-        <v>162000</v>
+        <v>486000</v>
       </c>
     </row>
     <row r="58">
@@ -4123,22 +4123,22 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6281595092</v>
+        <v>3910.6281481481</v>
       </c>
       <c r="O91" t="n">
-        <v>62570.0505521472</v>
+        <v>50838.1659259253</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
       </c>
       <c r="Q91" t="n">
-        <v>145600</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="92">
@@ -7157,22 +7157,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N162" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O162" t="n">
-        <v>4995016.799676561</v>
+        <v>4933349.92648648</v>
       </c>
       <c r="P162" t="n">
         <v>98900</v>
       </c>
       <c r="Q162" t="n">
-        <v>8010900</v>
+        <v>7912000</v>
       </c>
     </row>
     <row r="163">
@@ -10333,22 +10333,22 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M236" t="n">
-        <v>1054</v>
+        <v>1043</v>
       </c>
       <c r="N236" t="n">
-        <v>1098.0593600211</v>
+        <v>1098.059452236</v>
       </c>
       <c r="O236" t="n">
-        <v>1157354.565462239</v>
+        <v>1145276.008682148</v>
       </c>
       <c r="P236" t="n">
         <v>1500</v>
       </c>
       <c r="Q236" t="n">
-        <v>1581000</v>
+        <v>1564500</v>
       </c>
     </row>
     <row r="237">
@@ -11253,22 +11253,22 @@
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M258" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="N258" t="n">
         <v>2189</v>
       </c>
       <c r="O258" t="n">
-        <v>599786</v>
+        <v>591030</v>
       </c>
       <c r="P258" t="n">
         <v>4500</v>
       </c>
       <c r="Q258" t="n">
-        <v>1233000</v>
+        <v>1215000</v>
       </c>
     </row>
     <row r="259">
@@ -11555,22 +11555,22 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M265" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N265" t="n">
         <v>13593.35</v>
       </c>
       <c r="O265" t="n">
-        <v>4159565.1</v>
+        <v>4132378.4</v>
       </c>
       <c r="P265" t="n">
         <v>25500</v>
       </c>
       <c r="Q265" t="n">
-        <v>7803000</v>
+        <v>7752000</v>
       </c>
     </row>
     <row r="266">
@@ -12121,22 +12121,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M278" t="n">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="N278" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O278" t="n">
-        <v>2499623.566825897</v>
+        <v>2458307.460089947</v>
       </c>
       <c r="P278" t="n">
         <v>4500</v>
       </c>
       <c r="Q278" t="n">
-        <v>4356000</v>
+        <v>4284000</v>
       </c>
     </row>
     <row r="279">
@@ -12167,22 +12167,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M279" t="n">
-        <v>1408</v>
+        <v>1401</v>
       </c>
       <c r="N279" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O279" t="n">
-        <v>7345389.750585498</v>
+        <v>7308871.472251544</v>
       </c>
       <c r="P279" t="n">
         <v>8500</v>
       </c>
       <c r="Q279" t="n">
-        <v>11968000</v>
+        <v>11908500</v>
       </c>
     </row>
     <row r="280">
@@ -12300,22 +12300,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M282" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N282" t="n">
-        <v>2033.5487958115</v>
+        <v>2033.5474193548</v>
       </c>
       <c r="O282" t="n">
-        <v>239958.757905757</v>
+        <v>229790.8583870924</v>
       </c>
       <c r="P282" t="n">
         <v>4100</v>
       </c>
       <c r="Q282" t="n">
-        <v>483800</v>
+        <v>463300</v>
       </c>
     </row>
     <row r="283">
@@ -12872,10 +12872,10 @@
         <v>85</v>
       </c>
       <c r="N295" t="n">
-        <v>3230.0672564612</v>
+        <v>3230.067250996</v>
       </c>
       <c r="O295" t="n">
-        <v>274555.716799202</v>
+        <v>274555.71633466</v>
       </c>
       <c r="P295" t="n">
         <v>6200</v>
@@ -13219,22 +13219,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N303" t="n">
         <v>7507.39</v>
       </c>
       <c r="O303" t="n">
-        <v>2162128.32</v>
+        <v>2154620.93</v>
       </c>
       <c r="P303" t="n">
         <v>13500</v>
       </c>
       <c r="Q303" t="n">
-        <v>3888000</v>
+        <v>3874500</v>
       </c>
     </row>
     <row r="304">
@@ -13268,22 +13268,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N304" t="n">
         <v>9664</v>
       </c>
       <c r="O304" t="n">
-        <v>347904</v>
+        <v>338240</v>
       </c>
       <c r="P304" t="n">
         <v>15900</v>
       </c>
       <c r="Q304" t="n">
-        <v>572400</v>
+        <v>556500</v>
       </c>
     </row>
     <row r="305">
@@ -13543,10 +13543,10 @@
         <v>468</v>
       </c>
       <c r="N310" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O310" t="n">
-        <v>1776392.283534055</v>
+        <v>1776392.283534757</v>
       </c>
       <c r="P310" t="n">
         <v>6200</v>
@@ -13926,22 +13926,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M319" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="N319" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O319" t="n">
-        <v>1574879.475659568</v>
+        <v>1560206.68556098</v>
       </c>
       <c r="P319" t="n">
         <v>8200</v>
       </c>
       <c r="Q319" t="n">
-        <v>2640400</v>
+        <v>2615800</v>
       </c>
     </row>
     <row r="320">
@@ -14021,22 +14021,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M321" t="n">
-        <v>769</v>
+        <v>683</v>
       </c>
       <c r="N321" t="n">
         <v>1203.38</v>
       </c>
       <c r="O321" t="n">
-        <v>925399.2200000001</v>
+        <v>821908.54</v>
       </c>
       <c r="P321" t="n">
         <v>1900</v>
       </c>
       <c r="Q321" t="n">
-        <v>1461100</v>
+        <v>1297700</v>
       </c>
     </row>
     <row r="322">
@@ -14420,22 +14420,22 @@
         <v>0</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M330" t="n">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="N330" t="n">
         <v>5667.94</v>
       </c>
       <c r="O330" t="n">
-        <v>4290630.58</v>
+        <v>4279294.699999999</v>
       </c>
       <c r="P330" t="n">
         <v>9500</v>
       </c>
       <c r="Q330" t="n">
-        <v>7191500</v>
+        <v>7172500</v>
       </c>
     </row>
     <row r="331">
@@ -14512,22 +14512,22 @@
         <v>0</v>
       </c>
       <c r="L332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M332" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N332" t="n">
         <v>8662</v>
       </c>
       <c r="O332" t="n">
-        <v>242536</v>
+        <v>225212</v>
       </c>
       <c r="P332" t="n">
         <v>14200</v>
       </c>
       <c r="Q332" t="n">
-        <v>397600</v>
+        <v>369200</v>
       </c>
     </row>
     <row r="333">
@@ -14774,22 +14774,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M338" t="n">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="N338" t="n">
         <v>489.88</v>
       </c>
       <c r="O338" t="n">
-        <v>374758.2</v>
+        <v>366920.12</v>
       </c>
       <c r="P338" t="n">
         <v>700</v>
       </c>
       <c r="Q338" t="n">
-        <v>535500</v>
+        <v>524300</v>
       </c>
     </row>
     <row r="339">
@@ -14903,10 +14903,10 @@
         <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="O341" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="P341" t="n">
         <v>5200</v>
@@ -14943,22 +14943,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N342" t="n">
         <v>4891</v>
       </c>
       <c r="O342" t="n">
-        <v>24455</v>
+        <v>19564</v>
       </c>
       <c r="P342" t="n">
         <v>8200</v>
       </c>
       <c r="Q342" t="n">
-        <v>41000</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="343">
@@ -15041,10 +15041,10 @@
         <v>288</v>
       </c>
       <c r="N344" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O344" t="n">
-        <v>4268845.109084256</v>
+        <v>4268845.108687968</v>
       </c>
       <c r="P344" t="n">
         <v>24900</v>
@@ -15893,22 +15893,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M364" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="N364" t="n">
-        <v>4242.5421445221</v>
+        <v>4242.5421749409</v>
       </c>
       <c r="O364" t="n">
-        <v>1713987.026386928</v>
+        <v>1688531.785626478</v>
       </c>
       <c r="P364" t="n">
         <v>5900</v>
       </c>
       <c r="Q364" t="n">
-        <v>2383600</v>
+        <v>2348200</v>
       </c>
     </row>
     <row r="365">
@@ -15983,22 +15983,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M366" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N366" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O366" t="n">
-        <v>380207.5016447375</v>
+        <v>349790.901523175</v>
       </c>
       <c r="P366" t="n">
         <v>5500</v>
       </c>
       <c r="Q366" t="n">
-        <v>687500</v>
+        <v>632500</v>
       </c>
     </row>
     <row r="367">
@@ -16024,22 +16024,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M367" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N367" t="n">
         <v>3981.47</v>
       </c>
       <c r="O367" t="n">
-        <v>593239.03</v>
+        <v>585276.09</v>
       </c>
       <c r="P367" t="n">
         <v>7000</v>
       </c>
       <c r="Q367" t="n">
-        <v>1043000</v>
+        <v>1029000</v>
       </c>
     </row>
     <row r="368">
@@ -16070,22 +16070,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M368" t="n">
-        <v>8135</v>
+        <v>8126</v>
       </c>
       <c r="N368" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O368" t="n">
-        <v>35567934.7735888</v>
+        <v>35528584.88060044</v>
       </c>
       <c r="P368" t="n">
         <v>7500</v>
       </c>
       <c r="Q368" t="n">
-        <v>61012500</v>
+        <v>60945000</v>
       </c>
     </row>
     <row r="369">
@@ -16242,22 +16242,22 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M372" t="n">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="N372" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O372" t="n">
-        <v>703914.5562552636</v>
+        <v>683211.1469869686</v>
       </c>
       <c r="P372" t="n">
         <v>3900</v>
       </c>
       <c r="Q372" t="n">
-        <v>1723800</v>
+        <v>1673100</v>
       </c>
     </row>
     <row r="373">
@@ -16847,22 +16847,22 @@
         <v>0</v>
       </c>
       <c r="L386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M386" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N386" t="n">
         <v>4648.6</v>
       </c>
       <c r="O386" t="n">
-        <v>1106366.8</v>
+        <v>1097069.6</v>
       </c>
       <c r="P386" t="n">
         <v>8900</v>
       </c>
       <c r="Q386" t="n">
-        <v>2118200</v>
+        <v>2100400</v>
       </c>
     </row>
     <row r="387">
@@ -17058,22 +17058,22 @@
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M391" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="N391" t="n">
         <v>1343.77</v>
       </c>
       <c r="O391" t="n">
-        <v>286223.01</v>
+        <v>275472.85</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
       </c>
       <c r="Q391" t="n">
-        <v>532500</v>
+        <v>512500</v>
       </c>
     </row>
     <row r="392">
@@ -17190,22 +17190,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M394" t="n">
-        <v>2564</v>
+        <v>2554</v>
       </c>
       <c r="N394" t="n">
         <v>1387.55</v>
       </c>
       <c r="O394" t="n">
-        <v>3557678.2</v>
+        <v>3543802.7</v>
       </c>
       <c r="P394" t="n">
         <v>2300</v>
       </c>
       <c r="Q394" t="n">
-        <v>5897200</v>
+        <v>5874200</v>
       </c>
     </row>
     <row r="395">
@@ -17415,22 +17415,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N399" t="n">
         <v>16897</v>
       </c>
       <c r="O399" t="n">
-        <v>1317966</v>
+        <v>1301069</v>
       </c>
       <c r="P399" t="n">
         <v>27900</v>
       </c>
       <c r="Q399" t="n">
-        <v>2176200</v>
+        <v>2148300</v>
       </c>
     </row>
     <row r="400">
@@ -18205,22 +18205,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M417" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N417" t="n">
-        <v>8296.642647058799</v>
+        <v>8296.6427272727</v>
       </c>
       <c r="O417" t="n">
-        <v>149339.5676470584</v>
+        <v>141042.9263636359</v>
       </c>
       <c r="P417" t="n">
         <v>15900</v>
       </c>
       <c r="Q417" t="n">
-        <v>286200</v>
+        <v>270300</v>
       </c>
     </row>
     <row r="418">
@@ -18334,22 +18334,22 @@
         <v>0</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M420" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N420" t="n">
         <v>3751</v>
       </c>
       <c r="O420" t="n">
-        <v>180048</v>
+        <v>176297</v>
       </c>
       <c r="P420" t="n">
         <v>6400</v>
       </c>
       <c r="Q420" t="n">
-        <v>307200</v>
+        <v>300800</v>
       </c>
     </row>
     <row r="421">
@@ -18560,22 +18560,22 @@
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M425" t="n">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="N425" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O425" t="n">
-        <v>707820.831224717</v>
+        <v>686618.8388787059</v>
       </c>
       <c r="P425" t="n">
         <v>2500</v>
       </c>
       <c r="Q425" t="n">
-        <v>1085000</v>
+        <v>1052500</v>
       </c>
     </row>
     <row r="426">
@@ -18652,22 +18652,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M427" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N427" t="n">
-        <v>1690.5974723655</v>
+        <v>1690.5973219585</v>
       </c>
       <c r="O427" t="n">
-        <v>23668.364613117</v>
+        <v>18596.5705415435</v>
       </c>
       <c r="P427" t="n">
         <v>2900</v>
       </c>
       <c r="Q427" t="n">
-        <v>40600</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="428">
@@ -18698,22 +18698,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M428" t="n">
-        <v>661</v>
+        <v>604</v>
       </c>
       <c r="N428" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O428" t="n">
-        <v>1024677.992753442</v>
+        <v>936316.9794712048</v>
       </c>
       <c r="P428" t="n">
         <v>2500</v>
       </c>
       <c r="Q428" t="n">
-        <v>1652500</v>
+        <v>1510000</v>
       </c>
     </row>
     <row r="429">
@@ -18744,22 +18744,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M429" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="N429" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O429" t="n">
-        <v>168994.8022597429</v>
+        <v>161097.8363684232</v>
       </c>
       <c r="P429" t="n">
         <v>2900</v>
       </c>
       <c r="Q429" t="n">
-        <v>310300</v>
+        <v>295800</v>
       </c>
     </row>
     <row r="430">
@@ -18790,22 +18790,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M430" t="n">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="N430" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O430" t="n">
-        <v>1901177.886513189</v>
+        <v>1869932.308722775</v>
       </c>
       <c r="P430" t="n">
         <v>3500</v>
       </c>
       <c r="Q430" t="n">
-        <v>2768500</v>
+        <v>2723000</v>
       </c>
     </row>
     <row r="431">
@@ -18880,22 +18880,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M432" t="n">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="N432" t="n">
-        <v>2521.5305629139</v>
+        <v>2521.5288070175</v>
       </c>
       <c r="O432" t="n">
-        <v>582473.5600331109</v>
+        <v>539607.164701745</v>
       </c>
       <c r="P432" t="n">
         <v>3900</v>
       </c>
       <c r="Q432" t="n">
-        <v>900900</v>
+        <v>834600</v>
       </c>
     </row>
     <row r="433">
@@ -20887,22 +20887,22 @@
         <v>0</v>
       </c>
       <c r="L478" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M478" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N478" t="n">
         <v>6280.31</v>
       </c>
       <c r="O478" t="n">
-        <v>37681.86</v>
+        <v>25121.24</v>
       </c>
       <c r="P478" t="n">
         <v>10500</v>
       </c>
       <c r="Q478" t="n">
-        <v>63000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="479">
@@ -22163,22 +22163,22 @@
         <v>0</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M508" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N508" t="n">
         <v>9338</v>
       </c>
       <c r="O508" t="n">
-        <v>317492</v>
+        <v>289478</v>
       </c>
       <c r="P508" t="n">
         <v>15500</v>
       </c>
       <c r="Q508" t="n">
-        <v>527000</v>
+        <v>480500</v>
       </c>
     </row>
     <row r="509">
@@ -22461,22 +22461,22 @@
         <v>0</v>
       </c>
       <c r="L515" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M515" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N515" t="n">
         <v>8538</v>
       </c>
       <c r="O515" t="n">
-        <v>85380</v>
+        <v>68304</v>
       </c>
       <c r="P515" t="n">
         <v>12900</v>
       </c>
       <c r="Q515" t="n">
-        <v>129000</v>
+        <v>103200</v>
       </c>
     </row>
     <row r="516">
@@ -22830,22 +22830,22 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M524" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N524" t="n">
         <v>1969</v>
       </c>
       <c r="O524" t="n">
-        <v>378048</v>
+        <v>372141</v>
       </c>
       <c r="P524" t="n">
         <v>1500</v>
       </c>
       <c r="Q524" t="n">
-        <v>288000</v>
+        <v>283500</v>
       </c>
     </row>
     <row r="525">
@@ -23207,22 +23207,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M533" t="n">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="N533" t="n">
         <v>6652</v>
       </c>
       <c r="O533" t="n">
-        <v>4377016</v>
+        <v>4363712</v>
       </c>
       <c r="P533" t="n">
         <v>5900</v>
       </c>
       <c r="Q533" t="n">
-        <v>3882200</v>
+        <v>3870400</v>
       </c>
     </row>
     <row r="534">
@@ -23421,10 +23421,10 @@
         <v>218</v>
       </c>
       <c r="N538" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O538" t="n">
-        <v>442512.4811953834</v>
+        <v>442512.5014822454</v>
       </c>
       <c r="P538" t="n">
         <v>3600</v>
@@ -23456,22 +23456,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M539" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N539" t="n">
         <v>3444</v>
       </c>
       <c r="O539" t="n">
-        <v>10332</v>
+        <v>6888</v>
       </c>
       <c r="P539" t="n">
         <v>2900</v>
       </c>
       <c r="Q539" t="n">
-        <v>8700</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="540">
@@ -23661,22 +23661,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M544" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N544" t="n">
         <v>2673</v>
       </c>
       <c r="O544" t="n">
-        <v>780516</v>
+        <v>769824</v>
       </c>
       <c r="P544" t="n">
         <v>2500</v>
       </c>
       <c r="Q544" t="n">
-        <v>730000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="545">
@@ -23948,22 +23948,22 @@
         <v>0</v>
       </c>
       <c r="L551" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M551" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N551" t="n">
         <v>7103</v>
       </c>
       <c r="O551" t="n">
-        <v>951802</v>
+        <v>937596</v>
       </c>
       <c r="P551" t="n">
         <v>10700</v>
       </c>
       <c r="Q551" t="n">
-        <v>1433800</v>
+        <v>1412400</v>
       </c>
     </row>
     <row r="552">
@@ -24161,22 +24161,22 @@
         <v>0</v>
       </c>
       <c r="L556" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M556" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N556" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O556" t="n">
-        <v>487894.6253218856</v>
+        <v>482533.14585636</v>
       </c>
       <c r="P556" t="n">
         <v>4900</v>
       </c>
       <c r="Q556" t="n">
-        <v>891800</v>
+        <v>882000</v>
       </c>
     </row>
     <row r="557">
@@ -24622,22 +24622,22 @@
         <v>0</v>
       </c>
       <c r="L567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M567" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N567" t="n">
         <v>5894.64</v>
       </c>
       <c r="O567" t="n">
-        <v>677883.6000000001</v>
+        <v>671988.9600000001</v>
       </c>
       <c r="P567" t="n">
         <v>11000</v>
       </c>
       <c r="Q567" t="n">
-        <v>1265000</v>
+        <v>1254000</v>
       </c>
     </row>
     <row r="568">
@@ -24745,22 +24745,22 @@
         <v>0</v>
       </c>
       <c r="L570" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M570" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N570" t="n">
         <v>2465</v>
       </c>
       <c r="O570" t="n">
-        <v>288405</v>
+        <v>281010</v>
       </c>
       <c r="P570" t="n">
         <v>3700</v>
       </c>
       <c r="Q570" t="n">
-        <v>432900</v>
+        <v>421800</v>
       </c>
     </row>
     <row r="571">
@@ -25380,22 +25380,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M585" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N585" t="n">
         <v>1589</v>
       </c>
       <c r="O585" t="n">
-        <v>49259</v>
+        <v>36547</v>
       </c>
       <c r="P585" t="n">
         <v>2700</v>
       </c>
       <c r="Q585" t="n">
-        <v>83700</v>
+        <v>62100</v>
       </c>
     </row>
     <row r="586">
@@ -25598,22 +25598,22 @@
         <v>0</v>
       </c>
       <c r="L590" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M590" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N590" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O590" t="n">
-        <v>994165.3527429751</v>
+        <v>985594.964502165</v>
       </c>
       <c r="P590" t="n">
         <v>6900</v>
       </c>
       <c r="Q590" t="n">
-        <v>1600800</v>
+        <v>1587000</v>
       </c>
     </row>
     <row r="591">
@@ -25647,22 +25647,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M591" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="N591" t="n">
         <v>9776.99</v>
       </c>
       <c r="O591" t="n">
-        <v>2405139.54</v>
+        <v>2366031.58</v>
       </c>
       <c r="P591" t="n">
         <v>15900</v>
       </c>
       <c r="Q591" t="n">
-        <v>3911400</v>
+        <v>3847800</v>
       </c>
     </row>
     <row r="592">
@@ -26109,10 +26109,10 @@
         <v>201</v>
       </c>
       <c r="N602" t="n">
-        <v>4605.2147274436</v>
+        <v>4605.2147318909</v>
       </c>
       <c r="O602" t="n">
-        <v>925648.1602161636</v>
+        <v>925648.1611100709</v>
       </c>
       <c r="P602" t="n">
         <v>7600</v>
@@ -26283,10 +26283,10 @@
         <v>89</v>
       </c>
       <c r="N606" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O606" t="n">
-        <v>1029021.424565229</v>
+        <v>1029021.424196146</v>
       </c>
       <c r="P606" t="n">
         <v>18500</v>
@@ -26329,10 +26329,10 @@
         <v>2</v>
       </c>
       <c r="N607" t="n">
-        <v>13513.643014706</v>
+        <v>13513.643059701</v>
       </c>
       <c r="O607" t="n">
-        <v>27027.286029412</v>
+        <v>27027.286119402</v>
       </c>
       <c r="P607" t="n">
         <v>21900</v>
@@ -27325,22 +27325,22 @@
         <v>0</v>
       </c>
       <c r="L631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M631" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N631" t="n">
-        <v>17534.423333333</v>
+        <v>17534.424</v>
       </c>
       <c r="O631" t="n">
-        <v>105206.539999998</v>
+        <v>87672.12</v>
       </c>
       <c r="P631" t="n">
         <v>26700</v>
       </c>
       <c r="Q631" t="n">
-        <v>160200</v>
+        <v>133500</v>
       </c>
     </row>
     <row r="632">
@@ -27709,22 +27709,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M640" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N640" t="n">
         <v>4793.53</v>
       </c>
       <c r="O640" t="n">
-        <v>1687322.56</v>
+        <v>1677735.5</v>
       </c>
       <c r="P640" t="n">
         <v>7900</v>
       </c>
       <c r="Q640" t="n">
-        <v>2780800</v>
+        <v>2765000</v>
       </c>
     </row>
     <row r="641">
@@ -27750,22 +27750,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M641" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N641" t="n">
         <v>15137.62</v>
       </c>
       <c r="O641" t="n">
-        <v>181651.44</v>
+        <v>151376.2</v>
       </c>
       <c r="P641" t="n">
         <v>31500</v>
       </c>
       <c r="Q641" t="n">
-        <v>378000</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="642">
@@ -28191,10 +28191,10 @@
         <v>142</v>
       </c>
       <c r="N651" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O651" t="n">
-        <v>3851574.661791102</v>
+        <v>3851574.659251006</v>
       </c>
       <c r="P651" t="n">
         <v>44500</v>
@@ -28477,22 +28477,22 @@
         <v>0</v>
       </c>
       <c r="L658" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M658" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N658" t="n">
         <v>16974.69</v>
       </c>
       <c r="O658" t="n">
-        <v>1408899.27</v>
+        <v>1307051.13</v>
       </c>
       <c r="P658" t="n">
         <v>26900</v>
       </c>
       <c r="Q658" t="n">
-        <v>2232700</v>
+        <v>2071300</v>
       </c>
     </row>
     <row r="659">
@@ -28907,22 +28907,22 @@
         <v>0</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M668" t="n">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="N668" t="n">
-        <v>1561.0002330508</v>
+        <v>1561.0003094984</v>
       </c>
       <c r="O668" t="n">
-        <v>583814.0871609992</v>
+        <v>561960.1114194239</v>
       </c>
       <c r="P668" t="n">
         <v>2900</v>
       </c>
       <c r="Q668" t="n">
-        <v>1084600</v>
+        <v>1044000</v>
       </c>
     </row>
     <row r="669">
@@ -29624,22 +29624,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M685" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N685" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O685" t="n">
-        <v>1330981.677875573</v>
+        <v>1315041.777583594</v>
       </c>
       <c r="P685" t="n">
         <v>12900</v>
       </c>
       <c r="Q685" t="n">
-        <v>2154300</v>
+        <v>2128500</v>
       </c>
     </row>
     <row r="686">
@@ -29788,22 +29788,22 @@
         <v>0</v>
       </c>
       <c r="L689" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M689" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N689" t="n">
         <v>17044.07</v>
       </c>
       <c r="O689" t="n">
-        <v>392013.61</v>
+        <v>357925.47</v>
       </c>
       <c r="P689" t="n">
         <v>34700</v>
       </c>
       <c r="Q689" t="n">
-        <v>798100</v>
+        <v>728700</v>
       </c>
     </row>
     <row r="690">
@@ -30976,22 +30976,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M717" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N717" t="n">
         <v>5164.33</v>
       </c>
       <c r="O717" t="n">
-        <v>475118.36</v>
+        <v>469954.03</v>
       </c>
       <c r="P717" t="n">
         <v>10200</v>
       </c>
       <c r="Q717" t="n">
-        <v>938400</v>
+        <v>928200</v>
       </c>
     </row>
     <row r="718">
@@ -31529,10 +31529,10 @@
         <v>25</v>
       </c>
       <c r="N729" t="n">
-        <v>3610.6500258065</v>
+        <v>3610.6500258732</v>
       </c>
       <c r="O729" t="n">
-        <v>90266.25064516249</v>
+        <v>90266.25064683</v>
       </c>
       <c r="P729" t="n">
         <v>5800</v>
@@ -31848,22 +31848,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M736" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N736" t="n">
-        <v>1664.355973236</v>
+        <v>1664.355782984</v>
       </c>
       <c r="O736" t="n">
-        <v>81553.442688564</v>
+        <v>66574.23131936</v>
       </c>
       <c r="P736" t="n">
         <v>2900</v>
       </c>
       <c r="Q736" t="n">
-        <v>142100</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="737">
@@ -32818,10 +32818,10 @@
         <v>1233</v>
       </c>
       <c r="N757" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O757" t="n">
-        <v>2192856.7468335</v>
+        <v>2192856.764449001</v>
       </c>
       <c r="P757" t="n">
         <v>4900</v>
@@ -32858,22 +32858,22 @@
         <v>0</v>
       </c>
       <c r="L758" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M758" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="N758" t="n">
         <v>2325</v>
       </c>
       <c r="O758" t="n">
-        <v>744000</v>
+        <v>730050</v>
       </c>
       <c r="P758" t="n">
         <v>4900</v>
       </c>
       <c r="Q758" t="n">
-        <v>1568000</v>
+        <v>1538600</v>
       </c>
     </row>
     <row r="759">
@@ -35310,10 +35310,10 @@
         <v>135</v>
       </c>
       <c r="N811" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O811" t="n">
-        <v>304060.078451619</v>
+        <v>304060.093053732</v>
       </c>
       <c r="P811" t="n">
         <v>3900</v>
@@ -35350,22 +35350,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M812" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N812" t="n">
         <v>27218</v>
       </c>
       <c r="O812" t="n">
-        <v>1143156</v>
+        <v>1115938</v>
       </c>
       <c r="P812" t="n">
         <v>43900</v>
       </c>
       <c r="Q812" t="n">
-        <v>1843800</v>
+        <v>1799900</v>
       </c>
     </row>
     <row r="813">
@@ -35445,22 +35445,22 @@
         <v>0</v>
       </c>
       <c r="L814" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M814" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N814" t="n">
         <v>21231</v>
       </c>
       <c r="O814" t="n">
-        <v>700623</v>
+        <v>679392</v>
       </c>
       <c r="P814" t="n">
         <v>34500</v>
       </c>
       <c r="Q814" t="n">
-        <v>1138500</v>
+        <v>1104000</v>
       </c>
     </row>
     <row r="815">
@@ -35543,10 +35543,10 @@
         <v>450</v>
       </c>
       <c r="N816" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O816" t="n">
-        <v>1047653.422269525</v>
+        <v>1047653.42015268</v>
       </c>
       <c r="P816" t="n">
         <v>4500</v>
@@ -35767,22 +35767,22 @@
         <v>0</v>
       </c>
       <c r="L821" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M821" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N821" t="n">
         <v>3519</v>
       </c>
       <c r="O821" t="n">
-        <v>239292</v>
+        <v>232254</v>
       </c>
       <c r="P821" t="n">
         <v>5900</v>
       </c>
       <c r="Q821" t="n">
-        <v>401200</v>
+        <v>389400</v>
       </c>
     </row>
     <row r="822">
@@ -36549,22 +36549,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M838" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N838" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O838" t="n">
-        <v>70267.25827010699</v>
+        <v>50748.576898396</v>
       </c>
       <c r="P838" t="n">
         <v>7500</v>
       </c>
       <c r="Q838" t="n">
-        <v>135000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="839">
@@ -36866,22 +36866,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M845" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N845" t="n">
         <v>11922</v>
       </c>
       <c r="O845" t="n">
-        <v>178830</v>
+        <v>166908</v>
       </c>
       <c r="P845" t="n">
         <v>19900</v>
       </c>
       <c r="Q845" t="n">
-        <v>298500</v>
+        <v>278600</v>
       </c>
     </row>
     <row r="846">
@@ -37510,22 +37510,22 @@
         <v>0</v>
       </c>
       <c r="L859" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M859" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N859" t="n">
         <v>7635</v>
       </c>
       <c r="O859" t="n">
-        <v>3443385</v>
+        <v>3435750</v>
       </c>
       <c r="P859" t="n">
         <v>13900</v>
       </c>
       <c r="Q859" t="n">
-        <v>6268900</v>
+        <v>6255000</v>
       </c>
     </row>
     <row r="860">
@@ -37556,22 +37556,22 @@
         <v>0</v>
       </c>
       <c r="L860" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M860" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N860" t="n">
         <v>5682</v>
       </c>
       <c r="O860" t="n">
-        <v>397740</v>
+        <v>380694</v>
       </c>
       <c r="P860" t="n">
         <v>9900</v>
       </c>
       <c r="Q860" t="n">
-        <v>693000</v>
+        <v>663300</v>
       </c>
     </row>
     <row r="861">
@@ -38704,22 +38704,22 @@
         <v>0</v>
       </c>
       <c r="L885" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M885" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N885" t="n">
         <v>4303</v>
       </c>
       <c r="O885" t="n">
-        <v>167817</v>
+        <v>159211</v>
       </c>
       <c r="P885" t="n">
         <v>7900</v>
       </c>
       <c r="Q885" t="n">
-        <v>308100</v>
+        <v>292300</v>
       </c>
     </row>
     <row r="886">
@@ -38888,22 +38888,22 @@
         <v>0</v>
       </c>
       <c r="L889" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M889" t="n">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="N889" t="n">
         <v>1326</v>
       </c>
       <c r="O889" t="n">
-        <v>2250222</v>
+        <v>2244918</v>
       </c>
       <c r="P889" t="n">
         <v>2500</v>
       </c>
       <c r="Q889" t="n">
-        <v>4242500</v>
+        <v>4232500</v>
       </c>
     </row>
     <row r="890">
@@ -39164,22 +39164,22 @@
         <v>0</v>
       </c>
       <c r="L895" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M895" t="n">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="N895" t="n">
         <v>3821</v>
       </c>
       <c r="O895" t="n">
-        <v>5914908</v>
+        <v>5907266</v>
       </c>
       <c r="P895" t="n">
         <v>5900</v>
       </c>
       <c r="Q895" t="n">
-        <v>9133200</v>
+        <v>9121400</v>
       </c>
     </row>
     <row r="896">
@@ -39348,22 +39348,22 @@
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M899" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N899" t="n">
         <v>4118</v>
       </c>
       <c r="O899" t="n">
-        <v>4118</v>
+        <v>0</v>
       </c>
       <c r="P899" t="n">
         <v>6900</v>
       </c>
       <c r="Q899" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="900">
@@ -39541,10 +39541,10 @@
         <v>1297</v>
       </c>
       <c r="N903" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O903" t="n">
-        <v>1966302.321878622</v>
+        <v>1966302.317609417</v>
       </c>
       <c r="P903" t="n">
         <v>2300</v>
@@ -39631,10 +39631,10 @@
         <v>297</v>
       </c>
       <c r="N905" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O905" t="n">
-        <v>730178.4150881253</v>
+        <v>730178.3842246574</v>
       </c>
       <c r="P905" t="n">
         <v>3500</v>
@@ -39723,10 +39723,10 @@
         <v>109</v>
       </c>
       <c r="N907" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O907" t="n">
-        <v>193048.8589564017</v>
+        <v>193048.8548143254</v>
       </c>
       <c r="P907" t="n">
         <v>2500</v>
@@ -39769,10 +39769,10 @@
         <v>329</v>
       </c>
       <c r="N908" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O908" t="n">
-        <v>684117.344373741</v>
+        <v>684117.3284469825</v>
       </c>
       <c r="P908" t="n">
         <v>2900</v>
@@ -39855,22 +39855,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M910" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N910" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O910" t="n">
-        <v>320739.7281081047</v>
+        <v>314126.4955752225</v>
       </c>
       <c r="P910" t="n">
         <v>4900</v>
       </c>
       <c r="Q910" t="n">
-        <v>475300</v>
+        <v>465500</v>
       </c>
     </row>
     <row r="911">
@@ -39907,10 +39907,10 @@
         <v>108</v>
       </c>
       <c r="N911" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O911" t="n">
-        <v>227749.5175609764</v>
+        <v>227749.5395727048</v>
       </c>
       <c r="P911" t="n">
         <v>2900</v>
@@ -39947,22 +39947,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M912" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="N912" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O912" t="n">
-        <v>766919.0937311063</v>
+        <v>762806.8636258603</v>
       </c>
       <c r="P912" t="n">
         <v>2900</v>
       </c>
       <c r="Q912" t="n">
-        <v>1081700</v>
+        <v>1075900</v>
       </c>
     </row>
     <row r="913">
@@ -40039,22 +40039,22 @@
         <v>0</v>
       </c>
       <c r="L914" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M914" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N914" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O914" t="n">
-        <v>389143.753335536</v>
+        <v>385831.8901982833</v>
       </c>
       <c r="P914" t="n">
         <v>2500</v>
       </c>
       <c r="Q914" t="n">
-        <v>587500</v>
+        <v>582500</v>
       </c>
     </row>
     <row r="915">
@@ -40272,22 +40272,22 @@
         <v>0</v>
       </c>
       <c r="L919" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M919" t="n">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="N919" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="O919" t="n">
-        <v>748370.7661997899</v>
+        <v>710156.2496880916</v>
       </c>
       <c r="P919" t="n">
         <v>2500</v>
       </c>
       <c r="Q919" t="n">
-        <v>1175000</v>
+        <v>1115000</v>
       </c>
     </row>
     <row r="920">
@@ -40495,22 +40495,22 @@
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M924" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N924" t="n">
-        <v>3033.7177351916</v>
+        <v>3033.7172791519</v>
       </c>
       <c r="O924" t="n">
-        <v>709889.9500348343</v>
+        <v>697754.974204937</v>
       </c>
       <c r="P924" t="n">
         <v>4500</v>
       </c>
       <c r="Q924" t="n">
-        <v>1053000</v>
+        <v>1035000</v>
       </c>
     </row>
     <row r="925">
@@ -40547,10 +40547,10 @@
         <v>214</v>
       </c>
       <c r="N925" t="n">
-        <v>1668.6302167183</v>
+        <v>1668.6318954248</v>
       </c>
       <c r="O925" t="n">
-        <v>357086.8663777162</v>
+        <v>357087.2256209072</v>
       </c>
       <c r="P925" t="n">
         <v>2500</v>
@@ -40639,10 +40639,10 @@
         <v>1090</v>
       </c>
       <c r="N927" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O927" t="n">
-        <v>1372609.254322391</v>
+        <v>1372609.256554057</v>
       </c>
       <c r="P927" t="n">
         <v>1900</v>
@@ -40862,10 +40862,10 @@
         <v>2650</v>
       </c>
       <c r="N932" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O932" t="n">
-        <v>1834203.384633911</v>
+        <v>1834203.407398444</v>
       </c>
       <c r="P932" t="n">
         <v>1200</v>
@@ -41892,10 +41892,10 @@
         <v>72</v>
       </c>
       <c r="N954" t="n">
-        <v>527.91977777778</v>
+        <v>527.92037313433</v>
       </c>
       <c r="O954" t="n">
-        <v>38010.22400000016</v>
+        <v>38010.26686567176</v>
       </c>
       <c r="P954" t="n">
         <v>1300</v>
@@ -42685,22 +42685,22 @@
         <v>0</v>
       </c>
       <c r="L972" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M972" t="n">
-        <v>1989</v>
+        <v>1779</v>
       </c>
       <c r="N972" t="n">
         <v>177.65</v>
       </c>
       <c r="O972" t="n">
-        <v>353345.85</v>
+        <v>316039.35</v>
       </c>
       <c r="P972" t="n">
         <v>300</v>
       </c>
       <c r="Q972" t="n">
-        <v>596700</v>
+        <v>533700</v>
       </c>
     </row>
     <row r="973">
@@ -42948,22 +42948,22 @@
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M978" t="n">
-        <v>1598</v>
+        <v>1454</v>
       </c>
       <c r="N978" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O978" t="n">
-        <v>826628.5119752676</v>
+        <v>752139.3435509747</v>
       </c>
       <c r="P978" t="n">
         <v>900</v>
       </c>
       <c r="Q978" t="n">
-        <v>1438200</v>
+        <v>1308600</v>
       </c>
     </row>
     <row r="979">
@@ -43133,22 +43133,22 @@
         <v>0</v>
       </c>
       <c r="L982" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M982" t="n">
-        <v>1538</v>
+        <v>1484</v>
       </c>
       <c r="N982" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O982" t="n">
-        <v>4784474.528494294</v>
+        <v>4616488.864898493</v>
       </c>
       <c r="P982" t="n">
         <v>4500</v>
       </c>
       <c r="Q982" t="n">
-        <v>6921000</v>
+        <v>6678000</v>
       </c>
     </row>
     <row r="983">
@@ -43265,22 +43265,22 @@
         <v>0</v>
       </c>
       <c r="L985" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M985" t="n">
-        <v>14345</v>
+        <v>14301</v>
       </c>
       <c r="N985" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O985" t="n">
-        <v>10095941.89832968</v>
+        <v>10064974.80762578</v>
       </c>
       <c r="P985" t="n">
         <v>900</v>
       </c>
       <c r="Q985" t="n">
-        <v>12910500</v>
+        <v>12870900</v>
       </c>
     </row>
     <row r="986">
@@ -44014,10 +44014,10 @@
         <v>81</v>
       </c>
       <c r="N1002" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O1002" t="n">
-        <v>129236.5363438566</v>
+        <v>129236.4768282885</v>
       </c>
       <c r="P1002" t="n">
         <v>2500</v>
@@ -44443,22 +44443,22 @@
         <v>0</v>
       </c>
       <c r="L1011" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1011" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N1011" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O1011" t="n">
-        <v>41968.099425288</v>
+        <v>37771.29</v>
       </c>
       <c r="P1011" t="n">
         <v>9500</v>
       </c>
       <c r="Q1011" t="n">
-        <v>190000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="1012">
@@ -44866,10 +44866,10 @@
         <v>3</v>
       </c>
       <c r="N1020" t="n">
-        <v>5796.335</v>
+        <v>5796.3355555556</v>
       </c>
       <c r="O1020" t="n">
-        <v>17389.005</v>
+        <v>17389.0066666668</v>
       </c>
       <c r="P1020" t="n">
         <v>15900</v>
@@ -44999,22 +44999,22 @@
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1023" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N1023" t="n">
         <v>2672.89</v>
       </c>
       <c r="O1023" t="n">
-        <v>173737.85</v>
+        <v>168392.07</v>
       </c>
       <c r="P1023" t="n">
         <v>10200</v>
       </c>
       <c r="Q1023" t="n">
-        <v>663000</v>
+        <v>642600</v>
       </c>
     </row>
     <row r="1024">
@@ -45333,22 +45333,22 @@
         <v>0</v>
       </c>
       <c r="L1030" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1030" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N1030" t="n">
-        <v>13121.87</v>
+        <v>0</v>
       </c>
       <c r="O1030" t="n">
-        <v>26243.74</v>
+        <v>0</v>
       </c>
       <c r="P1030" t="n">
         <v>20900</v>
       </c>
       <c r="Q1030" t="n">
-        <v>41800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1031">
@@ -47827,10 +47827,10 @@
         <v>16</v>
       </c>
       <c r="N1083" t="n">
-        <v>665.32358222629</v>
+        <v>665.32359209922</v>
       </c>
       <c r="O1083" t="n">
-        <v>10645.17731562064</v>
+        <v>10645.17747358752</v>
       </c>
       <c r="P1083" t="n">
         <v>2900</v>
@@ -48058,22 +48058,22 @@
         <v>0</v>
       </c>
       <c r="L1088" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1088" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N1088" t="n">
         <v>7811.9</v>
       </c>
       <c r="O1088" t="n">
-        <v>1999846.4</v>
+        <v>1984222.6</v>
       </c>
       <c r="P1088" t="n">
         <v>13900</v>
       </c>
       <c r="Q1088" t="n">
-        <v>3558400</v>
+        <v>3530600</v>
       </c>
     </row>
     <row r="1089">
@@ -48107,22 +48107,22 @@
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1089" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N1089" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1089" t="n">
-        <v>1319569.92</v>
+        <v>1314988.08</v>
       </c>
       <c r="P1089" t="n">
         <v>7900</v>
       </c>
       <c r="Q1089" t="n">
-        <v>2275200</v>
+        <v>2267300</v>
       </c>
     </row>
     <row r="1090">
@@ -48156,22 +48156,22 @@
         <v>0</v>
       </c>
       <c r="L1090" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1090" t="n">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N1090" t="n">
         <v>3155</v>
       </c>
       <c r="O1090" t="n">
-        <v>1249380</v>
+        <v>1243070</v>
       </c>
       <c r="P1090" t="n">
         <v>5900</v>
       </c>
       <c r="Q1090" t="n">
-        <v>2336400</v>
+        <v>2324600</v>
       </c>
     </row>
     <row r="1091">
@@ -48205,22 +48205,22 @@
         <v>0</v>
       </c>
       <c r="L1091" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1091" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="N1091" t="n">
-        <v>430.60997624703</v>
+        <v>430.6099761621</v>
       </c>
       <c r="O1091" t="n">
-        <v>44352.82755344409</v>
+        <v>41769.1676877237</v>
       </c>
       <c r="P1091" t="n">
         <v>2200</v>
       </c>
       <c r="Q1091" t="n">
-        <v>226600</v>
+        <v>213400</v>
       </c>
     </row>
     <row r="1092">
@@ -48892,22 +48892,22 @@
         <v>0</v>
       </c>
       <c r="L1107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M1107" t="n">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="N1107" t="n">
-        <v>4282.1072450249</v>
+        <v>4282.1072260488</v>
       </c>
       <c r="O1107" t="n">
-        <v>1160451.063401748</v>
+        <v>1113347.878772688</v>
       </c>
       <c r="P1107" t="n">
         <v>5300</v>
       </c>
       <c r="Q1107" t="n">
-        <v>1436300</v>
+        <v>1378000</v>
       </c>
     </row>
     <row r="1108">
@@ -49537,22 +49537,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1122" t="n">
-        <v>1541</v>
+        <v>1517</v>
       </c>
       <c r="N1122" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1122" t="n">
-        <v>1813094.37</v>
+        <v>1784856.69</v>
       </c>
       <c r="P1122" t="n">
         <v>1900</v>
       </c>
       <c r="Q1122" t="n">
-        <v>2927900</v>
+        <v>2882300</v>
       </c>
     </row>
     <row r="1123">
@@ -49625,22 +49625,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1124" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N1124" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1124" t="n">
-        <v>241824.4</v>
+        <v>235460.6</v>
       </c>
       <c r="P1124" t="n">
         <v>5100</v>
       </c>
       <c r="Q1124" t="n">
-        <v>387600</v>
+        <v>377400</v>
       </c>
     </row>
     <row r="1125">
@@ -49672,10 +49672,10 @@
         <v>125</v>
       </c>
       <c r="N1125" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O1125" t="n">
-        <v>151710.2649325625</v>
+        <v>151710.2669902875</v>
       </c>
       <c r="P1125" t="n">
         <v>1500</v>
@@ -50194,10 +50194,10 @@
         <v>3</v>
       </c>
       <c r="N1137" t="n">
-        <v>8922.2151190476</v>
+        <v>8922.2151807229</v>
       </c>
       <c r="O1137" t="n">
-        <v>26766.6453571428</v>
+        <v>26766.6455421687</v>
       </c>
       <c r="P1137" t="n">
         <v>8200</v>
@@ -50586,10 +50586,10 @@
         <v>380</v>
       </c>
       <c r="N1146" t="n">
-        <v>22951.704839538</v>
+        <v>22951.704819588</v>
       </c>
       <c r="O1146" t="n">
-        <v>8721647.839024439</v>
+        <v>8721647.83144344</v>
       </c>
       <c r="P1146" t="n">
         <v>37900</v>
@@ -51806,22 +51806,22 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1173" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N1173" t="n">
         <v>7480</v>
       </c>
       <c r="O1173" t="n">
-        <v>845240</v>
+        <v>830280</v>
       </c>
       <c r="P1173" t="n">
         <v>9500</v>
       </c>
       <c r="Q1173" t="n">
-        <v>1073500</v>
+        <v>1054500</v>
       </c>
     </row>
     <row r="1174">
@@ -51852,22 +51852,22 @@
         <v>0</v>
       </c>
       <c r="L1174" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M1174" t="n">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="N1174" t="n">
         <v>6336</v>
       </c>
       <c r="O1174" t="n">
-        <v>830016</v>
+        <v>443520</v>
       </c>
       <c r="P1174" t="n">
         <v>7500</v>
       </c>
       <c r="Q1174" t="n">
-        <v>982500</v>
+        <v>525000</v>
       </c>
     </row>
     <row r="1175">
@@ -51898,22 +51898,22 @@
         <v>0</v>
       </c>
       <c r="L1175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1175" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N1175" t="n">
         <v>5280</v>
       </c>
       <c r="O1175" t="n">
-        <v>232320</v>
+        <v>227040</v>
       </c>
       <c r="P1175" t="n">
         <v>6900</v>
       </c>
       <c r="Q1175" t="n">
-        <v>303600</v>
+        <v>296700</v>
       </c>
     </row>
     <row r="1176">
@@ -51944,22 +51944,22 @@
         <v>0</v>
       </c>
       <c r="L1176" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M1176" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="N1176" t="n">
         <v>1584</v>
       </c>
       <c r="O1176" t="n">
-        <v>304128</v>
+        <v>166320</v>
       </c>
       <c r="P1176" t="n">
         <v>2000</v>
       </c>
       <c r="Q1176" t="n">
-        <v>384000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="1177">
@@ -51990,22 +51990,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1177" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N1177" t="n">
         <v>3872</v>
       </c>
       <c r="O1177" t="n">
-        <v>511104</v>
+        <v>495616</v>
       </c>
       <c r="P1177" t="n">
         <v>4900</v>
       </c>
       <c r="Q1177" t="n">
-        <v>646800</v>
+        <v>627200</v>
       </c>
     </row>
     <row r="1178">
@@ -52036,22 +52036,22 @@
         <v>0</v>
       </c>
       <c r="L1178" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1178" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N1178" t="n">
         <v>6160</v>
       </c>
       <c r="O1178" t="n">
-        <v>369600</v>
+        <v>295680</v>
       </c>
       <c r="P1178" t="n">
         <v>7900</v>
       </c>
       <c r="Q1178" t="n">
-        <v>474000</v>
+        <v>379200</v>
       </c>
     </row>
     <row r="1179">
@@ -52082,22 +52082,22 @@
         <v>0</v>
       </c>
       <c r="L1179" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M1179" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N1179" t="n">
         <v>4400</v>
       </c>
       <c r="O1179" t="n">
-        <v>633600</v>
+        <v>563200</v>
       </c>
       <c r="P1179" t="n">
         <v>5900</v>
       </c>
       <c r="Q1179" t="n">
-        <v>849600</v>
+        <v>755200</v>
       </c>
     </row>
     <row r="1180">
@@ -52128,22 +52128,22 @@
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M1180" t="n">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="N1180" t="n">
         <v>3520</v>
       </c>
       <c r="O1180" t="n">
-        <v>661760</v>
+        <v>545600</v>
       </c>
       <c r="P1180" t="n">
         <v>4500</v>
       </c>
       <c r="Q1180" t="n">
-        <v>846000</v>
+        <v>697500</v>
       </c>
     </row>
     <row r="1181">
@@ -52220,22 +52220,22 @@
         <v>0</v>
       </c>
       <c r="L1182" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M1182" t="n">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="N1182" t="n">
         <v>9240</v>
       </c>
       <c r="O1182" t="n">
-        <v>2383920</v>
+        <v>1672440</v>
       </c>
       <c r="P1182" t="n">
         <v>11500</v>
       </c>
       <c r="Q1182" t="n">
-        <v>2967000</v>
+        <v>2081500</v>
       </c>
     </row>
     <row r="1183">
@@ -52312,22 +52312,22 @@
         <v>0</v>
       </c>
       <c r="L1184" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1184" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="N1184" t="n">
         <v>4576</v>
       </c>
       <c r="O1184" t="n">
-        <v>887744</v>
+        <v>841984</v>
       </c>
       <c r="P1184" t="n">
         <v>5900</v>
       </c>
       <c r="Q1184" t="n">
-        <v>1144600</v>
+        <v>1085600</v>
       </c>
     </row>
     <row r="1185">
@@ -52358,22 +52358,22 @@
         <v>0</v>
       </c>
       <c r="L1185" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1185" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N1185" t="n">
         <v>5280</v>
       </c>
       <c r="O1185" t="n">
-        <v>359040</v>
+        <v>327360</v>
       </c>
       <c r="P1185" t="n">
         <v>6900</v>
       </c>
       <c r="Q1185" t="n">
-        <v>469200</v>
+        <v>427800</v>
       </c>
     </row>
     <row r="1186">
@@ -54027,22 +54027,22 @@
         <v>0</v>
       </c>
       <c r="L1221" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1221" t="n">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="N1221" t="n">
-        <v>4687.974185654</v>
+        <v>4687.974206955</v>
       </c>
       <c r="O1221" t="n">
-        <v>2812784.5113924</v>
+        <v>2784656.67893127</v>
       </c>
       <c r="P1221" t="n">
         <v>5900</v>
       </c>
       <c r="Q1221" t="n">
-        <v>3540000</v>
+        <v>3504600</v>
       </c>
     </row>
     <row r="1222">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1030,22 +1030,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.307219032</v>
+        <v>1811.307345576</v>
       </c>
       <c r="O15" t="n">
-        <v>99621.89704676</v>
+        <v>79697.523205344</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
       </c>
       <c r="Q15" t="n">
-        <v>143000</v>
+        <v>114400</v>
       </c>
     </row>
     <row r="16">
@@ -1191,22 +1191,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="N19" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O19" t="n">
-        <v>3852867.717800932</v>
+        <v>3849490.970232582</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
       </c>
       <c r="Q19" t="n">
-        <v>5134500</v>
+        <v>5130000</v>
       </c>
     </row>
     <row r="20">
@@ -2702,22 +2702,22 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N56" t="n">
         <v>2812</v>
       </c>
       <c r="O56" t="n">
-        <v>939208</v>
+        <v>936396</v>
       </c>
       <c r="P56" t="n">
         <v>5000</v>
       </c>
       <c r="Q56" t="n">
-        <v>1670000</v>
+        <v>1665000</v>
       </c>
     </row>
     <row r="57">
@@ -2780,22 +2780,22 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8547682119</v>
+        <v>6272.8547761194</v>
       </c>
       <c r="O58" t="n">
-        <v>288551.3193377474</v>
+        <v>282278.464925373</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>363400</v>
+        <v>355500</v>
       </c>
     </row>
     <row r="59">
@@ -2824,22 +2824,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>68478.76000000001</v>
+        <v>63587.42</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>128800</v>
+        <v>119600</v>
       </c>
     </row>
     <row r="60">
@@ -3069,22 +3069,22 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
-        <v>22510.483333333</v>
+        <v>22510.483207547</v>
       </c>
       <c r="O65" t="n">
-        <v>135062.899999998</v>
+        <v>112552.416037735</v>
       </c>
       <c r="P65" t="n">
         <v>44900</v>
       </c>
       <c r="Q65" t="n">
-        <v>269400</v>
+        <v>224500</v>
       </c>
     </row>
     <row r="66">
@@ -6423,10 +6423,10 @@
         <v>15</v>
       </c>
       <c r="N144" t="n">
-        <v>141416.88456026</v>
+        <v>141416.88457516</v>
       </c>
       <c r="O144" t="n">
-        <v>2121253.2684039</v>
+        <v>2121253.2686274</v>
       </c>
       <c r="P144" t="n">
         <v>251900</v>
@@ -7121,10 +7121,10 @@
         <v>80</v>
       </c>
       <c r="N161" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O161" t="n">
-        <v>4933349.92737128</v>
+        <v>4933349.92915528</v>
       </c>
       <c r="P161" t="n">
         <v>98900</v>
@@ -9827,22 +9827,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N224" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O224" t="n">
-        <v>1012148.583531604</v>
+        <v>1007211.273392862</v>
       </c>
       <c r="P224" t="n">
         <v>7500</v>
       </c>
       <c r="Q224" t="n">
-        <v>1537500</v>
+        <v>1530000</v>
       </c>
     </row>
     <row r="225">
@@ -10297,10 +10297,10 @@
         <v>1043</v>
       </c>
       <c r="N235" t="n">
-        <v>1098.0595661432</v>
+        <v>1098.0597873486</v>
       </c>
       <c r="O235" t="n">
-        <v>1145276.127487358</v>
+        <v>1145276.35820459</v>
       </c>
       <c r="P235" t="n">
         <v>1500</v>
@@ -12079,22 +12079,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M277" t="n">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="N277" t="n">
-        <v>2582.2557353886</v>
+        <v>2582.2557142857</v>
       </c>
       <c r="O277" t="n">
-        <v>2458307.460089947</v>
+        <v>2409244.581428558</v>
       </c>
       <c r="P277" t="n">
         <v>4500</v>
       </c>
       <c r="Q277" t="n">
-        <v>4284000</v>
+        <v>4198500</v>
       </c>
     </row>
     <row r="278">
@@ -12131,10 +12131,10 @@
         <v>1395</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961202577</v>
+        <v>5216.8961124659</v>
       </c>
       <c r="O278" t="n">
-        <v>7277570.087759492</v>
+        <v>7277570.07688993</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
@@ -12258,22 +12258,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N281" t="n">
-        <v>2033.5474193548</v>
+        <v>2033.5471351351</v>
       </c>
       <c r="O281" t="n">
-        <v>229790.8583870924</v>
+        <v>227757.2791351312</v>
       </c>
       <c r="P281" t="n">
         <v>4100</v>
       </c>
       <c r="Q281" t="n">
-        <v>463300</v>
+        <v>459200</v>
       </c>
     </row>
     <row r="282">
@@ -12556,10 +12556,10 @@
         <v>2830</v>
       </c>
       <c r="N288" t="n">
-        <v>3158.8608260699</v>
+        <v>3158.8608262318</v>
       </c>
       <c r="O288" t="n">
-        <v>8939576.137777818</v>
+        <v>8939576.138235994</v>
       </c>
       <c r="P288" t="n">
         <v>5600</v>
@@ -12642,22 +12642,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M290" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N290" t="n">
-        <v>3841.6247928994</v>
+        <v>3841.6248214286</v>
       </c>
       <c r="O290" t="n">
-        <v>875890.4527810632</v>
+        <v>868207.2096428636</v>
       </c>
       <c r="P290" t="n">
         <v>6900</v>
       </c>
       <c r="Q290" t="n">
-        <v>1573200</v>
+        <v>1559400</v>
       </c>
     </row>
     <row r="291">
@@ -12952,22 +12952,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M297" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N297" t="n">
         <v>1480</v>
       </c>
       <c r="O297" t="n">
-        <v>438080</v>
+        <v>432160</v>
       </c>
       <c r="P297" t="n">
         <v>2600</v>
       </c>
       <c r="Q297" t="n">
-        <v>769600</v>
+        <v>759200</v>
       </c>
     </row>
     <row r="298">
@@ -13177,22 +13177,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N302" t="n">
         <v>7507.39</v>
       </c>
       <c r="O302" t="n">
-        <v>2154620.93</v>
+        <v>2147113.54</v>
       </c>
       <c r="P302" t="n">
         <v>13500</v>
       </c>
       <c r="Q302" t="n">
-        <v>3874500</v>
+        <v>3861000</v>
       </c>
     </row>
     <row r="303">
@@ -13226,22 +13226,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M303" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N303" t="n">
         <v>9664</v>
       </c>
       <c r="O303" t="n">
-        <v>338240</v>
+        <v>318912</v>
       </c>
       <c r="P303" t="n">
         <v>15900</v>
       </c>
       <c r="Q303" t="n">
-        <v>556500</v>
+        <v>524700</v>
       </c>
     </row>
     <row r="304">
@@ -13623,22 +13623,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M312" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N312" t="n">
         <v>7939.23</v>
       </c>
       <c r="O312" t="n">
-        <v>1254398.34</v>
+        <v>1246459.11</v>
       </c>
       <c r="P312" t="n">
         <v>14900</v>
       </c>
       <c r="Q312" t="n">
-        <v>2354200</v>
+        <v>2339300</v>
       </c>
     </row>
     <row r="313">
@@ -13890,10 +13890,10 @@
         <v>319</v>
       </c>
       <c r="N318" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O318" t="n">
-        <v>1560206.68556098</v>
+        <v>1560206.68557996</v>
       </c>
       <c r="P318" t="n">
         <v>8200</v>
@@ -13979,22 +13979,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M320" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="N320" t="n">
         <v>1203.38</v>
       </c>
       <c r="O320" t="n">
-        <v>821908.54</v>
+        <v>817095.02</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1297700</v>
+        <v>1290100</v>
       </c>
     </row>
     <row r="321">
@@ -14689,10 +14689,10 @@
         <v>362</v>
       </c>
       <c r="N336" t="n">
-        <v>3594.2540186916</v>
+        <v>3594.254</v>
       </c>
       <c r="O336" t="n">
-        <v>1301119.954766359</v>
+        <v>1301119.948</v>
       </c>
       <c r="P336" t="n">
         <v>6500</v>
@@ -14732,22 +14732,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M337" t="n">
-        <v>749</v>
+        <v>713</v>
       </c>
       <c r="N337" t="n">
         <v>489.88</v>
       </c>
       <c r="O337" t="n">
-        <v>366920.12</v>
+        <v>349284.44</v>
       </c>
       <c r="P337" t="n">
         <v>700</v>
       </c>
       <c r="Q337" t="n">
-        <v>524300</v>
+        <v>499100</v>
       </c>
     </row>
     <row r="338">
@@ -14861,10 +14861,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="O340" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="P340" t="n">
         <v>5200</v>
@@ -15941,22 +15941,22 @@
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M365" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N365" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O365" t="n">
-        <v>349790.901523175</v>
+        <v>337624.2614741022</v>
       </c>
       <c r="P365" t="n">
         <v>5500</v>
       </c>
       <c r="Q365" t="n">
-        <v>632500</v>
+        <v>610500</v>
       </c>
     </row>
     <row r="366">
@@ -15982,22 +15982,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M366" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N366" t="n">
         <v>3981.47</v>
       </c>
       <c r="O366" t="n">
-        <v>569350.21</v>
+        <v>561387.27</v>
       </c>
       <c r="P366" t="n">
         <v>7000</v>
       </c>
       <c r="Q366" t="n">
-        <v>1001000</v>
+        <v>987000</v>
       </c>
     </row>
     <row r="367">
@@ -16206,10 +16206,10 @@
         <v>428</v>
       </c>
       <c r="N371" t="n">
-        <v>1592.566762142</v>
+        <v>1592.5667254408</v>
       </c>
       <c r="O371" t="n">
-        <v>681618.574196776</v>
+        <v>681618.5584886624</v>
       </c>
       <c r="P371" t="n">
         <v>3900</v>
@@ -17016,22 +17016,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M390" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="N390" t="n">
         <v>1343.77</v>
       </c>
       <c r="O390" t="n">
-        <v>266066.46</v>
+        <v>249941.22</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>495000</v>
+        <v>465000</v>
       </c>
     </row>
     <row r="391">
@@ -17148,22 +17148,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M393" t="n">
-        <v>2554</v>
+        <v>2544</v>
       </c>
       <c r="N393" t="n">
         <v>1387.55</v>
       </c>
       <c r="O393" t="n">
-        <v>3543802.7</v>
+        <v>3529927.2</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
       </c>
       <c r="Q393" t="n">
-        <v>5874200</v>
+        <v>5851200</v>
       </c>
     </row>
     <row r="394">
@@ -18518,22 +18518,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M424" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N424" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O424" t="n">
-        <v>686618.8314332367</v>
+        <v>683357.0038165185</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1052500</v>
+        <v>1047500</v>
       </c>
     </row>
     <row r="425">
@@ -18616,10 +18616,10 @@
         <v>11</v>
       </c>
       <c r="N426" t="n">
-        <v>1690.5972035794</v>
+        <v>1690.5971524664</v>
       </c>
       <c r="O426" t="n">
-        <v>18596.5692393734</v>
+        <v>18596.5686771304</v>
       </c>
       <c r="P426" t="n">
         <v>2900</v>
@@ -18656,22 +18656,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M427" t="n">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="N427" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O427" t="n">
-        <v>936316.9799108563</v>
+        <v>922365.2499053405</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1510000</v>
+        <v>1487500</v>
       </c>
     </row>
     <row r="428">
@@ -18708,10 +18708,10 @@
         <v>102</v>
       </c>
       <c r="N428" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O428" t="n">
-        <v>161097.8363684232</v>
+        <v>161097.8235200034</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
@@ -18748,22 +18748,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M429" t="n">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="N429" t="n">
-        <v>2403.5119996136</v>
+        <v>2403.5120742613</v>
       </c>
       <c r="O429" t="n">
-        <v>1869932.335699381</v>
+        <v>1845897.273032678</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
       </c>
       <c r="Q429" t="n">
-        <v>2723000</v>
+        <v>2688000</v>
       </c>
     </row>
     <row r="430">
@@ -18838,22 +18838,22 @@
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M431" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N431" t="n">
-        <v>2521.52825</v>
+        <v>2530.9356343284</v>
       </c>
       <c r="O431" t="n">
-        <v>539607.0455</v>
+        <v>526434.6119403072</v>
       </c>
       <c r="P431" t="n">
         <v>3900</v>
       </c>
       <c r="Q431" t="n">
-        <v>834600</v>
+        <v>811200</v>
       </c>
     </row>
     <row r="432">
@@ -22294,10 +22294,10 @@
         <v>360</v>
       </c>
       <c r="N511" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O511" t="n">
-        <v>1510874.110482516</v>
+        <v>1510874.110735092</v>
       </c>
       <c r="P511" t="n">
         <v>5900</v>
@@ -22548,10 +22548,10 @@
         <v>6</v>
       </c>
       <c r="N517" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="O517" t="n">
-        <v>45224.83318181821</v>
+        <v>45224.8333846152</v>
       </c>
       <c r="P517" t="n">
         <v>8900</v>
@@ -23291,22 +23291,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M535" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N535" t="n">
         <v>2517.22</v>
       </c>
       <c r="O535" t="n">
-        <v>95654.35999999999</v>
+        <v>93137.14</v>
       </c>
       <c r="P535" t="n">
         <v>4200</v>
       </c>
       <c r="Q535" t="n">
-        <v>159600</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="536">
@@ -23379,10 +23379,10 @@
         <v>218</v>
       </c>
       <c r="N537" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O537" t="n">
-        <v>442512.4912150558</v>
+        <v>442512.5014822454</v>
       </c>
       <c r="P537" t="n">
         <v>3600</v>
@@ -25338,22 +25338,22 @@
         <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M584" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N584" t="n">
         <v>1589</v>
       </c>
       <c r="O584" t="n">
-        <v>36547</v>
+        <v>23835</v>
       </c>
       <c r="P584" t="n">
         <v>2700</v>
       </c>
       <c r="Q584" t="n">
-        <v>62100</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="585">
@@ -25556,22 +25556,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M589" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N589" t="n">
-        <v>4285.1955097614</v>
+        <v>4285.1955337691</v>
       </c>
       <c r="O589" t="n">
-        <v>977024.5762255992</v>
+        <v>959883.7995642783</v>
       </c>
       <c r="P589" t="n">
         <v>6900</v>
       </c>
       <c r="Q589" t="n">
-        <v>1573200</v>
+        <v>1545600</v>
       </c>
     </row>
     <row r="590">
@@ -26067,10 +26067,10 @@
         <v>201</v>
       </c>
       <c r="N601" t="n">
-        <v>4605.2147318909</v>
+        <v>4605.2147408106</v>
       </c>
       <c r="O601" t="n">
-        <v>925648.1611100709</v>
+        <v>925648.1629029306</v>
       </c>
       <c r="P601" t="n">
         <v>7600</v>
@@ -28865,22 +28865,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M667" t="n">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="N667" t="n">
-        <v>1561.0003205128</v>
+        <v>1561.0009152542</v>
       </c>
       <c r="O667" t="n">
-        <v>561960.115384608</v>
+        <v>452690.265423718</v>
       </c>
       <c r="P667" t="n">
         <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>1044000</v>
+        <v>841000</v>
       </c>
     </row>
     <row r="668">
@@ -31668,22 +31668,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M732" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N732" t="n">
         <v>5791.05</v>
       </c>
       <c r="O732" t="n">
-        <v>81074.7</v>
+        <v>75283.65000000001</v>
       </c>
       <c r="P732" t="n">
         <v>9300</v>
       </c>
       <c r="Q732" t="n">
-        <v>130200</v>
+        <v>120900</v>
       </c>
     </row>
     <row r="733">
@@ -31806,22 +31806,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M735" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N735" t="n">
-        <v>1664.355659204</v>
+        <v>1664.3554968553</v>
       </c>
       <c r="O735" t="n">
-        <v>66574.22636816</v>
+        <v>59916.7978867908</v>
       </c>
       <c r="P735" t="n">
         <v>2900</v>
       </c>
       <c r="Q735" t="n">
-        <v>116000</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="736">
@@ -32776,10 +32776,10 @@
         <v>1233</v>
       </c>
       <c r="N756" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O756" t="n">
-        <v>2192856.752684085</v>
+        <v>2192856.772339708</v>
       </c>
       <c r="P756" t="n">
         <v>4900</v>
@@ -35501,10 +35501,10 @@
         <v>450</v>
       </c>
       <c r="N815" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O815" t="n">
-        <v>1047653.42015268</v>
+        <v>1047653.419443615</v>
       </c>
       <c r="P815" t="n">
         <v>4500</v>
@@ -39453,10 +39453,10 @@
         <v>1297</v>
       </c>
       <c r="N901" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O901" t="n">
-        <v>1966302.321270199</v>
+        <v>1966302.317303454</v>
       </c>
       <c r="P901" t="n">
         <v>2300</v>
@@ -39543,10 +39543,10 @@
         <v>297</v>
       </c>
       <c r="N903" t="n">
-        <v>2458.5131328074</v>
+        <v>2458.5130759032</v>
       </c>
       <c r="O903" t="n">
-        <v>730178.4004437978</v>
+        <v>730178.3835432504</v>
       </c>
       <c r="P903" t="n">
         <v>3500</v>
@@ -39675,22 +39675,22 @@
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M906" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N906" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839709361</v>
       </c>
       <c r="O906" t="n">
-        <v>684117.344373741</v>
+        <v>677879.1745251686</v>
       </c>
       <c r="P906" t="n">
         <v>2900</v>
       </c>
       <c r="Q906" t="n">
-        <v>954100</v>
+        <v>945400</v>
       </c>
     </row>
     <row r="907">
@@ -39721,22 +39721,22 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M907" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N907" t="n">
-        <v>1803.0156051587</v>
+        <v>1803.0156237558</v>
       </c>
       <c r="O907" t="n">
-        <v>571555.9468353079</v>
+        <v>564343.8902355655</v>
       </c>
       <c r="P907" t="n">
         <v>2500</v>
       </c>
       <c r="Q907" t="n">
-        <v>792500</v>
+        <v>782500</v>
       </c>
     </row>
     <row r="908">
@@ -39767,22 +39767,22 @@
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M908" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N908" t="n">
-        <v>3306.5951153324</v>
+        <v>3306.5946745562</v>
       </c>
       <c r="O908" t="n">
-        <v>310819.9408412456</v>
+        <v>307513.3047337266</v>
       </c>
       <c r="P908" t="n">
         <v>4900</v>
       </c>
       <c r="Q908" t="n">
-        <v>460600</v>
+        <v>455700</v>
       </c>
     </row>
     <row r="909">
@@ -39819,10 +39819,10 @@
         <v>108</v>
       </c>
       <c r="N909" t="n">
-        <v>2108.7920330806</v>
+        <v>2108.792083045</v>
       </c>
       <c r="O909" t="n">
-        <v>227749.5395727048</v>
+        <v>227749.54496886</v>
       </c>
       <c r="P909" t="n">
         <v>2900</v>
@@ -39865,10 +39865,10 @@
         <v>291</v>
       </c>
       <c r="N910" t="n">
-        <v>2056.0831723454</v>
+        <v>2056.0829891304</v>
       </c>
       <c r="O910" t="n">
-        <v>598320.2031525114</v>
+        <v>598320.1498369464</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
@@ -39911,10 +39911,10 @@
         <v>156</v>
       </c>
       <c r="N911" t="n">
-        <v>3224.5688003933</v>
+        <v>3224.5688090551</v>
       </c>
       <c r="O911" t="n">
-        <v>503032.7328613548</v>
+        <v>503032.7342125956</v>
       </c>
       <c r="P911" t="n">
         <v>4500</v>
@@ -39951,22 +39951,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M912" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N912" t="n">
-        <v>1655.9308592201</v>
+        <v>1655.9308045213</v>
       </c>
       <c r="O912" t="n">
-        <v>385831.8901982833</v>
+        <v>382520.0158444203</v>
       </c>
       <c r="P912" t="n">
         <v>2500</v>
       </c>
       <c r="Q912" t="n">
-        <v>582500</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="913">
@@ -40092,22 +40092,22 @@
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M915" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N915" t="n">
         <v>1662</v>
       </c>
       <c r="O915" t="n">
-        <v>372288</v>
+        <v>365640</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
       </c>
       <c r="Q915" t="n">
-        <v>649600</v>
+        <v>638000</v>
       </c>
     </row>
     <row r="916">
@@ -40184,22 +40184,22 @@
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M917" t="n">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="N917" t="n">
-        <v>1592.2786119257</v>
+        <v>1592.2787749004</v>
       </c>
       <c r="O917" t="n">
-        <v>710156.2609188622</v>
+        <v>699010.3821812756</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
       </c>
       <c r="Q917" t="n">
-        <v>1115000</v>
+        <v>1097500</v>
       </c>
     </row>
     <row r="918">
@@ -40367,10 +40367,10 @@
         <v>159</v>
       </c>
       <c r="N921" t="n">
-        <v>1906.1836708861</v>
+        <v>1906.1834782609</v>
       </c>
       <c r="O921" t="n">
-        <v>303083.2036708899</v>
+        <v>303083.1730434831</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
@@ -40413,10 +40413,10 @@
         <v>230</v>
       </c>
       <c r="N922" t="n">
-        <v>3033.7172791519</v>
+        <v>3033.7169285714</v>
       </c>
       <c r="O922" t="n">
-        <v>697754.974204937</v>
+        <v>697754.893571422</v>
       </c>
       <c r="P922" t="n">
         <v>4500</v>
@@ -40459,10 +40459,10 @@
         <v>214</v>
       </c>
       <c r="N923" t="n">
-        <v>1668.6318954248</v>
+        <v>1668.6326421405</v>
       </c>
       <c r="O923" t="n">
-        <v>357087.2256209072</v>
+        <v>357087.385418067</v>
       </c>
       <c r="P923" t="n">
         <v>2500</v>
@@ -40499,22 +40499,22 @@
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M924" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="N924" t="n">
-        <v>2546.9839186296</v>
+        <v>2546.9838660907</v>
       </c>
       <c r="O924" t="n">
-        <v>415158.3787366248</v>
+        <v>404970.4347084213</v>
       </c>
       <c r="P924" t="n">
         <v>3900</v>
       </c>
       <c r="Q924" t="n">
-        <v>635700</v>
+        <v>620100</v>
       </c>
     </row>
     <row r="925">
@@ -40551,10 +40551,10 @@
         <v>1090</v>
       </c>
       <c r="N925" t="n">
-        <v>1259.2745472973</v>
+        <v>1259.274561681</v>
       </c>
       <c r="O925" t="n">
-        <v>1372609.256554057</v>
+        <v>1372609.27223229</v>
       </c>
       <c r="P925" t="n">
         <v>1900</v>
@@ -40730,10 +40730,10 @@
         <v>128</v>
       </c>
       <c r="N929" t="n">
-        <v>2556.7459385666</v>
+        <v>2556.7460207612</v>
       </c>
       <c r="O929" t="n">
-        <v>327263.4801365248</v>
+        <v>327263.4906574336</v>
       </c>
       <c r="P929" t="n">
         <v>3900</v>
@@ -42597,22 +42597,22 @@
         <v>0</v>
       </c>
       <c r="L970" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M970" t="n">
-        <v>1779</v>
+        <v>1749</v>
       </c>
       <c r="N970" t="n">
         <v>177.65</v>
       </c>
       <c r="O970" t="n">
-        <v>316039.35</v>
+        <v>310709.85</v>
       </c>
       <c r="P970" t="n">
         <v>300</v>
       </c>
       <c r="Q970" t="n">
-        <v>533700</v>
+        <v>524700</v>
       </c>
     </row>
     <row r="971">
@@ -42866,10 +42866,10 @@
         <v>1454</v>
       </c>
       <c r="N976" t="n">
-        <v>517.2898138359</v>
+        <v>517.28990087531</v>
       </c>
       <c r="O976" t="n">
-        <v>752139.3893173985</v>
+        <v>752139.5158727007</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
@@ -42947,22 +42947,22 @@
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M978" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N978" t="n">
         <v>7651.36</v>
       </c>
       <c r="O978" t="n">
-        <v>22954.08</v>
+        <v>15302.72</v>
       </c>
       <c r="P978" t="n">
         <v>14500</v>
       </c>
       <c r="Q978" t="n">
-        <v>43500</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="979">
@@ -43045,22 +43045,22 @@
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M980" t="n">
-        <v>1484</v>
+        <v>1428</v>
       </c>
       <c r="N980" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O980" t="n">
-        <v>4616488.819808192</v>
+        <v>4442281.523784023</v>
       </c>
       <c r="P980" t="n">
         <v>4500</v>
       </c>
       <c r="Q980" t="n">
-        <v>6678000</v>
+        <v>6426000</v>
       </c>
     </row>
     <row r="981">
@@ -43177,22 +43177,22 @@
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M983" t="n">
-        <v>14301</v>
+        <v>14249</v>
       </c>
       <c r="N983" t="n">
-        <v>703.795175</v>
+        <v>703.79516919374</v>
       </c>
       <c r="O983" t="n">
-        <v>10064974.797675</v>
+        <v>10028377.3658416</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
       </c>
       <c r="Q983" t="n">
-        <v>12870900</v>
+        <v>12824100</v>
       </c>
     </row>
     <row r="984">
@@ -43493,22 +43493,22 @@
         <v>0</v>
       </c>
       <c r="L990" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M990" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N990" t="n">
         <v>1300</v>
       </c>
       <c r="O990" t="n">
-        <v>253500</v>
+        <v>248300</v>
       </c>
       <c r="P990" t="n">
         <v>2200</v>
       </c>
       <c r="Q990" t="n">
-        <v>429000</v>
+        <v>420200</v>
       </c>
     </row>
     <row r="991">
@@ -43926,10 +43926,10 @@
         <v>81</v>
       </c>
       <c r="N1000" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O1000" t="n">
-        <v>129236.4997329258</v>
+        <v>129236.4690295194</v>
       </c>
       <c r="P1000" t="n">
         <v>2500</v>
@@ -46977,22 +46977,22 @@
         <v>0</v>
       </c>
       <c r="L1065" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1065" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1065" t="n">
         <v>7884.67</v>
       </c>
       <c r="O1065" t="n">
-        <v>15769.34</v>
+        <v>7884.67</v>
       </c>
       <c r="P1065" t="n">
         <v>49000</v>
       </c>
       <c r="Q1065" t="n">
-        <v>98000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="1066">
@@ -47410,10 +47410,10 @@
         <v>41</v>
       </c>
       <c r="N1074" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O1074" t="n">
-        <v>288924.5329538138</v>
+        <v>288924.53294472</v>
       </c>
       <c r="P1074" t="n">
         <v>9900</v>
@@ -47970,22 +47970,22 @@
         <v>0</v>
       </c>
       <c r="L1086" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1086" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N1086" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1086" t="n">
-        <v>1301242.56</v>
+        <v>1292078.88</v>
       </c>
       <c r="P1086" t="n">
         <v>7900</v>
       </c>
       <c r="Q1086" t="n">
-        <v>2243600</v>
+        <v>2227800</v>
       </c>
     </row>
     <row r="1087">
@@ -48068,22 +48068,22 @@
         <v>0</v>
       </c>
       <c r="L1088" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1088" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="N1088" t="n">
-        <v>430.6099761621</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O1088" t="n">
-        <v>41769.1676877237</v>
+        <v>39185.50782296696</v>
       </c>
       <c r="P1088" t="n">
         <v>2200</v>
       </c>
       <c r="Q1088" t="n">
-        <v>213400</v>
+        <v>200200</v>
       </c>
     </row>
     <row r="1089">
@@ -48117,22 +48117,22 @@
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1089" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="N1089" t="n">
-        <v>465.87094835681</v>
+        <v>465.87095553453</v>
       </c>
       <c r="O1089" t="n">
-        <v>80595.67406572813</v>
+        <v>76868.70766319745</v>
       </c>
       <c r="P1089" t="n">
         <v>2500</v>
       </c>
       <c r="Q1089" t="n">
-        <v>432500</v>
+        <v>412500</v>
       </c>
     </row>
     <row r="1090">
@@ -49400,22 +49400,22 @@
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1119" t="n">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="N1119" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1119" t="n">
-        <v>1784856.69</v>
+        <v>1780150.41</v>
       </c>
       <c r="P1119" t="n">
         <v>1900</v>
       </c>
       <c r="Q1119" t="n">
-        <v>2882300</v>
+        <v>2874700</v>
       </c>
     </row>
     <row r="1120">
@@ -49570,22 +49570,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1123" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N1123" t="n">
         <v>2093.95</v>
       </c>
       <c r="O1123" t="n">
-        <v>276401.4</v>
+        <v>268025.6</v>
       </c>
       <c r="P1123" t="n">
         <v>3400</v>
       </c>
       <c r="Q1123" t="n">
-        <v>448800</v>
+        <v>435200</v>
       </c>
     </row>
     <row r="1124">
@@ -50449,10 +50449,10 @@
         <v>380</v>
       </c>
       <c r="N1143" t="n">
-        <v>22951.704812903</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O1143" t="n">
-        <v>8721647.828903141</v>
+        <v>8721647.82380354</v>
       </c>
       <c r="P1143" t="n">
         <v>37900</v>
@@ -51669,22 +51669,22 @@
         <v>0</v>
       </c>
       <c r="L1170" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M1170" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="N1170" t="n">
         <v>7480</v>
       </c>
       <c r="O1170" t="n">
-        <v>830280</v>
+        <v>650760</v>
       </c>
       <c r="P1170" t="n">
         <v>9500</v>
       </c>
       <c r="Q1170" t="n">
-        <v>1054500</v>
+        <v>826500</v>
       </c>
     </row>
     <row r="1171">
@@ -51715,22 +51715,22 @@
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1171" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="N1171" t="n">
         <v>6336</v>
       </c>
       <c r="O1171" t="n">
-        <v>443520</v>
+        <v>329472</v>
       </c>
       <c r="P1171" t="n">
         <v>7500</v>
       </c>
       <c r="Q1171" t="n">
-        <v>525000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="1172">
@@ -51807,22 +51807,22 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M1173" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="N1173" t="n">
         <v>1584</v>
       </c>
       <c r="O1173" t="n">
-        <v>128304</v>
+        <v>102960</v>
       </c>
       <c r="P1173" t="n">
         <v>2000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>162000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="1174">
@@ -51991,22 +51991,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1177" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N1177" t="n">
         <v>3520</v>
       </c>
       <c r="O1177" t="n">
-        <v>545600</v>
+        <v>531520</v>
       </c>
       <c r="P1177" t="n">
         <v>4500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>697500</v>
+        <v>679500</v>
       </c>
     </row>
     <row r="1178">
@@ -52083,22 +52083,22 @@
         <v>0</v>
       </c>
       <c r="L1179" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M1179" t="n">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="N1179" t="n">
         <v>9240</v>
       </c>
       <c r="O1179" t="n">
-        <v>1672440</v>
+        <v>997920</v>
       </c>
       <c r="P1179" t="n">
         <v>11500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>2081500</v>
+        <v>1242000</v>
       </c>
     </row>
     <row r="1180">
@@ -52175,22 +52175,22 @@
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1181" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="N1181" t="n">
         <v>4576</v>
       </c>
       <c r="O1181" t="n">
-        <v>841984</v>
+        <v>828256</v>
       </c>
       <c r="P1181" t="n">
         <v>5900</v>
       </c>
       <c r="Q1181" t="n">
-        <v>1085600</v>
+        <v>1067900</v>
       </c>
     </row>
     <row r="1182">
@@ -52405,22 +52405,22 @@
         <v>0</v>
       </c>
       <c r="L1186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1186" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N1186" t="n">
         <v>25000</v>
       </c>
       <c r="O1186" t="n">
-        <v>375000</v>
+        <v>350000</v>
       </c>
       <c r="P1186" t="n">
         <v>30000</v>
       </c>
       <c r="Q1186" t="n">
-        <v>450000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="1187">
@@ -53890,22 +53890,22 @@
         <v>0</v>
       </c>
       <c r="L1218" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1218" t="n">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="N1218" t="n">
-        <v>4687.9742393162</v>
+        <v>4687.9742611684</v>
       </c>
       <c r="O1218" t="n">
-        <v>2742464.929999977</v>
+        <v>2714337.097216503</v>
       </c>
       <c r="P1218" t="n">
         <v>5900</v>
       </c>
       <c r="Q1218" t="n">
-        <v>3451500</v>
+        <v>3416100</v>
       </c>
     </row>
     <row r="1219">
@@ -53936,22 +53936,22 @@
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1219" t="n">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="N1219" t="n">
-        <v>4171.6687</v>
+        <v>4171.6686912752</v>
       </c>
       <c r="O1219" t="n">
-        <v>2736614.6672</v>
+        <v>2711584.64932888</v>
       </c>
       <c r="P1219" t="n">
         <v>5500</v>
       </c>
       <c r="Q1219" t="n">
-        <v>3608000</v>
+        <v>3575000</v>
       </c>
     </row>
     <row r="1220">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1024,13 +1024,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>44</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>1140</v>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>333</v>
@@ -2774,13 +2774,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>45</v>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>26</v>
@@ -3063,13 +3063,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>5</v>
@@ -4087,10 +4087,10 @@
         <v>11</v>
       </c>
       <c r="N90" t="n">
-        <v>3910.6281404959</v>
+        <v>3910.628136646</v>
       </c>
       <c r="O90" t="n">
-        <v>43016.9095454549</v>
+        <v>43016.909503106</v>
       </c>
       <c r="P90" t="n">
         <v>9100</v>
@@ -9821,13 +9821,13 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
         <v>204</v>
@@ -12073,28 +12073,28 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>952</v>
+        <v>921</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="N277" t="n">
-        <v>2582.2557142857</v>
+        <v>2582.2556563454</v>
       </c>
       <c r="O277" t="n">
-        <v>2409244.581428558</v>
+        <v>2378257.459494113</v>
       </c>
       <c r="P277" t="n">
         <v>4500</v>
       </c>
       <c r="Q277" t="n">
-        <v>4198500</v>
+        <v>4144500</v>
       </c>
     </row>
     <row r="278">
@@ -12131,10 +12131,10 @@
         <v>1395</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961124659</v>
+        <v>5216.8961063218</v>
       </c>
       <c r="O278" t="n">
-        <v>7277570.07688993</v>
+        <v>7277570.068318912</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
@@ -12252,13 +12252,13 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>112</v>
@@ -12636,13 +12636,13 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
         <v>226</v>
@@ -12946,13 +12946,13 @@
         </is>
       </c>
       <c r="J297" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K297" t="n">
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
         <v>292</v>
@@ -13171,13 +13171,13 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
         <v>286</v>
@@ -13220,13 +13220,13 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>33</v>
@@ -13617,13 +13617,13 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>157</v>
@@ -13890,10 +13890,10 @@
         <v>319</v>
       </c>
       <c r="N318" t="n">
-        <v>4890.93004884</v>
+        <v>4890.9300488998</v>
       </c>
       <c r="O318" t="n">
-        <v>1560206.68557996</v>
+        <v>1560206.685599036</v>
       </c>
       <c r="P318" t="n">
         <v>8200</v>
@@ -13973,28 +13973,28 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="N320" t="n">
         <v>1203.38</v>
       </c>
       <c r="O320" t="n">
-        <v>817095.02</v>
+        <v>788213.9</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1290100</v>
+        <v>1244500</v>
       </c>
     </row>
     <row r="321">
@@ -14019,7 +14019,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14028,19 +14028,19 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N321" t="n">
         <v>3472</v>
       </c>
       <c r="O321" t="n">
-        <v>458304</v>
+        <v>437472</v>
       </c>
       <c r="P321" t="n">
         <v>4800</v>
       </c>
       <c r="Q321" t="n">
-        <v>633600</v>
+        <v>604800</v>
       </c>
     </row>
     <row r="322">
@@ -14372,7 +14372,7 @@
         </is>
       </c>
       <c r="J329" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -14381,19 +14381,19 @@
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="N329" t="n">
         <v>5667.94</v>
       </c>
       <c r="O329" t="n">
-        <v>4279294.699999999</v>
+        <v>4273626.76</v>
       </c>
       <c r="P329" t="n">
         <v>9500</v>
       </c>
       <c r="Q329" t="n">
-        <v>7172500</v>
+        <v>7163000</v>
       </c>
     </row>
     <row r="330">
@@ -14726,13 +14726,13 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>749</v>
+        <v>713</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
         <v>713</v>
@@ -14861,10 +14861,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>3240.850037037</v>
+        <v>3240.8500371058</v>
       </c>
       <c r="O340" t="n">
-        <v>3240.850037037</v>
+        <v>3240.8500371058</v>
       </c>
       <c r="P340" t="n">
         <v>5200</v>
@@ -15254,10 +15254,10 @@
         <v>198</v>
       </c>
       <c r="N349" t="n">
-        <v>5191.4800278552</v>
+        <v>5191.4800280899</v>
       </c>
       <c r="O349" t="n">
-        <v>1027913.04551533</v>
+        <v>1027913.0455618</v>
       </c>
       <c r="P349" t="n">
         <v>9100</v>
@@ -15935,13 +15935,13 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M365" t="n">
         <v>111</v>
@@ -15976,13 +15976,13 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M366" t="n">
         <v>141</v>
@@ -16034,10 +16034,10 @@
         <v>8126</v>
       </c>
       <c r="N367" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O367" t="n">
-        <v>35528584.88151624</v>
+        <v>35528584.88243204</v>
       </c>
       <c r="P367" t="n">
         <v>7500</v>
@@ -17010,13 +17010,13 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M390" t="n">
         <v>186</v>
@@ -17142,28 +17142,28 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>2554</v>
+        <v>2520</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>2544</v>
+        <v>2520</v>
       </c>
       <c r="N393" t="n">
         <v>1387.55</v>
       </c>
       <c r="O393" t="n">
-        <v>3529927.2</v>
+        <v>3496626</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
       </c>
       <c r="Q393" t="n">
-        <v>5851200</v>
+        <v>5796000</v>
       </c>
     </row>
     <row r="394">
@@ -18512,22 +18512,22 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M424" t="n">
         <v>419</v>
       </c>
       <c r="N424" t="n">
-        <v>1630.9236367936</v>
+        <v>1630.9236471425</v>
       </c>
       <c r="O424" t="n">
-        <v>683357.0038165185</v>
+        <v>683357.0081527075</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -18613,19 +18613,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N426" t="n">
-        <v>1690.5971524664</v>
+        <v>1690.5969977427</v>
       </c>
       <c r="O426" t="n">
-        <v>18596.5686771304</v>
+        <v>13524.7759819416</v>
       </c>
       <c r="P426" t="n">
         <v>2900</v>
       </c>
       <c r="Q426" t="n">
-        <v>31900</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="427">
@@ -18650,28 +18650,28 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>604</v>
+        <v>589</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="N427" t="n">
-        <v>1550.1936973199</v>
+        <v>1550.1936995315</v>
       </c>
       <c r="O427" t="n">
-        <v>922365.2499053405</v>
+        <v>913064.0890240535</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1487500</v>
+        <v>1472500</v>
       </c>
     </row>
     <row r="428">
@@ -18742,22 +18742,22 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M429" t="n">
         <v>768</v>
       </c>
       <c r="N429" t="n">
-        <v>2403.5120742613</v>
+        <v>2403.5121001364</v>
       </c>
       <c r="O429" t="n">
-        <v>1845897.273032678</v>
+        <v>1845897.292904755</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
@@ -18832,22 +18832,22 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M431" t="n">
         <v>208</v>
       </c>
       <c r="N431" t="n">
-        <v>2530.9356343284</v>
+        <v>2521.5268283582</v>
       </c>
       <c r="O431" t="n">
-        <v>526434.6119403072</v>
+        <v>524477.5802985056</v>
       </c>
       <c r="P431" t="n">
         <v>3900</v>
@@ -20196,7 +20196,7 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
@@ -20205,19 +20205,19 @@
         <v>0</v>
       </c>
       <c r="M462" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N462" t="n">
         <v>3253</v>
       </c>
       <c r="O462" t="n">
-        <v>123614</v>
+        <v>104096</v>
       </c>
       <c r="P462" t="n">
         <v>3900</v>
       </c>
       <c r="Q462" t="n">
-        <v>148200</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="463">
@@ -20629,7 +20629,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -20638,19 +20638,19 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N472" t="n">
         <v>3253</v>
       </c>
       <c r="O472" t="n">
-        <v>91084</v>
+        <v>71566</v>
       </c>
       <c r="P472" t="n">
         <v>3900</v>
       </c>
       <c r="Q472" t="n">
-        <v>109200</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="473">
@@ -23285,13 +23285,13 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M535" t="n">
         <v>37</v>
@@ -24125,10 +24125,10 @@
         <v>180</v>
       </c>
       <c r="N555" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O555" t="n">
-        <v>482533.145789796</v>
+        <v>482533.14511512</v>
       </c>
       <c r="P555" t="n">
         <v>4900</v>
@@ -25332,13 +25332,13 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M584" t="n">
         <v>15</v>
@@ -25550,13 +25550,13 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M589" t="n">
         <v>224</v>
@@ -26241,10 +26241,10 @@
         <v>89</v>
       </c>
       <c r="N605" t="n">
-        <v>11562.038474114</v>
+        <v>11562.038465753</v>
       </c>
       <c r="O605" t="n">
-        <v>1029021.424196146</v>
+        <v>1029021.423452017</v>
       </c>
       <c r="P605" t="n">
         <v>18500</v>
@@ -26287,10 +26287,10 @@
         <v>2</v>
       </c>
       <c r="N606" t="n">
-        <v>13513.643059701</v>
+        <v>13513.643082707</v>
       </c>
       <c r="O606" t="n">
-        <v>27027.286119402</v>
+        <v>27027.286165414</v>
       </c>
       <c r="P606" t="n">
         <v>21900</v>
@@ -28859,28 +28859,28 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N667" t="n">
-        <v>1561.0009152542</v>
+        <v>1561.0009337861</v>
       </c>
       <c r="O667" t="n">
-        <v>452690.265423718</v>
+        <v>448007.2679966107</v>
       </c>
       <c r="P667" t="n">
         <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>841000</v>
+        <v>832300</v>
       </c>
     </row>
     <row r="668">
@@ -31662,13 +31662,13 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M732" t="n">
         <v>13</v>
@@ -31708,7 +31708,7 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
@@ -31717,19 +31717,19 @@
         <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N733" t="n">
         <v>10977.27</v>
       </c>
       <c r="O733" t="n">
-        <v>603749.85</v>
+        <v>592772.5800000001</v>
       </c>
       <c r="P733" t="n">
         <v>17900</v>
       </c>
       <c r="Q733" t="n">
-        <v>984500</v>
+        <v>966600</v>
       </c>
     </row>
     <row r="734">
@@ -31800,13 +31800,13 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M735" t="n">
         <v>36</v>
@@ -39531,7 +39531,7 @@
         </is>
       </c>
       <c r="J903" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K903" t="n">
         <v>0</v>
@@ -39540,19 +39540,19 @@
         <v>0</v>
       </c>
       <c r="M903" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N903" t="n">
-        <v>2458.5130759032</v>
+        <v>2458.5130690113</v>
       </c>
       <c r="O903" t="n">
-        <v>730178.3835432504</v>
+        <v>725261.3553583336</v>
       </c>
       <c r="P903" t="n">
         <v>3500</v>
       </c>
       <c r="Q903" t="n">
-        <v>1039500</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="904">
@@ -39669,13 +39669,13 @@
         </is>
       </c>
       <c r="J906" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K906" t="n">
         <v>0</v>
       </c>
       <c r="L906" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M906" t="n">
         <v>326</v>
@@ -39715,13 +39715,13 @@
         </is>
       </c>
       <c r="J907" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K907" t="n">
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M907" t="n">
         <v>313</v>
@@ -39761,13 +39761,13 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M908" t="n">
         <v>93</v>
@@ -39807,7 +39807,7 @@
         </is>
       </c>
       <c r="J909" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
@@ -39816,19 +39816,19 @@
         <v>0</v>
       </c>
       <c r="M909" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N909" t="n">
-        <v>2108.792083045</v>
+        <v>2108.7921081831</v>
       </c>
       <c r="O909" t="n">
-        <v>227749.54496886</v>
+        <v>223531.9634674086</v>
       </c>
       <c r="P909" t="n">
         <v>2900</v>
       </c>
       <c r="Q909" t="n">
-        <v>313200</v>
+        <v>307400</v>
       </c>
     </row>
     <row r="910">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
@@ -39862,19 +39862,19 @@
         <v>0</v>
       </c>
       <c r="M910" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N910" t="n">
-        <v>2056.0829891304</v>
+        <v>2056.0829843644</v>
       </c>
       <c r="O910" t="n">
-        <v>598320.1498369464</v>
+        <v>594207.9824813117</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
       </c>
       <c r="Q910" t="n">
-        <v>843900</v>
+        <v>838100</v>
       </c>
     </row>
     <row r="911">
@@ -39945,13 +39945,13 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K912" t="n">
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M912" t="n">
         <v>231</v>
@@ -40086,13 +40086,13 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M915" t="n">
         <v>220</v>
@@ -40178,28 +40178,28 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M917" t="n">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="N917" t="n">
-        <v>1592.2787749004</v>
+        <v>1592.27881</v>
       </c>
       <c r="O917" t="n">
-        <v>699010.3821812756</v>
+        <v>695825.83997</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
       </c>
       <c r="Q917" t="n">
-        <v>1097500</v>
+        <v>1092500</v>
       </c>
     </row>
     <row r="918">
@@ -40355,7 +40355,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40364,19 +40364,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N921" t="n">
-        <v>1906.1834782609</v>
+        <v>1906.1829245283</v>
       </c>
       <c r="O921" t="n">
-        <v>303083.1730434831</v>
+        <v>299270.7191509431</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
       </c>
       <c r="Q921" t="n">
-        <v>461100</v>
+        <v>455300</v>
       </c>
     </row>
     <row r="922">
@@ -40493,28 +40493,28 @@
         </is>
       </c>
       <c r="J924" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="K924" t="n">
         <v>0</v>
       </c>
       <c r="L924" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M924" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="N924" t="n">
-        <v>2546.9838660907</v>
+        <v>2546.9837028825</v>
       </c>
       <c r="O924" t="n">
-        <v>404970.4347084213</v>
+        <v>374406.6043237275</v>
       </c>
       <c r="P924" t="n">
         <v>3900</v>
       </c>
       <c r="Q924" t="n">
-        <v>620100</v>
+        <v>573300</v>
       </c>
     </row>
     <row r="925">
@@ -42591,13 +42591,13 @@
         </is>
       </c>
       <c r="J970" t="n">
-        <v>1779</v>
+        <v>1749</v>
       </c>
       <c r="K970" t="n">
         <v>0</v>
       </c>
       <c r="L970" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M970" t="n">
         <v>1749</v>
@@ -42720,7 +42720,7 @@
         </is>
       </c>
       <c r="J973" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K973" t="n">
         <v>0</v>
@@ -42729,19 +42729,19 @@
         <v>0</v>
       </c>
       <c r="M973" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N973" t="n">
-        <v>4032.3968461538</v>
+        <v>4032.3968380463</v>
       </c>
       <c r="O973" t="n">
-        <v>125004.3022307678</v>
+        <v>120971.905141389</v>
       </c>
       <c r="P973" t="n">
         <v>4200</v>
       </c>
       <c r="Q973" t="n">
-        <v>130200</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="974">
@@ -42866,10 +42866,10 @@
         <v>1454</v>
       </c>
       <c r="N976" t="n">
-        <v>517.28990087531</v>
+        <v>517.2899423715</v>
       </c>
       <c r="O976" t="n">
-        <v>752139.5158727007</v>
+        <v>752139.5762081611</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
@@ -42941,13 +42941,13 @@
         </is>
       </c>
       <c r="J978" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K978" t="n">
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M978" t="n">
         <v>2</v>
@@ -43039,22 +43039,22 @@
         </is>
       </c>
       <c r="J980" t="n">
-        <v>1484</v>
+        <v>1428</v>
       </c>
       <c r="K980" t="n">
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M980" t="n">
         <v>1428</v>
       </c>
       <c r="N980" t="n">
-        <v>3110.8414032101</v>
+        <v>3110.8413822526</v>
       </c>
       <c r="O980" t="n">
-        <v>4442281.523784023</v>
+        <v>4442281.493856713</v>
       </c>
       <c r="P980" t="n">
         <v>4500</v>
@@ -43171,28 +43171,28 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>14301</v>
+        <v>14242</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M983" t="n">
-        <v>14249</v>
+        <v>14242</v>
       </c>
       <c r="N983" t="n">
-        <v>703.79516919374</v>
+        <v>703.79516599434</v>
       </c>
       <c r="O983" t="n">
-        <v>10028377.3658416</v>
+        <v>10023450.75409139</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
       </c>
       <c r="Q983" t="n">
-        <v>12824100</v>
+        <v>12817800</v>
       </c>
     </row>
     <row r="984">
@@ -43487,13 +43487,13 @@
         </is>
       </c>
       <c r="J990" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K990" t="n">
         <v>0</v>
       </c>
       <c r="L990" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M990" t="n">
         <v>191</v>
@@ -46971,13 +46971,13 @@
         </is>
       </c>
       <c r="J1065" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1065" t="n">
         <v>0</v>
       </c>
       <c r="L1065" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1065" t="n">
         <v>1</v>
@@ -47964,13 +47964,13 @@
         </is>
       </c>
       <c r="J1086" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K1086" t="n">
         <v>0</v>
       </c>
       <c r="L1086" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1086" t="n">
         <v>282</v>
@@ -48062,13 +48062,13 @@
         </is>
       </c>
       <c r="J1088" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K1088" t="n">
         <v>0</v>
       </c>
       <c r="L1088" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1088" t="n">
         <v>91</v>
@@ -48111,13 +48111,13 @@
         </is>
       </c>
       <c r="J1089" t="n">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="K1089" t="n">
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M1089" t="n">
         <v>165</v>
@@ -49394,13 +49394,13 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1119" t="n">
         <v>1513</v>
@@ -49564,13 +49564,13 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1123" t="n">
         <v>128</v>
@@ -49608,7 +49608,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -49617,19 +49617,19 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="N1124" t="n">
-        <v>1794.2879692219</v>
+        <v>1794.2879686376</v>
       </c>
       <c r="O1124" t="n">
-        <v>2190825.61041994</v>
+        <v>2187237.033769235</v>
       </c>
       <c r="P1124" t="n">
         <v>1600</v>
       </c>
       <c r="Q1124" t="n">
-        <v>1953600</v>
+        <v>1950400</v>
       </c>
     </row>
     <row r="1125">
@@ -50001,7 +50001,7 @@
         </is>
       </c>
       <c r="J1133" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="K1133" t="n">
         <v>0</v>
@@ -50010,19 +50010,19 @@
         <v>0</v>
       </c>
       <c r="M1133" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="N1133" t="n">
-        <v>2523.3377470356</v>
+        <v>2523.3377457627</v>
       </c>
       <c r="O1133" t="n">
-        <v>4973498.699407168</v>
+        <v>4968452.021406756</v>
       </c>
       <c r="P1133" t="n">
         <v>2800</v>
       </c>
       <c r="Q1133" t="n">
-        <v>5518800</v>
+        <v>5513200</v>
       </c>
     </row>
     <row r="1134">
@@ -51663,13 +51663,13 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
       </c>
       <c r="L1170" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M1170" t="n">
         <v>87</v>
@@ -51709,28 +51709,28 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="N1171" t="n">
         <v>6336</v>
       </c>
       <c r="O1171" t="n">
-        <v>329472</v>
+        <v>253440</v>
       </c>
       <c r="P1171" t="n">
         <v>7500</v>
       </c>
       <c r="Q1171" t="n">
-        <v>390000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="1172">
@@ -51801,28 +51801,28 @@
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="N1173" t="n">
         <v>1584</v>
       </c>
       <c r="O1173" t="n">
-        <v>102960</v>
+        <v>93456</v>
       </c>
       <c r="P1173" t="n">
         <v>2000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>130000</v>
+        <v>118000</v>
       </c>
     </row>
     <row r="1174">
@@ -51985,13 +51985,13 @@
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1177" t="n">
         <v>151</v>
@@ -52077,28 +52077,28 @@
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
       </c>
       <c r="L1179" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="N1179" t="n">
         <v>9240</v>
       </c>
       <c r="O1179" t="n">
-        <v>997920</v>
+        <v>803880</v>
       </c>
       <c r="P1179" t="n">
         <v>11500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>1242000</v>
+        <v>1000500</v>
       </c>
     </row>
     <row r="1180">
@@ -52169,13 +52169,13 @@
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1181" t="n">
         <v>181</v>
@@ -52399,13 +52399,13 @@
         </is>
       </c>
       <c r="J1186" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1186" t="n">
         <v>0</v>
       </c>
       <c r="L1186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1186" t="n">
         <v>14</v>
@@ -53884,13 +53884,13 @@
         </is>
       </c>
       <c r="J1218" t="n">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="K1218" t="n">
         <v>0</v>
       </c>
       <c r="L1218" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1218" t="n">
         <v>579</v>
@@ -53930,13 +53930,13 @@
         </is>
       </c>
       <c r="J1219" t="n">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="K1219" t="n">
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1219" t="n">
         <v>650</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1036,10 +1036,10 @@
         <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O15" t="n">
-        <v>79697.523205344</v>
+        <v>79697.5259259256</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
@@ -1475,22 +1475,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N26" t="n">
         <v>4072</v>
       </c>
       <c r="O26" t="n">
-        <v>1946416</v>
+        <v>1938272</v>
       </c>
       <c r="P26" t="n">
         <v>7500</v>
       </c>
       <c r="Q26" t="n">
-        <v>3585000</v>
+        <v>3570000</v>
       </c>
     </row>
     <row r="27">
@@ -2545,22 +2545,22 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N52" t="n">
         <v>4604.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1335218</v>
+        <v>1326009.6</v>
       </c>
       <c r="P52" t="n">
         <v>7500</v>
       </c>
       <c r="Q52" t="n">
-        <v>2175000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="53">
@@ -2902,22 +2902,22 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N61" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O61" t="n">
-        <v>98170.927423535</v>
+        <v>94244.09029045681</v>
       </c>
       <c r="P61" t="n">
         <v>4800</v>
       </c>
       <c r="Q61" t="n">
-        <v>120000</v>
+        <v>115200</v>
       </c>
     </row>
     <row r="62">
@@ -5123,10 +5123,10 @@
         <v>13</v>
       </c>
       <c r="N113" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O113" t="n">
-        <v>204255.556995711</v>
+        <v>204255.556767236</v>
       </c>
       <c r="P113" t="n">
         <v>28500</v>
@@ -9740,22 +9740,22 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M222" t="n">
-        <v>9240</v>
+        <v>9237</v>
       </c>
       <c r="N222" t="n">
         <v>1726.32</v>
       </c>
       <c r="O222" t="n">
-        <v>15951196.8</v>
+        <v>15946017.84</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
       </c>
       <c r="Q222" t="n">
-        <v>13860000</v>
+        <v>13855500</v>
       </c>
     </row>
     <row r="223">
@@ -10297,10 +10297,10 @@
         <v>1043</v>
       </c>
       <c r="N235" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O235" t="n">
-        <v>1145276.35820459</v>
+        <v>1145276.46429928</v>
       </c>
       <c r="P235" t="n">
         <v>1500</v>
@@ -12556,10 +12556,10 @@
         <v>2830</v>
       </c>
       <c r="N288" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O288" t="n">
-        <v>8939576.138235994</v>
+        <v>8943518.329682972</v>
       </c>
       <c r="P288" t="n">
         <v>5600</v>
@@ -12648,10 +12648,10 @@
         <v>226</v>
       </c>
       <c r="N290" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O290" t="n">
-        <v>868207.2096428636</v>
+        <v>871666.2025099616</v>
       </c>
       <c r="P290" t="n">
         <v>6900</v>
@@ -14689,10 +14689,10 @@
         <v>362</v>
       </c>
       <c r="N336" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O336" t="n">
-        <v>1301119.948</v>
+        <v>1301119.946641667</v>
       </c>
       <c r="P336" t="n">
         <v>6500</v>
@@ -14732,22 +14732,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M337" t="n">
-        <v>713</v>
+        <v>689</v>
       </c>
       <c r="N337" t="n">
         <v>489.88</v>
       </c>
       <c r="O337" t="n">
-        <v>349284.44</v>
+        <v>337527.32</v>
       </c>
       <c r="P337" t="n">
         <v>700</v>
       </c>
       <c r="Q337" t="n">
-        <v>499100</v>
+        <v>482300</v>
       </c>
     </row>
     <row r="338">
@@ -15128,10 +15128,10 @@
         <v>6357</v>
       </c>
       <c r="N346" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O346" t="n">
-        <v>13291533.45</v>
+        <v>13293318.74663539</v>
       </c>
       <c r="P346" t="n">
         <v>2900</v>
@@ -15671,22 +15671,22 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M359" t="n">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="N359" t="n">
         <v>1441.01</v>
       </c>
       <c r="O359" t="n">
-        <v>3912342.15</v>
+        <v>3905137.1</v>
       </c>
       <c r="P359" t="n">
         <v>2100</v>
       </c>
       <c r="Q359" t="n">
-        <v>5701500</v>
+        <v>5691000</v>
       </c>
     </row>
     <row r="360">
@@ -15800,22 +15800,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N362" t="n">
         <v>48017.67</v>
       </c>
       <c r="O362" t="n">
-        <v>144053.01</v>
+        <v>96035.34</v>
       </c>
       <c r="P362" t="n">
         <v>82900</v>
       </c>
       <c r="Q362" t="n">
-        <v>248700</v>
+        <v>165800</v>
       </c>
     </row>
     <row r="363">
@@ -16028,22 +16028,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>8126</v>
+        <v>8125</v>
       </c>
       <c r="N367" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O367" t="n">
-        <v>35528584.88243204</v>
+        <v>35524212.67209994</v>
       </c>
       <c r="P367" t="n">
         <v>7500</v>
       </c>
       <c r="Q367" t="n">
-        <v>60945000</v>
+        <v>60937500</v>
       </c>
     </row>
     <row r="368">
@@ -16206,10 +16206,10 @@
         <v>428</v>
       </c>
       <c r="N371" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O371" t="n">
-        <v>681618.5584886624</v>
+        <v>685087.3480916023</v>
       </c>
       <c r="P371" t="n">
         <v>3900</v>
@@ -17016,22 +17016,22 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M390" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N390" t="n">
         <v>1343.77</v>
       </c>
       <c r="O390" t="n">
-        <v>249941.22</v>
+        <v>244566.14</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>465000</v>
+        <v>455000</v>
       </c>
     </row>
     <row r="391">
@@ -17148,22 +17148,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M393" t="n">
-        <v>2520</v>
+        <v>2498</v>
       </c>
       <c r="N393" t="n">
         <v>1387.55</v>
       </c>
       <c r="O393" t="n">
-        <v>3496626</v>
+        <v>3466099.9</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
       </c>
       <c r="Q393" t="n">
-        <v>5796000</v>
+        <v>5745400</v>
       </c>
     </row>
     <row r="394">
@@ -17689,10 +17689,10 @@
         <v>1</v>
       </c>
       <c r="N405" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O405" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="P405" t="n">
         <v>6900</v>
@@ -18518,22 +18518,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N424" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O424" t="n">
-        <v>683357.0081527075</v>
+        <v>681726.0884926162</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1047500</v>
+        <v>1045000</v>
       </c>
     </row>
     <row r="425">
@@ -18616,10 +18616,10 @@
         <v>8</v>
       </c>
       <c r="N426" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O426" t="n">
-        <v>13524.7759819416</v>
+        <v>13524.7757045968</v>
       </c>
       <c r="P426" t="n">
         <v>2900</v>
@@ -18656,22 +18656,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M427" t="n">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="N427" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O427" t="n">
-        <v>913064.0890240535</v>
+        <v>906863.3174670615</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1472500</v>
+        <v>1462500</v>
       </c>
     </row>
     <row r="428">
@@ -18702,22 +18702,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M428" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N428" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O428" t="n">
-        <v>161097.8235200034</v>
+        <v>157939.03753351</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
       </c>
       <c r="Q428" t="n">
-        <v>295800</v>
+        <v>290000</v>
       </c>
     </row>
     <row r="429">
@@ -18754,10 +18754,10 @@
         <v>768</v>
       </c>
       <c r="N429" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O429" t="n">
-        <v>1845897.292904755</v>
+        <v>1845897.305595033</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
@@ -21850,22 +21850,22 @@
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M501" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N501" t="n">
         <v>2992.7</v>
       </c>
       <c r="O501" t="n">
-        <v>50875.89999999999</v>
+        <v>38905.1</v>
       </c>
       <c r="P501" t="n">
         <v>5900</v>
       </c>
       <c r="Q501" t="n">
-        <v>100300</v>
+        <v>76700</v>
       </c>
     </row>
     <row r="502">
@@ -23906,22 +23906,22 @@
         <v>0</v>
       </c>
       <c r="L550" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M550" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="N550" t="n">
         <v>7103</v>
       </c>
       <c r="O550" t="n">
-        <v>937596</v>
+        <v>916287</v>
       </c>
       <c r="P550" t="n">
         <v>10700</v>
       </c>
       <c r="Q550" t="n">
-        <v>1412400</v>
+        <v>1380300</v>
       </c>
     </row>
     <row r="551">
@@ -24125,10 +24125,10 @@
         <v>180</v>
       </c>
       <c r="N555" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O555" t="n">
-        <v>482533.14511512</v>
+        <v>482533.145080938</v>
       </c>
       <c r="P555" t="n">
         <v>4900</v>
@@ -27667,22 +27667,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M639" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="N639" t="n">
         <v>4793.53</v>
       </c>
       <c r="O639" t="n">
-        <v>1663354.91</v>
+        <v>1648974.32</v>
       </c>
       <c r="P639" t="n">
         <v>7900</v>
       </c>
       <c r="Q639" t="n">
-        <v>2741300</v>
+        <v>2717600</v>
       </c>
     </row>
     <row r="640">
@@ -28395,10 +28395,10 @@
         <v>2</v>
       </c>
       <c r="N656" t="n">
-        <v>1466.8807185629</v>
+        <v>1484.6610909091</v>
       </c>
       <c r="O656" t="n">
-        <v>2933.7614371258</v>
+        <v>2969.3221818182</v>
       </c>
       <c r="P656" t="n">
         <v>3400</v>
@@ -28865,22 +28865,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M667" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N667" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O667" t="n">
-        <v>448007.2679966107</v>
+        <v>443324.270476204</v>
       </c>
       <c r="P667" t="n">
         <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>832300</v>
+        <v>823600</v>
       </c>
     </row>
     <row r="668">
@@ -31113,22 +31113,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M720" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N720" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O720" t="n">
-        <v>28025.0102472525</v>
+        <v>15569.4501381215</v>
       </c>
       <c r="P720" t="n">
         <v>5000</v>
       </c>
       <c r="Q720" t="n">
-        <v>45000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="721">
@@ -31251,22 +31251,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M723" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N723" t="n">
         <v>10911.29</v>
       </c>
       <c r="O723" t="n">
-        <v>163669.35</v>
+        <v>152758.06</v>
       </c>
       <c r="P723" t="n">
         <v>17400</v>
       </c>
       <c r="Q723" t="n">
-        <v>261000</v>
+        <v>243600</v>
       </c>
     </row>
     <row r="724">
@@ -31481,22 +31481,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M728" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N728" t="n">
-        <v>3610.6500258732</v>
+        <v>3610.6500261438</v>
       </c>
       <c r="O728" t="n">
-        <v>90266.25064683</v>
+        <v>61381.0504444446</v>
       </c>
       <c r="P728" t="n">
         <v>5800</v>
       </c>
       <c r="Q728" t="n">
-        <v>145000</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="729">
@@ -31668,22 +31668,22 @@
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M732" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N732" t="n">
         <v>5791.05</v>
       </c>
       <c r="O732" t="n">
-        <v>75283.65000000001</v>
+        <v>69492.60000000001</v>
       </c>
       <c r="P732" t="n">
         <v>9300</v>
       </c>
       <c r="Q732" t="n">
-        <v>120900</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="733">
@@ -31714,22 +31714,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M733" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N733" t="n">
         <v>10977.27</v>
       </c>
       <c r="O733" t="n">
-        <v>592772.5800000001</v>
+        <v>581795.3100000001</v>
       </c>
       <c r="P733" t="n">
         <v>17900</v>
       </c>
       <c r="Q733" t="n">
-        <v>966600</v>
+        <v>948700</v>
       </c>
     </row>
     <row r="734">
@@ -36237,10 +36237,10 @@
         <v>15</v>
       </c>
       <c r="N831" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O831" t="n">
-        <v>73617.33138385499</v>
+        <v>74352.27978369451</v>
       </c>
       <c r="P831" t="n">
         <v>8200</v>
@@ -36732,22 +36732,22 @@
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M842" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N842" t="n">
         <v>4202</v>
       </c>
       <c r="O842" t="n">
-        <v>33616</v>
+        <v>16808</v>
       </c>
       <c r="P842" t="n">
         <v>7900</v>
       </c>
       <c r="Q842" t="n">
-        <v>63200</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="843">
@@ -38846,22 +38846,22 @@
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M888" t="n">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="N888" t="n">
         <v>1326</v>
       </c>
       <c r="O888" t="n">
-        <v>2244918</v>
+        <v>2240940</v>
       </c>
       <c r="P888" t="n">
         <v>2500</v>
       </c>
       <c r="Q888" t="n">
-        <v>4232500</v>
+        <v>4225000</v>
       </c>
     </row>
     <row r="889">
@@ -39727,10 +39727,10 @@
         <v>313</v>
       </c>
       <c r="N907" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O907" t="n">
-        <v>564343.8902355655</v>
+        <v>564343.8943332362</v>
       </c>
       <c r="P907" t="n">
         <v>2500</v>
@@ -39773,10 +39773,10 @@
         <v>93</v>
       </c>
       <c r="N908" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O908" t="n">
-        <v>307513.3047337266</v>
+        <v>307513.3040000031</v>
       </c>
       <c r="P908" t="n">
         <v>4900</v>
@@ -39865,10 +39865,10 @@
         <v>289</v>
       </c>
       <c r="N910" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O910" t="n">
-        <v>594207.9824813117</v>
+        <v>594207.9817919021</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
@@ -39957,10 +39957,10 @@
         <v>231</v>
       </c>
       <c r="N912" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O912" t="n">
-        <v>382520.0158444203</v>
+        <v>382520.0115989406</v>
       </c>
       <c r="P912" t="n">
         <v>2500</v>
@@ -40184,22 +40184,22 @@
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M917" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N917" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O917" t="n">
-        <v>695825.83997</v>
+        <v>694233.5650049967</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
       </c>
       <c r="Q917" t="n">
-        <v>1092500</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="918">
@@ -40367,10 +40367,10 @@
         <v>157</v>
       </c>
       <c r="N921" t="n">
-        <v>1906.1829245283</v>
+        <v>1906.1827536232</v>
       </c>
       <c r="O921" t="n">
-        <v>299270.7191509431</v>
+        <v>299270.6923188424</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
@@ -40407,22 +40407,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M922" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N922" t="n">
-        <v>3033.7169285714</v>
+        <v>3033.7165703971</v>
       </c>
       <c r="O922" t="n">
-        <v>697754.893571422</v>
+        <v>688653.6614801417</v>
       </c>
       <c r="P922" t="n">
         <v>4500</v>
       </c>
       <c r="Q922" t="n">
-        <v>1035000</v>
+        <v>1021500</v>
       </c>
     </row>
     <row r="923">
@@ -42860,22 +42860,22 @@
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M976" t="n">
-        <v>1454</v>
+        <v>1405</v>
       </c>
       <c r="N976" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O976" t="n">
-        <v>752139.5762081611</v>
+        <v>726792.4089900731</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>1308600</v>
+        <v>1264500</v>
       </c>
     </row>
     <row r="977">
@@ -43051,10 +43051,10 @@
         <v>1428</v>
       </c>
       <c r="N980" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O980" t="n">
-        <v>4442281.493856713</v>
+        <v>4442281.478838151</v>
       </c>
       <c r="P980" t="n">
         <v>4500</v>
@@ -43183,10 +43183,10 @@
         <v>14242</v>
       </c>
       <c r="N983" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O983" t="n">
-        <v>10023450.75409139</v>
+        <v>10023450.72589323</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
@@ -44361,10 +44361,10 @@
         <v>18</v>
       </c>
       <c r="N1009" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O1009" t="n">
-        <v>37771.2902608704</v>
+        <v>37991.5310204082</v>
       </c>
       <c r="P1009" t="n">
         <v>9500</v>
@@ -44533,22 +44533,22 @@
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1013" t="n">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="N1013" t="n">
         <v>1669.6</v>
       </c>
       <c r="O1013" t="n">
-        <v>1686296</v>
+        <v>1676278.4</v>
       </c>
       <c r="P1013" t="n">
         <v>2900</v>
       </c>
       <c r="Q1013" t="n">
-        <v>2929000</v>
+        <v>2911600</v>
       </c>
     </row>
     <row r="1014">
@@ -44816,22 +44816,22 @@
         <v>0</v>
       </c>
       <c r="L1019" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1019" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="N1019" t="n">
-        <v>3063.6219074262</v>
+        <v>3063.621911315</v>
       </c>
       <c r="O1019" t="n">
-        <v>2092453.762772094</v>
+        <v>2080199.277782885</v>
       </c>
       <c r="P1019" t="n">
         <v>3500</v>
       </c>
       <c r="Q1019" t="n">
-        <v>2390500</v>
+        <v>2376500</v>
       </c>
     </row>
     <row r="1020">
@@ -44911,22 +44911,22 @@
         <v>0</v>
       </c>
       <c r="L1021" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1021" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N1021" t="n">
         <v>2672.89</v>
       </c>
       <c r="O1021" t="n">
-        <v>168392.07</v>
+        <v>160373.4</v>
       </c>
       <c r="P1021" t="n">
         <v>10200</v>
       </c>
       <c r="Q1021" t="n">
-        <v>642600</v>
+        <v>612000</v>
       </c>
     </row>
     <row r="1022">
@@ -44963,10 +44963,10 @@
         <v>2</v>
       </c>
       <c r="N1022" t="n">
-        <v>875.69016806723</v>
+        <v>883.11127118644</v>
       </c>
       <c r="O1022" t="n">
-        <v>1751.38033613446</v>
+        <v>1766.22254237288</v>
       </c>
       <c r="P1022" t="n">
         <v>4500</v>
@@ -47690,10 +47690,10 @@
         <v>16</v>
       </c>
       <c r="N1080" t="n">
-        <v>665.32359209922</v>
+        <v>665.32360534809</v>
       </c>
       <c r="O1080" t="n">
-        <v>10645.17747358752</v>
+        <v>10645.17768556944</v>
       </c>
       <c r="P1080" t="n">
         <v>2900</v>
@@ -48500,22 +48500,22 @@
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1098" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N1098" t="n">
         <v>2459</v>
       </c>
       <c r="O1098" t="n">
-        <v>211474</v>
+        <v>201638</v>
       </c>
       <c r="P1098" t="n">
         <v>3900</v>
       </c>
       <c r="Q1098" t="n">
-        <v>335400</v>
+        <v>319800</v>
       </c>
     </row>
     <row r="1099">
@@ -49488,22 +49488,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1121" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N1121" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1121" t="n">
-        <v>235460.6</v>
+        <v>225914.9</v>
       </c>
       <c r="P1121" t="n">
         <v>5100</v>
       </c>
       <c r="Q1121" t="n">
-        <v>377400</v>
+        <v>362100</v>
       </c>
     </row>
     <row r="1122">
@@ -50723,10 +50723,10 @@
         <v>1</v>
       </c>
       <c r="N1149" t="n">
-        <v>2367.1669565217</v>
+        <v>2367.1668181818</v>
       </c>
       <c r="O1149" t="n">
-        <v>2367.1669565217</v>
+        <v>2367.1668181818</v>
       </c>
       <c r="P1149" t="n">
         <v>2900</v>
@@ -51767,10 +51767,10 @@
         <v>43</v>
       </c>
       <c r="N1172" t="n">
-        <v>5280</v>
+        <v>5301.8181818182</v>
       </c>
       <c r="O1172" t="n">
-        <v>227040</v>
+        <v>227978.1818181826</v>
       </c>
       <c r="P1172" t="n">
         <v>6900</v>
@@ -51807,22 +51807,22 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M1173" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="N1173" t="n">
         <v>1584</v>
       </c>
       <c r="O1173" t="n">
-        <v>93456</v>
+        <v>38016</v>
       </c>
       <c r="P1173" t="n">
         <v>2000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>118000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="1174">
@@ -51991,22 +51991,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1177" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="N1177" t="n">
         <v>3520</v>
       </c>
       <c r="O1177" t="n">
-        <v>531520</v>
+        <v>468160</v>
       </c>
       <c r="P1177" t="n">
         <v>4500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>679500</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="1178">
@@ -52175,22 +52175,22 @@
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1181" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N1181" t="n">
         <v>4576</v>
       </c>
       <c r="O1181" t="n">
-        <v>828256</v>
+        <v>814528</v>
       </c>
       <c r="P1181" t="n">
         <v>5900</v>
       </c>
       <c r="Q1181" t="n">
-        <v>1067900</v>
+        <v>1050200</v>
       </c>
     </row>
     <row r="1182">
@@ -53844,22 +53844,22 @@
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1217" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="N1217" t="n">
-        <v>2539.5715559441</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O1217" t="n">
-        <v>840598.1850174972</v>
+        <v>815202.4738624329</v>
       </c>
       <c r="P1217" t="n">
         <v>3500</v>
       </c>
       <c r="Q1217" t="n">
-        <v>1158500</v>
+        <v>1123500</v>
       </c>
     </row>
     <row r="1218">
@@ -53890,22 +53890,22 @@
         <v>0</v>
       </c>
       <c r="L1218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1218" t="n">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="N1218" t="n">
-        <v>4687.9742611684</v>
+        <v>4687.9742758621</v>
       </c>
       <c r="O1218" t="n">
-        <v>2714337.097216503</v>
+        <v>2695585.208620708</v>
       </c>
       <c r="P1218" t="n">
         <v>5900</v>
       </c>
       <c r="Q1218" t="n">
-        <v>3416100</v>
+        <v>3392500</v>
       </c>
     </row>
     <row r="1219">
@@ -53936,22 +53936,22 @@
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1219" t="n">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="N1219" t="n">
-        <v>4171.6686912752</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O1219" t="n">
-        <v>2711584.64932888</v>
+        <v>2686554.631486465</v>
       </c>
       <c r="P1219" t="n">
         <v>5500</v>
       </c>
       <c r="Q1219" t="n">
-        <v>3575000</v>
+        <v>3542000</v>
       </c>
     </row>
     <row r="1220">
@@ -61945,10 +61945,10 @@
         <v>26</v>
       </c>
       <c r="N1412" t="n">
-        <v>2403.9772262774</v>
+        <v>2403.9772058824</v>
       </c>
       <c r="O1412" t="n">
-        <v>62503.4078832124</v>
+        <v>62503.40735294241</v>
       </c>
       <c r="P1412" t="n">
         <v>3000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1036,10 +1036,10 @@
         <v>44</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3074074074</v>
+        <v>1811.3076124567</v>
       </c>
       <c r="O15" t="n">
-        <v>79697.5259259256</v>
+        <v>79697.53494809481</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1113,19 +1113,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N17" t="n">
-        <v>1990.0435294118</v>
+        <v>1990.0435171103</v>
       </c>
       <c r="O17" t="n">
-        <v>302486.6164705936</v>
+        <v>300496.5710836553</v>
       </c>
       <c r="P17" t="n">
         <v>4400</v>
       </c>
       <c r="Q17" t="n">
-        <v>668800</v>
+        <v>664400</v>
       </c>
     </row>
     <row r="18">
@@ -1197,10 +1197,10 @@
         <v>1140</v>
       </c>
       <c r="N19" t="n">
-        <v>3376.7464651163</v>
+        <v>3376.7464631809</v>
       </c>
       <c r="O19" t="n">
-        <v>3849490.970232582</v>
+        <v>3849490.968026226</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>476</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2431,19 +2431,19 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>31658.725454545</v>
+        <v>31658.725660377</v>
       </c>
       <c r="O49" t="n">
-        <v>189952.35272727</v>
+        <v>126634.902641508</v>
       </c>
       <c r="P49" t="n">
         <v>62900</v>
       </c>
       <c r="Q49" t="n">
-        <v>377400</v>
+        <v>251600</v>
       </c>
     </row>
     <row r="50">
@@ -2539,13 +2539,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>288</v>
@@ -2588,10 +2588,10 @@
         <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>1854.2404977376</v>
+        <v>1854.2405454545</v>
       </c>
       <c r="O53" t="n">
-        <v>12979.6834841632</v>
+        <v>12979.6838181815</v>
       </c>
       <c r="P53" t="n">
         <v>3200</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2705,19 +2705,19 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N56" t="n">
         <v>2812</v>
       </c>
       <c r="O56" t="n">
-        <v>936396</v>
+        <v>930772</v>
       </c>
       <c r="P56" t="n">
         <v>5000</v>
       </c>
       <c r="Q56" t="n">
-        <v>1665000</v>
+        <v>1655000</v>
       </c>
     </row>
     <row r="57">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2783,19 +2783,19 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8547761194</v>
+        <v>6272.8548484848</v>
       </c>
       <c r="O58" t="n">
-        <v>282278.464925373</v>
+        <v>225822.7745454528</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
       </c>
       <c r="Q58" t="n">
-        <v>355500</v>
+        <v>284400</v>
       </c>
     </row>
     <row r="59">
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2827,19 +2827,19 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N59" t="n">
         <v>2445.67</v>
       </c>
       <c r="O59" t="n">
-        <v>63587.42</v>
+        <v>58696.08</v>
       </c>
       <c r="P59" t="n">
         <v>4600</v>
       </c>
       <c r="Q59" t="n">
-        <v>119600</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="60">
@@ -2896,13 +2896,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>24</v>
@@ -3153,10 +3153,10 @@
         <v>86</v>
       </c>
       <c r="N67" t="n">
-        <v>2413.0010741139</v>
+        <v>2413.0010834236</v>
       </c>
       <c r="O67" t="n">
-        <v>207518.0923737954</v>
+        <v>207518.0931744296</v>
       </c>
       <c r="P67" t="n">
         <v>4700</v>
@@ -3348,10 +3348,10 @@
         <v>54</v>
       </c>
       <c r="N72" t="n">
-        <v>3716.3301938611</v>
+        <v>3716.3301954397</v>
       </c>
       <c r="O72" t="n">
-        <v>200681.8304684994</v>
+        <v>200681.8305537438</v>
       </c>
       <c r="P72" t="n">
         <v>9500</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3914,19 +3914,19 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N86" t="n">
         <v>1800</v>
       </c>
       <c r="O86" t="n">
-        <v>39600</v>
+        <v>37800</v>
       </c>
       <c r="P86" t="n">
         <v>2200</v>
       </c>
       <c r="Q86" t="n">
-        <v>48400</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="87">
@@ -4087,10 +4087,10 @@
         <v>11</v>
       </c>
       <c r="N90" t="n">
-        <v>3910.628136646</v>
+        <v>3910.628089172</v>
       </c>
       <c r="O90" t="n">
-        <v>43016.909503106</v>
+        <v>43016.908980892</v>
       </c>
       <c r="P90" t="n">
         <v>9100</v>
@@ -5042,10 +5042,10 @@
         <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>16486.408837209</v>
+        <v>16486.40875</v>
       </c>
       <c r="O111" t="n">
-        <v>16486.408837209</v>
+        <v>16486.40875</v>
       </c>
       <c r="P111" t="n">
         <v>30500</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5120,19 +5120,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N113" t="n">
-        <v>15711.965905172</v>
+        <v>15711.965869565</v>
       </c>
       <c r="O113" t="n">
-        <v>204255.556767236</v>
+        <v>188543.59043478</v>
       </c>
       <c r="P113" t="n">
         <v>28500</v>
       </c>
       <c r="Q113" t="n">
-        <v>370500</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="114">
@@ -5217,10 +5217,10 @@
         <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>30238.812608696</v>
+        <v>30238.812647059</v>
       </c>
       <c r="O115" t="n">
-        <v>120955.250434784</v>
+        <v>120955.250588236</v>
       </c>
       <c r="P115" t="n">
         <v>51100</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5295,19 +5295,19 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N117" t="n">
         <v>20742.53</v>
       </c>
       <c r="O117" t="n">
-        <v>207425.3</v>
+        <v>186682.77</v>
       </c>
       <c r="P117" t="n">
         <v>36500</v>
       </c>
       <c r="Q117" t="n">
-        <v>365000</v>
+        <v>328500</v>
       </c>
     </row>
     <row r="118">
@@ -6376,10 +6376,10 @@
         <v>10</v>
       </c>
       <c r="N143" t="n">
-        <v>62349.657575758</v>
+        <v>62349.656875</v>
       </c>
       <c r="O143" t="n">
-        <v>623496.57575758</v>
+        <v>623496.56875</v>
       </c>
       <c r="P143" t="n">
         <v>109900</v>
@@ -6645,10 +6645,10 @@
         <v>1</v>
       </c>
       <c r="N149" t="n">
-        <v>344599.17862745</v>
+        <v>344599.1786</v>
       </c>
       <c r="O149" t="n">
-        <v>344599.17862745</v>
+        <v>344599.1786</v>
       </c>
       <c r="P149" t="n">
         <v>532900</v>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -7765,19 +7765,19 @@
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N176" t="n">
         <v>2572.67</v>
       </c>
       <c r="O176" t="n">
-        <v>519679.34</v>
+        <v>517106.67</v>
       </c>
       <c r="P176" t="n">
         <v>4700</v>
       </c>
       <c r="Q176" t="n">
-        <v>949400</v>
+        <v>944700</v>
       </c>
     </row>
     <row r="177">
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -8922,19 +8922,19 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N203" t="n">
-        <v>3340.6800821355</v>
+        <v>3340.6800824742</v>
       </c>
       <c r="O203" t="n">
-        <v>63472.9215605745</v>
+        <v>60132.2414845356</v>
       </c>
       <c r="P203" t="n">
         <v>7100</v>
       </c>
       <c r="Q203" t="n">
-        <v>134900</v>
+        <v>127800</v>
       </c>
     </row>
     <row r="204">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9005,19 +9005,19 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N205" t="n">
         <v>2563.34</v>
       </c>
       <c r="O205" t="n">
-        <v>253770.66</v>
+        <v>251207.32</v>
       </c>
       <c r="P205" t="n">
         <v>4700</v>
       </c>
       <c r="Q205" t="n">
-        <v>465300</v>
+        <v>460600</v>
       </c>
     </row>
     <row r="206">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -9661,19 +9661,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="N220" t="n">
         <v>2833</v>
       </c>
       <c r="O220" t="n">
-        <v>1798955</v>
+        <v>1790456</v>
       </c>
       <c r="P220" t="n">
         <v>3500</v>
       </c>
       <c r="Q220" t="n">
-        <v>2222500</v>
+        <v>2212000</v>
       </c>
     </row>
     <row r="221">
@@ -9734,28 +9734,28 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>9240</v>
+        <v>9236</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>9237</v>
+        <v>9236</v>
       </c>
       <c r="N222" t="n">
         <v>1726.32</v>
       </c>
       <c r="O222" t="n">
-        <v>15946017.84</v>
+        <v>15944291.52</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
       </c>
       <c r="Q222" t="n">
-        <v>13855500</v>
+        <v>13854000</v>
       </c>
     </row>
     <row r="223">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -9784,19 +9784,19 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N223" t="n">
         <v>2088.01</v>
       </c>
       <c r="O223" t="n">
-        <v>329905.58</v>
+        <v>317377.52</v>
       </c>
       <c r="P223" t="n">
         <v>3500</v>
       </c>
       <c r="Q223" t="n">
-        <v>553000</v>
+        <v>532000</v>
       </c>
     </row>
     <row r="224">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -10086,19 +10086,19 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N230" t="n">
         <v>3775.99</v>
       </c>
       <c r="O230" t="n">
-        <v>75519.79999999999</v>
+        <v>67967.81999999999</v>
       </c>
       <c r="P230" t="n">
         <v>7300</v>
       </c>
       <c r="Q230" t="n">
-        <v>146000</v>
+        <v>131400</v>
       </c>
     </row>
     <row r="231">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10294,19 +10294,19 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="N235" t="n">
-        <v>1098.0598890693</v>
+        <v>1098.0599864057</v>
       </c>
       <c r="O235" t="n">
-        <v>1145276.46429928</v>
+        <v>1140884.325875522</v>
       </c>
       <c r="P235" t="n">
         <v>1500</v>
       </c>
       <c r="Q235" t="n">
-        <v>1564500</v>
+        <v>1558500</v>
       </c>
     </row>
     <row r="236">
@@ -10326,7 +10326,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10335,19 +10335,19 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N236" t="n">
-        <v>21084.771466667</v>
+        <v>21084.771470588</v>
       </c>
       <c r="O236" t="n">
-        <v>2466918.261600039</v>
+        <v>2445833.490588208</v>
       </c>
       <c r="P236" t="n">
         <v>30000</v>
       </c>
       <c r="Q236" t="n">
-        <v>3510000</v>
+        <v>3480000</v>
       </c>
     </row>
     <row r="237">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -11342,19 +11342,19 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N260" t="n">
         <v>13000</v>
       </c>
       <c r="O260" t="n">
-        <v>403000</v>
+        <v>390000</v>
       </c>
       <c r="P260" t="n">
         <v>16900</v>
       </c>
       <c r="Q260" t="n">
-        <v>523900</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="261">
@@ -11758,7 +11758,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11767,19 +11767,19 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N270" t="n">
         <v>2804.33</v>
       </c>
       <c r="O270" t="n">
-        <v>291650.32</v>
+        <v>257998.36</v>
       </c>
       <c r="P270" t="n">
         <v>4900</v>
       </c>
       <c r="Q270" t="n">
-        <v>509600</v>
+        <v>450800</v>
       </c>
     </row>
     <row r="271">
@@ -12073,7 +12073,7 @@
         </is>
       </c>
       <c r="J277" t="n">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
@@ -12082,19 +12082,19 @@
         <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="N277" t="n">
-        <v>2582.2556563454</v>
+        <v>2582.2556363636</v>
       </c>
       <c r="O277" t="n">
-        <v>2378257.459494113</v>
+        <v>2347270.373454513</v>
       </c>
       <c r="P277" t="n">
         <v>4500</v>
       </c>
       <c r="Q277" t="n">
-        <v>4144500</v>
+        <v>4090500</v>
       </c>
     </row>
     <row r="278">
@@ -12131,10 +12131,10 @@
         <v>1395</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8961063218</v>
+        <v>5216.8960979122</v>
       </c>
       <c r="O278" t="n">
-        <v>7277570.068318912</v>
+        <v>7277570.056587519</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
@@ -12261,19 +12261,19 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N281" t="n">
-        <v>2033.5471351351</v>
+        <v>2033.5396296296</v>
       </c>
       <c r="O281" t="n">
-        <v>227757.2791351312</v>
+        <v>197253.3440740712</v>
       </c>
       <c r="P281" t="n">
         <v>4100</v>
       </c>
       <c r="Q281" t="n">
-        <v>459200</v>
+        <v>397700</v>
       </c>
     </row>
     <row r="282">
@@ -12556,10 +12556,10 @@
         <v>2830</v>
       </c>
       <c r="N288" t="n">
-        <v>3160.2538267431</v>
+        <v>3158.8608271635</v>
       </c>
       <c r="O288" t="n">
-        <v>8943518.329682972</v>
+        <v>8939576.140872704</v>
       </c>
       <c r="P288" t="n">
         <v>5600</v>
@@ -12636,7 +12636,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -12645,19 +12645,19 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N290" t="n">
-        <v>3856.9300996016</v>
+        <v>3841.6248454636</v>
       </c>
       <c r="O290" t="n">
-        <v>871666.2025099616</v>
+        <v>864365.5902293101</v>
       </c>
       <c r="P290" t="n">
         <v>6900</v>
       </c>
       <c r="Q290" t="n">
-        <v>1559400</v>
+        <v>1552500</v>
       </c>
     </row>
     <row r="291">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -12737,19 +12737,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N292" t="n">
         <v>8477.629999999999</v>
       </c>
       <c r="O292" t="n">
-        <v>42388.14999999999</v>
+        <v>25432.89</v>
       </c>
       <c r="P292" t="n">
         <v>13600</v>
       </c>
       <c r="Q292" t="n">
-        <v>68000</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="293">
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13047,19 +13047,19 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N299" t="n">
-        <v>2694.8231862975</v>
+        <v>2694.8231670588</v>
       </c>
       <c r="O299" t="n">
-        <v>88929.16514781749</v>
+        <v>86234.34134588161</v>
       </c>
       <c r="P299" t="n">
         <v>4900</v>
       </c>
       <c r="Q299" t="n">
-        <v>161700</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="300">
@@ -13501,10 +13501,10 @@
         <v>468</v>
       </c>
       <c r="N309" t="n">
-        <v>3795.7100075529</v>
+        <v>3795.7100075657</v>
       </c>
       <c r="O309" t="n">
-        <v>1776392.283534757</v>
+        <v>1776392.283540748</v>
       </c>
       <c r="P309" t="n">
         <v>6200</v>
@@ -13890,10 +13890,10 @@
         <v>319</v>
       </c>
       <c r="N318" t="n">
-        <v>4890.9300488998</v>
+        <v>4890.9300489297</v>
       </c>
       <c r="O318" t="n">
-        <v>1560206.685599036</v>
+        <v>1560206.685608574</v>
       </c>
       <c r="P318" t="n">
         <v>8200</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>655</v>
+        <v>630</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -13982,19 +13982,19 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>655</v>
+        <v>630</v>
       </c>
       <c r="N320" t="n">
         <v>1203.38</v>
       </c>
       <c r="O320" t="n">
-        <v>788213.9</v>
+        <v>758129.4</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1244500</v>
+        <v>1197000</v>
       </c>
     </row>
     <row r="321">
@@ -14019,7 +14019,7 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
@@ -14028,19 +14028,19 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N321" t="n">
         <v>3472</v>
       </c>
       <c r="O321" t="n">
-        <v>437472</v>
+        <v>434000</v>
       </c>
       <c r="P321" t="n">
         <v>4800</v>
       </c>
       <c r="Q321" t="n">
-        <v>604800</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="322">
@@ -14689,10 +14689,10 @@
         <v>362</v>
       </c>
       <c r="N336" t="n">
-        <v>3594.2539962477</v>
+        <v>3594.2539736347</v>
       </c>
       <c r="O336" t="n">
-        <v>1301119.946641667</v>
+        <v>1301119.938455761</v>
       </c>
       <c r="P336" t="n">
         <v>6500</v>
@@ -14726,28 +14726,28 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>713</v>
+        <v>562</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>689</v>
+        <v>562</v>
       </c>
       <c r="N337" t="n">
         <v>489.88</v>
       </c>
       <c r="O337" t="n">
-        <v>337527.32</v>
+        <v>275312.56</v>
       </c>
       <c r="P337" t="n">
         <v>700</v>
       </c>
       <c r="Q337" t="n">
-        <v>482300</v>
+        <v>393400</v>
       </c>
     </row>
     <row r="338">
@@ -14861,10 +14861,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>3240.8500371058</v>
+        <v>3240.8500374532</v>
       </c>
       <c r="O340" t="n">
-        <v>3240.8500371058</v>
+        <v>3240.8500374532</v>
       </c>
       <c r="P340" t="n">
         <v>5200</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
@@ -14996,19 +14996,19 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N343" t="n">
-        <v>14822.378849611</v>
+        <v>14822.37884823</v>
       </c>
       <c r="O343" t="n">
-        <v>4268845.108687968</v>
+        <v>4254022.72944201</v>
       </c>
       <c r="P343" t="n">
         <v>24900</v>
       </c>
       <c r="Q343" t="n">
-        <v>7171200</v>
+        <v>7146300</v>
       </c>
     </row>
     <row r="344">
@@ -15128,10 +15128,10 @@
         <v>6357</v>
       </c>
       <c r="N346" t="n">
-        <v>2091.1308394896</v>
+        <v>2090.85</v>
       </c>
       <c r="O346" t="n">
-        <v>13293318.74663539</v>
+        <v>13291533.45</v>
       </c>
       <c r="P346" t="n">
         <v>2900</v>
@@ -15665,13 +15665,13 @@
         </is>
       </c>
       <c r="J359" t="n">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
         <v>2710</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M362" t="n">
         <v>2</v>
@@ -15935,7 +15935,7 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -15944,19 +15944,19 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N365" t="n">
-        <v>3041.6600132802</v>
+        <v>3041.6600134228</v>
       </c>
       <c r="O365" t="n">
-        <v>337624.2614741022</v>
+        <v>328499.2814496624</v>
       </c>
       <c r="P365" t="n">
         <v>5500</v>
       </c>
       <c r="Q365" t="n">
-        <v>610500</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="366">
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
@@ -15985,19 +15985,19 @@
         <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="N366" t="n">
         <v>3981.47</v>
       </c>
       <c r="O366" t="n">
-        <v>561387.27</v>
+        <v>537498.45</v>
       </c>
       <c r="P366" t="n">
         <v>7000</v>
       </c>
       <c r="Q366" t="n">
-        <v>987000</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="367">
@@ -16022,22 +16022,22 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>8126</v>
+        <v>8125</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>8125</v>
       </c>
       <c r="N367" t="n">
-        <v>4372.2107904123</v>
+        <v>4372.2107907508</v>
       </c>
       <c r="O367" t="n">
-        <v>35524212.67209994</v>
+        <v>35524212.67485025</v>
       </c>
       <c r="P367" t="n">
         <v>7500</v>
@@ -16194,7 +16194,7 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="K371" t="n">
         <v>0</v>
@@ -16203,19 +16203,19 @@
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="N371" t="n">
-        <v>1600.6713740458</v>
+        <v>1592.5665147453</v>
       </c>
       <c r="O371" t="n">
-        <v>685087.3480916023</v>
+        <v>635434.0393833747</v>
       </c>
       <c r="P371" t="n">
         <v>3900</v>
       </c>
       <c r="Q371" t="n">
-        <v>1669200</v>
+        <v>1556100</v>
       </c>
     </row>
     <row r="372">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16808,19 +16808,19 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N385" t="n">
         <v>4648.6</v>
       </c>
       <c r="O385" t="n">
-        <v>1097069.6</v>
+        <v>1087772.4</v>
       </c>
       <c r="P385" t="n">
         <v>8900</v>
       </c>
       <c r="Q385" t="n">
-        <v>2100400</v>
+        <v>2082600</v>
       </c>
     </row>
     <row r="386">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="K388" t="n">
         <v>0</v>
@@ -16934,19 +16934,19 @@
         <v>0</v>
       </c>
       <c r="M388" t="n">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="N388" t="n">
-        <v>1532.62902709</v>
+        <v>1532.6290268774</v>
       </c>
       <c r="O388" t="n">
-        <v>3909736.64810659</v>
+        <v>3906671.389510493</v>
       </c>
       <c r="P388" t="n">
         <v>1200</v>
       </c>
       <c r="Q388" t="n">
-        <v>3061200</v>
+        <v>3058800</v>
       </c>
     </row>
     <row r="389">
@@ -16966,7 +16966,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>1916</v>
+        <v>1908</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -16975,19 +16975,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>1916</v>
+        <v>1908</v>
       </c>
       <c r="N389" t="n">
         <v>17472.91</v>
       </c>
       <c r="O389" t="n">
-        <v>33478095.56</v>
+        <v>33338312.28</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
       </c>
       <c r="Q389" t="n">
-        <v>5556400</v>
+        <v>5533200</v>
       </c>
     </row>
     <row r="390">
@@ -17010,28 +17010,28 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
       </c>
       <c r="L390" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="N390" t="n">
         <v>1343.77</v>
       </c>
       <c r="O390" t="n">
-        <v>244566.14</v>
+        <v>232472.21</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>455000</v>
+        <v>432500</v>
       </c>
     </row>
     <row r="391">
@@ -17054,7 +17054,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17063,19 +17063,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="N391" t="n">
         <v>1530.63</v>
       </c>
       <c r="O391" t="n">
-        <v>2724521.4</v>
+        <v>2716868.25</v>
       </c>
       <c r="P391" t="n">
         <v>2900</v>
       </c>
       <c r="Q391" t="n">
-        <v>5162000</v>
+        <v>5147500</v>
       </c>
     </row>
     <row r="392">
@@ -17142,28 +17142,28 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>2520</v>
+        <v>2408</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>2498</v>
+        <v>2408</v>
       </c>
       <c r="N393" t="n">
         <v>1387.55</v>
       </c>
       <c r="O393" t="n">
-        <v>3466099.9</v>
+        <v>3341220.4</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
       </c>
       <c r="Q393" t="n">
-        <v>5745400</v>
+        <v>5538400</v>
       </c>
     </row>
     <row r="394">
@@ -17318,7 +17318,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -17327,19 +17327,19 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N397" t="n">
         <v>13304.13</v>
       </c>
       <c r="O397" t="n">
-        <v>1835969.94</v>
+        <v>1822665.81</v>
       </c>
       <c r="P397" t="n">
         <v>20900</v>
       </c>
       <c r="Q397" t="n">
-        <v>2884200</v>
+        <v>2863300</v>
       </c>
     </row>
     <row r="398">
@@ -17689,10 +17689,10 @@
         <v>1</v>
       </c>
       <c r="N405" t="n">
-        <v>3775.3787545788</v>
+        <v>3761.6</v>
       </c>
       <c r="O405" t="n">
-        <v>3775.3787545788</v>
+        <v>3761.6</v>
       </c>
       <c r="P405" t="n">
         <v>6900</v>
@@ -18286,7 +18286,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -18295,19 +18295,19 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N419" t="n">
         <v>3751</v>
       </c>
       <c r="O419" t="n">
-        <v>176297</v>
+        <v>172546</v>
       </c>
       <c r="P419" t="n">
         <v>6400</v>
       </c>
       <c r="Q419" t="n">
-        <v>300800</v>
+        <v>294400</v>
       </c>
     </row>
     <row r="420">
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -18385,19 +18385,19 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N421" t="n">
         <v>6557.57</v>
       </c>
       <c r="O421" t="n">
-        <v>347551.21</v>
+        <v>340993.64</v>
       </c>
       <c r="P421" t="n">
         <v>9900</v>
       </c>
       <c r="Q421" t="n">
-        <v>524700</v>
+        <v>514800</v>
       </c>
     </row>
     <row r="422">
@@ -18512,28 +18512,28 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>419</v>
+        <v>351</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>418</v>
+        <v>351</v>
       </c>
       <c r="N424" t="n">
-        <v>1630.9236566809</v>
+        <v>1630.923733916</v>
       </c>
       <c r="O424" t="n">
-        <v>681726.0884926162</v>
+        <v>572454.230604516</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1045000</v>
+        <v>877500</v>
       </c>
     </row>
     <row r="425">
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -18613,19 +18613,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N426" t="n">
-        <v>1690.5969630746</v>
+        <v>1690.5964846154</v>
       </c>
       <c r="O426" t="n">
-        <v>13524.7757045968</v>
+        <v>6762.3859384616</v>
       </c>
       <c r="P426" t="n">
         <v>2900</v>
       </c>
       <c r="Q426" t="n">
-        <v>23200</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="427">
@@ -18650,28 +18650,28 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>589</v>
+        <v>507</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>585</v>
+        <v>507</v>
       </c>
       <c r="N427" t="n">
-        <v>1550.1937050719</v>
+        <v>1550.1937906027</v>
       </c>
       <c r="O427" t="n">
-        <v>906863.3174670615</v>
+        <v>785948.2518355688</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1462500</v>
+        <v>1267500</v>
       </c>
     </row>
     <row r="428">
@@ -18696,28 +18696,28 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N428" t="n">
-        <v>1579.3903753351</v>
+        <v>1579.3897428571</v>
       </c>
       <c r="O428" t="n">
-        <v>157939.03753351</v>
+        <v>151621.4153142816</v>
       </c>
       <c r="P428" t="n">
         <v>2900</v>
       </c>
       <c r="Q428" t="n">
-        <v>290000</v>
+        <v>278400</v>
       </c>
     </row>
     <row r="429">
@@ -18742,7 +18742,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -18751,19 +18751,19 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="N429" t="n">
-        <v>2403.5121166602</v>
+        <v>2403.5124244849</v>
       </c>
       <c r="O429" t="n">
-        <v>1845897.305595033</v>
+        <v>1795423.78109022</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
       </c>
       <c r="Q429" t="n">
-        <v>2688000</v>
+        <v>2614500</v>
       </c>
     </row>
     <row r="430">
@@ -18832,7 +18832,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -18841,19 +18841,19 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="N431" t="n">
-        <v>2521.5268283582</v>
+        <v>2521.5190322581</v>
       </c>
       <c r="O431" t="n">
-        <v>524477.5802985056</v>
+        <v>469002.5400000066</v>
       </c>
       <c r="P431" t="n">
         <v>3900</v>
       </c>
       <c r="Q431" t="n">
-        <v>811200</v>
+        <v>725400</v>
       </c>
     </row>
     <row r="432">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -18882,19 +18882,19 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N432" t="n">
-        <v>1232.8074537037</v>
+        <v>1232.8070952381</v>
       </c>
       <c r="O432" t="n">
-        <v>77666.8695833331</v>
+        <v>70270.0044285717</v>
       </c>
       <c r="P432" t="n">
         <v>2400</v>
       </c>
       <c r="Q432" t="n">
-        <v>151200</v>
+        <v>136800</v>
       </c>
     </row>
     <row r="433">
@@ -19081,7 +19081,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -19090,19 +19090,19 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N437" t="n">
-        <v>1830.7553551913</v>
+        <v>1830.7553038674</v>
       </c>
       <c r="O437" t="n">
-        <v>309397.6550273297</v>
+        <v>305736.1357458558</v>
       </c>
       <c r="P437" t="n">
         <v>3150</v>
       </c>
       <c r="Q437" t="n">
-        <v>532350</v>
+        <v>526050</v>
       </c>
     </row>
     <row r="438">
@@ -19166,7 +19166,7 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -19175,19 +19175,19 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N439" t="n">
         <v>2423.42</v>
       </c>
       <c r="O439" t="n">
-        <v>743989.9400000001</v>
+        <v>739143.1</v>
       </c>
       <c r="P439" t="n">
         <v>3150</v>
       </c>
       <c r="Q439" t="n">
-        <v>967050</v>
+        <v>960750</v>
       </c>
     </row>
     <row r="440">
@@ -20839,7 +20839,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -20848,19 +20848,19 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N477" t="n">
         <v>6280.31</v>
       </c>
       <c r="O477" t="n">
-        <v>25121.24</v>
+        <v>12560.62</v>
       </c>
       <c r="P477" t="n">
         <v>10500</v>
       </c>
       <c r="Q477" t="n">
-        <v>42000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="478">
@@ -21172,7 +21172,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -21181,19 +21181,19 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N485" t="n">
         <v>20352</v>
       </c>
       <c r="O485" t="n">
-        <v>142464</v>
+        <v>122112</v>
       </c>
       <c r="P485" t="n">
         <v>20900</v>
       </c>
       <c r="Q485" t="n">
-        <v>146300</v>
+        <v>125400</v>
       </c>
     </row>
     <row r="486">
@@ -21844,28 +21844,28 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
       </c>
       <c r="L501" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N501" t="n">
         <v>2992.7</v>
       </c>
       <c r="O501" t="n">
-        <v>38905.1</v>
+        <v>17956.2</v>
       </c>
       <c r="P501" t="n">
         <v>5900</v>
       </c>
       <c r="Q501" t="n">
-        <v>76700</v>
+        <v>35400</v>
       </c>
     </row>
     <row r="502">
@@ -22782,7 +22782,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -22791,19 +22791,19 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N523" t="n">
         <v>1969</v>
       </c>
       <c r="O523" t="n">
-        <v>372141</v>
+        <v>368203</v>
       </c>
       <c r="P523" t="n">
         <v>1500</v>
       </c>
       <c r="Q523" t="n">
-        <v>283500</v>
+        <v>280500</v>
       </c>
     </row>
     <row r="524">
@@ -23285,7 +23285,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -23294,19 +23294,19 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N535" t="n">
         <v>2517.22</v>
       </c>
       <c r="O535" t="n">
-        <v>93137.14</v>
+        <v>88102.7</v>
       </c>
       <c r="P535" t="n">
         <v>4200</v>
       </c>
       <c r="Q535" t="n">
-        <v>155400</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="536">
@@ -23367,7 +23367,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -23376,19 +23376,19 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N537" t="n">
-        <v>2029.8738600103</v>
+        <v>2029.8738739669</v>
       </c>
       <c r="O537" t="n">
-        <v>442512.5014822454</v>
+        <v>428303.3874070159</v>
       </c>
       <c r="P537" t="n">
         <v>3600</v>
       </c>
       <c r="Q537" t="n">
-        <v>784800</v>
+        <v>759600</v>
       </c>
     </row>
     <row r="538">
@@ -23900,13 +23900,13 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
       </c>
       <c r="L550" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M550" t="n">
         <v>129</v>
@@ -24195,7 +24195,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -24204,19 +24204,19 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="N557" t="n">
-        <v>880.32952448883</v>
+        <v>880.32953355545</v>
       </c>
       <c r="O557" t="n">
-        <v>538761.6689871639</v>
+        <v>535240.3564017136</v>
       </c>
       <c r="P557" t="n">
         <v>1200</v>
       </c>
       <c r="Q557" t="n">
-        <v>734400</v>
+        <v>729600</v>
       </c>
     </row>
     <row r="558">
@@ -25460,7 +25460,7 @@
         </is>
       </c>
       <c r="J587" t="n">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K587" t="n">
         <v>0</v>
@@ -25469,19 +25469,19 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="N587" t="n">
         <v>3877.89</v>
       </c>
       <c r="O587" t="n">
-        <v>973350.39</v>
+        <v>946205.1599999999</v>
       </c>
       <c r="P587" t="n">
         <v>6500</v>
       </c>
       <c r="Q587" t="n">
-        <v>1631500</v>
+        <v>1586000</v>
       </c>
     </row>
     <row r="588">
@@ -25550,7 +25550,7 @@
         </is>
       </c>
       <c r="J589" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K589" t="n">
         <v>0</v>
@@ -25559,19 +25559,19 @@
         <v>0</v>
       </c>
       <c r="M589" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="N589" t="n">
-        <v>4285.1955337691</v>
+        <v>4285.1956570156</v>
       </c>
       <c r="O589" t="n">
-        <v>959883.7995642783</v>
+        <v>917031.8706013383</v>
       </c>
       <c r="P589" t="n">
         <v>6900</v>
       </c>
       <c r="Q589" t="n">
-        <v>1545600</v>
+        <v>1476600</v>
       </c>
     </row>
     <row r="590">
@@ -25599,7 +25599,7 @@
         </is>
       </c>
       <c r="J590" t="n">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
@@ -25608,19 +25608,19 @@
         <v>0</v>
       </c>
       <c r="M590" t="n">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="N590" t="n">
         <v>9776.99</v>
       </c>
       <c r="O590" t="n">
-        <v>2356254.59</v>
+        <v>2268261.68</v>
       </c>
       <c r="P590" t="n">
         <v>15900</v>
       </c>
       <c r="Q590" t="n">
-        <v>3831900</v>
+        <v>3688800</v>
       </c>
     </row>
     <row r="591">
@@ -25845,7 +25845,7 @@
         </is>
       </c>
       <c r="J596" t="n">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="K596" t="n">
         <v>0</v>
@@ -25854,19 +25854,19 @@
         <v>0</v>
       </c>
       <c r="M596" t="n">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N596" t="n">
         <v>1106</v>
       </c>
       <c r="O596" t="n">
-        <v>340648</v>
+        <v>332906</v>
       </c>
       <c r="P596" t="n">
         <v>2100</v>
       </c>
       <c r="Q596" t="n">
-        <v>646800</v>
+        <v>632100</v>
       </c>
     </row>
     <row r="597">
@@ -26067,10 +26067,10 @@
         <v>201</v>
       </c>
       <c r="N601" t="n">
-        <v>4605.2147408106</v>
+        <v>4605.2147497639</v>
       </c>
       <c r="O601" t="n">
-        <v>925648.1629029306</v>
+        <v>925648.1647025439</v>
       </c>
       <c r="P601" t="n">
         <v>7600</v>
@@ -26287,10 +26287,10 @@
         <v>2</v>
       </c>
       <c r="N606" t="n">
-        <v>13513.643082707</v>
+        <v>13513.643106061</v>
       </c>
       <c r="O606" t="n">
-        <v>27027.286165414</v>
+        <v>27027.286212122</v>
       </c>
       <c r="P606" t="n">
         <v>21900</v>
@@ -26449,7 +26449,7 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
@@ -26458,19 +26458,19 @@
         <v>0</v>
       </c>
       <c r="M610" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N610" t="n">
         <v>1650</v>
       </c>
       <c r="O610" t="n">
-        <v>656700</v>
+        <v>655050</v>
       </c>
       <c r="P610" t="n">
         <v>2900</v>
       </c>
       <c r="Q610" t="n">
-        <v>1154200</v>
+        <v>1151300</v>
       </c>
     </row>
     <row r="611">
@@ -26490,7 +26490,7 @@
         </is>
       </c>
       <c r="J611" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K611" t="n">
         <v>0</v>
@@ -26499,19 +26499,19 @@
         <v>0</v>
       </c>
       <c r="M611" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N611" t="n">
         <v>2856</v>
       </c>
       <c r="O611" t="n">
-        <v>328440</v>
+        <v>322728</v>
       </c>
       <c r="P611" t="n">
         <v>2400</v>
       </c>
       <c r="Q611" t="n">
-        <v>276000</v>
+        <v>271200</v>
       </c>
     </row>
     <row r="612">
@@ -26572,7 +26572,7 @@
         </is>
       </c>
       <c r="J613" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K613" t="n">
         <v>0</v>
@@ -26581,19 +26581,19 @@
         <v>0</v>
       </c>
       <c r="M613" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N613" t="n">
         <v>1679</v>
       </c>
       <c r="O613" t="n">
-        <v>705180</v>
+        <v>701822</v>
       </c>
       <c r="P613" t="n">
         <v>2900</v>
       </c>
       <c r="Q613" t="n">
-        <v>1218000</v>
+        <v>1212200</v>
       </c>
     </row>
     <row r="614">
@@ -26613,7 +26613,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
@@ -26622,19 +26622,19 @@
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="N614" t="n">
         <v>1358</v>
       </c>
       <c r="O614" t="n">
-        <v>685790</v>
+        <v>681716</v>
       </c>
       <c r="P614" t="n">
         <v>2400</v>
       </c>
       <c r="Q614" t="n">
-        <v>1212000</v>
+        <v>1204800</v>
       </c>
     </row>
     <row r="615">
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="J620" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K620" t="n">
         <v>0</v>
@@ -26868,19 +26868,19 @@
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N620" t="n">
         <v>1352</v>
       </c>
       <c r="O620" t="n">
-        <v>235248</v>
+        <v>232544</v>
       </c>
       <c r="P620" t="n">
         <v>2400</v>
       </c>
       <c r="Q620" t="n">
-        <v>417600</v>
+        <v>412800</v>
       </c>
     </row>
     <row r="621">
@@ -27661,13 +27661,13 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M639" t="n">
         <v>344</v>
@@ -27789,7 +27789,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -27798,19 +27798,19 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N642" t="n">
         <v>2014</v>
       </c>
       <c r="O642" t="n">
-        <v>489402</v>
+        <v>481346</v>
       </c>
       <c r="P642" t="n">
         <v>2000</v>
       </c>
       <c r="Q642" t="n">
-        <v>486000</v>
+        <v>478000</v>
       </c>
     </row>
     <row r="643">
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -27885,19 +27885,19 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N644" t="n">
         <v>22730.48</v>
       </c>
       <c r="O644" t="n">
-        <v>1227445.92</v>
+        <v>1204715.44</v>
       </c>
       <c r="P644" t="n">
         <v>36900</v>
       </c>
       <c r="Q644" t="n">
-        <v>1992600</v>
+        <v>1955700</v>
       </c>
     </row>
     <row r="645">
@@ -28149,10 +28149,10 @@
         <v>142</v>
       </c>
       <c r="N650" t="n">
-        <v>27123.765205993</v>
+        <v>27123.765196998</v>
       </c>
       <c r="O650" t="n">
-        <v>3851574.659251006</v>
+        <v>3851574.657973716</v>
       </c>
       <c r="P650" t="n">
         <v>44500</v>
@@ -28342,7 +28342,7 @@
         </is>
       </c>
       <c r="J655" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K655" t="n">
         <v>0</v>
@@ -28351,19 +28351,19 @@
         <v>0</v>
       </c>
       <c r="M655" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N655" t="n">
         <v>3242</v>
       </c>
       <c r="O655" t="n">
-        <v>32420</v>
+        <v>25936</v>
       </c>
       <c r="P655" t="n">
         <v>5600</v>
       </c>
       <c r="Q655" t="n">
-        <v>56000</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="656">
@@ -28516,7 +28516,7 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
@@ -28525,19 +28525,19 @@
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N659" t="n">
-        <v>8332.779622166199</v>
+        <v>8332.779621212099</v>
       </c>
       <c r="O659" t="n">
-        <v>666622.3697732959</v>
+        <v>658289.5900757558</v>
       </c>
       <c r="P659" t="n">
         <v>14900</v>
       </c>
       <c r="Q659" t="n">
-        <v>1192000</v>
+        <v>1177100</v>
       </c>
     </row>
     <row r="660">
@@ -28859,28 +28859,28 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N667" t="n">
-        <v>1561.000952381</v>
+        <v>1561.0010652921</v>
       </c>
       <c r="O667" t="n">
-        <v>443324.270476204</v>
+        <v>430836.2940206196</v>
       </c>
       <c r="P667" t="n">
         <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>823600</v>
+        <v>800400</v>
       </c>
     </row>
     <row r="668">
@@ -29530,7 +29530,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -29539,19 +29539,19 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N683" t="n">
         <v>11662.4</v>
       </c>
       <c r="O683" t="n">
-        <v>81636.8</v>
+        <v>69974.39999999999</v>
       </c>
       <c r="P683" t="n">
         <v>19900</v>
       </c>
       <c r="Q683" t="n">
-        <v>139300</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="684">
@@ -29786,7 +29786,7 @@
         </is>
       </c>
       <c r="J689" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K689" t="n">
         <v>0</v>
@@ -29795,19 +29795,19 @@
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N689" t="n">
         <v>9627.34</v>
       </c>
       <c r="O689" t="n">
-        <v>413975.62</v>
+        <v>385093.6</v>
       </c>
       <c r="P689" t="n">
         <v>15900</v>
       </c>
       <c r="Q689" t="n">
-        <v>683700</v>
+        <v>636000</v>
       </c>
     </row>
     <row r="690">
@@ -31107,13 +31107,13 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K720" t="n">
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M720" t="n">
         <v>5</v>
@@ -31245,13 +31245,13 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K723" t="n">
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M723" t="n">
         <v>14</v>
@@ -31475,13 +31475,13 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M728" t="n">
         <v>17</v>
@@ -31662,13 +31662,13 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
       </c>
       <c r="L732" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M732" t="n">
         <v>12</v>
@@ -31708,13 +31708,13 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M733" t="n">
         <v>53</v>
@@ -31800,7 +31800,7 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
@@ -31809,19 +31809,19 @@
         <v>0</v>
       </c>
       <c r="M735" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N735" t="n">
-        <v>1664.3554968553</v>
+        <v>1664.3547889182</v>
       </c>
       <c r="O735" t="n">
-        <v>59916.7978867908</v>
+        <v>43273.2245118732</v>
       </c>
       <c r="P735" t="n">
         <v>2900</v>
       </c>
       <c r="Q735" t="n">
-        <v>104400</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="736">
@@ -32212,7 +32212,7 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
@@ -32221,19 +32221,19 @@
         <v>0</v>
       </c>
       <c r="M744" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N744" t="n">
         <v>18536</v>
       </c>
       <c r="O744" t="n">
-        <v>148288</v>
+        <v>129752</v>
       </c>
       <c r="P744" t="n">
         <v>30900</v>
       </c>
       <c r="Q744" t="n">
-        <v>247200</v>
+        <v>216300</v>
       </c>
     </row>
     <row r="745">
@@ -32638,10 +32638,10 @@
         <v>18</v>
       </c>
       <c r="N753" t="n">
-        <v>23521.624262295</v>
+        <v>23521.624067797</v>
       </c>
       <c r="O753" t="n">
-        <v>423389.23672131</v>
+        <v>423389.233220346</v>
       </c>
       <c r="P753" t="n">
         <v>39000</v>
@@ -32776,10 +32776,10 @@
         <v>1233</v>
       </c>
       <c r="N756" t="n">
-        <v>1778.4726458554</v>
+        <v>1778.4726494689</v>
       </c>
       <c r="O756" t="n">
-        <v>2192856.772339708</v>
+        <v>2192856.776795154</v>
       </c>
       <c r="P756" t="n">
         <v>4900</v>
@@ -33181,7 +33181,7 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
@@ -33190,19 +33190,19 @@
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N765" t="n">
         <v>5148</v>
       </c>
       <c r="O765" t="n">
-        <v>422136</v>
+        <v>406692</v>
       </c>
       <c r="P765" t="n">
         <v>8600</v>
       </c>
       <c r="Q765" t="n">
-        <v>705200</v>
+        <v>679400</v>
       </c>
     </row>
     <row r="766">
@@ -34934,7 +34934,7 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K803" t="n">
         <v>0</v>
@@ -34943,19 +34943,19 @@
         <v>0</v>
       </c>
       <c r="M803" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N803" t="n">
         <v>3424</v>
       </c>
       <c r="O803" t="n">
-        <v>58208</v>
+        <v>54784</v>
       </c>
       <c r="P803" t="n">
         <v>5900</v>
       </c>
       <c r="Q803" t="n">
-        <v>100300</v>
+        <v>94400</v>
       </c>
     </row>
     <row r="804">
@@ -35072,7 +35072,7 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
@@ -35081,19 +35081,19 @@
         <v>0</v>
       </c>
       <c r="M806" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N806" t="n">
         <v>8858.16</v>
       </c>
       <c r="O806" t="n">
-        <v>451766.16</v>
+        <v>416333.52</v>
       </c>
       <c r="P806" t="n">
         <v>15500</v>
       </c>
       <c r="Q806" t="n">
-        <v>790500</v>
+        <v>728500</v>
       </c>
     </row>
     <row r="807">
@@ -35118,7 +35118,7 @@
         </is>
       </c>
       <c r="J807" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K807" t="n">
         <v>0</v>
@@ -35127,19 +35127,19 @@
         <v>0</v>
       </c>
       <c r="M807" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N807" t="n">
         <v>3764</v>
       </c>
       <c r="O807" t="n">
-        <v>429096</v>
+        <v>425332</v>
       </c>
       <c r="P807" t="n">
         <v>6200</v>
       </c>
       <c r="Q807" t="n">
-        <v>706800</v>
+        <v>700600</v>
       </c>
     </row>
     <row r="808">
@@ -35256,7 +35256,7 @@
         </is>
       </c>
       <c r="J810" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K810" t="n">
         <v>0</v>
@@ -35265,19 +35265,19 @@
         <v>0</v>
       </c>
       <c r="M810" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N810" t="n">
-        <v>2252.2969855832</v>
+        <v>2252.2972418478</v>
       </c>
       <c r="O810" t="n">
-        <v>304060.093053732</v>
+        <v>277032.5607472794</v>
       </c>
       <c r="P810" t="n">
         <v>3900</v>
       </c>
       <c r="Q810" t="n">
-        <v>526500</v>
+        <v>479700</v>
       </c>
     </row>
     <row r="811">
@@ -35501,10 +35501,10 @@
         <v>450</v>
       </c>
       <c r="N815" t="n">
-        <v>2328.1187098747</v>
+        <v>2328.1187082951</v>
       </c>
       <c r="O815" t="n">
-        <v>1047653.419443615</v>
+        <v>1047653.418732795</v>
       </c>
       <c r="P815" t="n">
         <v>4500</v>
@@ -36513,10 +36513,10 @@
         <v>12</v>
       </c>
       <c r="N837" t="n">
-        <v>3903.7366972477</v>
+        <v>3903.736710023</v>
       </c>
       <c r="O837" t="n">
-        <v>46844.8403669724</v>
+        <v>46844.840520276</v>
       </c>
       <c r="P837" t="n">
         <v>7500</v>
@@ -36726,13 +36726,13 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>4</v>
@@ -36910,7 +36910,7 @@
         </is>
       </c>
       <c r="J846" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K846" t="n">
         <v>0</v>
@@ -36919,19 +36919,19 @@
         <v>0</v>
       </c>
       <c r="M846" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N846" t="n">
         <v>2629</v>
       </c>
       <c r="O846" t="n">
-        <v>670395</v>
+        <v>665137</v>
       </c>
       <c r="P846" t="n">
         <v>4500</v>
       </c>
       <c r="Q846" t="n">
-        <v>1147500</v>
+        <v>1138500</v>
       </c>
     </row>
     <row r="847">
@@ -36968,10 +36968,10 @@
         <v>15</v>
       </c>
       <c r="N847" t="n">
-        <v>5869.1726202661</v>
+        <v>5869.1726127049</v>
       </c>
       <c r="O847" t="n">
-        <v>88037.58930399151</v>
+        <v>88037.58919057349</v>
       </c>
       <c r="P847" t="n">
         <v>9500</v>
@@ -37554,7 +37554,7 @@
         </is>
       </c>
       <c r="J860" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K860" t="n">
         <v>0</v>
@@ -37563,19 +37563,19 @@
         <v>0</v>
       </c>
       <c r="M860" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N860" t="n">
         <v>16086</v>
       </c>
       <c r="O860" t="n">
-        <v>289548</v>
+        <v>257376</v>
       </c>
       <c r="P860" t="n">
         <v>25900</v>
       </c>
       <c r="Q860" t="n">
-        <v>466200</v>
+        <v>414400</v>
       </c>
     </row>
     <row r="861">
@@ -38656,7 +38656,7 @@
         </is>
       </c>
       <c r="J884" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K884" t="n">
         <v>0</v>
@@ -38665,19 +38665,19 @@
         <v>0</v>
       </c>
       <c r="M884" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N884" t="n">
         <v>4303</v>
       </c>
       <c r="O884" t="n">
-        <v>159211</v>
+        <v>137696</v>
       </c>
       <c r="P884" t="n">
         <v>7900</v>
       </c>
       <c r="Q884" t="n">
-        <v>292300</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="885">
@@ -38840,28 +38840,28 @@
         </is>
       </c>
       <c r="J888" t="n">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="K888" t="n">
         <v>0</v>
       </c>
       <c r="L888" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M888" t="n">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="N888" t="n">
         <v>1326</v>
       </c>
       <c r="O888" t="n">
-        <v>2240940</v>
+        <v>2238288</v>
       </c>
       <c r="P888" t="n">
         <v>2500</v>
       </c>
       <c r="Q888" t="n">
-        <v>4225000</v>
+        <v>4220000</v>
       </c>
     </row>
     <row r="889">
@@ -38886,7 +38886,7 @@
         </is>
       </c>
       <c r="J889" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K889" t="n">
         <v>0</v>
@@ -38895,19 +38895,19 @@
         <v>0</v>
       </c>
       <c r="M889" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N889" t="n">
         <v>10713.21</v>
       </c>
       <c r="O889" t="n">
-        <v>224977.41</v>
+        <v>214264.2</v>
       </c>
       <c r="P889" t="n">
         <v>20900</v>
       </c>
       <c r="Q889" t="n">
-        <v>438900</v>
+        <v>418000</v>
       </c>
     </row>
     <row r="890">
@@ -39453,10 +39453,10 @@
         <v>1297</v>
       </c>
       <c r="N901" t="n">
-        <v>1516.0387951453</v>
+        <v>1516.0387934921</v>
       </c>
       <c r="O901" t="n">
-        <v>1966302.317303454</v>
+        <v>1966302.315159254</v>
       </c>
       <c r="P901" t="n">
         <v>2300</v>
@@ -39543,10 +39543,10 @@
         <v>295</v>
       </c>
       <c r="N903" t="n">
-        <v>2458.5130690113</v>
+        <v>2458.5130528766</v>
       </c>
       <c r="O903" t="n">
-        <v>725261.3553583336</v>
+        <v>725261.350598597</v>
       </c>
       <c r="P903" t="n">
         <v>3500</v>
@@ -39589,10 +39589,10 @@
         <v>5</v>
       </c>
       <c r="N904" t="n">
-        <v>1907.3930202775</v>
+        <v>1907.3929677419</v>
       </c>
       <c r="O904" t="n">
-        <v>9536.965101387501</v>
+        <v>9536.9648387095</v>
       </c>
       <c r="P904" t="n">
         <v>2500</v>
@@ -39669,7 +39669,7 @@
         </is>
       </c>
       <c r="J906" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K906" t="n">
         <v>0</v>
@@ -39678,19 +39678,19 @@
         <v>0</v>
       </c>
       <c r="M906" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="N906" t="n">
-        <v>2079.3839709361</v>
+        <v>2079.3839648173</v>
       </c>
       <c r="O906" t="n">
-        <v>677879.1745251686</v>
+        <v>673720.4046008051</v>
       </c>
       <c r="P906" t="n">
         <v>2900</v>
       </c>
       <c r="Q906" t="n">
-        <v>945400</v>
+        <v>939600</v>
       </c>
     </row>
     <row r="907">
@@ -39715,7 +39715,7 @@
         </is>
       </c>
       <c r="J907" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K907" t="n">
         <v>0</v>
@@ -39724,19 +39724,19 @@
         <v>0</v>
       </c>
       <c r="M907" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="N907" t="n">
-        <v>1803.0156368474</v>
+        <v>1803.0156556557</v>
       </c>
       <c r="O907" t="n">
-        <v>564343.8943332362</v>
+        <v>557131.8375976112</v>
       </c>
       <c r="P907" t="n">
         <v>2500</v>
       </c>
       <c r="Q907" t="n">
-        <v>782500</v>
+        <v>772500</v>
       </c>
     </row>
     <row r="908">
@@ -39761,7 +39761,7 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
@@ -39770,19 +39770,19 @@
         <v>0</v>
       </c>
       <c r="M908" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N908" t="n">
-        <v>3306.5946666667</v>
+        <v>3306.5946508172</v>
       </c>
       <c r="O908" t="n">
-        <v>307513.3040000031</v>
+        <v>300900.1132243652</v>
       </c>
       <c r="P908" t="n">
         <v>4900</v>
       </c>
       <c r="Q908" t="n">
-        <v>455700</v>
+        <v>445900</v>
       </c>
     </row>
     <row r="909">
@@ -39819,10 +39819,10 @@
         <v>106</v>
       </c>
       <c r="N909" t="n">
-        <v>2108.7921081831</v>
+        <v>2108.7923742027</v>
       </c>
       <c r="O909" t="n">
-        <v>223531.9634674086</v>
+        <v>223531.9916654862</v>
       </c>
       <c r="P909" t="n">
         <v>2900</v>
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
@@ -39862,19 +39862,19 @@
         <v>0</v>
       </c>
       <c r="M910" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N910" t="n">
-        <v>2056.0829819789</v>
+        <v>2056.0829556314</v>
       </c>
       <c r="O910" t="n">
-        <v>594207.9817919021</v>
+        <v>590095.8082662119</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
       </c>
       <c r="Q910" t="n">
-        <v>838100</v>
+        <v>832300</v>
       </c>
     </row>
     <row r="911">
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="J911" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K911" t="n">
         <v>0</v>
@@ -39908,19 +39908,19 @@
         <v>0</v>
       </c>
       <c r="M911" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N911" t="n">
-        <v>3224.5688090551</v>
+        <v>3224.5688526212</v>
       </c>
       <c r="O911" t="n">
-        <v>503032.7342125956</v>
+        <v>483685.32789318</v>
       </c>
       <c r="P911" t="n">
         <v>4500</v>
       </c>
       <c r="Q911" t="n">
-        <v>702000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="912">
@@ -39945,7 +39945,7 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K912" t="n">
         <v>0</v>
@@ -39954,19 +39954,19 @@
         <v>0</v>
       </c>
       <c r="M912" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N912" t="n">
-        <v>1655.9307861426</v>
+        <v>1655.9307707708</v>
       </c>
       <c r="O912" t="n">
-        <v>382520.0115989406</v>
+        <v>377552.2157357424</v>
       </c>
       <c r="P912" t="n">
         <v>2500</v>
       </c>
       <c r="Q912" t="n">
-        <v>577500</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="913">
@@ -40086,7 +40086,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40095,19 +40095,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N915" t="n">
         <v>1662</v>
       </c>
       <c r="O915" t="n">
-        <v>365640</v>
+        <v>362316</v>
       </c>
       <c r="P915" t="n">
         <v>2900</v>
       </c>
       <c r="Q915" t="n">
-        <v>638000</v>
+        <v>632200</v>
       </c>
     </row>
     <row r="916">
@@ -40178,28 +40178,28 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M917" t="n">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="N917" t="n">
-        <v>1592.2788188188</v>
+        <v>1592.279767184</v>
       </c>
       <c r="O917" t="n">
-        <v>694233.5650049967</v>
+        <v>656019.264079808</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
       </c>
       <c r="Q917" t="n">
-        <v>1090000</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="918">
@@ -40309,7 +40309,7 @@
         </is>
       </c>
       <c r="J920" t="n">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="K920" t="n">
         <v>0</v>
@@ -40318,19 +40318,19 @@
         <v>0</v>
       </c>
       <c r="M920" t="n">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="N920" t="n">
-        <v>2311.9201658768</v>
+        <v>2311.9177393617</v>
       </c>
       <c r="O920" t="n">
-        <v>499374.7558293889</v>
+        <v>467007.3833510634</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
       </c>
       <c r="Q920" t="n">
-        <v>756000</v>
+        <v>707000</v>
       </c>
     </row>
     <row r="921">
@@ -40355,7 +40355,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40364,19 +40364,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="N921" t="n">
-        <v>1906.1827536232</v>
+        <v>1906.1819786096</v>
       </c>
       <c r="O921" t="n">
-        <v>299270.6923188424</v>
+        <v>270677.8409625632</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
       </c>
       <c r="Q921" t="n">
-        <v>455300</v>
+        <v>411800</v>
       </c>
     </row>
     <row r="922">
@@ -40401,28 +40401,28 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="N922" t="n">
-        <v>3033.7165703971</v>
+        <v>3033.71092827</v>
       </c>
       <c r="O922" t="n">
-        <v>688653.6614801417</v>
+        <v>640113.0058649699</v>
       </c>
       <c r="P922" t="n">
         <v>4500</v>
       </c>
       <c r="Q922" t="n">
-        <v>1021500</v>
+        <v>949500</v>
       </c>
     </row>
     <row r="923">
@@ -40447,7 +40447,7 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
@@ -40456,19 +40456,19 @@
         <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="N923" t="n">
-        <v>1668.6326421405</v>
+        <v>1668.6340069686</v>
       </c>
       <c r="O923" t="n">
-        <v>357087.385418067</v>
+        <v>337064.0694076572</v>
       </c>
       <c r="P923" t="n">
         <v>2500</v>
       </c>
       <c r="Q923" t="n">
-        <v>535000</v>
+        <v>505000</v>
       </c>
     </row>
     <row r="924">
@@ -40493,7 +40493,7 @@
         </is>
       </c>
       <c r="J924" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K924" t="n">
         <v>0</v>
@@ -40502,19 +40502,19 @@
         <v>0</v>
       </c>
       <c r="M924" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="N924" t="n">
-        <v>2546.9837028825</v>
+        <v>2546.9835746606</v>
       </c>
       <c r="O924" t="n">
-        <v>374406.6043237275</v>
+        <v>351483.7333031628</v>
       </c>
       <c r="P924" t="n">
         <v>3900</v>
       </c>
       <c r="Q924" t="n">
-        <v>573300</v>
+        <v>538200</v>
       </c>
     </row>
     <row r="925">
@@ -40539,7 +40539,7 @@
         </is>
       </c>
       <c r="J925" t="n">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="K925" t="n">
         <v>0</v>
@@ -40548,19 +40548,19 @@
         <v>0</v>
       </c>
       <c r="M925" t="n">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="N925" t="n">
-        <v>1259.274561681</v>
+        <v>1259.2746169678</v>
       </c>
       <c r="O925" t="n">
-        <v>1372609.27223229</v>
+        <v>1368831.508643999</v>
       </c>
       <c r="P925" t="n">
         <v>1900</v>
       </c>
       <c r="Q925" t="n">
-        <v>2071000</v>
+        <v>2065300</v>
       </c>
     </row>
     <row r="926">
@@ -40718,7 +40718,7 @@
         </is>
       </c>
       <c r="J929" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="K929" t="n">
         <v>0</v>
@@ -40727,19 +40727,19 @@
         <v>0</v>
       </c>
       <c r="M929" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="N929" t="n">
-        <v>2556.7460207612</v>
+        <v>2556.7462815884</v>
       </c>
       <c r="O929" t="n">
-        <v>327263.4906574336</v>
+        <v>296582.5686642544</v>
       </c>
       <c r="P929" t="n">
         <v>3900</v>
       </c>
       <c r="Q929" t="n">
-        <v>499200</v>
+        <v>452400</v>
       </c>
     </row>
     <row r="930">
@@ -40774,10 +40774,10 @@
         <v>2650</v>
       </c>
       <c r="N930" t="n">
-        <v>692.15222920696</v>
+        <v>692.1522422179</v>
       </c>
       <c r="O930" t="n">
-        <v>1834203.407398444</v>
+        <v>1834203.441877435</v>
       </c>
       <c r="P930" t="n">
         <v>1200</v>
@@ -40959,10 +40959,10 @@
         <v>570</v>
       </c>
       <c r="N934" t="n">
-        <v>1185.3195716639</v>
+        <v>1185.31957078</v>
       </c>
       <c r="O934" t="n">
-        <v>675632.155848423</v>
+        <v>675632.1553446</v>
       </c>
       <c r="P934" t="n">
         <v>1900</v>
@@ -41323,7 +41323,7 @@
         </is>
       </c>
       <c r="J942" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K942" t="n">
         <v>0</v>
@@ -41332,19 +41332,19 @@
         <v>0</v>
       </c>
       <c r="M942" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N942" t="n">
         <v>2857.22</v>
       </c>
       <c r="O942" t="n">
-        <v>1451467.76</v>
+        <v>1448610.54</v>
       </c>
       <c r="P942" t="n">
         <v>4900</v>
       </c>
       <c r="Q942" t="n">
-        <v>2489200</v>
+        <v>2484300</v>
       </c>
     </row>
     <row r="943">
@@ -41418,7 +41418,7 @@
         </is>
       </c>
       <c r="J944" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K944" t="n">
         <v>0</v>
@@ -41427,19 +41427,19 @@
         <v>0</v>
       </c>
       <c r="M944" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N944" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O944" t="n">
-        <v>3318735.98</v>
+        <v>3309790.6</v>
       </c>
       <c r="P944" t="n">
         <v>14900</v>
       </c>
       <c r="Q944" t="n">
-        <v>5527900</v>
+        <v>5513000</v>
       </c>
     </row>
     <row r="945">
@@ -41848,10 +41848,10 @@
         <v>1150</v>
       </c>
       <c r="N953" t="n">
-        <v>574.67194894975</v>
+        <v>574.67195050559</v>
       </c>
       <c r="O953" t="n">
-        <v>660872.7412922125</v>
+        <v>660872.7430814285</v>
       </c>
       <c r="P953" t="n">
         <v>800</v>
@@ -42302,10 +42302,10 @@
         <v>1558</v>
       </c>
       <c r="N963" t="n">
-        <v>711.33664971986</v>
+        <v>711.3366494881</v>
       </c>
       <c r="O963" t="n">
-        <v>1108262.500263542</v>
+        <v>1108262.49990246</v>
       </c>
       <c r="P963" t="n">
         <v>900</v>
@@ -42375,7 +42375,7 @@
         </is>
       </c>
       <c r="J965" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K965" t="n">
         <v>0</v>
@@ -42384,19 +42384,19 @@
         <v>0</v>
       </c>
       <c r="M965" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N965" t="n">
-        <v>2590.4171559633</v>
+        <v>2590.4171296296</v>
       </c>
       <c r="O965" t="n">
-        <v>217595.0411009172</v>
+        <v>215004.6217592568</v>
       </c>
       <c r="P965" t="n">
         <v>2800</v>
       </c>
       <c r="Q965" t="n">
-        <v>235200</v>
+        <v>232400</v>
       </c>
     </row>
     <row r="966">
@@ -42591,7 +42591,7 @@
         </is>
       </c>
       <c r="J970" t="n">
-        <v>1749</v>
+        <v>1319</v>
       </c>
       <c r="K970" t="n">
         <v>0</v>
@@ -42600,19 +42600,19 @@
         <v>0</v>
       </c>
       <c r="M970" t="n">
-        <v>1749</v>
+        <v>1319</v>
       </c>
       <c r="N970" t="n">
         <v>177.65</v>
       </c>
       <c r="O970" t="n">
-        <v>310709.85</v>
+        <v>234320.35</v>
       </c>
       <c r="P970" t="n">
         <v>300</v>
       </c>
       <c r="Q970" t="n">
-        <v>524700</v>
+        <v>395700</v>
       </c>
     </row>
     <row r="971">
@@ -42732,10 +42732,10 @@
         <v>30</v>
       </c>
       <c r="N973" t="n">
-        <v>4032.3968380463</v>
+        <v>4032.3968134715</v>
       </c>
       <c r="O973" t="n">
-        <v>120971.905141389</v>
+        <v>120971.904404145</v>
       </c>
       <c r="P973" t="n">
         <v>4200</v>
@@ -42854,28 +42854,28 @@
         </is>
       </c>
       <c r="J976" t="n">
-        <v>1454</v>
+        <v>1399</v>
       </c>
       <c r="K976" t="n">
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M976" t="n">
-        <v>1405</v>
+        <v>1399</v>
       </c>
       <c r="N976" t="n">
-        <v>517.28997081144</v>
+        <v>517.29010591089</v>
       </c>
       <c r="O976" t="n">
-        <v>726792.4089900731</v>
+        <v>723688.8581693352</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>1264500</v>
+        <v>1259100</v>
       </c>
     </row>
     <row r="977">
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="J980" t="n">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="K980" t="n">
         <v>0</v>
@@ -43048,19 +43048,19 @@
         <v>0</v>
       </c>
       <c r="M980" t="n">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="N980" t="n">
-        <v>3110.8413717354</v>
+        <v>3110.8411757364</v>
       </c>
       <c r="O980" t="n">
-        <v>4442281.478838151</v>
+        <v>4417394.469545688</v>
       </c>
       <c r="P980" t="n">
         <v>4500</v>
       </c>
       <c r="Q980" t="n">
-        <v>6426000</v>
+        <v>6390000</v>
       </c>
     </row>
     <row r="981">
@@ -43171,7 +43171,7 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>14242</v>
+        <v>14026</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
@@ -43180,19 +43180,19 @@
         <v>0</v>
       </c>
       <c r="M983" t="n">
-        <v>14242</v>
+        <v>14026</v>
       </c>
       <c r="N983" t="n">
-        <v>703.79516401441</v>
+        <v>703.79514130448</v>
       </c>
       <c r="O983" t="n">
-        <v>10023450.72589323</v>
+        <v>9871430.651936637</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
       </c>
       <c r="Q983" t="n">
-        <v>12817800</v>
+        <v>12623400</v>
       </c>
     </row>
     <row r="984">
@@ -43487,7 +43487,7 @@
         </is>
       </c>
       <c r="J990" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="K990" t="n">
         <v>0</v>
@@ -43496,19 +43496,19 @@
         <v>0</v>
       </c>
       <c r="M990" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N990" t="n">
         <v>1300</v>
       </c>
       <c r="O990" t="n">
-        <v>248300</v>
+        <v>245700</v>
       </c>
       <c r="P990" t="n">
         <v>2200</v>
       </c>
       <c r="Q990" t="n">
-        <v>420200</v>
+        <v>415800</v>
       </c>
     </row>
     <row r="991">
@@ -43713,10 +43713,10 @@
         <v>23</v>
       </c>
       <c r="N995" t="n">
-        <v>3629.7160714286</v>
+        <v>3629.716029724</v>
       </c>
       <c r="O995" t="n">
-        <v>83483.4696428578</v>
+        <v>83483.468683652</v>
       </c>
       <c r="P995" t="n">
         <v>4900</v>
@@ -43926,10 +43926,10 @@
         <v>81</v>
       </c>
       <c r="N1000" t="n">
-        <v>1595.5119633274</v>
+        <v>1595.5118087506</v>
       </c>
       <c r="O1000" t="n">
-        <v>129236.4690295194</v>
+        <v>129236.4565087986</v>
       </c>
       <c r="P1000" t="n">
         <v>2500</v>
@@ -43960,7 +43960,7 @@
         </is>
       </c>
       <c r="J1001" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K1001" t="n">
         <v>0</v>
@@ -43969,19 +43969,19 @@
         <v>0</v>
       </c>
       <c r="M1001" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="N1001" t="n">
         <v>1567.02</v>
       </c>
       <c r="O1001" t="n">
-        <v>670684.5599999999</v>
+        <v>665983.5</v>
       </c>
       <c r="P1001" t="n">
         <v>2900</v>
       </c>
       <c r="Q1001" t="n">
-        <v>1241200</v>
+        <v>1232500</v>
       </c>
     </row>
     <row r="1002">
@@ -44361,10 +44361,10 @@
         <v>18</v>
       </c>
       <c r="N1009" t="n">
-        <v>2110.6406122449</v>
+        <v>2098.4050733138</v>
       </c>
       <c r="O1009" t="n">
-        <v>37991.5310204082</v>
+        <v>37771.2913196484</v>
       </c>
       <c r="P1009" t="n">
         <v>9500</v>
@@ -44527,28 +44527,28 @@
         </is>
       </c>
       <c r="J1013" t="n">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="K1013" t="n">
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1013" t="n">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="N1013" t="n">
         <v>1669.6</v>
       </c>
       <c r="O1013" t="n">
-        <v>1676278.4</v>
+        <v>1667930.4</v>
       </c>
       <c r="P1013" t="n">
         <v>2900</v>
       </c>
       <c r="Q1013" t="n">
-        <v>2911600</v>
+        <v>2897100</v>
       </c>
     </row>
     <row r="1014">
@@ -44810,22 +44810,22 @@
         </is>
       </c>
       <c r="J1019" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="K1019" t="n">
         <v>0</v>
       </c>
       <c r="L1019" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1019" t="n">
         <v>679</v>
       </c>
       <c r="N1019" t="n">
-        <v>3063.621911315</v>
+        <v>3063.621930999</v>
       </c>
       <c r="O1019" t="n">
-        <v>2080199.277782885</v>
+        <v>2080199.291148321</v>
       </c>
       <c r="P1019" t="n">
         <v>3500</v>
@@ -44905,13 +44905,13 @@
         </is>
       </c>
       <c r="J1021" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K1021" t="n">
         <v>0</v>
       </c>
       <c r="L1021" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1021" t="n">
         <v>60</v>
@@ -46045,10 +46045,10 @@
         <v>1</v>
       </c>
       <c r="N1045" t="n">
-        <v>22042.26</v>
+        <v>33063.39</v>
       </c>
       <c r="O1045" t="n">
-        <v>22042.26</v>
+        <v>33063.39</v>
       </c>
       <c r="P1045" t="n">
         <v>56000</v>
@@ -47210,7 +47210,7 @@
         </is>
       </c>
       <c r="J1070" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1070" t="n">
         <v>0</v>
@@ -47219,19 +47219,19 @@
         <v>0</v>
       </c>
       <c r="M1070" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1070" t="n">
         <v>5216.9</v>
       </c>
       <c r="O1070" t="n">
-        <v>20867.6</v>
+        <v>15650.7</v>
       </c>
       <c r="P1070" t="n">
         <v>20500</v>
       </c>
       <c r="Q1070" t="n">
-        <v>82000</v>
+        <v>61500</v>
       </c>
     </row>
     <row r="1071">
@@ -47398,7 +47398,7 @@
         </is>
       </c>
       <c r="J1074" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1074" t="n">
         <v>0</v>
@@ -47407,19 +47407,19 @@
         <v>0</v>
       </c>
       <c r="M1074" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1074" t="n">
-        <v>7046.93982792</v>
+        <v>7046.939827883</v>
       </c>
       <c r="O1074" t="n">
-        <v>288924.53294472</v>
+        <v>281877.59311532</v>
       </c>
       <c r="P1074" t="n">
         <v>9900</v>
       </c>
       <c r="Q1074" t="n">
-        <v>405900</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="1075">
@@ -47690,10 +47690,10 @@
         <v>16</v>
       </c>
       <c r="N1080" t="n">
-        <v>665.32360534809</v>
+        <v>665.32360867559</v>
       </c>
       <c r="O1080" t="n">
-        <v>10645.17768556944</v>
+        <v>10645.17773880944</v>
       </c>
       <c r="P1080" t="n">
         <v>2900</v>
@@ -47964,7 +47964,7 @@
         </is>
       </c>
       <c r="J1086" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="K1086" t="n">
         <v>0</v>
@@ -47973,19 +47973,19 @@
         <v>0</v>
       </c>
       <c r="M1086" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="N1086" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1086" t="n">
-        <v>1292078.88</v>
+        <v>1255424.16</v>
       </c>
       <c r="P1086" t="n">
         <v>7900</v>
       </c>
       <c r="Q1086" t="n">
-        <v>2227800</v>
+        <v>2164600</v>
       </c>
     </row>
     <row r="1087">
@@ -48013,7 +48013,7 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
@@ -48022,19 +48022,19 @@
         <v>0</v>
       </c>
       <c r="M1087" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N1087" t="n">
         <v>3155</v>
       </c>
       <c r="O1087" t="n">
-        <v>1233605</v>
+        <v>1211520</v>
       </c>
       <c r="P1087" t="n">
         <v>5900</v>
       </c>
       <c r="Q1087" t="n">
-        <v>2306900</v>
+        <v>2265600</v>
       </c>
     </row>
     <row r="1088">
@@ -48062,7 +48062,7 @@
         </is>
       </c>
       <c r="J1088" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K1088" t="n">
         <v>0</v>
@@ -48071,19 +48071,19 @@
         <v>0</v>
       </c>
       <c r="M1088" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N1088" t="n">
-        <v>430.60997607656</v>
+        <v>430.6099760479</v>
       </c>
       <c r="O1088" t="n">
-        <v>39185.50782296696</v>
+        <v>38324.2878682631</v>
       </c>
       <c r="P1088" t="n">
         <v>2200</v>
       </c>
       <c r="Q1088" t="n">
-        <v>200200</v>
+        <v>195800</v>
       </c>
     </row>
     <row r="1089">
@@ -48111,7 +48111,7 @@
         </is>
       </c>
       <c r="J1089" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K1089" t="n">
         <v>0</v>
@@ -48120,19 +48120,19 @@
         <v>0</v>
       </c>
       <c r="M1089" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N1089" t="n">
-        <v>465.87095553453</v>
+        <v>465.87095916429</v>
       </c>
       <c r="O1089" t="n">
-        <v>76868.70766319745</v>
+        <v>75005.22442545069</v>
       </c>
       <c r="P1089" t="n">
         <v>2500</v>
       </c>
       <c r="Q1089" t="n">
-        <v>412500</v>
+        <v>402500</v>
       </c>
     </row>
     <row r="1090">
@@ -48172,10 +48172,10 @@
         <v>13</v>
       </c>
       <c r="N1090" t="n">
-        <v>315.02697707736</v>
+        <v>315.02699712644</v>
       </c>
       <c r="O1090" t="n">
-        <v>4095.35070200568</v>
+        <v>4095.35096264372</v>
       </c>
       <c r="P1090" t="n">
         <v>2200</v>
@@ -48242,7 +48242,7 @@
         </is>
       </c>
       <c r="J1092" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K1092" t="n">
         <v>0</v>
@@ -48251,19 +48251,19 @@
         <v>0</v>
       </c>
       <c r="M1092" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N1092" t="n">
         <v>2752.52</v>
       </c>
       <c r="O1092" t="n">
-        <v>189923.88</v>
+        <v>181666.32</v>
       </c>
       <c r="P1092" t="n">
         <v>4500</v>
       </c>
       <c r="Q1092" t="n">
-        <v>310500</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="1093">
@@ -48494,28 +48494,28 @@
         </is>
       </c>
       <c r="J1098" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1098" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N1098" t="n">
         <v>2459</v>
       </c>
       <c r="O1098" t="n">
-        <v>201638</v>
+        <v>189343</v>
       </c>
       <c r="P1098" t="n">
         <v>3900</v>
       </c>
       <c r="Q1098" t="n">
-        <v>319800</v>
+        <v>300300</v>
       </c>
     </row>
     <row r="1099">
@@ -48761,10 +48761,10 @@
         <v>260</v>
       </c>
       <c r="N1104" t="n">
-        <v>4282.1072260488</v>
+        <v>4282.1072225705</v>
       </c>
       <c r="O1104" t="n">
-        <v>1113347.878772688</v>
+        <v>1113347.87786833</v>
       </c>
       <c r="P1104" t="n">
         <v>5300</v>
@@ -49394,7 +49394,7 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
@@ -49403,19 +49403,19 @@
         <v>0</v>
       </c>
       <c r="M1119" t="n">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="N1119" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1119" t="n">
-        <v>1780150.41</v>
+        <v>1776620.7</v>
       </c>
       <c r="P1119" t="n">
         <v>1900</v>
       </c>
       <c r="Q1119" t="n">
-        <v>2874700</v>
+        <v>2869000</v>
       </c>
     </row>
     <row r="1120">
@@ -49482,28 +49482,28 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K1121" t="n">
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1121" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N1121" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1121" t="n">
-        <v>225914.9</v>
+        <v>216369.2</v>
       </c>
       <c r="P1121" t="n">
         <v>5100</v>
       </c>
       <c r="Q1121" t="n">
-        <v>362100</v>
+        <v>346800</v>
       </c>
     </row>
     <row r="1122">
@@ -49620,10 +49620,10 @@
         <v>1219</v>
       </c>
       <c r="N1124" t="n">
-        <v>1794.2879686376</v>
+        <v>1794.287968053</v>
       </c>
       <c r="O1124" t="n">
-        <v>2187237.033769235</v>
+        <v>2187237.033056607</v>
       </c>
       <c r="P1124" t="n">
         <v>1600</v>
@@ -49664,10 +49664,10 @@
         <v>100</v>
       </c>
       <c r="N1125" t="n">
-        <v>2181.4247785548</v>
+        <v>2181.4247724621</v>
       </c>
       <c r="O1125" t="n">
-        <v>218142.47785548</v>
+        <v>218142.47724621</v>
       </c>
       <c r="P1125" t="n">
         <v>2900</v>
@@ -49708,10 +49708,10 @@
         <v>30</v>
       </c>
       <c r="N1126" t="n">
-        <v>2077.2842857143</v>
+        <v>2077.2842168675</v>
       </c>
       <c r="O1126" t="n">
-        <v>62318.528571429</v>
+        <v>62318.526506025</v>
       </c>
       <c r="P1126" t="n">
         <v>2900</v>
@@ -50318,10 +50318,10 @@
         <v>55</v>
       </c>
       <c r="N1140" t="n">
-        <v>6035.665</v>
+        <v>6035.6650381679</v>
       </c>
       <c r="O1140" t="n">
-        <v>331961.575</v>
+        <v>331961.5770992345</v>
       </c>
       <c r="P1140" t="n">
         <v>8500</v>
@@ -51663,7 +51663,7 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -51672,19 +51672,19 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="N1170" t="n">
         <v>7480</v>
       </c>
       <c r="O1170" t="n">
-        <v>650760</v>
+        <v>568480</v>
       </c>
       <c r="P1170" t="n">
         <v>9500</v>
       </c>
       <c r="Q1170" t="n">
-        <v>826500</v>
+        <v>722000</v>
       </c>
     </row>
     <row r="1171">
@@ -51709,7 +51709,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -51718,19 +51718,19 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="N1171" t="n">
         <v>6336</v>
       </c>
       <c r="O1171" t="n">
-        <v>253440</v>
+        <v>152064</v>
       </c>
       <c r="P1171" t="n">
         <v>7500</v>
       </c>
       <c r="Q1171" t="n">
-        <v>300000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="1172">
@@ -51767,10 +51767,10 @@
         <v>43</v>
       </c>
       <c r="N1172" t="n">
-        <v>5301.8181818182</v>
+        <v>5280</v>
       </c>
       <c r="O1172" t="n">
-        <v>227978.1818181826</v>
+        <v>227040</v>
       </c>
       <c r="P1172" t="n">
         <v>6900</v>
@@ -51801,28 +51801,28 @@
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N1173" t="n">
         <v>1584</v>
       </c>
       <c r="O1173" t="n">
-        <v>38016</v>
+        <v>30096</v>
       </c>
       <c r="P1173" t="n">
         <v>2000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>48000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="1174">
@@ -51847,7 +51847,7 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
@@ -51856,19 +51856,19 @@
         <v>0</v>
       </c>
       <c r="M1174" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N1174" t="n">
         <v>3872</v>
       </c>
       <c r="O1174" t="n">
-        <v>495616</v>
+        <v>480128</v>
       </c>
       <c r="P1174" t="n">
         <v>4900</v>
       </c>
       <c r="Q1174" t="n">
-        <v>627200</v>
+        <v>607600</v>
       </c>
     </row>
     <row r="1175">
@@ -51893,7 +51893,7 @@
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K1175" t="n">
         <v>0</v>
@@ -51902,19 +51902,19 @@
         <v>0</v>
       </c>
       <c r="M1175" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N1175" t="n">
         <v>6160</v>
       </c>
       <c r="O1175" t="n">
-        <v>295680</v>
+        <v>271040</v>
       </c>
       <c r="P1175" t="n">
         <v>7900</v>
       </c>
       <c r="Q1175" t="n">
-        <v>379200</v>
+        <v>347600</v>
       </c>
     </row>
     <row r="1176">
@@ -51939,7 +51939,7 @@
         </is>
       </c>
       <c r="J1176" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K1176" t="n">
         <v>0</v>
@@ -51948,19 +51948,19 @@
         <v>0</v>
       </c>
       <c r="M1176" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N1176" t="n">
         <v>4400</v>
       </c>
       <c r="O1176" t="n">
-        <v>563200</v>
+        <v>550000</v>
       </c>
       <c r="P1176" t="n">
         <v>5900</v>
       </c>
       <c r="Q1176" t="n">
-        <v>755200</v>
+        <v>737500</v>
       </c>
     </row>
     <row r="1177">
@@ -51985,28 +51985,28 @@
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M1177" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="N1177" t="n">
         <v>3520</v>
       </c>
       <c r="O1177" t="n">
-        <v>468160</v>
+        <v>390720</v>
       </c>
       <c r="P1177" t="n">
         <v>4500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>598500</v>
+        <v>499500</v>
       </c>
     </row>
     <row r="1178">
@@ -52077,7 +52077,7 @@
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
@@ -52086,19 +52086,19 @@
         <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="N1179" t="n">
         <v>9240</v>
       </c>
       <c r="O1179" t="n">
-        <v>803880</v>
+        <v>545160</v>
       </c>
       <c r="P1179" t="n">
         <v>11500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>1000500</v>
+        <v>678500</v>
       </c>
     </row>
     <row r="1180">
@@ -52169,28 +52169,28 @@
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1181" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N1181" t="n">
         <v>4576</v>
       </c>
       <c r="O1181" t="n">
-        <v>814528</v>
+        <v>800800</v>
       </c>
       <c r="P1181" t="n">
         <v>5900</v>
       </c>
       <c r="Q1181" t="n">
-        <v>1050200</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="1182">
@@ -53561,10 +53561,10 @@
         <v>29</v>
       </c>
       <c r="N1211" t="n">
-        <v>227.41601620029</v>
+        <v>227.41613363363</v>
       </c>
       <c r="O1211" t="n">
-        <v>6595.06446980841</v>
+        <v>6595.06787537527</v>
       </c>
       <c r="P1211" t="n">
         <v>1200</v>
@@ -53838,13 +53838,13 @@
         </is>
       </c>
       <c r="J1217" t="n">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="K1217" t="n">
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M1217" t="n">
         <v>321</v>
@@ -53884,28 +53884,28 @@
         </is>
       </c>
       <c r="J1218" t="n">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="K1218" t="n">
         <v>0</v>
       </c>
       <c r="L1218" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1218" t="n">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="N1218" t="n">
-        <v>4687.9742758621</v>
+        <v>4687.9743167972</v>
       </c>
       <c r="O1218" t="n">
-        <v>2695585.208620708</v>
+        <v>2644017.514673621</v>
       </c>
       <c r="P1218" t="n">
         <v>5900</v>
       </c>
       <c r="Q1218" t="n">
-        <v>3392500</v>
+        <v>3327600</v>
       </c>
     </row>
     <row r="1219">
@@ -53930,13 +53930,13 @@
         </is>
       </c>
       <c r="J1219" t="n">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K1219" t="n">
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1219" t="n">
         <v>644</v>
@@ -61570,7 +61570,7 @@
         </is>
       </c>
       <c r="J1404" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K1404" t="n">
         <v>0</v>
@@ -61579,19 +61579,19 @@
         <v>0</v>
       </c>
       <c r="M1404" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="N1404" t="n">
         <v>4550</v>
       </c>
       <c r="O1404" t="n">
-        <v>518700</v>
+        <v>468650</v>
       </c>
       <c r="P1404" t="n">
         <v>5500</v>
       </c>
       <c r="Q1404" t="n">
-        <v>627000</v>
+        <v>566500</v>
       </c>
     </row>
     <row r="1405">
@@ -61945,10 +61945,10 @@
         <v>26</v>
       </c>
       <c r="N1412" t="n">
-        <v>2403.9772058824</v>
+        <v>2403.9771641791</v>
       </c>
       <c r="O1412" t="n">
-        <v>62503.40735294241</v>
+        <v>62503.4062686566</v>
       </c>
       <c r="P1412" t="n">
         <v>3000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -28395,10 +28395,10 @@
         <v>2</v>
       </c>
       <c r="N656" t="n">
-        <v>1484.6610909091</v>
+        <v>1466.8807272727</v>
       </c>
       <c r="O656" t="n">
-        <v>2969.3221818182</v>
+        <v>2933.7614545454</v>
       </c>
       <c r="P656" t="n">
         <v>3400</v>
@@ -36237,10 +36237,10 @@
         <v>15</v>
       </c>
       <c r="N831" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O831" t="n">
-        <v>74352.27978369451</v>
+        <v>73617.33169717201</v>
       </c>
       <c r="P831" t="n">
         <v>8200</v>
@@ -44963,10 +44963,10 @@
         <v>2</v>
       </c>
       <c r="N1022" t="n">
-        <v>883.11127118644</v>
+        <v>875.69016949153</v>
       </c>
       <c r="O1022" t="n">
-        <v>1766.22254237288</v>
+        <v>1751.38033898306</v>
       </c>
       <c r="P1022" t="n">
         <v>4500</v>
@@ -46045,10 +46045,10 @@
         <v>1</v>
       </c>
       <c r="N1045" t="n">
-        <v>33063.39</v>
+        <v>22042.26</v>
       </c>
       <c r="O1045" t="n">
-        <v>33063.39</v>
+        <v>22042.26</v>
       </c>
       <c r="P1045" t="n">
         <v>56000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -645,10 +645,10 @@
         <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>96741.407702703</v>
+        <v>96741.42375</v>
       </c>
       <c r="O6" t="n">
-        <v>1451121.115540545</v>
+        <v>1451121.35625</v>
       </c>
       <c r="P6" t="n">
         <v>188900</v>
@@ -1030,22 +1030,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3076124567</v>
+        <v>1811.3076256499</v>
       </c>
       <c r="O15" t="n">
-        <v>79697.53494809481</v>
+        <v>76074.92027729581</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
       </c>
       <c r="Q15" t="n">
-        <v>114400</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="16">
@@ -3192,10 +3192,10 @@
         <v>290</v>
       </c>
       <c r="N68" t="n">
-        <v>2474.7041355932</v>
+        <v>2474.7040753425</v>
       </c>
       <c r="O68" t="n">
-        <v>717664.1993220281</v>
+        <v>717664.181849325</v>
       </c>
       <c r="P68" t="n">
         <v>4500</v>
@@ -5036,22 +5036,22 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>16486.40875</v>
+        <v>16486.408661417</v>
       </c>
       <c r="O111" t="n">
-        <v>16486.40875</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
         <v>30500</v>
       </c>
       <c r="Q111" t="n">
-        <v>30500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5075,22 +5075,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M112" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N112" t="n">
         <v>36762.36</v>
       </c>
       <c r="O112" t="n">
-        <v>3124800.6</v>
+        <v>2683652.28</v>
       </c>
       <c r="P112" t="n">
         <v>57100</v>
       </c>
       <c r="Q112" t="n">
-        <v>4853500</v>
+        <v>4168300</v>
       </c>
     </row>
     <row r="113">
@@ -9740,22 +9740,22 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M222" t="n">
-        <v>9236</v>
+        <v>9229</v>
       </c>
       <c r="N222" t="n">
         <v>1726.32</v>
       </c>
       <c r="O222" t="n">
-        <v>15944291.52</v>
+        <v>15932207.28</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
       </c>
       <c r="Q222" t="n">
-        <v>13854000</v>
+        <v>13843500</v>
       </c>
     </row>
     <row r="223">
@@ -10291,22 +10291,22 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M235" t="n">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="N235" t="n">
-        <v>1098.0599864057</v>
+        <v>1098.0603685231</v>
       </c>
       <c r="O235" t="n">
-        <v>1140884.325875522</v>
+        <v>1123315.756999131</v>
       </c>
       <c r="P235" t="n">
         <v>1500</v>
       </c>
       <c r="Q235" t="n">
-        <v>1558500</v>
+        <v>1534500</v>
       </c>
     </row>
     <row r="236">
@@ -12085,10 +12085,10 @@
         <v>909</v>
       </c>
       <c r="N277" t="n">
-        <v>2582.2556363636</v>
+        <v>2582.2556074972</v>
       </c>
       <c r="O277" t="n">
-        <v>2347270.373454513</v>
+        <v>2347270.347214955</v>
       </c>
       <c r="P277" t="n">
         <v>4500</v>
@@ -12131,10 +12131,10 @@
         <v>1395</v>
       </c>
       <c r="N278" t="n">
-        <v>5216.8960979122</v>
+        <v>5216.8960939752</v>
       </c>
       <c r="O278" t="n">
-        <v>7277570.056587519</v>
+        <v>7277570.051095404</v>
       </c>
       <c r="P278" t="n">
         <v>8500</v>
@@ -13884,22 +13884,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N318" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O318" t="n">
-        <v>1560206.685608574</v>
+        <v>1555315.755569153</v>
       </c>
       <c r="P318" t="n">
         <v>8200</v>
       </c>
       <c r="Q318" t="n">
-        <v>2615800</v>
+        <v>2607600</v>
       </c>
     </row>
     <row r="319">
@@ -13936,10 +13936,10 @@
         <v>21</v>
       </c>
       <c r="N319" t="n">
-        <v>4967.8308421053</v>
+        <v>4967.846</v>
       </c>
       <c r="O319" t="n">
-        <v>104324.4476842113</v>
+        <v>104324.766</v>
       </c>
       <c r="P319" t="n">
         <v>7500</v>
@@ -14470,22 +14470,22 @@
         <v>0</v>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M331" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N331" t="n">
         <v>8662</v>
       </c>
       <c r="O331" t="n">
-        <v>225212</v>
+        <v>216550</v>
       </c>
       <c r="P331" t="n">
         <v>14200</v>
       </c>
       <c r="Q331" t="n">
-        <v>369200</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="332">
@@ -14689,10 +14689,10 @@
         <v>362</v>
       </c>
       <c r="N336" t="n">
-        <v>3594.2539736347</v>
+        <v>3594.2539698492</v>
       </c>
       <c r="O336" t="n">
-        <v>1301119.938455761</v>
+        <v>1301119.93708541</v>
       </c>
       <c r="P336" t="n">
         <v>6500</v>
@@ -14861,10 +14861,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>3240.8500374532</v>
+        <v>3240.850037594</v>
       </c>
       <c r="O340" t="n">
-        <v>3240.8500374532</v>
+        <v>3240.850037594</v>
       </c>
       <c r="P340" t="n">
         <v>5200</v>
@@ -15043,10 +15043,10 @@
         <v>394</v>
       </c>
       <c r="N344" t="n">
-        <v>616.01871898278</v>
+        <v>616.01871837471</v>
       </c>
       <c r="O344" t="n">
-        <v>242711.3752792153</v>
+        <v>242711.3750396357</v>
       </c>
       <c r="P344" t="n">
         <v>800</v>
@@ -15941,22 +15941,22 @@
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N365" t="n">
-        <v>3041.6600134228</v>
+        <v>3041.660013459</v>
       </c>
       <c r="O365" t="n">
-        <v>328499.2814496624</v>
+        <v>325457.621440113</v>
       </c>
       <c r="P365" t="n">
         <v>5500</v>
       </c>
       <c r="Q365" t="n">
-        <v>594000</v>
+        <v>588500</v>
       </c>
     </row>
     <row r="366">
@@ -15982,22 +15982,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N366" t="n">
         <v>3981.47</v>
       </c>
       <c r="O366" t="n">
-        <v>537498.45</v>
+        <v>533516.98</v>
       </c>
       <c r="P366" t="n">
         <v>7000</v>
       </c>
       <c r="Q366" t="n">
-        <v>945000</v>
+        <v>938000</v>
       </c>
     </row>
     <row r="367">
@@ -16034,10 +16034,10 @@
         <v>8125</v>
       </c>
       <c r="N367" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O367" t="n">
-        <v>35524212.67485025</v>
+        <v>35524212.67760219</v>
       </c>
       <c r="P367" t="n">
         <v>7500</v>
@@ -16206,10 +16206,10 @@
         <v>399</v>
       </c>
       <c r="N371" t="n">
-        <v>1592.5665147453</v>
+        <v>1592.566460177</v>
       </c>
       <c r="O371" t="n">
-        <v>635434.0393833747</v>
+        <v>635434.017610623</v>
       </c>
       <c r="P371" t="n">
         <v>3900</v>
@@ -17148,22 +17148,22 @@
         <v>0</v>
       </c>
       <c r="L393" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M393" t="n">
-        <v>2408</v>
+        <v>2390</v>
       </c>
       <c r="N393" t="n">
         <v>1387.55</v>
       </c>
       <c r="O393" t="n">
-        <v>3341220.4</v>
+        <v>3316244.5</v>
       </c>
       <c r="P393" t="n">
         <v>2300</v>
       </c>
       <c r="Q393" t="n">
-        <v>5538400</v>
+        <v>5497000</v>
       </c>
     </row>
     <row r="394">
@@ -17373,22 +17373,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M398" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="N398" t="n">
         <v>16897</v>
       </c>
       <c r="O398" t="n">
-        <v>1301069</v>
+        <v>895541</v>
       </c>
       <c r="P398" t="n">
         <v>27900</v>
       </c>
       <c r="Q398" t="n">
-        <v>2148300</v>
+        <v>1478700</v>
       </c>
     </row>
     <row r="399">
@@ -18518,22 +18518,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M424" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="N424" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O424" t="n">
-        <v>572454.230604516</v>
+        <v>561037.7697903319</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>877500</v>
+        <v>860000</v>
       </c>
     </row>
     <row r="425">
@@ -18616,10 +18616,10 @@
         <v>4</v>
       </c>
       <c r="N426" t="n">
-        <v>1690.5964846154</v>
+        <v>1690.5964302236</v>
       </c>
       <c r="O426" t="n">
-        <v>6762.3859384616</v>
+        <v>6762.3857208944</v>
       </c>
       <c r="P426" t="n">
         <v>2900</v>
@@ -18656,22 +18656,22 @@
         <v>0</v>
       </c>
       <c r="L427" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M427" t="n">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="N427" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O427" t="n">
-        <v>785948.2518355688</v>
+        <v>779747.4772575939</v>
       </c>
       <c r="P427" t="n">
         <v>2500</v>
       </c>
       <c r="Q427" t="n">
-        <v>1267500</v>
+        <v>1257500</v>
       </c>
     </row>
     <row r="428">
@@ -18748,22 +18748,22 @@
         <v>0</v>
       </c>
       <c r="L429" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M429" t="n">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="N429" t="n">
-        <v>2403.5124244849</v>
+        <v>2403.5125045299</v>
       </c>
       <c r="O429" t="n">
-        <v>1795423.78109022</v>
+        <v>1773792.228343066</v>
       </c>
       <c r="P429" t="n">
         <v>3500</v>
       </c>
       <c r="Q429" t="n">
-        <v>2614500</v>
+        <v>2583000</v>
       </c>
     </row>
     <row r="430">
@@ -18844,10 +18844,10 @@
         <v>186</v>
       </c>
       <c r="N431" t="n">
-        <v>2521.5190322581</v>
+        <v>2521.5166341463</v>
       </c>
       <c r="O431" t="n">
-        <v>469002.5400000066</v>
+        <v>469002.0939512118</v>
       </c>
       <c r="P431" t="n">
         <v>3900</v>
@@ -23379,10 +23379,10 @@
         <v>211</v>
       </c>
       <c r="N537" t="n">
-        <v>2029.8738739669</v>
+        <v>2029.8739473684</v>
       </c>
       <c r="O537" t="n">
-        <v>428303.3874070159</v>
+        <v>428303.4028947324</v>
       </c>
       <c r="P537" t="n">
         <v>3600</v>
@@ -25556,22 +25556,22 @@
         <v>0</v>
       </c>
       <c r="L589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M589" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N589" t="n">
-        <v>4285.1956570156</v>
+        <v>4285.195701459</v>
       </c>
       <c r="O589" t="n">
-        <v>917031.8706013383</v>
+        <v>912746.6844107669</v>
       </c>
       <c r="P589" t="n">
         <v>6900</v>
       </c>
       <c r="Q589" t="n">
-        <v>1476600</v>
+        <v>1469700</v>
       </c>
     </row>
     <row r="590">
@@ -28865,22 +28865,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M667" t="n">
-        <v>276</v>
+        <v>226</v>
       </c>
       <c r="N667" t="n">
-        <v>1561.0010652921</v>
+        <v>1561.0013915094</v>
       </c>
       <c r="O667" t="n">
-        <v>430836.2940206196</v>
+        <v>352786.3144811244</v>
       </c>
       <c r="P667" t="n">
         <v>2900</v>
       </c>
       <c r="Q667" t="n">
-        <v>800400</v>
+        <v>655400</v>
       </c>
     </row>
     <row r="668">
@@ -31119,10 +31119,10 @@
         <v>5</v>
       </c>
       <c r="N720" t="n">
-        <v>3113.8900276243</v>
+        <v>3113.8900280899</v>
       </c>
       <c r="O720" t="n">
-        <v>15569.4501381215</v>
+        <v>15569.4501404495</v>
       </c>
       <c r="P720" t="n">
         <v>5000</v>
@@ -31806,22 +31806,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M735" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N735" t="n">
-        <v>1664.3547889182</v>
+        <v>1664.3547486772</v>
       </c>
       <c r="O735" t="n">
-        <v>43273.2245118732</v>
+        <v>39944.5139682528</v>
       </c>
       <c r="P735" t="n">
         <v>2900</v>
       </c>
       <c r="Q735" t="n">
-        <v>75400</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="736">
@@ -34940,22 +34940,22 @@
         <v>0</v>
       </c>
       <c r="L803" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M803" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N803" t="n">
         <v>3424</v>
       </c>
       <c r="O803" t="n">
-        <v>54784</v>
+        <v>51360</v>
       </c>
       <c r="P803" t="n">
         <v>5900</v>
       </c>
       <c r="Q803" t="n">
-        <v>94400</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="804">
@@ -35268,10 +35268,10 @@
         <v>123</v>
       </c>
       <c r="N810" t="n">
-        <v>2252.2972418478</v>
+        <v>2252.2973618785</v>
       </c>
       <c r="O810" t="n">
-        <v>277032.5607472794</v>
+        <v>277032.5755110555</v>
       </c>
       <c r="P810" t="n">
         <v>3900</v>
@@ -35501,10 +35501,10 @@
         <v>450</v>
       </c>
       <c r="N815" t="n">
-        <v>2328.1187082951</v>
+        <v>2328.1186987357</v>
       </c>
       <c r="O815" t="n">
-        <v>1047653.418732795</v>
+        <v>1047653.414431065</v>
       </c>
       <c r="P815" t="n">
         <v>4500</v>
@@ -36237,10 +36237,10 @@
         <v>15</v>
       </c>
       <c r="N831" t="n">
-        <v>4907.8221131448</v>
+        <v>4907.8221561969</v>
       </c>
       <c r="O831" t="n">
-        <v>73617.33169717201</v>
+        <v>73617.33234295351</v>
       </c>
       <c r="P831" t="n">
         <v>8200</v>
@@ -37514,22 +37514,22 @@
         <v>0</v>
       </c>
       <c r="L859" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M859" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N859" t="n">
         <v>5682</v>
       </c>
       <c r="O859" t="n">
-        <v>380694</v>
+        <v>375012</v>
       </c>
       <c r="P859" t="n">
         <v>9900</v>
       </c>
       <c r="Q859" t="n">
-        <v>663300</v>
+        <v>653400</v>
       </c>
     </row>
     <row r="860">
@@ -37560,22 +37560,22 @@
         <v>0</v>
       </c>
       <c r="L860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M860" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N860" t="n">
         <v>16086</v>
       </c>
       <c r="O860" t="n">
-        <v>257376</v>
+        <v>241290</v>
       </c>
       <c r="P860" t="n">
         <v>25900</v>
       </c>
       <c r="Q860" t="n">
-        <v>414400</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="861">
@@ -37652,22 +37652,22 @@
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M862" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N862" t="n">
         <v>23439</v>
       </c>
       <c r="O862" t="n">
-        <v>585975</v>
+        <v>562536</v>
       </c>
       <c r="P862" t="n">
         <v>37900</v>
       </c>
       <c r="Q862" t="n">
-        <v>947500</v>
+        <v>909600</v>
       </c>
     </row>
     <row r="863">
@@ -38294,22 +38294,22 @@
         <v>0</v>
       </c>
       <c r="L876" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M876" t="n">
-        <v>273</v>
+        <v>183</v>
       </c>
       <c r="N876" t="n">
         <v>10755</v>
       </c>
       <c r="O876" t="n">
-        <v>2936115</v>
+        <v>1968165</v>
       </c>
       <c r="P876" t="n">
         <v>17900</v>
       </c>
       <c r="Q876" t="n">
-        <v>4886700</v>
+        <v>3275700</v>
       </c>
     </row>
     <row r="877">
@@ -39543,10 +39543,10 @@
         <v>295</v>
       </c>
       <c r="N903" t="n">
-        <v>2458.5130528766</v>
+        <v>2458.5130063609</v>
       </c>
       <c r="O903" t="n">
-        <v>725261.350598597</v>
+        <v>725261.3368764655</v>
       </c>
       <c r="P903" t="n">
         <v>3500</v>
@@ -39635,10 +39635,10 @@
         <v>109</v>
       </c>
       <c r="N905" t="n">
-        <v>1771.0904111406</v>
+        <v>1771.0903664224</v>
       </c>
       <c r="O905" t="n">
-        <v>193048.8548143254</v>
+        <v>193048.8499400416</v>
       </c>
       <c r="P905" t="n">
         <v>2500</v>
@@ -39727,10 +39727,10 @@
         <v>309</v>
       </c>
       <c r="N907" t="n">
-        <v>1803.0156556557</v>
+        <v>1803.0157013118</v>
       </c>
       <c r="O907" t="n">
-        <v>557131.8375976112</v>
+        <v>557131.8517053463</v>
       </c>
       <c r="P907" t="n">
         <v>2500</v>
@@ -39865,10 +39865,10 @@
         <v>287</v>
       </c>
       <c r="N910" t="n">
-        <v>2056.0829556314</v>
+        <v>2056.0829120879</v>
       </c>
       <c r="O910" t="n">
-        <v>590095.8082662119</v>
+        <v>590095.7957692272</v>
       </c>
       <c r="P910" t="n">
         <v>2900</v>
@@ -40184,22 +40184,22 @@
         <v>0</v>
       </c>
       <c r="L917" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M917" t="n">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="N917" t="n">
-        <v>1592.279767184</v>
+        <v>1592.2798435754</v>
       </c>
       <c r="O917" t="n">
-        <v>656019.264079808</v>
+        <v>644873.336648037</v>
       </c>
       <c r="P917" t="n">
         <v>2500</v>
       </c>
       <c r="Q917" t="n">
-        <v>1030000</v>
+        <v>1012500</v>
       </c>
     </row>
     <row r="918">
@@ -40321,10 +40321,10 @@
         <v>202</v>
       </c>
       <c r="N920" t="n">
-        <v>2311.9177393617</v>
+        <v>2311.9170054945</v>
       </c>
       <c r="O920" t="n">
-        <v>467007.3833510634</v>
+        <v>467007.2351098889</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
@@ -40367,10 +40367,10 @@
         <v>142</v>
       </c>
       <c r="N921" t="n">
-        <v>1906.1819786096</v>
+        <v>1906.1816666667</v>
       </c>
       <c r="O921" t="n">
-        <v>270677.8409625632</v>
+        <v>270677.7966666714</v>
       </c>
       <c r="P921" t="n">
         <v>2900</v>
@@ -42597,22 +42597,22 @@
         <v>0</v>
       </c>
       <c r="L970" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M970" t="n">
-        <v>1319</v>
+        <v>1309</v>
       </c>
       <c r="N970" t="n">
         <v>177.65</v>
       </c>
       <c r="O970" t="n">
-        <v>234320.35</v>
+        <v>232543.85</v>
       </c>
       <c r="P970" t="n">
         <v>300</v>
       </c>
       <c r="Q970" t="n">
-        <v>395700</v>
+        <v>392700</v>
       </c>
     </row>
     <row r="971">
@@ -42860,22 +42860,22 @@
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M976" t="n">
-        <v>1399</v>
+        <v>1374</v>
       </c>
       <c r="N976" t="n">
-        <v>517.29010591089</v>
+        <v>517.2904197169401</v>
       </c>
       <c r="O976" t="n">
-        <v>723688.8581693352</v>
+        <v>710757.0366910757</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>1259100</v>
+        <v>1236600</v>
       </c>
     </row>
     <row r="977">
@@ -43002,10 +43002,10 @@
         <v>1</v>
       </c>
       <c r="N979" t="n">
-        <v>3259.1342692308</v>
+        <v>3259.1343023256</v>
       </c>
       <c r="O979" t="n">
-        <v>3259.1342692308</v>
+        <v>3259.1343023256</v>
       </c>
       <c r="P979" t="n">
         <v>3600</v>
@@ -43051,10 +43051,10 @@
         <v>1420</v>
       </c>
       <c r="N980" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O980" t="n">
-        <v>4417394.469545688</v>
+        <v>4417393.72388253</v>
       </c>
       <c r="P980" t="n">
         <v>4500</v>
@@ -43177,22 +43177,22 @@
         <v>0</v>
       </c>
       <c r="L983" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M983" t="n">
-        <v>14026</v>
+        <v>13928</v>
       </c>
       <c r="N983" t="n">
-        <v>703.79514130448</v>
+        <v>703.79512253205</v>
       </c>
       <c r="O983" t="n">
-        <v>9871430.651936637</v>
+        <v>9802458.466626393</v>
       </c>
       <c r="P983" t="n">
         <v>900</v>
       </c>
       <c r="Q983" t="n">
-        <v>12623400</v>
+        <v>12535200</v>
       </c>
     </row>
     <row r="984">
@@ -43622,22 +43622,22 @@
         <v>0</v>
       </c>
       <c r="L993" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M993" t="n">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="N993" t="n">
         <v>2525.02</v>
       </c>
       <c r="O993" t="n">
-        <v>1237259.8</v>
+        <v>1222109.68</v>
       </c>
       <c r="P993" t="n">
         <v>3000</v>
       </c>
       <c r="Q993" t="n">
-        <v>1470000</v>
+        <v>1452000</v>
       </c>
     </row>
     <row r="994">
@@ -47970,22 +47970,22 @@
         <v>0</v>
       </c>
       <c r="L1086" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1086" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N1086" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1086" t="n">
-        <v>1255424.16</v>
+        <v>1246260.48</v>
       </c>
       <c r="P1086" t="n">
         <v>7900</v>
       </c>
       <c r="Q1086" t="n">
-        <v>2164600</v>
+        <v>2148800</v>
       </c>
     </row>
     <row r="1087">
@@ -48019,22 +48019,22 @@
         <v>0</v>
       </c>
       <c r="L1087" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1087" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N1087" t="n">
         <v>3155</v>
       </c>
       <c r="O1087" t="n">
-        <v>1211520</v>
+        <v>1208365</v>
       </c>
       <c r="P1087" t="n">
         <v>5900</v>
       </c>
       <c r="Q1087" t="n">
-        <v>2265600</v>
+        <v>2259700</v>
       </c>
     </row>
     <row r="1088">
@@ -48500,22 +48500,22 @@
         <v>0</v>
       </c>
       <c r="L1098" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1098" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N1098" t="n">
         <v>2459</v>
       </c>
       <c r="O1098" t="n">
-        <v>189343</v>
+        <v>177048</v>
       </c>
       <c r="P1098" t="n">
         <v>3900</v>
       </c>
       <c r="Q1098" t="n">
-        <v>300300</v>
+        <v>280800</v>
       </c>
     </row>
     <row r="1099">
@@ -49535,10 +49535,10 @@
         <v>125</v>
       </c>
       <c r="N1122" t="n">
-        <v>1213.6821359223</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O1122" t="n">
-        <v>151710.2669902875</v>
+        <v>151710.267509725</v>
       </c>
       <c r="P1122" t="n">
         <v>1500</v>
@@ -51669,22 +51669,22 @@
         <v>0</v>
       </c>
       <c r="L1170" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M1170" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="N1170" t="n">
         <v>7480</v>
       </c>
       <c r="O1170" t="n">
-        <v>568480</v>
+        <v>254320</v>
       </c>
       <c r="P1170" t="n">
         <v>9500</v>
       </c>
       <c r="Q1170" t="n">
-        <v>722000</v>
+        <v>323000</v>
       </c>
     </row>
     <row r="1171">
@@ -51715,22 +51715,22 @@
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M1171" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N1171" t="n">
         <v>6336</v>
       </c>
       <c r="O1171" t="n">
-        <v>152064</v>
+        <v>6336</v>
       </c>
       <c r="P1171" t="n">
         <v>7500</v>
       </c>
       <c r="Q1171" t="n">
-        <v>180000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="1172">
@@ -51761,22 +51761,22 @@
         <v>0</v>
       </c>
       <c r="L1172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1172" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1172" t="n">
         <v>5280</v>
       </c>
       <c r="O1172" t="n">
-        <v>227040</v>
+        <v>216480</v>
       </c>
       <c r="P1172" t="n">
         <v>6900</v>
       </c>
       <c r="Q1172" t="n">
-        <v>296700</v>
+        <v>282900</v>
       </c>
     </row>
     <row r="1173">
@@ -51807,22 +51807,22 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1173" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N1173" t="n">
         <v>1584</v>
       </c>
       <c r="O1173" t="n">
-        <v>30096</v>
+        <v>20592</v>
       </c>
       <c r="P1173" t="n">
         <v>2000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>38000</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="1174">
@@ -51945,22 +51945,22 @@
         <v>0</v>
       </c>
       <c r="L1176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1176" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N1176" t="n">
         <v>4400</v>
       </c>
       <c r="O1176" t="n">
-        <v>550000</v>
+        <v>536800</v>
       </c>
       <c r="P1176" t="n">
         <v>5900</v>
       </c>
       <c r="Q1176" t="n">
-        <v>737500</v>
+        <v>719800</v>
       </c>
     </row>
     <row r="1177">
@@ -51991,22 +51991,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1177" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N1177" t="n">
         <v>3520</v>
       </c>
       <c r="O1177" t="n">
-        <v>390720</v>
+        <v>376640</v>
       </c>
       <c r="P1177" t="n">
         <v>4500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>499500</v>
+        <v>481500</v>
       </c>
     </row>
     <row r="1178">
@@ -52083,22 +52083,22 @@
         <v>0</v>
       </c>
       <c r="L1179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1179" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N1179" t="n">
         <v>9240</v>
       </c>
       <c r="O1179" t="n">
-        <v>545160</v>
+        <v>535920</v>
       </c>
       <c r="P1179" t="n">
         <v>11500</v>
       </c>
       <c r="Q1179" t="n">
-        <v>678500</v>
+        <v>667000</v>
       </c>
     </row>
     <row r="1180">
@@ -52175,22 +52175,22 @@
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1181" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N1181" t="n">
         <v>4576</v>
       </c>
       <c r="O1181" t="n">
-        <v>800800</v>
+        <v>787072</v>
       </c>
       <c r="P1181" t="n">
         <v>5900</v>
       </c>
       <c r="Q1181" t="n">
-        <v>1032500</v>
+        <v>1014800</v>
       </c>
     </row>
     <row r="1182">
@@ -52221,22 +52221,22 @@
         <v>0</v>
       </c>
       <c r="L1182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1182" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N1182" t="n">
         <v>5280</v>
       </c>
       <c r="O1182" t="n">
-        <v>327360</v>
+        <v>316800</v>
       </c>
       <c r="P1182" t="n">
         <v>6900</v>
       </c>
       <c r="Q1182" t="n">
-        <v>427800</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="1183">
@@ -61576,22 +61576,22 @@
         <v>0</v>
       </c>
       <c r="L1404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1404" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N1404" t="n">
         <v>4550</v>
       </c>
       <c r="O1404" t="n">
-        <v>468650</v>
+        <v>459550</v>
       </c>
       <c r="P1404" t="n">
         <v>5500</v>
       </c>
       <c r="Q1404" t="n">
-        <v>566500</v>
+        <v>555500</v>
       </c>
     </row>
     <row r="1405">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -989,22 +989,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N14" t="n">
-        <v>14490.384964539</v>
+        <v>14490.384928571</v>
       </c>
       <c r="O14" t="n">
-        <v>1492509.651347517</v>
+        <v>1478019.262714242</v>
       </c>
       <c r="P14" t="n">
         <v>23600</v>
       </c>
       <c r="Q14" t="n">
-        <v>2430800</v>
+        <v>2407200</v>
       </c>
     </row>
     <row r="15">
@@ -5075,22 +5075,22 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O112" t="n">
-        <v>188543.59043478</v>
+        <v>172831.624366808</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
       </c>
       <c r="Q112" t="n">
-        <v>342000</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="113">
@@ -6956,22 +6956,22 @@
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N157" t="n">
         <v>20961.76</v>
       </c>
       <c r="O157" t="n">
-        <v>1257705.6</v>
+        <v>1236743.84</v>
       </c>
       <c r="P157" t="n">
         <v>38300</v>
       </c>
       <c r="Q157" t="n">
-        <v>2298000</v>
+        <v>2259700</v>
       </c>
     </row>
     <row r="158">
@@ -7582,22 +7582,22 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N172" t="n">
         <v>16010.3</v>
       </c>
       <c r="O172" t="n">
-        <v>352226.6</v>
+        <v>336216.3</v>
       </c>
       <c r="P172" t="n">
         <v>30500</v>
       </c>
       <c r="Q172" t="n">
-        <v>671000</v>
+        <v>640500</v>
       </c>
     </row>
     <row r="173">
@@ -12514,10 +12514,10 @@
         <v>2830</v>
       </c>
       <c r="N287" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O287" t="n">
-        <v>8939576.140872704</v>
+        <v>8939576.140987603</v>
       </c>
       <c r="P287" t="n">
         <v>5600</v>
@@ -14647,10 +14647,10 @@
         <v>362</v>
       </c>
       <c r="N335" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O335" t="n">
-        <v>1301119.93433964</v>
+        <v>1301119.931586884</v>
       </c>
       <c r="P335" t="n">
         <v>6500</v>
@@ -14819,10 +14819,10 @@
         <v>1</v>
       </c>
       <c r="N339" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O339" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="P339" t="n">
         <v>5200</v>
@@ -19043,22 +19043,22 @@
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M436" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N436" t="n">
-        <v>893.67886945501</v>
+        <v>893.67886888156</v>
       </c>
       <c r="O436" t="n">
-        <v>252911.1200557679</v>
+        <v>251123.7621557183</v>
       </c>
       <c r="P436" t="n">
         <v>1200</v>
       </c>
       <c r="Q436" t="n">
-        <v>339600</v>
+        <v>337200</v>
       </c>
     </row>
     <row r="437">
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M642" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N642" t="n">
         <v>22730.48</v>
       </c>
       <c r="O642" t="n">
-        <v>1204715.44</v>
+        <v>1181984.96</v>
       </c>
       <c r="P642" t="n">
         <v>36900</v>
       </c>
       <c r="Q642" t="n">
-        <v>1955700</v>
+        <v>1918800</v>
       </c>
     </row>
     <row r="643">
@@ -32130,22 +32130,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M742" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N742" t="n">
         <v>18536</v>
       </c>
       <c r="O742" t="n">
-        <v>129752</v>
+        <v>111216</v>
       </c>
       <c r="P742" t="n">
         <v>30900</v>
       </c>
       <c r="Q742" t="n">
-        <v>216300</v>
+        <v>185400</v>
       </c>
     </row>
     <row r="743">
@@ -39501,10 +39501,10 @@
         <v>5</v>
       </c>
       <c r="N902" t="n">
-        <v>1907.3929677419</v>
+        <v>1907.3929220779</v>
       </c>
       <c r="O902" t="n">
-        <v>9536.9648387095</v>
+        <v>9536.964610389499</v>
       </c>
       <c r="P902" t="n">
         <v>2500</v>
@@ -39639,10 +39639,10 @@
         <v>309</v>
       </c>
       <c r="N905" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O905" t="n">
-        <v>557131.8517053463</v>
+        <v>557131.8552679617</v>
       </c>
       <c r="P905" t="n">
         <v>2500</v>
@@ -39731,10 +39731,10 @@
         <v>100</v>
       </c>
       <c r="N907" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O907" t="n">
-        <v>210879.24270463</v>
+        <v>210879.24803431</v>
       </c>
       <c r="P907" t="n">
         <v>2900</v>
@@ -39777,10 +39777,10 @@
         <v>287</v>
       </c>
       <c r="N908" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O908" t="n">
-        <v>590095.7957692272</v>
+        <v>590095.7915691546</v>
       </c>
       <c r="P908" t="n">
         <v>2900</v>
@@ -40096,22 +40096,22 @@
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M915" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N915" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O915" t="n">
-        <v>638504.2618757223</v>
+        <v>636911.98642532</v>
       </c>
       <c r="P915" t="n">
         <v>2500</v>
       </c>
       <c r="Q915" t="n">
-        <v>1002500</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="916">
@@ -41336,22 +41336,22 @@
         <v>0</v>
       </c>
       <c r="L942" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M942" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N942" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O942" t="n">
-        <v>3309790.6</v>
+        <v>3300845.22</v>
       </c>
       <c r="P942" t="n">
         <v>14900</v>
       </c>
       <c r="Q942" t="n">
-        <v>5513000</v>
+        <v>5498100</v>
       </c>
     </row>
     <row r="943">
@@ -43095,10 +43095,10 @@
         <v>13880</v>
       </c>
       <c r="N981" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O981" t="n">
-        <v>9768676.232405009</v>
+        <v>9768676.222513009</v>
       </c>
       <c r="P981" t="n">
         <v>900</v>
@@ -49746,22 +49746,22 @@
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1127" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1127" t="n">
         <v>1977</v>
       </c>
       <c r="O1127" t="n">
-        <v>31632</v>
+        <v>29655</v>
       </c>
       <c r="P1127" t="n">
         <v>2000</v>
       </c>
       <c r="Q1127" t="n">
-        <v>32000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1128">
@@ -50361,10 +50361,10 @@
         <v>380</v>
       </c>
       <c r="N1141" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O1141" t="n">
-        <v>8721647.82124348</v>
+        <v>8721647.81867696</v>
       </c>
       <c r="P1141" t="n">
         <v>37900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -5081,10 +5081,10 @@
         <v>11</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O112" t="n">
-        <v>172831.623964758</v>
+        <v>172831.62376106</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
@@ -5128,10 +5128,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="O113" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="P113" t="n">
         <v>18500</v>
@@ -12037,22 +12037,22 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M276" t="n">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="N276" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O276" t="n">
-        <v>2241397.822222261</v>
+        <v>2236233.309392832</v>
       </c>
       <c r="P276" t="n">
         <v>4500</v>
       </c>
       <c r="Q276" t="n">
-        <v>3906000</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="277">
@@ -13043,22 +13043,22 @@
         <v>0</v>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M299" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N299" t="n">
         <v>2742</v>
       </c>
       <c r="O299" t="n">
-        <v>191940</v>
+        <v>180972</v>
       </c>
       <c r="P299" t="n">
         <v>3500</v>
       </c>
       <c r="Q299" t="n">
-        <v>245000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="300">
@@ -13135,22 +13135,22 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N301" t="n">
         <v>7507.39</v>
       </c>
       <c r="O301" t="n">
-        <v>2147113.54</v>
+        <v>2139606.15</v>
       </c>
       <c r="P301" t="n">
         <v>13500</v>
       </c>
       <c r="Q301" t="n">
-        <v>3861000</v>
+        <v>3847500</v>
       </c>
     </row>
     <row r="302">
@@ -13184,22 +13184,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N302" t="n">
         <v>9664</v>
       </c>
       <c r="O302" t="n">
-        <v>309248</v>
+        <v>299584</v>
       </c>
       <c r="P302" t="n">
         <v>15900</v>
       </c>
       <c r="Q302" t="n">
-        <v>508800</v>
+        <v>492900</v>
       </c>
     </row>
     <row r="303">
@@ -13937,22 +13937,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M319" t="n">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="N319" t="n">
         <v>1203.38</v>
       </c>
       <c r="O319" t="n">
-        <v>743688.8400000001</v>
+        <v>740078.7000000001</v>
       </c>
       <c r="P319" t="n">
         <v>1900</v>
       </c>
       <c r="Q319" t="n">
-        <v>1174200</v>
+        <v>1168500</v>
       </c>
     </row>
     <row r="320">
@@ -14690,22 +14690,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M336" t="n">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="N336" t="n">
         <v>489.88</v>
       </c>
       <c r="O336" t="n">
-        <v>246409.64</v>
+        <v>243470.36</v>
       </c>
       <c r="P336" t="n">
         <v>700</v>
       </c>
       <c r="Q336" t="n">
-        <v>352100</v>
+        <v>347900</v>
       </c>
     </row>
     <row r="337">
@@ -39817,22 +39817,22 @@
         <v>0</v>
       </c>
       <c r="L909" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M909" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="N909" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O909" t="n">
-        <v>375896.2715983944</v>
+        <v>369272.5459650404</v>
       </c>
       <c r="P909" t="n">
         <v>2500</v>
       </c>
       <c r="Q909" t="n">
-        <v>567500</v>
+        <v>557500</v>
       </c>
     </row>
     <row r="910">
@@ -39958,22 +39958,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M912" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="N912" t="n">
         <v>1662</v>
       </c>
       <c r="O912" t="n">
-        <v>362316</v>
+        <v>354006</v>
       </c>
       <c r="P912" t="n">
         <v>2900</v>
       </c>
       <c r="Q912" t="n">
-        <v>632200</v>
+        <v>617700</v>
       </c>
     </row>
     <row r="913">
@@ -40056,10 +40056,10 @@
         <v>400</v>
       </c>
       <c r="N914" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O914" t="n">
-        <v>636912.23557692</v>
+        <v>636912.27151516</v>
       </c>
       <c r="P914" t="n">
         <v>2500</v>
@@ -40187,10 +40187,10 @@
         <v>189</v>
       </c>
       <c r="N917" t="n">
-        <v>2311.9153823529</v>
+        <v>2311.9150892857</v>
       </c>
       <c r="O917" t="n">
-        <v>436952.0072646981</v>
+        <v>436951.9518749973</v>
       </c>
       <c r="P917" t="n">
         <v>3500</v>
@@ -40233,10 +40233,10 @@
         <v>142</v>
       </c>
       <c r="N918" t="n">
-        <v>1906.1813793103</v>
+        <v>1906.1812280702</v>
       </c>
       <c r="O918" t="n">
-        <v>270677.7558620626</v>
+        <v>270677.7343859684</v>
       </c>
       <c r="P918" t="n">
         <v>2900</v>
@@ -40417,10 +40417,10 @@
         <v>1077</v>
       </c>
       <c r="N922" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O922" t="n">
-        <v>1356238.783026389</v>
+        <v>1356238.788765506</v>
       </c>
       <c r="P922" t="n">
         <v>1900</v>
@@ -42911,22 +42911,22 @@
         <v>0</v>
       </c>
       <c r="L977" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M977" t="n">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="N977" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O977" t="n">
-        <v>4212077.935780105</v>
+        <v>4199634.56005965</v>
       </c>
       <c r="P977" t="n">
         <v>4500</v>
       </c>
       <c r="Q977" t="n">
-        <v>6093000</v>
+        <v>6075000</v>
       </c>
     </row>
     <row r="978">
@@ -43792,10 +43792,10 @@
         <v>81</v>
       </c>
       <c r="N997" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O997" t="n">
-        <v>129236.4437716134</v>
+        <v>129236.4397034694</v>
       </c>
       <c r="P997" t="n">
         <v>2500</v>
@@ -51486,22 +51486,22 @@
         <v>0</v>
       </c>
       <c r="L1166" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1166" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N1166" t="n">
         <v>7480</v>
       </c>
       <c r="O1166" t="n">
-        <v>209440</v>
+        <v>179520</v>
       </c>
       <c r="P1166" t="n">
         <v>9500</v>
       </c>
       <c r="Q1166" t="n">
-        <v>266000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="1167">
@@ -51624,22 +51624,22 @@
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1169" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1169" t="n">
         <v>6160</v>
       </c>
       <c r="O1169" t="n">
-        <v>264880</v>
+        <v>252560</v>
       </c>
       <c r="P1169" t="n">
         <v>7900</v>
       </c>
       <c r="Q1169" t="n">
-        <v>339700</v>
+        <v>323900</v>
       </c>
     </row>
     <row r="1170">
@@ -51670,22 +51670,22 @@
         <v>0</v>
       </c>
       <c r="L1170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1170" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N1170" t="n">
         <v>4400</v>
       </c>
       <c r="O1170" t="n">
-        <v>510400</v>
+        <v>501600</v>
       </c>
       <c r="P1170" t="n">
         <v>5900</v>
       </c>
       <c r="Q1170" t="n">
-        <v>684400</v>
+        <v>672600</v>
       </c>
     </row>
     <row r="1171">
@@ -51808,22 +51808,22 @@
         <v>0</v>
       </c>
       <c r="L1173" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1173" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N1173" t="n">
         <v>9240</v>
       </c>
       <c r="O1173" t="n">
-        <v>452760</v>
+        <v>378840</v>
       </c>
       <c r="P1173" t="n">
         <v>11500</v>
       </c>
       <c r="Q1173" t="n">
-        <v>563500</v>
+        <v>471500</v>
       </c>
     </row>
     <row r="1174">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -1514,22 +1514,22 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
         <v>48710.1</v>
       </c>
       <c r="O27" t="n">
-        <v>584521.2</v>
+        <v>535811.1</v>
       </c>
       <c r="P27" t="n">
         <v>67900</v>
       </c>
       <c r="Q27" t="n">
-        <v>814800</v>
+        <v>746900</v>
       </c>
     </row>
     <row r="28">
@@ -12085,10 +12085,10 @@
         <v>861</v>
       </c>
       <c r="N277" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O277" t="n">
-        <v>2223322.025633793</v>
+        <v>2223322.023060436</v>
       </c>
       <c r="P277" t="n">
         <v>4500</v>
@@ -13979,22 +13979,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M320" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="N320" t="n">
         <v>1203.38</v>
       </c>
       <c r="O320" t="n">
-        <v>696757.02</v>
+        <v>693146.8800000001</v>
       </c>
       <c r="P320" t="n">
         <v>1900</v>
       </c>
       <c r="Q320" t="n">
-        <v>1100100</v>
+        <v>1094400</v>
       </c>
     </row>
     <row r="321">
@@ -14732,22 +14732,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M337" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="N337" t="n">
         <v>489.88</v>
       </c>
       <c r="O337" t="n">
-        <v>237591.8</v>
+        <v>235632.28</v>
       </c>
       <c r="P337" t="n">
         <v>700</v>
       </c>
       <c r="Q337" t="n">
-        <v>339500</v>
+        <v>336700</v>
       </c>
     </row>
     <row r="338">
@@ -18169,10 +18169,10 @@
         <v>17</v>
       </c>
       <c r="N416" t="n">
-        <v>8296.6427272727</v>
+        <v>8296.6429032258</v>
       </c>
       <c r="O416" t="n">
-        <v>141042.9263636359</v>
+        <v>141042.9293548386</v>
       </c>
       <c r="P416" t="n">
         <v>15900</v>
@@ -18616,10 +18616,10 @@
         <v>449</v>
       </c>
       <c r="N426" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O426" t="n">
-        <v>696037.057497628</v>
+        <v>696037.0582310247</v>
       </c>
       <c r="P426" t="n">
         <v>2500</v>
@@ -28482,10 +28482,10 @@
         <v>79</v>
       </c>
       <c r="N658" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O658" t="n">
-        <v>658289.5900757558</v>
+        <v>658289.5900000029</v>
       </c>
       <c r="P658" t="n">
         <v>14900</v>
@@ -40052,10 +40052,10 @@
         <v>400</v>
       </c>
       <c r="N914" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O914" t="n">
-        <v>636912.4160401201</v>
+        <v>636912.45512012</v>
       </c>
       <c r="P914" t="n">
         <v>2500</v>
@@ -42728,10 +42728,10 @@
         <v>1339</v>
       </c>
       <c r="N973" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O973" t="n">
-        <v>692652.5982106454</v>
+        <v>692652.6123551318</v>
       </c>
       <c r="P973" t="n">
         <v>900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -10943,22 +10943,22 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M251" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="N251" t="n">
         <v>1789</v>
       </c>
       <c r="O251" t="n">
-        <v>783582</v>
+        <v>772848</v>
       </c>
       <c r="P251" t="n">
         <v>2700</v>
       </c>
       <c r="Q251" t="n">
-        <v>1182600</v>
+        <v>1166400</v>
       </c>
     </row>
     <row r="252">
@@ -10984,22 +10984,22 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M252" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="N252" t="n">
         <v>1267</v>
       </c>
       <c r="O252" t="n">
-        <v>241997</v>
+        <v>226793</v>
       </c>
       <c r="P252" t="n">
         <v>1900</v>
       </c>
       <c r="Q252" t="n">
-        <v>362900</v>
+        <v>340100</v>
       </c>
     </row>
     <row r="253">
@@ -12730,22 +12730,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M292" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N292" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O292" t="n">
-        <v>245485.0963752668</v>
+        <v>235794.8938197418</v>
       </c>
       <c r="P292" t="n">
         <v>6200</v>
       </c>
       <c r="Q292" t="n">
-        <v>471200</v>
+        <v>452600</v>
       </c>
     </row>
     <row r="293">
@@ -13233,10 +13233,10 @@
         <v>240</v>
       </c>
       <c r="N303" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O303" t="n">
-        <v>1200480</v>
+        <v>1203214.578587688</v>
       </c>
       <c r="P303" t="n">
         <v>8400</v>
@@ -13790,22 +13790,22 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M316" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N316" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O316" t="n">
-        <v>1506406.455191114</v>
+        <v>1496624.595111106</v>
       </c>
       <c r="P316" t="n">
         <v>8200</v>
       </c>
       <c r="Q316" t="n">
-        <v>2525600</v>
+        <v>2509200</v>
       </c>
     </row>
     <row r="317">
@@ -14151,22 +14151,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M324" t="n">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="N324" t="n">
         <v>1789</v>
       </c>
       <c r="O324" t="n">
-        <v>935647</v>
+        <v>924913</v>
       </c>
       <c r="P324" t="n">
         <v>2700</v>
       </c>
       <c r="Q324" t="n">
-        <v>1412100</v>
+        <v>1395900</v>
       </c>
     </row>
     <row r="325">
@@ -14284,22 +14284,22 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M327" t="n">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="N327" t="n">
         <v>5667.94</v>
       </c>
       <c r="O327" t="n">
-        <v>4262290.88</v>
+        <v>4250955</v>
       </c>
       <c r="P327" t="n">
         <v>9500</v>
       </c>
       <c r="Q327" t="n">
-        <v>7144000</v>
+        <v>7125000</v>
       </c>
     </row>
     <row r="328">
@@ -14638,22 +14638,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M335" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N335" t="n">
         <v>489.88</v>
       </c>
       <c r="O335" t="n">
-        <v>235632.28</v>
+        <v>232693</v>
       </c>
       <c r="P335" t="n">
         <v>700</v>
       </c>
       <c r="Q335" t="n">
-        <v>336700</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="336">
@@ -15034,10 +15034,10 @@
         <v>6313</v>
       </c>
       <c r="N344" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O344" t="n">
-        <v>13199536.05</v>
+        <v>13210861.26325642</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
@@ -15934,22 +15934,22 @@
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M365" t="n">
-        <v>8125</v>
+        <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O365" t="n">
-        <v>35524212.68311419</v>
+        <v>35515468.26245017</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
       </c>
       <c r="Q365" t="n">
-        <v>60937500</v>
+        <v>60922500</v>
       </c>
     </row>
     <row r="366">
@@ -16106,22 +16106,22 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M369" t="n">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="N369" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O369" t="n">
-        <v>590842.0679651041</v>
+        <v>590335.6045218835</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
       </c>
       <c r="Q369" t="n">
-        <v>1446900</v>
+        <v>1423500</v>
       </c>
     </row>
     <row r="370">
@@ -16711,22 +16711,22 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M383" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N383" t="n">
         <v>4648.6</v>
       </c>
       <c r="O383" t="n">
-        <v>1073826.6</v>
+        <v>1064529.4</v>
       </c>
       <c r="P383" t="n">
         <v>8900</v>
       </c>
       <c r="Q383" t="n">
-        <v>2055900</v>
+        <v>2038100</v>
       </c>
     </row>
     <row r="384">
@@ -17054,22 +17054,22 @@
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M391" t="n">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="N391" t="n">
         <v>1387.55</v>
       </c>
       <c r="O391" t="n">
-        <v>3253804.75</v>
+        <v>3249642.1</v>
       </c>
       <c r="P391" t="n">
         <v>2300</v>
       </c>
       <c r="Q391" t="n">
-        <v>5393500</v>
+        <v>5386600</v>
       </c>
     </row>
     <row r="392">
@@ -18424,22 +18424,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M422" t="n">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O422" t="n">
-        <v>468075.1524143247</v>
+        <v>450134.9927520804</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>717500</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="423">
@@ -18516,22 +18516,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M424" t="n">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O424" t="n">
-        <v>691386.4822168468</v>
+        <v>665033.1888136794</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1115000</v>
+        <v>1072500</v>
       </c>
     </row>
     <row r="425">
@@ -18608,22 +18608,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M426" t="n">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O426" t="n">
-        <v>1634389.137775876</v>
+        <v>1615161.04592976</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2380000</v>
+        <v>2352000</v>
       </c>
     </row>
     <row r="427">
@@ -18698,22 +18698,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M428" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N428" t="n">
-        <v>2521.5033757962</v>
+        <v>2521.5026451613</v>
       </c>
       <c r="O428" t="n">
-        <v>383268.5131210224</v>
+        <v>378225.396774195</v>
       </c>
       <c r="P428" t="n">
         <v>3900</v>
       </c>
       <c r="Q428" t="n">
-        <v>592800</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="429">
@@ -23157,10 +23157,10 @@
         <v>23</v>
       </c>
       <c r="N532" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O532" t="n">
-        <v>57896.06</v>
+        <v>58458.6128097174</v>
       </c>
       <c r="P532" t="n">
         <v>4200</v>
@@ -23766,22 +23766,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M547" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N547" t="n">
         <v>7103</v>
       </c>
       <c r="O547" t="n">
-        <v>916287</v>
+        <v>902081</v>
       </c>
       <c r="P547" t="n">
         <v>10700</v>
       </c>
       <c r="Q547" t="n">
-        <v>1380300</v>
+        <v>1358900</v>
       </c>
     </row>
     <row r="548">
@@ -26356,22 +26356,22 @@
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M608" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N608" t="n">
         <v>2856</v>
       </c>
       <c r="O608" t="n">
-        <v>322728</v>
+        <v>305592</v>
       </c>
       <c r="P608" t="n">
         <v>2400</v>
       </c>
       <c r="Q608" t="n">
-        <v>271200</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="609">
@@ -26397,22 +26397,22 @@
         <v>0</v>
       </c>
       <c r="L609" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M609" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N609" t="n">
         <v>926</v>
       </c>
       <c r="O609" t="n">
-        <v>15742</v>
+        <v>14816</v>
       </c>
       <c r="P609" t="n">
         <v>1600</v>
       </c>
       <c r="Q609" t="n">
-        <v>27200</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="610">
@@ -26725,22 +26725,22 @@
         <v>0</v>
       </c>
       <c r="L617" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M617" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N617" t="n">
         <v>1352</v>
       </c>
       <c r="O617" t="n">
-        <v>232544</v>
+        <v>224432</v>
       </c>
       <c r="P617" t="n">
         <v>2400</v>
       </c>
       <c r="Q617" t="n">
-        <v>412800</v>
+        <v>398400</v>
       </c>
     </row>
     <row r="618">
@@ -31574,22 +31574,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M730" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N730" t="n">
-        <v>1664.3525567322</v>
+        <v>1664.3525037936</v>
       </c>
       <c r="O730" t="n">
-        <v>21636.5832375186</v>
+        <v>18307.8775417296</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
       </c>
       <c r="Q730" t="n">
-        <v>37700</v>
+        <v>31900</v>
       </c>
     </row>
     <row r="731">
@@ -34892,22 +34892,22 @@
         <v>0</v>
       </c>
       <c r="L802" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M802" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N802" t="n">
         <v>13019</v>
       </c>
       <c r="O802" t="n">
-        <v>872273</v>
+        <v>859254</v>
       </c>
       <c r="P802" t="n">
         <v>20900</v>
       </c>
       <c r="Q802" t="n">
-        <v>1400300</v>
+        <v>1379400</v>
       </c>
     </row>
     <row r="803">
@@ -39129,10 +39129,10 @@
         <v>1284</v>
       </c>
       <c r="N894" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O894" t="n">
-        <v>1946593.805205556</v>
+        <v>1948894.290301312</v>
       </c>
       <c r="P894" t="n">
         <v>2300</v>
@@ -39397,22 +39397,22 @@
         <v>0</v>
       </c>
       <c r="L900" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M900" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N900" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O900" t="n">
-        <v>544510.7980131918</v>
+        <v>539101.7521870579</v>
       </c>
       <c r="P900" t="n">
         <v>2500</v>
       </c>
       <c r="Q900" t="n">
-        <v>755000</v>
+        <v>747500</v>
       </c>
     </row>
     <row r="901">
@@ -39860,22 +39860,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M910" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="N910" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O910" t="n">
-        <v>633728.0495026128</v>
+        <v>620989.8448412881</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
       </c>
       <c r="Q910" t="n">
-        <v>995000</v>
+        <v>975000</v>
       </c>
     </row>
     <row r="911">
@@ -42273,22 +42273,22 @@
         <v>0</v>
       </c>
       <c r="L963" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M963" t="n">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="N963" t="n">
         <v>177.65</v>
       </c>
       <c r="O963" t="n">
-        <v>176939.4</v>
+        <v>175162.9</v>
       </c>
       <c r="P963" t="n">
         <v>300</v>
       </c>
       <c r="Q963" t="n">
-        <v>298800</v>
+        <v>295800</v>
       </c>
     </row>
     <row r="964">
@@ -42536,22 +42536,22 @@
         <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M969" t="n">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="N969" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O969" t="n">
-        <v>684893.6585123597</v>
+        <v>682872.9825046274</v>
       </c>
       <c r="P969" t="n">
         <v>900</v>
       </c>
       <c r="Q969" t="n">
-        <v>1191600</v>
+        <v>1186200</v>
       </c>
     </row>
     <row r="970">
@@ -42853,22 +42853,22 @@
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M976" t="n">
-        <v>13771</v>
+        <v>13764</v>
       </c>
       <c r="N976" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O976" t="n">
-        <v>9691961.246407667</v>
+        <v>9687034.634490304</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>12393900</v>
+        <v>12387600</v>
       </c>
     </row>
     <row r="977">
@@ -47916,22 +47916,22 @@
         <v>0</v>
       </c>
       <c r="L1085" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1085" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N1085" t="n">
         <v>2331</v>
       </c>
       <c r="O1085" t="n">
-        <v>1065267</v>
+        <v>1062936</v>
       </c>
       <c r="P1085" t="n">
         <v>3500</v>
       </c>
       <c r="Q1085" t="n">
-        <v>1599500</v>
+        <v>1596000</v>
       </c>
     </row>
     <row r="1086">
@@ -49027,22 +49027,22 @@
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1111" t="n">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="N1111" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1111" t="n">
-        <v>1756619.01</v>
+        <v>1749559.59</v>
       </c>
       <c r="P1111" t="n">
         <v>1900</v>
       </c>
       <c r="Q1111" t="n">
-        <v>2836700</v>
+        <v>2825300</v>
       </c>
     </row>
     <row r="1112">
@@ -49115,22 +49115,22 @@
         <v>0</v>
       </c>
       <c r="L1113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1113" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N1113" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1113" t="n">
-        <v>190914</v>
+        <v>187732.1</v>
       </c>
       <c r="P1113" t="n">
         <v>5100</v>
       </c>
       <c r="Q1113" t="n">
-        <v>306000</v>
+        <v>300900</v>
       </c>
     </row>
     <row r="1114">
@@ -51388,22 +51388,22 @@
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1164" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="N1164" t="n">
         <v>3872</v>
       </c>
       <c r="O1164" t="n">
-        <v>433664</v>
+        <v>387200</v>
       </c>
       <c r="P1164" t="n">
         <v>4900</v>
       </c>
       <c r="Q1164" t="n">
-        <v>548800</v>
+        <v>490000</v>
       </c>
     </row>
     <row r="1165">
@@ -51434,22 +51434,22 @@
         <v>0</v>
       </c>
       <c r="L1165" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1165" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N1165" t="n">
         <v>6160</v>
       </c>
       <c r="O1165" t="n">
-        <v>246400</v>
+        <v>172480</v>
       </c>
       <c r="P1165" t="n">
         <v>7900</v>
       </c>
       <c r="Q1165" t="n">
-        <v>316000</v>
+        <v>221200</v>
       </c>
     </row>
     <row r="1166">
@@ -51532,10 +51532,10 @@
         <v>50</v>
       </c>
       <c r="N1167" t="n">
-        <v>3520</v>
+        <v>3571.512195122</v>
       </c>
       <c r="O1167" t="n">
-        <v>176000</v>
+        <v>178575.6097561</v>
       </c>
       <c r="P1167" t="n">
         <v>4500</v>
@@ -51618,22 +51618,22 @@
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1169" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N1169" t="n">
         <v>9240</v>
       </c>
       <c r="O1169" t="n">
-        <v>341880</v>
+        <v>295680</v>
       </c>
       <c r="P1169" t="n">
         <v>11500</v>
       </c>
       <c r="Q1169" t="n">
-        <v>425500</v>
+        <v>368000</v>
       </c>
     </row>
     <row r="1170">
@@ -51710,22 +51710,22 @@
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1171" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N1171" t="n">
         <v>4576</v>
       </c>
       <c r="O1171" t="n">
-        <v>649792</v>
+        <v>640640</v>
       </c>
       <c r="P1171" t="n">
         <v>5900</v>
       </c>
       <c r="Q1171" t="n">
-        <v>837800</v>
+        <v>826000</v>
       </c>
     </row>
     <row r="1172">
@@ -51756,22 +51756,22 @@
         <v>0</v>
       </c>
       <c r="L1172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1172" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N1172" t="n">
         <v>5280</v>
       </c>
       <c r="O1172" t="n">
-        <v>279840</v>
+        <v>269280</v>
       </c>
       <c r="P1172" t="n">
         <v>6900</v>
       </c>
       <c r="Q1172" t="n">
-        <v>365700</v>
+        <v>351900</v>
       </c>
     </row>
     <row r="1173">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -642,19 +642,19 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>96741.43166666701</v>
+        <v>96741.433529412</v>
       </c>
       <c r="O6" t="n">
-        <v>1064155.748333337</v>
+        <v>967414.33529412</v>
       </c>
       <c r="P6" t="n">
         <v>188900</v>
       </c>
       <c r="Q6" t="n">
-        <v>2077900</v>
+        <v>1889000</v>
       </c>
     </row>
     <row r="7">
@@ -1036,10 +1036,10 @@
         <v>42</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3078994614</v>
+        <v>1811.3079710145</v>
       </c>
       <c r="O15" t="n">
-        <v>76074.93177737881</v>
+        <v>76074.93478260899</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2219,19 +2219,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N44" t="n">
-        <v>9994.763070175401</v>
+        <v>9994.7630837004</v>
       </c>
       <c r="O44" t="n">
-        <v>1759078.30035087</v>
+        <v>1749083.53964757</v>
       </c>
       <c r="P44" t="n">
         <v>16500</v>
       </c>
       <c r="Q44" t="n">
-        <v>2904000</v>
+        <v>2887500</v>
       </c>
     </row>
     <row r="45">
@@ -2541,10 +2541,10 @@
         <v>7</v>
       </c>
       <c r="N52" t="n">
-        <v>1854.2405936073</v>
+        <v>1854.2409952607</v>
       </c>
       <c r="O52" t="n">
-        <v>12979.6841552511</v>
+        <v>12979.6869668249</v>
       </c>
       <c r="P52" t="n">
         <v>3200</v>
@@ -2583,10 +2583,10 @@
         <v>49</v>
       </c>
       <c r="N53" t="n">
-        <v>1933.3880645161</v>
+        <v>1933.3881018519</v>
       </c>
       <c r="O53" t="n">
-        <v>94736.0151612889</v>
+        <v>94736.0169907431</v>
       </c>
       <c r="P53" t="n">
         <v>4500</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2736,19 +2736,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N57" t="n">
-        <v>6272.8549740933</v>
+        <v>6272.8549913345</v>
       </c>
       <c r="O57" t="n">
-        <v>169367.0843005191</v>
+        <v>163094.229774697</v>
       </c>
       <c r="P57" t="n">
         <v>7900</v>
       </c>
       <c r="Q57" t="n">
-        <v>213300</v>
+        <v>205400</v>
       </c>
     </row>
     <row r="58">
@@ -4040,10 +4040,10 @@
         <v>25</v>
       </c>
       <c r="N89" t="n">
-        <v>3910.6280349345</v>
+        <v>3910.6280306346</v>
       </c>
       <c r="O89" t="n">
-        <v>97765.70087336251</v>
+        <v>97765.700765865</v>
       </c>
       <c r="P89" t="n">
         <v>9100</v>
@@ -4864,10 +4864,10 @@
         <v>6</v>
       </c>
       <c r="N107" t="n">
-        <v>12837.9714</v>
+        <v>12837.974318182</v>
       </c>
       <c r="O107" t="n">
-        <v>77027.8284</v>
+        <v>77027.84590909199</v>
       </c>
       <c r="P107" t="n">
         <v>22900</v>
@@ -4995,10 +4995,10 @@
         <v>9</v>
       </c>
       <c r="N110" t="n">
-        <v>16486.40848</v>
+        <v>16486.408292683</v>
       </c>
       <c r="O110" t="n">
-        <v>148377.67632</v>
+        <v>148377.674634147</v>
       </c>
       <c r="P110" t="n">
         <v>30500</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5031,19 +5031,19 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N111" t="n">
         <v>36762.36</v>
       </c>
       <c r="O111" t="n">
-        <v>2683652.28</v>
+        <v>2646889.92</v>
       </c>
       <c r="P111" t="n">
         <v>57100</v>
       </c>
       <c r="Q111" t="n">
-        <v>4168300</v>
+        <v>4111200</v>
       </c>
     </row>
     <row r="112">
@@ -5076,10 +5076,10 @@
         <v>9</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.96573991</v>
+        <v>15711.96562212</v>
       </c>
       <c r="O112" t="n">
-        <v>141407.69165919</v>
+        <v>141407.69059908</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
@@ -5516,10 +5516,10 @@
         <v>30</v>
       </c>
       <c r="N123" t="n">
-        <v>14708.815698925</v>
+        <v>14708.815652174</v>
       </c>
       <c r="O123" t="n">
-        <v>441264.47096775</v>
+        <v>441264.46956522</v>
       </c>
       <c r="P123" t="n">
         <v>16900</v>
@@ -6371,10 +6371,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>200072.20121739</v>
+        <v>200072.20172727</v>
       </c>
       <c r="O143" t="n">
-        <v>200072.20121739</v>
+        <v>200072.20172727</v>
       </c>
       <c r="P143" t="n">
         <v>312000</v>
@@ -6551,10 +6551,10 @@
         <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>344599.1786</v>
+        <v>344599.17851064</v>
       </c>
       <c r="O147" t="n">
-        <v>344599.1786</v>
+        <v>344599.17851064</v>
       </c>
       <c r="P147" t="n">
         <v>532900</v>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7195,19 +7195,19 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N163" t="n">
         <v>2300</v>
       </c>
       <c r="O163" t="n">
-        <v>133400</v>
+        <v>124200</v>
       </c>
       <c r="P163" t="n">
         <v>2800</v>
       </c>
       <c r="Q163" t="n">
-        <v>162400</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="164">
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -7901,19 +7901,19 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="N179" t="n">
         <v>2570.16</v>
       </c>
       <c r="O179" t="n">
-        <v>444637.68</v>
+        <v>406085.28</v>
       </c>
       <c r="P179" t="n">
         <v>4700</v>
       </c>
       <c r="Q179" t="n">
-        <v>813100</v>
+        <v>742600</v>
       </c>
     </row>
     <row r="180">
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8105,19 +8105,19 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N184" t="n">
         <v>3667.11</v>
       </c>
       <c r="O184" t="n">
-        <v>47672.43</v>
+        <v>44005.32</v>
       </c>
       <c r="P184" t="n">
         <v>7300</v>
       </c>
       <c r="Q184" t="n">
-        <v>94900</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="185">
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K193" t="n">
         <v>0</v>
@@ -8471,19 +8471,19 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N193" t="n">
-        <v>1801.0166666667</v>
+        <v>1801.0175</v>
       </c>
       <c r="O193" t="n">
-        <v>46826.4333333342</v>
+        <v>32418.315</v>
       </c>
       <c r="P193" t="n">
         <v>3200</v>
       </c>
       <c r="Q193" t="n">
-        <v>83200</v>
+        <v>57600</v>
       </c>
     </row>
     <row r="194">
@@ -8831,10 +8831,10 @@
         <v>17</v>
       </c>
       <c r="N201" t="n">
-        <v>3340.680083682</v>
+        <v>3340.6800838574</v>
       </c>
       <c r="O201" t="n">
-        <v>56791.56142259399</v>
+        <v>56791.5614255758</v>
       </c>
       <c r="P201" t="n">
         <v>7100</v>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>9214</v>
+        <v>9166</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -9649,19 +9649,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>9214</v>
+        <v>9166</v>
       </c>
       <c r="N220" t="n">
         <v>1726.32</v>
       </c>
       <c r="O220" t="n">
-        <v>15906312.48</v>
+        <v>15823449.12</v>
       </c>
       <c r="P220" t="n">
         <v>1500</v>
       </c>
       <c r="Q220" t="n">
-        <v>13821000</v>
+        <v>13749000</v>
       </c>
     </row>
     <row r="221">
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -9690,19 +9690,19 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N221" t="n">
         <v>2088.01</v>
       </c>
       <c r="O221" t="n">
-        <v>317377.52</v>
+        <v>311113.49</v>
       </c>
       <c r="P221" t="n">
         <v>3500</v>
       </c>
       <c r="Q221" t="n">
-        <v>532000</v>
+        <v>521500</v>
       </c>
     </row>
     <row r="222">
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -9992,19 +9992,19 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N228" t="n">
         <v>3775.99</v>
       </c>
       <c r="O228" t="n">
-        <v>67967.81999999999</v>
+        <v>64191.82999999999</v>
       </c>
       <c r="P228" t="n">
         <v>7300</v>
       </c>
       <c r="Q228" t="n">
-        <v>131400</v>
+        <v>124100</v>
       </c>
     </row>
     <row r="229">
@@ -10191,7 +10191,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>962</v>
+        <v>910</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10200,19 +10200,19 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>962</v>
+        <v>910</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0617613973</v>
+        <v>1098.0622084592</v>
       </c>
       <c r="O233" t="n">
-        <v>1056335.414464202</v>
+        <v>999236.6096978721</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
       </c>
       <c r="Q233" t="n">
-        <v>1443000</v>
+        <v>1365000</v>
       </c>
     </row>
     <row r="234">
@@ -10937,13 +10937,13 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
       </c>
       <c r="L251" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
         <v>432</v>
@@ -10978,13 +10978,13 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
         <v>179</v>
@@ -11019,7 +11019,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11028,19 +11028,19 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N253" t="n">
         <v>5879</v>
       </c>
       <c r="O253" t="n">
-        <v>511473</v>
+        <v>505594</v>
       </c>
       <c r="P253" t="n">
         <v>10050</v>
       </c>
       <c r="Q253" t="n">
-        <v>874350</v>
+        <v>864300</v>
       </c>
     </row>
     <row r="254">
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11120,19 +11120,19 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N255" t="n">
         <v>2189</v>
       </c>
       <c r="O255" t="n">
-        <v>591030</v>
+        <v>577896</v>
       </c>
       <c r="P255" t="n">
         <v>4500</v>
       </c>
       <c r="Q255" t="n">
-        <v>1215000</v>
+        <v>1188000</v>
       </c>
     </row>
     <row r="256">
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -11988,19 +11988,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2555195682</v>
+        <v>2582.2555145238</v>
       </c>
       <c r="O275" t="n">
-        <v>2220739.746828652</v>
+        <v>2218157.486975944</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>3870000</v>
+        <v>3865500</v>
       </c>
     </row>
     <row r="276">
@@ -12037,10 +12037,10 @@
         <v>1383</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960541642</v>
+        <v>5216.8960524399</v>
       </c>
       <c r="O276" t="n">
-        <v>7214967.242909089</v>
+        <v>7214967.240524381</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12167,19 +12167,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N279" t="n">
-        <v>2033.5247692308</v>
+        <v>2033.5241860465</v>
       </c>
       <c r="O279" t="n">
-        <v>180983.7044615412</v>
+        <v>178950.128372092</v>
       </c>
       <c r="P279" t="n">
         <v>4100</v>
       </c>
       <c r="Q279" t="n">
-        <v>364900</v>
+        <v>360800</v>
       </c>
     </row>
     <row r="280">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12459,19 +12459,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="N286" t="n">
-        <v>3158.8608303391</v>
+        <v>3158.8608305026</v>
       </c>
       <c r="O286" t="n">
-        <v>8939576.149859654</v>
+        <v>8936417.289491855</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
       </c>
       <c r="Q286" t="n">
-        <v>15848000</v>
+        <v>15842400</v>
       </c>
     </row>
     <row r="287">
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12505,19 +12505,19 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N287" t="n">
         <v>1903</v>
       </c>
       <c r="O287" t="n">
-        <v>17127</v>
+        <v>15224</v>
       </c>
       <c r="P287" t="n">
         <v>3200</v>
       </c>
       <c r="Q287" t="n">
-        <v>28800</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="288">
@@ -12724,13 +12724,13 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>73</v>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13086,19 +13086,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N300" t="n">
         <v>7507.39</v>
       </c>
       <c r="O300" t="n">
-        <v>2139606.15</v>
+        <v>2132098.76</v>
       </c>
       <c r="P300" t="n">
         <v>13500</v>
       </c>
       <c r="Q300" t="n">
-        <v>3847500</v>
+        <v>3834000</v>
       </c>
     </row>
     <row r="301">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13135,19 +13135,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N301" t="n">
         <v>9664</v>
       </c>
       <c r="O301" t="n">
-        <v>299584</v>
+        <v>289920</v>
       </c>
       <c r="P301" t="n">
         <v>15900</v>
       </c>
       <c r="Q301" t="n">
-        <v>492900</v>
+        <v>477000</v>
       </c>
     </row>
     <row r="302">
@@ -13233,10 +13233,10 @@
         <v>240</v>
       </c>
       <c r="N303" t="n">
-        <v>5013.3940774487</v>
+        <v>5002</v>
       </c>
       <c r="O303" t="n">
-        <v>1203214.578587688</v>
+        <v>1200480</v>
       </c>
       <c r="P303" t="n">
         <v>8400</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13532,19 +13532,19 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N310" t="n">
         <v>7939.23</v>
       </c>
       <c r="O310" t="n">
-        <v>1246459.11</v>
+        <v>1238519.88</v>
       </c>
       <c r="P310" t="n">
         <v>14900</v>
       </c>
       <c r="Q310" t="n">
-        <v>2339300</v>
+        <v>2324400</v>
       </c>
     </row>
     <row r="311">
@@ -13784,13 +13784,13 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>306</v>
@@ -13842,10 +13842,10 @@
         <v>21</v>
       </c>
       <c r="N317" t="n">
-        <v>4967.8663636364</v>
+        <v>4967.8801694915</v>
       </c>
       <c r="O317" t="n">
-        <v>104325.1936363644</v>
+        <v>104325.4835593215</v>
       </c>
       <c r="P317" t="n">
         <v>7500</v>
@@ -14145,13 +14145,13 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M324" t="n">
         <v>517</v>
@@ -14278,13 +14278,13 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M327" t="n">
         <v>750</v>
@@ -14595,10 +14595,10 @@
         <v>360</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2537131631</v>
+        <v>3594.2536883629</v>
       </c>
       <c r="O334" t="n">
-        <v>1293931.336738716</v>
+        <v>1293931.327810644</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M335" t="n">
         <v>475</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>6313</v>
+        <v>6311</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -15031,19 +15031,19 @@
         <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>6313</v>
+        <v>6311</v>
       </c>
       <c r="N344" t="n">
-        <v>2092.643951094</v>
+        <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>13210861.26325642</v>
+        <v>13195354.35</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>18307700</v>
+        <v>18301900</v>
       </c>
     </row>
     <row r="345">
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15850,19 +15850,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N363" t="n">
-        <v>3041.660013541</v>
+        <v>3041.6600136054</v>
       </c>
       <c r="O363" t="n">
-        <v>325457.621448887</v>
+        <v>316332.6414149616</v>
       </c>
       <c r="P363" t="n">
         <v>5500</v>
       </c>
       <c r="Q363" t="n">
-        <v>588500</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="364">
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -15891,19 +15891,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N364" t="n">
         <v>3981.47</v>
       </c>
       <c r="O364" t="n">
-        <v>521572.5699999999</v>
+        <v>509628.16</v>
       </c>
       <c r="P364" t="n">
         <v>7000</v>
       </c>
       <c r="Q364" t="n">
-        <v>917000</v>
+        <v>896000</v>
       </c>
     </row>
     <row r="365">
@@ -15928,22 +15928,22 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>8125</v>
+        <v>8123</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M365" t="n">
         <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4372.2107918811</v>
+        <v>4372.2107921642</v>
       </c>
       <c r="O365" t="n">
-        <v>35515468.26245017</v>
+        <v>35515468.2647498</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
@@ -16100,28 +16100,28 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="N369" t="n">
-        <v>1617.3578206079</v>
+        <v>1592.5661309524</v>
       </c>
       <c r="O369" t="n">
-        <v>590335.6045218835</v>
+        <v>574916.3732738164</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
       </c>
       <c r="Q369" t="n">
-        <v>1423500</v>
+        <v>1407900</v>
       </c>
     </row>
     <row r="370">
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -16150,19 +16150,19 @@
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N370" t="n">
         <v>4513.76</v>
       </c>
       <c r="O370" t="n">
-        <v>306935.68</v>
+        <v>302421.92</v>
       </c>
       <c r="P370" t="n">
         <v>8900</v>
       </c>
       <c r="Q370" t="n">
-        <v>605200</v>
+        <v>596300</v>
       </c>
     </row>
     <row r="371">
@@ -16400,7 +16400,7 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K376" t="n">
         <v>0</v>
@@ -16409,19 +16409,19 @@
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N376" t="n">
         <v>6446.04</v>
       </c>
       <c r="O376" t="n">
-        <v>1411682.76</v>
+        <v>1392344.64</v>
       </c>
       <c r="P376" t="n">
         <v>5300</v>
       </c>
       <c r="Q376" t="n">
-        <v>1160700</v>
+        <v>1144800</v>
       </c>
     </row>
     <row r="377">
@@ -16705,13 +16705,13 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>229</v>
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
@@ -16840,19 +16840,19 @@
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="N386" t="n">
-        <v>1532.6290266647</v>
+        <v>1532.6290265229</v>
       </c>
       <c r="O386" t="n">
-        <v>3906671.38896832</v>
+        <v>3903606.130553826</v>
       </c>
       <c r="P386" t="n">
         <v>1200</v>
       </c>
       <c r="Q386" t="n">
-        <v>3058800</v>
+        <v>3056400</v>
       </c>
     </row>
     <row r="387">
@@ -17048,28 +17048,28 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>2345</v>
+        <v>2329</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
       </c>
       <c r="L391" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>2342</v>
+        <v>2329</v>
       </c>
       <c r="N391" t="n">
         <v>1387.55</v>
       </c>
       <c r="O391" t="n">
-        <v>3249642.1</v>
+        <v>3231603.95</v>
       </c>
       <c r="P391" t="n">
         <v>2300</v>
       </c>
       <c r="Q391" t="n">
-        <v>5386600</v>
+        <v>5356700</v>
       </c>
     </row>
     <row r="392">
@@ -18418,28 +18418,28 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9238867829</v>
+        <v>1630.9239095069</v>
       </c>
       <c r="O422" t="n">
-        <v>450134.9927520804</v>
+        <v>440349.455566863</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>690000</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="423">
@@ -18510,28 +18510,28 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1939133186</v>
+        <v>1550.1939407455</v>
       </c>
       <c r="O424" t="n">
-        <v>665033.1888136794</v>
+        <v>640230.0975278915</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1072500</v>
+        <v>1032500</v>
       </c>
     </row>
     <row r="425">
@@ -18568,10 +18568,10 @@
         <v>90</v>
       </c>
       <c r="N425" t="n">
-        <v>1579.3888161994</v>
+        <v>1579.388566879</v>
       </c>
       <c r="O425" t="n">
-        <v>142144.993457946</v>
+        <v>142144.97101911</v>
       </c>
       <c r="P425" t="n">
         <v>2900</v>
@@ -18602,28 +18602,28 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.513461205</v>
+        <v>2403.5136926808</v>
       </c>
       <c r="O426" t="n">
-        <v>1615161.04592976</v>
+        <v>1598336.605632732</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2352000</v>
+        <v>2327500</v>
       </c>
     </row>
     <row r="427">
@@ -18692,28 +18692,28 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="N428" t="n">
-        <v>2521.5026451613</v>
+        <v>2521.499109589</v>
       </c>
       <c r="O428" t="n">
-        <v>378225.396774195</v>
+        <v>355531.374452049</v>
       </c>
       <c r="P428" t="n">
         <v>3900</v>
       </c>
       <c r="Q428" t="n">
-        <v>585000</v>
+        <v>549900</v>
       </c>
     </row>
     <row r="429">
@@ -18941,7 +18941,7 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
@@ -18950,19 +18950,19 @@
         <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N434" t="n">
-        <v>1830.7552777778</v>
+        <v>1830.7551977401</v>
       </c>
       <c r="O434" t="n">
-        <v>305736.1313888926</v>
+        <v>300243.8524293764</v>
       </c>
       <c r="P434" t="n">
         <v>3150</v>
       </c>
       <c r="Q434" t="n">
-        <v>526050</v>
+        <v>516600</v>
       </c>
     </row>
     <row r="435">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -19207,19 +19207,19 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N440" t="n">
         <v>2638</v>
       </c>
       <c r="O440" t="n">
-        <v>643672</v>
+        <v>638396</v>
       </c>
       <c r="P440" t="n">
         <v>4500</v>
       </c>
       <c r="Q440" t="n">
-        <v>1098000</v>
+        <v>1089000</v>
       </c>
     </row>
     <row r="441">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -20708,19 +20708,19 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N474" t="n">
         <v>6280.31</v>
       </c>
       <c r="O474" t="n">
-        <v>12560.62</v>
+        <v>6280.31</v>
       </c>
       <c r="P474" t="n">
         <v>10500</v>
       </c>
       <c r="Q474" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="475">
@@ -22154,10 +22154,10 @@
         <v>360</v>
       </c>
       <c r="N508" t="n">
-        <v>4196.8725319267</v>
+        <v>4196.8725326298</v>
       </c>
       <c r="O508" t="n">
-        <v>1510874.111493612</v>
+        <v>1510874.111746728</v>
       </c>
       <c r="P508" t="n">
         <v>5900</v>
@@ -22978,7 +22978,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -22987,19 +22987,19 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N528" t="n">
         <v>13152</v>
       </c>
       <c r="O528" t="n">
-        <v>1394112</v>
+        <v>1380960</v>
       </c>
       <c r="P528" t="n">
         <v>16900</v>
       </c>
       <c r="Q528" t="n">
-        <v>1791400</v>
+        <v>1774500</v>
       </c>
     </row>
     <row r="529">
@@ -23019,7 +23019,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -23028,19 +23028,19 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="N529" t="n">
         <v>6652</v>
       </c>
       <c r="O529" t="n">
-        <v>4303844</v>
+        <v>4290540</v>
       </c>
       <c r="P529" t="n">
         <v>5900</v>
       </c>
       <c r="Q529" t="n">
-        <v>3817300</v>
+        <v>3805500</v>
       </c>
     </row>
     <row r="530">
@@ -23157,10 +23157,10 @@
         <v>23</v>
       </c>
       <c r="N532" t="n">
-        <v>2541.6788178138</v>
+        <v>2517.22</v>
       </c>
       <c r="O532" t="n">
-        <v>58458.6128097174</v>
+        <v>57896.06</v>
       </c>
       <c r="P532" t="n">
         <v>4200</v>
@@ -23227,7 +23227,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -23236,19 +23236,19 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N534" t="n">
-        <v>2029.8739515279</v>
+        <v>2029.873953611</v>
       </c>
       <c r="O534" t="n">
-        <v>428303.4037723869</v>
+        <v>426273.53025831</v>
       </c>
       <c r="P534" t="n">
         <v>3600</v>
       </c>
       <c r="Q534" t="n">
-        <v>759600</v>
+        <v>756000</v>
       </c>
     </row>
     <row r="535">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M547" t="n">
         <v>127</v>
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -23941,19 +23941,19 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N551" t="n">
         <v>3473</v>
       </c>
       <c r="O551" t="n">
-        <v>83352</v>
+        <v>79879</v>
       </c>
       <c r="P551" t="n">
         <v>5300</v>
       </c>
       <c r="Q551" t="n">
-        <v>127200</v>
+        <v>121900</v>
       </c>
     </row>
     <row r="552">
@@ -24067,10 +24067,10 @@
         <v>596</v>
       </c>
       <c r="N554" t="n">
-        <v>880.32956314156</v>
+        <v>880.32958602536</v>
       </c>
       <c r="O554" t="n">
-        <v>524676.4196323698</v>
+        <v>524676.4332711145</v>
       </c>
       <c r="P554" t="n">
         <v>1200</v>
@@ -24096,7 +24096,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -24105,19 +24105,19 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N555" t="n">
         <v>6773.76</v>
       </c>
       <c r="O555" t="n">
-        <v>521579.52</v>
+        <v>514805.76</v>
       </c>
       <c r="P555" t="n">
         <v>5000</v>
       </c>
       <c r="Q555" t="n">
-        <v>385000</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="556">
@@ -25320,7 +25320,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -25329,19 +25329,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N584" t="n">
         <v>3877.89</v>
       </c>
       <c r="O584" t="n">
-        <v>884158.9199999999</v>
+        <v>868647.36</v>
       </c>
       <c r="P584" t="n">
         <v>6500</v>
       </c>
       <c r="Q584" t="n">
-        <v>1482000</v>
+        <v>1456000</v>
       </c>
     </row>
     <row r="585">
@@ -25410,7 +25410,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -25419,19 +25419,19 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="N586" t="n">
-        <v>4285.1957531144</v>
+        <v>4285.1957990868</v>
       </c>
       <c r="O586" t="n">
-        <v>899891.108154024</v>
+        <v>878465.1388127941</v>
       </c>
       <c r="P586" t="n">
         <v>6900</v>
       </c>
       <c r="Q586" t="n">
-        <v>1449000</v>
+        <v>1414500</v>
       </c>
     </row>
     <row r="587">
@@ -25915,7 +25915,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -25924,19 +25924,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N598" t="n">
-        <v>4605.2147542533</v>
+        <v>4605.2147677725</v>
       </c>
       <c r="O598" t="n">
-        <v>925648.1656049134</v>
+        <v>911832.524018955</v>
       </c>
       <c r="P598" t="n">
         <v>7600</v>
       </c>
       <c r="Q598" t="n">
-        <v>1527600</v>
+        <v>1504800</v>
       </c>
     </row>
     <row r="599">
@@ -26101,10 +26101,10 @@
         <v>86</v>
       </c>
       <c r="N602" t="n">
-        <v>11562.038444444</v>
+        <v>11562.038426966</v>
       </c>
       <c r="O602" t="n">
-        <v>994335.3062221841</v>
+        <v>994335.304719076</v>
       </c>
       <c r="P602" t="n">
         <v>18500</v>
@@ -26147,10 +26147,10 @@
         <v>2</v>
       </c>
       <c r="N603" t="n">
-        <v>13513.643153846</v>
+        <v>13513.643203125</v>
       </c>
       <c r="O603" t="n">
-        <v>27027.286307692</v>
+        <v>27027.28640625</v>
       </c>
       <c r="P603" t="n">
         <v>21900</v>
@@ -26309,7 +26309,7 @@
         </is>
       </c>
       <c r="J607" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K607" t="n">
         <v>0</v>
@@ -26318,19 +26318,19 @@
         <v>0</v>
       </c>
       <c r="M607" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N607" t="n">
         <v>1650</v>
       </c>
       <c r="O607" t="n">
-        <v>651750</v>
+        <v>650100</v>
       </c>
       <c r="P607" t="n">
         <v>2900</v>
       </c>
       <c r="Q607" t="n">
-        <v>1145500</v>
+        <v>1142600</v>
       </c>
     </row>
     <row r="608">
@@ -26350,13 +26350,13 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M608" t="n">
         <v>107</v>
@@ -26391,13 +26391,13 @@
         </is>
       </c>
       <c r="J609" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K609" t="n">
         <v>0</v>
       </c>
       <c r="L609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M609" t="n">
         <v>16</v>
@@ -26719,28 +26719,28 @@
         </is>
       </c>
       <c r="J617" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="K617" t="n">
         <v>0</v>
       </c>
       <c r="L617" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M617" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="N617" t="n">
         <v>1352</v>
       </c>
       <c r="O617" t="n">
-        <v>224432</v>
+        <v>216320</v>
       </c>
       <c r="P617" t="n">
         <v>2400</v>
       </c>
       <c r="Q617" t="n">
-        <v>398400</v>
+        <v>384000</v>
       </c>
     </row>
     <row r="618">
@@ -26883,7 +26883,7 @@
         </is>
       </c>
       <c r="J621" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="K621" t="n">
         <v>0</v>
@@ -26892,19 +26892,19 @@
         <v>0</v>
       </c>
       <c r="M621" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="N621" t="n">
         <v>1647</v>
       </c>
       <c r="O621" t="n">
-        <v>502335</v>
+        <v>482571</v>
       </c>
       <c r="P621" t="n">
         <v>2900</v>
       </c>
       <c r="Q621" t="n">
-        <v>884500</v>
+        <v>849700</v>
       </c>
     </row>
     <row r="622">
@@ -28009,10 +28009,10 @@
         <v>139</v>
       </c>
       <c r="N647" t="n">
-        <v>27123.765160681</v>
+        <v>27123.765142315</v>
       </c>
       <c r="O647" t="n">
-        <v>3770203.357334659</v>
+        <v>3770203.354781785</v>
       </c>
       <c r="P647" t="n">
         <v>44500</v>
@@ -28388,10 +28388,10 @@
         <v>79</v>
       </c>
       <c r="N656" t="n">
-        <v>8332.779620253201</v>
+        <v>8332.7796143959</v>
       </c>
       <c r="O656" t="n">
-        <v>658289.5900000029</v>
+        <v>658289.5895372761</v>
       </c>
       <c r="P656" t="n">
         <v>14900</v>
@@ -28673,7 +28673,7 @@
         </is>
       </c>
       <c r="J663" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="K663" t="n">
         <v>0</v>
@@ -28682,19 +28682,19 @@
         <v>0</v>
       </c>
       <c r="M663" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N663" t="n">
-        <v>1561.0026027397</v>
+        <v>1561.0027356625</v>
       </c>
       <c r="O663" t="n">
-        <v>301273.5023287621</v>
+        <v>288785.5060975625</v>
       </c>
       <c r="P663" t="n">
         <v>2900</v>
       </c>
       <c r="Q663" t="n">
-        <v>559700</v>
+        <v>536500</v>
       </c>
     </row>
     <row r="664">
@@ -29057,7 +29057,7 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -29066,19 +29066,19 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N672" t="n">
         <v>7409</v>
       </c>
       <c r="O672" t="n">
-        <v>874262</v>
+        <v>866853</v>
       </c>
       <c r="P672" t="n">
         <v>12600</v>
       </c>
       <c r="Q672" t="n">
-        <v>1486800</v>
+        <v>1474200</v>
       </c>
     </row>
     <row r="673">
@@ -31568,22 +31568,22 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M730" t="n">
         <v>11</v>
       </c>
       <c r="N730" t="n">
-        <v>1664.3525037936</v>
+        <v>1664.3520684292</v>
       </c>
       <c r="O730" t="n">
-        <v>18307.8775417296</v>
+        <v>18307.8727527212</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
@@ -32544,10 +32544,10 @@
         <v>1233</v>
       </c>
       <c r="N751" t="n">
-        <v>1778.4726559172</v>
+        <v>1778.4726787358</v>
       </c>
       <c r="O751" t="n">
-        <v>2192856.784745907</v>
+        <v>2192856.812881242</v>
       </c>
       <c r="P751" t="n">
         <v>4900</v>
@@ -33547,7 +33547,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -33556,19 +33556,19 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="N773" t="n">
         <v>4850</v>
       </c>
       <c r="O773" t="n">
-        <v>334650</v>
+        <v>106700</v>
       </c>
       <c r="P773" t="n">
         <v>7800</v>
       </c>
       <c r="Q773" t="n">
-        <v>538200</v>
+        <v>171600</v>
       </c>
     </row>
     <row r="774">
@@ -34300,10 +34300,10 @@
         <v>1</v>
       </c>
       <c r="N789" t="n">
-        <v>26445.445</v>
+        <v>26445.446</v>
       </c>
       <c r="O789" t="n">
-        <v>26445.445</v>
+        <v>26445.446</v>
       </c>
       <c r="P789" t="n">
         <v>44900</v>
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -34849,19 +34849,19 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N801" t="n">
         <v>3764</v>
       </c>
       <c r="O801" t="n">
-        <v>425332</v>
+        <v>421568</v>
       </c>
       <c r="P801" t="n">
         <v>6200</v>
       </c>
       <c r="Q801" t="n">
-        <v>700600</v>
+        <v>694400</v>
       </c>
     </row>
     <row r="802">
@@ -34886,13 +34886,13 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
       </c>
       <c r="L802" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M802" t="n">
         <v>66</v>
@@ -34990,10 +34990,10 @@
         <v>111</v>
       </c>
       <c r="N804" t="n">
-        <v>2252.2974859551</v>
+        <v>2252.2975176305</v>
       </c>
       <c r="O804" t="n">
-        <v>250005.0209410161</v>
+        <v>250005.0244569855</v>
       </c>
       <c r="P804" t="n">
         <v>3900</v>
@@ -35211,7 +35211,7 @@
         </is>
       </c>
       <c r="J809" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
@@ -35220,19 +35220,19 @@
         <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="N809" t="n">
-        <v>2328.1186975309</v>
+        <v>2328.1186963238</v>
       </c>
       <c r="O809" t="n">
-        <v>1047653.413888905</v>
+        <v>1040669.057256739</v>
       </c>
       <c r="P809" t="n">
         <v>4500</v>
       </c>
       <c r="Q809" t="n">
-        <v>2025000</v>
+        <v>2011500</v>
       </c>
     </row>
     <row r="810">
@@ -36223,7 +36223,7 @@
         </is>
       </c>
       <c r="J831" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K831" t="n">
         <v>0</v>
@@ -36232,19 +36232,19 @@
         <v>0</v>
       </c>
       <c r="M831" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N831" t="n">
-        <v>3903.736969697</v>
+        <v>3903.7370093458</v>
       </c>
       <c r="O831" t="n">
-        <v>46844.843636364</v>
+        <v>35133.6330841122</v>
       </c>
       <c r="P831" t="n">
         <v>7500</v>
       </c>
       <c r="Q831" t="n">
-        <v>90000</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="832">
@@ -36690,10 +36690,10 @@
         <v>15</v>
       </c>
       <c r="N841" t="n">
-        <v>5869.1725975359</v>
+        <v>5869.1725823045</v>
       </c>
       <c r="O841" t="n">
-        <v>88037.58896303851</v>
+        <v>88037.5887345675</v>
       </c>
       <c r="P841" t="n">
         <v>9500</v>
@@ -36770,7 +36770,7 @@
         </is>
       </c>
       <c r="J843" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K843" t="n">
         <v>0</v>
@@ -36779,19 +36779,19 @@
         <v>0</v>
       </c>
       <c r="M843" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N843" t="n">
         <v>4984</v>
       </c>
       <c r="O843" t="n">
-        <v>104664</v>
+        <v>99680</v>
       </c>
       <c r="P843" t="n">
         <v>7900</v>
       </c>
       <c r="Q843" t="n">
-        <v>165900</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="844">
@@ -37644,7 +37644,7 @@
         </is>
       </c>
       <c r="J862" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K862" t="n">
         <v>0</v>
@@ -37653,19 +37653,19 @@
         <v>0</v>
       </c>
       <c r="M862" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N862" t="n">
         <v>10398</v>
       </c>
       <c r="O862" t="n">
-        <v>249552</v>
+        <v>239154</v>
       </c>
       <c r="P862" t="n">
         <v>16900</v>
       </c>
       <c r="Q862" t="n">
-        <v>405600</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="863">
@@ -37869,7 +37869,7 @@
         </is>
       </c>
       <c r="J867" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K867" t="n">
         <v>0</v>
@@ -37878,19 +37878,19 @@
         <v>0</v>
       </c>
       <c r="M867" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N867" t="n">
         <v>21346</v>
       </c>
       <c r="O867" t="n">
-        <v>853840</v>
+        <v>832494</v>
       </c>
       <c r="P867" t="n">
         <v>34900</v>
       </c>
       <c r="Q867" t="n">
-        <v>1396000</v>
+        <v>1361100</v>
       </c>
     </row>
     <row r="868">
@@ -39117,7 +39117,7 @@
         </is>
       </c>
       <c r="J894" t="n">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
@@ -39126,19 +39126,19 @@
         <v>0</v>
       </c>
       <c r="M894" t="n">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="N894" t="n">
-        <v>1517.8304441599</v>
+        <v>1516.0387847976</v>
       </c>
       <c r="O894" t="n">
-        <v>1948894.290301312</v>
+        <v>1943561.722110523</v>
       </c>
       <c r="P894" t="n">
         <v>2300</v>
       </c>
       <c r="Q894" t="n">
-        <v>2953200</v>
+        <v>2948600</v>
       </c>
     </row>
     <row r="895">
@@ -39311,10 +39311,10 @@
         <v>107</v>
       </c>
       <c r="N898" t="n">
-        <v>1771.0902626263</v>
+        <v>1771.090242915</v>
       </c>
       <c r="O898" t="n">
-        <v>189506.6581010141</v>
+        <v>189506.655991905</v>
       </c>
       <c r="P898" t="n">
         <v>2500</v>
@@ -39345,7 +39345,7 @@
         </is>
       </c>
       <c r="J899" t="n">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="K899" t="n">
         <v>0</v>
@@ -39354,19 +39354,19 @@
         <v>0</v>
       </c>
       <c r="M899" t="n">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="N899" t="n">
-        <v>2079.3839381583</v>
+        <v>2079.3838525155</v>
       </c>
       <c r="O899" t="n">
-        <v>648767.7887053897</v>
+        <v>563513.0240317006</v>
       </c>
       <c r="P899" t="n">
         <v>2900</v>
       </c>
       <c r="Q899" t="n">
-        <v>904800</v>
+        <v>785900</v>
       </c>
     </row>
     <row r="900">
@@ -39391,22 +39391,22 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
       </c>
       <c r="L900" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M900" t="n">
         <v>299</v>
       </c>
       <c r="N900" t="n">
-        <v>1803.0158936022</v>
+        <v>1803.0158997564</v>
       </c>
       <c r="O900" t="n">
-        <v>539101.7521870579</v>
+        <v>539101.7540271636</v>
       </c>
       <c r="P900" t="n">
         <v>2500</v>
@@ -39495,10 +39495,10 @@
         <v>59</v>
       </c>
       <c r="N902" t="n">
-        <v>2108.7933180778</v>
+        <v>2108.7936087295</v>
       </c>
       <c r="O902" t="n">
-        <v>124418.8057665902</v>
+        <v>124418.8229150405</v>
       </c>
       <c r="P902" t="n">
         <v>2900</v>
@@ -39541,10 +39541,10 @@
         <v>252</v>
       </c>
       <c r="N903" t="n">
-        <v>2056.0827781666</v>
+        <v>2056.0827629734</v>
       </c>
       <c r="O903" t="n">
-        <v>518132.8600979832</v>
+        <v>518132.8562692968</v>
       </c>
       <c r="P903" t="n">
         <v>2900</v>
@@ -39587,10 +39587,10 @@
         <v>138</v>
       </c>
       <c r="N904" t="n">
-        <v>3224.5689410589</v>
+        <v>3224.56895</v>
       </c>
       <c r="O904" t="n">
-        <v>444990.5138661282</v>
+        <v>444990.5151</v>
       </c>
       <c r="P904" t="n">
         <v>4500</v>
@@ -39621,7 +39621,7 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
@@ -39630,19 +39630,19 @@
         <v>0</v>
       </c>
       <c r="M905" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N905" t="n">
-        <v>1655.9305111492</v>
+        <v>1655.9303958333</v>
       </c>
       <c r="O905" t="n">
-        <v>349401.3378524812</v>
+        <v>347745.383124993</v>
       </c>
       <c r="P905" t="n">
         <v>2500</v>
       </c>
       <c r="Q905" t="n">
-        <v>527500</v>
+        <v>525000</v>
       </c>
     </row>
     <row r="906">
@@ -39854,22 +39854,22 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M910" t="n">
         <v>390</v>
       </c>
       <c r="N910" t="n">
-        <v>1592.2816534392</v>
+        <v>1592.2817466667</v>
       </c>
       <c r="O910" t="n">
-        <v>620989.8448412881</v>
+        <v>620989.881200013</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
@@ -39997,10 +39997,10 @@
         <v>189</v>
       </c>
       <c r="N913" t="n">
-        <v>2311.9148648649</v>
+        <v>2311.9128246753</v>
       </c>
       <c r="O913" t="n">
-        <v>436951.9094594661</v>
+        <v>436951.5238636316</v>
       </c>
       <c r="P913" t="n">
         <v>3500</v>
@@ -40089,10 +40089,10 @@
         <v>186</v>
       </c>
       <c r="N915" t="n">
-        <v>3033.7063207547</v>
+        <v>3033.7037</v>
       </c>
       <c r="O915" t="n">
-        <v>564269.3756603742</v>
+        <v>564268.8882</v>
       </c>
       <c r="P915" t="n">
         <v>4500</v>
@@ -40123,7 +40123,7 @@
         </is>
       </c>
       <c r="J916" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K916" t="n">
         <v>0</v>
@@ -40132,19 +40132,19 @@
         <v>0</v>
       </c>
       <c r="M916" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N916" t="n">
-        <v>1668.6351079137</v>
+        <v>1668.6353623188</v>
       </c>
       <c r="O916" t="n">
-        <v>337064.2917985674</v>
+        <v>333727.07246376</v>
       </c>
       <c r="P916" t="n">
         <v>2500</v>
       </c>
       <c r="Q916" t="n">
-        <v>505000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="917">
@@ -40169,7 +40169,7 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
@@ -40178,19 +40178,19 @@
         <v>0</v>
       </c>
       <c r="M917" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N917" t="n">
-        <v>2546.9828463476</v>
+        <v>2546.9826614987</v>
       </c>
       <c r="O917" t="n">
-        <v>341295.7014105784</v>
+        <v>331107.745994831</v>
       </c>
       <c r="P917" t="n">
         <v>3900</v>
       </c>
       <c r="Q917" t="n">
-        <v>522600</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="918">
@@ -40450,10 +40450,10 @@
         <v>2638</v>
       </c>
       <c r="N923" t="n">
-        <v>692.1522598039199</v>
+        <v>692.15226424361</v>
       </c>
       <c r="O923" t="n">
-        <v>1825897.661362741</v>
+        <v>1825897.673074643</v>
       </c>
       <c r="P923" t="n">
         <v>1200</v>
@@ -40635,10 +40635,10 @@
         <v>570</v>
       </c>
       <c r="N927" t="n">
-        <v>1185.31957078</v>
+        <v>1185.3195703545</v>
       </c>
       <c r="O927" t="n">
-        <v>675632.1553446</v>
+        <v>675632.1551020649</v>
       </c>
       <c r="P927" t="n">
         <v>1900</v>
@@ -41094,7 +41094,7 @@
         </is>
       </c>
       <c r="J937" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K937" t="n">
         <v>0</v>
@@ -41103,19 +41103,19 @@
         <v>0</v>
       </c>
       <c r="M937" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N937" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O937" t="n">
-        <v>3300845.22</v>
+        <v>3291899.84</v>
       </c>
       <c r="P937" t="n">
         <v>14900</v>
       </c>
       <c r="Q937" t="n">
-        <v>5498100</v>
+        <v>5483200</v>
       </c>
     </row>
     <row r="938">
@@ -41247,10 +41247,10 @@
         <v>321</v>
       </c>
       <c r="N940" t="n">
-        <v>1530.4499191266</v>
+        <v>1530.4499189299</v>
       </c>
       <c r="O940" t="n">
-        <v>491274.4240396386</v>
+        <v>491274.4239764979</v>
       </c>
       <c r="P940" t="n">
         <v>2600</v>
@@ -42267,28 +42267,28 @@
         </is>
       </c>
       <c r="J963" t="n">
-        <v>996</v>
+        <v>966</v>
       </c>
       <c r="K963" t="n">
         <v>0</v>
       </c>
       <c r="L963" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M963" t="n">
-        <v>986</v>
+        <v>966</v>
       </c>
       <c r="N963" t="n">
         <v>177.65</v>
       </c>
       <c r="O963" t="n">
-        <v>175162.9</v>
+        <v>171609.9</v>
       </c>
       <c r="P963" t="n">
         <v>300</v>
       </c>
       <c r="Q963" t="n">
-        <v>295800</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="964">
@@ -42530,22 +42530,22 @@
         </is>
       </c>
       <c r="J969" t="n">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="K969" t="n">
         <v>0</v>
       </c>
       <c r="L969" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M969" t="n">
         <v>1318</v>
       </c>
       <c r="N969" t="n">
-        <v>518.11303680169</v>
+        <v>517.29151641831</v>
       </c>
       <c r="O969" t="n">
-        <v>682872.9825046274</v>
+        <v>681790.2186393327</v>
       </c>
       <c r="P969" t="n">
         <v>900</v>
@@ -42678,10 +42678,10 @@
         <v>1</v>
       </c>
       <c r="N972" t="n">
-        <v>3259.1343700787</v>
+        <v>3259.1344047619</v>
       </c>
       <c r="O972" t="n">
-        <v>3259.1343700787</v>
+        <v>3259.1344047619</v>
       </c>
       <c r="P972" t="n">
         <v>3600</v>
@@ -42715,7 +42715,7 @@
         </is>
       </c>
       <c r="J973" t="n">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="K973" t="n">
         <v>0</v>
@@ -42724,19 +42724,19 @@
         <v>0</v>
       </c>
       <c r="M973" t="n">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="N973" t="n">
-        <v>3110.8402590245</v>
+        <v>3110.8401559454</v>
       </c>
       <c r="O973" t="n">
-        <v>4199634.349683075</v>
+        <v>4193412.530214399</v>
       </c>
       <c r="P973" t="n">
         <v>4500</v>
       </c>
       <c r="Q973" t="n">
-        <v>6075000</v>
+        <v>6066000</v>
       </c>
     </row>
     <row r="974">
@@ -42847,28 +42847,28 @@
         </is>
       </c>
       <c r="J976" t="n">
-        <v>13771</v>
+        <v>13740</v>
       </c>
       <c r="K976" t="n">
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M976" t="n">
-        <v>13764</v>
+        <v>13740</v>
       </c>
       <c r="N976" t="n">
-        <v>703.79501848956</v>
+        <v>703.79500857932</v>
       </c>
       <c r="O976" t="n">
-        <v>9687034.634490304</v>
+        <v>9670143.417879857</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>12387600</v>
+        <v>12366000</v>
       </c>
     </row>
     <row r="977">
@@ -42949,10 +42949,10 @@
         <v>45</v>
       </c>
       <c r="N978" t="n">
-        <v>3006.0209045226</v>
+        <v>3006.0209473684</v>
       </c>
       <c r="O978" t="n">
-        <v>135270.940703517</v>
+        <v>135270.942631578</v>
       </c>
       <c r="P978" t="n">
         <v>3900</v>
@@ -43602,10 +43602,10 @@
         <v>81</v>
       </c>
       <c r="N993" t="n">
-        <v>1595.5115507777</v>
+        <v>1595.5001480385</v>
       </c>
       <c r="O993" t="n">
-        <v>129236.4356129937</v>
+        <v>129235.5119911185</v>
       </c>
       <c r="P993" t="n">
         <v>2500</v>
@@ -44486,7 +44486,7 @@
         </is>
       </c>
       <c r="J1012" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K1012" t="n">
         <v>0</v>
@@ -44495,19 +44495,19 @@
         <v>0</v>
       </c>
       <c r="M1012" t="n">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N1012" t="n">
-        <v>3063.6219329897</v>
+        <v>3063.6219339866</v>
       </c>
       <c r="O1012" t="n">
-        <v>2074072.048634027</v>
+        <v>2071008.427374942</v>
       </c>
       <c r="P1012" t="n">
         <v>3500</v>
       </c>
       <c r="Q1012" t="n">
-        <v>2369500</v>
+        <v>2366000</v>
       </c>
     </row>
     <row r="1013">
@@ -47037,10 +47037,10 @@
         <v>38</v>
       </c>
       <c r="N1066" t="n">
-        <v>7046.9398275862</v>
+        <v>7046.9398275119</v>
       </c>
       <c r="O1066" t="n">
-        <v>267783.7134482756</v>
+        <v>267783.7134454522</v>
       </c>
       <c r="P1066" t="n">
         <v>9900</v>
@@ -47317,10 +47317,10 @@
         <v>16</v>
       </c>
       <c r="N1072" t="n">
-        <v>665.32370265152</v>
+        <v>665.32371673004</v>
       </c>
       <c r="O1072" t="n">
-        <v>10645.17924242432</v>
+        <v>10645.17946768064</v>
       </c>
       <c r="P1072" t="n">
         <v>2900</v>
@@ -47591,7 +47591,7 @@
         </is>
       </c>
       <c r="J1078" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K1078" t="n">
         <v>0</v>
@@ -47600,19 +47600,19 @@
         <v>0</v>
       </c>
       <c r="M1078" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N1078" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1078" t="n">
-        <v>1232514.96</v>
+        <v>1223351.28</v>
       </c>
       <c r="P1078" t="n">
         <v>7900</v>
       </c>
       <c r="Q1078" t="n">
-        <v>2125100</v>
+        <v>2109300</v>
       </c>
     </row>
     <row r="1079">
@@ -47640,7 +47640,7 @@
         </is>
       </c>
       <c r="J1079" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K1079" t="n">
         <v>0</v>
@@ -47649,19 +47649,19 @@
         <v>0</v>
       </c>
       <c r="M1079" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N1079" t="n">
         <v>3155</v>
       </c>
       <c r="O1079" t="n">
-        <v>1198900</v>
+        <v>1195745</v>
       </c>
       <c r="P1079" t="n">
         <v>5900</v>
       </c>
       <c r="Q1079" t="n">
-        <v>2242000</v>
+        <v>2236100</v>
       </c>
     </row>
     <row r="1080">
@@ -47738,7 +47738,7 @@
         </is>
       </c>
       <c r="J1081" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K1081" t="n">
         <v>0</v>
@@ -47747,19 +47747,19 @@
         <v>0</v>
       </c>
       <c r="M1081" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N1081" t="n">
-        <v>465.87095916429</v>
+        <v>465.87096374046</v>
       </c>
       <c r="O1081" t="n">
-        <v>75005.22442545069</v>
+        <v>73141.74130725222</v>
       </c>
       <c r="P1081" t="n">
         <v>2500</v>
       </c>
       <c r="Q1081" t="n">
-        <v>402500</v>
+        <v>392500</v>
       </c>
     </row>
     <row r="1082">
@@ -47910,13 +47910,13 @@
         </is>
       </c>
       <c r="J1085" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K1085" t="n">
         <v>0</v>
       </c>
       <c r="L1085" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1085" t="n">
         <v>456</v>
@@ -49021,28 +49021,28 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>1493</v>
+        <v>1463</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1111" t="n">
-        <v>1487</v>
+        <v>1463</v>
       </c>
       <c r="N1111" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1111" t="n">
-        <v>1749559.59</v>
+        <v>1721321.91</v>
       </c>
       <c r="P1111" t="n">
         <v>1900</v>
       </c>
       <c r="Q1111" t="n">
-        <v>2825300</v>
+        <v>2779700</v>
       </c>
     </row>
     <row r="1112">
@@ -49109,13 +49109,13 @@
         </is>
       </c>
       <c r="J1113" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K1113" t="n">
         <v>0</v>
       </c>
       <c r="L1113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1113" t="n">
         <v>59</v>
@@ -49247,10 +49247,10 @@
         <v>1219</v>
       </c>
       <c r="N1116" t="n">
-        <v>1794.287966297</v>
+        <v>1794.287966004</v>
       </c>
       <c r="O1116" t="n">
-        <v>2187237.030916043</v>
+        <v>2187237.030558876</v>
       </c>
       <c r="P1116" t="n">
         <v>1600</v>
@@ -50076,10 +50076,10 @@
         <v>380</v>
       </c>
       <c r="N1135" t="n">
-        <v>22951.704785992</v>
+        <v>22951.704779221</v>
       </c>
       <c r="O1135" t="n">
-        <v>8721647.81867696</v>
+        <v>8721647.81610398</v>
       </c>
       <c r="P1135" t="n">
         <v>37900</v>
@@ -50934,10 +50934,10 @@
         <v>3</v>
       </c>
       <c r="N1154" t="n">
-        <v>9855.0381481481</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="O1154" t="n">
-        <v>29565.1144444443</v>
+        <v>29565.1142307693</v>
       </c>
       <c r="P1154" t="n">
         <v>15500</v>
@@ -51290,7 +51290,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51299,19 +51299,19 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N1162" t="n">
         <v>7480</v>
       </c>
       <c r="O1162" t="n">
-        <v>52360</v>
+        <v>29920</v>
       </c>
       <c r="P1162" t="n">
         <v>9500</v>
       </c>
       <c r="Q1162" t="n">
-        <v>66500</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="1163">
@@ -51336,7 +51336,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51345,19 +51345,19 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N1163" t="n">
         <v>5280</v>
       </c>
       <c r="O1163" t="n">
-        <v>89760</v>
+        <v>84480</v>
       </c>
       <c r="P1163" t="n">
         <v>6900</v>
       </c>
       <c r="Q1163" t="n">
-        <v>117300</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="1164">
@@ -51382,28 +51382,28 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N1164" t="n">
         <v>3872</v>
       </c>
       <c r="O1164" t="n">
-        <v>387200</v>
+        <v>371712</v>
       </c>
       <c r="P1164" t="n">
         <v>4900</v>
       </c>
       <c r="Q1164" t="n">
-        <v>490000</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="1165">
@@ -51428,28 +51428,28 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
       </c>
       <c r="L1165" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N1165" t="n">
         <v>6160</v>
       </c>
       <c r="O1165" t="n">
-        <v>172480</v>
+        <v>147840</v>
       </c>
       <c r="P1165" t="n">
         <v>7900</v>
       </c>
       <c r="Q1165" t="n">
-        <v>221200</v>
+        <v>189600</v>
       </c>
     </row>
     <row r="1166">
@@ -51474,7 +51474,7 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -51483,19 +51483,19 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="N1166" t="n">
         <v>4400</v>
       </c>
       <c r="O1166" t="n">
-        <v>396000</v>
+        <v>365200</v>
       </c>
       <c r="P1166" t="n">
         <v>5900</v>
       </c>
       <c r="Q1166" t="n">
-        <v>531000</v>
+        <v>489700</v>
       </c>
     </row>
     <row r="1167">
@@ -51520,7 +51520,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51529,19 +51529,19 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N1167" t="n">
-        <v>3571.512195122</v>
+        <v>3520</v>
       </c>
       <c r="O1167" t="n">
-        <v>178575.6097561</v>
+        <v>151360</v>
       </c>
       <c r="P1167" t="n">
         <v>4500</v>
       </c>
       <c r="Q1167" t="n">
-        <v>225000</v>
+        <v>193500</v>
       </c>
     </row>
     <row r="1168">
@@ -51612,28 +51612,28 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N1169" t="n">
         <v>9240</v>
       </c>
       <c r="O1169" t="n">
-        <v>295680</v>
+        <v>267960</v>
       </c>
       <c r="P1169" t="n">
         <v>11500</v>
       </c>
       <c r="Q1169" t="n">
-        <v>368000</v>
+        <v>333500</v>
       </c>
     </row>
     <row r="1170">
@@ -51704,28 +51704,28 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N1171" t="n">
         <v>4576</v>
       </c>
       <c r="O1171" t="n">
-        <v>640640</v>
+        <v>631488</v>
       </c>
       <c r="P1171" t="n">
         <v>5900</v>
       </c>
       <c r="Q1171" t="n">
-        <v>826000</v>
+        <v>814200</v>
       </c>
     </row>
     <row r="1172">
@@ -51750,13 +51750,13 @@
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
       </c>
       <c r="L1172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1172" t="n">
         <v>51</v>
@@ -52348,7 +52348,7 @@
         </is>
       </c>
       <c r="J1185" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K1185" t="n">
         <v>0</v>
@@ -52357,19 +52357,19 @@
         <v>0</v>
       </c>
       <c r="M1185" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="N1185" t="n">
         <v>2700</v>
       </c>
       <c r="O1185" t="n">
-        <v>175500</v>
+        <v>153900</v>
       </c>
       <c r="P1185" t="n">
         <v>3300</v>
       </c>
       <c r="Q1185" t="n">
-        <v>214500</v>
+        <v>188100</v>
       </c>
     </row>
     <row r="1186">
@@ -53385,10 +53385,10 @@
         <v>305</v>
       </c>
       <c r="N1207" t="n">
-        <v>2539.5715935542</v>
+        <v>2539.5715978456</v>
       </c>
       <c r="O1207" t="n">
-        <v>774569.3360340309</v>
+        <v>774569.337342908</v>
       </c>
       <c r="P1207" t="n">
         <v>3500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -11985,22 +11985,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M275" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O275" t="n">
-        <v>2218157.486975944</v>
+        <v>2202663.948712542</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>3865500</v>
+        <v>3838500</v>
       </c>
     </row>
     <row r="276">
@@ -12548,22 +12548,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M288" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="N288" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O288" t="n">
-        <v>864365.5935</v>
+        <v>852840.7221665058</v>
       </c>
       <c r="P288" t="n">
         <v>6900</v>
       </c>
       <c r="Q288" t="n">
-        <v>1552500</v>
+        <v>1531800</v>
       </c>
     </row>
     <row r="289">
@@ -15028,22 +15028,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M344" t="n">
-        <v>6311</v>
+        <v>6308</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>13195354.35</v>
+        <v>13189081.8</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>18301900</v>
+        <v>18293200</v>
       </c>
     </row>
     <row r="345">
@@ -16616,22 +16616,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M381" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N381" t="n">
         <v>5633.97</v>
       </c>
       <c r="O381" t="n">
-        <v>366208.05</v>
+        <v>349306.14</v>
       </c>
       <c r="P381" t="n">
         <v>9600</v>
       </c>
       <c r="Q381" t="n">
-        <v>624000</v>
+        <v>595200</v>
       </c>
     </row>
     <row r="382">
@@ -18424,22 +18424,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M422" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O422" t="n">
-        <v>440349.455566863</v>
+        <v>430563.9136863504</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>675000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="423">
@@ -18608,22 +18608,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M426" t="n">
-        <v>665</v>
+        <v>650</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O426" t="n">
-        <v>1598336.605632732</v>
+        <v>1562283.92977215</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2327500</v>
+        <v>2275000</v>
       </c>
     </row>
     <row r="427">
@@ -18698,22 +18698,22 @@
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M428" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N428" t="n">
-        <v>2521.499109589</v>
+        <v>2521.4955797101</v>
       </c>
       <c r="O428" t="n">
-        <v>355531.374452049</v>
+        <v>335358.9121014433</v>
       </c>
       <c r="P428" t="n">
         <v>3900</v>
       </c>
       <c r="Q428" t="n">
-        <v>549900</v>
+        <v>518700</v>
       </c>
     </row>
     <row r="429">
@@ -31574,22 +31574,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M730" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N730" t="n">
-        <v>1664.3520684292</v>
+        <v>1664.351984375</v>
       </c>
       <c r="O730" t="n">
-        <v>18307.8727527212</v>
+        <v>13314.815875</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
       </c>
       <c r="Q730" t="n">
-        <v>31900</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="731">
@@ -31756,22 +31756,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M734" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N734" t="n">
         <v>10161</v>
       </c>
       <c r="O734" t="n">
-        <v>528372</v>
+        <v>487728</v>
       </c>
       <c r="P734" t="n">
         <v>16900</v>
       </c>
       <c r="Q734" t="n">
-        <v>878800</v>
+        <v>811200</v>
       </c>
     </row>
     <row r="735">
@@ -34616,22 +34616,22 @@
         <v>0</v>
       </c>
       <c r="L796" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M796" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N796" t="n">
         <v>24847</v>
       </c>
       <c r="O796" t="n">
-        <v>422399</v>
+        <v>397552</v>
       </c>
       <c r="P796" t="n">
         <v>39900</v>
       </c>
       <c r="Q796" t="n">
-        <v>678300</v>
+        <v>638400</v>
       </c>
     </row>
     <row r="797">
@@ -34846,22 +34846,22 @@
         <v>0</v>
       </c>
       <c r="L801" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M801" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="N801" t="n">
         <v>3764</v>
       </c>
       <c r="O801" t="n">
-        <v>421568</v>
+        <v>361344</v>
       </c>
       <c r="P801" t="n">
         <v>6200</v>
       </c>
       <c r="Q801" t="n">
-        <v>694400</v>
+        <v>595200</v>
       </c>
     </row>
     <row r="802">
@@ -36546,22 +36546,22 @@
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M838" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N838" t="n">
         <v>11922</v>
       </c>
       <c r="O838" t="n">
-        <v>166908</v>
+        <v>131142</v>
       </c>
       <c r="P838" t="n">
         <v>19900</v>
       </c>
       <c r="Q838" t="n">
-        <v>278600</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="839">
@@ -37328,22 +37328,22 @@
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M855" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N855" t="n">
         <v>8806</v>
       </c>
       <c r="O855" t="n">
-        <v>739704</v>
+        <v>704480</v>
       </c>
       <c r="P855" t="n">
         <v>14900</v>
       </c>
       <c r="Q855" t="n">
-        <v>1251600</v>
+        <v>1192000</v>
       </c>
     </row>
     <row r="856">
@@ -38154,22 +38154,22 @@
         <v>0</v>
       </c>
       <c r="L873" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M873" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N873" t="n">
         <v>10659</v>
       </c>
       <c r="O873" t="n">
-        <v>298452</v>
+        <v>255816</v>
       </c>
       <c r="P873" t="n">
         <v>17900</v>
       </c>
       <c r="Q873" t="n">
-        <v>501200</v>
+        <v>429600</v>
       </c>
     </row>
     <row r="874">
@@ -39860,22 +39860,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M910" t="n">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N910" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O910" t="n">
-        <v>620989.881200013</v>
+        <v>616213.054216854</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
       </c>
       <c r="Q910" t="n">
-        <v>975000</v>
+        <v>967500</v>
       </c>
     </row>
     <row r="911">
@@ -40083,22 +40083,22 @@
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M915" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="N915" t="n">
-        <v>3033.7037</v>
+        <v>3033.7022680412</v>
       </c>
       <c r="O915" t="n">
-        <v>564268.8882</v>
+        <v>546066.408247416</v>
       </c>
       <c r="P915" t="n">
         <v>4500</v>
       </c>
       <c r="Q915" t="n">
-        <v>837000</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="916">
@@ -40354,22 +40354,22 @@
         <v>0</v>
       </c>
       <c r="L921" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M921" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N921" t="n">
         <v>14003</v>
       </c>
       <c r="O921" t="n">
-        <v>630135</v>
+        <v>588126</v>
       </c>
       <c r="P921" t="n">
         <v>22500</v>
       </c>
       <c r="Q921" t="n">
-        <v>1012500</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="922">
@@ -42273,22 +42273,22 @@
         <v>0</v>
       </c>
       <c r="L963" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M963" t="n">
-        <v>966</v>
+        <v>916</v>
       </c>
       <c r="N963" t="n">
         <v>177.65</v>
       </c>
       <c r="O963" t="n">
-        <v>171609.9</v>
+        <v>162727.4</v>
       </c>
       <c r="P963" t="n">
         <v>300</v>
       </c>
       <c r="Q963" t="n">
-        <v>289800</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="964">
@@ -42853,22 +42853,22 @@
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M976" t="n">
-        <v>13740</v>
+        <v>13729</v>
       </c>
       <c r="N976" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O976" t="n">
-        <v>9670143.417879857</v>
+        <v>9662401.663411599</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>12366000</v>
+        <v>12356100</v>
       </c>
     </row>
     <row r="977">
@@ -44921,22 +44921,22 @@
         <v>0</v>
       </c>
       <c r="L1021" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1021" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N1021" t="n">
         <v>11229.38</v>
       </c>
       <c r="O1021" t="n">
-        <v>123523.18</v>
+        <v>101064.42</v>
       </c>
       <c r="P1021" t="n">
         <v>23900</v>
       </c>
       <c r="Q1021" t="n">
-        <v>262900</v>
+        <v>215100</v>
       </c>
     </row>
     <row r="1022">
@@ -51618,22 +51618,22 @@
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1169" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N1169" t="n">
         <v>9240</v>
       </c>
       <c r="O1169" t="n">
-        <v>267960</v>
+        <v>212520</v>
       </c>
       <c r="P1169" t="n">
         <v>11500</v>
       </c>
       <c r="Q1169" t="n">
-        <v>333500</v>
+        <v>264500</v>
       </c>
     </row>
     <row r="1170">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-05</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1036,10 +1036,10 @@
         <v>42</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.3079710145</v>
+        <v>1811.3080365297</v>
       </c>
       <c r="O15" t="n">
-        <v>76074.93478260899</v>
+        <v>76074.93753424741</v>
       </c>
       <c r="P15" t="n">
         <v>2600</v>
@@ -1197,10 +1197,10 @@
         <v>1140</v>
       </c>
       <c r="N19" t="n">
-        <v>3376.7464515243</v>
+        <v>3376.746444689</v>
       </c>
       <c r="O19" t="n">
-        <v>3849490.954737702</v>
+        <v>3849490.94694546</v>
       </c>
       <c r="P19" t="n">
         <v>4500</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2580,19 +2580,19 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N53" t="n">
-        <v>1933.3881018519</v>
+        <v>1933.3882159624</v>
       </c>
       <c r="O53" t="n">
-        <v>94736.0169907431</v>
+        <v>88935.8579342704</v>
       </c>
       <c r="P53" t="n">
         <v>4500</v>
       </c>
       <c r="Q53" t="n">
-        <v>220500</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="54">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2736,19 +2736,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="N57" t="n">
-        <v>6272.8549913345</v>
+        <v>6272.8550437828</v>
       </c>
       <c r="O57" t="n">
-        <v>163094.229774697</v>
+        <v>125457.100875656</v>
       </c>
       <c r="P57" t="n">
         <v>7900</v>
       </c>
       <c r="Q57" t="n">
-        <v>205400</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="58">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3181,19 +3181,19 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N68" t="n">
         <v>3526.1</v>
       </c>
       <c r="O68" t="n">
-        <v>232722.6</v>
+        <v>229196.5</v>
       </c>
       <c r="P68" t="n">
         <v>6300</v>
       </c>
       <c r="Q68" t="n">
-        <v>415800</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="69">
@@ -4040,10 +4040,10 @@
         <v>25</v>
       </c>
       <c r="N89" t="n">
-        <v>3910.6280306346</v>
+        <v>3910.6280263158</v>
       </c>
       <c r="O89" t="n">
-        <v>97765.700765865</v>
+        <v>97765.70065789499</v>
       </c>
       <c r="P89" t="n">
         <v>9100</v>
@@ -4132,10 +4132,10 @@
         <v>2</v>
       </c>
       <c r="N91" t="n">
-        <v>29000</v>
+        <v>30074.074074074</v>
       </c>
       <c r="O91" t="n">
-        <v>58000</v>
+        <v>60148.148148148</v>
       </c>
       <c r="P91" t="n">
         <v>34800</v>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -6138,19 +6138,19 @@
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N138" t="n">
-        <v>80027.72500000001</v>
+        <v>80027.71666666699</v>
       </c>
       <c r="O138" t="n">
-        <v>320110.9</v>
+        <v>240083.150000001</v>
       </c>
       <c r="P138" t="n">
         <v>129900</v>
       </c>
       <c r="Q138" t="n">
-        <v>519600</v>
+        <v>389700</v>
       </c>
     </row>
     <row r="139">
@@ -6329,10 +6329,10 @@
         <v>15</v>
       </c>
       <c r="N142" t="n">
-        <v>141416.88457516</v>
+        <v>141416.88459016</v>
       </c>
       <c r="O142" t="n">
-        <v>2121253.2686274</v>
+        <v>2121253.2688524</v>
       </c>
       <c r="P142" t="n">
         <v>251900</v>
@@ -6371,10 +6371,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>200072.20172727</v>
+        <v>200072.20183486</v>
       </c>
       <c r="O143" t="n">
-        <v>200072.20172727</v>
+        <v>200072.20183486</v>
       </c>
       <c r="P143" t="n">
         <v>312000</v>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6410,19 +6410,19 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N144" t="n">
-        <v>174389.79826087</v>
+        <v>174389.79954545</v>
       </c>
       <c r="O144" t="n">
-        <v>1046338.78956522</v>
+        <v>871948.99772725</v>
       </c>
       <c r="P144" t="n">
         <v>368200</v>
       </c>
       <c r="Q144" t="n">
-        <v>2209200</v>
+        <v>1841000</v>
       </c>
     </row>
     <row r="145">
@@ -7027,10 +7027,10 @@
         <v>80</v>
       </c>
       <c r="N159" t="n">
-        <v>61666.874114441</v>
+        <v>61666.874148352</v>
       </c>
       <c r="O159" t="n">
-        <v>4933349.92915528</v>
+        <v>4933349.93186816</v>
       </c>
       <c r="P159" t="n">
         <v>98900</v>
@@ -7812,10 +7812,10 @@
         <v>73</v>
       </c>
       <c r="N177" t="n">
-        <v>6303.1779245283</v>
+        <v>6303.1779047619</v>
       </c>
       <c r="O177" t="n">
-        <v>460131.9884905659</v>
+        <v>460131.9870476187</v>
       </c>
       <c r="P177" t="n">
         <v>13500</v>
@@ -9258,10 +9258,10 @@
         <v>44</v>
       </c>
       <c r="N211" t="n">
-        <v>732.63425531915</v>
+        <v>732.63427046263</v>
       </c>
       <c r="O211" t="n">
-        <v>32235.9072340426</v>
+        <v>32235.90790035572</v>
       </c>
       <c r="P211" t="n">
         <v>6200</v>
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9567,19 +9567,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="N218" t="n">
         <v>2833</v>
       </c>
       <c r="O218" t="n">
-        <v>1781957</v>
+        <v>1776291</v>
       </c>
       <c r="P218" t="n">
         <v>3500</v>
       </c>
       <c r="Q218" t="n">
-        <v>2201500</v>
+        <v>2194500</v>
       </c>
     </row>
     <row r="219">
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>9166</v>
+        <v>9152</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -9649,19 +9649,19 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>9166</v>
+        <v>9152</v>
       </c>
       <c r="N220" t="n">
         <v>1726.32</v>
       </c>
       <c r="O220" t="n">
-        <v>15823449.12</v>
+        <v>15799280.64</v>
       </c>
       <c r="P220" t="n">
         <v>1500</v>
       </c>
       <c r="Q220" t="n">
-        <v>13749000</v>
+        <v>13728000</v>
       </c>
     </row>
     <row r="221">
@@ -9739,10 +9739,10 @@
         <v>204</v>
       </c>
       <c r="N222" t="n">
-        <v>4937.3101649175</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O222" t="n">
-        <v>1007211.27364317</v>
+        <v>1007211.273744354</v>
       </c>
       <c r="P222" t="n">
         <v>7500</v>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -9992,19 +9992,19 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N228" t="n">
         <v>3775.99</v>
       </c>
       <c r="O228" t="n">
-        <v>64191.82999999999</v>
+        <v>60415.84</v>
       </c>
       <c r="P228" t="n">
         <v>7300</v>
       </c>
       <c r="Q228" t="n">
-        <v>124100</v>
+        <v>116800</v>
       </c>
     </row>
     <row r="229">
@@ -10077,10 +10077,10 @@
         <v>107</v>
       </c>
       <c r="N230" t="n">
-        <v>1946.3308510638</v>
+        <v>1946.3308648649</v>
       </c>
       <c r="O230" t="n">
-        <v>208257.4010638266</v>
+        <v>208257.4025405443</v>
       </c>
       <c r="P230" t="n">
         <v>3500</v>
@@ -10106,7 +10106,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -10115,19 +10115,19 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N231" t="n">
         <v>14233.54</v>
       </c>
       <c r="O231" t="n">
-        <v>640509.3</v>
+        <v>626275.76</v>
       </c>
       <c r="P231" t="n">
         <v>10000</v>
       </c>
       <c r="Q231" t="n">
-        <v>450000</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="232">
@@ -10203,10 +10203,10 @@
         <v>910</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0622084592</v>
+        <v>1098.0624184202</v>
       </c>
       <c r="O233" t="n">
-        <v>999236.6096978721</v>
+        <v>999236.800762382</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
@@ -11120,19 +11120,19 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N255" t="n">
         <v>2189</v>
       </c>
       <c r="O255" t="n">
-        <v>577896</v>
+        <v>573518</v>
       </c>
       <c r="P255" t="n">
         <v>4500</v>
       </c>
       <c r="Q255" t="n">
-        <v>1188000</v>
+        <v>1179000</v>
       </c>
     </row>
     <row r="256">
@@ -11466,10 +11466,10 @@
         <v>280</v>
       </c>
       <c r="N263" t="n">
-        <v>17207.41</v>
+        <v>17234.854035088</v>
       </c>
       <c r="O263" t="n">
-        <v>4818074.8</v>
+        <v>4825759.12982464</v>
       </c>
       <c r="P263" t="n">
         <v>20000</v>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="J270" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11755,19 +11755,19 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N270" t="n">
         <v>1194.83</v>
       </c>
       <c r="O270" t="n">
-        <v>28675.92</v>
+        <v>26286.26</v>
       </c>
       <c r="P270" t="n">
         <v>2500</v>
       </c>
       <c r="Q270" t="n">
-        <v>60000</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="271">
@@ -11979,28 +11979,28 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2555084555</v>
+        <v>2582.2554768392</v>
       </c>
       <c r="O275" t="n">
-        <v>2202663.948712542</v>
+        <v>2158765.578637571</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>3838500</v>
+        <v>3762000</v>
       </c>
     </row>
     <row r="276">
@@ -12037,10 +12037,10 @@
         <v>1383</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960524399</v>
+        <v>5216.8960380117</v>
       </c>
       <c r="O276" t="n">
-        <v>7214967.240524381</v>
+        <v>7214967.220570181</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12170,10 +12170,10 @@
         <v>88</v>
       </c>
       <c r="N279" t="n">
-        <v>2033.5241860465</v>
+        <v>2033.522992126</v>
       </c>
       <c r="O279" t="n">
-        <v>178950.128372092</v>
+        <v>178950.023307088</v>
       </c>
       <c r="P279" t="n">
         <v>4100</v>
@@ -12404,7 +12404,7 @@
         </is>
       </c>
       <c r="J285" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K285" t="n">
         <v>0</v>
@@ -12413,19 +12413,19 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N285" t="n">
         <v>6713.08</v>
       </c>
       <c r="O285" t="n">
-        <v>335654</v>
+        <v>322227.84</v>
       </c>
       <c r="P285" t="n">
         <v>9900</v>
       </c>
       <c r="Q285" t="n">
-        <v>495000</v>
+        <v>475200</v>
       </c>
     </row>
     <row r="286">
@@ -12462,10 +12462,10 @@
         <v>2829</v>
       </c>
       <c r="N286" t="n">
-        <v>3158.8608305026</v>
+        <v>3158.860831485</v>
       </c>
       <c r="O286" t="n">
-        <v>8936417.289491855</v>
+        <v>8936417.292271065</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
@@ -12542,13 +12542,13 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
         <v>222</v>
@@ -12956,10 +12956,10 @@
         <v>32</v>
       </c>
       <c r="N297" t="n">
-        <v>2694.8231638418</v>
+        <v>2694.8231444759</v>
       </c>
       <c r="O297" t="n">
-        <v>86234.3412429376</v>
+        <v>86234.3406232288</v>
       </c>
       <c r="P297" t="n">
         <v>4900</v>
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13135,19 +13135,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N301" t="n">
         <v>9664</v>
       </c>
       <c r="O301" t="n">
-        <v>289920</v>
+        <v>280256</v>
       </c>
       <c r="P301" t="n">
         <v>15900</v>
       </c>
       <c r="Q301" t="n">
-        <v>477000</v>
+        <v>461100</v>
       </c>
     </row>
     <row r="302">
@@ -13187,10 +13187,10 @@
         <v>326</v>
       </c>
       <c r="N302" t="n">
-        <v>8796</v>
+        <v>8807.6968085106</v>
       </c>
       <c r="O302" t="n">
-        <v>2867496</v>
+        <v>2871309.159574456</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
@@ -13407,10 +13407,10 @@
         <v>468</v>
       </c>
       <c r="N307" t="n">
-        <v>3795.7100075887</v>
+        <v>3795.7100075916</v>
       </c>
       <c r="O307" t="n">
-        <v>1776392.283551512</v>
+        <v>1776392.283552869</v>
       </c>
       <c r="P307" t="n">
         <v>6200</v>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13532,19 +13532,19 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N310" t="n">
         <v>7939.23</v>
       </c>
       <c r="O310" t="n">
-        <v>1238519.88</v>
+        <v>1230580.65</v>
       </c>
       <c r="P310" t="n">
         <v>14900</v>
       </c>
       <c r="Q310" t="n">
-        <v>2324400</v>
+        <v>2309500</v>
       </c>
     </row>
     <row r="311">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="J313" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -13660,19 +13660,19 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N313" t="n">
         <v>4357.55</v>
       </c>
       <c r="O313" t="n">
-        <v>1655869</v>
+        <v>1651511.45</v>
       </c>
       <c r="P313" t="n">
         <v>7500</v>
       </c>
       <c r="Q313" t="n">
-        <v>2850000</v>
+        <v>2842500</v>
       </c>
     </row>
     <row r="314">
@@ -13796,10 +13796,10 @@
         <v>306</v>
       </c>
       <c r="N316" t="n">
-        <v>4890.9300493827</v>
+        <v>4890.930049597</v>
       </c>
       <c r="O316" t="n">
-        <v>1496624.595111106</v>
+        <v>1496624.595176682</v>
       </c>
       <c r="P316" t="n">
         <v>8200</v>
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -13888,19 +13888,19 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="N318" t="n">
         <v>1203.38</v>
       </c>
       <c r="O318" t="n">
-        <v>693146.8800000001</v>
+        <v>681113.0800000001</v>
       </c>
       <c r="P318" t="n">
         <v>1900</v>
       </c>
       <c r="Q318" t="n">
-        <v>1094400</v>
+        <v>1075400</v>
       </c>
     </row>
     <row r="319">
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
@@ -13934,19 +13934,19 @@
         <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N319" t="n">
         <v>3472</v>
       </c>
       <c r="O319" t="n">
-        <v>434000</v>
+        <v>430528</v>
       </c>
       <c r="P319" t="n">
         <v>4800</v>
       </c>
       <c r="Q319" t="n">
-        <v>600000</v>
+        <v>595200</v>
       </c>
     </row>
     <row r="320">
@@ -13983,10 +13983,10 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>5888</v>
+        <v>5946.1052631579</v>
       </c>
       <c r="O320" t="n">
-        <v>5888</v>
+        <v>5946.1052631579</v>
       </c>
       <c r="P320" t="n">
         <v>9500</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="J332" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -14502,19 +14502,19 @@
         <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="N332" t="n">
         <v>1789</v>
       </c>
       <c r="O332" t="n">
-        <v>1381108</v>
+        <v>1379319</v>
       </c>
       <c r="P332" t="n">
         <v>2700</v>
       </c>
       <c r="Q332" t="n">
-        <v>2084400</v>
+        <v>2081700</v>
       </c>
     </row>
     <row r="333">
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -14592,19 +14592,19 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2536883629</v>
+        <v>3594.253608522</v>
       </c>
       <c r="O334" t="n">
-        <v>1293931.327810644</v>
+        <v>1286742.791850876</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
       </c>
       <c r="Q334" t="n">
-        <v>2340000</v>
+        <v>2327000</v>
       </c>
     </row>
     <row r="335">
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -14641,19 +14641,19 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="N335" t="n">
         <v>489.88</v>
       </c>
       <c r="O335" t="n">
-        <v>232693</v>
+        <v>230243.6</v>
       </c>
       <c r="P335" t="n">
         <v>700</v>
       </c>
       <c r="Q335" t="n">
-        <v>332500</v>
+        <v>329000</v>
       </c>
     </row>
     <row r="336">
@@ -14767,10 +14767,10 @@
         <v>1</v>
       </c>
       <c r="N338" t="n">
-        <v>3240.8500375235</v>
+        <v>3240.8500395257</v>
       </c>
       <c r="O338" t="n">
-        <v>3240.8500375235</v>
+        <v>3240.8500395257</v>
       </c>
       <c r="P338" t="n">
         <v>5200</v>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -14856,19 +14856,19 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N340" t="n">
         <v>8154</v>
       </c>
       <c r="O340" t="n">
-        <v>244620</v>
+        <v>236466</v>
       </c>
       <c r="P340" t="n">
         <v>13500</v>
       </c>
       <c r="Q340" t="n">
-        <v>405000</v>
+        <v>391500</v>
       </c>
     </row>
     <row r="341">
@@ -14905,10 +14905,10 @@
         <v>286</v>
       </c>
       <c r="N341" t="n">
-        <v>14822.378847539</v>
+        <v>14822.378837068</v>
       </c>
       <c r="O341" t="n">
-        <v>4239200.350396154</v>
+        <v>4239200.347401448</v>
       </c>
       <c r="P341" t="n">
         <v>24900</v>
@@ -15022,28 +15022,28 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>6311</v>
+        <v>6276</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>6308</v>
+        <v>6276</v>
       </c>
       <c r="N344" t="n">
         <v>2090.85</v>
       </c>
       <c r="O344" t="n">
-        <v>13189081.8</v>
+        <v>13122174.6</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>18293200</v>
+        <v>18200400</v>
       </c>
     </row>
     <row r="345">
@@ -15333,10 +15333,10 @@
         <v>1</v>
       </c>
       <c r="N351" t="n">
-        <v>2665.4</v>
+        <v>2667.0463248919</v>
       </c>
       <c r="O351" t="n">
-        <v>2665.4</v>
+        <v>2667.0463248919</v>
       </c>
       <c r="P351" t="n">
         <v>20900</v>
@@ -15571,7 +15571,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15580,19 +15580,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="N357" t="n">
         <v>1441.01</v>
       </c>
       <c r="O357" t="n">
-        <v>3905137.1</v>
+        <v>3899373.06</v>
       </c>
       <c r="P357" t="n">
         <v>2100</v>
       </c>
       <c r="Q357" t="n">
-        <v>5691000</v>
+        <v>5682600</v>
       </c>
     </row>
     <row r="358">
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15850,19 +15850,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="N363" t="n">
-        <v>3041.6600136054</v>
+        <v>3041.6600136893</v>
       </c>
       <c r="O363" t="n">
-        <v>316332.6414149616</v>
+        <v>288957.7013004835</v>
       </c>
       <c r="P363" t="n">
         <v>5500</v>
       </c>
       <c r="Q363" t="n">
-        <v>572000</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="364">
@@ -15882,7 +15882,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -15891,19 +15891,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="N364" t="n">
         <v>3981.47</v>
       </c>
       <c r="O364" t="n">
-        <v>509628.16</v>
+        <v>485739.34</v>
       </c>
       <c r="P364" t="n">
         <v>7000</v>
       </c>
       <c r="Q364" t="n">
-        <v>896000</v>
+        <v>854000</v>
       </c>
     </row>
     <row r="365">
@@ -15940,10 +15940,10 @@
         <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4372.2107921642</v>
+        <v>4372.5234503719</v>
       </c>
       <c r="O365" t="n">
-        <v>35515468.2647498</v>
+        <v>35518007.98737095</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16109,19 +16109,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="N369" t="n">
-        <v>1592.5661309524</v>
+        <v>1592.5660665658</v>
       </c>
       <c r="O369" t="n">
-        <v>574916.3732738164</v>
+        <v>565360.953630859</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
       </c>
       <c r="Q369" t="n">
-        <v>1407900</v>
+        <v>1384500</v>
       </c>
     </row>
     <row r="370">
@@ -16610,13 +16610,13 @@
         </is>
       </c>
       <c r="J381" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M381" t="n">
         <v>62</v>
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16714,19 +16714,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N383" t="n">
         <v>4648.6</v>
       </c>
       <c r="O383" t="n">
-        <v>1064529.4</v>
+        <v>1059880.8</v>
       </c>
       <c r="P383" t="n">
         <v>8900</v>
       </c>
       <c r="Q383" t="n">
-        <v>2038100</v>
+        <v>2029200</v>
       </c>
     </row>
     <row r="384">
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16799,19 +16799,19 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="N385" t="n">
         <v>1312.43</v>
       </c>
       <c r="O385" t="n">
-        <v>1353115.33</v>
+        <v>1342615.89</v>
       </c>
       <c r="P385" t="n">
         <v>2300</v>
       </c>
       <c r="Q385" t="n">
-        <v>2371300</v>
+        <v>2352900</v>
       </c>
     </row>
     <row r="386">
@@ -16884,10 +16884,10 @@
         <v>1908</v>
       </c>
       <c r="N387" t="n">
-        <v>17472.91</v>
+        <v>17473.953844316</v>
       </c>
       <c r="O387" t="n">
-        <v>33338312.28</v>
+        <v>33340303.93495493</v>
       </c>
       <c r="P387" t="n">
         <v>2900</v>
@@ -16972,10 +16972,10 @@
         <v>1774</v>
       </c>
       <c r="N389" t="n">
-        <v>1530.63</v>
+        <v>1530.7162764218</v>
       </c>
       <c r="O389" t="n">
-        <v>2715337.62</v>
+        <v>2715490.674372273</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17048,7 +17048,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>2329</v>
+        <v>2233</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17057,19 +17057,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>2329</v>
+        <v>2233</v>
       </c>
       <c r="N391" t="n">
         <v>1387.55</v>
       </c>
       <c r="O391" t="n">
-        <v>3231603.95</v>
+        <v>3098399.15</v>
       </c>
       <c r="P391" t="n">
         <v>2300</v>
       </c>
       <c r="Q391" t="n">
-        <v>5356700</v>
+        <v>5135900</v>
       </c>
     </row>
     <row r="392">
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
@@ -18201,19 +18201,19 @@
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N417" t="n">
         <v>3751</v>
       </c>
       <c r="O417" t="n">
-        <v>168795</v>
+        <v>146289</v>
       </c>
       <c r="P417" t="n">
         <v>6400</v>
       </c>
       <c r="Q417" t="n">
-        <v>288000</v>
+        <v>249600</v>
       </c>
     </row>
     <row r="418">
@@ -18418,28 +18418,28 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9239154786</v>
+        <v>1630.9239476386</v>
       </c>
       <c r="O422" t="n">
-        <v>430563.9136863504</v>
+        <v>420778.3784907588</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>660000</v>
+        <v>645000</v>
       </c>
     </row>
     <row r="423">
@@ -18476,10 +18476,10 @@
         <v>14</v>
       </c>
       <c r="N423" t="n">
-        <v>1467.3144171779</v>
+        <v>1467.3135220126</v>
       </c>
       <c r="O423" t="n">
-        <v>20542.4018404906</v>
+        <v>20542.3893081764</v>
       </c>
       <c r="P423" t="n">
         <v>2500</v>
@@ -18510,7 +18510,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -18519,19 +18519,19 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1939407455</v>
+        <v>1550.1940319426</v>
       </c>
       <c r="O424" t="n">
-        <v>640230.0975278915</v>
+        <v>624728.1948728678</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1032500</v>
+        <v>1007500</v>
       </c>
     </row>
     <row r="425">
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
@@ -18565,19 +18565,19 @@
         <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N425" t="n">
-        <v>1579.388566879</v>
+        <v>1579.3884193548</v>
       </c>
       <c r="O425" t="n">
-        <v>142144.97101911</v>
+        <v>140565.5693225772</v>
       </c>
       <c r="P425" t="n">
         <v>2900</v>
       </c>
       <c r="Q425" t="n">
-        <v>261000</v>
+        <v>258100</v>
       </c>
     </row>
     <row r="426">
@@ -18602,28 +18602,28 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.513738111</v>
+        <v>2403.5140171519</v>
       </c>
       <c r="O426" t="n">
-        <v>1562283.92977215</v>
+        <v>1521424.372857153</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2275000</v>
+        <v>2215500</v>
       </c>
     </row>
     <row r="427">
@@ -18692,28 +18692,28 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
       </c>
       <c r="L428" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N428" t="n">
-        <v>2521.4955797101</v>
+        <v>2521.490546875</v>
       </c>
       <c r="O428" t="n">
-        <v>335358.9121014433</v>
+        <v>310143.337265625</v>
       </c>
       <c r="P428" t="n">
         <v>3900</v>
       </c>
       <c r="Q428" t="n">
-        <v>518700</v>
+        <v>479700</v>
       </c>
     </row>
     <row r="429">
@@ -19026,7 +19026,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -19035,19 +19035,19 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N436" t="n">
         <v>2423.42</v>
       </c>
       <c r="O436" t="n">
-        <v>727026</v>
+        <v>722179.16</v>
       </c>
       <c r="P436" t="n">
         <v>3150</v>
       </c>
       <c r="Q436" t="n">
-        <v>945000</v>
+        <v>938700</v>
       </c>
     </row>
     <row r="437">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -19207,19 +19207,19 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N440" t="n">
         <v>2638</v>
       </c>
       <c r="O440" t="n">
-        <v>638396</v>
+        <v>630482</v>
       </c>
       <c r="P440" t="n">
         <v>4500</v>
       </c>
       <c r="Q440" t="n">
-        <v>1089000</v>
+        <v>1075500</v>
       </c>
     </row>
     <row r="441">
@@ -21704,7 +21704,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -21713,19 +21713,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N498" t="n">
         <v>2992.7</v>
       </c>
       <c r="O498" t="n">
-        <v>17956.2</v>
+        <v>8978.099999999999</v>
       </c>
       <c r="P498" t="n">
         <v>5900</v>
       </c>
       <c r="Q498" t="n">
-        <v>35400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="499">
@@ -22154,10 +22154,10 @@
         <v>360</v>
       </c>
       <c r="N508" t="n">
-        <v>4196.8725326298</v>
+        <v>4196.8725382689</v>
       </c>
       <c r="O508" t="n">
-        <v>1510874.111746728</v>
+        <v>1510874.113776804</v>
       </c>
       <c r="P508" t="n">
         <v>5900</v>
@@ -22642,7 +22642,7 @@
         </is>
       </c>
       <c r="J520" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -22651,19 +22651,19 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N520" t="n">
         <v>1969</v>
       </c>
       <c r="O520" t="n">
-        <v>348513</v>
+        <v>334730</v>
       </c>
       <c r="P520" t="n">
         <v>1500</v>
       </c>
       <c r="Q520" t="n">
-        <v>265500</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="521">
@@ -22826,10 +22826,10 @@
         <v>368</v>
       </c>
       <c r="N524" t="n">
-        <v>2567</v>
+        <v>2569.7269830028</v>
       </c>
       <c r="O524" t="n">
-        <v>944656</v>
+        <v>945659.5297450303</v>
       </c>
       <c r="P524" t="n">
         <v>4500</v>
@@ -23239,10 +23239,10 @@
         <v>210</v>
       </c>
       <c r="N534" t="n">
-        <v>2029.873953611</v>
+        <v>2029.8739872408</v>
       </c>
       <c r="O534" t="n">
-        <v>426273.53025831</v>
+        <v>426273.537320568</v>
       </c>
       <c r="P534" t="n">
         <v>3600</v>
@@ -23850,7 +23850,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -23859,19 +23859,19 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N549" t="n">
         <v>15355</v>
       </c>
       <c r="O549" t="n">
-        <v>1335885</v>
+        <v>1320530</v>
       </c>
       <c r="P549" t="n">
         <v>17900</v>
       </c>
       <c r="Q549" t="n">
-        <v>1557300</v>
+        <v>1539400</v>
       </c>
     </row>
     <row r="550">
@@ -24067,10 +24067,10 @@
         <v>596</v>
       </c>
       <c r="N554" t="n">
-        <v>880.32958602536</v>
+        <v>880.32962749339</v>
       </c>
       <c r="O554" t="n">
-        <v>524676.4332711145</v>
+        <v>524676.4579860604</v>
       </c>
       <c r="P554" t="n">
         <v>1200</v>
@@ -25035,10 +25035,10 @@
         <v>179</v>
       </c>
       <c r="N577" t="n">
-        <v>3731.0243521595</v>
+        <v>3731.0243959732</v>
       </c>
       <c r="O577" t="n">
-        <v>667853.3590365505</v>
+        <v>667853.3668792028</v>
       </c>
       <c r="P577" t="n">
         <v>5200</v>
@@ -25320,7 +25320,7 @@
         </is>
       </c>
       <c r="J584" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K584" t="n">
         <v>0</v>
@@ -25329,19 +25329,19 @@
         <v>0</v>
       </c>
       <c r="M584" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N584" t="n">
         <v>3877.89</v>
       </c>
       <c r="O584" t="n">
-        <v>868647.36</v>
+        <v>849257.9099999999</v>
       </c>
       <c r="P584" t="n">
         <v>6500</v>
       </c>
       <c r="Q584" t="n">
-        <v>1456000</v>
+        <v>1423500</v>
       </c>
     </row>
     <row r="585">
@@ -25410,7 +25410,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -25419,19 +25419,19 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N586" t="n">
-        <v>4285.1957990868</v>
+        <v>4285.1958525346</v>
       </c>
       <c r="O586" t="n">
-        <v>878465.1388127941</v>
+        <v>844183.5829493161</v>
       </c>
       <c r="P586" t="n">
         <v>6900</v>
       </c>
       <c r="Q586" t="n">
-        <v>1414500</v>
+        <v>1359300</v>
       </c>
     </row>
     <row r="587">
@@ -25459,7 +25459,7 @@
         </is>
       </c>
       <c r="J587" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K587" t="n">
         <v>0</v>
@@ -25468,19 +25468,19 @@
         <v>0</v>
       </c>
       <c r="M587" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N587" t="n">
         <v>9776.99</v>
       </c>
       <c r="O587" t="n">
-        <v>2199822.75</v>
+        <v>2180268.77</v>
       </c>
       <c r="P587" t="n">
         <v>15900</v>
       </c>
       <c r="Q587" t="n">
-        <v>3577500</v>
+        <v>3545700</v>
       </c>
     </row>
     <row r="588">
@@ -25915,7 +25915,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -25924,19 +25924,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N598" t="n">
-        <v>4605.2147677725</v>
+        <v>4605.2147813688</v>
       </c>
       <c r="O598" t="n">
-        <v>911832.524018955</v>
+        <v>907227.3119296535</v>
       </c>
       <c r="P598" t="n">
         <v>7600</v>
       </c>
       <c r="Q598" t="n">
-        <v>1504800</v>
+        <v>1497200</v>
       </c>
     </row>
     <row r="599">
@@ -26147,10 +26147,10 @@
         <v>2</v>
       </c>
       <c r="N603" t="n">
-        <v>13513.643203125</v>
+        <v>13513.643253968</v>
       </c>
       <c r="O603" t="n">
-        <v>27027.28640625</v>
+        <v>27027.286507936</v>
       </c>
       <c r="P603" t="n">
         <v>21900</v>
@@ -28009,10 +28009,10 @@
         <v>139</v>
       </c>
       <c r="N647" t="n">
-        <v>27123.765142315</v>
+        <v>27123.765105163</v>
       </c>
       <c r="O647" t="n">
-        <v>3770203.354781785</v>
+        <v>3770203.349617657</v>
       </c>
       <c r="P647" t="n">
         <v>44500</v>
@@ -28388,10 +28388,10 @@
         <v>79</v>
       </c>
       <c r="N656" t="n">
-        <v>8332.7796143959</v>
+        <v>8332.779613402099</v>
       </c>
       <c r="O656" t="n">
-        <v>658289.5895372761</v>
+        <v>658289.5894587658</v>
       </c>
       <c r="P656" t="n">
         <v>14900</v>
@@ -28673,7 +28673,7 @@
         </is>
       </c>
       <c r="J663" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="K663" t="n">
         <v>0</v>
@@ -28682,19 +28682,19 @@
         <v>0</v>
       </c>
       <c r="M663" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="N663" t="n">
-        <v>1561.0027356625</v>
+        <v>1561.0028372093</v>
       </c>
       <c r="O663" t="n">
-        <v>288785.5060975625</v>
+        <v>279419.5078604647</v>
       </c>
       <c r="P663" t="n">
         <v>2900</v>
       </c>
       <c r="Q663" t="n">
-        <v>536500</v>
+        <v>519100</v>
       </c>
     </row>
     <row r="664">
@@ -29180,7 +29180,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -29189,19 +29189,19 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N675" t="n">
-        <v>2568.8354237288</v>
+        <v>2568.8354081633</v>
       </c>
       <c r="O675" t="n">
-        <v>403307.1615254216</v>
+        <v>400738.3236734748</v>
       </c>
       <c r="P675" t="n">
         <v>4500</v>
       </c>
       <c r="Q675" t="n">
-        <v>706500</v>
+        <v>702000</v>
       </c>
     </row>
     <row r="676">
@@ -29402,10 +29402,10 @@
         <v>165</v>
       </c>
       <c r="N680" t="n">
-        <v>7969.9501675552</v>
+        <v>7982.1180305344</v>
       </c>
       <c r="O680" t="n">
-        <v>1315041.777646608</v>
+        <v>1317049.475038176</v>
       </c>
       <c r="P680" t="n">
         <v>12900</v>
@@ -29653,10 +29653,10 @@
         <v>19</v>
       </c>
       <c r="N686" t="n">
-        <v>9994.710151515201</v>
+        <v>10148.474923077</v>
       </c>
       <c r="O686" t="n">
-        <v>189899.4928787888</v>
+        <v>192821.023538463</v>
       </c>
       <c r="P686" t="n">
         <v>20800</v>
@@ -30875,7 +30875,7 @@
         </is>
       </c>
       <c r="J715" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K715" t="n">
         <v>0</v>
@@ -30884,19 +30884,19 @@
         <v>0</v>
       </c>
       <c r="M715" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N715" t="n">
         <v>2634.61</v>
       </c>
       <c r="O715" t="n">
-        <v>152807.38</v>
+        <v>136999.72</v>
       </c>
       <c r="P715" t="n">
         <v>4200</v>
       </c>
       <c r="Q715" t="n">
-        <v>243600</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="716">
@@ -31013,7 +31013,7 @@
         </is>
       </c>
       <c r="J718" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K718" t="n">
         <v>0</v>
@@ -31022,19 +31022,19 @@
         <v>0</v>
       </c>
       <c r="M718" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N718" t="n">
         <v>10911.29</v>
       </c>
       <c r="O718" t="n">
-        <v>152758.06</v>
+        <v>87290.32000000001</v>
       </c>
       <c r="P718" t="n">
         <v>17400</v>
       </c>
       <c r="Q718" t="n">
-        <v>243600</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="719">
@@ -31476,7 +31476,7 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
@@ -31485,19 +31485,19 @@
         <v>0</v>
       </c>
       <c r="M728" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N728" t="n">
         <v>10977.27</v>
       </c>
       <c r="O728" t="n">
-        <v>548863.5</v>
+        <v>526908.96</v>
       </c>
       <c r="P728" t="n">
         <v>17900</v>
       </c>
       <c r="Q728" t="n">
-        <v>895000</v>
+        <v>859200</v>
       </c>
     </row>
     <row r="729">
@@ -31534,10 +31534,10 @@
         <v>16</v>
       </c>
       <c r="N729" t="n">
-        <v>14380</v>
+        <v>14447.670588235</v>
       </c>
       <c r="O729" t="n">
-        <v>230080</v>
+        <v>231162.72941176</v>
       </c>
       <c r="P729" t="n">
         <v>23000</v>
@@ -31568,28 +31568,28 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M730" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N730" t="n">
-        <v>1664.351984375</v>
+        <v>1664.3497007042</v>
       </c>
       <c r="O730" t="n">
-        <v>13314.815875</v>
+        <v>3328.6994014084</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
       </c>
       <c r="Q730" t="n">
-        <v>23200</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="731">
@@ -31750,13 +31750,13 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M734" t="n">
         <v>48</v>
@@ -32394,7 +32394,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -32403,19 +32403,19 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N748" t="n">
-        <v>23521.623965517</v>
+        <v>23521.623269231</v>
       </c>
       <c r="O748" t="n">
-        <v>423389.231379306</v>
+        <v>399867.595576927</v>
       </c>
       <c r="P748" t="n">
         <v>39000</v>
       </c>
       <c r="Q748" t="n">
-        <v>702000</v>
+        <v>663000</v>
       </c>
     </row>
     <row r="749">
@@ -32532,7 +32532,7 @@
         </is>
       </c>
       <c r="J751" t="n">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="K751" t="n">
         <v>0</v>
@@ -32541,19 +32541,19 @@
         <v>0</v>
       </c>
       <c r="M751" t="n">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="N751" t="n">
-        <v>1778.4726787358</v>
+        <v>1778.4726973583</v>
       </c>
       <c r="O751" t="n">
-        <v>2192856.812881242</v>
+        <v>2178629.054263917</v>
       </c>
       <c r="P751" t="n">
         <v>4900</v>
       </c>
       <c r="Q751" t="n">
-        <v>6041700</v>
+        <v>6002500</v>
       </c>
     </row>
     <row r="752">
@@ -32578,7 +32578,7 @@
         </is>
       </c>
       <c r="J752" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="K752" t="n">
         <v>0</v>
@@ -32587,19 +32587,19 @@
         <v>0</v>
       </c>
       <c r="M752" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N752" t="n">
         <v>2325</v>
       </c>
       <c r="O752" t="n">
-        <v>730050</v>
+        <v>716100</v>
       </c>
       <c r="P752" t="n">
         <v>4900</v>
       </c>
       <c r="Q752" t="n">
-        <v>1538600</v>
+        <v>1509200</v>
       </c>
     </row>
     <row r="753">
@@ -34610,13 +34610,13 @@
         </is>
       </c>
       <c r="J796" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K796" t="n">
         <v>0</v>
       </c>
       <c r="L796" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M796" t="n">
         <v>16</v>
@@ -34840,13 +34840,13 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
       </c>
       <c r="L801" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M801" t="n">
         <v>96</v>
@@ -35177,10 +35177,10 @@
         <v>1</v>
       </c>
       <c r="N808" t="n">
-        <v>22942</v>
+        <v>23400.84</v>
       </c>
       <c r="O808" t="n">
-        <v>22942</v>
+        <v>23400.84</v>
       </c>
       <c r="P808" t="n">
         <v>36900</v>
@@ -35223,10 +35223,10 @@
         <v>447</v>
       </c>
       <c r="N809" t="n">
-        <v>2328.1186963238</v>
+        <v>2328.1186869944</v>
       </c>
       <c r="O809" t="n">
-        <v>1040669.057256739</v>
+        <v>1040669.053086497</v>
       </c>
       <c r="P809" t="n">
         <v>4500</v>
@@ -35407,10 +35407,10 @@
         <v>56</v>
       </c>
       <c r="N813" t="n">
-        <v>50153.86</v>
+        <v>50584.365236051</v>
       </c>
       <c r="O813" t="n">
-        <v>2808616.16</v>
+        <v>2832724.453218856</v>
       </c>
       <c r="P813" t="n">
         <v>11500</v>
@@ -35959,10 +35959,10 @@
         <v>15</v>
       </c>
       <c r="N825" t="n">
-        <v>4907.8222048611</v>
+        <v>4907.8223782772</v>
       </c>
       <c r="O825" t="n">
-        <v>73617.33307291649</v>
+        <v>73617.33567415801</v>
       </c>
       <c r="P825" t="n">
         <v>8200</v>
@@ -36235,10 +36235,10 @@
         <v>9</v>
       </c>
       <c r="N831" t="n">
-        <v>3903.7370093458</v>
+        <v>3903.7373747017</v>
       </c>
       <c r="O831" t="n">
-        <v>35133.6330841122</v>
+        <v>35133.6363723153</v>
       </c>
       <c r="P831" t="n">
         <v>7500</v>
@@ -36540,13 +36540,13 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M838" t="n">
         <v>11</v>
@@ -36598,10 +36598,10 @@
         <v>1</v>
       </c>
       <c r="N839" t="n">
-        <v>9839</v>
+        <v>9952.091954023001</v>
       </c>
       <c r="O839" t="n">
-        <v>9839</v>
+        <v>9952.091954023001</v>
       </c>
       <c r="P839" t="n">
         <v>16900</v>
@@ -37322,13 +37322,13 @@
         </is>
       </c>
       <c r="J855" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K855" t="n">
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M855" t="n">
         <v>80</v>
@@ -37835,10 +37835,10 @@
         <v>63</v>
       </c>
       <c r="N866" t="n">
-        <v>59834</v>
+        <v>59958.524453694</v>
       </c>
       <c r="O866" t="n">
-        <v>3769542</v>
+        <v>3777387.040582722</v>
       </c>
       <c r="P866" t="n">
         <v>7900</v>
@@ -37973,10 +37973,10 @@
         <v>88</v>
       </c>
       <c r="N869" t="n">
-        <v>10219</v>
+        <v>10270.481108312</v>
       </c>
       <c r="O869" t="n">
-        <v>899272</v>
+        <v>903802.337531456</v>
       </c>
       <c r="P869" t="n">
         <v>16900</v>
@@ -38148,13 +38148,13 @@
         </is>
       </c>
       <c r="J873" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K873" t="n">
         <v>0</v>
       </c>
       <c r="L873" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M873" t="n">
         <v>24</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="J887" t="n">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K887" t="n">
         <v>0</v>
@@ -38801,19 +38801,19 @@
         <v>0</v>
       </c>
       <c r="M887" t="n">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="N887" t="n">
-        <v>3821</v>
+        <v>3821.6520477816</v>
       </c>
       <c r="O887" t="n">
-        <v>5895803</v>
+        <v>5892987.457679227</v>
       </c>
       <c r="P887" t="n">
         <v>5900</v>
       </c>
       <c r="Q887" t="n">
-        <v>9103700</v>
+        <v>9097800</v>
       </c>
     </row>
     <row r="888">
@@ -38850,10 +38850,10 @@
         <v>12</v>
       </c>
       <c r="N888" t="n">
-        <v>15472</v>
+        <v>15512.291666667</v>
       </c>
       <c r="O888" t="n">
-        <v>185664</v>
+        <v>186147.500000004</v>
       </c>
       <c r="P888" t="n">
         <v>25900</v>
@@ -38988,10 +38988,10 @@
         <v>1</v>
       </c>
       <c r="N891" t="n">
-        <v>5476</v>
+        <v>5486.9301397206</v>
       </c>
       <c r="O891" t="n">
-        <v>5476</v>
+        <v>5486.9301397206</v>
       </c>
       <c r="P891" t="n">
         <v>8900</v>
@@ -39129,10 +39129,10 @@
         <v>1282</v>
       </c>
       <c r="N894" t="n">
-        <v>1516.0387847976</v>
+        <v>1516.0387762203</v>
       </c>
       <c r="O894" t="n">
-        <v>1943561.722110523</v>
+        <v>1943561.711114425</v>
       </c>
       <c r="P894" t="n">
         <v>2300</v>
@@ -39219,10 +39219,10 @@
         <v>267</v>
       </c>
       <c r="N896" t="n">
-        <v>2458.5128483396</v>
+        <v>2458.5128385327</v>
       </c>
       <c r="O896" t="n">
-        <v>656422.9305066733</v>
+        <v>656422.9278882309</v>
       </c>
       <c r="P896" t="n">
         <v>3500</v>
@@ -39265,10 +39265,10 @@
         <v>5</v>
       </c>
       <c r="N897" t="n">
-        <v>1907.392860262</v>
+        <v>1907.3928289474</v>
       </c>
       <c r="O897" t="n">
-        <v>9536.964301310001</v>
+        <v>9536.964144737</v>
       </c>
       <c r="P897" t="n">
         <v>2500</v>
@@ -39311,10 +39311,10 @@
         <v>107</v>
       </c>
       <c r="N898" t="n">
-        <v>1771.090242915</v>
+        <v>1771.0901699524</v>
       </c>
       <c r="O898" t="n">
-        <v>189506.655991905</v>
+        <v>189506.6481849068</v>
       </c>
       <c r="P898" t="n">
         <v>2500</v>
@@ -39345,7 +39345,7 @@
         </is>
       </c>
       <c r="J899" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K899" t="n">
         <v>0</v>
@@ -39354,19 +39354,19 @@
         <v>0</v>
       </c>
       <c r="M899" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N899" t="n">
-        <v>2079.3838525155</v>
+        <v>2079.3837839721</v>
       </c>
       <c r="O899" t="n">
-        <v>563513.0240317006</v>
+        <v>561433.621672467</v>
       </c>
       <c r="P899" t="n">
         <v>2900</v>
       </c>
       <c r="Q899" t="n">
-        <v>785900</v>
+        <v>783000</v>
       </c>
     </row>
     <row r="900">
@@ -39391,7 +39391,7 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
@@ -39400,19 +39400,19 @@
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N900" t="n">
-        <v>1803.0158997564</v>
+        <v>1803.0159162304</v>
       </c>
       <c r="O900" t="n">
-        <v>539101.7540271636</v>
+        <v>533692.7112041984</v>
       </c>
       <c r="P900" t="n">
         <v>2500</v>
       </c>
       <c r="Q900" t="n">
-        <v>747500</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="901">
@@ -39437,7 +39437,7 @@
         </is>
       </c>
       <c r="J901" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K901" t="n">
         <v>0</v>
@@ -39446,19 +39446,19 @@
         <v>0</v>
       </c>
       <c r="M901" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N901" t="n">
-        <v>3306.5945945946</v>
+        <v>3306.5945783133</v>
       </c>
       <c r="O901" t="n">
-        <v>297593.513513514</v>
+        <v>290980.3228915704</v>
       </c>
       <c r="P901" t="n">
         <v>4900</v>
       </c>
       <c r="Q901" t="n">
-        <v>441000</v>
+        <v>431200</v>
       </c>
     </row>
     <row r="902">
@@ -39495,10 +39495,10 @@
         <v>59</v>
       </c>
       <c r="N902" t="n">
-        <v>2108.7936087295</v>
+        <v>2108.7939012739</v>
       </c>
       <c r="O902" t="n">
-        <v>124418.8229150405</v>
+        <v>124418.8401751601</v>
       </c>
       <c r="P902" t="n">
         <v>2900</v>
@@ -39541,10 +39541,10 @@
         <v>252</v>
       </c>
       <c r="N903" t="n">
-        <v>2056.0827629734</v>
+        <v>2056.082714437</v>
       </c>
       <c r="O903" t="n">
-        <v>518132.8562692968</v>
+        <v>518132.844038124</v>
       </c>
       <c r="P903" t="n">
         <v>2900</v>
@@ -39587,10 +39587,10 @@
         <v>138</v>
       </c>
       <c r="N904" t="n">
-        <v>3224.56895</v>
+        <v>3224.5689724311</v>
       </c>
       <c r="O904" t="n">
-        <v>444990.5151</v>
+        <v>444990.5181954918</v>
       </c>
       <c r="P904" t="n">
         <v>4500</v>
@@ -39633,10 +39633,10 @@
         <v>210</v>
       </c>
       <c r="N905" t="n">
-        <v>1655.9303958333</v>
+        <v>1655.9303421788</v>
       </c>
       <c r="O905" t="n">
-        <v>347745.383124993</v>
+        <v>347745.371857548</v>
       </c>
       <c r="P905" t="n">
         <v>2500</v>
@@ -39762,7 +39762,7 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
@@ -39771,19 +39771,19 @@
         <v>0</v>
       </c>
       <c r="M908" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="N908" t="n">
         <v>1662</v>
       </c>
       <c r="O908" t="n">
-        <v>345696</v>
+        <v>324090</v>
       </c>
       <c r="P908" t="n">
         <v>2900</v>
       </c>
       <c r="Q908" t="n">
-        <v>603200</v>
+        <v>565500</v>
       </c>
     </row>
     <row r="909">
@@ -39808,7 +39808,7 @@
         </is>
       </c>
       <c r="J909" t="n">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
@@ -39817,19 +39817,19 @@
         <v>0</v>
       </c>
       <c r="M909" t="n">
-        <v>832</v>
+        <v>812</v>
       </c>
       <c r="N909" t="n">
         <v>2454</v>
       </c>
       <c r="O909" t="n">
-        <v>2041728</v>
+        <v>1992648</v>
       </c>
       <c r="P909" t="n">
         <v>4200</v>
       </c>
       <c r="Q909" t="n">
-        <v>3494400</v>
+        <v>3410400</v>
       </c>
     </row>
     <row r="910">
@@ -39854,28 +39854,28 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M910" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N910" t="n">
-        <v>1592.281793842</v>
+        <v>1592.2820519836</v>
       </c>
       <c r="O910" t="n">
-        <v>616213.054216854</v>
+        <v>614620.8720656696</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
       </c>
       <c r="Q910" t="n">
-        <v>967500</v>
+        <v>965000</v>
       </c>
     </row>
     <row r="911">
@@ -39951,10 +39951,10 @@
         <v>4</v>
       </c>
       <c r="N912" t="n">
-        <v>5347.73</v>
+        <v>5372.836713615</v>
       </c>
       <c r="O912" t="n">
-        <v>21390.92</v>
+        <v>21491.34685446</v>
       </c>
       <c r="P912" t="n">
         <v>9500</v>
@@ -39985,7 +39985,7 @@
         </is>
       </c>
       <c r="J913" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K913" t="n">
         <v>0</v>
@@ -39994,19 +39994,19 @@
         <v>0</v>
       </c>
       <c r="M913" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="N913" t="n">
-        <v>2311.9128246753</v>
+        <v>2311.912006689</v>
       </c>
       <c r="O913" t="n">
-        <v>436951.5238636316</v>
+        <v>432327.545250843</v>
       </c>
       <c r="P913" t="n">
         <v>3500</v>
       </c>
       <c r="Q913" t="n">
-        <v>661500</v>
+        <v>654500</v>
       </c>
     </row>
     <row r="914">
@@ -40031,7 +40031,7 @@
         </is>
       </c>
       <c r="J914" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K914" t="n">
         <v>0</v>
@@ -40040,19 +40040,19 @@
         <v>0</v>
       </c>
       <c r="M914" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N914" t="n">
-        <v>1906.1809090909</v>
+        <v>1906.180625</v>
       </c>
       <c r="O914" t="n">
-        <v>264959.1463636351</v>
+        <v>257334.384375</v>
       </c>
       <c r="P914" t="n">
         <v>2900</v>
       </c>
       <c r="Q914" t="n">
-        <v>403100</v>
+        <v>391500</v>
       </c>
     </row>
     <row r="915">
@@ -40077,28 +40077,28 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
       </c>
       <c r="L915" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N915" t="n">
-        <v>3033.7022680412</v>
+        <v>3033.7020207254</v>
       </c>
       <c r="O915" t="n">
-        <v>546066.408247416</v>
+        <v>543032.6617098466</v>
       </c>
       <c r="P915" t="n">
         <v>4500</v>
       </c>
       <c r="Q915" t="n">
-        <v>810000</v>
+        <v>805500</v>
       </c>
     </row>
     <row r="916">
@@ -40135,10 +40135,10 @@
         <v>200</v>
       </c>
       <c r="N916" t="n">
-        <v>1668.6353623188</v>
+        <v>1668.636969697</v>
       </c>
       <c r="O916" t="n">
-        <v>333727.07246376</v>
+        <v>333727.3939394</v>
       </c>
       <c r="P916" t="n">
         <v>2500</v>
@@ -40169,7 +40169,7 @@
         </is>
       </c>
       <c r="J917" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
@@ -40178,19 +40178,19 @@
         <v>0</v>
       </c>
       <c r="M917" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N917" t="n">
-        <v>2546.9826614987</v>
+        <v>2546.9826041667</v>
       </c>
       <c r="O917" t="n">
-        <v>331107.745994831</v>
+        <v>328560.7559375043</v>
       </c>
       <c r="P917" t="n">
         <v>3900</v>
       </c>
       <c r="Q917" t="n">
-        <v>507000</v>
+        <v>503100</v>
       </c>
     </row>
     <row r="918">
@@ -40227,10 +40227,10 @@
         <v>1077</v>
       </c>
       <c r="N918" t="n">
-        <v>1259.2746638947</v>
+        <v>1259.2746779425</v>
       </c>
       <c r="O918" t="n">
-        <v>1356238.813014592</v>
+        <v>1356238.828144072</v>
       </c>
       <c r="P918" t="n">
         <v>1900</v>
@@ -40314,10 +40314,10 @@
         <v>20</v>
       </c>
       <c r="N920" t="n">
-        <v>2842.2744460028</v>
+        <v>2842.2744382022</v>
       </c>
       <c r="O920" t="n">
-        <v>56845.488920056</v>
+        <v>56845.488764044</v>
       </c>
       <c r="P920" t="n">
         <v>4900</v>
@@ -40348,13 +40348,13 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
       </c>
       <c r="L921" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M921" t="n">
         <v>42</v>
@@ -40450,10 +40450,10 @@
         <v>2638</v>
       </c>
       <c r="N923" t="n">
-        <v>692.15226424361</v>
+        <v>692.15226870079</v>
       </c>
       <c r="O923" t="n">
-        <v>1825897.673074643</v>
+        <v>1825897.684832684</v>
       </c>
       <c r="P923" t="n">
         <v>1200</v>
@@ -40499,10 +40499,10 @@
         <v>3</v>
       </c>
       <c r="N924" t="n">
-        <v>18491</v>
+        <v>18654.637168142</v>
       </c>
       <c r="O924" t="n">
-        <v>55473</v>
+        <v>55963.911504426</v>
       </c>
       <c r="P924" t="n">
         <v>13500</v>
@@ -41094,7 +41094,7 @@
         </is>
       </c>
       <c r="J937" t="n">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K937" t="n">
         <v>0</v>
@@ -41103,19 +41103,19 @@
         <v>0</v>
       </c>
       <c r="M937" t="n">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="N937" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O937" t="n">
-        <v>3291899.84</v>
+        <v>3256118.32</v>
       </c>
       <c r="P937" t="n">
         <v>14900</v>
       </c>
       <c r="Q937" t="n">
-        <v>5483200</v>
+        <v>5423600</v>
       </c>
     </row>
     <row r="938">
@@ -41797,10 +41797,10 @@
         <v>3563</v>
       </c>
       <c r="N952" t="n">
-        <v>481.48791273054</v>
+        <v>481.48791226097</v>
       </c>
       <c r="O952" t="n">
-        <v>1715541.433058914</v>
+        <v>1715541.431385836</v>
       </c>
       <c r="P952" t="n">
         <v>650</v>
@@ -42022,10 +42022,10 @@
         <v>351</v>
       </c>
       <c r="N957" t="n">
-        <v>2286.1646666667</v>
+        <v>2286.16463138</v>
       </c>
       <c r="O957" t="n">
-        <v>802443.7980000118</v>
+        <v>802443.78561438</v>
       </c>
       <c r="P957" t="n">
         <v>3000</v>
@@ -42267,28 +42267,28 @@
         </is>
       </c>
       <c r="J963" t="n">
-        <v>966</v>
+        <v>744</v>
       </c>
       <c r="K963" t="n">
         <v>0</v>
       </c>
       <c r="L963" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M963" t="n">
-        <v>916</v>
+        <v>744</v>
       </c>
       <c r="N963" t="n">
         <v>177.65</v>
       </c>
       <c r="O963" t="n">
-        <v>162727.4</v>
+        <v>132171.6</v>
       </c>
       <c r="P963" t="n">
         <v>300</v>
       </c>
       <c r="Q963" t="n">
-        <v>274800</v>
+        <v>223200</v>
       </c>
     </row>
     <row r="964">
@@ -42396,7 +42396,7 @@
         </is>
       </c>
       <c r="J966" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K966" t="n">
         <v>0</v>
@@ -42405,19 +42405,19 @@
         <v>0</v>
       </c>
       <c r="M966" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N966" t="n">
-        <v>4032.3968051948</v>
+        <v>4032.396796875</v>
       </c>
       <c r="O966" t="n">
-        <v>120971.904155844</v>
+        <v>116939.507109375</v>
       </c>
       <c r="P966" t="n">
         <v>4200</v>
       </c>
       <c r="Q966" t="n">
-        <v>126000</v>
+        <v>121800</v>
       </c>
     </row>
     <row r="967">
@@ -42530,7 +42530,7 @@
         </is>
       </c>
       <c r="J969" t="n">
-        <v>1318</v>
+        <v>1136</v>
       </c>
       <c r="K969" t="n">
         <v>0</v>
@@ -42539,19 +42539,19 @@
         <v>0</v>
       </c>
       <c r="M969" t="n">
-        <v>1318</v>
+        <v>1136</v>
       </c>
       <c r="N969" t="n">
-        <v>517.29151641831</v>
+        <v>517.2923857868</v>
       </c>
       <c r="O969" t="n">
-        <v>681790.2186393327</v>
+        <v>587644.1502538047</v>
       </c>
       <c r="P969" t="n">
         <v>900</v>
       </c>
       <c r="Q969" t="n">
-        <v>1186200</v>
+        <v>1022400</v>
       </c>
     </row>
     <row r="970">
@@ -42715,7 +42715,7 @@
         </is>
       </c>
       <c r="J973" t="n">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="K973" t="n">
         <v>0</v>
@@ -42724,19 +42724,19 @@
         <v>0</v>
       </c>
       <c r="M973" t="n">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="N973" t="n">
-        <v>3110.8401559454</v>
+        <v>3110.8400113026</v>
       </c>
       <c r="O973" t="n">
-        <v>4193412.530214399</v>
+        <v>4162303.935122879</v>
       </c>
       <c r="P973" t="n">
         <v>4500</v>
       </c>
       <c r="Q973" t="n">
-        <v>6066000</v>
+        <v>6021000</v>
       </c>
     </row>
     <row r="974">
@@ -42847,28 +42847,28 @@
         </is>
       </c>
       <c r="J976" t="n">
-        <v>13740</v>
+        <v>13678</v>
       </c>
       <c r="K976" t="n">
         <v>0</v>
       </c>
       <c r="L976" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M976" t="n">
-        <v>13729</v>
+        <v>13678</v>
       </c>
       <c r="N976" t="n">
-        <v>703.79500789654</v>
+        <v>703.7949766627</v>
       </c>
       <c r="O976" t="n">
-        <v>9662401.663411599</v>
+        <v>9626507.690792412</v>
       </c>
       <c r="P976" t="n">
         <v>900</v>
       </c>
       <c r="Q976" t="n">
-        <v>12356100</v>
+        <v>12310200</v>
       </c>
     </row>
     <row r="977">
@@ -42949,10 +42949,10 @@
         <v>45</v>
       </c>
       <c r="N978" t="n">
-        <v>3006.0209473684</v>
+        <v>3006.0209574468</v>
       </c>
       <c r="O978" t="n">
-        <v>135270.942631578</v>
+        <v>135270.943085106</v>
       </c>
       <c r="P978" t="n">
         <v>3900</v>
@@ -43163,7 +43163,7 @@
         </is>
       </c>
       <c r="J983" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K983" t="n">
         <v>0</v>
@@ -43172,19 +43172,19 @@
         <v>0</v>
       </c>
       <c r="M983" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N983" t="n">
         <v>1300</v>
       </c>
       <c r="O983" t="n">
-        <v>245700</v>
+        <v>240500</v>
       </c>
       <c r="P983" t="n">
         <v>2200</v>
       </c>
       <c r="Q983" t="n">
-        <v>415800</v>
+        <v>407000</v>
       </c>
     </row>
     <row r="984">
@@ -43207,7 +43207,7 @@
         </is>
       </c>
       <c r="J984" t="n">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K984" t="n">
         <v>0</v>
@@ -43216,19 +43216,19 @@
         <v>0</v>
       </c>
       <c r="M984" t="n">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="N984" t="n">
         <v>1937</v>
       </c>
       <c r="O984" t="n">
-        <v>776737</v>
+        <v>768989</v>
       </c>
       <c r="P984" t="n">
         <v>3300</v>
       </c>
       <c r="Q984" t="n">
-        <v>1323300</v>
+        <v>1310100</v>
       </c>
     </row>
     <row r="985">
@@ -43292,7 +43292,7 @@
         </is>
       </c>
       <c r="J986" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K986" t="n">
         <v>0</v>
@@ -43301,19 +43301,19 @@
         <v>0</v>
       </c>
       <c r="M986" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N986" t="n">
         <v>2525.02</v>
       </c>
       <c r="O986" t="n">
-        <v>1214534.62</v>
+        <v>1199384.5</v>
       </c>
       <c r="P986" t="n">
         <v>3000</v>
       </c>
       <c r="Q986" t="n">
-        <v>1443000</v>
+        <v>1425000</v>
       </c>
     </row>
     <row r="987">
@@ -43333,7 +43333,7 @@
         </is>
       </c>
       <c r="J987" t="n">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="K987" t="n">
         <v>0</v>
@@ -43342,19 +43342,19 @@
         <v>0</v>
       </c>
       <c r="M987" t="n">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="N987" t="n">
-        <v>2077.4946875</v>
+        <v>2077.4947226387</v>
       </c>
       <c r="O987" t="n">
-        <v>874625.2634375</v>
+        <v>866315.2993403379</v>
       </c>
       <c r="P987" t="n">
         <v>2900</v>
       </c>
       <c r="Q987" t="n">
-        <v>1220900</v>
+        <v>1209300</v>
       </c>
     </row>
     <row r="988">
@@ -43602,10 +43602,10 @@
         <v>81</v>
       </c>
       <c r="N993" t="n">
-        <v>1595.5001480385</v>
+        <v>1595.4999702159</v>
       </c>
       <c r="O993" t="n">
-        <v>129235.5119911185</v>
+        <v>129235.4975874879</v>
       </c>
       <c r="P993" t="n">
         <v>2500</v>
@@ -44203,7 +44203,7 @@
         </is>
       </c>
       <c r="J1006" t="n">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="K1006" t="n">
         <v>0</v>
@@ -44212,19 +44212,19 @@
         <v>0</v>
       </c>
       <c r="M1006" t="n">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="N1006" t="n">
         <v>1669.6</v>
       </c>
       <c r="O1006" t="n">
-        <v>1667930.4</v>
+        <v>1659582.4</v>
       </c>
       <c r="P1006" t="n">
         <v>2900</v>
       </c>
       <c r="Q1006" t="n">
-        <v>2897100</v>
+        <v>2882600</v>
       </c>
     </row>
     <row r="1007">
@@ -44454,10 +44454,10 @@
         <v>3</v>
       </c>
       <c r="N1011" t="n">
-        <v>5796.3355555556</v>
+        <v>5796.3358823529</v>
       </c>
       <c r="O1011" t="n">
-        <v>17389.0066666668</v>
+        <v>17389.0076470587</v>
       </c>
       <c r="P1011" t="n">
         <v>15900</v>
@@ -44486,7 +44486,7 @@
         </is>
       </c>
       <c r="J1012" t="n">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="K1012" t="n">
         <v>0</v>
@@ -44495,19 +44495,19 @@
         <v>0</v>
       </c>
       <c r="M1012" t="n">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="N1012" t="n">
-        <v>3063.6219339866</v>
+        <v>3063.6219379845</v>
       </c>
       <c r="O1012" t="n">
-        <v>2071008.427374942</v>
+        <v>2058753.942325584</v>
       </c>
       <c r="P1012" t="n">
         <v>3500</v>
       </c>
       <c r="Q1012" t="n">
-        <v>2366000</v>
+        <v>2352000</v>
       </c>
     </row>
     <row r="1013">
@@ -44639,10 +44639,10 @@
         <v>2</v>
       </c>
       <c r="N1015" t="n">
-        <v>875.69017316017</v>
+        <v>875.6901754386</v>
       </c>
       <c r="O1015" t="n">
-        <v>1751.38034632034</v>
+        <v>1751.3803508772</v>
       </c>
       <c r="P1015" t="n">
         <v>4500</v>
@@ -44915,13 +44915,13 @@
         </is>
       </c>
       <c r="J1021" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K1021" t="n">
         <v>0</v>
       </c>
       <c r="L1021" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1021" t="n">
         <v>9</v>
@@ -45845,7 +45845,7 @@
         </is>
       </c>
       <c r="J1041" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1041" t="n">
         <v>0</v>
@@ -45854,19 +45854,19 @@
         <v>0</v>
       </c>
       <c r="M1041" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1041" t="n">
-        <v>34880.158</v>
+        <v>34880.17</v>
       </c>
       <c r="O1041" t="n">
-        <v>69760.31600000001</v>
+        <v>34880.17</v>
       </c>
       <c r="P1041" t="n">
         <v>65900</v>
       </c>
       <c r="Q1041" t="n">
-        <v>131800</v>
+        <v>65900</v>
       </c>
     </row>
     <row r="1042">
@@ -46849,10 +46849,10 @@
         <v>3</v>
       </c>
       <c r="N1062" t="n">
-        <v>5216.9</v>
+        <v>5235.0773519164</v>
       </c>
       <c r="O1062" t="n">
-        <v>15650.7</v>
+        <v>15705.2320557492</v>
       </c>
       <c r="P1062" t="n">
         <v>20500</v>
@@ -47037,10 +47037,10 @@
         <v>38</v>
       </c>
       <c r="N1066" t="n">
-        <v>7046.9398275119</v>
+        <v>7049.9805782093</v>
       </c>
       <c r="O1066" t="n">
-        <v>267783.7134454522</v>
+        <v>267899.2619719534</v>
       </c>
       <c r="P1066" t="n">
         <v>9900</v>
@@ -47317,10 +47317,10 @@
         <v>16</v>
       </c>
       <c r="N1072" t="n">
-        <v>665.32371673004</v>
+        <v>665.32374700527</v>
       </c>
       <c r="O1072" t="n">
-        <v>10645.17946768064</v>
+        <v>10645.17995208432</v>
       </c>
       <c r="P1072" t="n">
         <v>2900</v>
@@ -47591,7 +47591,7 @@
         </is>
       </c>
       <c r="J1078" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="K1078" t="n">
         <v>0</v>
@@ -47600,19 +47600,19 @@
         <v>0</v>
       </c>
       <c r="M1078" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="N1078" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1078" t="n">
-        <v>1223351.28</v>
+        <v>1195860.24</v>
       </c>
       <c r="P1078" t="n">
         <v>7900</v>
       </c>
       <c r="Q1078" t="n">
-        <v>2109300</v>
+        <v>2061900</v>
       </c>
     </row>
     <row r="1079">
@@ -47640,7 +47640,7 @@
         </is>
       </c>
       <c r="J1079" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K1079" t="n">
         <v>0</v>
@@ -47649,19 +47649,19 @@
         <v>0</v>
       </c>
       <c r="M1079" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N1079" t="n">
         <v>3155</v>
       </c>
       <c r="O1079" t="n">
-        <v>1195745</v>
+        <v>1183125</v>
       </c>
       <c r="P1079" t="n">
         <v>5900</v>
       </c>
       <c r="Q1079" t="n">
-        <v>2236100</v>
+        <v>2212500</v>
       </c>
     </row>
     <row r="1080">
@@ -47689,7 +47689,7 @@
         </is>
       </c>
       <c r="J1080" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K1080" t="n">
         <v>0</v>
@@ -47698,19 +47698,19 @@
         <v>0</v>
       </c>
       <c r="M1080" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N1080" t="n">
-        <v>430.6099760479</v>
+        <v>430.60997577226</v>
       </c>
       <c r="O1080" t="n">
-        <v>38324.2878682631</v>
+        <v>37032.45791641436</v>
       </c>
       <c r="P1080" t="n">
         <v>2200</v>
       </c>
       <c r="Q1080" t="n">
-        <v>195800</v>
+        <v>189200</v>
       </c>
     </row>
     <row r="1081">
@@ -47738,7 +47738,7 @@
         </is>
       </c>
       <c r="J1081" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K1081" t="n">
         <v>0</v>
@@ -47747,19 +47747,19 @@
         <v>0</v>
       </c>
       <c r="M1081" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N1081" t="n">
-        <v>465.87096374046</v>
+        <v>465.87096743295</v>
       </c>
       <c r="O1081" t="n">
-        <v>73141.74130725222</v>
+        <v>71744.1289846743</v>
       </c>
       <c r="P1081" t="n">
         <v>2500</v>
       </c>
       <c r="Q1081" t="n">
-        <v>392500</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="1082">
@@ -47799,10 +47799,10 @@
         <v>13</v>
       </c>
       <c r="N1082" t="n">
-        <v>315.02705797101</v>
+        <v>315.02716176471</v>
       </c>
       <c r="O1082" t="n">
-        <v>4095.35175362313</v>
+        <v>4095.35310294123</v>
       </c>
       <c r="P1082" t="n">
         <v>2200</v>
@@ -49021,7 +49021,7 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>1463</v>
+        <v>1451</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
@@ -49030,19 +49030,19 @@
         <v>0</v>
       </c>
       <c r="M1111" t="n">
-        <v>1463</v>
+        <v>1451</v>
       </c>
       <c r="N1111" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1111" t="n">
-        <v>1721321.91</v>
+        <v>1707203.07</v>
       </c>
       <c r="P1111" t="n">
         <v>1900</v>
       </c>
       <c r="Q1111" t="n">
-        <v>2779700</v>
+        <v>2756900</v>
       </c>
     </row>
     <row r="1112">
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="J1117" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
@@ -49288,19 +49288,19 @@
         <v>0</v>
       </c>
       <c r="M1117" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N1117" t="n">
-        <v>2181.4247724621</v>
+        <v>2181.4247663551</v>
       </c>
       <c r="O1117" t="n">
-        <v>218142.47724621</v>
+        <v>215961.0518691549</v>
       </c>
       <c r="P1117" t="n">
         <v>2900</v>
       </c>
       <c r="Q1117" t="n">
-        <v>290000</v>
+        <v>287100</v>
       </c>
     </row>
     <row r="1118">
@@ -49379,10 +49379,10 @@
         <v>1</v>
       </c>
       <c r="N1119" t="n">
-        <v>1727.31</v>
+        <v>1728.3970421649</v>
       </c>
       <c r="O1119" t="n">
-        <v>1727.31</v>
+        <v>1728.3970421649</v>
       </c>
       <c r="P1119" t="n">
         <v>2850</v>
@@ -50076,10 +50076,10 @@
         <v>380</v>
       </c>
       <c r="N1135" t="n">
-        <v>22951.704779221</v>
+        <v>22951.704751958</v>
       </c>
       <c r="O1135" t="n">
-        <v>8721647.81610398</v>
+        <v>8721647.805744041</v>
       </c>
       <c r="P1135" t="n">
         <v>37900</v>
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="J1136" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1136" t="n">
         <v>0</v>
@@ -50114,19 +50114,19 @@
         <v>0</v>
       </c>
       <c r="M1136" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1136" t="n">
         <v>3238</v>
       </c>
       <c r="O1136" t="n">
-        <v>51808</v>
+        <v>48570</v>
       </c>
       <c r="P1136" t="n">
         <v>3300</v>
       </c>
       <c r="Q1136" t="n">
-        <v>52800</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="1137">
@@ -50304,10 +50304,10 @@
         <v>1</v>
       </c>
       <c r="N1140" t="n">
-        <v>1757.3205652174</v>
+        <v>1757.3205676856</v>
       </c>
       <c r="O1140" t="n">
-        <v>1757.3205652174</v>
+        <v>1757.3205676856</v>
       </c>
       <c r="P1140" t="n">
         <v>2000</v>
@@ -51382,7 +51382,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51391,19 +51391,19 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="N1164" t="n">
         <v>3872</v>
       </c>
       <c r="O1164" t="n">
-        <v>371712</v>
+        <v>344608</v>
       </c>
       <c r="P1164" t="n">
         <v>4900</v>
       </c>
       <c r="Q1164" t="n">
-        <v>470400</v>
+        <v>436100</v>
       </c>
     </row>
     <row r="1165">
@@ -51428,7 +51428,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51437,19 +51437,19 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N1165" t="n">
         <v>6160</v>
       </c>
       <c r="O1165" t="n">
-        <v>147840</v>
+        <v>141680</v>
       </c>
       <c r="P1165" t="n">
         <v>7900</v>
       </c>
       <c r="Q1165" t="n">
-        <v>189600</v>
+        <v>181700</v>
       </c>
     </row>
     <row r="1166">
@@ -51474,7 +51474,7 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -51483,19 +51483,19 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N1166" t="n">
         <v>4400</v>
       </c>
       <c r="O1166" t="n">
-        <v>365200</v>
+        <v>352000</v>
       </c>
       <c r="P1166" t="n">
         <v>5900</v>
       </c>
       <c r="Q1166" t="n">
-        <v>489700</v>
+        <v>472000</v>
       </c>
     </row>
     <row r="1167">
@@ -51520,7 +51520,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51529,19 +51529,19 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N1167" t="n">
         <v>3520</v>
       </c>
       <c r="O1167" t="n">
-        <v>151360</v>
+        <v>109120</v>
       </c>
       <c r="P1167" t="n">
         <v>4500</v>
       </c>
       <c r="Q1167" t="n">
-        <v>193500</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="1168">
@@ -51612,28 +51612,28 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N1169" t="n">
         <v>9240</v>
       </c>
       <c r="O1169" t="n">
-        <v>212520</v>
+        <v>166320</v>
       </c>
       <c r="P1169" t="n">
         <v>11500</v>
       </c>
       <c r="Q1169" t="n">
-        <v>264500</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="1170">
@@ -51704,7 +51704,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -51713,19 +51713,19 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N1171" t="n">
         <v>4576</v>
       </c>
       <c r="O1171" t="n">
-        <v>631488</v>
+        <v>613184</v>
       </c>
       <c r="P1171" t="n">
         <v>5900</v>
       </c>
       <c r="Q1171" t="n">
-        <v>814200</v>
+        <v>790600</v>
       </c>
     </row>
     <row r="1172">
@@ -51750,7 +51750,7 @@
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -51759,19 +51759,19 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N1172" t="n">
         <v>5280</v>
       </c>
       <c r="O1172" t="n">
-        <v>269280</v>
+        <v>264000</v>
       </c>
       <c r="P1172" t="n">
         <v>6900</v>
       </c>
       <c r="Q1172" t="n">
-        <v>351900</v>
+        <v>345000</v>
       </c>
     </row>
     <row r="1173">
@@ -53373,7 +53373,7 @@
         </is>
       </c>
       <c r="J1207" t="n">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="K1207" t="n">
         <v>0</v>
@@ -53382,19 +53382,19 @@
         <v>0</v>
       </c>
       <c r="M1207" t="n">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="N1207" t="n">
-        <v>2539.5715978456</v>
+        <v>2539.5716527391</v>
       </c>
       <c r="O1207" t="n">
-        <v>774569.337342908</v>
+        <v>693303.0611977744</v>
       </c>
       <c r="P1207" t="n">
         <v>3500</v>
       </c>
       <c r="Q1207" t="n">
-        <v>1067500</v>
+        <v>955500</v>
       </c>
     </row>
     <row r="1208">
@@ -53419,7 +53419,7 @@
         </is>
       </c>
       <c r="J1208" t="n">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="K1208" t="n">
         <v>0</v>
@@ -53428,19 +53428,19 @@
         <v>0</v>
       </c>
       <c r="M1208" t="n">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="N1208" t="n">
-        <v>4687.9744010648</v>
+        <v>4687.9744444444</v>
       </c>
       <c r="O1208" t="n">
-        <v>2540882.125377122</v>
+        <v>2489314.429999976</v>
       </c>
       <c r="P1208" t="n">
         <v>5900</v>
       </c>
       <c r="Q1208" t="n">
-        <v>3197800</v>
+        <v>3132900</v>
       </c>
     </row>
     <row r="1209">
@@ -53465,7 +53465,7 @@
         </is>
       </c>
       <c r="J1209" t="n">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="K1209" t="n">
         <v>0</v>
@@ -53474,19 +53474,19 @@
         <v>0</v>
       </c>
       <c r="M1209" t="n">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="N1209" t="n">
-        <v>4171.6686597938</v>
+        <v>4171.6686473988</v>
       </c>
       <c r="O1209" t="n">
-        <v>2623979.5870103</v>
+        <v>2590606.230034655</v>
       </c>
       <c r="P1209" t="n">
         <v>5500</v>
       </c>
       <c r="Q1209" t="n">
-        <v>3459500</v>
+        <v>3415500</v>
       </c>
     </row>
     <row r="1210">
@@ -61480,10 +61480,10 @@
         <v>26</v>
       </c>
       <c r="N1402" t="n">
-        <v>2403.9771641791</v>
+        <v>2403.9770542636</v>
       </c>
       <c r="O1402" t="n">
-        <v>62503.4062686566</v>
+        <v>62503.40341085361</v>
       </c>
       <c r="P1402" t="n">
         <v>3000</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -4132,10 +4132,10 @@
         <v>2</v>
       </c>
       <c r="N91" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O91" t="n">
-        <v>60148.148148148</v>
+        <v>58000</v>
       </c>
       <c r="P91" t="n">
         <v>34800</v>
@@ -11466,10 +11466,10 @@
         <v>280</v>
       </c>
       <c r="N263" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O263" t="n">
-        <v>4825759.12982464</v>
+        <v>4818074.8</v>
       </c>
       <c r="P263" t="n">
         <v>20000</v>
@@ -13187,10 +13187,10 @@
         <v>326</v>
       </c>
       <c r="N302" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O302" t="n">
-        <v>2871309.159574456</v>
+        <v>2867496</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
@@ -13983,10 +13983,10 @@
         <v>1</v>
       </c>
       <c r="N320" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="O320" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="P320" t="n">
         <v>9500</v>
@@ -15333,10 +15333,10 @@
         <v>1</v>
       </c>
       <c r="N351" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O351" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="P351" t="n">
         <v>20900</v>
@@ -15940,10 +15940,10 @@
         <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O365" t="n">
-        <v>35518007.98737095</v>
+        <v>35515468.2661299</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
@@ -16884,10 +16884,10 @@
         <v>1908</v>
       </c>
       <c r="N387" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O387" t="n">
-        <v>33340303.93495493</v>
+        <v>33338312.28</v>
       </c>
       <c r="P387" t="n">
         <v>2900</v>
@@ -16972,10 +16972,10 @@
         <v>1774</v>
       </c>
       <c r="N389" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O389" t="n">
-        <v>2715490.674372273</v>
+        <v>2715337.62</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -22826,10 +22826,10 @@
         <v>368</v>
       </c>
       <c r="N524" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O524" t="n">
-        <v>945659.5297450303</v>
+        <v>944656</v>
       </c>
       <c r="P524" t="n">
         <v>4500</v>
@@ -29402,10 +29402,10 @@
         <v>165</v>
       </c>
       <c r="N680" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O680" t="n">
-        <v>1317049.475038176</v>
+        <v>1315041.777709919</v>
       </c>
       <c r="P680" t="n">
         <v>12900</v>
@@ -29653,10 +29653,10 @@
         <v>19</v>
       </c>
       <c r="N686" t="n">
-        <v>10148.474923077</v>
+        <v>9994.710153846199</v>
       </c>
       <c r="O686" t="n">
-        <v>192821.023538463</v>
+        <v>189899.4929230778</v>
       </c>
       <c r="P686" t="n">
         <v>20800</v>
@@ -31534,10 +31534,10 @@
         <v>16</v>
       </c>
       <c r="N729" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O729" t="n">
-        <v>231162.72941176</v>
+        <v>230080</v>
       </c>
       <c r="P729" t="n">
         <v>23000</v>
@@ -35177,10 +35177,10 @@
         <v>1</v>
       </c>
       <c r="N808" t="n">
-        <v>23400.84</v>
+        <v>22942</v>
       </c>
       <c r="O808" t="n">
-        <v>23400.84</v>
+        <v>22942</v>
       </c>
       <c r="P808" t="n">
         <v>36900</v>
@@ -35407,10 +35407,10 @@
         <v>56</v>
       </c>
       <c r="N813" t="n">
-        <v>50584.365236051</v>
+        <v>50153.86</v>
       </c>
       <c r="O813" t="n">
-        <v>2832724.453218856</v>
+        <v>2808616.16</v>
       </c>
       <c r="P813" t="n">
         <v>11500</v>
@@ -36598,10 +36598,10 @@
         <v>1</v>
       </c>
       <c r="N839" t="n">
-        <v>9952.091954023001</v>
+        <v>9839</v>
       </c>
       <c r="O839" t="n">
-        <v>9952.091954023001</v>
+        <v>9839</v>
       </c>
       <c r="P839" t="n">
         <v>16900</v>
@@ -37835,10 +37835,10 @@
         <v>63</v>
       </c>
       <c r="N866" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O866" t="n">
-        <v>3777387.040582722</v>
+        <v>3769542</v>
       </c>
       <c r="P866" t="n">
         <v>7900</v>
@@ -37973,10 +37973,10 @@
         <v>88</v>
       </c>
       <c r="N869" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O869" t="n">
-        <v>903802.337531456</v>
+        <v>899272</v>
       </c>
       <c r="P869" t="n">
         <v>16900</v>
@@ -38804,10 +38804,10 @@
         <v>1542</v>
       </c>
       <c r="N887" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O887" t="n">
-        <v>5892987.457679227</v>
+        <v>5891982</v>
       </c>
       <c r="P887" t="n">
         <v>5900</v>
@@ -38850,10 +38850,10 @@
         <v>12</v>
       </c>
       <c r="N888" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O888" t="n">
-        <v>186147.500000004</v>
+        <v>185664</v>
       </c>
       <c r="P888" t="n">
         <v>25900</v>
@@ -38988,10 +38988,10 @@
         <v>1</v>
       </c>
       <c r="N891" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O891" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="P891" t="n">
         <v>8900</v>
@@ -39951,10 +39951,10 @@
         <v>4</v>
       </c>
       <c r="N912" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O912" t="n">
-        <v>21491.34685446</v>
+        <v>21390.92</v>
       </c>
       <c r="P912" t="n">
         <v>9500</v>
@@ -40499,10 +40499,10 @@
         <v>3</v>
       </c>
       <c r="N924" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O924" t="n">
-        <v>55963.911504426</v>
+        <v>55473</v>
       </c>
       <c r="P924" t="n">
         <v>13500</v>
@@ -46849,10 +46849,10 @@
         <v>3</v>
       </c>
       <c r="N1062" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O1062" t="n">
-        <v>15705.2320557492</v>
+        <v>15650.7</v>
       </c>
       <c r="P1062" t="n">
         <v>20500</v>
@@ -47037,10 +47037,10 @@
         <v>38</v>
       </c>
       <c r="N1066" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O1066" t="n">
-        <v>267899.2619719534</v>
+        <v>267783.7134412076</v>
       </c>
       <c r="P1066" t="n">
         <v>9900</v>
@@ -49379,10 +49379,10 @@
         <v>1</v>
       </c>
       <c r="N1119" t="n">
-        <v>1728.3970421649</v>
+        <v>1727.31</v>
       </c>
       <c r="O1119" t="n">
-        <v>1728.3970421649</v>
+        <v>1727.31</v>
       </c>
       <c r="P1119" t="n">
         <v>2850</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2816,22 +2816,22 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N59" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O59" t="n">
-        <v>259517.168873235</v>
+        <v>247159.20851064</v>
       </c>
       <c r="P59" t="n">
         <v>15900</v>
       </c>
       <c r="Q59" t="n">
-        <v>333900</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="60">
@@ -4900,22 +4900,22 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
-        <v>10994.361818182</v>
+        <v>10994.362222222</v>
       </c>
       <c r="O108" t="n">
-        <v>65966.170909092</v>
+        <v>54971.81111111</v>
       </c>
       <c r="P108" t="n">
         <v>16900</v>
       </c>
       <c r="Q108" t="n">
-        <v>101400</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="109">
@@ -5076,10 +5076,10 @@
         <v>9</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O112" t="n">
-        <v>141407.69059908</v>
+        <v>141407.690046732</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
@@ -5123,10 +5123,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>9392.0750746269</v>
+        <v>9392.075312499999</v>
       </c>
       <c r="O113" t="n">
-        <v>9392.0750746269</v>
+        <v>9392.075312499999</v>
       </c>
       <c r="P113" t="n">
         <v>18500</v>
@@ -5719,10 +5719,10 @@
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>22267.5525</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O128" t="n">
-        <v>44535.105</v>
+        <v>44535.105555556</v>
       </c>
       <c r="P128" t="n">
         <v>46300</v>
@@ -6235,10 +6235,10 @@
         <v>7</v>
       </c>
       <c r="N140" t="n">
-        <v>56906.803962264</v>
+        <v>56906.805744681</v>
       </c>
       <c r="O140" t="n">
-        <v>398347.627735848</v>
+        <v>398347.640212767</v>
       </c>
       <c r="P140" t="n">
         <v>95900</v>
@@ -6282,10 +6282,10 @@
         <v>10</v>
       </c>
       <c r="N141" t="n">
-        <v>62349.656875</v>
+        <v>62349.656129032</v>
       </c>
       <c r="O141" t="n">
-        <v>623496.56875</v>
+        <v>623496.56129032</v>
       </c>
       <c r="P141" t="n">
         <v>109900</v>
@@ -6329,10 +6329,10 @@
         <v>15</v>
       </c>
       <c r="N142" t="n">
-        <v>141416.88459016</v>
+        <v>141416.88460526</v>
       </c>
       <c r="O142" t="n">
-        <v>2121253.2688524</v>
+        <v>2121253.2690789</v>
       </c>
       <c r="P142" t="n">
         <v>251900</v>
@@ -6371,10 +6371,10 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="O143" t="n">
-        <v>200072.20183486</v>
+        <v>200072.20194444</v>
       </c>
       <c r="P143" t="n">
         <v>312000</v>
@@ -6413,10 +6413,10 @@
         <v>5</v>
       </c>
       <c r="N144" t="n">
-        <v>174389.79954545</v>
+        <v>174389.80095238</v>
       </c>
       <c r="O144" t="n">
-        <v>871948.99772725</v>
+        <v>871949.0047619001</v>
       </c>
       <c r="P144" t="n">
         <v>368200</v>
@@ -6551,10 +6551,10 @@
         <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="O147" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17844444</v>
       </c>
       <c r="P147" t="n">
         <v>532900</v>
@@ -7021,22 +7021,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N159" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O159" t="n">
-        <v>4933349.93186816</v>
+        <v>4871683.05862262</v>
       </c>
       <c r="P159" t="n">
         <v>98900</v>
       </c>
       <c r="Q159" t="n">
-        <v>7912000</v>
+        <v>7813100</v>
       </c>
     </row>
     <row r="160">
@@ -7622,22 +7622,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N173" t="n">
         <v>6187.41</v>
       </c>
       <c r="O173" t="n">
-        <v>216559.35</v>
+        <v>210371.94</v>
       </c>
       <c r="P173" t="n">
         <v>11500</v>
       </c>
       <c r="Q173" t="n">
-        <v>402500</v>
+        <v>391000</v>
       </c>
     </row>
     <row r="174">
@@ -9646,22 +9646,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M220" t="n">
-        <v>9152</v>
+        <v>9143</v>
       </c>
       <c r="N220" t="n">
         <v>1726.32</v>
       </c>
       <c r="O220" t="n">
-        <v>15799280.64</v>
+        <v>15783743.76</v>
       </c>
       <c r="P220" t="n">
         <v>1500</v>
       </c>
       <c r="Q220" t="n">
-        <v>13728000</v>
+        <v>13714500</v>
       </c>
     </row>
     <row r="221">
@@ -10203,10 +10203,10 @@
         <v>910</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0624184202</v>
+        <v>1098.0625007652</v>
       </c>
       <c r="O233" t="n">
-        <v>999236.800762382</v>
+        <v>999236.875696332</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -11327,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N260" t="n">
         <v>2093</v>
       </c>
       <c r="O260" t="n">
-        <v>535808</v>
+        <v>531622</v>
       </c>
       <c r="P260" t="n">
         <v>3550</v>
       </c>
       <c r="Q260" t="n">
-        <v>908800</v>
+        <v>901700</v>
       </c>
     </row>
     <row r="261">
@@ -11991,10 +11991,10 @@
         <v>836</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2554768392</v>
+        <v>2582.2554727273</v>
       </c>
       <c r="O275" t="n">
-        <v>2158765.578637571</v>
+        <v>2158765.575200023</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
@@ -14595,10 +14595,10 @@
         <v>358</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.253608522</v>
+        <v>3594.2536</v>
       </c>
       <c r="O334" t="n">
-        <v>1286742.791850876</v>
+        <v>1286742.7888</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
@@ -14905,10 +14905,10 @@
         <v>286</v>
       </c>
       <c r="N341" t="n">
-        <v>14822.378837068</v>
+        <v>14822.378836364</v>
       </c>
       <c r="O341" t="n">
-        <v>4239200.347401448</v>
+        <v>4239200.347200104</v>
       </c>
       <c r="P341" t="n">
         <v>24900</v>
@@ -15577,22 +15577,22 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M357" t="n">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="N357" t="n">
         <v>1441.01</v>
       </c>
       <c r="O357" t="n">
-        <v>3899373.06</v>
+        <v>3895050.03</v>
       </c>
       <c r="P357" t="n">
         <v>2100</v>
       </c>
       <c r="Q357" t="n">
-        <v>5682600</v>
+        <v>5676300</v>
       </c>
     </row>
     <row r="358">
@@ -16112,10 +16112,10 @@
         <v>355</v>
       </c>
       <c r="N369" t="n">
-        <v>1592.5660665658</v>
+        <v>1592.5660516325</v>
       </c>
       <c r="O369" t="n">
-        <v>565360.953630859</v>
+        <v>565360.9483295375</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
@@ -18522,10 +18522,10 @@
         <v>403</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O424" t="n">
-        <v>624728.1948728678</v>
+        <v>624728.1969941389</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -18614,10 +18614,10 @@
         <v>633</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5140171519</v>
+        <v>2403.5141965714</v>
       </c>
       <c r="O426" t="n">
-        <v>1521424.372857153</v>
+        <v>1521424.486429696</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
@@ -23239,10 +23239,10 @@
         <v>210</v>
       </c>
       <c r="N534" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O534" t="n">
-        <v>426273.537320568</v>
+        <v>426273.539104959</v>
       </c>
       <c r="P534" t="n">
         <v>3600</v>
@@ -25416,22 +25416,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M586" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N586" t="n">
-        <v>4285.1958525346</v>
+        <v>4285.1958592849</v>
       </c>
       <c r="O586" t="n">
-        <v>844183.5829493161</v>
+        <v>839898.3884198404</v>
       </c>
       <c r="P586" t="n">
         <v>6900</v>
       </c>
       <c r="Q586" t="n">
-        <v>1359300</v>
+        <v>1352400</v>
       </c>
     </row>
     <row r="587">
@@ -30881,22 +30881,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M715" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N715" t="n">
         <v>2634.61</v>
       </c>
       <c r="O715" t="n">
-        <v>136999.72</v>
+        <v>126461.28</v>
       </c>
       <c r="P715" t="n">
         <v>4200</v>
       </c>
       <c r="Q715" t="n">
-        <v>218400</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="716">
@@ -31157,22 +31157,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M721" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N721" t="n">
         <v>2495.98</v>
       </c>
       <c r="O721" t="n">
-        <v>202174.38</v>
+        <v>194686.44</v>
       </c>
       <c r="P721" t="n">
         <v>4100</v>
       </c>
       <c r="Q721" t="n">
-        <v>332100</v>
+        <v>319800</v>
       </c>
     </row>
     <row r="722">
@@ -31580,10 +31580,10 @@
         <v>2</v>
       </c>
       <c r="N730" t="n">
-        <v>1664.3497007042</v>
+        <v>1664.3491877256</v>
       </c>
       <c r="O730" t="n">
-        <v>3328.6994014084</v>
+        <v>3328.6983754512</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
@@ -32544,10 +32544,10 @@
         <v>1225</v>
       </c>
       <c r="N751" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O751" t="n">
-        <v>2178629.054263917</v>
+        <v>2178629.054774375</v>
       </c>
       <c r="P751" t="n">
         <v>4900</v>
@@ -35959,10 +35959,10 @@
         <v>15</v>
       </c>
       <c r="N825" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O825" t="n">
-        <v>73617.33567415801</v>
+        <v>73617.3358757055</v>
       </c>
       <c r="P825" t="n">
         <v>8200</v>
@@ -38568,22 +38568,22 @@
         <v>0</v>
       </c>
       <c r="L882" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M882" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N882" t="n">
         <v>10713.21</v>
       </c>
       <c r="O882" t="n">
-        <v>214264.2</v>
+        <v>192837.78</v>
       </c>
       <c r="P882" t="n">
         <v>20900</v>
       </c>
       <c r="Q882" t="n">
-        <v>418000</v>
+        <v>376200</v>
       </c>
     </row>
     <row r="883">
@@ -38660,22 +38660,22 @@
         <v>0</v>
       </c>
       <c r="L884" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M884" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N884" t="n">
         <v>12489</v>
       </c>
       <c r="O884" t="n">
-        <v>562005</v>
+        <v>549516</v>
       </c>
       <c r="P884" t="n">
         <v>20900</v>
       </c>
       <c r="Q884" t="n">
-        <v>940500</v>
+        <v>919600</v>
       </c>
     </row>
     <row r="885">
@@ -39541,10 +39541,10 @@
         <v>252</v>
       </c>
       <c r="N903" t="n">
-        <v>2056.082714437</v>
+        <v>2056.08270929</v>
       </c>
       <c r="O903" t="n">
-        <v>518132.844038124</v>
+        <v>518132.84274108</v>
       </c>
       <c r="P903" t="n">
         <v>2900</v>
@@ -39587,10 +39587,10 @@
         <v>138</v>
       </c>
       <c r="N904" t="n">
-        <v>3224.5689724311</v>
+        <v>3224.568981435</v>
       </c>
       <c r="O904" t="n">
-        <v>444990.5181954918</v>
+        <v>444990.51943803</v>
       </c>
       <c r="P904" t="n">
         <v>4500</v>
@@ -39866,10 +39866,10 @@
         <v>386</v>
       </c>
       <c r="N910" t="n">
-        <v>1592.2820519836</v>
+        <v>1592.2820684932</v>
       </c>
       <c r="O910" t="n">
-        <v>614620.8720656696</v>
+        <v>614620.8784383752</v>
       </c>
       <c r="P910" t="n">
         <v>2500</v>
@@ -39997,10 +39997,10 @@
         <v>187</v>
       </c>
       <c r="N913" t="n">
-        <v>2311.912006689</v>
+        <v>2311.9102135231</v>
       </c>
       <c r="O913" t="n">
-        <v>432327.545250843</v>
+        <v>432327.2099288197</v>
       </c>
       <c r="P913" t="n">
         <v>3500</v>
@@ -42542,10 +42542,10 @@
         <v>1136</v>
       </c>
       <c r="N969" t="n">
-        <v>517.2923857868</v>
+        <v>517.29240467717</v>
       </c>
       <c r="O969" t="n">
-        <v>587644.1502538047</v>
+        <v>587644.1717132651</v>
       </c>
       <c r="P969" t="n">
         <v>900</v>
@@ -42727,10 +42727,10 @@
         <v>1338</v>
       </c>
       <c r="N973" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O973" t="n">
-        <v>4162303.935122879</v>
+        <v>4162303.885847952</v>
       </c>
       <c r="P973" t="n">
         <v>4500</v>
@@ -47597,22 +47597,22 @@
         <v>0</v>
       </c>
       <c r="L1078" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1078" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N1078" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1078" t="n">
-        <v>1195860.24</v>
+        <v>1191278.4</v>
       </c>
       <c r="P1078" t="n">
         <v>7900</v>
       </c>
       <c r="Q1078" t="n">
-        <v>2061900</v>
+        <v>2054000</v>
       </c>
     </row>
     <row r="1079">
@@ -47646,22 +47646,22 @@
         <v>0</v>
       </c>
       <c r="L1079" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1079" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N1079" t="n">
         <v>3155</v>
       </c>
       <c r="O1079" t="n">
-        <v>1183125</v>
+        <v>1179970</v>
       </c>
       <c r="P1079" t="n">
         <v>5900</v>
       </c>
       <c r="Q1079" t="n">
-        <v>2212500</v>
+        <v>2206600</v>
       </c>
     </row>
     <row r="1080">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -9611,10 +9611,10 @@
         <v>12</v>
       </c>
       <c r="N219" t="n">
-        <v>33815</v>
+        <v>35594.736842105</v>
       </c>
       <c r="O219" t="n">
-        <v>405780</v>
+        <v>427136.84210526</v>
       </c>
       <c r="P219" t="n">
         <v>47900</v>
@@ -11985,22 +11985,22 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M275" t="n">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O275" t="n">
-        <v>2145854.293556321</v>
+        <v>2130360.755639078</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>3739500</v>
+        <v>3712500</v>
       </c>
     </row>
     <row r="276">
@@ -12164,22 +12164,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M279" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N279" t="n">
-        <v>2033.522992126</v>
+        <v>2033.5191735537</v>
       </c>
       <c r="O279" t="n">
-        <v>178950.023307088</v>
+        <v>166748.5722314034</v>
       </c>
       <c r="P279" t="n">
         <v>4100</v>
       </c>
       <c r="Q279" t="n">
-        <v>360800</v>
+        <v>336200</v>
       </c>
     </row>
     <row r="280">
@@ -13089,10 +13089,10 @@
         <v>284</v>
       </c>
       <c r="N300" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O300" t="n">
-        <v>2132098.76</v>
+        <v>2135168.736616284</v>
       </c>
       <c r="P300" t="n">
         <v>13500</v>
@@ -13187,10 +13187,10 @@
         <v>326</v>
       </c>
       <c r="N302" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O302" t="n">
-        <v>2867496</v>
+        <v>2878981.297730293</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
@@ -14638,22 +14638,22 @@
         <v>0</v>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M335" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="N335" t="n">
         <v>489.88</v>
       </c>
       <c r="O335" t="n">
-        <v>230243.6</v>
+        <v>228284.08</v>
       </c>
       <c r="P335" t="n">
         <v>700</v>
       </c>
       <c r="Q335" t="n">
-        <v>329000</v>
+        <v>326200</v>
       </c>
     </row>
     <row r="336">
@@ -15539,10 +15539,10 @@
         <v>16</v>
       </c>
       <c r="N356" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O356" t="n">
-        <v>253625.76</v>
+        <v>255622.813228352</v>
       </c>
       <c r="P356" t="n">
         <v>23900</v>
@@ -18516,22 +18516,22 @@
         <v>0</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M424" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O424" t="n">
-        <v>624728.2096590184</v>
+        <v>618527.4340967422</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>1007500</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="425">
@@ -18608,22 +18608,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M426" t="n">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O426" t="n">
-        <v>1509406.977003462</v>
+        <v>1502196.4402925</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2198000</v>
+        <v>2187500</v>
       </c>
     </row>
     <row r="427">
@@ -25711,22 +25711,22 @@
         <v>0</v>
       </c>
       <c r="L593" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M593" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="N593" t="n">
         <v>1106</v>
       </c>
       <c r="O593" t="n">
-        <v>306362</v>
+        <v>299726</v>
       </c>
       <c r="P593" t="n">
         <v>2100</v>
       </c>
       <c r="Q593" t="n">
-        <v>581700</v>
+        <v>569100</v>
       </c>
     </row>
     <row r="594">
@@ -31580,10 +31580,10 @@
         <v>9</v>
       </c>
       <c r="N730" t="n">
-        <v>15502</v>
+        <v>15634.495726496</v>
       </c>
       <c r="O730" t="n">
-        <v>139518</v>
+        <v>140710.461538464</v>
       </c>
       <c r="P730" t="n">
         <v>25900</v>
@@ -32498,10 +32498,10 @@
         <v>1225</v>
       </c>
       <c r="N750" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O750" t="n">
-        <v>2178629.058352722</v>
+        <v>2178629.058864527</v>
       </c>
       <c r="P750" t="n">
         <v>4900</v>
@@ -34530,10 +34530,10 @@
         <v>23</v>
       </c>
       <c r="N794" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O794" t="n">
-        <v>646668</v>
+        <v>658113.4513274319</v>
       </c>
       <c r="P794" t="n">
         <v>45900</v>
@@ -35355,22 +35355,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M812" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N812" t="n">
         <v>50153.86</v>
       </c>
       <c r="O812" t="n">
-        <v>2808616.16</v>
+        <v>2708308.44</v>
       </c>
       <c r="P812" t="n">
         <v>11500</v>
       </c>
       <c r="Q812" t="n">
-        <v>644000</v>
+        <v>621000</v>
       </c>
     </row>
     <row r="813">
@@ -37012,10 +37012,10 @@
         <v>20</v>
       </c>
       <c r="N848" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O848" t="n">
-        <v>543720</v>
+        <v>546191.4545454599</v>
       </c>
       <c r="P848" t="n">
         <v>43900</v>
@@ -37976,10 +37976,10 @@
         <v>183</v>
       </c>
       <c r="N869" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O869" t="n">
-        <v>1968165</v>
+        <v>1975082.978910435</v>
       </c>
       <c r="P869" t="n">
         <v>17900</v>
@@ -38528,10 +38528,10 @@
         <v>18</v>
       </c>
       <c r="N881" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O881" t="n">
-        <v>192837.78</v>
+        <v>194262.689704428</v>
       </c>
       <c r="P881" t="n">
         <v>20900</v>
@@ -39351,22 +39351,22 @@
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M899" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N899" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O899" t="n">
-        <v>533692.7148793344</v>
+        <v>530086.6842422005</v>
       </c>
       <c r="P899" t="n">
         <v>2500</v>
       </c>
       <c r="Q899" t="n">
-        <v>740000</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="900">
@@ -39991,22 +39991,22 @@
         <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M913" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N913" t="n">
-        <v>1906.180625</v>
+        <v>1906.1803846154</v>
       </c>
       <c r="O913" t="n">
-        <v>257334.384375</v>
+        <v>249709.6303846174</v>
       </c>
       <c r="P913" t="n">
         <v>2900</v>
       </c>
       <c r="Q913" t="n">
-        <v>391500</v>
+        <v>379900</v>
       </c>
     </row>
     <row r="914">
@@ -42813,10 +42813,10 @@
         <v>13678</v>
       </c>
       <c r="N975" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O975" t="n">
-        <v>9626507.606430747</v>
+        <v>9626507.598672859</v>
       </c>
       <c r="P975" t="n">
         <v>900</v>
@@ -51210,10 +51210,10 @@
         <v>4</v>
       </c>
       <c r="N1160" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O1160" t="n">
-        <v>29920</v>
+        <v>30099.3406593408</v>
       </c>
       <c r="P1160" t="n">
         <v>9500</v>
@@ -51618,22 +51618,22 @@
         <v>0</v>
       </c>
       <c r="L1169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1169" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1169" t="n">
         <v>4576</v>
       </c>
       <c r="O1169" t="n">
-        <v>594880</v>
+        <v>585728</v>
       </c>
       <c r="P1169" t="n">
         <v>5900</v>
       </c>
       <c r="Q1169" t="n">
-        <v>767000</v>
+        <v>755200</v>
       </c>
     </row>
     <row r="1170">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -2733,22 +2733,22 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N57" t="n">
-        <v>6272.8550526316</v>
+        <v>6272.8550704225</v>
       </c>
       <c r="O57" t="n">
-        <v>119184.2460000004</v>
+        <v>106638.5361971825</v>
       </c>
       <c r="P57" t="n">
         <v>7900</v>
       </c>
       <c r="Q57" t="n">
-        <v>150100</v>
+        <v>134300</v>
       </c>
     </row>
     <row r="58">
@@ -3178,22 +3178,22 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N68" t="n">
         <v>3526.1</v>
       </c>
       <c r="O68" t="n">
-        <v>229196.5</v>
+        <v>218618.2</v>
       </c>
       <c r="P68" t="n">
         <v>6300</v>
       </c>
       <c r="Q68" t="n">
-        <v>409500</v>
+        <v>390600</v>
       </c>
     </row>
     <row r="69">
@@ -5719,10 +5719,10 @@
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O128" t="n">
-        <v>47009.277777778</v>
+        <v>44535.105555556</v>
       </c>
       <c r="P128" t="n">
         <v>46300</v>
@@ -6504,10 +6504,10 @@
         <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>432516.155</v>
+        <v>288344.22</v>
       </c>
       <c r="O146" t="n">
-        <v>432516.155</v>
+        <v>288344.22</v>
       </c>
       <c r="P146" t="n">
         <v>450000</v>
@@ -9570,10 +9570,10 @@
         <v>619</v>
       </c>
       <c r="N218" t="n">
-        <v>2834.5536057033</v>
+        <v>2833</v>
       </c>
       <c r="O218" t="n">
-        <v>1754588.681930343</v>
+        <v>1753627</v>
       </c>
       <c r="P218" t="n">
         <v>3500</v>
@@ -10203,10 +10203,10 @@
         <v>886</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0627514701</v>
+        <v>1098.0628221049</v>
       </c>
       <c r="O233" t="n">
-        <v>972883.5978025086</v>
+        <v>972883.6603849415</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -11425,10 +11425,10 @@
         <v>299</v>
       </c>
       <c r="N262" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O262" t="n">
-        <v>4079120.01544034</v>
+        <v>4064411.65</v>
       </c>
       <c r="P262" t="n">
         <v>25500</v>
@@ -11676,10 +11676,10 @@
         <v>92</v>
       </c>
       <c r="N268" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O268" t="n">
-        <v>258363.9693906444</v>
+        <v>257998.36</v>
       </c>
       <c r="P268" t="n">
         <v>4900</v>
@@ -11991,10 +11991,10 @@
         <v>812</v>
       </c>
       <c r="N275" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O275" t="n">
-        <v>2098241.123761233</v>
+        <v>2096791.392173285</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
@@ -12037,10 +12037,10 @@
         <v>1383</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O276" t="n">
-        <v>7214967.183470652</v>
+        <v>7214967.181033669</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12416,10 +12416,10 @@
         <v>48</v>
       </c>
       <c r="N285" t="n">
-        <v>6754.0134146341</v>
+        <v>6713.08</v>
       </c>
       <c r="O285" t="n">
-        <v>324192.6439024368</v>
+        <v>322227.84</v>
       </c>
       <c r="P285" t="n">
         <v>9900</v>
@@ -12462,10 +12462,10 @@
         <v>2829</v>
       </c>
       <c r="N286" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O286" t="n">
-        <v>8943471.1987209</v>
+        <v>8936417.294475988</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
@@ -12864,10 +12864,10 @@
         <v>292</v>
       </c>
       <c r="N295" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O295" t="n">
-        <v>432793.046875</v>
+        <v>432160</v>
       </c>
       <c r="P295" t="n">
         <v>2600</v>
@@ -13187,10 +13187,10 @@
         <v>326</v>
       </c>
       <c r="N302" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O302" t="n">
-        <v>2871334.682730922</v>
+        <v>2867496</v>
       </c>
       <c r="P302" t="n">
         <v>14900</v>
@@ -13576,10 +13576,10 @@
         <v>536</v>
       </c>
       <c r="N311" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O311" t="n">
-        <v>1404060.325989661</v>
+        <v>1400444.72</v>
       </c>
       <c r="P311" t="n">
         <v>4900</v>
@@ -13663,10 +13663,10 @@
         <v>379</v>
       </c>
       <c r="N313" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O313" t="n">
-        <v>1653472.088840511</v>
+        <v>1651511.45</v>
       </c>
       <c r="P313" t="n">
         <v>7500</v>
@@ -13796,10 +13796,10 @@
         <v>306</v>
       </c>
       <c r="N316" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O316" t="n">
-        <v>1496624.595195532</v>
+        <v>1496624.595214412</v>
       </c>
       <c r="P316" t="n">
         <v>8200</v>
@@ -14382,10 +14382,10 @@
         <v>21</v>
       </c>
       <c r="N329" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O329" t="n">
-        <v>182090.1096173733</v>
+        <v>181902</v>
       </c>
       <c r="P329" t="n">
         <v>14200</v>
@@ -14595,10 +14595,10 @@
         <v>358</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O334" t="n">
-        <v>1286742.781137117</v>
+        <v>1286742.779598398</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
@@ -14644,10 +14644,10 @@
         <v>430</v>
       </c>
       <c r="N335" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="O335" t="n">
-        <v>215393.1786015956</v>
+        <v>210648.4</v>
       </c>
       <c r="P335" t="n">
         <v>700</v>
@@ -14905,10 +14905,10 @@
         <v>286</v>
       </c>
       <c r="N341" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O341" t="n">
-        <v>4246922.023606548</v>
+        <v>4239200.346593784</v>
       </c>
       <c r="P341" t="n">
         <v>24900</v>
@@ -15333,10 +15333,10 @@
         <v>1</v>
       </c>
       <c r="N351" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O351" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="P351" t="n">
         <v>20900</v>
@@ -15847,22 +15847,22 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M363" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N363" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O363" t="n">
-        <v>282874.3812765924</v>
+        <v>270707.7412250494</v>
       </c>
       <c r="P363" t="n">
         <v>5500</v>
       </c>
       <c r="Q363" t="n">
-        <v>511500</v>
+        <v>489500</v>
       </c>
     </row>
     <row r="364">
@@ -15888,22 +15888,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M364" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="N364" t="n">
         <v>3981.47</v>
       </c>
       <c r="O364" t="n">
-        <v>485739.34</v>
+        <v>461850.52</v>
       </c>
       <c r="P364" t="n">
         <v>7000</v>
       </c>
       <c r="Q364" t="n">
-        <v>854000</v>
+        <v>812000</v>
       </c>
     </row>
     <row r="365">
@@ -15940,10 +15940,10 @@
         <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O365" t="n">
-        <v>35515468.26889253</v>
+        <v>35535806.40390731</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
@@ -17016,10 +17016,10 @@
         <v>1</v>
       </c>
       <c r="N390" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O390" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="P390" t="n">
         <v>16900</v>
@@ -17285,10 +17285,10 @@
         <v>52</v>
       </c>
       <c r="N396" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O396" t="n">
-        <v>881928.6504672801</v>
+        <v>878644</v>
       </c>
       <c r="P396" t="n">
         <v>27900</v>
@@ -18253,10 +18253,10 @@
         <v>1</v>
       </c>
       <c r="N418" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O418" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="P418" t="n">
         <v>15900</v>
@@ -18522,10 +18522,10 @@
         <v>384</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O424" t="n">
-        <v>595274.53844928</v>
+        <v>595274.601165504</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -18614,10 +18614,10 @@
         <v>621</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O426" t="n">
-        <v>1492582.564702721</v>
+        <v>1583380.407083001</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
@@ -21943,10 +21943,10 @@
         <v>30</v>
       </c>
       <c r="N503" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O503" t="n">
-        <v>281907.444794952</v>
+        <v>280140</v>
       </c>
       <c r="P503" t="n">
         <v>15500</v>
@@ -22695,10 +22695,10 @@
         <v>252</v>
       </c>
       <c r="N521" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O521" t="n">
-        <v>2217459.642257337</v>
+        <v>2216208.96</v>
       </c>
       <c r="P521" t="n">
         <v>14500</v>
@@ -23113,10 +23113,10 @@
         <v>20</v>
       </c>
       <c r="N531" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O531" t="n">
-        <v>50471.425399496</v>
+        <v>50344.39999999999</v>
       </c>
       <c r="P531" t="n">
         <v>4200</v>
@@ -24361,10 +24361,10 @@
         <v>2</v>
       </c>
       <c r="N561" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O561" t="n">
-        <v>28322.146285714</v>
+        <v>28121.28</v>
       </c>
       <c r="P561" t="n">
         <v>22900</v>
@@ -25282,22 +25282,22 @@
         <v>0</v>
       </c>
       <c r="L583" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M583" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N583" t="n">
         <v>3877.89</v>
       </c>
       <c r="O583" t="n">
-        <v>849257.9099999999</v>
+        <v>825990.5699999999</v>
       </c>
       <c r="P583" t="n">
         <v>6500</v>
       </c>
       <c r="Q583" t="n">
-        <v>1423500</v>
+        <v>1384500</v>
       </c>
     </row>
     <row r="584">
@@ -25372,22 +25372,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M585" t="n">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="N585" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O585" t="n">
-        <v>835613.193879906</v>
+        <v>771335.274500586</v>
       </c>
       <c r="P585" t="n">
         <v>6900</v>
       </c>
       <c r="Q585" t="n">
-        <v>1345500</v>
+        <v>1242000</v>
       </c>
     </row>
     <row r="586">
@@ -26011,10 +26011,10 @@
         <v>3</v>
       </c>
       <c r="N600" t="n">
-        <v>12379.333333333</v>
+        <v>11980</v>
       </c>
       <c r="O600" t="n">
-        <v>37137.999999999</v>
+        <v>35940</v>
       </c>
       <c r="P600" t="n">
         <v>19500</v>
@@ -26057,10 +26057,10 @@
         <v>86</v>
       </c>
       <c r="N601" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O601" t="n">
-        <v>997136.249239456</v>
+        <v>994335.30433801</v>
       </c>
       <c r="P601" t="n">
         <v>18500</v>
@@ -26103,10 +26103,10 @@
         <v>2</v>
       </c>
       <c r="N602" t="n">
-        <v>13621.7524</v>
+        <v>13513.64328</v>
       </c>
       <c r="O602" t="n">
-        <v>27243.5048</v>
+        <v>27027.28656</v>
       </c>
       <c r="P602" t="n">
         <v>21900</v>
@@ -27965,10 +27965,10 @@
         <v>139</v>
       </c>
       <c r="N646" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O646" t="n">
-        <v>3874106.590196869</v>
+        <v>3770203.32952757</v>
       </c>
       <c r="P646" t="n">
         <v>44500</v>
@@ -28257,10 +28257,10 @@
         <v>72</v>
       </c>
       <c r="N653" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O653" t="n">
-        <v>1229063.188056336</v>
+        <v>1222177.68</v>
       </c>
       <c r="P653" t="n">
         <v>26900</v>
@@ -29568,10 +29568,10 @@
         <v>40</v>
       </c>
       <c r="N684" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="O684" t="n">
-        <v>387269.270056496</v>
+        <v>385093.6</v>
       </c>
       <c r="P684" t="n">
         <v>15900</v>
@@ -31718,10 +31718,10 @@
         <v>30</v>
       </c>
       <c r="N733" t="n">
-        <v>11048.707428571</v>
+        <v>10451.48</v>
       </c>
       <c r="O733" t="n">
-        <v>331461.22285713</v>
+        <v>313544.4</v>
       </c>
       <c r="P733" t="n">
         <v>16900</v>
@@ -31994,10 +31994,10 @@
         <v>67</v>
       </c>
       <c r="N739" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O739" t="n">
-        <v>1063120.659340691</v>
+        <v>1060208</v>
       </c>
       <c r="P739" t="n">
         <v>26900</v>
@@ -32408,10 +32408,10 @@
         <v>656</v>
       </c>
       <c r="N748" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O748" t="n">
-        <v>2292376.646808523</v>
+        <v>2286816</v>
       </c>
       <c r="P748" t="n">
         <v>6900</v>
@@ -32454,10 +32454,10 @@
         <v>1225</v>
       </c>
       <c r="N749" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O749" t="n">
-        <v>2178629.084658617</v>
+        <v>2178629.086219023</v>
       </c>
       <c r="P749" t="n">
         <v>4900</v>
@@ -34164,10 +34164,10 @@
         <v>56</v>
       </c>
       <c r="N786" t="n">
-        <v>32376.967005076</v>
+        <v>32295</v>
       </c>
       <c r="O786" t="n">
-        <v>1813110.152284256</v>
+        <v>1808520</v>
       </c>
       <c r="P786" t="n">
         <v>51900</v>
@@ -34716,10 +34716,10 @@
         <v>46</v>
       </c>
       <c r="N798" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O798" t="n">
-        <v>408127.6684738527</v>
+        <v>407475.36</v>
       </c>
       <c r="P798" t="n">
         <v>15500</v>
@@ -34854,10 +34854,10 @@
         <v>1</v>
       </c>
       <c r="N801" t="n">
-        <v>5040.7413333333</v>
+        <v>5014</v>
       </c>
       <c r="O801" t="n">
-        <v>5040.7413333333</v>
+        <v>5014</v>
       </c>
       <c r="P801" t="n">
         <v>8200</v>
@@ -35133,10 +35133,10 @@
         <v>447</v>
       </c>
       <c r="N807" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O807" t="n">
-        <v>1044571.56166875</v>
+        <v>1040669.05051875</v>
       </c>
       <c r="P807" t="n">
         <v>4500</v>
@@ -35225,10 +35225,10 @@
         <v>93</v>
       </c>
       <c r="N809" t="n">
-        <v>9384</v>
+        <v>9686.7096774194</v>
       </c>
       <c r="O809" t="n">
-        <v>872712</v>
+        <v>900864.0000000042</v>
       </c>
       <c r="P809" t="n">
         <v>15900</v>
@@ -35495,22 +35495,22 @@
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M815" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N815" t="n">
         <v>9178</v>
       </c>
       <c r="O815" t="n">
-        <v>1881490</v>
+        <v>1863134</v>
       </c>
       <c r="P815" t="n">
         <v>14900</v>
       </c>
       <c r="Q815" t="n">
-        <v>3054500</v>
+        <v>3024700</v>
       </c>
     </row>
     <row r="816">
@@ -36145,10 +36145,10 @@
         <v>9</v>
       </c>
       <c r="N829" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O829" t="n">
-        <v>35306.7127093593</v>
+        <v>35133.6413793105</v>
       </c>
       <c r="P829" t="n">
         <v>7500</v>
@@ -36278,10 +36278,10 @@
         <v>34</v>
       </c>
       <c r="N832" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O832" t="n">
-        <v>1132788.461538472</v>
+        <v>1122000</v>
       </c>
       <c r="P832" t="n">
         <v>52900</v>
@@ -36462,10 +36462,10 @@
         <v>11</v>
       </c>
       <c r="N836" t="n">
-        <v>12463.909090909</v>
+        <v>11922</v>
       </c>
       <c r="O836" t="n">
-        <v>137102.999999999</v>
+        <v>131142</v>
       </c>
       <c r="P836" t="n">
         <v>19900</v>
@@ -36830,10 +36830,10 @@
         <v>2</v>
       </c>
       <c r="N844" t="n">
-        <v>9751.4516129032</v>
+        <v>8637</v>
       </c>
       <c r="O844" t="n">
-        <v>19502.9032258064</v>
+        <v>17274</v>
       </c>
       <c r="P844" t="n">
         <v>14500</v>
@@ -37060,10 +37060,10 @@
         <v>184</v>
       </c>
       <c r="N849" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O849" t="n">
-        <v>2503604.594180736</v>
+        <v>2495960</v>
       </c>
       <c r="P849" t="n">
         <v>22500</v>
@@ -37106,10 +37106,10 @@
         <v>450</v>
       </c>
       <c r="N850" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O850" t="n">
-        <v>3441508.240223475</v>
+        <v>3435750</v>
       </c>
       <c r="P850" t="n">
         <v>13900</v>
@@ -37152,10 +37152,10 @@
         <v>65</v>
       </c>
       <c r="N851" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O851" t="n">
-        <v>369905.2803738305</v>
+        <v>369330</v>
       </c>
       <c r="P851" t="n">
         <v>9900</v>
@@ -38668,10 +38668,10 @@
         <v>27</v>
       </c>
       <c r="N884" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O884" t="n">
-        <v>589201.6288088519</v>
+        <v>587574</v>
       </c>
       <c r="P884" t="n">
         <v>35900</v>
@@ -38760,10 +38760,10 @@
         <v>12</v>
       </c>
       <c r="N886" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O886" t="n">
-        <v>186148.762402092</v>
+        <v>185664</v>
       </c>
       <c r="P886" t="n">
         <v>25900</v>
@@ -38898,10 +38898,10 @@
         <v>1</v>
       </c>
       <c r="N889" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O889" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="P889" t="n">
         <v>8900</v>
@@ -39724,22 +39724,22 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M907" t="n">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="N907" t="n">
         <v>2454</v>
       </c>
       <c r="O907" t="n">
-        <v>1992648</v>
+        <v>1977924</v>
       </c>
       <c r="P907" t="n">
         <v>4200</v>
       </c>
       <c r="Q907" t="n">
-        <v>3410400</v>
+        <v>3385200</v>
       </c>
     </row>
     <row r="908">
@@ -39776,10 +39776,10 @@
         <v>386</v>
       </c>
       <c r="N908" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="O908" t="n">
-        <v>614620.9105655026</v>
+        <v>690852.9614883694</v>
       </c>
       <c r="P908" t="n">
         <v>2500</v>
@@ -40872,10 +40872,10 @@
         <v>1</v>
       </c>
       <c r="N932" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O932" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="P932" t="n">
         <v>24900</v>
@@ -40915,22 +40915,22 @@
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M933" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="N933" t="n">
         <v>2857.22</v>
       </c>
       <c r="O933" t="n">
-        <v>1442896.1</v>
+        <v>1428610</v>
       </c>
       <c r="P933" t="n">
         <v>4900</v>
       </c>
       <c r="Q933" t="n">
-        <v>2474500</v>
+        <v>2450000</v>
       </c>
     </row>
     <row r="934">
@@ -42631,22 +42631,22 @@
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M971" t="n">
-        <v>1318</v>
+        <v>1303</v>
       </c>
       <c r="N971" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O971" t="n">
-        <v>4100086.911695372</v>
+        <v>4053424.256767679</v>
       </c>
       <c r="P971" t="n">
         <v>4500</v>
       </c>
       <c r="Q971" t="n">
-        <v>5931000</v>
+        <v>5863500</v>
       </c>
     </row>
     <row r="972">
@@ -43803,10 +43803,10 @@
         <v>24</v>
       </c>
       <c r="N997" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O997" t="n">
-        <v>446923.545806448</v>
+        <v>442169.04</v>
       </c>
       <c r="P997" t="n">
         <v>10000</v>
@@ -46947,10 +46947,10 @@
         <v>1</v>
       </c>
       <c r="N1064" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O1064" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="P1064" t="n">
         <v>27900</v>
@@ -47461,22 +47461,22 @@
         <v>0</v>
       </c>
       <c r="L1075" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1075" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="N1075" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1075" t="n">
-        <v>1191278.4</v>
+        <v>1163787.36</v>
       </c>
       <c r="P1075" t="n">
         <v>7900</v>
       </c>
       <c r="Q1075" t="n">
-        <v>2054000</v>
+        <v>2006600</v>
       </c>
     </row>
     <row r="1076">
@@ -51626,10 +51626,10 @@
         <v>128</v>
       </c>
       <c r="N1169" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O1169" t="n">
-        <v>588637.2450331136</v>
+        <v>585728</v>
       </c>
       <c r="P1169" t="n">
         <v>5900</v>
@@ -61027,10 +61027,10 @@
         <v>96</v>
       </c>
       <c r="N1392" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O1392" t="n">
-        <v>438338.0281690176</v>
+        <v>436800</v>
       </c>
       <c r="P1392" t="n">
         <v>5500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>17</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3142,19 +3142,19 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N67" t="n">
-        <v>2474.7040138408</v>
+        <v>2474.7039930556</v>
       </c>
       <c r="O67" t="n">
-        <v>712714.7559861505</v>
+        <v>707765.3420139017</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
       </c>
       <c r="Q67" t="n">
-        <v>1296000</v>
+        <v>1287000</v>
       </c>
     </row>
     <row r="68">
@@ -3172,28 +3172,28 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N68" t="n">
         <v>3526.1</v>
       </c>
       <c r="O68" t="n">
-        <v>218618.2</v>
+        <v>211566</v>
       </c>
       <c r="P68" t="n">
         <v>6300</v>
       </c>
       <c r="Q68" t="n">
-        <v>390600</v>
+        <v>378000</v>
       </c>
     </row>
     <row r="69">
@@ -4995,10 +4995,10 @@
         <v>8</v>
       </c>
       <c r="N110" t="n">
-        <v>16486.408196721</v>
+        <v>16486.408099174</v>
       </c>
       <c r="O110" t="n">
-        <v>131891.265573768</v>
+        <v>131891.264793392</v>
       </c>
       <c r="P110" t="n">
         <v>30500</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5031,19 +5031,19 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N111" t="n">
         <v>36762.36</v>
       </c>
       <c r="O111" t="n">
-        <v>2610127.56</v>
+        <v>2536602.84</v>
       </c>
       <c r="P111" t="n">
         <v>57100</v>
       </c>
       <c r="Q111" t="n">
-        <v>4054100</v>
+        <v>3939900</v>
       </c>
     </row>
     <row r="112">
@@ -5076,10 +5076,10 @@
         <v>9</v>
       </c>
       <c r="N112" t="n">
-        <v>15711.96478022</v>
+        <v>15711.964751381</v>
       </c>
       <c r="O112" t="n">
-        <v>141407.68302198</v>
+        <v>141407.682762429</v>
       </c>
       <c r="P112" t="n">
         <v>28500</v>
@@ -5123,10 +5123,10 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>9392.0755737705</v>
+        <v>9392.0756666667</v>
       </c>
       <c r="O113" t="n">
-        <v>9392.0755737705</v>
+        <v>9392.0756666667</v>
       </c>
       <c r="P113" t="n">
         <v>18500</v>
@@ -6235,10 +6235,10 @@
         <v>7</v>
       </c>
       <c r="N140" t="n">
-        <v>56906.805744681</v>
+        <v>56906.806444444</v>
       </c>
       <c r="O140" t="n">
-        <v>398347.640212767</v>
+        <v>398347.645111108</v>
       </c>
       <c r="P140" t="n">
         <v>95900</v>
@@ -6329,10 +6329,10 @@
         <v>15</v>
       </c>
       <c r="N142" t="n">
-        <v>141416.88460526</v>
+        <v>141416.88462046</v>
       </c>
       <c r="O142" t="n">
-        <v>2121253.2690789</v>
+        <v>2121253.2693069</v>
       </c>
       <c r="P142" t="n">
         <v>251900</v>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6368,19 +6368,19 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N143" t="n">
-        <v>200072.20205607</v>
+        <v>200072.20216981</v>
       </c>
       <c r="O143" t="n">
-        <v>200072.20205607</v>
+        <v>400144.40433962</v>
       </c>
       <c r="P143" t="n">
         <v>312000</v>
       </c>
       <c r="Q143" t="n">
-        <v>312000</v>
+        <v>624000</v>
       </c>
     </row>
     <row r="144">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6410,19 +6410,19 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N144" t="n">
-        <v>174389.80095238</v>
+        <v>174389.8025</v>
       </c>
       <c r="O144" t="n">
-        <v>871949.0047619001</v>
+        <v>1046338.815</v>
       </c>
       <c r="P144" t="n">
         <v>368200</v>
       </c>
       <c r="Q144" t="n">
-        <v>1841000</v>
+        <v>2209200</v>
       </c>
     </row>
     <row r="145">
@@ -6504,10 +6504,10 @@
         <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>288344.22</v>
+        <v>288344.57</v>
       </c>
       <c r="O146" t="n">
-        <v>288344.22</v>
+        <v>288344.57</v>
       </c>
       <c r="P146" t="n">
         <v>450000</v>
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -8609,19 +8609,19 @@
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N196" t="n">
-        <v>4333.614</v>
+        <v>4333.6175</v>
       </c>
       <c r="O196" t="n">
-        <v>17334.456</v>
+        <v>13000.8525</v>
       </c>
       <c r="P196" t="n">
         <v>7500</v>
       </c>
       <c r="Q196" t="n">
-        <v>30000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="197">
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9567,19 +9567,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="N218" t="n">
         <v>2833</v>
       </c>
       <c r="O218" t="n">
-        <v>1753627</v>
+        <v>1745128</v>
       </c>
       <c r="P218" t="n">
         <v>3500</v>
       </c>
       <c r="Q218" t="n">
-        <v>2166500</v>
+        <v>2156000</v>
       </c>
     </row>
     <row r="219">
@@ -10203,10 +10203,10 @@
         <v>886</v>
       </c>
       <c r="N233" t="n">
-        <v>1098.0628221049</v>
+        <v>1098.062979056</v>
       </c>
       <c r="O233" t="n">
-        <v>972883.6603849415</v>
+        <v>972883.7994436159</v>
       </c>
       <c r="P233" t="n">
         <v>1500</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -11330,19 +11330,19 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N260" t="n">
         <v>2093</v>
       </c>
       <c r="O260" t="n">
-        <v>531622</v>
+        <v>529529</v>
       </c>
       <c r="P260" t="n">
         <v>3550</v>
       </c>
       <c r="Q260" t="n">
-        <v>901700</v>
+        <v>898150</v>
       </c>
     </row>
     <row r="261">
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="J275" t="n">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -11988,19 +11988,19 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2554090804</v>
+        <v>2582.2554027233</v>
       </c>
       <c r="O275" t="n">
-        <v>2096791.392173285</v>
+        <v>2081297.85459498</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
       </c>
       <c r="Q275" t="n">
-        <v>3654000</v>
+        <v>3627000</v>
       </c>
     </row>
     <row r="276">
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="J276" t="n">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
@@ -12034,19 +12034,19 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="N276" t="n">
-        <v>5216.8960094242</v>
+        <v>5216.8960047177</v>
       </c>
       <c r="O276" t="n">
-        <v>7214967.181033669</v>
+        <v>7194099.590505708</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
       </c>
       <c r="Q276" t="n">
-        <v>11755500</v>
+        <v>11721500</v>
       </c>
     </row>
     <row r="277">
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12167,19 +12167,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N279" t="n">
-        <v>2033.5191735537</v>
+        <v>2033.5178151261</v>
       </c>
       <c r="O279" t="n">
-        <v>166748.5722314034</v>
+        <v>162681.425210088</v>
       </c>
       <c r="P279" t="n">
         <v>4100</v>
       </c>
       <c r="Q279" t="n">
-        <v>336200</v>
+        <v>328000</v>
       </c>
     </row>
     <row r="280">
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>2829</v>
+        <v>2809</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12459,19 +12459,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>2829</v>
+        <v>2809</v>
       </c>
       <c r="N286" t="n">
-        <v>3158.8608322644</v>
+        <v>3158.8608345701</v>
       </c>
       <c r="O286" t="n">
-        <v>8936417.294475988</v>
+        <v>8873240.084307412</v>
       </c>
       <c r="P286" t="n">
         <v>5600</v>
       </c>
       <c r="Q286" t="n">
-        <v>15842400</v>
+        <v>15730400</v>
       </c>
     </row>
     <row r="287">
@@ -12554,10 +12554,10 @@
         <v>222</v>
       </c>
       <c r="N288" t="n">
-        <v>3841.6249390244</v>
+        <v>3841.6250103093</v>
       </c>
       <c r="O288" t="n">
-        <v>852840.7364634168</v>
+        <v>852840.7522886646</v>
       </c>
       <c r="P288" t="n">
         <v>6900</v>
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="J292" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -12733,19 +12733,19 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N292" t="n">
-        <v>3230.0666985646</v>
+        <v>3230.0666176471</v>
       </c>
       <c r="O292" t="n">
-        <v>226104.668899522</v>
+        <v>216414.4633823557</v>
       </c>
       <c r="P292" t="n">
         <v>6200</v>
       </c>
       <c r="Q292" t="n">
-        <v>434000</v>
+        <v>415400</v>
       </c>
     </row>
     <row r="293">
@@ -12956,10 +12956,10 @@
         <v>32</v>
       </c>
       <c r="N297" t="n">
-        <v>2694.8231444759</v>
+        <v>2694.8231379962</v>
       </c>
       <c r="O297" t="n">
-        <v>86234.3406232288</v>
+        <v>86234.3404158784</v>
       </c>
       <c r="P297" t="n">
         <v>4900</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -13358,19 +13358,19 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N306" t="n">
         <v>3719.06</v>
       </c>
       <c r="O306" t="n">
-        <v>442568.14</v>
+        <v>438849.08</v>
       </c>
       <c r="P306" t="n">
         <v>6000</v>
       </c>
       <c r="Q306" t="n">
-        <v>714000</v>
+        <v>708000</v>
       </c>
     </row>
     <row r="307">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -13793,19 +13793,19 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N316" t="n">
-        <v>4890.9300497203</v>
+        <v>4890.9300498132</v>
       </c>
       <c r="O316" t="n">
-        <v>1496624.595214412</v>
+        <v>1481951.805093399</v>
       </c>
       <c r="P316" t="n">
         <v>8200</v>
       </c>
       <c r="Q316" t="n">
-        <v>2509200</v>
+        <v>2484600</v>
       </c>
     </row>
     <row r="317">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -13888,19 +13888,19 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N318" t="n">
         <v>1203.38</v>
       </c>
       <c r="O318" t="n">
-        <v>567995.3600000001</v>
+        <v>561978.4600000001</v>
       </c>
       <c r="P318" t="n">
         <v>1900</v>
       </c>
       <c r="Q318" t="n">
-        <v>896800</v>
+        <v>887300</v>
       </c>
     </row>
     <row r="319">
@@ -14595,10 +14595,10 @@
         <v>358</v>
       </c>
       <c r="N334" t="n">
-        <v>3594.2535742972</v>
+        <v>3594.2535483871</v>
       </c>
       <c r="O334" t="n">
-        <v>1286742.779598398</v>
+        <v>1286742.770322582</v>
       </c>
       <c r="P334" t="n">
         <v>6500</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -14641,19 +14641,19 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="N335" t="n">
         <v>489.88</v>
       </c>
       <c r="O335" t="n">
-        <v>210648.4</v>
+        <v>207709.12</v>
       </c>
       <c r="P335" t="n">
         <v>700</v>
       </c>
       <c r="Q335" t="n">
-        <v>301000</v>
+        <v>296800</v>
       </c>
     </row>
     <row r="336">
@@ -14767,10 +14767,10 @@
         <v>1</v>
       </c>
       <c r="N338" t="n">
-        <v>3240.8500422833</v>
+        <v>3240.8500449438</v>
       </c>
       <c r="O338" t="n">
-        <v>3240.8500422833</v>
+        <v>3240.8500449438</v>
       </c>
       <c r="P338" t="n">
         <v>5200</v>
@@ -14905,10 +14905,10 @@
         <v>286</v>
       </c>
       <c r="N341" t="n">
-        <v>14822.378834244</v>
+        <v>14822.378831406</v>
       </c>
       <c r="O341" t="n">
-        <v>4239200.346593784</v>
+        <v>4239200.345782116</v>
       </c>
       <c r="P341" t="n">
         <v>24900</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="J355" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K355" t="n">
         <v>0</v>
@@ -15492,19 +15492,19 @@
         <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N355" t="n">
         <v>2696.09</v>
       </c>
       <c r="O355" t="n">
-        <v>703679.49</v>
+        <v>700983.4</v>
       </c>
       <c r="P355" t="n">
         <v>8200</v>
       </c>
       <c r="Q355" t="n">
-        <v>2140200</v>
+        <v>2132000</v>
       </c>
     </row>
     <row r="356">
@@ -15751,7 +15751,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15760,19 +15760,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N361" t="n">
-        <v>4242.5422384428</v>
+        <v>4242.5422439024</v>
       </c>
       <c r="O361" t="n">
-        <v>1637621.304038921</v>
+        <v>1633378.763902424</v>
       </c>
       <c r="P361" t="n">
         <v>5900</v>
       </c>
       <c r="Q361" t="n">
-        <v>2277400</v>
+        <v>2271500</v>
       </c>
     </row>
     <row r="362">
@@ -15841,28 +15841,28 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N363" t="n">
-        <v>3041.6600137646</v>
+        <v>3041.6600137931</v>
       </c>
       <c r="O363" t="n">
-        <v>270707.7412250494</v>
+        <v>261582.7611862066</v>
       </c>
       <c r="P363" t="n">
         <v>5500</v>
       </c>
       <c r="Q363" t="n">
-        <v>489500</v>
+        <v>473000</v>
       </c>
     </row>
     <row r="364">
@@ -15882,28 +15882,28 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N364" t="n">
         <v>3981.47</v>
       </c>
       <c r="O364" t="n">
-        <v>461850.52</v>
+        <v>453887.58</v>
       </c>
       <c r="P364" t="n">
         <v>7000</v>
       </c>
       <c r="Q364" t="n">
-        <v>812000</v>
+        <v>798000</v>
       </c>
     </row>
     <row r="365">
@@ -15940,10 +15940,10 @@
         <v>8123</v>
       </c>
       <c r="N365" t="n">
-        <v>4374.7145640659</v>
+        <v>4372.2107930714</v>
       </c>
       <c r="O365" t="n">
-        <v>35535806.40390731</v>
+        <v>35515468.27211899</v>
       </c>
       <c r="P365" t="n">
         <v>7500</v>
@@ -16100,7 +16100,7 @@
         </is>
       </c>
       <c r="J369" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -16109,19 +16109,19 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="N369" t="n">
-        <v>1592.5657792208</v>
+        <v>1592.565713108</v>
       </c>
       <c r="O369" t="n">
-        <v>558990.5885065008</v>
+        <v>539879.776743612</v>
       </c>
       <c r="P369" t="n">
         <v>3900</v>
       </c>
       <c r="Q369" t="n">
-        <v>1368900</v>
+        <v>1322100</v>
       </c>
     </row>
     <row r="370">
@@ -16141,7 +16141,7 @@
         </is>
       </c>
       <c r="J370" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -16150,19 +16150,19 @@
         <v>0</v>
       </c>
       <c r="M370" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N370" t="n">
         <v>4513.76</v>
       </c>
       <c r="O370" t="n">
-        <v>302421.92</v>
+        <v>297908.16</v>
       </c>
       <c r="P370" t="n">
         <v>8900</v>
       </c>
       <c r="Q370" t="n">
-        <v>596300</v>
+        <v>587400</v>
       </c>
     </row>
     <row r="371">
@@ -16656,7 +16656,7 @@
         </is>
       </c>
       <c r="J382" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16665,19 +16665,19 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N382" t="n">
         <v>6242.93</v>
       </c>
       <c r="O382" t="n">
-        <v>2241211.87</v>
+        <v>2234968.94</v>
       </c>
       <c r="P382" t="n">
         <v>10400</v>
       </c>
       <c r="Q382" t="n">
-        <v>3733600</v>
+        <v>3723200</v>
       </c>
     </row>
     <row r="383">
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16714,19 +16714,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N383" t="n">
         <v>4648.6</v>
       </c>
       <c r="O383" t="n">
-        <v>1059880.8</v>
+        <v>1050583.6</v>
       </c>
       <c r="P383" t="n">
         <v>8900</v>
       </c>
       <c r="Q383" t="n">
-        <v>2029200</v>
+        <v>2011400</v>
       </c>
     </row>
     <row r="384">
@@ -16843,10 +16843,10 @@
         <v>2547</v>
       </c>
       <c r="N386" t="n">
-        <v>1532.6290265229</v>
+        <v>1532.6290255288</v>
       </c>
       <c r="O386" t="n">
-        <v>3903606.130553826</v>
+        <v>3903606.128021854</v>
       </c>
       <c r="P386" t="n">
         <v>1200</v>
@@ -17048,7 +17048,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>2195</v>
+        <v>2187</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17057,19 +17057,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>2195</v>
+        <v>2187</v>
       </c>
       <c r="N391" t="n">
         <v>1387.55</v>
       </c>
       <c r="O391" t="n">
-        <v>3045672.25</v>
+        <v>3034571.85</v>
       </c>
       <c r="P391" t="n">
         <v>2300</v>
       </c>
       <c r="Q391" t="n">
-        <v>5048500</v>
+        <v>5030100</v>
       </c>
     </row>
     <row r="392">
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -18427,19 +18427,19 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9239968815</v>
+        <v>1630.9240698598</v>
       </c>
       <c r="O422" t="n">
-        <v>401207.303232849</v>
+        <v>368588.8397883148</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
       </c>
       <c r="Q422" t="n">
-        <v>615000</v>
+        <v>565000</v>
       </c>
     </row>
     <row r="423">
@@ -18510,7 +18510,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -18519,19 +18519,19 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1942738685</v>
+        <v>1550.1941645158</v>
       </c>
       <c r="O424" t="n">
-        <v>595274.601165504</v>
+        <v>589073.7825160039</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
       </c>
       <c r="Q424" t="n">
-        <v>960000</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="425">
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
@@ -18565,19 +18565,19 @@
         <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="N425" t="n">
-        <v>1579.3881518152</v>
+        <v>1579.3874912892</v>
       </c>
       <c r="O425" t="n">
-        <v>131089.2166006616</v>
+        <v>124771.6118118468</v>
       </c>
       <c r="P425" t="n">
         <v>2900</v>
       </c>
       <c r="Q425" t="n">
-        <v>240700</v>
+        <v>229100</v>
       </c>
     </row>
     <row r="426">
@@ -18602,7 +18602,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -18611,19 +18611,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="N426" t="n">
-        <v>2549.7269035153</v>
+        <v>2403.5147075539</v>
       </c>
       <c r="O426" t="n">
-        <v>1583380.407083001</v>
+        <v>1485372.08926831</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
       </c>
       <c r="Q426" t="n">
-        <v>2173500</v>
+        <v>2163000</v>
       </c>
     </row>
     <row r="427">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
@@ -18701,19 +18701,19 @@
         <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="N428" t="n">
-        <v>2521.4820175439</v>
+        <v>2521.4791818182</v>
       </c>
       <c r="O428" t="n">
-        <v>274841.5399122851</v>
+        <v>264755.3140909109</v>
       </c>
       <c r="P428" t="n">
         <v>3900</v>
       </c>
       <c r="Q428" t="n">
-        <v>425100</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="429">
@@ -20056,7 +20056,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -20065,19 +20065,19 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N459" t="n">
         <v>3253</v>
       </c>
       <c r="O459" t="n">
-        <v>104096</v>
+        <v>100843</v>
       </c>
       <c r="P459" t="n">
         <v>3900</v>
       </c>
       <c r="Q459" t="n">
-        <v>124800</v>
+        <v>120900</v>
       </c>
     </row>
     <row r="460">
@@ -20489,7 +20489,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -20498,19 +20498,19 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N469" t="n">
         <v>3253</v>
       </c>
       <c r="O469" t="n">
-        <v>71566</v>
+        <v>68313</v>
       </c>
       <c r="P469" t="n">
         <v>3900</v>
       </c>
       <c r="Q469" t="n">
-        <v>85800</v>
+        <v>81900</v>
       </c>
     </row>
     <row r="470">
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -22107,19 +22107,19 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N507" t="n">
-        <v>4196.8725389755</v>
+        <v>4196.8725410978</v>
       </c>
       <c r="O507" t="n">
-        <v>1510874.11403118</v>
+        <v>1506677.24225411</v>
       </c>
       <c r="P507" t="n">
         <v>5900</v>
       </c>
       <c r="Q507" t="n">
-        <v>2124000</v>
+        <v>2118100</v>
       </c>
     </row>
     <row r="508">
@@ -22229,7 +22229,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -22238,19 +22238,19 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N510" t="n">
         <v>8538</v>
       </c>
       <c r="O510" t="n">
-        <v>59766</v>
+        <v>42690</v>
       </c>
       <c r="P510" t="n">
         <v>12900</v>
       </c>
       <c r="Q510" t="n">
-        <v>90300</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="511">
@@ -23429,7 +23429,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -23438,19 +23438,19 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N539" t="n">
         <v>2673</v>
       </c>
       <c r="O539" t="n">
-        <v>769824</v>
+        <v>764478</v>
       </c>
       <c r="P539" t="n">
         <v>2500</v>
       </c>
       <c r="Q539" t="n">
-        <v>720000</v>
+        <v>715000</v>
       </c>
     </row>
     <row r="540">
@@ -23806,7 +23806,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -23815,19 +23815,19 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N548" t="n">
         <v>15355</v>
       </c>
       <c r="O548" t="n">
-        <v>1289820</v>
+        <v>1274465</v>
       </c>
       <c r="P548" t="n">
         <v>17900</v>
       </c>
       <c r="Q548" t="n">
-        <v>1503600</v>
+        <v>1485700</v>
       </c>
     </row>
     <row r="549">
@@ -24023,10 +24023,10 @@
         <v>584</v>
       </c>
       <c r="N553" t="n">
-        <v>880.32965533864</v>
+        <v>880.32968334542</v>
       </c>
       <c r="O553" t="n">
-        <v>514112.5187177657</v>
+        <v>514112.5350737253</v>
       </c>
       <c r="P553" t="n">
         <v>1200</v>
@@ -25276,28 +25276,28 @@
         </is>
       </c>
       <c r="J583" t="n">
-        <v>219</v>
+        <v>450</v>
       </c>
       <c r="K583" t="n">
         <v>0</v>
       </c>
       <c r="L583" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M583" t="n">
-        <v>213</v>
+        <v>450</v>
       </c>
       <c r="N583" t="n">
         <v>3877.89</v>
       </c>
       <c r="O583" t="n">
-        <v>825990.5699999999</v>
+        <v>1745050.5</v>
       </c>
       <c r="P583" t="n">
         <v>6500</v>
       </c>
       <c r="Q583" t="n">
-        <v>1384500</v>
+        <v>2925000</v>
       </c>
     </row>
     <row r="584">
@@ -25366,28 +25366,28 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N585" t="n">
-        <v>4285.1959694477</v>
+        <v>4285.1960260973</v>
       </c>
       <c r="O585" t="n">
-        <v>771335.274500586</v>
+        <v>754194.5005931248</v>
       </c>
       <c r="P585" t="n">
         <v>6900</v>
       </c>
       <c r="Q585" t="n">
-        <v>1242000</v>
+        <v>1214400</v>
       </c>
     </row>
     <row r="586">
@@ -26103,10 +26103,10 @@
         <v>2</v>
       </c>
       <c r="N602" t="n">
-        <v>13513.64328</v>
+        <v>13513.643306452</v>
       </c>
       <c r="O602" t="n">
-        <v>27027.28656</v>
+        <v>27027.286612904</v>
       </c>
       <c r="P602" t="n">
         <v>21900</v>
@@ -27692,7 +27692,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -27701,19 +27701,19 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N640" t="n">
         <v>22730.48</v>
       </c>
       <c r="O640" t="n">
-        <v>1136524</v>
+        <v>1113793.52</v>
       </c>
       <c r="P640" t="n">
         <v>36900</v>
       </c>
       <c r="Q640" t="n">
-        <v>1845000</v>
+        <v>1808100</v>
       </c>
     </row>
     <row r="641">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
@@ -28638,19 +28638,19 @@
         <v>0</v>
       </c>
       <c r="M662" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N662" t="n">
-        <v>1561.0030188679</v>
+        <v>1561.003125</v>
       </c>
       <c r="O662" t="n">
-        <v>271614.5252830146</v>
+        <v>266931.534375</v>
       </c>
       <c r="P662" t="n">
         <v>2900</v>
       </c>
       <c r="Q662" t="n">
-        <v>504600</v>
+        <v>495900</v>
       </c>
     </row>
     <row r="663">
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -29565,19 +29565,19 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N684" t="n">
         <v>9627.34</v>
       </c>
       <c r="O684" t="n">
-        <v>385093.6</v>
+        <v>375466.26</v>
       </c>
       <c r="P684" t="n">
         <v>15900</v>
       </c>
       <c r="Q684" t="n">
-        <v>636000</v>
+        <v>620100</v>
       </c>
     </row>
     <row r="685">
@@ -32454,10 +32454,10 @@
         <v>1225</v>
       </c>
       <c r="N749" t="n">
-        <v>1778.4727234441</v>
+        <v>1778.4727448514</v>
       </c>
       <c r="O749" t="n">
-        <v>2178629.086219023</v>
+        <v>2178629.112442965</v>
       </c>
       <c r="P749" t="n">
         <v>4900</v>
@@ -34704,7 +34704,7 @@
         </is>
       </c>
       <c r="J798" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K798" t="n">
         <v>0</v>
@@ -34713,19 +34713,19 @@
         <v>0</v>
       </c>
       <c r="M798" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N798" t="n">
         <v>8858.16</v>
       </c>
       <c r="O798" t="n">
-        <v>407475.36</v>
+        <v>398617.2</v>
       </c>
       <c r="P798" t="n">
         <v>15500</v>
       </c>
       <c r="Q798" t="n">
-        <v>713000</v>
+        <v>697500</v>
       </c>
     </row>
     <row r="799">
@@ -35225,10 +35225,10 @@
         <v>93</v>
       </c>
       <c r="N809" t="n">
-        <v>9686.7096774194</v>
+        <v>9384</v>
       </c>
       <c r="O809" t="n">
-        <v>900864.0000000042</v>
+        <v>872712</v>
       </c>
       <c r="P809" t="n">
         <v>15900</v>
@@ -35443,7 +35443,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -35452,19 +35452,19 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N814" t="n">
         <v>9003</v>
       </c>
       <c r="O814" t="n">
-        <v>720240</v>
+        <v>711237</v>
       </c>
       <c r="P814" t="n">
         <v>14900</v>
       </c>
       <c r="Q814" t="n">
-        <v>1192000</v>
+        <v>1177100</v>
       </c>
     </row>
     <row r="815">
@@ -35489,13 +35489,13 @@
         </is>
       </c>
       <c r="J815" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K815" t="n">
         <v>0</v>
       </c>
       <c r="L815" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M815" t="n">
         <v>203</v>
@@ -35535,7 +35535,7 @@
         </is>
       </c>
       <c r="J816" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K816" t="n">
         <v>0</v>
@@ -35544,19 +35544,19 @@
         <v>0</v>
       </c>
       <c r="M816" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N816" t="n">
         <v>4544</v>
       </c>
       <c r="O816" t="n">
-        <v>1185984</v>
+        <v>1181440</v>
       </c>
       <c r="P816" t="n">
         <v>7900</v>
       </c>
       <c r="Q816" t="n">
-        <v>2061900</v>
+        <v>2054000</v>
       </c>
     </row>
     <row r="817">
@@ -35869,10 +35869,10 @@
         <v>15</v>
       </c>
       <c r="N823" t="n">
-        <v>4907.8224423077</v>
+        <v>4907.822504931</v>
       </c>
       <c r="O823" t="n">
-        <v>73617.33663461549</v>
+        <v>73617.33757396501</v>
       </c>
       <c r="P823" t="n">
         <v>8200</v>
@@ -36145,10 +36145,10 @@
         <v>9</v>
       </c>
       <c r="N829" t="n">
-        <v>3903.7379310345</v>
+        <v>3903.7383067896</v>
       </c>
       <c r="O829" t="n">
-        <v>35133.6413793105</v>
+        <v>35133.6447611064</v>
       </c>
       <c r="P829" t="n">
         <v>7500</v>
@@ -36450,7 +36450,7 @@
         </is>
       </c>
       <c r="J836" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K836" t="n">
         <v>0</v>
@@ -36459,19 +36459,19 @@
         <v>0</v>
       </c>
       <c r="M836" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N836" t="n">
         <v>11922</v>
       </c>
       <c r="O836" t="n">
-        <v>131142</v>
+        <v>119220</v>
       </c>
       <c r="P836" t="n">
         <v>19900</v>
       </c>
       <c r="Q836" t="n">
-        <v>218900</v>
+        <v>199000</v>
       </c>
     </row>
     <row r="837">
@@ -36634,7 +36634,7 @@
         </is>
       </c>
       <c r="J840" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K840" t="n">
         <v>0</v>
@@ -36643,19 +36643,19 @@
         <v>0</v>
       </c>
       <c r="M840" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N840" t="n">
         <v>6849.2</v>
       </c>
       <c r="O840" t="n">
-        <v>82190.39999999999</v>
+        <v>68492</v>
       </c>
       <c r="P840" t="n">
         <v>11500</v>
       </c>
       <c r="Q840" t="n">
-        <v>138000</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="841">
@@ -39027,7 +39027,7 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
@@ -39036,19 +39036,19 @@
         <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="N892" t="n">
-        <v>1516.0387724372</v>
+        <v>1516.0387635597</v>
       </c>
       <c r="O892" t="n">
-        <v>1943561.70626449</v>
+        <v>1928401.307247939</v>
       </c>
       <c r="P892" t="n">
         <v>2300</v>
       </c>
       <c r="Q892" t="n">
-        <v>2948600</v>
+        <v>2925600</v>
       </c>
     </row>
     <row r="893">
@@ -39117,7 +39117,7 @@
         </is>
       </c>
       <c r="J894" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
@@ -39126,19 +39126,19 @@
         <v>0</v>
       </c>
       <c r="M894" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N894" t="n">
-        <v>2458.5128114246</v>
+        <v>2458.5127187173</v>
       </c>
       <c r="O894" t="n">
-        <v>656422.9206503682</v>
+        <v>649047.3577413672</v>
       </c>
       <c r="P894" t="n">
         <v>3500</v>
       </c>
       <c r="Q894" t="n">
-        <v>934500</v>
+        <v>924000</v>
       </c>
     </row>
     <row r="895">
@@ -39175,10 +39175,10 @@
         <v>5</v>
       </c>
       <c r="N895" t="n">
-        <v>1907.3928289474</v>
+        <v>1907.3928131868</v>
       </c>
       <c r="O895" t="n">
-        <v>9536.964144737</v>
+        <v>9536.964065934</v>
       </c>
       <c r="P895" t="n">
         <v>2500</v>
@@ -39255,7 +39255,7 @@
         </is>
       </c>
       <c r="J897" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="K897" t="n">
         <v>0</v>
@@ -39264,19 +39264,19 @@
         <v>0</v>
       </c>
       <c r="M897" t="n">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N897" t="n">
-        <v>2079.3837709497</v>
+        <v>2079.3836916549</v>
       </c>
       <c r="O897" t="n">
-        <v>561433.618156419</v>
+        <v>553116.0619802034</v>
       </c>
       <c r="P897" t="n">
         <v>2900</v>
       </c>
       <c r="Q897" t="n">
-        <v>783000</v>
+        <v>771400</v>
       </c>
     </row>
     <row r="898">
@@ -39313,10 +39313,10 @@
         <v>294</v>
       </c>
       <c r="N898" t="n">
-        <v>1803.0159704121</v>
+        <v>1803.0161346363</v>
       </c>
       <c r="O898" t="n">
-        <v>530086.6953011574</v>
+        <v>530086.7435830722</v>
       </c>
       <c r="P898" t="n">
         <v>2500</v>
@@ -39359,10 +39359,10 @@
         <v>88</v>
       </c>
       <c r="N899" t="n">
-        <v>3306.5944954128</v>
+        <v>3306.5944785276</v>
       </c>
       <c r="O899" t="n">
-        <v>290980.3155963264</v>
+        <v>290980.3141104288</v>
       </c>
       <c r="P899" t="n">
         <v>4900</v>
@@ -39393,7 +39393,7 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
@@ -39402,19 +39402,19 @@
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="N900" t="n">
-        <v>2108.7941491086</v>
+        <v>2108.7945137157</v>
       </c>
       <c r="O900" t="n">
-        <v>124418.8547974074</v>
+        <v>73807.80798004949</v>
       </c>
       <c r="P900" t="n">
         <v>2900</v>
       </c>
       <c r="Q900" t="n">
-        <v>171100</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="901">
@@ -39439,7 +39439,7 @@
         </is>
       </c>
       <c r="J901" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="K901" t="n">
         <v>0</v>
@@ -39448,19 +39448,19 @@
         <v>0</v>
       </c>
       <c r="M901" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="N901" t="n">
-        <v>2056.0826834456</v>
+        <v>2056.0824863487</v>
       </c>
       <c r="O901" t="n">
-        <v>518132.8362282913</v>
+        <v>468786.8068875036</v>
       </c>
       <c r="P901" t="n">
         <v>2900</v>
       </c>
       <c r="Q901" t="n">
-        <v>730800</v>
+        <v>661200</v>
       </c>
     </row>
     <row r="902">
@@ -39497,10 +39497,10 @@
         <v>138</v>
       </c>
       <c r="N902" t="n">
-        <v>3224.5691001525</v>
+        <v>3224.5693083723</v>
       </c>
       <c r="O902" t="n">
-        <v>444990.535821045</v>
+        <v>444990.5645553774</v>
       </c>
       <c r="P902" t="n">
         <v>4500</v>
@@ -39543,10 +39543,10 @@
         <v>202</v>
       </c>
       <c r="N903" t="n">
-        <v>1655.9302708407</v>
+        <v>1655.9298420859</v>
       </c>
       <c r="O903" t="n">
-        <v>334497.9147098214</v>
+        <v>334497.8281013518</v>
       </c>
       <c r="P903" t="n">
         <v>2500</v>
@@ -39718,28 +39718,28 @@
         </is>
       </c>
       <c r="J907" t="n">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="K907" t="n">
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M907" t="n">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="N907" t="n">
         <v>2454</v>
       </c>
       <c r="O907" t="n">
-        <v>1977924</v>
+        <v>1960746</v>
       </c>
       <c r="P907" t="n">
         <v>4200</v>
       </c>
       <c r="Q907" t="n">
-        <v>3385200</v>
+        <v>3355800</v>
       </c>
     </row>
     <row r="908">
@@ -39776,10 +39776,10 @@
         <v>386</v>
       </c>
       <c r="N908" t="n">
-        <v>1789.7745116279</v>
+        <v>1592.2821517241</v>
       </c>
       <c r="O908" t="n">
-        <v>690852.9614883694</v>
+        <v>614620.9105655026</v>
       </c>
       <c r="P908" t="n">
         <v>2500</v>
@@ -39895,7 +39895,7 @@
         </is>
       </c>
       <c r="J911" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K911" t="n">
         <v>0</v>
@@ -39904,19 +39904,19 @@
         <v>0</v>
       </c>
       <c r="M911" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N911" t="n">
-        <v>2311.8972959184</v>
+        <v>2311.8966321244</v>
       </c>
       <c r="O911" t="n">
-        <v>432324.7943367407</v>
+        <v>425388.9803108897</v>
       </c>
       <c r="P911" t="n">
         <v>3500</v>
       </c>
       <c r="Q911" t="n">
-        <v>654500</v>
+        <v>644000</v>
       </c>
     </row>
     <row r="912">
@@ -39941,7 +39941,7 @@
         </is>
       </c>
       <c r="J912" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="K912" t="n">
         <v>0</v>
@@ -39950,19 +39950,19 @@
         <v>0</v>
       </c>
       <c r="M912" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="N912" t="n">
-        <v>1906.1803846154</v>
+        <v>1906.1797959184</v>
       </c>
       <c r="O912" t="n">
-        <v>249709.6303846174</v>
+        <v>232553.9351020448</v>
       </c>
       <c r="P912" t="n">
         <v>2900</v>
       </c>
       <c r="Q912" t="n">
-        <v>379900</v>
+        <v>353800</v>
       </c>
     </row>
     <row r="913">
@@ -39987,7 +39987,7 @@
         </is>
       </c>
       <c r="J913" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="K913" t="n">
         <v>0</v>
@@ -39996,19 +39996,19 @@
         <v>0</v>
       </c>
       <c r="M913" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="N913" t="n">
-        <v>3033.701005291</v>
+        <v>3033.6993989071</v>
       </c>
       <c r="O913" t="n">
-        <v>530897.675925925</v>
+        <v>512695.1984152999</v>
       </c>
       <c r="P913" t="n">
         <v>4500</v>
       </c>
       <c r="Q913" t="n">
-        <v>787500</v>
+        <v>760500</v>
       </c>
     </row>
     <row r="914">
@@ -40033,7 +40033,7 @@
         </is>
       </c>
       <c r="J914" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K914" t="n">
         <v>0</v>
@@ -40042,19 +40042,19 @@
         <v>0</v>
       </c>
       <c r="M914" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N914" t="n">
-        <v>1668.6382745098</v>
+        <v>1668.6384251969</v>
       </c>
       <c r="O914" t="n">
-        <v>333727.65490196</v>
+        <v>332059.0466141831</v>
       </c>
       <c r="P914" t="n">
         <v>2500</v>
       </c>
       <c r="Q914" t="n">
-        <v>500000</v>
+        <v>497500</v>
       </c>
     </row>
     <row r="915">
@@ -40137,10 +40137,10 @@
         <v>1077</v>
       </c>
       <c r="N916" t="n">
-        <v>1259.2746942571</v>
+        <v>1259.2747051969</v>
       </c>
       <c r="O916" t="n">
-        <v>1356238.845714897</v>
+        <v>1356238.857497061</v>
       </c>
       <c r="P916" t="n">
         <v>1900</v>
@@ -40304,7 +40304,7 @@
         </is>
       </c>
       <c r="J920" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K920" t="n">
         <v>0</v>
@@ -40313,19 +40313,19 @@
         <v>0</v>
       </c>
       <c r="M920" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N920" t="n">
-        <v>2556.7471311475</v>
+        <v>2556.747219917</v>
       </c>
       <c r="O920" t="n">
-        <v>253117.9659836025</v>
+        <v>245447.733112032</v>
       </c>
       <c r="P920" t="n">
         <v>3900</v>
       </c>
       <c r="Q920" t="n">
-        <v>386100</v>
+        <v>374400</v>
       </c>
     </row>
     <row r="921">
@@ -40348,7 +40348,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>2626</v>
+        <v>2566</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40357,19 +40357,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>2626</v>
+        <v>2566</v>
       </c>
       <c r="N921" t="n">
-        <v>692.15228029678</v>
+        <v>692.15231697102</v>
       </c>
       <c r="O921" t="n">
-        <v>1817591.888059344</v>
+        <v>1776062.845347637</v>
       </c>
       <c r="P921" t="n">
         <v>1200</v>
       </c>
       <c r="Q921" t="n">
-        <v>3151200</v>
+        <v>3079200</v>
       </c>
     </row>
     <row r="922">
@@ -40909,13 +40909,13 @@
         </is>
       </c>
       <c r="J933" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
       </c>
       <c r="L933" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M933" t="n">
         <v>500</v>
@@ -41004,7 +41004,7 @@
         </is>
       </c>
       <c r="J935" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K935" t="n">
         <v>0</v>
@@ -41013,19 +41013,19 @@
         <v>0</v>
       </c>
       <c r="M935" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N935" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O935" t="n">
-        <v>3238227.56</v>
+        <v>3229282.18</v>
       </c>
       <c r="P935" t="n">
         <v>14900</v>
       </c>
       <c r="Q935" t="n">
-        <v>5393800</v>
+        <v>5378900</v>
       </c>
     </row>
     <row r="936">
@@ -41932,10 +41932,10 @@
         <v>351</v>
       </c>
       <c r="N955" t="n">
-        <v>2286.1645697897</v>
+        <v>2286.1645384615</v>
       </c>
       <c r="O955" t="n">
-        <v>802443.7639961848</v>
+        <v>802443.7529999864</v>
       </c>
       <c r="P955" t="n">
         <v>3000</v>
@@ -42177,7 +42177,7 @@
         </is>
       </c>
       <c r="J961" t="n">
-        <v>444</v>
+        <v>289</v>
       </c>
       <c r="K961" t="n">
         <v>0</v>
@@ -42186,19 +42186,19 @@
         <v>0</v>
       </c>
       <c r="M961" t="n">
-        <v>444</v>
+        <v>289</v>
       </c>
       <c r="N961" t="n">
         <v>177.65</v>
       </c>
       <c r="O961" t="n">
-        <v>78876.60000000001</v>
+        <v>51340.85</v>
       </c>
       <c r="P961" t="n">
         <v>300</v>
       </c>
       <c r="Q961" t="n">
-        <v>133200</v>
+        <v>86700</v>
       </c>
     </row>
     <row r="962">
@@ -42452,10 +42452,10 @@
         <v>1037</v>
       </c>
       <c r="N967" t="n">
-        <v>517.29272348033</v>
+        <v>517.29287307808</v>
       </c>
       <c r="O967" t="n">
-        <v>536432.5542491022</v>
+        <v>536432.7093819689</v>
       </c>
       <c r="P967" t="n">
         <v>900</v>
@@ -42625,28 +42625,28 @@
         </is>
       </c>
       <c r="J971" t="n">
-        <v>1318</v>
+        <v>1291</v>
       </c>
       <c r="K971" t="n">
         <v>0</v>
       </c>
       <c r="L971" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M971" t="n">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="N971" t="n">
-        <v>3110.8397979798</v>
+        <v>3110.8397028838</v>
       </c>
       <c r="O971" t="n">
-        <v>4053424.256767679</v>
+        <v>4016094.056422986</v>
       </c>
       <c r="P971" t="n">
         <v>4500</v>
       </c>
       <c r="Q971" t="n">
-        <v>5863500</v>
+        <v>5809500</v>
       </c>
     </row>
     <row r="972">
@@ -42757,7 +42757,7 @@
         </is>
       </c>
       <c r="J974" t="n">
-        <v>13643</v>
+        <v>13586</v>
       </c>
       <c r="K974" t="n">
         <v>0</v>
@@ -42766,19 +42766,19 @@
         <v>0</v>
       </c>
       <c r="M974" t="n">
-        <v>13643</v>
+        <v>13586</v>
       </c>
       <c r="N974" t="n">
-        <v>703.7949437622</v>
+        <v>703.79492130965</v>
       </c>
       <c r="O974" t="n">
-        <v>9601874.417747695</v>
+        <v>9561757.800912905</v>
       </c>
       <c r="P974" t="n">
         <v>900</v>
       </c>
       <c r="Q974" t="n">
-        <v>12278700</v>
+        <v>12227400</v>
       </c>
     </row>
     <row r="975">
@@ -42859,10 +42859,10 @@
         <v>45</v>
       </c>
       <c r="N976" t="n">
-        <v>3006.0209574468</v>
+        <v>3006.0209677419</v>
       </c>
       <c r="O976" t="n">
-        <v>135270.943085106</v>
+        <v>135270.9435483855</v>
       </c>
       <c r="P976" t="n">
         <v>3900</v>
@@ -43947,10 +43947,10 @@
         <v>18</v>
       </c>
       <c r="N1000" t="n">
-        <v>2098.4051032448</v>
+        <v>2098.4051183432</v>
       </c>
       <c r="O1000" t="n">
-        <v>37771.2918584064</v>
+        <v>37771.29213017759</v>
       </c>
       <c r="P1000" t="n">
         <v>9500</v>
@@ -47132,10 +47132,10 @@
         <v>24</v>
       </c>
       <c r="N1068" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="O1068" t="n">
-        <v>1058726.494883712</v>
+        <v>1058726.498313264</v>
       </c>
       <c r="P1068" t="n">
         <v>71900</v>
@@ -47181,10 +47181,10 @@
         <v>16</v>
       </c>
       <c r="N1069" t="n">
-        <v>665.3237759536501</v>
+        <v>665.3237979601701</v>
       </c>
       <c r="O1069" t="n">
-        <v>10645.1804152584</v>
+        <v>10645.18076736272</v>
       </c>
       <c r="P1069" t="n">
         <v>2900</v>
@@ -47455,28 +47455,28 @@
         </is>
       </c>
       <c r="J1075" t="n">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="K1075" t="n">
         <v>0</v>
       </c>
       <c r="L1075" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1075" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N1075" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1075" t="n">
-        <v>1163787.36</v>
+        <v>1150041.84</v>
       </c>
       <c r="P1075" t="n">
         <v>7900</v>
       </c>
       <c r="Q1075" t="n">
-        <v>2006600</v>
+        <v>1982900</v>
       </c>
     </row>
     <row r="1076">
@@ -47504,7 +47504,7 @@
         </is>
       </c>
       <c r="J1076" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K1076" t="n">
         <v>0</v>
@@ -47513,19 +47513,19 @@
         <v>0</v>
       </c>
       <c r="M1076" t="n">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="N1076" t="n">
         <v>3155</v>
       </c>
       <c r="O1076" t="n">
-        <v>1170505</v>
+        <v>1157885</v>
       </c>
       <c r="P1076" t="n">
         <v>5900</v>
       </c>
       <c r="Q1076" t="n">
-        <v>2188900</v>
+        <v>2165300</v>
       </c>
     </row>
     <row r="1077">
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="J1108" t="n">
-        <v>1451</v>
+        <v>1438</v>
       </c>
       <c r="K1108" t="n">
         <v>0</v>
@@ -48894,19 +48894,19 @@
         <v>0</v>
       </c>
       <c r="M1108" t="n">
-        <v>1451</v>
+        <v>1438</v>
       </c>
       <c r="N1108" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1108" t="n">
-        <v>1707203.07</v>
+        <v>1691907.66</v>
       </c>
       <c r="P1108" t="n">
         <v>1900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>2756900</v>
+        <v>2732200</v>
       </c>
     </row>
     <row r="1109">
@@ -48973,7 +48973,7 @@
         </is>
       </c>
       <c r="J1110" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1110" t="n">
         <v>0</v>
@@ -48982,19 +48982,19 @@
         <v>0</v>
       </c>
       <c r="M1110" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N1110" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1110" t="n">
-        <v>133639.8</v>
+        <v>130457.9</v>
       </c>
       <c r="P1110" t="n">
         <v>5100</v>
       </c>
       <c r="Q1110" t="n">
-        <v>214200</v>
+        <v>209100</v>
       </c>
     </row>
     <row r="1111">
@@ -50168,10 +50168,10 @@
         <v>1</v>
       </c>
       <c r="N1137" t="n">
-        <v>1757.3205764967</v>
+        <v>1757.3205829596</v>
       </c>
       <c r="O1137" t="n">
-        <v>1757.3205764967</v>
+        <v>1757.3205829596</v>
       </c>
       <c r="P1137" t="n">
         <v>2000</v>
@@ -51200,7 +51200,7 @@
         </is>
       </c>
       <c r="J1160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1160" t="n">
         <v>0</v>
@@ -51209,19 +51209,19 @@
         <v>0</v>
       </c>
       <c r="M1160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1160" t="n">
         <v>5280</v>
       </c>
       <c r="O1160" t="n">
-        <v>84480</v>
+        <v>79200</v>
       </c>
       <c r="P1160" t="n">
         <v>6900</v>
       </c>
       <c r="Q1160" t="n">
-        <v>110400</v>
+        <v>103500</v>
       </c>
     </row>
     <row r="1161">
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="J1161" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K1161" t="n">
         <v>0</v>
@@ -51255,19 +51255,19 @@
         <v>0</v>
       </c>
       <c r="M1161" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N1161" t="n">
         <v>3872</v>
       </c>
       <c r="O1161" t="n">
-        <v>298144</v>
+        <v>290400</v>
       </c>
       <c r="P1161" t="n">
         <v>4900</v>
       </c>
       <c r="Q1161" t="n">
-        <v>377300</v>
+        <v>367500</v>
       </c>
     </row>
     <row r="1162">
@@ -51292,7 +51292,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51301,19 +51301,19 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N1162" t="n">
         <v>6160</v>
       </c>
       <c r="O1162" t="n">
-        <v>67760</v>
+        <v>18480</v>
       </c>
       <c r="P1162" t="n">
         <v>7900</v>
       </c>
       <c r="Q1162" t="n">
-        <v>86900</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="1163">
@@ -51338,7 +51338,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51347,19 +51347,19 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="N1163" t="n">
         <v>4400</v>
       </c>
       <c r="O1163" t="n">
-        <v>294800</v>
+        <v>233200</v>
       </c>
       <c r="P1163" t="n">
         <v>5900</v>
       </c>
       <c r="Q1163" t="n">
-        <v>395300</v>
+        <v>312700</v>
       </c>
     </row>
     <row r="1164">
@@ -51384,7 +51384,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51393,19 +51393,19 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="N1164" t="n">
         <v>6160</v>
       </c>
       <c r="O1164" t="n">
-        <v>1774080</v>
+        <v>1675520</v>
       </c>
       <c r="P1164" t="n">
         <v>7500</v>
       </c>
       <c r="Q1164" t="n">
-        <v>2160000</v>
+        <v>2040000</v>
       </c>
     </row>
     <row r="1165">
@@ -51430,7 +51430,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51439,19 +51439,19 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N1165" t="n">
         <v>3520</v>
       </c>
       <c r="O1165" t="n">
-        <v>52800</v>
+        <v>24640</v>
       </c>
       <c r="P1165" t="n">
         <v>4500</v>
       </c>
       <c r="Q1165" t="n">
-        <v>67500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="1166">
@@ -51522,7 +51522,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51531,19 +51531,19 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N1167" t="n">
         <v>9240</v>
       </c>
       <c r="O1167" t="n">
-        <v>147840</v>
+        <v>27720</v>
       </c>
       <c r="P1167" t="n">
         <v>11500</v>
       </c>
       <c r="Q1167" t="n">
-        <v>184000</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="1168">
@@ -51614,7 +51614,7 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -51623,19 +51623,19 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N1169" t="n">
         <v>4576</v>
       </c>
       <c r="O1169" t="n">
-        <v>585728</v>
+        <v>576576</v>
       </c>
       <c r="P1169" t="n">
         <v>5900</v>
       </c>
       <c r="Q1169" t="n">
-        <v>755200</v>
+        <v>743400</v>
       </c>
     </row>
     <row r="1170">
@@ -53329,7 +53329,7 @@
         </is>
       </c>
       <c r="J1206" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="K1206" t="n">
         <v>0</v>
@@ -53338,19 +53338,19 @@
         <v>0</v>
       </c>
       <c r="M1206" t="n">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="N1206" t="n">
-        <v>4687.9744968268</v>
+        <v>4687.9745338208</v>
       </c>
       <c r="O1206" t="n">
-        <v>2428370.789356282</v>
+        <v>2404930.935850071</v>
       </c>
       <c r="P1206" t="n">
         <v>5900</v>
       </c>
       <c r="Q1206" t="n">
-        <v>3056200</v>
+        <v>3026700</v>
       </c>
     </row>
     <row r="1207">
@@ -53387,10 +53387,10 @@
         <v>610</v>
       </c>
       <c r="N1207" t="n">
-        <v>4171.6686299766</v>
+        <v>4171.6686251469</v>
       </c>
       <c r="O1207" t="n">
-        <v>2544717.864285726</v>
+        <v>2544717.861339609</v>
       </c>
       <c r="P1207" t="n">
         <v>5500</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -11991,10 +11991,10 @@
         <v>806</v>
       </c>
       <c r="N275" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O275" t="n">
-        <v>2081297.85459498</v>
+        <v>2081297.852027709</v>
       </c>
       <c r="P275" t="n">
         <v>4500</v>
@@ -12736,10 +12736,10 @@
         <v>67</v>
       </c>
       <c r="N292" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O292" t="n">
-        <v>216414.4633823557</v>
+        <v>216414.4617037042</v>
       </c>
       <c r="P292" t="n">
         <v>6200</v>
@@ -18430,10 +18430,10 @@
         <v>226</v>
       </c>
       <c r="N422" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O422" t="n">
-        <v>368588.8397883148</v>
+        <v>368588.8402753448</v>
       </c>
       <c r="P422" t="n">
         <v>2500</v>
@@ -18522,10 +18522,10 @@
         <v>380</v>
       </c>
       <c r="N424" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O424" t="n">
-        <v>589073.7825160039</v>
+        <v>589073.783404444</v>
       </c>
       <c r="P424" t="n">
         <v>2500</v>
@@ -18614,10 +18614,10 @@
         <v>618</v>
       </c>
       <c r="N426" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O426" t="n">
-        <v>1485372.08926831</v>
+        <v>1485372.10220064</v>
       </c>
       <c r="P426" t="n">
         <v>3500</v>
@@ -21937,22 +21937,22 @@
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M503" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N503" t="n">
         <v>9338</v>
       </c>
       <c r="O503" t="n">
-        <v>280140</v>
+        <v>270802</v>
       </c>
       <c r="P503" t="n">
         <v>15500</v>
       </c>
       <c r="Q503" t="n">
-        <v>465000</v>
+        <v>449500</v>
       </c>
     </row>
     <row r="504">
@@ -28344,10 +28344,10 @@
         <v>79</v>
       </c>
       <c r="N655" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O655" t="n">
-        <v>658289.5894587658</v>
+        <v>663419.1187272756</v>
       </c>
       <c r="P655" t="n">
         <v>14900</v>
@@ -32825,10 +32825,10 @@
         <v>5</v>
       </c>
       <c r="N757" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="O757" t="n">
-        <v>134780</v>
+        <v>140395.833333335</v>
       </c>
       <c r="P757" t="n">
         <v>44900</v>
@@ -36145,10 +36145,10 @@
         <v>9</v>
       </c>
       <c r="N829" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O829" t="n">
-        <v>35133.6447611064</v>
+        <v>35133.6451764708</v>
       </c>
       <c r="P829" t="n">
         <v>7500</v>
@@ -37284,22 +37284,22 @@
         <v>0</v>
       </c>
       <c r="L854" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M854" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N854" t="n">
         <v>23439</v>
       </c>
       <c r="O854" t="n">
-        <v>539097</v>
+        <v>515658</v>
       </c>
       <c r="P854" t="n">
         <v>37900</v>
       </c>
       <c r="Q854" t="n">
-        <v>871700</v>
+        <v>833800</v>
       </c>
     </row>
     <row r="855">
@@ -39776,10 +39776,10 @@
         <v>386</v>
       </c>
       <c r="N908" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="O908" t="n">
-        <v>614620.9105655026</v>
+        <v>614620.9235408154</v>
       </c>
       <c r="P908" t="n">
         <v>2500</v>
@@ -42452,10 +42452,10 @@
         <v>1037</v>
       </c>
       <c r="N967" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O967" t="n">
-        <v>536432.7093819689</v>
+        <v>536432.7822188579</v>
       </c>
       <c r="P967" t="n">
         <v>900</v>
@@ -42637,10 +42637,10 @@
         <v>1291</v>
       </c>
       <c r="N971" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O971" t="n">
-        <v>4016094.056422986</v>
+        <v>4016094.033148579</v>
       </c>
       <c r="P971" t="n">
         <v>4500</v>
@@ -51390,22 +51390,22 @@
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1164" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="N1164" t="n">
         <v>6160</v>
       </c>
       <c r="O1164" t="n">
-        <v>1675520</v>
+        <v>1601600</v>
       </c>
       <c r="P1164" t="n">
         <v>7500</v>
       </c>
       <c r="Q1164" t="n">
-        <v>2040000</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="1165">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -9576,22 +9576,22 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M219" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="N219" t="n">
         <v>6513</v>
       </c>
       <c r="O219" t="n">
-        <v>879255</v>
+        <v>814125</v>
       </c>
       <c r="P219" t="n">
         <v>11500</v>
       </c>
       <c r="Q219" t="n">
-        <v>1552500</v>
+        <v>1437500</v>
       </c>
     </row>
     <row r="220">
@@ -11838,22 +11838,22 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M272" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="N272" t="n">
-        <v>2033.5164102564</v>
+        <v>2033.5050485437</v>
       </c>
       <c r="O272" t="n">
-        <v>158614.2799999992</v>
+        <v>130144.3231067968</v>
       </c>
       <c r="P272" t="n">
         <v>4100</v>
       </c>
       <c r="Q272" t="n">
-        <v>319800</v>
+        <v>262400</v>
       </c>
     </row>
     <row r="273">
@@ -13559,22 +13559,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M311" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N311" t="n">
         <v>1203.38</v>
       </c>
       <c r="O311" t="n">
-        <v>547537.9</v>
+        <v>543927.76</v>
       </c>
       <c r="P311" t="n">
         <v>1900</v>
       </c>
       <c r="Q311" t="n">
-        <v>864500</v>
+        <v>858800</v>
       </c>
     </row>
     <row r="312">
@@ -18144,22 +18144,22 @@
         <v>0</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M416" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N416" t="n">
         <v>12754</v>
       </c>
       <c r="O416" t="n">
-        <v>357112</v>
+        <v>280588</v>
       </c>
       <c r="P416" t="n">
         <v>21500</v>
       </c>
       <c r="Q416" t="n">
-        <v>602000</v>
+        <v>473000</v>
       </c>
     </row>
     <row r="417">
@@ -18374,22 +18374,22 @@
         <v>0</v>
       </c>
       <c r="L421" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M421" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="N421" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O421" t="n">
-        <v>1199354.255978457</v>
+        <v>1189740.213108364</v>
       </c>
       <c r="P421" t="n">
         <v>3500</v>
       </c>
       <c r="Q421" t="n">
-        <v>1746500</v>
+        <v>1732500</v>
       </c>
     </row>
     <row r="422">
@@ -18464,22 +18464,22 @@
         <v>0</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M423" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="N423" t="n">
-        <v>2521.4791818182</v>
+        <v>2521.4745192308</v>
       </c>
       <c r="O423" t="n">
-        <v>264755.3140909109</v>
+        <v>249625.9774038492</v>
       </c>
       <c r="P423" t="n">
         <v>3900</v>
       </c>
       <c r="Q423" t="n">
-        <v>409500</v>
+        <v>386100</v>
       </c>
     </row>
     <row r="424">
@@ -34985,22 +34985,22 @@
         <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M804" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N804" t="n">
         <v>21676</v>
       </c>
       <c r="O804" t="n">
-        <v>1885812</v>
+        <v>1842460</v>
       </c>
       <c r="P804" t="n">
         <v>34900</v>
       </c>
       <c r="Q804" t="n">
-        <v>3036300</v>
+        <v>2966500</v>
       </c>
     </row>
     <row r="805">
@@ -35399,22 +35399,22 @@
         <v>0</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M813" t="n">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="N813" t="n">
         <v>3196</v>
       </c>
       <c r="O813" t="n">
-        <v>1198500</v>
+        <v>1160148</v>
       </c>
       <c r="P813" t="n">
         <v>6400</v>
       </c>
       <c r="Q813" t="n">
-        <v>2400000</v>
+        <v>2323200</v>
       </c>
     </row>
     <row r="814">
@@ -42688,22 +42688,22 @@
         <v>0</v>
       </c>
       <c r="L972" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M972" t="n">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="N972" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O972" t="n">
-        <v>4016093.96675955</v>
+        <v>4009872.279650799</v>
       </c>
       <c r="P972" t="n">
         <v>4500</v>
       </c>
       <c r="Q972" t="n">
-        <v>5809500</v>
+        <v>5800500</v>
       </c>
     </row>
     <row r="973">
@@ -42820,22 +42820,22 @@
         <v>0</v>
       </c>
       <c r="L975" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M975" t="n">
-        <v>13575</v>
+        <v>13555</v>
       </c>
       <c r="N975" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O975" t="n">
-        <v>9554015.56219971</v>
+        <v>9539939.646828355</v>
       </c>
       <c r="P975" t="n">
         <v>900</v>
       </c>
       <c r="Q975" t="n">
-        <v>12217500</v>
+        <v>12199500</v>
       </c>
     </row>
     <row r="976">

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -11711,10 +11711,10 @@
         <v>1379</v>
       </c>
       <c r="N269" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O269" t="n">
-        <v>7204735.448920797</v>
+        <v>7194099.575029605</v>
       </c>
       <c r="P269" t="n">
         <v>8500</v>
@@ -13470,10 +13470,10 @@
         <v>300</v>
       </c>
       <c r="N309" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O309" t="n">
-        <v>1471005.43809525</v>
+        <v>1467279.01523811</v>
       </c>
       <c r="P309" t="n">
         <v>8200</v>
@@ -13657,10 +13657,10 @@
         <v>1</v>
       </c>
       <c r="N313" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="O313" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="P313" t="n">
         <v>9500</v>
@@ -14533,10 +14533,10 @@
         <v>29</v>
       </c>
       <c r="N333" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O333" t="n">
-        <v>237343.9678217808</v>
+        <v>236466</v>
       </c>
       <c r="P333" t="n">
         <v>13500</v>
@@ -14579,10 +14579,10 @@
         <v>285</v>
       </c>
       <c r="N334" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O334" t="n">
-        <v>4226952.237294195</v>
+        <v>4224377.96654487</v>
       </c>
       <c r="P334" t="n">
         <v>24900</v>
@@ -15437,10 +15437,10 @@
         <v>2</v>
       </c>
       <c r="N354" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O354" t="n">
-        <v>30143.52</v>
+        <v>28773.36</v>
       </c>
       <c r="P354" t="n">
         <v>21900</v>
@@ -19962,10 +19962,10 @@
         <v>28</v>
       </c>
       <c r="N457" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O457" t="n">
-        <v>305405.620000012</v>
+        <v>303435.261818192</v>
       </c>
       <c r="P457" t="n">
         <v>19900</v>
@@ -20851,10 +20851,10 @@
         <v>2</v>
       </c>
       <c r="N478" t="n">
-        <v>17970.414</v>
+        <v>16336.74</v>
       </c>
       <c r="O478" t="n">
-        <v>35940.828</v>
+        <v>32673.48</v>
       </c>
       <c r="P478" t="n">
         <v>30900</v>
@@ -21622,10 +21622,10 @@
         <v>29</v>
       </c>
       <c r="N496" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O496" t="n">
-        <v>274341.8954248358</v>
+        <v>270802</v>
       </c>
       <c r="P496" t="n">
         <v>15500</v>
@@ -22956,10 +22956,10 @@
         <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O528" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="P528" t="n">
         <v>36500</v>
@@ -23366,10 +23366,10 @@
         <v>19</v>
       </c>
       <c r="N538" t="n">
-        <v>39703.055555556</v>
+        <v>38630</v>
       </c>
       <c r="O538" t="n">
-        <v>754358.055555564</v>
+        <v>733970</v>
       </c>
       <c r="P538" t="n">
         <v>46500</v>
@@ -23456,10 +23456,10 @@
         <v>37</v>
       </c>
       <c r="N540" t="n">
-        <v>24573.894298246</v>
+        <v>24538.02</v>
       </c>
       <c r="O540" t="n">
-        <v>909234.0890351019</v>
+        <v>907906.74</v>
       </c>
       <c r="P540" t="n">
         <v>52900</v>
@@ -24245,10 +24245,10 @@
         <v>2</v>
       </c>
       <c r="N559" t="n">
-        <v>33243.75</v>
+        <v>26595</v>
       </c>
       <c r="O559" t="n">
-        <v>66487.5</v>
+        <v>53190</v>
       </c>
       <c r="P559" t="n">
         <v>39900</v>
@@ -25736,10 +25736,10 @@
         <v>3</v>
       </c>
       <c r="N594" t="n">
-        <v>12393.103448276</v>
+        <v>11980</v>
       </c>
       <c r="O594" t="n">
-        <v>37179.310344828</v>
+        <v>35940</v>
       </c>
       <c r="P594" t="n">
         <v>19500</v>
@@ -25782,10 +25782,10 @@
         <v>86</v>
       </c>
       <c r="N595" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O595" t="n">
-        <v>997144.161129978</v>
+        <v>994335.3039547941</v>
       </c>
       <c r="P595" t="n">
         <v>18500</v>
@@ -25874,10 +25874,10 @@
         <v>75</v>
       </c>
       <c r="N597" t="n">
-        <v>12056.245617021</v>
+        <v>12005.159829787</v>
       </c>
       <c r="O597" t="n">
-        <v>904218.4212765751</v>
+        <v>900386.987234025</v>
       </c>
       <c r="P597" t="n">
         <v>19500</v>
@@ -27690,10 +27690,10 @@
         <v>138</v>
       </c>
       <c r="N640" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O640" t="n">
-        <v>3758051.87448</v>
+        <v>3743079.55344</v>
       </c>
       <c r="P640" t="n">
         <v>44500</v>
@@ -28581,10 +28581,10 @@
         <v>19</v>
       </c>
       <c r="N661" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O661" t="n">
-        <v>513209.777777787</v>
+        <v>510226</v>
       </c>
       <c r="P661" t="n">
         <v>43900</v>
@@ -29334,10 +29334,10 @@
         <v>19</v>
       </c>
       <c r="N679" t="n">
-        <v>10317.12016129</v>
+        <v>9994.710161290301</v>
       </c>
       <c r="O679" t="n">
-        <v>196025.28306451</v>
+        <v>189899.4930645157</v>
       </c>
       <c r="P679" t="n">
         <v>20800</v>
@@ -29913,10 +29913,10 @@
         <v>15</v>
       </c>
       <c r="N693" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O693" t="n">
-        <v>196193.463962265</v>
+        <v>194723.85</v>
       </c>
       <c r="P693" t="n">
         <v>21900</v>
@@ -29959,10 +29959,10 @@
         <v>25</v>
       </c>
       <c r="N694" t="n">
-        <v>13974.031438356</v>
+        <v>13878.97</v>
       </c>
       <c r="O694" t="n">
-        <v>349350.7859589</v>
+        <v>346974.25</v>
       </c>
       <c r="P694" t="n">
         <v>21900</v>
@@ -30174,10 +30174,10 @@
         <v>3</v>
       </c>
       <c r="N699" t="n">
-        <v>23309.866666667</v>
+        <v>21853</v>
       </c>
       <c r="O699" t="n">
-        <v>69929.600000001</v>
+        <v>65559</v>
       </c>
       <c r="P699" t="n">
         <v>37200</v>
@@ -34671,10 +34671,10 @@
         <v>41</v>
       </c>
       <c r="N797" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O797" t="n">
-        <v>1123741.762237776</v>
+        <v>1115938</v>
       </c>
       <c r="P797" t="n">
         <v>43900</v>
@@ -34766,10 +34766,10 @@
         <v>32</v>
       </c>
       <c r="N799" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="O799" t="n">
-        <v>686619.574468096</v>
+        <v>679392</v>
       </c>
       <c r="P799" t="n">
         <v>34500</v>
@@ -34812,10 +34812,10 @@
         <v>1</v>
       </c>
       <c r="N800" t="n">
-        <v>23419.958333333</v>
+        <v>22942</v>
       </c>
       <c r="O800" t="n">
-        <v>23419.958333333</v>
+        <v>22942</v>
       </c>
       <c r="P800" t="n">
         <v>36900</v>
@@ -35226,10 +35226,10 @@
         <v>203</v>
       </c>
       <c r="N809" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O809" t="n">
-        <v>1867260.542635664</v>
+        <v>1863134</v>
       </c>
       <c r="P809" t="n">
         <v>14900</v>
@@ -35272,10 +35272,10 @@
         <v>257</v>
       </c>
       <c r="N810" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O810" t="n">
-        <v>1173948.971078006</v>
+        <v>1167808</v>
       </c>
       <c r="P810" t="n">
         <v>7900</v>
@@ -35364,10 +35364,10 @@
         <v>161</v>
       </c>
       <c r="N812" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O812" t="n">
-        <v>2245703.296577888</v>
+        <v>2241442</v>
       </c>
       <c r="P812" t="n">
         <v>22900</v>
@@ -35548,10 +35548,10 @@
         <v>9</v>
       </c>
       <c r="N816" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O816" t="n">
-        <v>227343.441176469</v>
+        <v>225684</v>
       </c>
       <c r="P816" t="n">
         <v>40900</v>
@@ -36233,10 +36233,10 @@
         <v>1</v>
       </c>
       <c r="N831" t="n">
-        <v>10198.963414634</v>
+        <v>9839</v>
       </c>
       <c r="O831" t="n">
-        <v>10198.963414634</v>
+        <v>9839</v>
       </c>
       <c r="P831" t="n">
         <v>16900</v>
@@ -36647,10 +36647,10 @@
         <v>2</v>
       </c>
       <c r="N840" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O840" t="n">
-        <v>26243.890310786</v>
+        <v>26196</v>
       </c>
       <c r="P840" t="n">
         <v>21200</v>
@@ -37245,10 +37245,10 @@
         <v>3</v>
       </c>
       <c r="N853" t="n">
-        <v>145341.6</v>
+        <v>121118</v>
       </c>
       <c r="O853" t="n">
-        <v>436024.8</v>
+        <v>363354</v>
       </c>
       <c r="P853" t="n">
         <v>193900</v>
@@ -37516,10 +37516,10 @@
         <v>39</v>
       </c>
       <c r="N859" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="O859" t="n">
-        <v>845012.706766917</v>
+        <v>832494</v>
       </c>
       <c r="P859" t="n">
         <v>34900</v>
@@ -37703,10 +37703,10 @@
         <v>18</v>
       </c>
       <c r="N863" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O863" t="n">
-        <v>311867.779141098</v>
+        <v>309024</v>
       </c>
       <c r="P863" t="n">
         <v>27900</v>
@@ -37749,10 +37749,10 @@
         <v>75</v>
       </c>
       <c r="N864" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O864" t="n">
-        <v>2046680.6949807</v>
+        <v>2044050</v>
       </c>
       <c r="P864" t="n">
         <v>43900</v>
@@ -37933,10 +37933,10 @@
         <v>18</v>
       </c>
       <c r="N868" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O868" t="n">
-        <v>725698.8875379959</v>
+        <v>721314</v>
       </c>
       <c r="P868" t="n">
         <v>64900</v>
@@ -44015,10 +44015,10 @@
         <v>1</v>
       </c>
       <c r="N1001" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="O1001" t="n">
-        <v>10639.697586207</v>
+        <v>10548.76</v>
       </c>
       <c r="P1001" t="n">
         <v>35900</v>
@@ -46917,10 +46917,10 @@
         <v>1</v>
       </c>
       <c r="N1063" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O1063" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="P1063" t="n">
         <v>27900</v>

--- a/bodegas/CM-105.xlsx
+++ b/bodegas/CM-105.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-12</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -895,10 +895,10 @@
         <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>1811.3087042532</v>
+        <v>1811.3087824351</v>
       </c>
       <c r="O12" t="n">
-        <v>76074.96557863439</v>
+        <v>76074.9688622742</v>
       </c>
       <c r="P12" t="n">
         <v>2600</v>
@@ -2801,10 +2801,10 @@
         <v>38</v>
       </c>
       <c r="N59" t="n">
-        <v>20752.143589744</v>
+        <v>20752.143684211</v>
       </c>
       <c r="O59" t="n">
-        <v>788581.4564102719</v>
+        <v>788581.460000018</v>
       </c>
       <c r="P59" t="n">
         <v>38600</v>
@@ -3004,10 +3004,10 @@
         <v>283</v>
       </c>
       <c r="N64" t="n">
-        <v>2474.703951049</v>
+        <v>2474.7036162362</v>
       </c>
       <c r="O64" t="n">
-        <v>700341.218146867</v>
+        <v>700341.1233948446</v>
       </c>
       <c r="P64" t="n">
         <v>4500</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -3040,19 +3040,19 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N65" t="n">
         <v>3526.1</v>
       </c>
       <c r="O65" t="n">
-        <v>197461.6</v>
+        <v>190409.4</v>
       </c>
       <c r="P65" t="n">
         <v>6300</v>
       </c>
       <c r="Q65" t="n">
-        <v>352800</v>
+        <v>340200</v>
       </c>
     </row>
     <row r="66">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4762,19 +4762,19 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>10994.366666667</v>
+        <v>10994.367272727</v>
       </c>
       <c r="O105" t="n">
-        <v>21988.733333334</v>
+        <v>10994.367272727</v>
       </c>
       <c r="P105" t="n">
         <v>16900</v>
       </c>
       <c r="Q105" t="n">
-        <v>33800</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="106">
@@ -4935,10 +4935,10 @@
         <v>19</v>
       </c>
       <c r="N109" t="n">
-        <v>15711.964632768</v>
+        <v>15711.964602273</v>
       </c>
       <c r="O109" t="n">
-        <v>298527.328022592</v>
+        <v>298527.327443187</v>
       </c>
       <c r="P109" t="n">
         <v>28500</v>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5099,19 +5099,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N113" t="n">
-        <v>7407.7300555556</v>
+        <v>7407.7300557103</v>
       </c>
       <c r="O113" t="n">
-        <v>1081528.588111118</v>
+        <v>1074120.858077993</v>
       </c>
       <c r="P113" t="n">
         <v>10900</v>
       </c>
       <c r="Q113" t="n">
-        <v>1591400</v>
+        <v>1580500</v>
       </c>
     </row>
     <row r="114">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5950,19 +5950,19 @@
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N134" t="n">
-        <v>80027.71666666699</v>
+        <v>80027.7</v>
       </c>
       <c r="O134" t="n">
-        <v>240083.150000001</v>
+        <v>160055.4</v>
       </c>
       <c r="P134" t="n">
         <v>129900</v>
       </c>
       <c r="Q134" t="n">
-        <v>389700</v>
+        <v>259800</v>
       </c>
     </row>
     <row r="135">
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -8145,19 +8145,19 @@
         <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N186" t="n">
-        <v>1801.0175</v>
+        <v>1801.018</v>
       </c>
       <c r="O186" t="n">
-        <v>32418.315</v>
+        <v>25214.252</v>
       </c>
       <c r="P186" t="n">
         <v>3200</v>
       </c>
       <c r="Q186" t="n">
-        <v>57600</v>
+        <v>44800</v>
       </c>
     </row>
     <row r="187">
@@ -9877,10 +9877,10 @@
         <v>886</v>
       </c>
       <c r="N226" t="n">
-        <v>1098.0630438871</v>
+        <v>1098.0630728186</v>
       </c>
       <c r="O226" t="n">
-        <v>972883.8568839707</v>
+        <v>972883.8825172796</v>
       </c>
       <c r="P226" t="n">
         <v>1500</v>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="J268" t="n">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
@@ -11662,19 +11662,19 @@
         <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="N268" t="n">
-        <v>2582.2551814224</v>
+        <v>2582.2551438323</v>
       </c>
       <c r="O268" t="n">
-        <v>1673301.357561715</v>
+        <v>1642314.271477343</v>
       </c>
       <c r="P268" t="n">
         <v>4500</v>
       </c>
       <c r="Q268" t="n">
-        <v>2916000</v>
+        <v>2862000</v>
       </c>
     </row>
     <row r="269">
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -11708,19 +11708,19 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="N269" t="n">
-        <v>5216.895993495</v>
+        <v>5216.8959816133</v>
       </c>
       <c r="O269" t="n">
-        <v>7194099.575029605</v>
+        <v>7188882.662663127</v>
       </c>
       <c r="P269" t="n">
         <v>8500</v>
       </c>
       <c r="Q269" t="n">
-        <v>11721500</v>
+        <v>11713000</v>
       </c>
     </row>
     <row r="270">
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -11841,19 +11841,19 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N272" t="n">
-        <v>2033.5050485437</v>
+        <v>2033.5022</v>
       </c>
       <c r="O272" t="n">
-        <v>130144.3231067968</v>
+        <v>124043.6342</v>
       </c>
       <c r="P272" t="n">
         <v>4100</v>
       </c>
       <c r="Q272" t="n">
-        <v>262400</v>
+        <v>250100</v>
       </c>
     </row>
     <row r="273">
@@ -12136,10 +12136,10 @@
         <v>2809</v>
       </c>
       <c r="N279" t="n">
-        <v>3158.8608347353</v>
+        <v>3158.8608348592</v>
       </c>
       <c r="O279" t="n">
-        <v>8873240.084771458</v>
+        <v>8873240.085119493</v>
       </c>
       <c r="P279" t="n">
         <v>5600</v>
@@ -12630,10 +12630,10 @@
         <v>32</v>
       </c>
       <c r="N290" t="n">
-        <v>2694.8231282537</v>
+        <v>2694.823125</v>
       </c>
       <c r="O290" t="n">
-        <v>86234.3401041184</v>
+        <v>86234.34</v>
       </c>
       <c r="P290" t="n">
         <v>4900</v>
@@ -13081,10 +13081,10 @@
         <v>468</v>
       </c>
       <c r="N300" t="n">
-        <v>3795.7100076132</v>
+        <v>3795.7100076147</v>
       </c>
       <c r="O300" t="n">
-        <v>1776392.283562978</v>
+        <v>1776392.28356368</v>
       </c>
       <c r="P300" t="n">
         <v>6200</v>
@@ -13197,7 +13197,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13206,19 +13206,19 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N303" t="n">
         <v>7939.23</v>
       </c>
       <c r="O303" t="n">
-        <v>1206762.96</v>
+        <v>1198823.73</v>
       </c>
       <c r="P303" t="n">
         <v>14900</v>
       </c>
       <c r="Q303" t="n">
-        <v>2264800</v>
+        <v>2249900</v>
       </c>
     </row>
     <row r="304">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -13334,19 +13334,19 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N306" t="n">
         <v>4357.55</v>
       </c>
       <c r="O306" t="n">
-        <v>1651511.45</v>
+        <v>1642796.35</v>
       </c>
       <c r="P306" t="n">
         <v>7500</v>
       </c>
       <c r="Q306" t="n">
-        <v>2842500</v>
+        <v>2827500</v>
       </c>
     </row>
     <row r="307">
@@ -13470,10 +13470,10 @@
         <v>300</v>
       </c>
       <c r="N309" t="n">
-        <v>4890.9300507937</v>
+        <v>4890.9300509879</v>
       </c>
       <c r="O309" t="n">
-        <v>1467279.01523811</v>
+        <v>1467279.01529637</v>
       </c>
       <c r="P309" t="n">
         <v>8200</v>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -13562,19 +13562,19 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>452</v>
+        <v>392</v>
       </c>
       <c r="N311" t="n">
         <v>1203.38</v>
       </c>
       <c r="O311" t="n">
-        <v>543927.76</v>
+        <v>471724.96</v>
       </c>
       <c r="P311" t="n">
         <v>1900</v>
       </c>
       <c r="Q311" t="n">
-        <v>858800</v>
+        <v>744800</v>
       </c>
     </row>
     <row r="312">
@@ -13599,7 +13599,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13608,19 +13608,19 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N312" t="n">
         <v>3472</v>
       </c>
       <c r="O312" t="n">
-        <v>1232560</v>
+        <v>1225616</v>
       </c>
       <c r="P312" t="n">
         <v>4800</v>
       </c>
       <c r="Q312" t="n">
-        <v>1704000</v>
+        <v>1694400</v>
       </c>
     </row>
     <row r="313">
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -13961,19 +13961,19 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="N320" t="n">
         <v>5667.94</v>
       </c>
       <c r="O320" t="n">
-        <v>4228283.239999999</v>
+        <v>4222615.3</v>
       </c>
       <c r="P320" t="n">
         <v>9500</v>
       </c>
       <c r="Q320" t="n">
-        <v>7087000</v>
+        <v>7077500</v>
       </c>
     </row>
     <row r="321">
@@ -14044,7 +14044,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14053,19 +14053,19 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N322" t="n">
         <v>8662</v>
       </c>
       <c r="O322" t="n">
-        <v>181902</v>
+        <v>173240</v>
       </c>
       <c r="P322" t="n">
         <v>14200</v>
       </c>
       <c r="Q322" t="n">
-        <v>298200</v>
+        <v>284000</v>
       </c>
     </row>
     <row r="323">
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14176,19 +14176,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="N325" t="n">
         <v>1789</v>
       </c>
       <c r="O325" t="n">
-        <v>1379319</v>
+        <v>1377530</v>
       </c>
       <c r="P325" t="n">
         <v>2700</v>
       </c>
       <c r="Q325" t="n">
-        <v>2081700</v>
+        <v>2079000</v>
       </c>
     </row>
     <row r="326">
@@ -14269,10 +14269,10 @@
         <v>358</v>
       </c>
       <c r="N327" t="n">
-        <v>3594.2534111187</v>
+        <v>3594.2533147632</v>
       </c>
       <c r="O327" t="n">
-        <v>1286742.721180495</v>
+        <v>1286742.686685225</v>
       </c>
       <c r="P327" t="n">
         <v>6500</v>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -14315,19 +14315,19 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="N328" t="n">
         <v>489.88</v>
       </c>
       <c r="O328" t="n">
-        <v>202810.32</v>
+        <v>191053.2</v>
       </c>
       <c r="P328" t="n">
         <v>700</v>
       </c>
       <c r="Q328" t="n">
-        <v>289800</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="329">
@@ -14441,10 +14441,10 @@
         <v>1</v>
       </c>
       <c r="N331" t="n">
-        <v>3240.8500479616</v>
+        <v>3240.8500492611</v>
       </c>
       <c r="O331" t="n">
-        <v>3240.8500479616</v>
+        <v>3240.8500492611</v>
       </c>
       <c r="P331" t="n">
         <v>5200</v>
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -14530,19 +14530,19 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N333" t="n">
         <v>8154</v>
       </c>
       <c r="O333" t="n">
-        <v>236466</v>
+        <v>228312</v>
       </c>
       <c r="P333" t="n">
         <v>13500</v>
       </c>
       <c r="Q333" t="n">
-        <v>391500</v>
+        <v>378000</v>
       </c>
     </row>
     <row r="334">
@@ -14579,10 +14579,10 @@
         <v>285</v>
       </c>
       <c r="N334" t="n">
-        <v>14822.378829982</v>
+        <v>14822.378829268</v>
       </c>
       <c r="O334" t="n">
-        <v>4224377.96654487</v>
+        <v>4224377.96634138</v>
       </c>
       <c r="P334" t="n">
         <v>24900</v>
@@ -15619,10 +15619,10 @@
         <v>85</v>
       </c>
       <c r="N358" t="n">
-        <v>3041.66001386</v>
+        <v>3041.6600138793</v>
       </c>
       <c r="O358" t="n">
-        <v>258541.1011781</v>
+        <v>258541.1011797405</v>
       </c>
       <c r="P358" t="n">
         <v>5500</v>
@@ -15706,10 +15706,10 @@
         <v>8119</v>
       </c>
       <c r="N360" t="n">
-        <v>4371.171261065</v>
+        <v>4371.1712612367</v>
       </c>
       <c r="O360" t="n">
-        <v>35489539.46858674</v>
+        <v>35489539.46998077</v>
       </c>
       <c r="P360" t="n">
         <v>8900</v>
@@ -15866,7 +15866,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -15875,19 +15875,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="N364" t="n">
-        <v>1592.5656302521</v>
+        <v>1592.5655172414</v>
       </c>
       <c r="O364" t="n">
-        <v>528731.7892436972</v>
+        <v>509620.965517248</v>
       </c>
       <c r="P364" t="n">
         <v>3900</v>
       </c>
       <c r="Q364" t="n">
-        <v>1294800</v>
+        <v>1248000</v>
       </c>
     </row>
     <row r="365">
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16691,19 +16691,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="N383" t="n">
         <v>1343.77</v>
       </c>
       <c r="O383" t="n">
-        <v>221722.05</v>
+        <v>217690.74</v>
       </c>
       <c r="P383" t="n">
         <v>2500</v>
       </c>
       <c r="Q383" t="n">
-        <v>412500</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="384">
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
@@ -16999,19 +16999,19 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N390" t="n">
         <v>13304.13</v>
       </c>
       <c r="O390" t="n">
-        <v>1809361.68</v>
+        <v>1782753.42</v>
       </c>
       <c r="P390" t="n">
         <v>20900</v>
       </c>
       <c r="Q390" t="n">
-        <v>2842400</v>
+        <v>2800600</v>
       </c>
     </row>
     <row r="391">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17048,19 +17048,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N391" t="n">
         <v>16897</v>
       </c>
       <c r="O391" t="n">
-        <v>878644</v>
+        <v>861747</v>
       </c>
       <c r="P391" t="n">
         <v>27900</v>
       </c>
       <c r="Q391" t="n">
-        <v>1450800</v>
+        <v>1422900</v>
       </c>
     </row>
     <row r="392">
@@ -18184,7 +18184,7 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
@@ -18193,19 +18193,19 @@
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="N417" t="n">
-        <v>1630.9241816204</v>
+        <v>1630.9242252747</v>
       </c>
       <c r="O417" t="n">
-        <v>334339.457232182</v>
+        <v>306613.7543516436</v>
       </c>
       <c r="P417" t="n">
         <v>2500</v>
       </c>
       <c r="Q417" t="n">
-        <v>512500</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="418">
@@ -18276,7 +18276,7 @@
         </is>
       </c>
       <c r="J419" t="n">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -18285,19 +18285,19 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="N419" t="n">
-        <v>1550.1943423824</v>
+        <v>1550.1943880809</v>
       </c>
       <c r="O419" t="n">
-        <v>570471.5179967232</v>
+        <v>539467.6470521531</v>
       </c>
       <c r="P419" t="n">
         <v>2500</v>
       </c>
       <c r="Q419" t="n">
-        <v>920000</v>
+        <v>870000</v>
       </c>
     </row>
     <row r="420">
@@ -18322,7 +18322,7 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -18331,19 +18331,19 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="N420" t="n">
-        <v>1579.3866044776</v>
+        <v>1579.3858102767</v>
       </c>
       <c r="O420" t="n">
-        <v>94763.196268656</v>
+        <v>82128.06213438841</v>
       </c>
       <c r="P420" t="n">
         <v>2900</v>
       </c>
       <c r="Q420" t="n">
-        <v>174000</v>
+        <v>150800</v>
       </c>
     </row>
     <row r="421">
@@ -18368,7 +18368,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -18377,19 +18377,19 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>485</v>
+        <v>438</v>
       </c>
       <c r="N421" t="n">
-        <v>2403.5162209454</v>
+        <v>2403.5165803524</v>
       </c>
       <c r="O421" t="n">
-        <v>1165705.367158519</v>
+        <v>1052740.262194351</v>
       </c>
       <c r="P421" t="n">
         <v>3500</v>
       </c>
       <c r="Q421" t="n">
-        <v>1697500</v>
+        <v>1533000</v>
       </c>
     </row>
     <row r="422">
@@ -18458,7 +18458,7 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="K423" t="n">
         <v>0</v>
@@ -18467,19 +18467,19 @@
         <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="N423" t="n">
-        <v>2521.4644086022</v>
+        <v>2521.42109375</v>
       </c>
       <c r="O423" t="n">
-        <v>221888.8679569936</v>
+        <v>148763.84453125</v>
       </c>
       <c r="P423" t="n">
         <v>3900</v>
       </c>
       <c r="Q423" t="n">
-        <v>343200</v>
+        <v>230100</v>
       </c>
     </row>
     <row r="424">
@@ -18511,10 +18511,10 @@
         <v>50</v>
       </c>
       <c r="N424" t="n">
-        <v>1232.8061025641</v>
+        <v>1232.8060309278</v>
       </c>
       <c r="O424" t="n">
-        <v>61640.305128205</v>
+        <v>61640.30154639</v>
       </c>
       <c r="P424" t="n">
         <v>2400</v>
@@ -21213,7 +21213,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -21222,19 +21222,19 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N487" t="n">
         <v>8600</v>
       </c>
       <c r="O487" t="n">
-        <v>129000</v>
+        <v>111800</v>
       </c>
       <c r="P487" t="n">
         <v>14900</v>
       </c>
       <c r="Q487" t="n">
-        <v>223500</v>
+        <v>193700</v>
       </c>
     </row>
     <row r="488">
@@ -21610,7 +21610,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -21619,19 +21619,19 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N496" t="n">
         <v>9338</v>
       </c>
       <c r="O496" t="n">
-        <v>270802</v>
+        <v>252126</v>
       </c>
       <c r="P496" t="n">
         <v>15500</v>
       </c>
       <c r="Q496" t="n">
-        <v>449500</v>
+        <v>418500</v>
       </c>
     </row>
     <row r="497">
@@ -21789,10 +21789,10 @@
         <v>359</v>
       </c>
       <c r="N500" t="n">
-        <v>4196.8725410978</v>
+        <v>4196.872541806</v>
       </c>
       <c r="O500" t="n">
-        <v>1506677.24225411</v>
+        <v>1506677.242508354</v>
       </c>
       <c r="P500" t="n">
         <v>5900</v>
@@ -22362,7 +22362,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -22371,19 +22371,19 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N514" t="n">
         <v>8794.48</v>
       </c>
       <c r="O514" t="n">
-        <v>2216208.96</v>
+        <v>2207414.48</v>
       </c>
       <c r="P514" t="n">
         <v>14500</v>
       </c>
       <c r="Q514" t="n">
-        <v>3654000</v>
+        <v>3639500</v>
       </c>
     </row>
     <row r="515">
@@ -22449,7 +22449,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -22458,19 +22458,19 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="N516" t="n">
         <v>2567</v>
       </c>
       <c r="O516" t="n">
-        <v>926687</v>
+        <v>895883</v>
       </c>
       <c r="P516" t="n">
         <v>4500</v>
       </c>
       <c r="Q516" t="n">
-        <v>1624500</v>
+        <v>1570500</v>
       </c>
     </row>
     <row r="517">
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -22663,19 +22663,19 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="N521" t="n">
         <v>6652</v>
       </c>
       <c r="O521" t="n">
-        <v>4290540</v>
+        <v>4277236</v>
       </c>
       <c r="P521" t="n">
         <v>5900</v>
       </c>
       <c r="Q521" t="n">
-        <v>3805500</v>
+        <v>3793700</v>
       </c>
     </row>
     <row r="522">
@@ -22874,10 +22874,10 @@
         <v>197</v>
       </c>
       <c r="N526" t="n">
-        <v>2029.8740628386</v>
+        <v>2029.8740827436</v>
       </c>
       <c r="O526" t="n">
-        <v>399885.1903792042</v>
+        <v>399885.1943004892</v>
       </c>
       <c r="P526" t="n">
         <v>3600</v>
@@ -22956,10 +22956,10 @@
         <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>22485.6955</v>
+        <v>22485.695494368</v>
       </c>
       <c r="O528" t="n">
-        <v>22485.6955</v>
+        <v>22485.695494368</v>
       </c>
       <c r="P528" t="n">
         <v>36500</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -23404,19 +23404,19 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N539" t="n">
         <v>7103</v>
       </c>
       <c r="O539" t="n">
-        <v>852360</v>
+        <v>838154</v>
       </c>
       <c r="P539" t="n">
         <v>10700</v>
       </c>
       <c r="Q539" t="n">
-        <v>1284000</v>
+        <v>1262600</v>
       </c>
     </row>
     <row r="540">
@@ -24192,7 +24192,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -24201,19 +24201,19 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="N558" t="n">
         <v>2465</v>
       </c>
       <c r="O558" t="n">
-        <v>281010</v>
+        <v>263755</v>
       </c>
       <c r="P558" t="n">
         <v>3700</v>
       </c>
       <c r="Q558" t="n">
-        <v>421800</v>
+        <v>395900</v>
       </c>
     </row>
     <row r="559">
@@ -24716,10 +24716,10 @@
         <v>435</v>
       </c>
       <c r="N570" t="n">
-        <v>998.76126091703</v>
+        <v>998.76126229508</v>
       </c>
       <c r="O570" t="n">
-        <v>434461.148498908</v>
+        <v>434461.1490983598</v>
       </c>
       <c r="P570" t="n">
         <v>1600</v>
@@ -24873,7 +24873,7 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
@@ -24882,19 +24882,19 @@
         <v>0</v>
       </c>
       <c r="M574" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N574" t="n">
         <v>1589</v>
       </c>
       <c r="O574" t="n">
-        <v>23835</v>
+        <v>22246</v>
       </c>
       <c r="P574" t="n">
         <v>2700</v>
       </c>
       <c r="Q574" t="n">
-        <v>40500</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="575">
@@ -25001,7 +25001,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -25010,19 +25010,19 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="N577" t="n">
         <v>3877.89</v>
       </c>
       <c r="O577" t="n">
-        <v>1717905.27</v>
+        <v>1698515.82</v>
       </c>
       <c r="P577" t="n">
         <v>6500</v>
       </c>
       <c r="Q577" t="n">
-        <v>2879500</v>
+        <v>2847000</v>
       </c>
     </row>
     <row r="578">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="J579" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="K579" t="n">
         <v>0</v>
@@ -25100,19 +25100,19 @@
         <v>0</v>
       </c>
       <c r="M579" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N579" t="n">
-        <v>4285.1960620525</v>
+        <v>4285.1961426844</v>
       </c>
       <c r="O579" t="n">
-        <v>732768.5266109775</v>
+        <v>702772.1674002416</v>
       </c>
       <c r="P579" t="n">
         <v>6900</v>
       </c>
       <c r="Q579" t="n">
-        <v>1179900</v>
+        <v>1131600</v>
       </c>
     </row>
     <row r="580">
@@ -25386,7 +25386,7 @@
         </is>
       </c>
       <c r="J586" t="n">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="K586" t="n">
         <v>0</v>
@@ -25395,19 +25395,19 @@
         <v>0</v>
       </c>
       <c r="M586" t="n">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="N586" t="n">
         <v>1106</v>
       </c>
       <c r="O586" t="n">
-        <v>299726</v>
+        <v>287560</v>
       </c>
       <c r="P586" t="n">
         <v>2100</v>
       </c>
       <c r="Q586" t="n">
-        <v>569100</v>
+        <v>546000</v>
       </c>
     </row>
     <row r="587">
@@ -25596,7 +25596,7 @@
         </is>
       </c>
       <c r="J591" t="n">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
@@ -25605,19 +25605,19 @@
         <v>0</v>
       </c>
       <c r="M591" t="n">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N591" t="n">
-        <v>4814.2679276196</v>
+        <v>4814.2679275122</v>
       </c>
       <c r="O591" t="n">
-        <v>4400240.885844314</v>
+        <v>4395426.617818639</v>
       </c>
       <c r="P591" t="n">
         <v>9900</v>
       </c>
       <c r="Q591" t="n">
-        <v>9048600</v>
+        <v>9038700</v>
       </c>
     </row>
     <row r="592">
@@ -25990,7 +25990,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -25999,19 +25999,19 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N600" t="n">
         <v>1650</v>
       </c>
       <c r="O600" t="n">
-        <v>650100</v>
+        <v>646800</v>
       </c>
       <c r="P600" t="n">
         <v>2900</v>
       </c>
       <c r="Q600" t="n">
-        <v>1142600</v>
+        <v>1136800</v>
       </c>
     </row>
     <row r="601">
@@ -27202,7 +27202,7 @@
         </is>
       </c>
       <c r="J629" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
@@ -27211,19 +27211,19 @@
         <v>0</v>
       </c>
       <c r="M629" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N629" t="n">
         <v>4793.53</v>
       </c>
       <c r="O629" t="n">
-        <v>1648974.32</v>
+        <v>1639387.26</v>
       </c>
       <c r="P629" t="n">
         <v>7900</v>
       </c>
       <c r="Q629" t="n">
-        <v>2717600</v>
+        <v>2701800</v>
       </c>
     </row>
     <row r="630">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -27426,19 +27426,19 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N634" t="n">
         <v>22730.48</v>
       </c>
       <c r="O634" t="n">
-        <v>1068332.56</v>
+        <v>1045602.08</v>
       </c>
       <c r="P634" t="n">
         <v>36900</v>
       </c>
       <c r="Q634" t="n">
-        <v>1734300</v>
+        <v>1697400</v>
       </c>
     </row>
     <row r="635">
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -27687,19 +27687,19 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N640" t="n">
-        <v>27123.76488</v>
+        <v>27123.764869739</v>
       </c>
       <c r="O640" t="n">
-        <v>3743079.55344</v>
+        <v>3715955.787154243</v>
       </c>
       <c r="P640" t="n">
         <v>44500</v>
       </c>
       <c r="Q640" t="n">
-        <v>6141000</v>
+        <v>6096500</v>
       </c>
     </row>
     <row r="641">
@@ -28354,7 +28354,7 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
@@ -28363,19 +28363,19 @@
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N656" t="n">
-        <v>1561.0033241379</v>
+        <v>1561.0035960591</v>
       </c>
       <c r="O656" t="n">
-        <v>257565.5484827535</v>
+        <v>254443.5861576333</v>
       </c>
       <c r="P656" t="n">
         <v>2900</v>
       </c>
       <c r="Q656" t="n">
-        <v>478500</v>
+        <v>472700</v>
       </c>
     </row>
     <row r="657">
@@ -28400,7 +28400,7 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
@@ -28409,19 +28409,19 @@
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N657" t="n">
         <v>3487.53</v>
       </c>
       <c r="O657" t="n">
-        <v>76725.66</v>
+        <v>69750.60000000001</v>
       </c>
       <c r="P657" t="n">
         <v>6500</v>
       </c>
       <c r="Q657" t="n">
-        <v>143000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="658">
@@ -29083,10 +29083,10 @@
         <v>165</v>
       </c>
       <c r="N673" t="n">
-        <v>7969.9501692308</v>
+        <v>7969.950169361</v>
       </c>
       <c r="O673" t="n">
-        <v>1315041.777923082</v>
+        <v>1315041.777944565</v>
       </c>
       <c r="P673" t="n">
         <v>12900</v>
@@ -30464,7 +30464,7 @@
         </is>
       </c>
       <c r="J706" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K706" t="n">
         <v>0</v>
@@ -30473,19 +30473,19 @@
         <v>0</v>
       </c>
       <c r="M706" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N706" t="n">
-        <v>16925.135609756</v>
+        <v>16925.1355</v>
       </c>
       <c r="O706" t="n">
-        <v>372352.983414632</v>
+        <v>355427.8455</v>
       </c>
       <c r="P706" t="n">
         <v>29500</v>
       </c>
       <c r="Q706" t="n">
-        <v>649000</v>
+        <v>619500</v>
       </c>
     </row>
     <row r="707">
@@ -32179,10 +32179,10 @@
         <v>1193</v>
       </c>
       <c r="N743" t="n">
-        <v>1778.4727487406</v>
+        <v>1778.4727855775</v>
       </c>
       <c r="O743" t="n">
-        <v>2121717.989247536</v>
+        <v>2121718.033193958</v>
       </c>
       <c r="P743" t="n">
         <v>4900</v>
@@ -33785,7 +33785,7 @@
         </is>
       </c>
       <c r="J778" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="K778" t="n">
         <v>0</v>
@@ -33794,19 +33794,19 @@
         <v>0</v>
       </c>
       <c r="M778" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N778" t="n">
         <v>1550</v>
       </c>
       <c r="O778" t="n">
-        <v>91450</v>
+        <v>72850</v>
       </c>
       <c r="P778" t="n">
         <v>2500</v>
       </c>
       <c r="Q778" t="n">
-        <v>147500</v>
+        <v>117500</v>
       </c>
     </row>
     <row r="779">
@@ -34613,7 +34613,7 @@
         </is>
       </c>
       <c r="J796" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K796" t="n">
         <v>0</v>
@@ -34622,19 +34622,19 @@
         <v>0</v>
       </c>
       <c r="M796" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N796" t="n">
-        <v>2252.2977023121</v>
+        <v>2252.2978962963</v>
       </c>
       <c r="O796" t="n">
-        <v>247752.747254331</v>
+        <v>238743.5770074078</v>
       </c>
       <c r="P796" t="n">
         <v>3900</v>
       </c>
       <c r="Q796" t="n">
-        <v>429000</v>
+        <v>413400</v>
       </c>
     </row>
     <row r="797">
@@ -34858,10 +34858,10 @@
         <v>447</v>
       </c>
       <c r="N801" t="n">
-        <v>2328.1186779449</v>
+        <v>2328.1186767012</v>
       </c>
       <c r="O801" t="n">
-        <v>1040669.04904137</v>
+        <v>1040669.048485436</v>
       </c>
       <c r="P801" t="n">
         <v>4500</v>
@@ -35076,7 +35076,7 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
@@ -35085,19 +35085,19 @@
         <v>0</v>
       </c>
       <c r="M806" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N806" t="n">
         <v>3519</v>
       </c>
       <c r="O806" t="n">
-        <v>225216</v>
+        <v>218178</v>
       </c>
       <c r="P806" t="n">
         <v>5900</v>
       </c>
       <c r="Q806" t="n">
-        <v>377600</v>
+        <v>365800</v>
       </c>
     </row>
     <row r="807">
@@ -35594,10 +35594,10 @@
         <v>15</v>
       </c>
       <c r="N817" t="n">
-        <v>4907.8225098814</v>
+        <v>4907.8225298805</v>
       </c>
       <c r="O817" t="n">
-        <v>73617.337648221</v>
+        <v>73617.3379482075</v>
       </c>
       <c r="P817" t="n">
         <v>8200</v>
@@ -35870,10 +35870,10 @@
         <v>9</v>
       </c>
       <c r="N823" t="n">
-        <v>3903.7386507259</v>
+        <v>3903.7388113695</v>
       </c>
       <c r="O823" t="n">
-        <v>35133.6478565331</v>
+        <v>35133.6493023255</v>
       </c>
       <c r="P823" t="n">
         <v>7500</v>
@@ -36865,7 +36865,7 @@
         </is>
       </c>
       <c r="J845" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K845" t="n">
         <v>0</v>
@@ -36874,19 +36874,19 @@
         <v>0</v>
       </c>
       <c r="M845" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N845" t="n">
         <v>5682</v>
       </c>
       <c r="O845" t="n">
-        <v>369330</v>
+        <v>363648</v>
       </c>
       <c r="P845" t="n">
         <v>9900</v>
       </c>
       <c r="Q845" t="n">
-        <v>643500</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="846">
@@ -37458,7 +37458,7 @@
         </is>
       </c>
       <c r="J858" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K858" t="n">
         <v>0</v>
@@ -37467,19 +37467,19 @@
         <v>0</v>
       </c>
       <c r="M858" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="N858" t="n">
         <v>59834</v>
       </c>
       <c r="O858" t="n">
-        <v>3350704</v>
+        <v>2393360</v>
       </c>
       <c r="P858" t="n">
         <v>7900</v>
       </c>
       <c r="Q858" t="n">
-        <v>442400</v>
+        <v>316000</v>
       </c>
     </row>
     <row r="859">
@@ -38151,7 +38151,7 @@
         </is>
       </c>
       <c r="J873" t="n">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="K873" t="n">
         <v>0</v>
@@ -38160,19 +38160,19 @@
         <v>0</v>
       </c>
       <c r="M873" t="n">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="N873" t="n">
         <v>1326</v>
       </c>
       <c r="O873" t="n">
-        <v>2203812</v>
+        <v>2198508</v>
       </c>
       <c r="P873" t="n">
         <v>2500</v>
       </c>
       <c r="Q873" t="n">
-        <v>4155000</v>
+        <v>4145000</v>
       </c>
     </row>
     <row r="874">
@@ -38381,7 +38381,7 @@
         </is>
       </c>
       <c r="J878" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K878" t="n">
         <v>0</v>
@@ -38390,19 +38390,19 @@
         <v>0</v>
       </c>
       <c r="M878" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N878" t="n">
         <v>21762</v>
       </c>
       <c r="O878" t="n">
-        <v>587574</v>
+        <v>565812</v>
       </c>
       <c r="P878" t="n">
         <v>35900</v>
       </c>
       <c r="Q878" t="n">
-        <v>969300</v>
+        <v>933400</v>
       </c>
     </row>
     <row r="879">
@@ -38427,7 +38427,7 @@
         </is>
       </c>
       <c r="J879" t="n">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="K879" t="n">
         <v>0</v>
@@ -38436,19 +38436,19 @@
         <v>0</v>
       </c>
       <c r="M879" t="n">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="N879" t="n">
         <v>3821</v>
       </c>
       <c r="O879" t="n">
-        <v>5891982</v>
+        <v>5872877</v>
       </c>
       <c r="P879" t="n">
         <v>5900</v>
       </c>
       <c r="Q879" t="n">
-        <v>9097800</v>
+        <v>9068300</v>
       </c>
     </row>
     <row r="880">
@@ -38764,10 +38764,10 @@
         <v>1272</v>
       </c>
       <c r="N886" t="n">
-        <v>1516.0387603223</v>
+        <v>1516.0387548048</v>
       </c>
       <c r="O886" t="n">
-        <v>1928401.303129966</v>
+        <v>1928401.296111705</v>
       </c>
       <c r="P886" t="n">
         <v>2300</v>
@@ -38842,7 +38842,7 @@
         </is>
       </c>
       <c r="J888" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="K888" t="n">
         <v>0</v>
@@ -38851,19 +38851,19 @@
         <v>0</v>
       </c>
       <c r="M888" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N888" t="n">
-        <v>2458.5126727464</v>
+        <v>2458.5126365879</v>
       </c>
       <c r="O888" t="n">
-        <v>619545.1935320927</v>
+        <v>604794.1086006234</v>
       </c>
       <c r="P888" t="n">
         <v>3500</v>
       </c>
       <c r="Q888" t="n">
-        <v>882000</v>
+        <v>861000</v>
       </c>
     </row>
     <row r="889">
@@ -38900,10 +38900,10 @@
         <v>5</v>
       </c>
       <c r="N889" t="n">
-        <v>1907.3927734807</v>
+        <v>1907.3927252503</v>
       </c>
       <c r="O889" t="n">
-        <v>9536.9638674035</v>
+        <v>9536.9636262515</v>
       </c>
       <c r="P889" t="n">
         <v>2500</v>
@@ -38946,10 +38946,10 @@
         <v>82</v>
       </c>
       <c r="N890" t="n">
-        <v>1771.0894683176</v>
+        <v>1771.0894375457</v>
       </c>
       <c r="O890" t="n">
-        <v>145229.3364020432</v>
+        <v>145229.3338787474</v>
       </c>
       <c r="P890" t="n">
         <v>2500</v>
@@ -38992,10 +38992,10 @@
         <v>194</v>
       </c>
       <c r="N891" t="n">
-        <v>2079.383486674</v>
+        <v>2079.3834819145</v>
       </c>
       <c r="O891" t="n">
-        <v>403400.396414756</v>
+        <v>403400.395491413</v>
       </c>
       <c r="P891" t="n">
         <v>2900</v>
@@ -39026,7 +39026,7 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
@@ -39035,19 +39035,19 @@
         <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N892" t="n">
-        <v>1803.0162940958</v>
+        <v>1803.0163011152</v>
       </c>
       <c r="O892" t="n">
-        <v>506647.5786409198</v>
+        <v>504844.5643122559</v>
       </c>
       <c r="P892" t="n">
         <v>2500</v>
       </c>
       <c r="Q892" t="n">
-        <v>702500</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="893">
@@ -39084,10 +39084,10 @@
         <v>88</v>
       </c>
       <c r="N893" t="n">
-        <v>3306.5944785276</v>
+        <v>3306.5944700461</v>
       </c>
       <c r="O893" t="n">
-        <v>290980.3141104288</v>
+        <v>290980.3133640568</v>
       </c>
       <c r="P893" t="n">
         <v>4900</v>
@@ -39118,7 +39118,7 @@
         </is>
       </c>
       <c r="J894" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
@@ -39127,19 +39127,19 @@
         <v>0</v>
       </c>
       <c r="M894" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N894" t="n">
-        <v>2108.7954376658</v>
+        <v>2108.7956032172</v>
       </c>
       <c r="O894" t="n">
-        <v>44284.7041909818</v>
+        <v>35849.5252546924</v>
       </c>
       <c r="P894" t="n">
         <v>2900</v>
       </c>
       <c r="Q894" t="n">
-        <v>60900</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="895">
@@ -39164,7 +39164,7 @@
         </is>
       </c>
       <c r="J895" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K895" t="n">
         <v>0</v>
@@ -39173,19 +39173,19 @@
         <v>0</v>
       </c>
       <c r="M895" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N895" t="n">
-        <v>2056.0823949889</v>
+        <v>2056.0823271375</v>
       </c>
       <c r="O895" t="n">
-        <v>468786.7860574692</v>
+        <v>464674.6059330751</v>
       </c>
       <c r="P895" t="n">
         <v>2900</v>
       </c>
       <c r="Q895" t="n">
-        <v>661200</v>
+        <v>655400</v>
       </c>
     </row>
     <row r="896">
@@ -39222,10 +39222,10 @@
         <v>138</v>
       </c>
       <c r="N896" t="n">
-        <v>3224.5693375065</v>
+        <v>3224.5693668237</v>
       </c>
       <c r="O896" t="n">
-        <v>444990.568575897</v>
+        <v>444990.5726216706</v>
       </c>
       <c r="P896" t="n">
         <v>4500</v>
@@ -39268,10 +39268,10 @@
         <v>202</v>
       </c>
       <c r="N897" t="n">
-        <v>1655.9297403561</v>
+        <v>1655.9297327394</v>
       </c>
       <c r="O897" t="n">
-        <v>334497.8075519322</v>
+        <v>334497.8060133588</v>
       </c>
       <c r="P897" t="n">
         <v>2500</v>
@@ -39397,7 +39397,7 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
@@ -39406,19 +39406,19 @@
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N900" t="n">
         <v>1662</v>
       </c>
       <c r="O900" t="n">
-        <v>320766</v>
+        <v>319104</v>
       </c>
       <c r="P900" t="n">
         <v>2900</v>
       </c>
       <c r="Q900" t="n">
-        <v>559700</v>
+        <v>556800</v>
       </c>
     </row>
     <row r="901">
@@ -39443,7 +39443,7 @@
         </is>
       </c>
       <c r="J901" t="n">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="K901" t="n">
         <v>0</v>
@@ -39452,19 +39452,19 @@
         <v>0</v>
       </c>
       <c r="M901" t="n">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="N901" t="n">
         <v>2454</v>
       </c>
       <c r="O901" t="n">
-        <v>1938660</v>
+        <v>1923936</v>
       </c>
       <c r="P901" t="n">
         <v>4200</v>
       </c>
       <c r="Q901" t="n">
-        <v>3318000</v>
+        <v>3292800</v>
       </c>
     </row>
     <row r="902">
@@ -39632,10 +39632,10 @@
         <v>184</v>
       </c>
       <c r="N905" t="n">
-        <v>2311.89640625</v>
+        <v>2311.8945108696</v>
       </c>
       <c r="O905" t="n">
-        <v>425388.93875</v>
+        <v>425388.5900000064</v>
       </c>
       <c r="P905" t="n">
         <v>3500</v>
@@ -39666,7 +39666,7 @@
         </is>
       </c>
       <c r="J906" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K906" t="n">
         <v>0</v>
@@ -39675,19 +39675,19 @@
         <v>0</v>
       </c>
       <c r="M906" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="N906" t="n">
-        <v>1906.1797260274</v>
+        <v>1906.1790510949</v>
       </c>
       <c r="O906" t="n">
-        <v>232553.9265753428</v>
+        <v>217304.4118248186</v>
       </c>
       <c r="P906" t="n">
         <v>2900</v>
       </c>
       <c r="Q906" t="n">
-        <v>353800</v>
+        <v>330600</v>
       </c>
     </row>
     <row r="907">
@@ -39712,7 +39712,7 @@
         </is>
       </c>
       <c r="J907" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="K907" t="n">
         <v>0</v>
@@ -39721,19 +39721,19 @@
         <v>0</v>
       </c>
       <c r="M907" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N907" t="n">
-        <v>3033.6979775281</v>
+        <v>3033.6928395062</v>
       </c>
       <c r="O907" t="n">
-        <v>497526.4683146084</v>
+        <v>448986.5402469176</v>
       </c>
       <c r="P907" t="n">
         <v>4500</v>
       </c>
       <c r="Q907" t="n">
-        <v>738000</v>
+        <v>666000</v>
       </c>
     </row>
     <row r="908">
@@ -39816,10 +39816,10 @@
         <v>123</v>
       </c>
       <c r="N909" t="n">
-        <v>2546.9822404372</v>
+        <v>2546.982132964</v>
       </c>
       <c r="O909" t="n">
-        <v>313278.8155737756</v>
+        <v>313278.802354572</v>
       </c>
       <c r="P909" t="n">
         <v>3900</v>
@@ -39850,7 +39850,7 @@
         </is>
       </c>
       <c r="J910" t="n">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="K910" t="n">
         <v>0</v>
@@ -39859,19 +39859,19 @@
         <v>0</v>
       </c>
       <c r="M910" t="n">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="N910" t="n">
-        <v>1259.2747095871</v>
+        <v>1259.2747272302</v>
       </c>
       <c r="O910" t="n">
-        <v>1353720.312806132</v>
+        <v>1347423.958136314</v>
       </c>
       <c r="P910" t="n">
         <v>1900</v>
       </c>
       <c r="Q910" t="n">
-        <v>2042500</v>
+        <v>2033000</v>
       </c>
     </row>
     <row r="911">
@@ -39949,10 +39949,10 @@
         <v>20</v>
       </c>
       <c r="N912" t="n">
-        <v>2842.2744146685</v>
+        <v>2842.2744067797</v>
       </c>
       <c r="O912" t="n">
-        <v>56845.48829337</v>
+        <v>56845.48813559399</v>
       </c>
       <c r="P912" t="n">
         <v>4900</v>
@@ -40073,7 +40073,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>2494</v>
+        <v>2458</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40082,19 +40082,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>2494</v>
+        <v>2458</v>
       </c>
       <c r="N915" t="n">
-        <v>692.15238407171</v>
+        <v>692.1524039631501</v>
       </c>
       <c r="O915" t="n">
-        <v>1726228.045874845</v>
+        <v>1701310.608941423</v>
       </c>
       <c r="P915" t="n">
         <v>1200</v>
       </c>
       <c r="Q915" t="n">
-        <v>2992800</v>
+        <v>2949600</v>
       </c>
     </row>
     <row r="916">
@@ -40270,10 +40270,10 @@
         <v>570</v>
       </c>
       <c r="N919" t="n">
-        <v>1185.3195700703</v>
+        <v>1185.319565762</v>
       </c>
       <c r="O919" t="n">
-        <v>675632.1549400709</v>
+        <v>675632.1524843399</v>
       </c>
       <c r="P919" t="n">
         <v>1900</v>
@@ -40356,7 +40356,7 @@
         </is>
       </c>
       <c r="J921" t="n">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="K921" t="n">
         <v>0</v>
@@ -40365,19 +40365,19 @@
         <v>0</v>
       </c>
       <c r="M921" t="n">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N921" t="n">
         <v>13518</v>
       </c>
       <c r="O921" t="n">
-        <v>8110800</v>
+        <v>8083764</v>
       </c>
       <c r="P921" t="n">
         <v>21900</v>
       </c>
       <c r="Q921" t="n">
-        <v>13140000</v>
+        <v>13096200</v>
       </c>
     </row>
     <row r="922">
@@ -40974,7 +40974,7 @@
         </is>
       </c>
       <c r="J934" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K934" t="n">
         <v>0</v>
@@ -40983,19 +40983,19 @@
         <v>0</v>
       </c>
       <c r="M934" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="N934" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O934" t="n">
-        <v>3193500.66</v>
+        <v>3175609.9</v>
       </c>
       <c r="P934" t="n">
         <v>14900</v>
       </c>
       <c r="Q934" t="n">
-        <v>5319300</v>
+        <v>5289500</v>
       </c>
     </row>
     <row r="935">
@@ -41902,10 +41902,10 @@
         <v>351</v>
       </c>
       <c r="N954" t="n">
-        <v>2286.1616470588</v>
+        <v>2286.1645384615</v>
       </c>
       <c r="O954" t="n">
-        <v>802442.7381176389</v>
+        <v>802443.7529999864</v>
       </c>
       <c r="P954" t="n">
         <v>3000</v>
@@ -42410,7 +42410,7 @@
         </is>
       </c>
       <c r="J966" t="n">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="K966" t="n">
         <v>0</v>
@@ -42419,19 +42419,19 @@
         <v>0</v>
       </c>
       <c r="M966" t="n">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="N966" t="n">
-        <v>517.29385463984</v>
+        <v>517.2940518305199</v>
       </c>
       <c r="O966" t="n">
-        <v>436596.013316025</v>
+        <v>435044.2975894673</v>
       </c>
       <c r="P966" t="n">
         <v>900</v>
       </c>
       <c r="Q966" t="n">
-        <v>759600</v>
+        <v>756900</v>
       </c>
     </row>
     <row r="967">
@@ -42607,10 +42607,10 @@
         <v>1189</v>
       </c>
       <c r="N970" t="n">
-        <v>3110.8392324094</v>
+        <v>3110.8390217391</v>
       </c>
       <c r="O970" t="n">
-        <v>3698787.847334777</v>
+        <v>3698787.59684779</v>
       </c>
       <c r="P970" t="n">
         <v>4500</v>
@@ -42727,7 +42727,7 @@
         </is>
       </c>
       <c r="J973" t="n">
-        <v>13227</v>
+        <v>13203</v>
       </c>
       <c r="K973" t="n">
         <v>0</v>
@@ -42736,19 +42736,19 @@
         <v>0</v>
       </c>
       <c r="M973" t="n">
-        <v>13227</v>
+        <v>13203</v>
       </c>
       <c r="N973" t="n">
-        <v>703.79485280542</v>
+        <v>703.79483731577</v>
       </c>
       <c r="O973" t="n">
-        <v>9309094.51805729</v>
+        <v>9292203.237080112</v>
       </c>
       <c r="P973" t="n">
         <v>900</v>
       </c>
       <c r="Q973" t="n">
-        <v>11904300</v>
+        <v>11882700</v>
       </c>
     </row>
     <row r="974">
@@ -43225,10 +43225,10 @@
         <v>415</v>
       </c>
       <c r="N984" t="n">
-        <v>2077.4947511312</v>
+        <v>2077.4947583082</v>
       </c>
       <c r="O984" t="n">
-        <v>862160.321719448</v>
+        <v>862160.3246979029</v>
       </c>
       <c r="P984" t="n">
         <v>2900</v>
@@ -43482,10 +43482,10 @@
         <v>81</v>
       </c>
       <c r="N990" t="n">
-        <v>1595.4997222222</v>
+        <v>1595.4994469697</v>
       </c>
       <c r="O990" t="n">
-        <v>129235.4774999982</v>
+        <v>129235.4552045457</v>
       </c>
       <c r="P990" t="n">
         <v>2500</v>
@@ -44461,7 +44461,7 @@
         </is>
       </c>
       <c r="J1011" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K1011" t="n">
         <v>0</v>
@@ -44470,19 +44470,19 @@
         <v>0</v>
       </c>
       <c r="M1011" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N1011" t="n">
         <v>2672.89</v>
       </c>
       <c r="O1011" t="n">
-        <v>160373.4</v>
+        <v>157700.51</v>
       </c>
       <c r="P1011" t="n">
         <v>10200</v>
       </c>
       <c r="Q1011" t="n">
-        <v>612000</v>
+        <v>601800</v>
       </c>
     </row>
     <row r="1012">
@@ -47102,10 +47102,10 @@
         <v>24</v>
       </c>
       <c r="N1067" t="n">
-        <v>44113.604387097</v>
+        <v>44113.604121212</v>
       </c>
       <c r="O1067" t="n">
-        <v>1058726.505290328</v>
+        <v>1058726.498909088</v>
       </c>
       <c r="P1067" t="n">
         <v>71900</v>
@@ -47151,10 +47151,10 @@
         <v>16</v>
       </c>
       <c r="N1068" t="n">
-        <v>665.32380905991</v>
+        <v>665.3238408644399</v>
       </c>
       <c r="O1068" t="n">
-        <v>10645.18094495856</v>
+        <v>10645.18145383104</v>
       </c>
       <c r="P1068" t="n">
         <v>2900</v>
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="J1074" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K1074" t="n">
         <v>0</v>
@@ -47434,19 +47434,19 @@
         <v>0</v>
       </c>
       <c r="M1074" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N1074" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1074" t="n">
-        <v>1140878.16</v>
+        <v>1136296.32</v>
       </c>
       <c r="P1074" t="n">
         <v>7900</v>
       </c>
       <c r="Q1074" t="n">
-        <v>1967100</v>
+        <v>1959200</v>
       </c>
     </row>
     <row r="1075">
@@ -47474,7 +47474,7 @@
         </is>
       </c>
       <c r="J1075" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K1075" t="n">
         <v>0</v>
@@ -47483,19 +47483,19 @@
         <v>0</v>
       </c>
       <c r="M1075" t="n">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N1075" t="n">
         <v>3155</v>
       </c>
       <c r="O1075" t="n">
-        <v>1142110</v>
+        <v>1129490</v>
       </c>
       <c r="P1075" t="n">
         <v>5900</v>
       </c>
       <c r="Q1075" t="n">
-        <v>2135800</v>
+        <v>2112200</v>
       </c>
     </row>
     <row r="1076">
@@ -48855,7 +48855,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>1438</v>
+        <v>1398</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -48864,19 +48864,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>1438</v>
+        <v>1398</v>
       </c>
       <c r="N1107" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1107" t="n">
-        <v>1691907.66</v>
+        <v>1644844.86</v>
       </c>
       <c r="P1107" t="n">
         <v>1900</v>
       </c>
       <c r="Q1107" t="n">
-        <v>2732200</v>
+        <v>2656200</v>
       </c>
     </row>
     <row r="1108">
@@ -48943,7 +48943,7 @@
         </is>
       </c>
       <c r="J1109" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1109" t="n">
         <v>0</v>
@@ -48952,19 +48952,19 @@
         <v>0</v>
       </c>
       <c r="M1109" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1109" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1109" t="n">
-        <v>130457.9</v>
+        <v>127276</v>
       </c>
       <c r="P1109" t="n">
         <v>5100</v>
       </c>
       <c r="Q1109" t="n">
-        <v>209100</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="1110">
@@ -49811,7 +49811,7 @@
         </is>
       </c>
       <c r="J1129" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K1129" t="n">
         <v>0</v>
@@ -49820,19 +49820,19 @@
         <v>0</v>
       </c>
       <c r="M1129" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N1129" t="n">
-        <v>3683.6327400468</v>
+        <v>3683.6327464789</v>
       </c>
       <c r="O1129" t="n">
-        <v>1186129.74229507</v>
+        <v>1182446.111619727</v>
       </c>
       <c r="P1129" t="n">
         <v>3600</v>
       </c>
       <c r="Q1129" t="n">
-        <v>1159200</v>
+        <v>1155600</v>
       </c>
     </row>
     <row r="1130">
@@ -49910,10 +49910,10 @@
         <v>378</v>
       </c>
       <c r="N1131" t="n">
-        <v>22951.70473822</v>
+        <v>22951.704717477</v>
       </c>
       <c r="O1131" t="n">
-        <v>8675744.391047159</v>
+        <v>8675744.383206306</v>
       </c>
       <c r="P1131" t="n">
         <v>37900</v>
@@ -50138,10 +50138,10 @@
         <v>1</v>
       </c>
       <c r="N1136" t="n">
-        <v>1757.3206175772</v>
+        <v>1757.3206205251</v>
       </c>
       <c r="O1136" t="n">
-        <v>1757.3206175772</v>
+        <v>1757.3206205251</v>
       </c>
       <c r="P1136" t="n">
         <v>2000</v>
@@ -51216,7 +51216,7 @@
         </is>
       </c>
       <c r="J1160" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="K1160" t="n">
         <v>0</v>
@@ -51225,19 +51225,19 @@
         <v>0</v>
       </c>
       <c r="M1160" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="N1160" t="n">
         <v>3872</v>
       </c>
       <c r="O1160" t="n">
-        <v>255552</v>
+        <v>147136</v>
       </c>
       <c r="P1160" t="n">
         <v>4900</v>
       </c>
       <c r="Q1160" t="n">
-        <v>323400</v>
+        <v>186200</v>
       </c>
     </row>
     <row r="1161">
@@ -51262,7 +51262,7 @@
         </is>
       </c>
       <c r="J1161" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K1161" t="n">
         <v>0</v>
@@ -51271,19 +51271,19 @@
         <v>0</v>
       </c>
       <c r="M1161" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N1161" t="n">
         <v>4400</v>
       </c>
       <c r="O1161" t="n">
-        <v>162800</v>
+        <v>101200</v>
       </c>
       <c r="P1161" t="n">
         <v>5900</v>
       </c>
       <c r="Q1161" t="n">
-        <v>218300</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="1162">
@@ -51308,7 +51308,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51317,19 +51317,19 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N1162" t="n">
         <v>6160</v>
       </c>
       <c r="O1162" t="n">
-        <v>1503040</v>
+        <v>1484560</v>
       </c>
       <c r="P1162" t="n">
         <v>7500</v>
       </c>
       <c r="Q1162" t="n">
-        <v>1830000</v>
+        <v>1807500</v>
       </c>
     </row>
     <row r="1163">
@@ -51538,7 +51538,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51547,19 +51547,19 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N1167" t="n">
         <v>4576</v>
       </c>
       <c r="O1167" t="n">
-        <v>576576</v>
+        <v>567424</v>
       </c>
       <c r="P1167" t="n">
         <v>5900</v>
       </c>
       <c r="Q1167" t="n">
-        <v>743400</v>
+        <v>731600</v>
       </c>
     </row>
     <row r="1168">
@@ -52729,7 +52729,7 @@
         </is>
       </c>
       <c r="J1193" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K1193" t="n">
         <v>0</v>
@@ -52738,19 +52738,19 @@
         <v>0</v>
       </c>
       <c r="M1193" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N1193" t="n">
         <v>6500</v>
       </c>
       <c r="O1193" t="n">
-        <v>97500</v>
+        <v>91000</v>
       </c>
       <c r="P1193" t="n">
         <v>7800</v>
       </c>
       <c r="Q1193" t="n">
-        <v>117000</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="1194">
@@ -52787,10 +52787,10 @@
         <v>1</v>
       </c>
       <c r="N1194" t="n">
-        <v>970.63461538462</v>
+        <v>970.635</v>
       </c>
       <c r="O1194" t="n">
-        <v>970.63461538462</v>
+        <v>970.635</v>
       </c>
       <c r="P1194" t="n">
         <v>7200</v>
@@ -53207,7 +53207,7 @@
         </is>
       </c>
       <c r="J1203" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="K1203" t="n">
         <v>0</v>
@@ -53216,19 +53216,19 @@
         <v>0</v>
       </c>
       <c r="M1203" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="N1203" t="n">
-        <v>2539.5716651076</v>
+        <v>2539.5716920152</v>
       </c>
       <c r="O1203" t="n">
-        <v>675526.0629186216</v>
+        <v>632353.3513117848</v>
       </c>
       <c r="P1203" t="n">
         <v>2900</v>
       </c>
       <c r="Q1203" t="n">
-        <v>771400</v>
+        <v>722100</v>
       </c>
     </row>
     <row r="1204">
@@ -53253,7 +53253,7 @@
         </is>
       </c>
       <c r="J1204" t="n">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="K1204" t="n">
         <v>0</v>
@@ -53262,19 +53262,19 @@
         <v>0</v>
       </c>
       <c r="M1204" t="n">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="N1204" t="n">
-        <v>4687.9745841035</v>
+        <v>4687.9746311858</v>
       </c>
       <c r="O1204" t="n">
-        <v>2348675.266635853</v>
+        <v>2297107.569281042</v>
       </c>
       <c r="P1204" t="n">
         <v>5500</v>
       </c>
       <c r="Q1204" t="n">
-        <v>2755500</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="1205">
@@ -53299,7 +53299,7 @@
         </is>
       </c>
       <c r="J1205" t="n">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="K1205" t="n">
         <v>0</v>
@@ -53308,19 +53308,19 @@
         <v>0</v>
       </c>
       <c r="M1205" t="n">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="N1205" t="n">
-        <v>4171.6686137441</v>
+        <v>4171.6685988024</v>
       </c>
       <c r="O1205" t="n">
-        <v>2519687.842701436</v>
+        <v>2482142.816287428</v>
       </c>
       <c r="P1205" t="n">
         <v>5000</v>
       </c>
       <c r="Q1205" t="n">
-        <v>3020000</v>
+        <v>2975000</v>
       </c>
     </row>
     <row r="1206">
